--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="450">
   <si>
     <t>trade_time</t>
   </si>
@@ -1362,6 +1362,9 @@
   <si>
     <t>2021-08-23</t>
   </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
 </sst>
 </file>
 
@@ -1718,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P984"/>
+  <dimension ref="A1:P985"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -50918,6 +50921,56 @@
         <v>448</v>
       </c>
     </row>
+    <row r="985" spans="1:16">
+      <c r="A985" s="1">
+        <v>0</v>
+      </c>
+      <c r="B985" t="s">
+        <v>189</v>
+      </c>
+      <c r="C985">
+        <v>0.5600712707795941</v>
+      </c>
+      <c r="D985" t="s">
+        <v>339</v>
+      </c>
+      <c r="E985">
+        <v>1.088924749687181</v>
+      </c>
+      <c r="F985">
+        <v>1</v>
+      </c>
+      <c r="G985">
+        <v>0.01573992872922041</v>
+      </c>
+      <c r="H985">
+        <v>0.01667107525031282</v>
+      </c>
+      <c r="I985">
+        <v>0.5288534789075872</v>
+      </c>
+      <c r="J985">
+        <v>1.340976807282757</v>
+      </c>
+      <c r="K985">
+        <v>5.66</v>
+      </c>
+      <c r="L985">
+        <v>8.15</v>
+      </c>
+      <c r="M985">
+        <v>5.81</v>
+      </c>
+      <c r="N985">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="O985">
+        <v>1</v>
+      </c>
+      <c r="P985" t="s">
+        <v>449</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="452">
   <si>
     <t>trade_time</t>
   </si>
@@ -586,7 +586,7 @@
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-08</t>
+    <t>2021-09-09</t>
   </si>
   <si>
     <t>2016-11-30</t>
@@ -1039,7 +1039,7 @@
     <t>2021-09-07</t>
   </si>
   <si>
-    <t>2021-09-09</t>
+    <t>2021-09-13</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1727,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P986"/>
+  <dimension ref="A1:P987"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -50935,40 +50935,40 @@
         <v>190</v>
       </c>
       <c r="C985">
-        <v>1.267644967891206</v>
+        <v>1.478357895886811</v>
       </c>
       <c r="D985" t="s">
         <v>341</v>
       </c>
       <c r="E985">
-        <v>1.478357895886811</v>
+        <v>1.112107103884245</v>
       </c>
       <c r="F985">
         <v>-1</v>
       </c>
       <c r="G985">
-        <v>0.0170723550321088</v>
+        <v>0.01792164210411319</v>
       </c>
       <c r="H985">
-        <v>0.01792164210411319</v>
+        <v>0.01792789289611576</v>
       </c>
       <c r="I985">
-        <v>-0.2107129279956048</v>
+        <v>0.3662507920025657</v>
       </c>
       <c r="J985">
         <v>1.330362800018315</v>
       </c>
       <c r="K985">
-        <v>5.94</v>
+        <v>6.18</v>
       </c>
       <c r="L985">
-        <v>9.17</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M985">
-        <v>6.18</v>
+        <v>6.32</v>
       </c>
       <c r="N985">
-        <v>9.699999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="O985">
         <v>1</v>
@@ -51024,6 +51024,56 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="987" spans="1:16">
+      <c r="A987" s="1">
+        <v>1</v>
+      </c>
+      <c r="B987" t="s">
+        <v>190</v>
+      </c>
+      <c r="C987">
+        <v>1.41276333099256</v>
+      </c>
+      <c r="D987" t="s">
+        <v>341</v>
+      </c>
+      <c r="E987">
+        <v>1.045026577972973</v>
+      </c>
+      <c r="F987">
+        <v>-1</v>
+      </c>
+      <c r="G987">
+        <v>0.01798723666900744</v>
+      </c>
+      <c r="H987">
+        <v>0.01799497342202703</v>
+      </c>
+      <c r="I987">
+        <v>0.367736753019587</v>
+      </c>
+      <c r="J987">
+        <v>1.340976807282757</v>
+      </c>
+      <c r="K987">
+        <v>6.18</v>
+      </c>
+      <c r="L987">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M987">
+        <v>6.32</v>
+      </c>
+      <c r="N987">
+        <v>9.52</v>
+      </c>
+      <c r="O987">
+        <v>1</v>
+      </c>
+      <c r="P987" t="s">
         <v>451</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -1039,7 +1039,7 @@
     <t>2021-09-07</t>
   </si>
   <si>
-    <t>2021-09-13</t>
+    <t>2021-09-14</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -50941,7 +50941,7 @@
         <v>341</v>
       </c>
       <c r="E985">
-        <v>1.112107103884245</v>
+        <v>1.02817966388791</v>
       </c>
       <c r="F985">
         <v>-1</v>
@@ -50950,10 +50950,10 @@
         <v>0.01792164210411319</v>
       </c>
       <c r="H985">
-        <v>0.01792789289611576</v>
+        <v>0.01731182033611209</v>
       </c>
       <c r="I985">
-        <v>0.3662507920025657</v>
+        <v>0.4501782319989012</v>
       </c>
       <c r="J985">
         <v>1.330362800018315</v>
@@ -50965,10 +50965,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M985">
-        <v>6.32</v>
+        <v>6.12</v>
       </c>
       <c r="N985">
-        <v>9.52</v>
+        <v>9.17</v>
       </c>
       <c r="O985">
         <v>1</v>
@@ -51041,7 +51041,7 @@
         <v>341</v>
       </c>
       <c r="E987">
-        <v>1.045026577972973</v>
+        <v>0.9632219394295252</v>
       </c>
       <c r="F987">
         <v>-1</v>
@@ -51050,10 +51050,10 @@
         <v>0.01798723666900744</v>
       </c>
       <c r="H987">
-        <v>0.01799497342202703</v>
+        <v>0.01737677806057047</v>
       </c>
       <c r="I987">
-        <v>0.367736753019587</v>
+        <v>0.4495413915630344</v>
       </c>
       <c r="J987">
         <v>1.340976807282757</v>
@@ -51065,10 +51065,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M987">
-        <v>6.32</v>
+        <v>6.12</v>
       </c>
       <c r="N987">
-        <v>9.52</v>
+        <v>9.17</v>
       </c>
       <c r="O987">
         <v>1</v>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2979" uniqueCount="454">
   <si>
     <t>trade_time</t>
   </si>
@@ -586,10 +586,10 @@
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-08</t>
+    <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-09</t>
+    <t>2021-09-14</t>
   </si>
   <si>
     <t>2016-11-30</t>
@@ -1042,7 +1042,7 @@
     <t>2021-09-07</t>
   </si>
   <si>
-    <t>2021-09-14</t>
+    <t>2021-09-16</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1373,6 +1373,9 @@
   </si>
   <si>
     <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
   </si>
 </sst>
 </file>
@@ -1730,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P987"/>
+  <dimension ref="A1:P989"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -50938,10 +50941,10 @@
         <v>190</v>
       </c>
       <c r="C985">
-        <v>1.267644967891206</v>
+        <v>1.478357895886811</v>
       </c>
       <c r="D985" t="s">
-        <v>342</v>
+        <v>191</v>
       </c>
       <c r="E985">
         <v>1.02817966388791</v>
@@ -50950,22 +50953,22 @@
         <v>-1</v>
       </c>
       <c r="G985">
-        <v>0.0170723550321088</v>
+        <v>0.01792164210411319</v>
       </c>
       <c r="H985">
         <v>0.01731182033611209</v>
       </c>
       <c r="I985">
-        <v>0.2394653040032964</v>
+        <v>0.4501782319989012</v>
       </c>
       <c r="J985">
         <v>1.330362800018315</v>
       </c>
       <c r="K985">
-        <v>5.94</v>
+        <v>6.18</v>
       </c>
       <c r="L985">
-        <v>9.17</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M985">
         <v>6.12</v>
@@ -51035,13 +51038,13 @@
         <v>1</v>
       </c>
       <c r="B987" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C987">
         <v>1.41276333099256</v>
       </c>
       <c r="D987" t="s">
-        <v>342</v>
+        <v>191</v>
       </c>
       <c r="E987">
         <v>0.9632219394295252</v>
@@ -51078,6 +51081,106 @@
       </c>
       <c r="P987" t="s">
         <v>452</v>
+      </c>
+    </row>
+    <row r="988" spans="1:16">
+      <c r="A988" s="1">
+        <v>0</v>
+      </c>
+      <c r="B988" t="s">
+        <v>191</v>
+      </c>
+      <c r="C988">
+        <v>0.9880706777811863</v>
+      </c>
+      <c r="D988" t="s">
+        <v>342</v>
+      </c>
+      <c r="E988">
+        <v>1.280794863275108</v>
+      </c>
+      <c r="F988">
+        <v>1</v>
+      </c>
+      <c r="G988">
+        <v>0.01735192932221882</v>
+      </c>
+      <c r="H988">
+        <v>0.01809920513672489</v>
+      </c>
+      <c r="I988">
+        <v>0.2927241854939222</v>
+      </c>
+      <c r="J988">
+        <v>1.336916555918107</v>
+      </c>
+      <c r="K988">
+        <v>6.12</v>
+      </c>
+      <c r="L988">
+        <v>9.17</v>
+      </c>
+      <c r="M988">
+        <v>6.29</v>
+      </c>
+      <c r="N988">
+        <v>9.69</v>
+      </c>
+      <c r="O988">
+        <v>1</v>
+      </c>
+      <c r="P988" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="989" spans="1:16">
+      <c r="A989" s="1">
+        <v>0</v>
+      </c>
+      <c r="B989" t="s">
+        <v>191</v>
+      </c>
+      <c r="C989">
+        <v>0.9608966978759845</v>
+      </c>
+      <c r="D989" t="s">
+        <v>342</v>
+      </c>
+      <c r="E989">
+        <v>1.252866050594761</v>
+      </c>
+      <c r="F989">
+        <v>1</v>
+      </c>
+      <c r="G989">
+        <v>0.01737910330212402</v>
+      </c>
+      <c r="H989">
+        <v>0.01812713394940524</v>
+      </c>
+      <c r="I989">
+        <v>0.2919693527187768</v>
+      </c>
+      <c r="J989">
+        <v>1.341356748713074</v>
+      </c>
+      <c r="K989">
+        <v>6.12</v>
+      </c>
+      <c r="L989">
+        <v>9.17</v>
+      </c>
+      <c r="M989">
+        <v>6.29</v>
+      </c>
+      <c r="N989">
+        <v>9.69</v>
+      </c>
+      <c r="O989">
+        <v>1</v>
+      </c>
+      <c r="P989" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2979" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="455">
   <si>
     <t>trade_time</t>
   </si>
@@ -1377,6 +1377,9 @@
   <si>
     <t>2021-09-10</t>
   </si>
+  <si>
+    <t>2021-09-13</t>
+  </si>
 </sst>
 </file>
 
@@ -1733,7 +1736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P989"/>
+  <dimension ref="A1:P990"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51183,6 +51186,56 @@
         <v>453</v>
       </c>
     </row>
+    <row r="990" spans="1:16">
+      <c r="A990" s="1">
+        <v>0</v>
+      </c>
+      <c r="B990" t="s">
+        <v>191</v>
+      </c>
+      <c r="C990">
+        <v>0.9478827029273607</v>
+      </c>
+      <c r="D990" t="s">
+        <v>342</v>
+      </c>
+      <c r="E990">
+        <v>1.239490555786455</v>
+      </c>
+      <c r="F990">
+        <v>1</v>
+      </c>
+      <c r="G990">
+        <v>0.01739211729707264</v>
+      </c>
+      <c r="H990">
+        <v>0.01814050944421354</v>
+      </c>
+      <c r="I990">
+        <v>0.2916078528590944</v>
+      </c>
+      <c r="J990">
+        <v>1.343483218475921</v>
+      </c>
+      <c r="K990">
+        <v>6.12</v>
+      </c>
+      <c r="L990">
+        <v>9.17</v>
+      </c>
+      <c r="M990">
+        <v>6.29</v>
+      </c>
+      <c r="N990">
+        <v>9.69</v>
+      </c>
+      <c r="O990">
+        <v>1</v>
+      </c>
+      <c r="P990" t="s">
+        <v>454</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2979" uniqueCount="455">
   <si>
     <t>trade_time</t>
   </si>
@@ -580,9 +580,6 @@
     <t>2021-01-26</t>
   </si>
   <si>
-    <t>2021-08-26</t>
-  </si>
-  <si>
     <t>2021-09-03</t>
   </si>
   <si>
@@ -590,6 +587,9 @@
   </si>
   <si>
     <t>2021-09-14</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
   </si>
   <si>
     <t>2016-11-30</t>
@@ -1036,13 +1036,16 @@
     <t>2021-01-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>2021-09-07</t>
   </si>
   <si>
+    <t>2021-09-13</t>
+  </si>
+  <si>
     <t>2021-09-16</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1376,9 +1379,6 @@
   </si>
   <si>
     <t>2021-09-10</t>
-  </si>
-  <si>
-    <t>2021-09-13</t>
   </si>
 </sst>
 </file>
@@ -1736,7 +1736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P990"/>
+  <dimension ref="A1:P989"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1883,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1983,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2033,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2083,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2133,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2433,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2533,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2583,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2633,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2683,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2733,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2833,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3083,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3133,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3183,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3233,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3283,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3333,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3433,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3483,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3533,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3583,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3633,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3933,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3983,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4033,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4083,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4133,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4183,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4233,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4283,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4333,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4383,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4433,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4483,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4533,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4583,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4633,7 +4633,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4683,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4733,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4783,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4833,7 +4833,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4883,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4933,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5383,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5433,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5483,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5533,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5583,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5633,7 +5633,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6033,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6083,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6133,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6183,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6233,7 +6233,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6283,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6533,7 +6533,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6583,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6683,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6733,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6783,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6833,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6883,7 +6883,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6933,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6983,7 +6983,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7033,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7083,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7133,7 +7133,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7183,7 +7183,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7283,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7333,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7383,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7433,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7533,7 +7533,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7583,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7633,7 +7633,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7683,7 +7683,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7733,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7783,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7833,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7883,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7933,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7983,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8033,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8083,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8133,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8183,7 +8183,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8233,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8283,7 +8283,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8333,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8383,7 +8383,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8433,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8483,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8533,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8583,7 +8583,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8633,7 +8633,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8683,7 +8683,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8733,7 +8733,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8783,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8833,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8883,7 +8883,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8933,7 +8933,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8983,7 +8983,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9033,7 +9033,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9083,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9133,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9183,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9433,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9483,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9533,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9583,7 +9583,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9633,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9683,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9733,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9783,7 +9783,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10133,7 +10133,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10183,7 +10183,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10233,7 +10233,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10483,7 +10483,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10533,7 +10533,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10583,7 +10583,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10633,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10683,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10733,7 +10733,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10783,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10833,7 +10833,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10883,7 +10883,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10933,7 +10933,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10983,7 +10983,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11033,7 +11033,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11083,7 +11083,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11483,7 +11483,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11733,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11833,7 +11833,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11883,7 +11883,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11933,7 +11933,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11983,7 +11983,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12033,7 +12033,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12083,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12133,7 +12133,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12183,7 +12183,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12233,7 +12233,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12283,7 +12283,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12333,7 +12333,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12383,7 +12383,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12433,7 +12433,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12483,7 +12483,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12533,7 +12533,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16383,7 +16383,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16433,7 +16433,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16483,7 +16483,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16533,7 +16533,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16583,7 +16583,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16633,7 +16633,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16833,7 +16833,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16883,7 +16883,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16933,7 +16933,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16983,7 +16983,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17033,7 +17033,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17083,7 +17083,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17333,7 +17333,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17383,7 +17383,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17433,7 +17433,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17483,7 +17483,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17533,7 +17533,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17583,7 +17583,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17633,7 +17633,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17683,7 +17683,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17733,7 +17733,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18883,7 +18883,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18933,7 +18933,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18983,7 +18983,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19033,7 +19033,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19083,7 +19083,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19133,7 +19133,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19183,7 +19183,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19233,7 +19233,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19283,7 +19283,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19333,7 +19333,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19933,7 +19933,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19983,7 +19983,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20033,7 +20033,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20083,7 +20083,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20133,7 +20133,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20183,7 +20183,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -21933,7 +21933,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21983,7 +21983,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22033,7 +22033,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22083,7 +22083,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22133,7 +22133,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22183,7 +22183,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22233,7 +22233,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22283,7 +22283,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22333,7 +22333,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22383,7 +22383,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22433,7 +22433,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22483,7 +22483,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22533,7 +22533,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22583,7 +22583,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22633,7 +22633,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22683,7 +22683,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22733,7 +22733,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22783,7 +22783,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22833,7 +22833,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23183,7 +23183,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23233,7 +23233,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23283,7 +23283,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23333,7 +23333,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23383,7 +23383,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23433,7 +23433,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23483,7 +23483,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23533,7 +23533,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23633,7 +23633,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23683,7 +23683,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23733,7 +23733,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23783,7 +23783,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23833,7 +23833,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23883,7 +23883,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23933,7 +23933,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23983,7 +23983,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24033,7 +24033,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24083,7 +24083,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24133,7 +24133,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24183,7 +24183,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24233,7 +24233,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24633,7 +24633,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24683,7 +24683,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24733,7 +24733,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24783,7 +24783,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24833,7 +24833,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24883,7 +24883,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24933,7 +24933,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25533,7 +25533,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25583,7 +25583,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25633,7 +25633,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25683,7 +25683,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25733,7 +25733,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25783,7 +25783,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25833,7 +25833,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25883,7 +25883,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25933,7 +25933,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25983,7 +25983,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26033,7 +26033,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26083,7 +26083,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26133,7 +26133,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26183,7 +26183,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26233,7 +26233,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26283,7 +26283,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26333,7 +26333,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26383,7 +26383,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26433,7 +26433,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26483,7 +26483,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26683,7 +26683,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26733,7 +26733,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26783,7 +26783,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26833,7 +26833,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26883,7 +26883,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26933,7 +26933,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26983,7 +26983,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27933,7 +27933,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27983,7 +27983,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28033,7 +28033,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29333,7 +29333,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29383,7 +29383,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29433,7 +29433,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29483,7 +29483,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29533,7 +29533,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29583,7 +29583,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29633,7 +29633,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29683,7 +29683,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29733,7 +29733,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29783,7 +29783,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30083,7 +30083,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30133,7 +30133,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30183,7 +30183,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30233,7 +30233,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30283,7 +30283,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30333,7 +30333,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30383,7 +30383,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30433,7 +30433,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30483,7 +30483,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30533,7 +30533,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30583,7 +30583,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30783,7 +30783,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30833,7 +30833,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30883,7 +30883,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30933,7 +30933,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30983,7 +30983,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31033,7 +31033,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31083,7 +31083,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31133,7 +31133,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31183,7 +31183,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31483,7 +31483,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31533,7 +31533,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31583,7 +31583,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31633,7 +31633,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31683,7 +31683,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31733,7 +31733,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31783,7 +31783,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31833,7 +31833,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31883,7 +31883,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31933,7 +31933,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31983,7 +31983,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32033,7 +32033,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32633,7 +32633,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32683,7 +32683,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32733,7 +32733,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32783,7 +32783,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32833,7 +32833,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32883,7 +32883,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32933,7 +32933,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32983,7 +32983,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33033,7 +33033,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33083,7 +33083,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33283,7 +33283,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33333,7 +33333,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33383,7 +33383,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33433,7 +33433,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33483,7 +33483,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34383,7 +34383,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34433,7 +34433,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34483,7 +34483,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34533,7 +34533,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34583,7 +34583,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34633,7 +34633,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34683,7 +34683,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34733,7 +34733,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34783,7 +34783,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35433,7 +35433,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35483,7 +35483,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35533,7 +35533,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35583,7 +35583,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35633,7 +35633,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35683,7 +35683,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35733,7 +35733,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35783,7 +35783,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35833,7 +35833,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36233,7 +36233,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36283,7 +36283,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36333,7 +36333,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36383,7 +36383,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36433,7 +36433,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36483,7 +36483,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36533,7 +36533,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36583,7 +36583,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36633,7 +36633,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36683,7 +36683,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36733,7 +36733,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36783,7 +36783,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36833,7 +36833,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37133,7 +37133,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37183,7 +37183,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37233,7 +37233,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37283,7 +37283,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37583,7 +37583,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37633,7 +37633,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37683,7 +37683,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37733,7 +37733,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37783,7 +37783,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37833,7 +37833,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37883,7 +37883,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37933,7 +37933,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37983,7 +37983,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38033,7 +38033,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38283,7 +38283,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38333,7 +38333,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38383,7 +38383,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38433,7 +38433,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38483,7 +38483,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39083,7 +39083,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39133,7 +39133,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39183,7 +39183,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39233,7 +39233,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39283,7 +39283,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39333,7 +39333,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39383,7 +39383,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39433,7 +39433,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39483,7 +39483,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39533,7 +39533,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40333,7 +40333,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40383,7 +40383,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40433,7 +40433,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40483,7 +40483,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40533,7 +40533,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40583,7 +40583,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40633,7 +40633,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42333,7 +42333,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42383,7 +42383,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42433,7 +42433,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42483,7 +42483,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42533,7 +42533,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43083,7 +43083,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43133,7 +43133,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43183,7 +43183,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43233,7 +43233,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43283,7 +43283,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43333,7 +43333,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43483,7 +43483,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43533,7 +43533,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43583,7 +43583,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43633,7 +43633,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43683,7 +43683,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43733,7 +43733,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43783,7 +43783,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43833,7 +43833,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43883,7 +43883,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43933,7 +43933,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43983,7 +43983,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44033,7 +44033,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44083,7 +44083,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44133,7 +44133,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44183,7 +44183,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44233,7 +44233,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44283,7 +44283,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44333,7 +44333,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44383,7 +44383,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44433,7 +44433,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44733,7 +44733,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44783,7 +44783,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44833,7 +44833,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44883,7 +44883,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -44933,7 +44933,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -44983,7 +44983,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45033,7 +45033,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45083,7 +45083,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45133,7 +45133,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45183,7 +45183,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45233,7 +45233,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45283,7 +45283,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45333,7 +45333,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45383,7 +45383,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45433,7 +45433,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45483,7 +45483,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45533,7 +45533,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45583,7 +45583,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45883,7 +45883,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -45933,7 +45933,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -45983,7 +45983,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46033,7 +46033,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46083,7 +46083,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46333,7 +46333,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46383,7 +46383,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46433,7 +46433,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46483,7 +46483,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46733,7 +46733,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46783,7 +46783,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46833,7 +46833,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46883,7 +46883,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -46933,7 +46933,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -46983,7 +46983,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47033,7 +47033,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47083,7 +47083,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47133,7 +47133,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47183,7 +47183,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47233,7 +47233,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47583,7 +47583,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47633,7 +47633,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47683,7 +47683,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47733,7 +47733,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47783,7 +47783,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47833,7 +47833,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -47883,7 +47883,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -47933,7 +47933,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -47983,7 +47983,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48033,7 +48033,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48083,7 +48083,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48133,7 +48133,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48183,7 +48183,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48233,7 +48233,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48283,7 +48283,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48833,7 +48833,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48883,7 +48883,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -48933,7 +48933,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -48983,7 +48983,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49183,7 +49183,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49233,7 +49233,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49283,7 +49283,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49333,7 +49333,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49383,7 +49383,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49433,7 +49433,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49483,7 +49483,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49533,7 +49533,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49583,7 +49583,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50583,7 +50583,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50633,7 +50633,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50683,7 +50683,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50733,7 +50733,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50783,7 +50783,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50833,7 +50833,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50844,46 +50844,46 @@
         <v>188</v>
       </c>
       <c r="C983">
-        <v>1.297829535910621</v>
+        <v>0.6201465518963349</v>
       </c>
       <c r="D983" t="s">
         <v>340</v>
       </c>
       <c r="E983">
-        <v>0.8616678599075076</v>
+        <v>1.150592131893589</v>
       </c>
       <c r="F983">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G983">
-        <v>0.01428217046408938</v>
+        <v>0.01567985344810367</v>
       </c>
       <c r="H983">
-        <v>0.01429833214009249</v>
+        <v>0.01660940786810641</v>
       </c>
       <c r="I983">
-        <v>0.4361616760031133</v>
+        <v>0.5304455799972541</v>
       </c>
       <c r="J983">
         <v>1.330362800018315</v>
       </c>
       <c r="K983">
-        <v>4.88</v>
+        <v>5.66</v>
       </c>
       <c r="L983">
-        <v>7.79</v>
+        <v>8.15</v>
       </c>
       <c r="M983">
-        <v>5.05</v>
+        <v>5.81</v>
       </c>
       <c r="N983">
-        <v>7.58</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="O983">
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -50894,196 +50894,196 @@
         <v>189</v>
       </c>
       <c r="C984">
-        <v>0.6201465518963349</v>
+        <v>1.478357895886811</v>
       </c>
       <c r="D984" t="s">
-        <v>341</v>
+        <v>190</v>
       </c>
       <c r="E984">
-        <v>1.150592131893589</v>
+        <v>1.02817966388791</v>
       </c>
       <c r="F984">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G984">
-        <v>0.01567985344810367</v>
+        <v>0.01792164210411319</v>
       </c>
       <c r="H984">
-        <v>0.01660940786810641</v>
+        <v>0.01731182033611209</v>
       </c>
       <c r="I984">
-        <v>0.5304455799972541</v>
+        <v>0.4501782319989012</v>
       </c>
       <c r="J984">
         <v>1.330362800018315</v>
       </c>
       <c r="K984">
-        <v>5.66</v>
+        <v>6.18</v>
       </c>
       <c r="L984">
-        <v>8.15</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M984">
-        <v>5.81</v>
+        <v>6.12</v>
       </c>
       <c r="N984">
-        <v>8.880000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="O984">
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="985" spans="1:16">
       <c r="A985" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B985" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C985">
-        <v>1.478357895886811</v>
+        <v>0.5600712707795941</v>
       </c>
       <c r="D985" t="s">
-        <v>191</v>
+        <v>340</v>
       </c>
       <c r="E985">
-        <v>1.02817966388791</v>
+        <v>1.088924749687181</v>
       </c>
       <c r="F985">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G985">
-        <v>0.01792164210411319</v>
+        <v>0.01573992872922041</v>
       </c>
       <c r="H985">
-        <v>0.01731182033611209</v>
+        <v>0.01667107525031282</v>
       </c>
       <c r="I985">
-        <v>0.4501782319989012</v>
+        <v>0.5288534789075872</v>
       </c>
       <c r="J985">
-        <v>1.330362800018315</v>
+        <v>1.340976807282757</v>
       </c>
       <c r="K985">
-        <v>6.18</v>
+        <v>5.66</v>
       </c>
       <c r="L985">
-        <v>9.699999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="M985">
-        <v>6.12</v>
+        <v>5.81</v>
       </c>
       <c r="N985">
-        <v>9.17</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="O985">
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="986" spans="1:16">
       <c r="A986" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B986" t="s">
         <v>189</v>
       </c>
       <c r="C986">
-        <v>0.5600712707795941</v>
+        <v>1.41276333099256</v>
       </c>
       <c r="D986" t="s">
         <v>341</v>
       </c>
       <c r="E986">
-        <v>1.088924749687181</v>
+        <v>1.045026577972973</v>
       </c>
       <c r="F986">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G986">
-        <v>0.01573992872922041</v>
+        <v>0.01798723666900744</v>
       </c>
       <c r="H986">
-        <v>0.01667107525031282</v>
+        <v>0.01799497342202703</v>
       </c>
       <c r="I986">
-        <v>0.5288534789075872</v>
+        <v>0.367736753019587</v>
       </c>
       <c r="J986">
         <v>1.340976807282757</v>
       </c>
       <c r="K986">
-        <v>5.66</v>
+        <v>6.18</v>
       </c>
       <c r="L986">
-        <v>8.15</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M986">
-        <v>5.81</v>
+        <v>6.32</v>
       </c>
       <c r="N986">
-        <v>8.880000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="O986">
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="987" spans="1:16">
       <c r="A987" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B987" t="s">
         <v>190</v>
       </c>
       <c r="C987">
-        <v>1.41276333099256</v>
+        <v>0.9880706777811863</v>
       </c>
       <c r="D987" t="s">
-        <v>191</v>
+        <v>342</v>
       </c>
       <c r="E987">
-        <v>0.9632219394295252</v>
+        <v>1.280794863275108</v>
       </c>
       <c r="F987">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G987">
-        <v>0.01798723666900744</v>
+        <v>0.01735192932221882</v>
       </c>
       <c r="H987">
-        <v>0.01737677806057047</v>
+        <v>0.01809920513672489</v>
       </c>
       <c r="I987">
-        <v>0.4495413915630344</v>
+        <v>0.2927241854939222</v>
       </c>
       <c r="J987">
-        <v>1.340976807282757</v>
+        <v>1.336916555918107</v>
       </c>
       <c r="K987">
-        <v>6.18</v>
+        <v>6.12</v>
       </c>
       <c r="L987">
-        <v>9.699999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="M987">
-        <v>6.12</v>
+        <v>6.29</v>
       </c>
       <c r="N987">
-        <v>9.17</v>
+        <v>9.69</v>
       </c>
       <c r="O987">
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>452</v>
+        <v>189</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51091,31 +51091,31 @@
         <v>0</v>
       </c>
       <c r="B988" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C988">
-        <v>0.9880706777811863</v>
+        <v>0.9608966978759845</v>
       </c>
       <c r="D988" t="s">
         <v>342</v>
       </c>
       <c r="E988">
-        <v>1.280794863275108</v>
+        <v>1.252866050594761</v>
       </c>
       <c r="F988">
         <v>1</v>
       </c>
       <c r="G988">
-        <v>0.01735192932221882</v>
+        <v>0.01737910330212402</v>
       </c>
       <c r="H988">
-        <v>0.01809920513672489</v>
+        <v>0.01812713394940524</v>
       </c>
       <c r="I988">
-        <v>0.2927241854939222</v>
+        <v>0.2919693527187768</v>
       </c>
       <c r="J988">
-        <v>1.336916555918107</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K988">
         <v>6.12</v>
@@ -51133,7 +51133,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>190</v>
+        <v>454</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51144,96 +51144,46 @@
         <v>191</v>
       </c>
       <c r="C989">
-        <v>0.9608966978759845</v>
+        <v>1.140084502779063</v>
       </c>
       <c r="D989" t="s">
+        <v>343</v>
+      </c>
+      <c r="E989">
+        <v>1.460084502779063</v>
+      </c>
+      <c r="F989">
+        <v>1</v>
+      </c>
+      <c r="G989">
+        <v>0.01715991549722094</v>
+      </c>
+      <c r="H989">
+        <v>0.01747991549722094</v>
+      </c>
+      <c r="I989">
+        <v>0.3200000000000003</v>
+      </c>
+      <c r="J989">
+        <v>1.341694388144211</v>
+      </c>
+      <c r="K989">
+        <v>5.97</v>
+      </c>
+      <c r="L989">
+        <v>9.15</v>
+      </c>
+      <c r="M989">
+        <v>5.97</v>
+      </c>
+      <c r="N989">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="O989">
+        <v>1</v>
+      </c>
+      <c r="P989" t="s">
         <v>342</v>
-      </c>
-      <c r="E989">
-        <v>1.252866050594761</v>
-      </c>
-      <c r="F989">
-        <v>1</v>
-      </c>
-      <c r="G989">
-        <v>0.01737910330212402</v>
-      </c>
-      <c r="H989">
-        <v>0.01812713394940524</v>
-      </c>
-      <c r="I989">
-        <v>0.2919693527187768</v>
-      </c>
-      <c r="J989">
-        <v>1.341356748713074</v>
-      </c>
-      <c r="K989">
-        <v>6.12</v>
-      </c>
-      <c r="L989">
-        <v>9.17</v>
-      </c>
-      <c r="M989">
-        <v>6.29</v>
-      </c>
-      <c r="N989">
-        <v>9.69</v>
-      </c>
-      <c r="O989">
-        <v>1</v>
-      </c>
-      <c r="P989" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="990" spans="1:16">
-      <c r="A990" s="1">
-        <v>0</v>
-      </c>
-      <c r="B990" t="s">
-        <v>191</v>
-      </c>
-      <c r="C990">
-        <v>0.9478827029273607</v>
-      </c>
-      <c r="D990" t="s">
-        <v>342</v>
-      </c>
-      <c r="E990">
-        <v>1.239490555786455</v>
-      </c>
-      <c r="F990">
-        <v>1</v>
-      </c>
-      <c r="G990">
-        <v>0.01739211729707264</v>
-      </c>
-      <c r="H990">
-        <v>0.01814050944421354</v>
-      </c>
-      <c r="I990">
-        <v>0.2916078528590944</v>
-      </c>
-      <c r="J990">
-        <v>1.343483218475921</v>
-      </c>
-      <c r="K990">
-        <v>6.12</v>
-      </c>
-      <c r="L990">
-        <v>9.17</v>
-      </c>
-      <c r="M990">
-        <v>6.29</v>
-      </c>
-      <c r="N990">
-        <v>9.69</v>
-      </c>
-      <c r="O990">
-        <v>1</v>
-      </c>
-      <c r="P990" t="s">
-        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3018" uniqueCount="458">
   <si>
     <t>trade_time</t>
   </si>
@@ -589,7 +589,7 @@
     <t>2021-09-23</t>
   </si>
   <si>
-    <t>2021-09-14</t>
+    <t>2021-10-08</t>
   </si>
   <si>
     <t>2016-11-30</t>
@@ -1039,13 +1039,16 @@
     <t>2021-09-07</t>
   </si>
   <si>
-    <t>2021-09-13</t>
+    <t>2021-09-14</t>
   </si>
   <si>
     <t>2021-09-28</t>
   </si>
   <si>
-    <t>2021-09-16</t>
+    <t>2021-09-13</t>
+  </si>
+  <si>
+    <t>2021-10-11</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1379,6 +1382,12 @@
   </si>
   <si>
     <t>2021-09-10</t>
+  </si>
+  <si>
+    <t>2021-09-16</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
   </si>
 </sst>
 </file>
@@ -1736,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P994"/>
+  <dimension ref="A1:P1002"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1833,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1883,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1933,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1983,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2033,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2083,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2133,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2433,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2483,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2533,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2583,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2633,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2683,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2733,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2783,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2833,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3083,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3133,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3183,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3233,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3283,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3333,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3383,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3433,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3483,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3533,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3583,7 +3592,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3633,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3933,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3983,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4033,7 +4042,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4083,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4133,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4183,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4233,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4283,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4333,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4383,7 +4392,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4433,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4483,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4533,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4583,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4633,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4683,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4733,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4783,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4833,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4883,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4933,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5383,7 +5392,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5433,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5483,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5533,7 +5542,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5583,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5633,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6033,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6083,7 +6092,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6133,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6183,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6233,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6283,7 +6292,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6533,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6583,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6633,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6683,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6733,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6783,7 +6792,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6833,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6883,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6933,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6983,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7033,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7083,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7133,7 +7142,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7183,7 +7192,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7233,7 +7242,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7283,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7333,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7383,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7433,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7483,7 +7492,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7533,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7583,7 +7592,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7633,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7683,7 +7692,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7733,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7783,7 +7792,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7833,7 +7842,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7883,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7933,7 +7942,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7983,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8033,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8083,7 +8092,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8133,7 +8142,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8183,7 +8192,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8233,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8283,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8333,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8383,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8433,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8483,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8533,7 +8542,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8583,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8633,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8683,7 +8692,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8733,7 +8742,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8783,7 +8792,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8833,7 +8842,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8883,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8933,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8983,7 +8992,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9033,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9083,7 +9092,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9133,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9183,7 +9192,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9433,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9483,7 +9492,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9533,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9583,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9633,7 +9642,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9683,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9733,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9783,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10133,7 +10142,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10183,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10233,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10483,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10533,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10583,7 +10592,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10633,7 +10642,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10683,7 +10692,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10733,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10783,7 +10792,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10833,7 +10842,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10883,7 +10892,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10933,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10983,7 +10992,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11033,7 +11042,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11083,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11483,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11733,7 +11742,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11783,7 +11792,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11833,7 +11842,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11883,7 +11892,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11933,7 +11942,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11983,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12033,7 +12042,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12083,7 +12092,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12133,7 +12142,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12183,7 +12192,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12233,7 +12242,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12283,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12333,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12383,7 +12392,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12433,7 +12442,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12483,7 +12492,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12533,7 +12542,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16383,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16433,7 +16442,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16483,7 +16492,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16533,7 +16542,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16583,7 +16592,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16633,7 +16642,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16833,7 +16842,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16883,7 +16892,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16933,7 +16942,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16983,7 +16992,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17033,7 +17042,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17083,7 +17092,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17333,7 +17342,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17383,7 +17392,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17433,7 +17442,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17483,7 +17492,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17533,7 +17542,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17583,7 +17592,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17633,7 +17642,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17683,7 +17692,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17733,7 +17742,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18883,7 +18892,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18933,7 +18942,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18983,7 +18992,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19033,7 +19042,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19083,7 +19092,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19133,7 +19142,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19183,7 +19192,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19233,7 +19242,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19283,7 +19292,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19333,7 +19342,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19933,7 +19942,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19983,7 +19992,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20033,7 +20042,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20083,7 +20092,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20133,7 +20142,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20183,7 +20192,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -21933,7 +21942,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21983,7 +21992,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22033,7 +22042,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22083,7 +22092,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22133,7 +22142,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22183,7 +22192,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22233,7 +22242,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22283,7 +22292,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22333,7 +22342,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22383,7 +22392,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22433,7 +22442,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22483,7 +22492,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22533,7 +22542,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22583,7 +22592,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22633,7 +22642,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22683,7 +22692,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22733,7 +22742,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22783,7 +22792,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22833,7 +22842,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23183,7 +23192,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23233,7 +23242,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23283,7 +23292,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23333,7 +23342,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23383,7 +23392,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23433,7 +23442,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23483,7 +23492,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23533,7 +23542,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23583,7 +23592,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23633,7 +23642,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23683,7 +23692,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23733,7 +23742,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23783,7 +23792,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23833,7 +23842,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23883,7 +23892,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23933,7 +23942,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23983,7 +23992,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24033,7 +24042,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24083,7 +24092,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24133,7 +24142,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24183,7 +24192,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24233,7 +24242,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24633,7 +24642,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24683,7 +24692,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24733,7 +24742,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24783,7 +24792,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24833,7 +24842,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24883,7 +24892,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24933,7 +24942,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25533,7 +25542,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25583,7 +25592,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25633,7 +25642,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25683,7 +25692,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25733,7 +25742,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25783,7 +25792,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25833,7 +25842,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25883,7 +25892,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25933,7 +25942,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25983,7 +25992,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26033,7 +26042,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26083,7 +26092,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26133,7 +26142,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26183,7 +26192,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26233,7 +26242,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26283,7 +26292,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26333,7 +26342,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26383,7 +26392,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26433,7 +26442,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26483,7 +26492,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26683,7 +26692,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26733,7 +26742,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26783,7 +26792,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26833,7 +26842,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26883,7 +26892,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26933,7 +26942,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26983,7 +26992,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27933,7 +27942,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27983,7 +27992,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28033,7 +28042,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29333,7 +29342,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29383,7 +29392,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29433,7 +29442,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29483,7 +29492,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29533,7 +29542,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29583,7 +29592,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29633,7 +29642,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29683,7 +29692,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29733,7 +29742,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29783,7 +29792,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30083,7 +30092,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30133,7 +30142,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30183,7 +30192,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30233,7 +30242,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30283,7 +30292,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30333,7 +30342,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30383,7 +30392,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30433,7 +30442,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30483,7 +30492,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30533,7 +30542,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30583,7 +30592,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30783,7 +30792,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30833,7 +30842,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30883,7 +30892,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30933,7 +30942,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30983,7 +30992,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31033,7 +31042,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31083,7 +31092,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31133,7 +31142,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31183,7 +31192,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31483,7 +31492,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31533,7 +31542,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31583,7 +31592,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31633,7 +31642,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31683,7 +31692,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31733,7 +31742,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31783,7 +31792,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31833,7 +31842,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31883,7 +31892,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31933,7 +31942,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31983,7 +31992,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32033,7 +32042,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32633,7 +32642,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32683,7 +32692,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32733,7 +32742,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32783,7 +32792,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32833,7 +32842,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32883,7 +32892,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32933,7 +32942,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32983,7 +32992,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33033,7 +33042,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33083,7 +33092,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33283,7 +33292,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33333,7 +33342,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33383,7 +33392,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33433,7 +33442,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33483,7 +33492,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34383,7 +34392,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34433,7 +34442,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34483,7 +34492,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34533,7 +34542,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34583,7 +34592,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34633,7 +34642,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34683,7 +34692,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34733,7 +34742,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34783,7 +34792,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35433,7 +35442,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35483,7 +35492,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35533,7 +35542,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35583,7 +35592,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35633,7 +35642,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35683,7 +35692,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35733,7 +35742,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35783,7 +35792,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35833,7 +35842,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36233,7 +36242,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36283,7 +36292,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36333,7 +36342,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36383,7 +36392,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36433,7 +36442,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36483,7 +36492,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36533,7 +36542,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36583,7 +36592,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36633,7 +36642,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36683,7 +36692,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36733,7 +36742,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36783,7 +36792,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36833,7 +36842,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37133,7 +37142,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37183,7 +37192,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37233,7 +37242,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37283,7 +37292,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37583,7 +37592,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37633,7 +37642,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37683,7 +37692,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37733,7 +37742,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37783,7 +37792,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37833,7 +37842,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37883,7 +37892,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37933,7 +37942,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37983,7 +37992,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38033,7 +38042,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38283,7 +38292,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38333,7 +38342,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38383,7 +38392,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38433,7 +38442,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38483,7 +38492,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39083,7 +39092,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39133,7 +39142,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39183,7 +39192,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39233,7 +39242,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39283,7 +39292,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39333,7 +39342,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39383,7 +39392,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39433,7 +39442,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39483,7 +39492,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39533,7 +39542,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40333,7 +40342,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40383,7 +40392,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40433,7 +40442,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40483,7 +40492,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40533,7 +40542,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40583,7 +40592,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40633,7 +40642,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42333,7 +42342,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42383,7 +42392,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42433,7 +42442,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42483,7 +42492,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42533,7 +42542,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43083,7 +43092,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43133,7 +43142,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43183,7 +43192,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43233,7 +43242,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43283,7 +43292,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43333,7 +43342,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43483,7 +43492,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43533,7 +43542,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43583,7 +43592,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43633,7 +43642,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43683,7 +43692,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43733,7 +43742,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43783,7 +43792,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43833,7 +43842,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43883,7 +43892,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43933,7 +43942,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43983,7 +43992,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44033,7 +44042,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44083,7 +44092,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44133,7 +44142,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44183,7 +44192,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44233,7 +44242,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44283,7 +44292,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44333,7 +44342,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44383,7 +44392,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44433,7 +44442,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44733,7 +44742,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44783,7 +44792,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44833,7 +44842,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44883,7 +44892,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -44933,7 +44942,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -44983,7 +44992,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45033,7 +45042,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45083,7 +45092,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45133,7 +45142,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45183,7 +45192,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45233,7 +45242,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45283,7 +45292,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45333,7 +45342,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45383,7 +45392,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45433,7 +45442,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45483,7 +45492,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45533,7 +45542,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45583,7 +45592,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45883,7 +45892,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -45933,7 +45942,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -45983,7 +45992,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46033,7 +46042,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46083,7 +46092,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46333,7 +46342,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46383,7 +46392,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46433,7 +46442,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46483,7 +46492,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46733,7 +46742,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46783,7 +46792,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46833,7 +46842,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46883,7 +46892,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -46933,7 +46942,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -46983,7 +46992,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47033,7 +47042,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47083,7 +47092,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47133,7 +47142,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47183,7 +47192,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47233,7 +47242,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47583,7 +47592,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47633,7 +47642,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47683,7 +47692,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47733,7 +47742,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47783,7 +47792,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47833,7 +47842,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -47883,7 +47892,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -47933,7 +47942,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -47983,7 +47992,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48033,7 +48042,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48083,7 +48092,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48133,7 +48142,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48183,7 +48192,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48233,7 +48242,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48283,7 +48292,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48833,7 +48842,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48883,7 +48892,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -48933,7 +48942,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -48983,7 +48992,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49183,7 +49192,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49233,7 +49242,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49283,7 +49292,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49333,7 +49342,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49383,7 +49392,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49433,7 +49442,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49483,7 +49492,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49533,7 +49542,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49583,7 +49592,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50583,7 +50592,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50633,7 +50642,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50683,7 +50692,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50733,7 +50742,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50783,7 +50792,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50833,7 +50842,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50883,7 +50892,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -50900,7 +50909,7 @@
         <v>341</v>
       </c>
       <c r="E984">
-        <v>1.112107103884245</v>
+        <v>1.02817966388791</v>
       </c>
       <c r="F984">
         <v>-1</v>
@@ -50909,10 +50918,10 @@
         <v>0.01792164210411319</v>
       </c>
       <c r="H984">
-        <v>0.01792789289611576</v>
+        <v>0.01731182033611209</v>
       </c>
       <c r="I984">
-        <v>0.3662507920025657</v>
+        <v>0.4501782319989012</v>
       </c>
       <c r="J984">
         <v>1.330362800018315</v>
@@ -50924,16 +50933,16 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M984">
-        <v>6.32</v>
+        <v>6.12</v>
       </c>
       <c r="N984">
-        <v>9.52</v>
+        <v>9.17</v>
       </c>
       <c r="O984">
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -50983,7 +50992,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51033,7 +51042,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51047,7 +51056,7 @@
         <v>1.41276333099256</v>
       </c>
       <c r="D987" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E987">
         <v>1.045026577972973</v>
@@ -51083,7 +51092,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51133,57 +51142,57 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="989" spans="1:16">
       <c r="A989" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B989" t="s">
         <v>191</v>
       </c>
       <c r="C989">
-        <v>0.9880706777811863</v>
+        <v>0.7518759093230418</v>
       </c>
       <c r="D989" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E989">
-        <v>1.280794863275108</v>
+        <v>0.9143684605219402</v>
       </c>
       <c r="F989">
         <v>1</v>
       </c>
       <c r="G989">
-        <v>0.01735192932221882</v>
+        <v>0.01646812409067696</v>
       </c>
       <c r="H989">
-        <v>0.01809920513672489</v>
+        <v>0.01692563153947806</v>
       </c>
       <c r="I989">
-        <v>0.2927241854939222</v>
+        <v>0.1624925511988984</v>
       </c>
       <c r="J989">
-        <v>1.336916555918107</v>
+        <v>1.340976807282757</v>
       </c>
       <c r="K989">
-        <v>6.12</v>
+        <v>5.86</v>
       </c>
       <c r="L989">
-        <v>9.17</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M989">
-        <v>6.29</v>
+        <v>5.97</v>
       </c>
       <c r="N989">
-        <v>9.69</v>
+        <v>8.92</v>
       </c>
       <c r="O989">
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>189</v>
+        <v>454</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51191,49 +51200,49 @@
         <v>0</v>
       </c>
       <c r="B990" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C990">
-        <v>0.9608966978759845</v>
+        <v>1.488608161168904</v>
       </c>
       <c r="D990" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E990">
-        <v>1.252866050594761</v>
+        <v>1.058608161168903</v>
       </c>
       <c r="F990">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G990">
-        <v>0.01737910330212402</v>
+        <v>0.01745139183883109</v>
       </c>
       <c r="H990">
-        <v>0.01812713394940524</v>
+        <v>0.0170213918388311</v>
       </c>
       <c r="I990">
-        <v>0.2919693527187768</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J990">
-        <v>1.341356748713074</v>
+        <v>1.336916555918107</v>
       </c>
       <c r="K990">
-        <v>6.12</v>
+        <v>5.97</v>
       </c>
       <c r="L990">
-        <v>9.17</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M990">
-        <v>6.29</v>
+        <v>5.97</v>
       </c>
       <c r="N990">
-        <v>9.69</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O990">
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>454</v>
+        <v>189</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51241,49 +51250,49 @@
         <v>1</v>
       </c>
       <c r="B991" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C991">
-        <v>1.462100210182946</v>
+        <v>0.7756689823198943</v>
       </c>
       <c r="D991" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E991">
-        <v>1.032100210182945</v>
+        <v>0.9386081611689034</v>
       </c>
       <c r="F991">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G991">
-        <v>0.01747789978981706</v>
+        <v>0.01644433101768011</v>
       </c>
       <c r="H991">
-        <v>0.01704789978981705</v>
+        <v>0.0169013918388311</v>
       </c>
       <c r="I991">
-        <v>0.4300000000000015</v>
+        <v>0.1629391788490091</v>
       </c>
       <c r="J991">
-        <v>1.341356748713074</v>
+        <v>1.336916555918107</v>
       </c>
       <c r="K991">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L991">
-        <v>9.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M991">
         <v>5.97</v>
       </c>
       <c r="N991">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="O991">
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>454</v>
+        <v>189</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51291,49 +51300,49 @@
         <v>0</v>
       </c>
       <c r="B992" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C992">
-        <v>0.9478827029273607</v>
+        <v>1.462100210182946</v>
       </c>
       <c r="D992" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E992">
-        <v>1.239490555786455</v>
+        <v>1.032100210182945</v>
       </c>
       <c r="F992">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G992">
-        <v>0.01739211729707264</v>
+        <v>0.01747789978981706</v>
       </c>
       <c r="H992">
-        <v>0.01814050944421354</v>
+        <v>0.01704789978981705</v>
       </c>
       <c r="I992">
-        <v>0.2916078528590944</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J992">
-        <v>1.343483218475921</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K992">
-        <v>6.12</v>
+        <v>5.97</v>
       </c>
       <c r="L992">
-        <v>9.17</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M992">
-        <v>6.29</v>
+        <v>5.97</v>
       </c>
       <c r="N992">
-        <v>9.69</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O992">
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>341</v>
+        <v>455</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51341,49 +51350,49 @@
         <v>1</v>
       </c>
       <c r="B993" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C993">
-        <v>1.449405185698751</v>
+        <v>0.7496494525413828</v>
       </c>
       <c r="D993" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E993">
-        <v>1.01940518569875</v>
+        <v>0.9121002101829454</v>
       </c>
       <c r="F993">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G993">
-        <v>0.01749059481430125</v>
+        <v>0.01647035054745861</v>
       </c>
       <c r="H993">
-        <v>0.01706059481430125</v>
+        <v>0.01692789978981706</v>
       </c>
       <c r="I993">
-        <v>0.4300000000000015</v>
+        <v>0.1624507576415626</v>
       </c>
       <c r="J993">
-        <v>1.343483218475921</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K993">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L993">
-        <v>9.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M993">
         <v>5.97</v>
       </c>
       <c r="N993">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="O993">
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>341</v>
+        <v>455</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51394,28 +51403,28 @@
         <v>190</v>
       </c>
       <c r="C994">
-        <v>1.446464800345405</v>
+        <v>1.449405185698751</v>
       </c>
       <c r="D994" t="s">
         <v>342</v>
       </c>
       <c r="E994">
-        <v>1.016464800345403</v>
+        <v>1.01940518569875</v>
       </c>
       <c r="F994">
         <v>-1</v>
       </c>
       <c r="G994">
-        <v>0.0174935351996546</v>
+        <v>0.01749059481430125</v>
       </c>
       <c r="H994">
-        <v>0.0170635351996546</v>
+        <v>0.01706059481430125</v>
       </c>
       <c r="I994">
         <v>0.4300000000000015</v>
       </c>
       <c r="J994">
-        <v>1.343975745335778</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K994">
         <v>5.97</v>
@@ -51433,7 +51442,407 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="995" spans="1:16">
+      <c r="A995" s="1">
+        <v>1</v>
+      </c>
+      <c r="B995" t="s">
         <v>191</v>
+      </c>
+      <c r="C995">
+        <v>0.7371883397310999</v>
+      </c>
+      <c r="D995" t="s">
+        <v>344</v>
+      </c>
+      <c r="E995">
+        <v>0.8994051856987504</v>
+      </c>
+      <c r="F995">
+        <v>1</v>
+      </c>
+      <c r="G995">
+        <v>0.0164828116602689</v>
+      </c>
+      <c r="H995">
+        <v>0.01694059481430125</v>
+      </c>
+      <c r="I995">
+        <v>0.1622168459676505</v>
+      </c>
+      <c r="J995">
+        <v>1.343483218475921</v>
+      </c>
+      <c r="K995">
+        <v>5.86</v>
+      </c>
+      <c r="L995">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M995">
+        <v>5.97</v>
+      </c>
+      <c r="N995">
+        <v>8.92</v>
+      </c>
+      <c r="O995">
+        <v>1</v>
+      </c>
+      <c r="P995" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="996" spans="1:16">
+      <c r="A996" s="1">
+        <v>0</v>
+      </c>
+      <c r="B996" t="s">
+        <v>190</v>
+      </c>
+      <c r="C996">
+        <v>1.446464800345405</v>
+      </c>
+      <c r="D996" t="s">
+        <v>342</v>
+      </c>
+      <c r="E996">
+        <v>1.016464800345403</v>
+      </c>
+      <c r="F996">
+        <v>-1</v>
+      </c>
+      <c r="G996">
+        <v>0.0174935351996546</v>
+      </c>
+      <c r="H996">
+        <v>0.0170635351996546</v>
+      </c>
+      <c r="I996">
+        <v>0.4300000000000015</v>
+      </c>
+      <c r="J996">
+        <v>1.343975745335778</v>
+      </c>
+      <c r="K996">
+        <v>5.97</v>
+      </c>
+      <c r="L996">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="M996">
+        <v>5.97</v>
+      </c>
+      <c r="N996">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="O996">
+        <v>1</v>
+      </c>
+      <c r="P996" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="997" spans="1:16">
+      <c r="A997" s="1">
+        <v>1</v>
+      </c>
+      <c r="B997" t="s">
+        <v>191</v>
+      </c>
+      <c r="C997">
+        <v>0.7343021323323375</v>
+      </c>
+      <c r="D997" t="s">
+        <v>344</v>
+      </c>
+      <c r="E997">
+        <v>0.8964648003454041</v>
+      </c>
+      <c r="F997">
+        <v>1</v>
+      </c>
+      <c r="G997">
+        <v>0.01648569786766766</v>
+      </c>
+      <c r="H997">
+        <v>0.0169435351996546</v>
+      </c>
+      <c r="I997">
+        <v>0.1621626680130666</v>
+      </c>
+      <c r="J997">
+        <v>1.343975745335778</v>
+      </c>
+      <c r="K997">
+        <v>5.86</v>
+      </c>
+      <c r="L997">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M997">
+        <v>5.97</v>
+      </c>
+      <c r="N997">
+        <v>8.92</v>
+      </c>
+      <c r="O997">
+        <v>1</v>
+      </c>
+      <c r="P997" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="998" spans="1:16">
+      <c r="A998" s="1">
+        <v>0</v>
+      </c>
+      <c r="B998" t="s">
+        <v>190</v>
+      </c>
+      <c r="C998">
+        <v>1.460084502779063</v>
+      </c>
+      <c r="D998" t="s">
+        <v>342</v>
+      </c>
+      <c r="E998">
+        <v>1.030084502779061</v>
+      </c>
+      <c r="F998">
+        <v>-1</v>
+      </c>
+      <c r="G998">
+        <v>0.01747991549722094</v>
+      </c>
+      <c r="H998">
+        <v>0.01704991549722094</v>
+      </c>
+      <c r="I998">
+        <v>0.4300000000000015</v>
+      </c>
+      <c r="J998">
+        <v>1.341694388144211</v>
+      </c>
+      <c r="K998">
+        <v>5.97</v>
+      </c>
+      <c r="L998">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="M998">
+        <v>5.97</v>
+      </c>
+      <c r="N998">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="O998">
+        <v>1</v>
+      </c>
+      <c r="P998" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="999" spans="1:16">
+      <c r="A999" s="1">
+        <v>1</v>
+      </c>
+      <c r="B999" t="s">
+        <v>191</v>
+      </c>
+      <c r="C999">
+        <v>0.7476708854749239</v>
+      </c>
+      <c r="D999" t="s">
+        <v>344</v>
+      </c>
+      <c r="E999">
+        <v>0.9100845027790623</v>
+      </c>
+      <c r="F999">
+        <v>1</v>
+      </c>
+      <c r="G999">
+        <v>0.01647232911452507</v>
+      </c>
+      <c r="H999">
+        <v>0.01692991549722094</v>
+      </c>
+      <c r="I999">
+        <v>0.1624136173041384</v>
+      </c>
+      <c r="J999">
+        <v>1.341694388144211</v>
+      </c>
+      <c r="K999">
+        <v>5.86</v>
+      </c>
+      <c r="L999">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M999">
+        <v>5.97</v>
+      </c>
+      <c r="N999">
+        <v>8.92</v>
+      </c>
+      <c r="O999">
+        <v>1</v>
+      </c>
+      <c r="P999" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:16">
+      <c r="A1000" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1000">
+        <v>1.453089006184717</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>342</v>
+      </c>
+      <c r="E1000">
+        <v>1.023089006184716</v>
+      </c>
+      <c r="F1000">
+        <v>-1</v>
+      </c>
+      <c r="G1000">
+        <v>0.01748691099381528</v>
+      </c>
+      <c r="H1000">
+        <v>0.01705691099381528</v>
+      </c>
+      <c r="I1000">
+        <v>0.4300000000000015</v>
+      </c>
+      <c r="J1000">
+        <v>1.342866163118138</v>
+      </c>
+      <c r="K1000">
+        <v>5.97</v>
+      </c>
+      <c r="L1000">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="M1000">
+        <v>5.97</v>
+      </c>
+      <c r="N1000">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="O1000">
+        <v>1</v>
+      </c>
+      <c r="P1000" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:16">
+      <c r="A1001" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1001">
+        <v>0.7408042841277105</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>344</v>
+      </c>
+      <c r="E1001">
+        <v>0.9030890061847163</v>
+      </c>
+      <c r="F1001">
+        <v>1</v>
+      </c>
+      <c r="G1001">
+        <v>0.01647919571587229</v>
+      </c>
+      <c r="H1001">
+        <v>0.01693691099381528</v>
+      </c>
+      <c r="I1001">
+        <v>0.1622847220570058</v>
+      </c>
+      <c r="J1001">
+        <v>1.342866163118138</v>
+      </c>
+      <c r="K1001">
+        <v>5.86</v>
+      </c>
+      <c r="L1001">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M1001">
+        <v>5.97</v>
+      </c>
+      <c r="N1001">
+        <v>8.92</v>
+      </c>
+      <c r="O1001">
+        <v>1</v>
+      </c>
+      <c r="P1001" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:16">
+      <c r="A1002" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1002">
+        <v>0.7315227730230491</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>344</v>
+      </c>
+      <c r="E1002">
+        <v>0.8936332687623914</v>
+      </c>
+      <c r="F1002">
+        <v>1</v>
+      </c>
+      <c r="G1002">
+        <v>0.01648847722697695</v>
+      </c>
+      <c r="H1002">
+        <v>0.01694636673123761</v>
+      </c>
+      <c r="I1002">
+        <v>0.1621104957393422</v>
+      </c>
+      <c r="J1002">
+        <v>1.344450038733268</v>
+      </c>
+      <c r="K1002">
+        <v>5.86</v>
+      </c>
+      <c r="L1002">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M1002">
+        <v>5.97</v>
+      </c>
+      <c r="N1002">
+        <v>8.92</v>
+      </c>
+      <c r="O1002">
+        <v>1</v>
+      </c>
+      <c r="P1002" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3018" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="458">
   <si>
     <t>trade_time</t>
   </si>
@@ -1045,10 +1045,7 @@
     <t>2021-09-28</t>
   </si>
   <si>
-    <t>2021-09-13</t>
-  </si>
-  <si>
-    <t>2021-10-11</t>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1382,6 +1379,9 @@
   </si>
   <si>
     <t>2021-09-10</t>
+  </si>
+  <si>
+    <t>2021-09-13</t>
   </si>
   <si>
     <t>2021-09-16</t>
@@ -1745,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1002"/>
+  <dimension ref="A1:P1001"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1842,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1892,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1942,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1992,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2042,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2092,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2142,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2442,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2542,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2592,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2642,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2692,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2792,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2842,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3092,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3142,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3192,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3242,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3292,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3342,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3392,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3492,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3542,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3592,7 +3592,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3642,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3942,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3992,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4042,7 +4042,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4092,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4142,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4192,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4242,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4292,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4342,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4392,7 +4392,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4442,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4492,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4542,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4592,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4642,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4692,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4742,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4792,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4842,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4892,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4942,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5392,7 +5392,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5442,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5492,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5542,7 +5542,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5592,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5642,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6042,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6092,7 +6092,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6142,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6192,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6242,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6292,7 +6292,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6542,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6592,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6642,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6692,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6742,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6792,7 +6792,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6842,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6892,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6942,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6992,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7042,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7092,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7142,7 +7142,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7192,7 +7192,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7242,7 +7242,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7292,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7342,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7392,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7442,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7492,7 +7492,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7542,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7592,7 +7592,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7642,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7692,7 +7692,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7742,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7792,7 +7792,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7842,7 +7842,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7892,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7942,7 +7942,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7992,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8042,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8092,7 +8092,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8142,7 +8142,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8192,7 +8192,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8242,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8292,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8342,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8392,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8442,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8492,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8542,7 +8542,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8592,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8642,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8692,7 +8692,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8742,7 +8742,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8792,7 +8792,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8842,7 +8842,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8892,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8942,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8992,7 +8992,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9042,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9092,7 +9092,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9142,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9192,7 +9192,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9442,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9492,7 +9492,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9542,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9592,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9642,7 +9642,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9692,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9742,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9792,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10142,7 +10142,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10242,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10492,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10542,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10592,7 +10592,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10642,7 +10642,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10692,7 +10692,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10742,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10792,7 +10792,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10842,7 +10842,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10892,7 +10892,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10942,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10992,7 +10992,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11042,7 +11042,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11092,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11492,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11742,7 +11742,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11792,7 +11792,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11842,7 +11842,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11892,7 +11892,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11942,7 +11942,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11992,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12042,7 +12042,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12092,7 +12092,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12142,7 +12142,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12192,7 +12192,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12242,7 +12242,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12292,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12342,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12392,7 +12392,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12442,7 +12442,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12492,7 +12492,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12542,7 +12542,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16392,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16442,7 +16442,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16492,7 +16492,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16542,7 +16542,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16592,7 +16592,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16642,7 +16642,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16842,7 +16842,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16892,7 +16892,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16942,7 +16942,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16992,7 +16992,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17042,7 +17042,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17092,7 +17092,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17342,7 +17342,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17392,7 +17392,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17442,7 +17442,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17492,7 +17492,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17542,7 +17542,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17592,7 +17592,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17642,7 +17642,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17692,7 +17692,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17742,7 +17742,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18892,7 +18892,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18942,7 +18942,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18992,7 +18992,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19042,7 +19042,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19092,7 +19092,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19142,7 +19142,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19192,7 +19192,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19242,7 +19242,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19292,7 +19292,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19342,7 +19342,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19942,7 +19942,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19992,7 +19992,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20042,7 +20042,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20092,7 +20092,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20142,7 +20142,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20192,7 +20192,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -21942,7 +21942,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21992,7 +21992,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22042,7 +22042,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22092,7 +22092,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22142,7 +22142,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22192,7 +22192,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22242,7 +22242,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22292,7 +22292,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22342,7 +22342,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22392,7 +22392,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22442,7 +22442,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22492,7 +22492,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22542,7 +22542,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22592,7 +22592,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22642,7 +22642,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22692,7 +22692,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22742,7 +22742,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22792,7 +22792,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22842,7 +22842,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23192,7 +23192,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23242,7 +23242,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23292,7 +23292,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23342,7 +23342,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23392,7 +23392,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23442,7 +23442,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23492,7 +23492,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23542,7 +23542,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23592,7 +23592,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23642,7 +23642,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23692,7 +23692,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23742,7 +23742,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23792,7 +23792,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23842,7 +23842,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23892,7 +23892,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23942,7 +23942,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23992,7 +23992,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24042,7 +24042,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24092,7 +24092,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24142,7 +24142,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24192,7 +24192,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24242,7 +24242,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24642,7 +24642,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24692,7 +24692,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24742,7 +24742,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24792,7 +24792,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24842,7 +24842,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24892,7 +24892,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24942,7 +24942,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25542,7 +25542,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25592,7 +25592,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25642,7 +25642,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25692,7 +25692,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25742,7 +25742,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25792,7 +25792,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25842,7 +25842,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25892,7 +25892,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25942,7 +25942,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25992,7 +25992,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26042,7 +26042,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26092,7 +26092,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26142,7 +26142,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26192,7 +26192,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26242,7 +26242,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26292,7 +26292,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26342,7 +26342,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26392,7 +26392,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26442,7 +26442,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26492,7 +26492,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26692,7 +26692,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26742,7 +26742,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26792,7 +26792,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26842,7 +26842,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26892,7 +26892,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26942,7 +26942,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26992,7 +26992,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27942,7 +27942,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27992,7 +27992,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28042,7 +28042,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29342,7 +29342,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29392,7 +29392,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29442,7 +29442,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29492,7 +29492,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29542,7 +29542,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29592,7 +29592,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29642,7 +29642,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29692,7 +29692,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29742,7 +29742,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29792,7 +29792,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30092,7 +30092,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30142,7 +30142,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30192,7 +30192,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30242,7 +30242,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30292,7 +30292,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30342,7 +30342,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30392,7 +30392,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30442,7 +30442,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30492,7 +30492,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30542,7 +30542,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30592,7 +30592,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30792,7 +30792,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30842,7 +30842,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30892,7 +30892,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30942,7 +30942,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30992,7 +30992,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31042,7 +31042,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31092,7 +31092,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31142,7 +31142,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31192,7 +31192,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31492,7 +31492,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31542,7 +31542,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31592,7 +31592,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31642,7 +31642,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31692,7 +31692,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31742,7 +31742,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31792,7 +31792,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31842,7 +31842,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31892,7 +31892,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31942,7 +31942,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31992,7 +31992,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32042,7 +32042,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32642,7 +32642,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32692,7 +32692,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32742,7 +32742,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32792,7 +32792,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32842,7 +32842,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32892,7 +32892,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32942,7 +32942,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32992,7 +32992,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33042,7 +33042,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33092,7 +33092,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33292,7 +33292,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33342,7 +33342,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33392,7 +33392,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33442,7 +33442,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33492,7 +33492,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34392,7 +34392,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34442,7 +34442,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34492,7 +34492,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34542,7 +34542,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34592,7 +34592,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34642,7 +34642,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34692,7 +34692,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34742,7 +34742,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34792,7 +34792,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35442,7 +35442,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35492,7 +35492,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35542,7 +35542,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35592,7 +35592,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35642,7 +35642,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35692,7 +35692,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35742,7 +35742,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35792,7 +35792,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35842,7 +35842,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36242,7 +36242,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36292,7 +36292,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36342,7 +36342,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36392,7 +36392,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36442,7 +36442,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36492,7 +36492,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36542,7 +36542,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36592,7 +36592,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36642,7 +36642,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36692,7 +36692,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36742,7 +36742,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36792,7 +36792,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36842,7 +36842,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37142,7 +37142,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37192,7 +37192,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37242,7 +37242,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37292,7 +37292,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37592,7 +37592,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37642,7 +37642,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37692,7 +37692,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37742,7 +37742,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37792,7 +37792,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37842,7 +37842,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37892,7 +37892,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37942,7 +37942,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37992,7 +37992,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38042,7 +38042,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38292,7 +38292,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38342,7 +38342,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38392,7 +38392,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38442,7 +38442,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38492,7 +38492,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39092,7 +39092,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39142,7 +39142,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39192,7 +39192,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39242,7 +39242,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39292,7 +39292,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39342,7 +39342,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39392,7 +39392,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39442,7 +39442,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39492,7 +39492,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39542,7 +39542,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40342,7 +40342,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40392,7 +40392,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40442,7 +40442,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40492,7 +40492,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40542,7 +40542,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40592,7 +40592,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40642,7 +40642,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42342,7 +42342,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42392,7 +42392,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42442,7 +42442,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42492,7 +42492,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42542,7 +42542,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43092,7 +43092,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43142,7 +43142,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43192,7 +43192,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43242,7 +43242,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43292,7 +43292,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43342,7 +43342,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43492,7 +43492,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43542,7 +43542,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43592,7 +43592,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43642,7 +43642,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43692,7 +43692,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43742,7 +43742,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43792,7 +43792,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43842,7 +43842,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43892,7 +43892,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43942,7 +43942,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43992,7 +43992,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44042,7 +44042,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44092,7 +44092,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44142,7 +44142,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44192,7 +44192,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44242,7 +44242,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44292,7 +44292,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44342,7 +44342,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44392,7 +44392,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44442,7 +44442,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44742,7 +44742,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44792,7 +44792,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44842,7 +44842,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44892,7 +44892,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -44942,7 +44942,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -44992,7 +44992,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45042,7 +45042,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45092,7 +45092,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45142,7 +45142,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45192,7 +45192,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45242,7 +45242,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45292,7 +45292,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45342,7 +45342,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45392,7 +45392,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45442,7 +45442,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45492,7 +45492,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45542,7 +45542,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45592,7 +45592,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45892,7 +45892,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -45942,7 +45942,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -45992,7 +45992,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46042,7 +46042,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46092,7 +46092,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46342,7 +46342,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46392,7 +46392,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46442,7 +46442,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46492,7 +46492,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46742,7 +46742,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46792,7 +46792,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46842,7 +46842,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46892,7 +46892,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -46942,7 +46942,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -46992,7 +46992,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47042,7 +47042,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47092,7 +47092,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47142,7 +47142,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47192,7 +47192,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47242,7 +47242,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47592,7 +47592,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47642,7 +47642,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47692,7 +47692,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47742,7 +47742,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47792,7 +47792,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47842,7 +47842,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -47892,7 +47892,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -47942,7 +47942,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -47992,7 +47992,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48042,7 +48042,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48092,7 +48092,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48142,7 +48142,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48192,7 +48192,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48242,7 +48242,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48292,7 +48292,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48842,7 +48842,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48892,7 +48892,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -48942,7 +48942,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -48992,7 +48992,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49192,7 +49192,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49242,7 +49242,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49292,7 +49292,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49342,7 +49342,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49392,7 +49392,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49442,7 +49442,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49492,7 +49492,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49542,7 +49542,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49592,7 +49592,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50592,7 +50592,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50642,7 +50642,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50692,7 +50692,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50742,7 +50742,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50792,7 +50792,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50842,7 +50842,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50892,7 +50892,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -50942,7 +50942,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -50956,10 +50956,10 @@
         <v>1.527734083890658</v>
       </c>
       <c r="D985" t="s">
-        <v>342</v>
+        <v>191</v>
       </c>
       <c r="E985">
-        <v>1.097734083890656</v>
+        <v>0.8140739918926707</v>
       </c>
       <c r="F985">
         <v>-1</v>
@@ -50968,10 +50968,10 @@
         <v>0.01741226591610934</v>
       </c>
       <c r="H985">
-        <v>0.01698226591610934</v>
+        <v>0.01640592600810733</v>
       </c>
       <c r="I985">
-        <v>0.4300000000000015</v>
+        <v>0.713660091997987</v>
       </c>
       <c r="J985">
         <v>1.330362800018315</v>
@@ -50983,16 +50983,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="M985">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="N985">
-        <v>9.039999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O985">
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51042,7 +51042,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51056,10 +51056,10 @@
         <v>1.41276333099256</v>
       </c>
       <c r="D987" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E987">
-        <v>1.045026577972973</v>
+        <v>0.9632219394295252</v>
       </c>
       <c r="F987">
         <v>-1</v>
@@ -51068,10 +51068,10 @@
         <v>0.01798723666900744</v>
       </c>
       <c r="H987">
-        <v>0.01799497342202703</v>
+        <v>0.01737677806057047</v>
       </c>
       <c r="I987">
-        <v>0.367736753019587</v>
+        <v>0.4495413915630344</v>
       </c>
       <c r="J987">
         <v>1.340976807282757</v>
@@ -51083,16 +51083,16 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M987">
-        <v>6.32</v>
+        <v>6.12</v>
       </c>
       <c r="N987">
-        <v>9.52</v>
+        <v>9.17</v>
       </c>
       <c r="O987">
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51106,10 +51106,10 @@
         <v>1.464368460521941</v>
       </c>
       <c r="D988" t="s">
-        <v>342</v>
+        <v>191</v>
       </c>
       <c r="E988">
-        <v>1.034368460521939</v>
+        <v>0.7518759093230418</v>
       </c>
       <c r="F988">
         <v>-1</v>
@@ -51118,10 +51118,10 @@
         <v>0.01747563153947806</v>
       </c>
       <c r="H988">
-        <v>0.01704563153947806</v>
+        <v>0.01646812409067696</v>
       </c>
       <c r="I988">
-        <v>0.4300000000000015</v>
+        <v>0.7124925511988991</v>
       </c>
       <c r="J988">
         <v>1.340976807282757</v>
@@ -51133,110 +51133,110 @@
         <v>9.470000000000001</v>
       </c>
       <c r="M988">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="N988">
-        <v>9.039999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O988">
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="989" spans="1:16">
       <c r="A989" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B989" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C989">
-        <v>0.7518759093230418</v>
+        <v>1.488608161168904</v>
       </c>
       <c r="D989" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E989">
-        <v>0.9143684605219402</v>
+        <v>1.058608161168903</v>
       </c>
       <c r="F989">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G989">
-        <v>0.01646812409067696</v>
+        <v>0.01745139183883109</v>
       </c>
       <c r="H989">
-        <v>0.01692563153947806</v>
+        <v>0.0170213918388311</v>
       </c>
       <c r="I989">
-        <v>0.1624925511988984</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J989">
-        <v>1.340976807282757</v>
+        <v>1.336916555918107</v>
       </c>
       <c r="K989">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="L989">
-        <v>8.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M989">
         <v>5.97</v>
       </c>
       <c r="N989">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O989">
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>454</v>
+        <v>189</v>
       </c>
     </row>
     <row r="990" spans="1:16">
       <c r="A990" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B990" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C990">
-        <v>1.488608161168904</v>
+        <v>0.7756689823198943</v>
       </c>
       <c r="D990" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E990">
-        <v>1.058608161168903</v>
+        <v>0.730902359952653</v>
       </c>
       <c r="F990">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G990">
-        <v>0.01745139183883109</v>
+        <v>0.01644433101768011</v>
       </c>
       <c r="H990">
-        <v>0.0170213918388311</v>
+        <v>0.01746909764004734</v>
       </c>
       <c r="I990">
-        <v>0.4300000000000015</v>
+        <v>-0.04476662236724138</v>
       </c>
       <c r="J990">
         <v>1.336916555918107</v>
       </c>
       <c r="K990">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L990">
-        <v>9.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M990">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="N990">
-        <v>9.039999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O990">
         <v>1</v>
@@ -51247,146 +51247,146 @@
     </row>
     <row r="991" spans="1:16">
       <c r="A991" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B991" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C991">
-        <v>0.7756689823198943</v>
+        <v>1.462100210182946</v>
       </c>
       <c r="D991" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E991">
-        <v>0.9386081611689034</v>
+        <v>1.032100210182945</v>
       </c>
       <c r="F991">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G991">
-        <v>0.01644433101768011</v>
+        <v>0.01747789978981706</v>
       </c>
       <c r="H991">
-        <v>0.0169013918388311</v>
+        <v>0.01704789978981705</v>
       </c>
       <c r="I991">
-        <v>0.1629391788490091</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J991">
-        <v>1.336916555918107</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K991">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="L991">
-        <v>8.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M991">
         <v>5.97</v>
       </c>
       <c r="N991">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O991">
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>189</v>
+        <v>454</v>
       </c>
     </row>
     <row r="992" spans="1:16">
       <c r="A992" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B992" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C992">
-        <v>1.462100210182946</v>
+        <v>0.7496494525413828</v>
       </c>
       <c r="D992" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E992">
-        <v>1.032100210182945</v>
+        <v>0.7031067530561543</v>
       </c>
       <c r="F992">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G992">
-        <v>0.01747789978981706</v>
+        <v>0.01647035054745861</v>
       </c>
       <c r="H992">
-        <v>0.01704789978981705</v>
+        <v>0.01749689324694385</v>
       </c>
       <c r="I992">
-        <v>0.4300000000000015</v>
+        <v>-0.04654269948522849</v>
       </c>
       <c r="J992">
         <v>1.341356748713074</v>
       </c>
       <c r="K992">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L992">
-        <v>9.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M992">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="N992">
-        <v>9.039999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O992">
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="993" spans="1:16">
       <c r="A993" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B993" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C993">
-        <v>0.7496494525413828</v>
+        <v>1.449405185698751</v>
       </c>
       <c r="D993" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E993">
-        <v>0.9121002101829454</v>
+        <v>1.01940518569875</v>
       </c>
       <c r="F993">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G993">
-        <v>0.01647035054745861</v>
+        <v>0.01749059481430125</v>
       </c>
       <c r="H993">
-        <v>0.01692789978981706</v>
+        <v>0.01706059481430125</v>
       </c>
       <c r="I993">
-        <v>0.1624507576415626</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J993">
-        <v>1.341356748713074</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K993">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="L993">
-        <v>8.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M993">
         <v>5.97</v>
       </c>
       <c r="N993">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O993">
         <v>1</v>
@@ -51397,146 +51397,146 @@
     </row>
     <row r="994" spans="1:16">
       <c r="A994" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B994" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C994">
-        <v>1.449405185698751</v>
+        <v>0.7371883397310999</v>
       </c>
       <c r="D994" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E994">
-        <v>1.01940518569875</v>
+        <v>0.6897950523407328</v>
       </c>
       <c r="F994">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G994">
-        <v>0.01749059481430125</v>
+        <v>0.0164828116602689</v>
       </c>
       <c r="H994">
-        <v>0.01706059481430125</v>
+        <v>0.01751020494765927</v>
       </c>
       <c r="I994">
-        <v>0.4300000000000015</v>
+        <v>-0.04739328739036708</v>
       </c>
       <c r="J994">
         <v>1.343483218475921</v>
       </c>
       <c r="K994">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L994">
-        <v>9.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M994">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="N994">
-        <v>9.039999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O994">
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>343</v>
+        <v>455</v>
       </c>
     </row>
     <row r="995" spans="1:16">
       <c r="A995" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B995" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C995">
-        <v>0.7371883397310999</v>
+        <v>1.446464800345405</v>
       </c>
       <c r="D995" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E995">
-        <v>0.8994051856987504</v>
+        <v>1.016464800345403</v>
       </c>
       <c r="F995">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G995">
-        <v>0.0164828116602689</v>
+        <v>0.0174935351996546</v>
       </c>
       <c r="H995">
-        <v>0.01694059481430125</v>
+        <v>0.0170635351996546</v>
       </c>
       <c r="I995">
-        <v>0.1622168459676505</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J995">
-        <v>1.343483218475921</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K995">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="L995">
-        <v>8.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M995">
         <v>5.97</v>
       </c>
       <c r="N995">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O995">
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="996" spans="1:16">
       <c r="A996" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B996" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C996">
-        <v>1.446464800345405</v>
+        <v>0.7343021323323375</v>
       </c>
       <c r="D996" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E996">
-        <v>1.016464800345403</v>
+        <v>0.6867118341980269</v>
       </c>
       <c r="F996">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G996">
-        <v>0.0174935351996546</v>
+        <v>0.01648569786766766</v>
       </c>
       <c r="H996">
-        <v>0.0170635351996546</v>
+        <v>0.01751328816580197</v>
       </c>
       <c r="I996">
-        <v>0.4300000000000015</v>
+        <v>-0.04759029813431059</v>
       </c>
       <c r="J996">
         <v>1.343975745335778</v>
       </c>
       <c r="K996">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L996">
-        <v>9.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M996">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="N996">
-        <v>9.039999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O996">
         <v>1</v>
@@ -51547,96 +51547,96 @@
     </row>
     <row r="997" spans="1:16">
       <c r="A997" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B997" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C997">
-        <v>0.7343021323323375</v>
+        <v>1.460084502779063</v>
       </c>
       <c r="D997" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E997">
-        <v>0.8964648003454041</v>
+        <v>1.030084502779061</v>
       </c>
       <c r="F997">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G997">
-        <v>0.01648569786766766</v>
+        <v>0.01747991549722094</v>
       </c>
       <c r="H997">
-        <v>0.0169435351996546</v>
+        <v>0.01704991549722094</v>
       </c>
       <c r="I997">
-        <v>0.1621626680130666</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J997">
-        <v>1.343975745335778</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K997">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="L997">
-        <v>8.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M997">
         <v>5.97</v>
       </c>
       <c r="N997">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O997">
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>341</v>
+        <v>456</v>
       </c>
     </row>
     <row r="998" spans="1:16">
       <c r="A998" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B998" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C998">
-        <v>1.460084502779063</v>
+        <v>0.7476708854749239</v>
       </c>
       <c r="D998" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E998">
-        <v>1.030084502779061</v>
+        <v>0.7009931302172401</v>
       </c>
       <c r="F998">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G998">
-        <v>0.01747991549722094</v>
+        <v>0.01647232911452507</v>
       </c>
       <c r="H998">
-        <v>0.01704991549722094</v>
+        <v>0.01749900686978276</v>
       </c>
       <c r="I998">
-        <v>0.4300000000000015</v>
+        <v>-0.04667775525768381</v>
       </c>
       <c r="J998">
         <v>1.341694388144211</v>
       </c>
       <c r="K998">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L998">
-        <v>9.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M998">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="N998">
-        <v>9.039999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O998">
         <v>1</v>
@@ -51647,96 +51647,96 @@
     </row>
     <row r="999" spans="1:16">
       <c r="A999" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B999" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C999">
-        <v>0.7476708854749239</v>
+        <v>1.453089006184717</v>
       </c>
       <c r="D999" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E999">
-        <v>0.9100845027790623</v>
+        <v>1.023089006184716</v>
       </c>
       <c r="F999">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G999">
-        <v>0.01647232911452507</v>
+        <v>0.01748691099381528</v>
       </c>
       <c r="H999">
-        <v>0.01692991549722094</v>
+        <v>0.01705691099381528</v>
       </c>
       <c r="I999">
-        <v>0.1624136173041384</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J999">
-        <v>1.341694388144211</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K999">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="L999">
-        <v>8.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M999">
         <v>5.97</v>
       </c>
       <c r="N999">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O999">
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
       <c r="A1000" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1000" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C1000">
-        <v>1.453089006184717</v>
+        <v>0.7408042841277105</v>
       </c>
       <c r="D1000" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E1000">
-        <v>1.023089006184716</v>
+        <v>0.6936578188804567</v>
       </c>
       <c r="F1000">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1000">
-        <v>0.01748691099381528</v>
+        <v>0.01647919571587229</v>
       </c>
       <c r="H1000">
-        <v>0.01705691099381528</v>
+        <v>0.01750634218111954</v>
       </c>
       <c r="I1000">
-        <v>0.4300000000000015</v>
+        <v>-0.04714646524725374</v>
       </c>
       <c r="J1000">
         <v>1.342866163118138</v>
       </c>
       <c r="K1000">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L1000">
-        <v>9.470000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M1000">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="N1000">
-        <v>9.039999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O1000">
         <v>1</v>
@@ -51747,34 +51747,34 @@
     </row>
     <row r="1001" spans="1:16">
       <c r="A1001" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1001" t="s">
         <v>191</v>
       </c>
       <c r="C1001">
-        <v>0.7408042841277105</v>
+        <v>0.7315227730230491</v>
       </c>
       <c r="D1001" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E1001">
-        <v>0.9030890061847163</v>
+        <v>0.6837427575297426</v>
       </c>
       <c r="F1001">
         <v>1</v>
       </c>
       <c r="G1001">
-        <v>0.01647919571587229</v>
+        <v>0.01648847722697695</v>
       </c>
       <c r="H1001">
-        <v>0.01693691099381528</v>
+        <v>0.01751625724247026</v>
       </c>
       <c r="I1001">
-        <v>0.1622847220570058</v>
+        <v>-0.04778001549330657</v>
       </c>
       <c r="J1001">
-        <v>1.342866163118138</v>
+        <v>1.344450038733268</v>
       </c>
       <c r="K1001">
         <v>5.86</v>
@@ -51783,65 +51783,15 @@
         <v>8.609999999999999</v>
       </c>
       <c r="M1001">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="N1001">
-        <v>8.92</v>
+        <v>9.1</v>
       </c>
       <c r="O1001">
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:16">
-      <c r="A1002" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>191</v>
-      </c>
-      <c r="C1002">
-        <v>0.7315227730230491</v>
-      </c>
-      <c r="D1002" t="s">
-        <v>344</v>
-      </c>
-      <c r="E1002">
-        <v>0.8936332687623914</v>
-      </c>
-      <c r="F1002">
-        <v>1</v>
-      </c>
-      <c r="G1002">
-        <v>0.01648847722697695</v>
-      </c>
-      <c r="H1002">
-        <v>0.01694636673123761</v>
-      </c>
-      <c r="I1002">
-        <v>0.1621104957393422</v>
-      </c>
-      <c r="J1002">
-        <v>1.344450038733268</v>
-      </c>
-      <c r="K1002">
-        <v>5.86</v>
-      </c>
-      <c r="L1002">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="M1002">
-        <v>5.97</v>
-      </c>
-      <c r="N1002">
-        <v>8.92</v>
-      </c>
-      <c r="O1002">
-        <v>1</v>
-      </c>
-      <c r="P1002" t="s">
         <v>190</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="468">
   <si>
     <t>trade_time</t>
   </si>
@@ -598,9 +598,6 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-09-29</t>
-  </si>
-  <si>
     <t>2021-10-15</t>
   </si>
   <si>
@@ -1057,10 +1054,13 @@
     <t>2021-09-14</t>
   </si>
   <si>
-    <t>2021-10-18</t>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2021-09-28</t>
+  </si>
+  <si>
+    <t>2021-10-18</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1406,6 +1406,12 @@
   </si>
   <si>
     <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-27</t>
+  </si>
+  <si>
+    <t>2021-09-29</t>
   </si>
   <si>
     <t>2021-09-30</t>
@@ -1830,7 +1836,7 @@
         <v>5.028606163154461</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E2">
         <v>4.601827608720447</v>
@@ -1880,7 +1886,7 @@
         <v>5.040216885937453</v>
       </c>
       <c r="D3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E3">
         <v>4.601827608720447</v>
@@ -1930,7 +1936,7 @@
         <v>1.215042657100271</v>
       </c>
       <c r="D4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E4">
         <v>1.076505618462547</v>
@@ -1980,7 +1986,7 @@
         <v>0.9371889532364994</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5">
         <v>1.106505618462547</v>
@@ -2030,7 +2036,7 @@
         <v>0.9964574725553605</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E6">
         <v>1.106505618462547</v>
@@ -2080,7 +2086,7 @@
         <v>1.217920433917637</v>
       </c>
       <c r="D7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E7">
         <v>1.057140807329312</v>
@@ -2130,7 +2136,7 @@
         <v>0.9443593223263207</v>
       </c>
       <c r="D8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E8">
         <v>1.113675987552369</v>
@@ -2180,7 +2186,7 @@
         <v>2.850211426818262</v>
       </c>
       <c r="D9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E9">
         <v>2.672419106455101</v>
@@ -2230,7 +2236,7 @@
         <v>2.543527980245384</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E10">
         <v>2.701305198692955</v>
@@ -2280,7 +2286,7 @@
         <v>2.517978577322106</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E11">
         <v>2.701305198692955</v>
@@ -2330,7 +2336,7 @@
         <v>2.834636854035667</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E12">
         <v>2.682429174398827</v>
@@ -2380,7 +2386,7 @@
         <v>2.827973543350242</v>
       </c>
       <c r="D13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E13">
         <v>2.682429174398827</v>
@@ -2430,7 +2436,7 @@
         <v>2.72973410868421</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E14">
         <v>2.560228587981063</v>
@@ -2480,7 +2486,7 @@
         <v>2.488324529492481</v>
       </c>
       <c r="D15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E15">
         <v>2.59070829553815</v>
@@ -2530,7 +2536,7 @@
         <v>2.403556997401141</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E16">
         <v>2.59070829553815</v>
@@ -2580,7 +2586,7 @@
         <v>2.724996120072402</v>
       </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E17">
         <v>2.564501640775549</v>
@@ -2630,7 +2636,7 @@
         <v>2.694021933218462</v>
       </c>
       <c r="D18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E18">
         <v>2.674021933218462</v>
@@ -2680,7 +2686,7 @@
         <v>2.608852577284488</v>
       </c>
       <c r="D19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E19">
         <v>2.447661659270211</v>
@@ -2730,7 +2736,7 @@
         <v>2.376077393192739</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E20">
         <v>2.47974032888285</v>
@@ -2780,7 +2786,7 @@
         <v>2.288751521812516</v>
       </c>
       <c r="D21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E21">
         <v>2.47974032888285</v>
@@ -2830,7 +2836,7 @@
         <v>2.614987530650434</v>
       </c>
       <c r="D22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E22">
         <v>2.44617844866471</v>
@@ -2880,7 +2886,7 @@
         <v>2.522977458670185</v>
       </c>
       <c r="D23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E23">
         <v>2.36769329484631</v>
@@ -2916,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2930,7 +2936,7 @@
         <v>2.296336211622314</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E24">
         <v>2.400907878726334</v>
@@ -2966,7 +2972,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2980,7 +2986,7 @@
         <v>2.207192877414276</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E25">
         <v>2.400907878726334</v>
@@ -3016,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3030,7 +3036,7 @@
         <v>2.536836629054347</v>
       </c>
       <c r="D26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E26">
         <v>2.362120792878222</v>
@@ -3066,7 +3072,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3080,7 +3086,7 @@
         <v>2.419036917127896</v>
       </c>
       <c r="D27" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E27">
         <v>2.270902102722273</v>
@@ -3130,7 +3136,7 @@
         <v>2.199819994475903</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E28">
         <v>2.305491561490423</v>
@@ -3180,7 +3186,7 @@
         <v>2.108476860446864</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E29">
         <v>2.305491561490423</v>
@@ -3230,7 +3236,7 @@
         <v>2.442245236751312</v>
       </c>
       <c r="D30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E30">
         <v>2.260380051156934</v>
@@ -3280,7 +3286,7 @@
         <v>1.962237985766278</v>
       </c>
       <c r="D31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E31">
         <v>2.333650929502008</v>
@@ -3330,7 +3336,7 @@
         <v>2.093297693568075</v>
       </c>
       <c r="D32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E32">
         <v>2.333650929502008</v>
@@ -3430,7 +3436,7 @@
         <v>2.51400416543594</v>
       </c>
       <c r="D34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E34">
         <v>2.613650929502008</v>
@@ -3480,7 +3486,7 @@
         <v>2.07288858017555</v>
       </c>
       <c r="D35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E35">
         <v>2.313294552836596</v>
@@ -3580,7 +3586,7 @@
         <v>2.493700525497641</v>
       </c>
       <c r="D37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37">
         <v>2.433294552836596</v>
@@ -3630,7 +3636,7 @@
         <v>2.470046771548235</v>
       </c>
       <c r="D38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E38">
         <v>2.433294552836596</v>
@@ -3680,7 +3686,7 @@
         <v>2.057053876296721</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E39">
         <v>2.258557238944802</v>
@@ -3730,7 +3736,7 @@
         <v>2.018009459771084</v>
       </c>
       <c r="D40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E40">
         <v>2.258557238944802</v>
@@ -3830,7 +3836,7 @@
         <v>2.439105018118521</v>
       </c>
       <c r="D42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42">
         <v>2.379105018118521</v>
@@ -3880,7 +3886,7 @@
         <v>2.414175005555058</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E43">
         <v>2.379105018118521</v>
@@ -3930,7 +3936,7 @@
         <v>2.013779087468848</v>
       </c>
       <c r="D44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E44">
         <v>2.203780066898736</v>
@@ -3980,7 +3986,7 @@
         <v>1.999296599035713</v>
       </c>
       <c r="D45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E45">
         <v>2.203780066898736</v>
@@ -4030,7 +4036,7 @@
         <v>1.963090377952877</v>
       </c>
       <c r="D46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E46">
         <v>2.203780066898736</v>
@@ -4230,7 +4236,7 @@
         <v>1.955311973767153</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E50">
         <v>2.149398606925594</v>
@@ -4280,7 +4286,7 @@
         <v>1.941956562224654</v>
       </c>
       <c r="D51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E51">
         <v>2.149398606925594</v>
@@ -4330,7 +4336,7 @@
         <v>1.908568033368406</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E52">
         <v>2.149398606925594</v>
@@ -4430,7 +4436,7 @@
         <v>2.330229180482781</v>
       </c>
       <c r="D54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E54">
         <v>2.239431724239342</v>
@@ -4480,7 +4486,7 @@
         <v>2.395278856453404</v>
       </c>
       <c r="D55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E55">
         <v>2.239431724239342</v>
@@ -4530,7 +4536,7 @@
         <v>2.358568033368406</v>
       </c>
       <c r="D56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E56">
         <v>2.239431724239342</v>
@@ -4580,7 +4586,7 @@
         <v>1.889864833308684</v>
       </c>
       <c r="D57" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E57">
         <v>2.093583493551073</v>
@@ -4630,7 +4636,7 @@
         <v>1.87777105338948</v>
       </c>
       <c r="D58" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E58">
         <v>2.093583493551073</v>
@@ -4680,7 +4686,7 @@
         <v>1.847536603591471</v>
       </c>
       <c r="D59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E59">
         <v>2.093583493551073</v>
@@ -4730,7 +4736,7 @@
         <v>1.937653828490475</v>
       </c>
       <c r="D60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E60">
         <v>2.093583493551073</v>
@@ -4780,7 +4786,7 @@
         <v>1.933466268652069</v>
       </c>
       <c r="D61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E61">
         <v>2.128524881101571</v>
@@ -4830,7 +4836,7 @@
         <v>2.26951315861167</v>
       </c>
       <c r="D62" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E62">
         <v>2.148759330899581</v>
@@ -4880,7 +4886,7 @@
         <v>2.331724163429878</v>
       </c>
       <c r="D63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E63">
         <v>2.148759330899581</v>
@@ -4930,7 +4936,7 @@
         <v>2.297536603591471</v>
       </c>
       <c r="D64" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E64">
         <v>2.148759330899581</v>
@@ -4980,7 +4986,7 @@
         <v>1.775456318615009</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E65">
         <v>2.014299333031558</v>
@@ -5030,7 +5036,7 @@
         <v>1.750249619911568</v>
       </c>
       <c r="D66" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E66">
         <v>2.014299333031558</v>
@@ -5080,7 +5086,7 @@
         <v>1.837852969263289</v>
       </c>
       <c r="D67" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E67">
         <v>2.014299333031558</v>
@@ -5130,7 +5136,7 @@
         <v>1.689340672772246</v>
       </c>
       <c r="D68" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E68">
         <v>2.014299333031558</v>
@@ -5180,7 +5186,7 @@
         <v>1.837687610300537</v>
       </c>
       <c r="D69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E69">
         <v>2.031489284976398</v>
@@ -5230,7 +5236,7 @@
         <v>2.172728950041225</v>
       </c>
       <c r="D70" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E70">
         <v>2.049092634328118</v>
@@ -5280,7 +5286,7 @@
         <v>2.230414978874321</v>
       </c>
       <c r="D71" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E71">
         <v>2.049092634328118</v>
@@ -5330,7 +5336,7 @@
         <v>2.200249619911569</v>
       </c>
       <c r="D72" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E72">
         <v>2.049092634328118</v>
@@ -5380,7 +5386,7 @@
         <v>1.657250003319568</v>
       </c>
       <c r="D73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E73">
         <v>1.914330752922327</v>
@@ -5430,7 +5436,7 @@
         <v>1.742450261803278</v>
       </c>
       <c r="D74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E74">
         <v>1.914330752922327</v>
@@ -5480,7 +5486,7 @@
         <v>1.588410856315811</v>
       </c>
       <c r="D75" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E75">
         <v>1.914330752922327</v>
@@ -5530,7 +5536,7 @@
         <v>2.080209951622827</v>
       </c>
       <c r="D76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E76">
         <v>1.829850132561424</v>
@@ -5580,7 +5586,7 @@
         <v>2.133570416893503</v>
       </c>
       <c r="D77" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E77">
         <v>1.829850132561424</v>
@@ -5630,7 +5636,7 @@
         <v>2.107250003319568</v>
       </c>
       <c r="D78" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E78">
         <v>1.829850132561424</v>
@@ -5680,7 +5686,7 @@
         <v>1.545168899465309</v>
       </c>
       <c r="D79" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E79">
         <v>1.804468343102783</v>
@@ -5730,7 +5736,7 @@
         <v>1.627473005394645</v>
       </c>
       <c r="D80" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E80">
         <v>1.804468343102783</v>
@@ -5780,7 +5786,7 @@
         <v>1.466772449032118</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E81">
         <v>1.804468343102783</v>
@@ -5830,7 +5836,7 @@
         <v>1.551629720651176</v>
       </c>
       <c r="D82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E82">
         <v>1.826938488872376</v>
@@ -5880,7 +5886,7 @@
         <v>1.968708078279442</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E83">
         <v>1.716320952429977</v>
@@ -5930,7 +5936,7 @@
         <v>2.016855468952246</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E84">
         <v>1.716320952429977</v>
@@ -5980,7 +5986,7 @@
         <v>1.995168899465309</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E85">
         <v>1.716320952429977</v>
@@ -6130,7 +6136,7 @@
         <v>1.313264500703522</v>
       </c>
       <c r="D88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E88">
         <v>1.590411561109409</v>
@@ -6180,7 +6186,7 @@
         <v>1.732793914578037</v>
       </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E89">
         <v>1.476117440297638</v>
@@ -6230,7 +6236,7 @@
         <v>1.769911552142724</v>
       </c>
       <c r="D90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E90">
         <v>1.476117440297638</v>
@@ -6280,7 +6286,7 @@
         <v>1.75802920764078</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E91">
         <v>1.476117440297638</v>
@@ -6330,7 +6336,7 @@
         <v>1.258237544033932</v>
       </c>
       <c r="D92" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E92">
         <v>1.56590422061944</v>
@@ -6366,7 +6372,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6380,7 +6386,7 @@
         <v>1.678332787797079</v>
       </c>
       <c r="D93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E93">
         <v>1.525332758040558</v>
@@ -6416,7 +6422,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6430,7 +6436,7 @@
         <v>1.712904190862917</v>
       </c>
       <c r="D94" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E94">
         <v>1.525332758040558</v>
@@ -6466,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6480,7 +6486,7 @@
         <v>1.703285165915505</v>
       </c>
       <c r="D95" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E95">
         <v>1.525332758040558</v>
@@ -6516,7 +6522,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6530,7 +6536,7 @@
         <v>0.5938182775466023</v>
       </c>
       <c r="D96" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E96">
         <v>0.8343117874589812</v>
@@ -6580,7 +6586,7 @@
         <v>0.956860945497624</v>
       </c>
       <c r="D97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E97">
         <v>0.585265392082662</v>
@@ -6630,7 +6636,7 @@
         <v>0.5810056569512305</v>
       </c>
       <c r="D98" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E98">
         <v>0.7840483249022538</v>
@@ -6680,7 +6686,7 @@
         <v>0.5553058141248099</v>
       </c>
       <c r="D99" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E99">
         <v>0.7944238789149818</v>
@@ -6730,7 +6736,7 @@
         <v>0.9198221732781962</v>
       </c>
       <c r="D100" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E100">
         <v>0.5506827718671756</v>
@@ -6780,7 +6786,7 @@
         <v>0.5443598690524336</v>
       </c>
       <c r="D101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E101">
         <v>0.7488762282058206</v>
@@ -6830,7 +6836,7 @@
         <v>0.4093999017952683</v>
       </c>
       <c r="D102" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E102">
         <v>0.6433070411450998</v>
@@ -6880,7 +6886,7 @@
         <v>0.7794993953490197</v>
       </c>
       <c r="D103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E103">
         <v>0.8895325598669377</v>
@@ -6930,7 +6936,7 @@
         <v>0.405525926963354</v>
       </c>
       <c r="D104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E104">
         <v>0.615625420517107</v>
@@ -6980,7 +6986,7 @@
         <v>0.3689689640067657</v>
       </c>
       <c r="D105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E105">
         <v>0.6014321412927224</v>
@@ -7030,7 +7036,7 @@
         <v>0.740615559771812</v>
       </c>
       <c r="D106" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E106">
         <v>0.3833598860468914</v>
@@ -7080,7 +7086,7 @@
         <v>0.3670546519758249</v>
       </c>
       <c r="D107" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E107">
         <v>0.5787012477408719</v>
@@ -7130,7 +7136,7 @@
         <v>0.2652632672207957</v>
       </c>
       <c r="D108" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E108">
         <v>0.494022669621538</v>
@@ -7180,7 +7186,7 @@
         <v>0.6408781932199989</v>
       </c>
       <c r="D109" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E109">
         <v>0.2902364032186728</v>
@@ -7230,7 +7236,7 @@
         <v>0.2683755068197868</v>
       </c>
       <c r="D110" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E110">
         <v>0.4839904328189908</v>
@@ -7280,7 +7286,7 @@
         <v>0.5427390896188848</v>
       </c>
       <c r="D111" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E111">
         <v>0.4852417760190972</v>
@@ -7330,7 +7336,7 @@
         <v>0.2319266556591515</v>
       </c>
       <c r="D112" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E112">
         <v>0.4594954647898355</v>
@@ -7380,7 +7386,7 @@
         <v>0.6088172173048463</v>
       </c>
       <c r="D113" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E113">
         <v>0.2603014867143392</v>
@@ -7430,7 +7436,7 @@
         <v>0.2366547004103658</v>
       </c>
       <c r="D114" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E114">
         <v>0.4535452620560614</v>
@@ -7530,7 +7536,7 @@
         <v>0.1698091881469042</v>
       </c>
       <c r="D116" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E116">
         <v>0.4494895079522143</v>
@@ -7580,7 +7586,7 @@
         <v>0.2222657318159307</v>
       </c>
       <c r="D117" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E117">
         <v>0.4494895079522143</v>
@@ -7630,7 +7636,7 @@
         <v>0.5995259716699124</v>
       </c>
       <c r="D118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E118">
         <v>0.251626371426549</v>
@@ -7680,7 +7686,7 @@
         <v>0.2274620356309747</v>
       </c>
       <c r="D119" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E119">
         <v>0.4447222754849562</v>
@@ -7730,7 +7736,7 @@
         <v>0.1319562177001394</v>
       </c>
       <c r="D120" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E120">
         <v>0.4134136722682085</v>
@@ -7780,7 +7786,7 @@
         <v>0.1874338904658561</v>
       </c>
       <c r="D121" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E121">
         <v>0.4134136722682085</v>
@@ -7830,7 +7836,7 @@
         <v>0.5660269813919063</v>
       </c>
       <c r="D122" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E122">
         <v>0.2203487996019922</v>
@@ -7880,7 +7886,7 @@
         <v>0.1943184723055209</v>
       </c>
       <c r="D123" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E123">
         <v>0.4129115632315719</v>
@@ -7930,7 +7936,7 @@
         <v>0.4849216723303957</v>
       </c>
       <c r="D124" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E124">
         <v>0.4323589087008166</v>
@@ -7980,7 +7986,7 @@
         <v>0.08200931527144117</v>
       </c>
       <c r="D125" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E125">
         <v>0.3658116948361627</v>
@@ -8030,7 +8036,7 @@
         <v>0.1414733605314673</v>
       </c>
       <c r="D126" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E126">
         <v>0.3658116948361627</v>
@@ -8080,7 +8086,7 @@
         <v>0.5218251452050078</v>
       </c>
       <c r="D127" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E127">
         <v>0.1790781196609093</v>
@@ -8130,7 +8136,7 @@
         <v>0.1505856211179522</v>
       </c>
       <c r="D128" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E128">
         <v>0.3709374057914925</v>
@@ -8230,7 +8236,7 @@
         <v>0.1301209626132955</v>
       </c>
       <c r="D130" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E130">
         <v>0.3249118201990129</v>
@@ -8280,7 +8286,7 @@
         <v>0.0390946684846778</v>
       </c>
       <c r="D131" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E131">
         <v>0.3249118201990129</v>
@@ -8330,7 +8336,7 @@
         <v>0.4838466901847962</v>
       </c>
       <c r="D132" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E132">
         <v>0.1436181298277148</v>
@@ -8380,7 +8386,7 @@
         <v>0.1130101205276635</v>
       </c>
       <c r="D133" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E133">
         <v>0.3348729843134146</v>
@@ -8480,7 +8486,7 @@
         <v>0.1185053657063797</v>
       </c>
       <c r="D135" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E135">
         <v>0.3133247628422371</v>
@@ -8530,7 +8536,7 @@
         <v>0.02693682012510568</v>
       </c>
       <c r="D136" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E136">
         <v>0.3133247628422371</v>
@@ -8580,7 +8586,7 @@
         <v>0.4730872797820762</v>
       </c>
       <c r="D137" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E137">
         <v>0.1335722081784905</v>
@@ -8630,7 +8636,7 @@
         <v>0.1023648683255027</v>
       </c>
       <c r="D138" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E138">
         <v>0.3246558253633509</v>
@@ -8680,7 +8686,7 @@
         <v>0.4703213566239093</v>
       </c>
       <c r="D139" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E139">
         <v>0.5140571365749054</v>
@@ -8730,7 +8736,7 @@
         <v>0.1082747062549414</v>
       </c>
       <c r="D140" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E140">
         <v>0.3031192401462075</v>
@@ -8780,7 +8786,7 @@
         <v>0.01622856232089642</v>
       </c>
       <c r="D141" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E141">
         <v>0.3031192401462075</v>
@@ -8830,7 +8836,7 @@
         <v>0.4636107229929056</v>
       </c>
       <c r="D142" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E142">
         <v>0.1247240702745431</v>
@@ -8880,7 +8886,7 @@
         <v>0.0929888585579679</v>
       </c>
       <c r="D143" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E143">
         <v>0.3156568669269504</v>
@@ -8930,7 +8936,7 @@
         <v>0.4619256803173224</v>
       </c>
       <c r="D144" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E144">
         <v>0.4194382225775701</v>
@@ -8980,7 +8986,7 @@
         <v>0.1029539075611501</v>
       </c>
       <c r="D145" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E145">
         <v>0.2978115146678801</v>
@@ -9030,7 +9036,7 @@
         <v>0.01065937253329263</v>
       </c>
       <c r="D146" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E146">
         <v>0.2978115146678801</v>
@@ -9080,7 +9086,7 @@
         <v>0.4586821207630312</v>
       </c>
       <c r="D147" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E147">
         <v>0.1201222984312649</v>
@@ -9130,7 +9136,7 @@
         <v>0.08811254918994837</v>
       </c>
       <c r="D148" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E148">
         <v>0.3109766557908884</v>
@@ -9180,7 +9186,7 @@
         <v>0.4575592263523935</v>
       </c>
       <c r="D149" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E149">
         <v>0.3255657258466043</v>
@@ -9230,7 +9236,7 @@
         <v>0.02638546696888966</v>
       </c>
       <c r="D150" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E150">
         <v>0.3127992948107261</v>
@@ -9280,7 +9286,7 @@
         <v>0.4725993451813872</v>
       </c>
       <c r="D151" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E151">
         <v>0.1331166299836823</v>
@@ -9330,7 +9336,7 @@
         <v>0.101882110749755</v>
       </c>
       <c r="D152" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E152">
         <v>0.3241924816311323</v>
@@ -9430,7 +9436,7 @@
         <v>0.08340592620937315</v>
       </c>
       <c r="D154" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E154">
         <v>0.3671427371854588</v>
@@ -9480,7 +9486,7 @@
         <v>0.5230611131007823</v>
       </c>
       <c r="D155" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E155">
         <v>0.18023212682089</v>
@@ -9530,7 +9536,7 @@
         <v>0.1518084752959998</v>
       </c>
       <c r="D156" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E156">
         <v>0.3721110835280639</v>
@@ -9630,7 +9636,7 @@
         <v>0.1326336220486173</v>
       </c>
       <c r="D158" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E158">
         <v>0.4140592735956314</v>
@@ -9680,7 +9686,7 @@
         <v>0.5666264683387991</v>
       </c>
       <c r="D159" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E159">
         <v>0.2209085327725662</v>
@@ -9730,7 +9736,7 @@
         <v>0.2697669895764108</v>
       </c>
       <c r="D160" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E160">
         <v>0.4134808373084624</v>
@@ -9830,7 +9836,7 @@
         <v>0.5970514875023341</v>
       </c>
       <c r="D162" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E162">
         <v>0.2493159777210128</v>
@@ -9880,7 +9886,7 @@
         <v>0.2989007612422894</v>
       </c>
       <c r="D163" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E163">
         <v>0.4423725000685295</v>
@@ -9980,7 +9986,7 @@
         <v>0.8264673601681558</v>
       </c>
       <c r="D165" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E165">
         <v>0.9378275992619312</v>
@@ -10016,7 +10022,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10030,7 +10036,7 @@
         <v>0.8485077188088193</v>
       </c>
       <c r="D166" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E166">
         <v>0.9378275992619312</v>
@@ -10066,7 +10072,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10080,7 +10086,7 @@
         <v>1.04238664288683</v>
       </c>
       <c r="D167" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E167">
         <v>0.885879418334687</v>
@@ -10116,7 +10122,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10130,7 +10136,7 @@
         <v>0.8582684061162329</v>
       </c>
       <c r="D168" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E168">
         <v>0.9701707084932139</v>
@@ -10180,7 +10186,7 @@
         <v>0.8811218596817048</v>
       </c>
       <c r="D169" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E169">
         <v>0.9701707084932139</v>
@@ -10230,7 +10236,7 @@
         <v>1.072561498985289</v>
       </c>
       <c r="D170" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E170">
         <v>0.9147894601056654</v>
@@ -10280,7 +10286,7 @@
         <v>0.890454471710437</v>
       </c>
       <c r="D171" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E171">
         <v>1.002905400205501</v>
@@ -10316,7 +10322,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10330,7 +10336,7 @@
         <v>0.9141308644530337</v>
       </c>
       <c r="D172" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E172">
         <v>1.002905400205501</v>
@@ -10366,7 +10372,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10380,7 +10386,7 @@
         <v>1.063379316961259</v>
       </c>
       <c r="D173" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E173">
         <v>0.9440495197367609</v>
@@ -10416,7 +10422,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10430,7 +10436,7 @@
         <v>1.103101686225244</v>
       </c>
       <c r="D174" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E174">
         <v>0.9440495197367609</v>
@@ -10466,7 +10472,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10480,7 +10486,7 @@
         <v>0.8952216225869147</v>
       </c>
       <c r="D175" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E175">
         <v>1.007753809335554</v>
@@ -10530,7 +10536,7 @@
         <v>0.9190199027098753</v>
       </c>
       <c r="D176" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E176">
         <v>1.007753809335554</v>
@@ -10580,7 +10586,7 @@
         <v>1.066108600501315</v>
       </c>
       <c r="D177" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E177">
         <v>0.9483832932608314</v>
@@ -10630,7 +10636,7 @@
         <v>1.068132924795474</v>
       </c>
       <c r="D178" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E178">
         <v>0.9483832932608314</v>
@@ -10680,7 +10686,7 @@
         <v>1.107625062340992</v>
       </c>
       <c r="D179" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E179">
         <v>0.9483832932608314</v>
@@ -10780,7 +10786,7 @@
         <v>0.9002742157630061</v>
       </c>
       <c r="D181" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E181">
         <v>1.012892526258966</v>
@@ -10830,7 +10836,7 @@
         <v>0.924201681506946</v>
       </c>
       <c r="D182" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E182">
         <v>1.012892526258966</v>
@@ -10880,7 +10886,7 @@
         <v>1.071304733256273</v>
       </c>
       <c r="D183" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E183">
         <v>0.9529765597845508</v>
@@ -10930,7 +10936,7 @@
         <v>1.073171164013679</v>
       </c>
       <c r="D184" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E184">
         <v>0.9529765597845508</v>
@@ -10980,7 +10986,7 @@
         <v>1.112419284275125</v>
       </c>
       <c r="D185" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E185">
         <v>0.9529765597845508</v>
@@ -11130,7 +11136,7 @@
         <v>1.074651024327075</v>
       </c>
       <c r="D188" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E188">
         <v>0.9559346071399553</v>
@@ -11180,7 +11186,7 @@
         <v>1.076415772206639</v>
       </c>
       <c r="D189" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E189">
         <v>0.9559346071399553</v>
@@ -11230,7 +11236,7 @@
         <v>1.115506746202329</v>
       </c>
       <c r="D190" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E190">
         <v>0.9559346071399553</v>
@@ -11330,7 +11336,7 @@
         <v>1.1321100696318</v>
       </c>
       <c r="D192" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E192">
         <v>0.9718419828807665</v>
@@ -11430,7 +11436,7 @@
         <v>1.161282995049877</v>
       </c>
       <c r="D194" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E194">
         <v>0.9997920910657498</v>
@@ -11480,7 +11486,7 @@
         <v>1.18828947410149</v>
       </c>
       <c r="D195" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E195">
         <v>1.025666562013403</v>
@@ -11530,7 +11536,7 @@
         <v>1.215609088742732</v>
       </c>
       <c r="D196" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E196">
         <v>1.051841043106808</v>
@@ -11580,7 +11586,7 @@
         <v>1.240067525701835</v>
       </c>
       <c r="D197" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E197">
         <v>1.075274276121518</v>
@@ -11616,7 +11622,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11666,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11716,7 +11722,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11730,7 +11736,7 @@
         <v>1.268045594928877</v>
       </c>
       <c r="D200" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E200">
         <v>1.102079611907905</v>
@@ -11880,7 +11886,7 @@
         <v>1.286712805706288</v>
       </c>
       <c r="D203" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E203">
         <v>1.119964364748539</v>
@@ -11980,7 +11986,7 @@
         <v>1.302282242677217</v>
       </c>
       <c r="D205" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E205">
         <v>1.13488119058895</v>
@@ -12080,7 +12086,7 @@
         <v>1.311299224369049</v>
       </c>
       <c r="D207" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E207">
         <v>1.143520214964358</v>
@@ -13466,7 +13472,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13516,7 +13522,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13566,7 +13572,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13580,7 +13586,7 @@
         <v>0.8200792964932733</v>
       </c>
       <c r="D237" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E237">
         <v>0.8219030850898417</v>
@@ -13616,7 +13622,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13630,7 +13636,7 @@
         <v>0.937074891230151</v>
       </c>
       <c r="D238" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E238">
         <v>0.8219030850898417</v>
@@ -13666,7 +13672,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13780,7 +13786,7 @@
         <v>0.8190773400228082</v>
       </c>
       <c r="D241" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E241">
         <v>0.8460555597919894</v>
@@ -13830,7 +13836,7 @@
         <v>0.9360555597919893</v>
       </c>
       <c r="D242" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E242">
         <v>0.8460555597919894</v>
@@ -14116,7 +14122,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14166,7 +14172,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14216,7 +14222,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14266,7 +14272,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14280,7 +14286,7 @@
         <v>0.7963991260233625</v>
       </c>
       <c r="D251" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E251">
         <v>0.848389834527401</v>
@@ -14316,7 +14322,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14330,7 +14336,7 @@
         <v>0.8040407192610317</v>
       </c>
       <c r="D252" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E252">
         <v>0.848389834527401</v>
@@ -14366,7 +14372,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14916,7 +14922,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14966,7 +14972,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15016,7 +15022,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15066,7 +15072,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15116,7 +15122,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15166,7 +15172,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15216,7 +15222,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15266,7 +15272,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15316,7 +15322,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15330,7 +15336,7 @@
         <v>0.709400862280603</v>
       </c>
       <c r="D272" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E272">
         <v>0.7643754237703098</v>
@@ -15366,7 +15372,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15380,7 +15386,7 @@
         <v>0.7145280548320647</v>
       </c>
       <c r="D273" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E273">
         <v>0.7643754237703098</v>
@@ -15416,7 +15422,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15430,7 +15436,7 @@
         <v>0.749400862280603</v>
       </c>
       <c r="D274" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E274">
         <v>0.7643754237703098</v>
@@ -15466,7 +15472,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15516,7 +15522,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15566,7 +15572,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15616,7 +15622,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15630,7 +15636,7 @@
         <v>0.6652568429569481</v>
       </c>
       <c r="D278" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E278">
         <v>0.7257163014198733</v>
@@ -15666,7 +15672,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15680,7 +15686,7 @@
         <v>0.669108196799634</v>
       </c>
       <c r="D279" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E279">
         <v>0.7257163014198733</v>
@@ -15716,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15730,7 +15736,7 @@
         <v>0.7052568429569481</v>
       </c>
       <c r="D280" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E280">
         <v>0.7257163014198733</v>
@@ -15766,7 +15772,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -16230,7 +16236,7 @@
         <v>0.5098981945395424</v>
       </c>
       <c r="D290" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E290">
         <v>0.4597052829411883</v>
@@ -16280,7 +16286,7 @@
         <v>0.4670290224146925</v>
       </c>
       <c r="D291" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E291">
         <v>0.4597052829411883</v>
@@ -16330,7 +16336,7 @@
         <v>0.4288915341107993</v>
       </c>
       <c r="D292" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E292">
         <v>0.4597052829411883</v>
@@ -16630,7 +16636,7 @@
         <v>0.3683952712899403</v>
       </c>
       <c r="D298" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E298">
         <v>0.375715173934144</v>
@@ -16780,7 +16786,7 @@
         <v>0.3328925326816705</v>
       </c>
       <c r="D301" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E301">
         <v>0.3761370628624148</v>
@@ -17180,7 +17186,7 @@
         <v>0.2591964526318904</v>
       </c>
       <c r="D309" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E309">
         <v>0.1842681443037231</v>
@@ -17230,7 +17236,7 @@
         <v>0.1964622097836042</v>
       </c>
       <c r="D310" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E310">
         <v>0.1842681443037231</v>
@@ -17280,7 +17286,7 @@
         <v>0.2493398359755563</v>
       </c>
       <c r="D311" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E311">
         <v>0.1842681443037231</v>
@@ -17330,7 +17336,7 @@
         <v>0.2221683550801181</v>
       </c>
       <c r="D312" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E312">
         <v>0.1904669351684678</v>
@@ -17380,7 +17386,7 @@
         <v>0.1768500318498596</v>
       </c>
       <c r="D313" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E313">
         <v>0.1904669351684678</v>
@@ -17430,7 +17436,7 @@
         <v>0.2296162252126424</v>
       </c>
       <c r="D314" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E314">
         <v>0.1904669351684678</v>
@@ -17480,7 +17486,7 @@
         <v>0.2053553502696301</v>
       </c>
       <c r="D315" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E315">
         <v>0.1123646202766642</v>
@@ -17530,7 +17536,7 @@
         <v>0.1596958936084336</v>
       </c>
       <c r="D316" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E316">
         <v>0.1123646202766642</v>
@@ -17580,7 +17586,7 @@
         <v>0.1543584402719747</v>
       </c>
       <c r="D317" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E317">
         <v>0.1123646202766642</v>
@@ -17680,7 +17686,7 @@
         <v>0.1340998453989064</v>
       </c>
       <c r="D319" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E319">
         <v>0.08288478726310178</v>
@@ -17730,7 +17736,7 @@
         <v>0.129053256246646</v>
       </c>
       <c r="D320" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E320">
         <v>0.08288478726310178</v>
@@ -17830,7 +17836,7 @@
         <v>0.1049880441022522</v>
       </c>
       <c r="D322" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E322">
         <v>0.1511669874093613</v>
@@ -17880,7 +17886,7 @@
         <v>0.100272270873818</v>
       </c>
       <c r="D323" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E323">
         <v>0.1511669874093613</v>
@@ -18180,7 +18186,7 @@
         <v>0.02103995734812436</v>
       </c>
       <c r="D329" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E329">
         <v>0.06193314098385727</v>
@@ -18230,7 +18236,7 @@
         <v>0.0172781396509869</v>
       </c>
       <c r="D330" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E330">
         <v>0.06193314098385727</v>
@@ -18280,7 +18286,7 @@
         <v>-0.03024549574328894</v>
       </c>
       <c r="D331" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E331">
         <v>0.06193314098385727</v>
@@ -18480,7 +18486,7 @@
         <v>-0.02692077305540685</v>
       </c>
       <c r="D335" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E335">
         <v>0.02601619170547753</v>
@@ -18530,7 +18536,7 @@
         <v>-0.03013758245250386</v>
       </c>
       <c r="D336" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E336">
         <v>0.02601619170547753</v>
@@ -18580,7 +18586,7 @@
         <v>-0.07657120124669881</v>
       </c>
       <c r="D337" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E337">
         <v>0.02601619170547753</v>
@@ -18730,7 +18736,7 @@
         <v>-0.0666863454204627</v>
       </c>
       <c r="D340" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E340">
         <v>0.05932763892745285</v>
@@ -18780,7 +18786,7 @@
         <v>-0.06945127331341183</v>
       </c>
       <c r="D341" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E341">
         <v>0.05932763892745285</v>
@@ -18830,7 +18836,7 @@
         <v>-0.1149811290993101</v>
       </c>
       <c r="D342" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E342">
         <v>0.05932763892745285</v>
@@ -18980,7 +18986,7 @@
         <v>-0.1222098013248543</v>
       </c>
       <c r="D345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E345">
         <v>0.03478777543614875</v>
@@ -19030,7 +19036,7 @@
         <v>-0.124343780855253</v>
       </c>
       <c r="D346" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E346">
         <v>0.03478777543614875</v>
@@ -19080,7 +19086,7 @@
         <v>-0.1686117399160514</v>
       </c>
       <c r="D347" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E347">
         <v>0.03478777543614875</v>
@@ -19230,7 +19236,7 @@
         <v>-0.1678666819248154</v>
       </c>
       <c r="D350" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E350">
         <v>-0.008923499456428452</v>
@@ -19280,7 +19286,7 @@
         <v>-0.1694818332665786</v>
       </c>
       <c r="D351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E351">
         <v>-0.008923499456428452</v>
@@ -19330,7 +19336,7 @@
         <v>-0.2127121359501061</v>
       </c>
       <c r="D352" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E352">
         <v>-0.008923499456428452</v>
@@ -19480,7 +19486,7 @@
         <v>-0.2230704748734498</v>
       </c>
       <c r="D355" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E355">
         <v>-0.06177485804645588</v>
@@ -19530,7 +19536,7 @@
         <v>-0.2240583103862512</v>
       </c>
       <c r="D356" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E356">
         <v>-0.06177485804645588</v>
@@ -19580,7 +19586,7 @@
         <v>-0.2660339814118542</v>
       </c>
       <c r="D357" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E357">
         <v>-0.06177485804645588</v>
@@ -19730,7 +19736,7 @@
         <v>-0.2547475324515673</v>
       </c>
       <c r="D360" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E360">
         <v>-0.09210204101187003</v>
@@ -19780,7 +19786,7 @@
         <v>-0.2553754014009808</v>
       </c>
       <c r="D361" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E361">
         <v>-0.09210204101187003</v>
@@ -19830,7 +19836,7 @@
         <v>-0.2966311392998087</v>
       </c>
       <c r="D362" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E362">
         <v>-0.09210204101187003</v>
@@ -19880,7 +19886,7 @@
         <v>0.1392877125289997</v>
       </c>
       <c r="D363" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E363">
         <v>0.06960164700370619</v>
@@ -20030,7 +20036,7 @@
         <v>-0.2851514146282588</v>
       </c>
       <c r="D366" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E366">
         <v>-0.1212103032094403</v>
@@ -20080,7 +20086,7 @@
         <v>-0.2854337849165738</v>
       </c>
       <c r="D367" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E367">
         <v>-0.1212103032094403</v>
@@ -20130,7 +20136,7 @@
         <v>-0.3259985254932039</v>
       </c>
       <c r="D368" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E368">
         <v>-0.1212103032094403</v>
@@ -20180,7 +20186,7 @@
         <v>0.1121660676327467</v>
       </c>
       <c r="D369" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E369">
         <v>-0.02205741407438655</v>
@@ -20280,7 +20286,7 @@
         <v>-0.3208678237650178</v>
       </c>
       <c r="D371" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E371">
         <v>-0.1554047062750312</v>
@@ -20330,7 +20336,7 @@
         <v>-0.3207443257676879</v>
       </c>
       <c r="D372" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E372">
         <v>-0.1554047062750312</v>
@@ -20380,7 +20386,7 @@
         <v>-0.3604973297730281</v>
       </c>
       <c r="D373" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E373">
         <v>-0.1554047062750312</v>
@@ -20430,7 +20436,7 @@
         <v>0.08030540720961454</v>
       </c>
       <c r="D374" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E374">
         <v>-0.1700650867823734</v>
@@ -20530,7 +20536,7 @@
         <v>-0.345691858448542</v>
       </c>
       <c r="D376" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E376">
         <v>-0.1791708985714733</v>
@@ -20580,7 +20586,7 @@
         <v>-0.3452862691479899</v>
       </c>
       <c r="D377" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E377">
         <v>-0.1791708985714733</v>
@@ -20630,7 +20636,7 @@
         <v>-0.3844750905468866</v>
       </c>
       <c r="D378" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E378">
         <v>-0.1791708985714733</v>
@@ -20780,7 +20786,7 @@
         <v>-0.3598244404072002</v>
       </c>
       <c r="D381" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E381">
         <v>-0.1927012398216661</v>
@@ -20830,7 +20836,7 @@
         <v>-0.3592582535843913</v>
       </c>
       <c r="D382" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E382">
         <v>-0.1927012398216661</v>
@@ -20880,7 +20886,7 @@
         <v>-0.3981258799387728</v>
       </c>
       <c r="D383" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E383">
         <v>-0.1927012398216661</v>
@@ -20930,7 +20936,7 @@
         <v>0.04555433440948597</v>
       </c>
       <c r="D384" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E384">
         <v>-0.07331329194489644</v>
@@ -20980,7 +20986,7 @@
         <v>-0.03472875900191852</v>
       </c>
       <c r="D385" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E385">
         <v>-0.07331329194489644</v>
@@ -21080,7 +21086,7 @@
         <v>-0.3763080661355378</v>
       </c>
       <c r="D387" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E387">
         <v>-0.2084824383172617</v>
@@ -21130,7 +21136,7 @@
         <v>-0.3755545653839976</v>
       </c>
       <c r="D388" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E388">
         <v>-0.2084824383172617</v>
@@ -21180,7 +21186,7 @@
         <v>-0.4140475638809171</v>
       </c>
       <c r="D389" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E389">
         <v>-0.2084824383172617</v>
@@ -21230,7 +21236,7 @@
         <v>0.03085019100409347</v>
       </c>
       <c r="D390" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E390">
         <v>-0.09764280749282594</v>
@@ -21280,7 +21286,7 @@
         <v>-0.04952655937167627</v>
       </c>
       <c r="D391" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E391">
         <v>-0.09764280749282594</v>
@@ -21380,7 +21386,7 @@
         <v>-0.4007277092358548</v>
       </c>
       <c r="D393" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E393">
         <v>-0.2318614716263721</v>
@@ -21430,7 +21436,7 @@
         <v>-0.3996967125399919</v>
       </c>
       <c r="D394" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E394">
         <v>-0.2318614716263721</v>
@@ -21480,7 +21486,7 @@
         <v>-0.4376347191482681</v>
       </c>
       <c r="D395" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E395">
         <v>-0.2318614716263721</v>
@@ -21530,7 +21536,7 @@
         <v>0.009066759374833921</v>
       </c>
       <c r="D396" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E396">
         <v>-0.1304177422772348</v>
@@ -21580,7 +21586,7 @@
         <v>-0.07144873897309711</v>
       </c>
       <c r="D397" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E397">
         <v>-0.1304177422772348</v>
@@ -21680,7 +21686,7 @@
         <v>-0.4077205864393338</v>
       </c>
       <c r="D399" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E399">
         <v>-0.2385563569035662</v>
@@ -21730,7 +21736,7 @@
         <v>-0.406610125229796</v>
       </c>
       <c r="D400" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E400">
         <v>-0.2385563569035662</v>
@@ -21780,7 +21786,7 @@
         <v>-0.4443892028107195</v>
       </c>
       <c r="D401" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E401">
         <v>-0.2385563569035662</v>
@@ -21830,7 +21836,7 @@
         <v>0.002828795051275534</v>
       </c>
       <c r="D402" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E402">
         <v>0.005604948075121463</v>
@@ -21880,7 +21886,7 @@
         <v>-0.07772643555349301</v>
       </c>
       <c r="D403" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E403">
         <v>0.005604948075121463</v>
@@ -21930,7 +21936,7 @@
         <v>0.4861229225744816</v>
       </c>
       <c r="D404" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E404">
         <v>0.1770614712898908</v>
@@ -21980,7 +21986,7 @@
         <v>0.4461229225744816</v>
       </c>
       <c r="D405" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E405">
         <v>0.1770614712898908</v>
@@ -22030,7 +22036,7 @@
         <v>0.4906257158146907</v>
       </c>
       <c r="D406" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E406">
         <v>0.1770614712898908</v>
@@ -22080,7 +22086,7 @@
         <v>0.4546033698930207</v>
       </c>
       <c r="D407" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E407">
         <v>0.1770614712898908</v>
@@ -22130,7 +22136,7 @@
         <v>0.4875866104517694</v>
       </c>
       <c r="D408" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E408">
         <v>0.1770614712898908</v>
@@ -22180,7 +22186,7 @@
         <v>-0.02241338954823124</v>
       </c>
       <c r="D409" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E409">
         <v>0.3145475050888473</v>
@@ -22230,7 +22236,7 @@
         <v>0.05951957268676189</v>
       </c>
       <c r="D410" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E410">
         <v>0.3145475050888473</v>
@@ -22280,7 +22286,7 @@
         <v>0.1380000200053004</v>
       </c>
       <c r="D411" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E411">
         <v>0.3145475050888473</v>
@@ -22330,7 +22336,7 @@
         <v>0.1180000200053</v>
       </c>
       <c r="D412" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E412">
         <v>0.03700560648571827</v>
@@ -22380,7 +22386,7 @@
         <v>0.1260111929661347</v>
       </c>
       <c r="D413" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E413">
         <v>0.03700560648571827</v>
@@ -22430,7 +22436,7 @@
         <v>0.4959765202796076</v>
       </c>
       <c r="D414" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E414">
         <v>0.1876054484520644</v>
@@ -22480,7 +22486,7 @@
         <v>0.4559765202796076</v>
       </c>
       <c r="D415" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E415">
         <v>0.1876054484520644</v>
@@ -22530,7 +22536,7 @@
         <v>0.5004479326354057</v>
       </c>
       <c r="D416" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E416">
         <v>0.1876054484520644</v>
@@ -22580,7 +22586,7 @@
         <v>0.4646766337890256</v>
       </c>
       <c r="D417" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E417">
         <v>0.1876054484520644</v>
@@ -22630,7 +22636,7 @@
         <v>0.4978481596542412</v>
       </c>
       <c r="D418" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E418">
         <v>0.1876054484520644</v>
@@ -22680,7 +22686,7 @@
         <v>-0.01215184034575945</v>
       </c>
       <c r="D419" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E419">
         <v>0.3252483866730769</v>
@@ -22730,7 +22736,7 @@
         <v>0.07053426311510336</v>
       </c>
       <c r="D420" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E420">
         <v>0.3252483866730769</v>
@@ -22780,7 +22786,7 @@
         <v>0.1292343766245203</v>
       </c>
       <c r="D421" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E421">
         <v>0.1050056754708999</v>
@@ -22830,7 +22836,7 @@
         <v>0.1371200260477101</v>
       </c>
       <c r="D422" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E422">
         <v>0.1050056754708999</v>
@@ -22880,7 +22886,7 @@
         <v>0.2644553699245202</v>
       </c>
       <c r="D423" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E423">
         <v>0.5136446756246755</v>
@@ -22930,7 +22936,7 @@
         <v>0.3066175087844885</v>
       </c>
       <c r="D424" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E424">
         <v>0.4518878839146296</v>
@@ -22980,7 +22986,7 @@
         <v>0.5375636061946913</v>
       </c>
       <c r="D425" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E425">
         <v>0.3814825367647066</v>
@@ -23030,7 +23036,7 @@
         <v>0.5533747315851132</v>
       </c>
       <c r="D426" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E426">
         <v>0.5155368704450822</v>
@@ -23080,7 +23086,7 @@
         <v>0.5455368704450816</v>
       </c>
       <c r="D427" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E427">
         <v>0.5155368704450822</v>
@@ -23130,7 +23136,7 @@
         <v>0.5472936621551279</v>
       </c>
       <c r="D428" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E428">
         <v>0.5155368704450822</v>
@@ -23180,7 +23186,7 @@
         <v>0.269705945999557</v>
       </c>
       <c r="D429" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E429">
         <v>0.5187456626377447</v>
@@ -23230,7 +23236,7 @@
         <v>0.3323781443528233</v>
       </c>
       <c r="D430" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E430">
         <v>0.4558019743357367</v>
@@ -23280,7 +23286,7 @@
         <v>0.5426496343015641</v>
       </c>
       <c r="D431" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E431">
         <v>0.3865536059653829</v>
@@ -23330,7 +23336,7 @@
         <v>0.5580568692246759</v>
       </c>
       <c r="D432" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E432">
         <v>0.4290171525864865</v>
@@ -23380,7 +23386,7 @@
         <v>0.5502489258970371</v>
       </c>
       <c r="D433" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E433">
         <v>0.4290171525864865</v>
@@ -23430,7 +23436,7 @@
         <v>0.5519608408884942</v>
       </c>
       <c r="D434" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E434">
         <v>0.4290171525864865</v>
@@ -23480,7 +23486,7 @@
         <v>0.2827549913852314</v>
       </c>
       <c r="D435" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E435">
         <v>0.5314229403486141</v>
@@ -23530,7 +23536,7 @@
         <v>0.3656874271108617</v>
       </c>
       <c r="D436" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E436">
         <v>0.5314229403486141</v>
@@ -23580,7 +23586,7 @@
         <v>0.5414229403486139</v>
       </c>
       <c r="D437" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E437">
         <v>0.3827549913852311</v>
@@ -23630,7 +23636,7 @@
         <v>0.3456874271108612</v>
       </c>
       <c r="D438" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E438">
         <v>0.4688881964888916</v>
@@ -23680,7 +23686,7 @@
         <v>0.5552897352449522</v>
       </c>
       <c r="D439" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E439">
         <v>0.3991565301412905</v>
@@ -23730,7 +23736,7 @@
         <v>0.5696931974460888</v>
       </c>
       <c r="D440" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E440">
         <v>0.4410252484827053</v>
@@ -23780,7 +23786,7 @@
         <v>0.5619596076534119</v>
       </c>
       <c r="D441" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E441">
         <v>0.4410252484827053</v>
@@ -23830,7 +23836,7 @@
         <v>0.5635599923424266</v>
       </c>
       <c r="D442" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E442">
         <v>0.4410252484827053</v>
@@ -23880,7 +23886,7 @@
         <v>0.2818837012820081</v>
       </c>
       <c r="D443" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E443">
         <v>0.5305764733252545</v>
@@ -23930,7 +23936,7 @@
         <v>0.364798760851734</v>
       </c>
       <c r="D444" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E444">
         <v>0.5305764733252545</v>
@@ -23980,7 +23986,7 @@
         <v>0.5405764733252543</v>
       </c>
       <c r="D445" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E445">
         <v>0.3818837012820078</v>
@@ -24030,7 +24036,7 @@
         <v>0.3447987608517336</v>
       </c>
       <c r="D446" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E446">
         <v>0.4680144240776825</v>
@@ -24080,7 +24086,7 @@
         <v>0.5544457505295792</v>
       </c>
       <c r="D447" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E447">
         <v>0.3983150277339043</v>
@@ -24130,7 +24136,7 @@
         <v>0.5689162350463484</v>
       </c>
       <c r="D448" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E448">
         <v>0.4402234630031003</v>
@@ -24180,7 +24186,7 @@
         <v>0.5611776806376989</v>
       </c>
       <c r="D449" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E449">
         <v>0.4402234630031003</v>
@@ -24230,7 +24236,7 @@
         <v>0.5627855122506729</v>
       </c>
       <c r="D450" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E450">
         <v>0.4402234630031003</v>
@@ -24280,7 +24286,7 @@
         <v>0.362536241667339</v>
       </c>
       <c r="D451" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E451">
         <v>0.5284213922026888</v>
@@ -24330,7 +24336,7 @@
         <v>0.5384213922026886</v>
       </c>
       <c r="D452" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E452">
         <v>0.3796654212995421</v>
@@ -24380,7 +24386,7 @@
         <v>0.3425362416673385</v>
       </c>
       <c r="D453" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E453">
         <v>0.4657898242092271</v>
@@ -24430,7 +24436,7 @@
         <v>0.5522969892930032</v>
       </c>
       <c r="D454" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E454">
         <v>0.3961725863833179</v>
@@ -24480,7 +24486,7 @@
         <v>0.5669381107315008</v>
       </c>
       <c r="D455" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E455">
         <v>0.4381821398283536</v>
@@ -24530,7 +24536,7 @@
         <v>0.5591869165508712</v>
       </c>
       <c r="D456" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E456">
         <v>0.4381821398283536</v>
@@ -24580,7 +24586,7 @@
         <v>0.5608137078218149</v>
       </c>
       <c r="D457" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E457">
         <v>0.4381821398283536</v>
@@ -24630,7 +24636,7 @@
         <v>0.3787781087183184</v>
       </c>
       <c r="D458" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E458">
         <v>0.5438919974104648</v>
@@ -24680,7 +24686,7 @@
         <v>0.5538919974104646</v>
       </c>
       <c r="D459" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E459">
         <v>0.3955897099444972</v>
@@ -24730,7 +24736,7 @@
         <v>0.3587781087183179</v>
       </c>
       <c r="D460" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E460">
         <v>0.4817594811978996</v>
@@ -24780,7 +24786,7 @@
         <v>0.5677222261570618</v>
       </c>
       <c r="D461" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E461">
         <v>0.4115524549036591</v>
@@ -24830,7 +24836,7 @@
         <v>0.5811384023151787</v>
       </c>
       <c r="D462" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E462">
         <v>0.4528361148492088</v>
@@ -24880,7 +24886,7 @@
         <v>0.5734779448219838</v>
       </c>
       <c r="D463" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E463">
         <v>0.4528361148492088</v>
@@ -24930,7 +24936,7 @@
         <v>0.5749686310617745</v>
       </c>
       <c r="D464" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E464">
         <v>0.4528361148492088</v>
@@ -24980,7 +24986,7 @@
         <v>0.5759260480051562</v>
       </c>
       <c r="D465" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E465">
         <v>0.4182699203806752</v>
@@ -25030,7 +25036,7 @@
         <v>0.381910631043537</v>
       </c>
       <c r="D466" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E466">
         <v>0.5045043076182258</v>
@@ -25080,7 +25086,7 @@
         <v>0.5896916607676044</v>
       </c>
       <c r="D467" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E467">
         <v>0.4334572735300526</v>
@@ -25130,7 +25136,7 @@
         <v>0.6013632053537075</v>
       </c>
       <c r="D468" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E468">
         <v>0.4737070777292249</v>
@@ -25180,7 +25186,7 @@
         <v>0.5938319798288108</v>
       </c>
       <c r="D469" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E469">
         <v>0.4737070777292249</v>
@@ -25230,7 +25236,7 @@
         <v>0.5951288181161551</v>
       </c>
       <c r="D470" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E470">
         <v>0.4737070777292249</v>
@@ -25280,7 +25286,7 @@
         <v>0.8275182606108249</v>
       </c>
       <c r="D471" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E471">
         <v>0.7045523383049392</v>
@@ -25330,7 +25336,7 @@
         <v>0.8516663182579531</v>
       </c>
       <c r="D472" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E472">
         <v>0.7320070951991022</v>
@@ -25380,7 +25386,7 @@
         <v>0.8457344736461829</v>
       </c>
       <c r="D473" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E473">
         <v>0.7320070951991022</v>
@@ -25430,7 +25436,7 @@
         <v>0.844632240563838</v>
       </c>
       <c r="D474" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E474">
         <v>0.7320070951991022</v>
@@ -25480,7 +25486,7 @@
         <v>0.6727685513402974</v>
       </c>
       <c r="D475" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E475">
         <v>0.7664959297873786</v>
@@ -25530,7 +25536,7 @@
         <v>1.961867488267962</v>
       </c>
       <c r="D476" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E476">
         <v>2.359173157777273</v>
@@ -25580,7 +25586,7 @@
         <v>2.029355876327454</v>
       </c>
       <c r="D477" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E477">
         <v>2.359173157777273</v>
@@ -25630,7 +25636,7 @@
         <v>2.417392420037491</v>
       </c>
       <c r="D478" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E478">
         <v>2.467575138587673</v>
@@ -25680,7 +25686,7 @@
         <v>1.940717323096565</v>
       </c>
       <c r="D479" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E479">
         <v>2.336812591587031</v>
@@ -25730,7 +25736,7 @@
         <v>2.007313836721119</v>
       </c>
       <c r="D480" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E480">
         <v>2.336812591587031</v>
@@ -25830,7 +25836,7 @@
         <v>1.900096592997466</v>
       </c>
       <c r="D482" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E482">
         <v>2.293867181150936</v>
@@ -25880,7 +25886,7 @@
         <v>1.964980184268443</v>
       </c>
       <c r="D483" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E483">
         <v>2.293867181150936</v>
@@ -26030,7 +26036,7 @@
         <v>1.861852628646782</v>
       </c>
       <c r="D486" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E486">
         <v>2.25343455618982</v>
@@ -26080,7 +26086,7 @@
         <v>1.925123522625862</v>
       </c>
       <c r="D487" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E487">
         <v>2.25343455618982</v>
@@ -26130,7 +26136,7 @@
         <v>2.430110142764237</v>
       </c>
       <c r="D488" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E488">
         <v>2.50019042193399</v>
@@ -26180,7 +26186,7 @@
         <v>2.430163662210739</v>
       </c>
       <c r="D489" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E489">
         <v>2.50019042193399</v>
@@ -26230,7 +26236,7 @@
         <v>1.831459736592777</v>
       </c>
       <c r="D490" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E490">
         <v>2.221302311879713</v>
@@ -26280,7 +26286,7 @@
         <v>1.903030398449984</v>
       </c>
       <c r="D491" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E491">
         <v>2.221302311879713</v>
@@ -26330,7 +26336,7 @@
         <v>1.893449002593677</v>
       </c>
       <c r="D492" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E492">
         <v>2.221302311879713</v>
@@ -26380,7 +26386,7 @@
         <v>2.398160988165298</v>
       </c>
       <c r="D493" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E493">
         <v>2.478318412878362</v>
@@ -26430,7 +26436,7 @@
         <v>2.399313045878813</v>
       </c>
       <c r="D494" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E494">
         <v>2.478318412878362</v>
@@ -26480,7 +26486,7 @@
         <v>2.402454369593227</v>
       </c>
       <c r="D495" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E495">
         <v>2.478318412878362</v>
@@ -26530,7 +26536,7 @@
         <v>2.395487738671498</v>
       </c>
       <c r="D496" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E496">
         <v>2.178404138073476</v>
@@ -26580,7 +26586,7 @@
         <v>2.392346507442251</v>
       </c>
       <c r="D497" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E497">
         <v>2.081770201129994</v>
@@ -26630,7 +26636,7 @@
         <v>2.396288876811025</v>
       </c>
       <c r="D498" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E498">
         <v>2.081770201129994</v>
@@ -26680,7 +26686,7 @@
         <v>2.352451083881302</v>
       </c>
       <c r="D499" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E499">
         <v>2.137017856475825</v>
@@ -26730,7 +26736,7 @@
         <v>2.350579370492474</v>
       </c>
       <c r="D500" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E500">
         <v>2.036194510658961</v>
@@ -26780,7 +26786,7 @@
         <v>2.354140884509123</v>
       </c>
       <c r="D501" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E501">
         <v>2.036194510658961</v>
@@ -26830,7 +26836,7 @@
         <v>2.299604104293275</v>
       </c>
       <c r="D502" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E502">
         <v>2.086197457225981</v>
@@ -26880,7 +26886,7 @@
         <v>2.299291298856895</v>
       </c>
       <c r="D503" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E503">
         <v>1.980229715166035</v>
@@ -26930,7 +26936,7 @@
         <v>2.30238514048781</v>
       </c>
       <c r="D504" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E504">
         <v>1.980229715166035</v>
@@ -26980,7 +26986,7 @@
         <v>1.834447701575086</v>
       </c>
       <c r="D505" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E505">
         <v>2.020009773964153</v>
@@ -27030,7 +27036,7 @@
         <v>2.24888552042234</v>
       </c>
       <c r="D506" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E506">
         <v>2.037423833798475</v>
@@ -27066,7 +27072,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27080,7 +27086,7 @@
         <v>2.250068838403982</v>
       </c>
       <c r="D507" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E507">
         <v>1.926518884459057</v>
@@ -27116,7 +27122,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27130,7 +27136,7 @@
         <v>2.252713843009491</v>
       </c>
       <c r="D508" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E508">
         <v>1.926518884459057</v>
@@ -27166,7 +27172,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27180,7 +27186,7 @@
         <v>1.784477179413162</v>
       </c>
       <c r="D509" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E509">
         <v>1.954198810770938</v>
@@ -27216,7 +27222,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27230,7 +27236,7 @@
         <v>2.18954595312629</v>
       </c>
       <c r="D510" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E510">
         <v>1.980359825130297</v>
@@ -27280,7 +27286,7 @@
         <v>2.19247970082168</v>
       </c>
       <c r="D511" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E511">
         <v>1.863678457735511</v>
@@ -27330,7 +27336,7 @@
         <v>2.194599576513064</v>
       </c>
       <c r="D512" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E512">
         <v>1.863678457735511</v>
@@ -27430,7 +27436,7 @@
         <v>2.12798379490697</v>
       </c>
       <c r="D514" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E514">
         <v>1.793301466175083</v>
@@ -27480,7 +27486,7 @@
         <v>2.129515562033781</v>
       </c>
       <c r="D515" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E515">
         <v>1.793301466175083</v>
@@ -27530,7 +27536,7 @@
         <v>1.660536740118322</v>
       </c>
       <c r="D516" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E516">
         <v>1.821856726399725</v>
@@ -27580,7 +27586,7 @@
         <v>1.723388493526535</v>
       </c>
       <c r="D517" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E517">
         <v>1.821856726399725</v>
@@ -27630,7 +27636,7 @@
         <v>2.053274487460548</v>
       </c>
       <c r="D518" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E518">
         <v>1.711779759873364</v>
@@ -27666,7 +27672,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27716,7 +27722,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27766,7 +27772,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27780,7 +27786,7 @@
         <v>1.978172341647824</v>
       </c>
       <c r="D521" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E521">
         <v>1.629829394077717</v>
@@ -27816,7 +27822,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27830,7 +27836,7 @@
         <v>1.508448517052806</v>
       </c>
       <c r="D522" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E522">
         <v>1.687122875108891</v>
@@ -27866,7 +27872,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27880,7 +27886,7 @@
         <v>1.577675225918856</v>
       </c>
       <c r="D523" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E523">
         <v>1.687122875108891</v>
@@ -27916,7 +27922,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27930,7 +27936,7 @@
         <v>1.898217593290899</v>
       </c>
       <c r="D524" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E524">
         <v>1.542583939183686</v>
@@ -27980,7 +27986,7 @@
         <v>1.427278650939697</v>
       </c>
       <c r="D525" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E525">
         <v>1.591409997284986</v>
@@ -28030,7 +28036,7 @@
         <v>1.499907689523063</v>
       </c>
       <c r="D526" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E526">
         <v>1.591409997284986</v>
@@ -28080,7 +28086,7 @@
         <v>1.773958940747064</v>
       </c>
       <c r="D527" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E527">
         <v>1.657280312655916</v>
@@ -28116,7 +28122,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28130,7 +28136,7 @@
         <v>1.803626803556179</v>
       </c>
       <c r="D528" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E528">
         <v>1.657280312655916</v>
@@ -28166,7 +28172,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28180,7 +28186,7 @@
         <v>1.61628390108326</v>
       </c>
       <c r="D529" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E529">
         <v>1.744291077937949</v>
@@ -28216,7 +28222,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28230,7 +28236,7 @@
         <v>1.593294666365293</v>
       </c>
       <c r="D530" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E530">
         <v>1.744291077937949</v>
@@ -28266,7 +28272,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28316,7 +28322,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28330,7 +28336,7 @@
         <v>1.804291077937949</v>
       </c>
       <c r="D532" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E532">
         <v>1.703958940747064</v>
@@ -28366,7 +28372,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28380,7 +28386,7 @@
         <v>1.761078645636388</v>
       </c>
       <c r="D533" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E533">
         <v>1.61323205942485</v>
@@ -28430,7 +28436,7 @@
         <v>1.572644764755269</v>
       </c>
       <c r="D534" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E534">
         <v>1.701470175416108</v>
@@ -28480,7 +28486,7 @@
         <v>1.550882880746527</v>
       </c>
       <c r="D535" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E535">
         <v>1.701470175416108</v>
@@ -28530,7 +28536,7 @@
         <v>1.721861705195829</v>
       </c>
       <c r="D536" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E536">
         <v>1.652644764755269</v>
@@ -28630,7 +28636,7 @@
         <v>1.761470175416108</v>
       </c>
       <c r="D538" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E538">
         <v>1.661274410526249</v>
@@ -28680,7 +28686,7 @@
         <v>1.581861705195828</v>
       </c>
       <c r="D539" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E539">
         <v>1.581078645636387</v>
@@ -28730,7 +28736,7 @@
         <v>1.751751519300945</v>
       </c>
       <c r="D540" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E540">
         <v>1.603576092096812</v>
@@ -28766,7 +28772,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28780,7 +28786,7 @@
         <v>1.563078481334303</v>
       </c>
       <c r="D541" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E541">
         <v>1.652580870571793</v>
@@ -28816,7 +28822,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28830,7 +28836,7 @@
         <v>1.541585649046775</v>
       </c>
       <c r="D542" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E542">
         <v>1.652580870571793</v>
@@ -28866,7 +28872,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28880,7 +28886,7 @@
         <v>1.712415000317624</v>
       </c>
       <c r="D543" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E543">
         <v>1.643078481334303</v>
@@ -28916,7 +28922,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28966,7 +28972,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28980,7 +28986,7 @@
         <v>1.752083259809285</v>
       </c>
       <c r="D545" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E545">
         <v>1.631585649046776</v>
@@ -29016,7 +29022,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29030,7 +29036,7 @@
         <v>1.572415000317624</v>
       </c>
       <c r="D546" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E546">
         <v>1.572415000317624</v>
@@ -29066,7 +29072,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29080,7 +29086,7 @@
         <v>1.550696711215447</v>
       </c>
       <c r="D547" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E547">
         <v>1.640315179547803</v>
@@ -29116,7 +29122,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29130,7 +29136,7 @@
         <v>1.529552116212513</v>
       </c>
       <c r="D548" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E548">
         <v>1.640315179547803</v>
@@ -29166,7 +29172,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29180,7 +29186,7 @@
         <v>1.700188002325254</v>
       </c>
       <c r="D549" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E549">
         <v>1.630696711215447</v>
@@ -29216,7 +29222,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29230,7 +29236,7 @@
         <v>1.739933647880158</v>
       </c>
       <c r="D550" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E550">
         <v>1.619552116212513</v>
@@ -29266,7 +29272,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29280,7 +29286,7 @@
         <v>1.560188002325254</v>
       </c>
       <c r="D551" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E551">
         <v>1.569552116212513</v>
@@ -29316,7 +29322,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29330,7 +29336,7 @@
         <v>1.454006350364605</v>
       </c>
       <c r="D552" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E552">
         <v>1.544531290829937</v>
@@ -29380,7 +29386,7 @@
         <v>1.4355811717606</v>
       </c>
       <c r="D553" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E553">
         <v>1.544531290829937</v>
@@ -29430,7 +29436,7 @@
         <v>1.604706270985048</v>
       </c>
       <c r="D554" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E554">
         <v>1.534006350364605</v>
@@ -29480,7 +29486,7 @@
         <v>1.645056231295269</v>
       </c>
       <c r="D555" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E555">
         <v>1.525581171760601</v>
@@ -29530,7 +29536,7 @@
         <v>1.464706270985047</v>
       </c>
       <c r="D556" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E556">
         <v>1.556106112225933</v>
@@ -29580,7 +29586,7 @@
         <v>1.381264364482504</v>
       </c>
       <c r="D557" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E557">
         <v>1.47247126106548</v>
@@ -29630,7 +29636,7 @@
         <v>1.364885054231434</v>
       </c>
       <c r="D558" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E558">
         <v>1.47247126106548</v>
@@ -29680,7 +29686,7 @@
         <v>1.532873559926473</v>
       </c>
       <c r="D559" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E559">
         <v>1.461264364482504</v>
@@ -29730,7 +29736,7 @@
         <v>1.573678157648457</v>
       </c>
       <c r="D560" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E560">
         <v>1.454885054231434</v>
@@ -29780,7 +29786,7 @@
         <v>1.392873559926473</v>
       </c>
       <c r="D561" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E561">
         <v>1.486091950814411</v>
@@ -29830,7 +29836,7 @@
         <v>1.323846162601001</v>
       </c>
       <c r="D562" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E562">
         <v>1.430640622329638</v>
@@ -29880,7 +29886,7 @@
         <v>1.491174879041532</v>
       </c>
       <c r="D563" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E563">
         <v>1.419037852193957</v>
@@ -29980,7 +29986,7 @@
         <v>1.53224339246532</v>
       </c>
       <c r="D565" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E565">
         <v>1.413846162601002</v>
@@ -30030,7 +30036,7 @@
         <v>1.351174879041532</v>
       </c>
       <c r="D566" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E566">
         <v>1.445448932736684</v>
@@ -30080,7 +30086,7 @@
         <v>1.290817037379022</v>
       </c>
       <c r="D567" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E567">
         <v>1.43889565831837</v>
@@ -30130,7 +30136,7 @@
         <v>1.457614738944602</v>
       </c>
       <c r="D568" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E568">
         <v>1.385052900197065</v>
@@ -30230,7 +30236,7 @@
         <v>1.49889565831837</v>
       </c>
       <c r="D570" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E570">
         <v>1.380817037379023</v>
@@ -30280,7 +30286,7 @@
         <v>1.317614738944601</v>
       </c>
       <c r="D571" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E571">
         <v>1.412738416439675</v>
@@ -30330,7 +30336,7 @@
         <v>1.465300255187212</v>
       </c>
       <c r="D572" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E572">
         <v>1.414659795500328</v>
@@ -30380,7 +30386,7 @@
         <v>1.263583293912756</v>
       </c>
       <c r="D573" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E573">
         <v>1.411399209931207</v>
@@ -30430,7 +30436,7 @@
         <v>1.429943153943507</v>
       </c>
       <c r="D574" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E574">
         <v>1.357031041968109</v>
@@ -30530,7 +30536,7 @@
         <v>1.471399209931207</v>
       </c>
       <c r="D576" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E576">
         <v>1.353583293912756</v>
@@ -30580,7 +30586,7 @@
         <v>1.438679489869704</v>
       </c>
       <c r="D577" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E577">
         <v>1.390135545857402</v>
@@ -30630,7 +30636,7 @@
         <v>1.397526326513801</v>
       </c>
       <c r="D578" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E578">
         <v>1.324203874950685</v>
@@ -30730,7 +30736,7 @@
         <v>1.407493681203151</v>
       </c>
       <c r="D580" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E580">
         <v>1.335799810110941</v>
@@ -30780,7 +30786,7 @@
         <v>1.358411271518721</v>
       </c>
       <c r="D581" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E581">
         <v>1.284593692677185</v>
@@ -30830,7 +30836,7 @@
         <v>1.361730508546035</v>
       </c>
       <c r="D582" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E582">
         <v>1.30077611383565</v>
@@ -30930,7 +30936,7 @@
         <v>1.369864008043327</v>
       </c>
       <c r="D584" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E584">
         <v>1.299407955147164</v>
@@ -30980,7 +30986,7 @@
         <v>1.334364057726781</v>
       </c>
       <c r="D585" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E585">
         <v>1.260242083773956</v>
@@ -31030,7 +31036,7 @@
         <v>1.337150603309337</v>
       </c>
       <c r="D586" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E586">
         <v>1.27612010982113</v>
@@ -31130,7 +31136,7 @@
         <v>1.194364057726781</v>
       </c>
       <c r="D588" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E588">
         <v>1.292608005632433</v>
@@ -31180,7 +31186,7 @@
         <v>1.346729979585258</v>
       </c>
       <c r="D589" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E589">
         <v>1.277034914467322</v>
@@ -31230,7 +31236,7 @@
         <v>1.323737513794956</v>
       </c>
       <c r="D590" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E590">
         <v>1.249481026627804</v>
@@ -31266,7 +31272,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31316,7 +31322,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31330,7 +31336,7 @@
         <v>1.183737513794956</v>
       </c>
       <c r="D592" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E592">
         <v>1.282250488129261</v>
@@ -31366,7 +31372,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31380,7 +31386,7 @@
         <v>1.336506975296414</v>
       </c>
       <c r="D593" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E593">
         <v>1.244597045756811</v>
@@ -31416,7 +31422,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31430,7 +31436,7 @@
         <v>1.107789411132176</v>
       </c>
       <c r="D594" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E594">
         <v>1.128853532923964</v>
@@ -31466,7 +31472,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31480,7 +31486,7 @@
         <v>1.314314361428908</v>
       </c>
       <c r="D595" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E595">
         <v>1.239938593852058</v>
@@ -31580,7 +31586,7 @@
         <v>1.356502245217332</v>
       </c>
       <c r="D597" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E597">
         <v>1.23978407089997</v>
@@ -31630,7 +31636,7 @@
         <v>1.174314361428907</v>
       </c>
       <c r="D598" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E598">
         <v>1.273065896582606</v>
@@ -31680,7 +31686,7 @@
         <v>1.327441664159455</v>
       </c>
       <c r="D599" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E599">
         <v>1.236038676361065</v>
@@ -31730,7 +31736,7 @@
         <v>1.099320502043702</v>
       </c>
       <c r="D600" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E600">
         <v>1.151508385832127</v>
@@ -31780,7 +31786,7 @@
         <v>1.304586839884553</v>
       </c>
       <c r="D601" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E601">
         <v>1.230087939123598</v>
@@ -31880,7 +31886,7 @@
         <v>1.34683629026503</v>
       </c>
       <c r="D603" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E603">
         <v>1.230210465835747</v>
@@ -31930,7 +31936,7 @@
         <v>1.164586839884553</v>
       </c>
       <c r="D604" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E604">
         <v>1.263584641406464</v>
@@ -31980,7 +31986,7 @@
         <v>1.318083542167419</v>
       </c>
       <c r="D605" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E605">
         <v>1.227203870401477</v>
@@ -32030,7 +32036,7 @@
         <v>1.090578045972193</v>
       </c>
       <c r="D606" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E606">
         <v>1.168451122303864</v>
@@ -32080,7 +32086,7 @@
         <v>1.288015597086421</v>
       </c>
       <c r="D607" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E607">
         <v>1.213306933758401</v>
@@ -32116,7 +32122,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32166,7 +32172,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32180,7 +32186,7 @@
         <v>1.330369928750431</v>
       </c>
       <c r="D609" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E609">
         <v>1.213901426246447</v>
@@ -32216,7 +32222,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32230,7 +32236,7 @@
         <v>1.148015597086421</v>
       </c>
       <c r="D610" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E610">
         <v>1.247432923742462</v>
@@ -32266,7 +32272,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32280,7 +32286,7 @@
         <v>1.302141587070481</v>
       </c>
       <c r="D611" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E611">
         <v>1.212153406214566</v>
@@ -32316,7 +32322,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32366,7 +32372,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32430,7 +32436,7 @@
         <v>1.316010539200704</v>
       </c>
       <c r="D614" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E614">
         <v>1.199679228316622</v>
@@ -32480,7 +32486,7 @@
         <v>1.13356474645676</v>
       </c>
       <c r="D615" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E615">
         <v>1.233347917432539</v>
@@ -32530,7 +32536,7 @@
         <v>1.288239502920428</v>
       </c>
       <c r="D616" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E616">
         <v>1.199028741243956</v>
@@ -32580,7 +32586,7 @@
         <v>1.062697430359874</v>
       </c>
       <c r="D617" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E617">
         <v>1.173703497707623</v>
@@ -32680,7 +32686,7 @@
         <v>1.289689339635371</v>
       </c>
       <c r="D619" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E619">
         <v>1.173609505180258</v>
@@ -32730,7 +32736,7 @@
         <v>1.107075895938781</v>
       </c>
       <c r="D620" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E620">
         <v>1.207529670725142</v>
@@ -32780,7 +32786,7 @@
         <v>1.262756558118322</v>
       </c>
       <c r="D621" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E621">
         <v>1.174970829539336</v>
@@ -32930,7 +32936,7 @@
         <v>1.276835319137715</v>
       </c>
       <c r="D624" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E624">
         <v>1.160878293795636</v>
@@ -32980,7 +32986,7 @@
         <v>1.094140002699101</v>
       </c>
       <c r="D625" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E625">
         <v>1.194921268453555</v>
@@ -33080,7 +33086,7 @@
         <v>1.101308040374834</v>
       </c>
       <c r="D627" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E627">
         <v>1.125351015032754</v>
@@ -33130,7 +33136,7 @@
         <v>1.261511807017353</v>
       </c>
       <c r="D628" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E628">
         <v>1.145701184657316</v>
@@ -33180,7 +33186,7 @@
         <v>1.078718888590712</v>
       </c>
       <c r="D629" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E629">
         <v>1.179890562297277</v>
@@ -33230,7 +33236,7 @@
         <v>1.087594961056931</v>
       </c>
       <c r="D630" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E630">
         <v>1.158991420270251</v>
@@ -33280,7 +33286,7 @@
         <v>1.226836158897406</v>
       </c>
       <c r="D631" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E631">
         <v>1.111356832538514</v>
@@ -33330,7 +33336,7 @@
         <v>1.043822376470001</v>
       </c>
       <c r="D632" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E632">
         <v>1.145877506179622</v>
@@ -33380,7 +33386,7 @@
         <v>1.056563568949589</v>
       </c>
       <c r="D633" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E633">
         <v>1.128070460163292</v>
@@ -33430,7 +33436,7 @@
         <v>1.201158127400802</v>
       </c>
       <c r="D634" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E634">
         <v>1.085924132553024</v>
@@ -33480,7 +33486,7 @@
         <v>1.017980790632654</v>
       </c>
       <c r="D635" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E635">
         <v>1.120690137705246</v>
@@ -33530,7 +33536,7 @@
         <v>1.168551502583454</v>
       </c>
       <c r="D636" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E636">
         <v>1.053629035998263</v>
@@ -33566,7 +33572,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33580,7 +33586,7 @@
         <v>0.9851664803069156</v>
       </c>
       <c r="D637" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E637">
         <v>1.088706569413071</v>
@@ -33616,7 +33622,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33630,7 +33636,7 @@
         <v>1.162722274727682</v>
       </c>
       <c r="D638" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E638">
         <v>1.047855501402259</v>
@@ -33680,7 +33686,7 @@
         <v>0.979300123611297</v>
       </c>
       <c r="D639" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E639">
         <v>1.082988728076835</v>
@@ -33730,7 +33736,7 @@
         <v>0.9086593724975383</v>
       </c>
       <c r="D640" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E640">
         <v>1.014136350408994</v>
@@ -33880,7 +33886,7 @@
         <v>0.7992043433997962</v>
       </c>
       <c r="D643" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E643">
         <v>1.019738497970907</v>
@@ -33916,7 +33922,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33930,7 +33936,7 @@
         <v>1.313286431175834</v>
       </c>
       <c r="D644" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E644">
         <v>1.130272652542017</v>
@@ -33966,7 +33972,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33980,7 +33986,7 @@
         <v>0.7800006615139132</v>
       </c>
       <c r="D645" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E645">
         <v>0.9989795883266597</v>
@@ -34016,7 +34022,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34066,7 +34072,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34080,7 +34086,7 @@
         <v>0.7633805417349455</v>
       </c>
       <c r="D647" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E647">
         <v>0.9810134729317896</v>
@@ -34116,7 +34122,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34130,7 +34136,7 @@
         <v>1.274182985696595</v>
       </c>
       <c r="D648" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E648">
         <v>0.9863695750502357</v>
@@ -34166,7 +34172,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34180,7 +34186,7 @@
         <v>1.137753720442226</v>
       </c>
       <c r="D649" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E649">
         <v>0.9863695750502357</v>
@@ -34216,7 +34222,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34230,7 +34236,7 @@
         <v>0.7497456373466673</v>
       </c>
       <c r="D650" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E650">
         <v>0.9662743333289678</v>
@@ -34266,7 +34272,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34280,7 +34286,7 @@
         <v>1.259299815413615</v>
       </c>
       <c r="D651" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E651">
         <v>0.9151278686163851</v>
@@ -34316,7 +34322,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34330,7 +34336,7 @@
         <v>1.122102386531737</v>
       </c>
       <c r="D652" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E652">
         <v>0.9151278686163851</v>
@@ -34366,7 +34372,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34380,7 +34386,7 @@
         <v>0.7499733438090663</v>
       </c>
       <c r="D653" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E653">
         <v>0.9665204808076879</v>
@@ -34430,7 +34436,7 @@
         <v>1.259548368242291</v>
       </c>
       <c r="D654" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E654">
         <v>0.9153916553281078</v>
@@ -34480,7 +34486,7 @@
         <v>1.122363767893505</v>
       </c>
       <c r="D655" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E655">
         <v>0.9153916553281078</v>
@@ -34530,7 +34536,7 @@
         <v>0.7430600171819424</v>
       </c>
       <c r="D656" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E656">
         <v>0.9590472720945642</v>
@@ -34580,7 +34586,7 @@
         <v>1.252002131430993</v>
       </c>
       <c r="D657" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E657">
         <v>0.9073829072283761</v>
@@ -34630,7 +34636,7 @@
         <v>1.114428047891947</v>
       </c>
       <c r="D658" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E658">
         <v>0.9073829072283761</v>
@@ -34680,7 +34686,7 @@
         <v>0.7298791026179612</v>
       </c>
       <c r="D659" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E659">
         <v>0.9447988890975849</v>
@@ -34730,7 +34736,7 @@
         <v>1.237614513421014</v>
       </c>
       <c r="D660" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E660">
         <v>0.8921134674693985</v>
@@ -34780,7 +34786,7 @@
         <v>1.099297843145969</v>
       </c>
       <c r="D661" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E661">
         <v>0.8921134674693985</v>
@@ -34830,7 +34836,7 @@
         <v>0.7205518880005681</v>
       </c>
       <c r="D662" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E662">
         <v>0.9347163014654027</v>
@@ -34880,7 +34886,7 @@
         <v>1.227433398873859</v>
       </c>
       <c r="D663" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E663">
         <v>0.8813083491274183</v>
@@ -34930,7 +34936,7 @@
         <v>1.088591251718961</v>
       </c>
       <c r="D664" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E664">
         <v>0.8813083491274183</v>
@@ -34980,7 +34986,7 @@
         <v>0.7334671047121053</v>
       </c>
       <c r="D665" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E665">
         <v>0.9486774688261139</v>
@@ -35016,7 +35022,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35030,7 +35036,7 @@
         <v>1.241530994580115</v>
       </c>
       <c r="D666" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E666">
         <v>0.8962699910221215</v>
@@ -35066,7 +35072,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35080,7 +35086,7 @@
         <v>1.10341646526812</v>
       </c>
       <c r="D667" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E667">
         <v>0.8962699910221215</v>
@@ -35116,7 +35122,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35130,7 +35136,7 @@
         <v>0.8045700379682295</v>
       </c>
       <c r="D668" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E668">
         <v>1.004863742954274</v>
@@ -35166,7 +35172,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35180,7 +35186,7 @@
         <v>1.234863742954274</v>
       </c>
       <c r="D669" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E669">
         <v>0.9443867707027893</v>
@@ -35216,7 +35222,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35230,7 +35236,7 @@
         <v>1.096405097429334</v>
       </c>
       <c r="D670" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E670">
         <v>0.9443867707027893</v>
@@ -35266,7 +35272,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35280,7 +35286,7 @@
         <v>0.7207520002925669</v>
       </c>
       <c r="D671" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E671">
         <v>0.903356547088833</v>
@@ -35316,7 +35322,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35330,7 +35336,7 @@
         <v>0.7297853816033166</v>
       </c>
       <c r="D672" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E672">
         <v>0.903356547088833</v>
@@ -35366,7 +35372,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35380,7 +35386,7 @@
         <v>0.7096588204869674</v>
       </c>
       <c r="D673" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E673">
         <v>0.943356547088833</v>
@@ -35416,7 +35422,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35430,7 +35436,7 @@
         <v>0.8405874255868655</v>
       </c>
       <c r="D674" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E674">
         <v>0.9485506684719898</v>
@@ -35480,7 +35486,7 @@
         <v>0.7932418398819072</v>
       </c>
       <c r="D675" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E675">
         <v>0.9485506684719898</v>
@@ -35530,7 +35536,7 @@
         <v>0.803058054307523</v>
       </c>
       <c r="D676" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E676">
         <v>0.9897859828323181</v>
@@ -35580,7 +35586,7 @@
         <v>0.8230580543075225</v>
       </c>
       <c r="D677" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E677">
         <v>0.9897859828323181</v>
@@ -35630,7 +35636,7 @@
         <v>0.8318227399471945</v>
       </c>
       <c r="D678" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E678">
         <v>0.9571315685372763</v>
@@ -35880,7 +35886,7 @@
         <v>0.777997561282735</v>
       </c>
       <c r="D683" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E683">
         <v>0.9334019652872323</v>
@@ -35930,7 +35936,7 @@
         <v>0.7885305913164626</v>
       </c>
       <c r="D684" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E684">
         <v>0.9750195813052205</v>
@@ -35980,7 +35986,7 @@
         <v>0.8085305913164622</v>
       </c>
       <c r="D685" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E685">
         <v>0.9750195813052205</v>
@@ -36030,7 +36036,7 @@
         <v>0.8169129752984747</v>
       </c>
       <c r="D686" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E686">
         <v>0.9423173793029713</v>
@@ -36180,7 +36186,7 @@
         <v>1.044210773296226</v>
       </c>
       <c r="D689" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E689">
         <v>1.03610416728948</v>
@@ -36230,7 +36236,7 @@
         <v>0.7528694316436244</v>
       </c>
       <c r="D690" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E690">
         <v>0.9084313787806551</v>
@@ -36280,7 +36286,7 @@
         <v>0.764584035171354</v>
       </c>
       <c r="D691" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E691">
         <v>0.950679167328778</v>
@@ -36330,7 +36336,7 @@
         <v>0.8145840351713538</v>
       </c>
       <c r="D692" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E692">
         <v>0.950679167328778</v>
@@ -36380,7 +36386,7 @@
         <v>0.7923362466232318</v>
       </c>
       <c r="D693" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E693">
         <v>0.9178981937602617</v>
@@ -36580,7 +36586,7 @@
         <v>0.7253017663654795</v>
       </c>
       <c r="D697" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E697">
         <v>0.9239756921847437</v>
@@ -36630,7 +36636,7 @@
         <v>0.7383126550943753</v>
       </c>
       <c r="D698" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E698">
         <v>0.9239756921847437</v>
@@ -36680,7 +36686,7 @@
         <v>0.7653735144389637</v>
       </c>
       <c r="D699" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E699">
         <v>0.8911082996028163</v>
@@ -36880,7 +36886,7 @@
         <v>0.71847767572971</v>
       </c>
       <c r="D703" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E703">
         <v>0.9038144796068437</v>
@@ -36930,7 +36936,7 @@
         <v>0.7450165619331228</v>
       </c>
       <c r="D704" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E704">
         <v>1.017804067975443</v>
@@ -37030,7 +37036,7 @@
         <v>1.023814479606843</v>
       </c>
       <c r="D706" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E706">
         <v>1.07328600503483</v>
@@ -37080,7 +37086,7 @@
         <v>0.98328600503483</v>
       </c>
       <c r="D707" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E707">
         <v>1.07328600503483</v>
@@ -37130,7 +37136,7 @@
         <v>0.6881995922217432</v>
       </c>
       <c r="D708" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E708">
         <v>0.8730384013043384</v>
@@ -37180,7 +37186,7 @@
         <v>0.7139416867538939</v>
       </c>
       <c r="D709" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E709">
         <v>0.9885219740565545</v>
@@ -37230,7 +37236,7 @@
         <v>0.9930384013043376</v>
       </c>
       <c r="D710" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E710">
         <v>0.9930384013043376</v>
@@ -37280,7 +37286,7 @@
         <v>0.9518127340199696</v>
       </c>
       <c r="D711" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E711">
         <v>0.9930384013043376</v>
@@ -37330,7 +37336,7 @@
         <v>0.6656441408663709</v>
       </c>
       <c r="D712" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E712">
         <v>0.8501119721306205</v>
@@ -37366,7 +37372,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37380,7 +37386,7 @@
         <v>0.6907926708891701</v>
       </c>
       <c r="D713" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E713">
         <v>0.9667084783378717</v>
@@ -37416,7 +37422,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37430,7 +37436,7 @@
         <v>0.742537707119221</v>
       </c>
       <c r="D714" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E714">
         <v>0.9667084783378717</v>
@@ -37466,7 +37472,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37480,7 +37486,7 @@
         <v>0.9701119721306197</v>
       </c>
       <c r="D715" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E715">
         <v>0.9732184058777698</v>
@@ -37516,7 +37522,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37530,7 +37536,7 @@
         <v>0.9776862371420201</v>
       </c>
       <c r="D716" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E716">
         <v>0.9732184058777698</v>
@@ -37566,7 +37572,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37580,7 +37586,7 @@
         <v>0.6508193548090921</v>
       </c>
       <c r="D717" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E717">
         <v>0.8350433573552944</v>
@@ -37630,7 +37636,7 @@
         <v>0.6755777588830156</v>
       </c>
       <c r="D718" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E718">
         <v>0.9523713497166879</v>
@@ -37680,7 +37686,7 @@
         <v>0.7276641553183332</v>
       </c>
       <c r="D719" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E719">
         <v>0.9523713497166879</v>
@@ -37730,7 +37736,7 @@
         <v>0.9550433573552937</v>
       </c>
       <c r="D720" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E720">
         <v>0.9345089558275728</v>
@@ -37780,7 +37786,7 @@
         <v>0.9624225593922562</v>
       </c>
       <c r="D721" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E721">
         <v>0.9345089558275728</v>
@@ -37830,7 +37836,7 @@
         <v>0.6242673164036452</v>
       </c>
       <c r="D722" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E722">
         <v>0.8080546077918633</v>
@@ -37880,7 +37886,7 @@
         <v>0.6483269826247939</v>
       </c>
       <c r="D723" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E723">
         <v>0.9266927336272097</v>
@@ -37930,7 +37936,7 @@
         <v>0.7010247746812892</v>
       </c>
       <c r="D724" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E724">
         <v>0.9266927336272097</v>
@@ -38080,7 +38086,7 @@
         <v>0.6355734784869522</v>
       </c>
       <c r="D727" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E727">
         <v>0.9146750085742434</v>
@@ -38130,7 +38136,7 @@
         <v>0.6885574068542324</v>
       </c>
       <c r="D728" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E728">
         <v>0.9146750085742434</v>
@@ -38180,7 +38186,7 @@
         <v>0.9154237335015001</v>
       </c>
       <c r="D729" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E729">
         <v>0.8587071518396838</v>
@@ -38230,7 +38236,7 @@
         <v>0.9222900601487689</v>
       </c>
       <c r="D730" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E730">
         <v>0.8587071518396838</v>
@@ -38280,7 +38286,7 @@
         <v>0.6415632406536673</v>
       </c>
       <c r="D731" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E731">
         <v>0.8890838888081336</v>
@@ -38330,7 +38336,7 @@
         <v>0.6084155554698558</v>
       </c>
       <c r="D732" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E732">
         <v>0.8890838888081336</v>
@@ -38380,7 +38386,7 @@
         <v>0.6718974073228061</v>
       </c>
       <c r="D733" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E733">
         <v>0.8890838888081336</v>
@@ -38430,7 +38436,7 @@
         <v>0.8885269443595689</v>
       </c>
       <c r="D734" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E734">
         <v>0.8153792591757565</v>
@@ -38480,7 +38486,7 @@
         <v>0.895045092506618</v>
       </c>
       <c r="D735" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E735">
         <v>0.8153792591757565</v>
@@ -38530,7 +38536,7 @@
         <v>0.6125179249261947</v>
       </c>
       <c r="D736" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E736">
         <v>0.862145961918932</v>
@@ -38580,7 +38586,7 @@
         <v>0.5798283677507028</v>
       </c>
       <c r="D737" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E737">
         <v>0.862145961918932</v>
@@ -38630,7 +38636,7 @@
         <v>0.6436767220103095</v>
       </c>
       <c r="D738" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E738">
         <v>0.862145961918932</v>
@@ -38680,7 +38686,7 @@
         <v>0.8602146334454073</v>
       </c>
       <c r="D739" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E739">
         <v>0.7909871648348172</v>
@@ -38730,7 +38736,7 @@
         <v>0.8663662791858018</v>
       </c>
       <c r="D740" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E740">
         <v>0.7909871648348172</v>
@@ -38780,7 +38786,7 @@
         <v>0.8640629877050143</v>
       </c>
       <c r="D741" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E741">
         <v>0.7909871648348172</v>
@@ -38830,7 +38836,7 @@
         <v>0.5868517408115368</v>
       </c>
       <c r="D742" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E742">
         <v>0.8383419930554954</v>
@@ -38880,7 +38886,7 @@
         <v>0.6187392308200419</v>
       </c>
       <c r="D743" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E743">
         <v>0.8383419930554954</v>
@@ -38930,7 +38936,7 @@
         <v>0.8351961763746525</v>
       </c>
       <c r="D744" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E744">
         <v>0.749997557492379</v>
@@ -38980,7 +38986,7 @@
         <v>0.8410239585930954</v>
       </c>
       <c r="D745" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E745">
         <v>0.749997557492379</v>
@@ -39030,7 +39036,7 @@
         <v>0.8393683941562111</v>
       </c>
       <c r="D746" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E746">
         <v>0.749997557492379</v>
@@ -39080,7 +39086,7 @@
         <v>0.5558537772765639</v>
       </c>
       <c r="D747" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E747">
         <v>0.8095930931208519</v>
@@ -39130,7 +39136,7 @@
         <v>0.5886213356504157</v>
       </c>
       <c r="D748" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E748">
         <v>0.8095930931208519</v>
@@ -39180,7 +39186,7 @@
         <v>0.8049804958310984</v>
       </c>
       <c r="D749" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E749">
         <v>0.7741072143856336</v>
@@ -39230,7 +39236,7 @@
         <v>0.8104171365538315</v>
       </c>
       <c r="D750" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E750">
         <v>0.7741072143856336</v>
@@ -39280,7 +39286,7 @@
         <v>0.809543855108366</v>
       </c>
       <c r="D751" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E751">
         <v>0.7741072143856336</v>
@@ -39330,7 +39336,7 @@
         <v>0.4884465484383016</v>
       </c>
       <c r="D752" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E752">
         <v>0.7470766095926207</v>
@@ -39380,7 +39386,7 @@
         <v>0.5569813576358316</v>
       </c>
       <c r="D753" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E753">
         <v>0.7470766095926207</v>
@@ -39580,7 +39586,7 @@
         <v>0.4354740041875989</v>
       </c>
       <c r="D757" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E757">
         <v>0.6979474991519057</v>
@@ -39616,7 +39622,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39630,7 +39636,7 @@
         <v>0.5056798715633839</v>
       </c>
       <c r="D758" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E758">
         <v>0.6979474991519057</v>
@@ -39666,7 +39672,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39680,7 +39686,7 @@
         <v>0.5198033919888561</v>
       </c>
       <c r="D759" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E759">
         <v>0.6979474991519057</v>
@@ -39716,7 +39722,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39766,7 +39772,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39780,7 +39786,7 @@
         <v>0.687638698088227</v>
       </c>
       <c r="D761" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E761">
         <v>0.6759886726270619</v>
@@ -39816,7 +39822,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39830,7 +39836,7 @@
         <v>0.6915563511379128</v>
       </c>
       <c r="D762" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E762">
         <v>0.6759886726270619</v>
@@ -39866,7 +39872,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39880,7 +39886,7 @@
         <v>0.6937210450385409</v>
       </c>
       <c r="D763" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E763">
         <v>0.6759886726270619</v>
@@ -39916,7 +39922,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39930,7 +39936,7 @@
         <v>0.7159886726270619</v>
       </c>
       <c r="D764" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E764">
         <v>0.6759886726270619</v>
@@ -39966,7 +39972,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -39980,7 +39986,7 @@
         <v>0.4606014325671115</v>
       </c>
       <c r="D765" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E765">
         <v>0.6547779191359311</v>
@@ -40030,7 +40036,7 @@
         <v>0.4756059648296436</v>
       </c>
       <c r="D766" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E766">
         <v>0.6547779191359311</v>
@@ -40130,7 +40136,7 @@
         <v>0.6422665884796004</v>
       </c>
       <c r="D768" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E768">
         <v>0.5897824513984631</v>
@@ -40180,7 +40186,7 @@
         <v>0.6455969003045796</v>
       </c>
       <c r="D769" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E769">
         <v>0.5897824513984631</v>
@@ -40230,7 +40236,7 @@
         <v>0.6489362766546218</v>
       </c>
       <c r="D770" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E770">
         <v>0.5897824513984631</v>
@@ -40280,7 +40286,7 @@
         <v>0.6731127632234415</v>
       </c>
       <c r="D771" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E771">
         <v>0.5897824513984631</v>
@@ -40330,7 +40336,7 @@
         <v>0.4311736090828546</v>
       </c>
       <c r="D772" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E772">
         <v>0.6265962249848842</v>
@@ -40380,7 +40386,7 @@
         <v>0.4467532779607151</v>
       </c>
       <c r="D773" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E773">
         <v>0.6265962249848842</v>
@@ -40480,7 +40486,7 @@
         <v>0.6126470527902352</v>
       </c>
       <c r="D775" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E775">
         <v>0.5324899998144046</v>
@@ -40530,7 +40536,7 @@
         <v>0.6155939402049952</v>
       </c>
       <c r="D776" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E776">
         <v>0.5324899998144046</v>
@@ -40580,7 +40586,7 @@
         <v>0.619700165375475</v>
       </c>
       <c r="D777" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E777">
         <v>0.5324899998144046</v>
@@ -40630,7 +40636,7 @@
         <v>0.6451227812775038</v>
       </c>
       <c r="D778" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E778">
         <v>0.4344945693741815</v>
@@ -40680,7 +40686,7 @@
         <v>0.4145254252315729</v>
       </c>
       <c r="D779" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E779">
         <v>0.6106530130882168</v>
@@ -40730,7 +40736,7 @@
         <v>0.4304304657807938</v>
       </c>
       <c r="D780" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E780">
         <v>0.6106530130882168</v>
@@ -40830,7 +40836,7 @@
         <v>0.5958904117151667</v>
       </c>
       <c r="D782" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E782">
         <v>0.5161129590225899</v>
@@ -40880,7 +40886,7 @@
         <v>0.598620384682353</v>
       </c>
       <c r="D783" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E783">
         <v>0.5161129590225899</v>
@@ -40930,7 +40936,7 @@
         <v>0.6031604387479801</v>
       </c>
       <c r="D784" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E784">
         <v>0.5161129590225899</v>
@@ -40980,7 +40986,7 @@
         <v>0.6292880266046232</v>
       </c>
       <c r="D785" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E785">
         <v>0.420178215834317</v>
@@ -41030,7 +41036,7 @@
         <v>0.4227821175677198</v>
       </c>
       <c r="D786" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E786">
         <v>0.6031825334382379</v>
@@ -41066,7 +41072,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41116,7 +41122,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41130,7 +41136,7 @@
         <v>0.5880387851442697</v>
       </c>
       <c r="D788" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E788">
         <v>0.508439201014788</v>
@@ -41166,7 +41172,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41180,7 +41186,7 @@
         <v>0.5906671189325454</v>
       </c>
       <c r="D789" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E789">
         <v>0.508439201014788</v>
@@ -41216,7 +41222,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41230,7 +41236,7 @@
         <v>0.5954104513559946</v>
       </c>
       <c r="D790" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E790">
         <v>0.508439201014788</v>
@@ -41266,7 +41272,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41280,7 +41286,7 @@
         <v>0.6218683665441</v>
       </c>
       <c r="D791" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E791">
         <v>0.4134700300261724</v>
@@ -41316,7 +41322,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41330,7 +41336,7 @@
         <v>0.4183317969287206</v>
       </c>
       <c r="D792" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E792">
         <v>0.5988357086280525</v>
@@ -41430,7 +41436,7 @@
         <v>0.5834701835580542</v>
       </c>
       <c r="D794" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E794">
         <v>0.5039740952573863</v>
@@ -41480,7 +41486,7 @@
         <v>0.5860393768727219</v>
       </c>
       <c r="D795" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E795">
         <v>0.5039740952573863</v>
@@ -41530,7 +41536,7 @@
         <v>0.5909009902433873</v>
       </c>
       <c r="D796" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E796">
         <v>0.5039740952573863</v>
@@ -41580,7 +41586,7 @@
         <v>0.6175511119707178</v>
       </c>
       <c r="D797" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E797">
         <v>0.4095667587680469</v>
@@ -41630,7 +41636,7 @@
         <v>0.4068527587148587</v>
       </c>
       <c r="D798" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E798">
         <v>0.5876236247912567</v>
@@ -41730,7 +41736,7 @@
         <v>0.5716860546275448</v>
       </c>
       <c r="D800" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E800">
         <v>0.492456920703944</v>
@@ -41780,7 +41786,7 @@
         <v>0.5741027025838896</v>
       </c>
       <c r="D801" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E801">
         <v>0.492456920703944</v>
@@ -41830,7 +41836,7 @@
         <v>0.5792694066712016</v>
       </c>
       <c r="D802" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E802">
         <v>0.492456920703944</v>
@@ -41880,7 +41886,7 @@
         <v>0.6064153008130848</v>
       </c>
       <c r="D803" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E803">
         <v>0.3994987651186794</v>
@@ -41930,7 +41936,7 @@
         <v>0.3579570329658832</v>
       </c>
       <c r="D804" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E804">
         <v>0.3699362230204524</v>
@@ -41980,7 +41986,7 @@
         <v>0.3977542302305785</v>
       </c>
       <c r="D805" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E805">
         <v>0.5787366899926578</v>
@@ -42080,7 +42086,7 @@
         <v>0.5623457047882017</v>
       </c>
       <c r="D807" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E807">
         <v>0.4833281645502812</v>
@@ -42130,7 +42136,7 @@
         <v>0.5646414420670132</v>
       </c>
       <c r="D808" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E808">
         <v>0.4833281645502812</v>
@@ -42180,7 +42186,7 @@
         <v>0.57004996750939</v>
       </c>
       <c r="D809" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E809">
         <v>0.4833281645502812</v>
@@ -42230,7 +42236,7 @@
         <v>0.5975888213532521</v>
       </c>
       <c r="D810" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E810">
         <v>0.3915186604015704</v>
@@ -42280,7 +42286,7 @@
         <v>0.3495537408774121</v>
       </c>
       <c r="D811" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E811">
         <v>0.4216840692788968</v>
@@ -42380,7 +42386,7 @@
         <v>0.5721210895999382</v>
       </c>
       <c r="D813" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E813">
         <v>0.4928821005151498</v>
@@ -42430,7 +42436,7 @@
         <v>0.5745433690769604</v>
       </c>
       <c r="D814" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E814">
         <v>0.4928821005151498</v>
@@ -42480,7 +42486,7 @@
         <v>0.5796988101229168</v>
       </c>
       <c r="D815" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E815">
         <v>0.4928821005151498</v>
@@ -42530,7 +42536,7 @@
         <v>0.6068264018225955</v>
       </c>
       <c r="D816" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E816">
         <v>0.3998704454834425</v>
@@ -42630,7 +42636,7 @@
         <v>0.6148946886098487</v>
       </c>
       <c r="D818" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E818">
         <v>0.5346867183177162</v>
@@ -42680,7 +42686,7 @@
         <v>0.6178706716339253</v>
       </c>
       <c r="D819" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E819">
         <v>0.5346867183177162</v>
@@ -42730,7 +42736,7 @@
         <v>0.6219187055857738</v>
       </c>
       <c r="D820" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E820">
         <v>0.5346867183177162</v>
@@ -42780,7 +42786,7 @@
         <v>0.6472467607575272</v>
       </c>
       <c r="D821" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E821">
         <v>0.4364148795889973</v>
@@ -42866,7 +42872,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42880,7 +42886,7 @@
         <v>0.6279001693216664</v>
       </c>
       <c r="D823" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E823">
         <v>0.5473975764891374</v>
@@ -42916,7 +42922,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -42930,7 +42936,7 @@
         <v>0.6310445080831126</v>
       </c>
       <c r="D824" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E824">
         <v>0.5473975764891374</v>
@@ -42966,7 +42972,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -42980,7 +42986,7 @@
         <v>0.6347558305602217</v>
       </c>
       <c r="D825" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E825">
         <v>0.5473975764891374</v>
@@ -43016,7 +43022,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43030,7 +43036,7 @@
         <v>0.6595367295855228</v>
       </c>
       <c r="D826" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E826">
         <v>0.4475263582554048</v>
@@ -43066,7 +43072,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43080,7 +43086,7 @@
         <v>1.962686724385328</v>
       </c>
       <c r="D827" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E827">
         <v>2.151981906363921</v>
@@ -43180,7 +43186,7 @@
         <v>1.958001051354043</v>
       </c>
       <c r="D829" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E829">
         <v>2.26470804772295</v>
@@ -43230,7 +43236,7 @@
         <v>2.365152550575952</v>
       </c>
       <c r="D830" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E830">
         <v>2.343253550057224</v>
@@ -43280,7 +43286,7 @@
         <v>2.013095064260612</v>
       </c>
       <c r="D831" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E831">
         <v>2.265466103249754</v>
@@ -43380,7 +43386,7 @@
         <v>2.011324180903594</v>
       </c>
       <c r="D833" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E833">
         <v>2.263769006699277</v>
@@ -43480,7 +43486,7 @@
         <v>2.024694880188124</v>
       </c>
       <c r="D835" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E835">
         <v>2.260773155550828</v>
@@ -43530,7 +43536,7 @@
         <v>2.027479225115583</v>
       </c>
       <c r="D836" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E836">
         <v>2.260773155550828</v>
@@ -43580,7 +43586,7 @@
         <v>2.544904144922141</v>
       </c>
       <c r="D837" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E837">
         <v>2.400982420284845</v>
@@ -43630,7 +43636,7 @@
         <v>2.403976029946321</v>
       </c>
       <c r="D838" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E838">
         <v>2.400982420284845</v>
@@ -43680,7 +43686,7 @@
         <v>2.412838650236485</v>
       </c>
       <c r="D839" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E839">
         <v>2.400982420284845</v>
@@ -43730,7 +43736,7 @@
         <v>2.021712430063359</v>
       </c>
       <c r="D840" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E840">
         <v>2.258015513224412</v>
@@ -43980,7 +43986,7 @@
         <v>2.019211875698086</v>
       </c>
       <c r="D845" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E845">
         <v>2.255703442856522</v>
@@ -44230,7 +44236,7 @@
         <v>2.018121327597043</v>
       </c>
       <c r="D850" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E850">
         <v>2.254695096873648</v>
@@ -44280,7 +44286,7 @@
         <v>2.537967230127533</v>
       </c>
       <c r="D851" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E851">
         <v>2.358275425066553</v>
@@ -44330,7 +44336,7 @@
         <v>2.397072148079306</v>
       </c>
       <c r="D852" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E852">
         <v>2.358275425066553</v>
@@ -44380,7 +44386,7 @@
         <v>2.442596737838175</v>
       </c>
       <c r="D853" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E853">
         <v>2.358275425066553</v>
@@ -44430,7 +44436,7 @@
         <v>2.40633116350059</v>
       </c>
       <c r="D854" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E854">
         <v>2.358275425066553</v>
@@ -44480,7 +44486,7 @@
         <v>2.021368606041688</v>
       </c>
       <c r="D855" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E855">
         <v>2.257697605586285</v>
@@ -44516,7 +44522,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44530,7 +44536,7 @@
         <v>2.541394006375651</v>
       </c>
       <c r="D856" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E856">
         <v>2.352254605738086</v>
@@ -44566,7 +44572,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44580,7 +44586,7 @@
         <v>2.40048260634529</v>
       </c>
       <c r="D857" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E857">
         <v>2.352254605738086</v>
@@ -44616,7 +44622,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44630,7 +44636,7 @@
         <v>2.445925606193489</v>
       </c>
       <c r="D858" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E858">
         <v>2.352254605738086</v>
@@ -44666,7 +44672,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44680,7 +44686,7 @@
         <v>2.409545805980967</v>
       </c>
       <c r="D859" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E859">
         <v>2.352254605738086</v>
@@ -44716,7 +44722,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44730,7 +44736,7 @@
         <v>2.025854940315086</v>
       </c>
       <c r="D860" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E860">
         <v>2.261845773959677</v>
@@ -44780,7 +44786,7 @@
         <v>2.546128328975719</v>
       </c>
       <c r="D861" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E861">
         <v>2.405581551654453</v>
@@ -44830,7 +44836,7 @@
         <v>2.467996217823106</v>
       </c>
       <c r="D862" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E862">
         <v>2.405581551654453</v>
@@ -44880,7 +44886,7 @@
         <v>2.450524662433555</v>
       </c>
       <c r="D863" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E863">
         <v>2.405581551654453</v>
@@ -44930,7 +44936,7 @@
         <v>2.413987051467698</v>
       </c>
       <c r="D864" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E864">
         <v>2.405581551654453</v>
@@ -44980,7 +44986,7 @@
         <v>2.419317329349228</v>
       </c>
       <c r="D865" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E865">
         <v>2.405581551654453</v>
@@ -45030,7 +45036,7 @@
         <v>2.077206228244958</v>
       </c>
       <c r="D866" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E866">
         <v>2.263969424227638</v>
@@ -45080,7 +45086,7 @@
         <v>2.028151714246195</v>
       </c>
       <c r="D867" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E867">
         <v>2.263969424227638</v>
@@ -45130,7 +45136,7 @@
         <v>2.548552060259804</v>
       </c>
       <c r="D868" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E868">
         <v>2.429642340235061</v>
@@ -45180,7 +45186,7 @@
         <v>2.470443032262278</v>
       </c>
       <c r="D869" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E869">
         <v>2.429642340235061</v>
@@ -45230,7 +45236,7 @@
         <v>2.452879144252381</v>
       </c>
       <c r="D870" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E870">
         <v>2.429642340235061</v>
@@ -45280,7 +45286,7 @@
         <v>2.421533312237536</v>
       </c>
       <c r="D871" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E871">
         <v>2.429642340235061</v>
@@ -45330,7 +45336,7 @@
         <v>2.078439011686218</v>
       </c>
       <c r="D872" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E872">
         <v>2.26511504116295</v>
@@ -45380,7 +45386,7 @@
         <v>2.029390723866451</v>
       </c>
       <c r="D873" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E873">
         <v>2.26511504116295</v>
@@ -45630,7 +45636,7 @@
         <v>2.551608670550823</v>
       </c>
       <c r="D878" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E878">
         <v>2.394327927360752</v>
@@ -45680,7 +45686,7 @@
         <v>2.473528753127496</v>
       </c>
       <c r="D879" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E879">
         <v>2.394327927360752</v>
@@ -45730,7 +45736,7 @@
         <v>2.455848422820799</v>
       </c>
       <c r="D880" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E880">
         <v>2.394327927360752</v>
@@ -45780,7 +45786,7 @@
         <v>2.493367886072415</v>
       </c>
       <c r="D881" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E881">
         <v>2.394327927360752</v>
@@ -45830,7 +45836,7 @@
         <v>2.451447803495741</v>
       </c>
       <c r="D882" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E882">
         <v>2.394327927360752</v>
@@ -45880,7 +45886,7 @@
         <v>2.550180575011903</v>
       </c>
       <c r="D883" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E883">
         <v>2.413975480844273</v>
@@ -45930,7 +45936,7 @@
         <v>2.472087056678682</v>
       </c>
       <c r="D884" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E884">
         <v>2.413975480844273</v>
@@ -45980,7 +45986,7 @@
         <v>2.454461130011562</v>
       </c>
       <c r="D885" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E885">
         <v>2.413975480844273</v>
@@ -46030,7 +46036,7 @@
         <v>2.492068999177492</v>
       </c>
       <c r="D886" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E886">
         <v>2.413975480844273</v>
@@ -46080,7 +46086,7 @@
         <v>2.450162517510712</v>
       </c>
       <c r="D887" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E887">
         <v>2.413975480844273</v>
@@ -46130,7 +46136,7 @@
         <v>2.549221397041758</v>
       </c>
       <c r="D888" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E888">
         <v>2.384991297253062</v>
@@ -46180,7 +46186,7 @@
         <v>2.471118743680251</v>
       </c>
       <c r="D889" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E889">
         <v>2.384991297253062</v>
@@ -46230,7 +46236,7 @@
         <v>2.453529357126279</v>
       </c>
       <c r="D890" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E890">
         <v>2.384991297253062</v>
@@ -46280,7 +46286,7 @@
         <v>2.491196603976075</v>
       </c>
       <c r="D891" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E891">
         <v>2.384991297253062</v>
@@ -46330,7 +46336,7 @@
         <v>2.546894368399535</v>
       </c>
       <c r="D892" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E892">
         <v>2.370017708251004</v>
@@ -46380,7 +46386,7 @@
         <v>2.468769552860483</v>
       </c>
       <c r="D893" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E893">
         <v>2.370017708251004</v>
@@ -46430,7 +46436,7 @@
         <v>2.485643261633848</v>
       </c>
       <c r="D894" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E894">
         <v>2.370017708251004</v>
@@ -46480,7 +46486,7 @@
         <v>2.48908011602053</v>
       </c>
       <c r="D895" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E895">
         <v>2.370017708251004</v>
@@ -46530,7 +46536,7 @@
         <v>2.546210539230263</v>
       </c>
       <c r="D896" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E896">
         <v>2.35126116481272</v>
@@ -46580,7 +46586,7 @@
         <v>2.468079211032456</v>
       </c>
       <c r="D897" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E897">
         <v>2.35126116481272</v>
@@ -46630,7 +46636,7 @@
         <v>2.484998508417106</v>
       </c>
       <c r="D898" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E898">
         <v>2.35126116481272</v>
@@ -46680,7 +46686,7 @@
         <v>2.48845815710943</v>
       </c>
       <c r="D899" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E899">
         <v>2.35126116481272</v>
@@ -46980,7 +46986,7 @@
         <v>2.486934855642235</v>
       </c>
       <c r="D905" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E905">
         <v>2.316934855642235</v>
@@ -47230,7 +47236,7 @@
         <v>2.490094687204029</v>
       </c>
       <c r="D910" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E910">
         <v>2.351980495447003</v>
@@ -47530,7 +47536,7 @@
         <v>2.493632488343625</v>
       </c>
       <c r="D916" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E916">
         <v>2.323632488343625</v>
@@ -47780,7 +47786,7 @@
         <v>2.496950334223138</v>
       </c>
       <c r="D921" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E921">
         <v>2.326950334223138</v>
@@ -48030,7 +48036,7 @@
         <v>2.499807210510219</v>
       </c>
       <c r="D926" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E926">
         <v>2.329807210510219</v>
@@ -48130,7 +48136,7 @@
         <v>2.564547678565647</v>
       </c>
       <c r="D928" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E928">
         <v>2.357179533157952</v>
@@ -48180,7 +48186,7 @@
         <v>2.486590989790082</v>
       </c>
       <c r="D929" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E929">
         <v>2.357179533157952</v>
@@ -48230,7 +48236,7 @@
         <v>2.468417744892343</v>
       </c>
       <c r="D930" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E930">
         <v>2.357179533157952</v>
@@ -48280,7 +48286,7 @@
         <v>2.505136221933517</v>
       </c>
       <c r="D931" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E931">
         <v>2.335136221933517</v>
@@ -48366,7 +48372,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48380,7 +48386,7 @@
         <v>2.571973511934736</v>
       </c>
       <c r="D933" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E933">
         <v>2.364004227635257</v>
@@ -48416,7 +48422,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48430,7 +48436,7 @@
         <v>2.494087545381733</v>
       </c>
       <c r="D934" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E934">
         <v>2.364004227635257</v>
@@ -48466,7 +48472,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48480,7 +48486,7 @@
         <v>2.475631411593743</v>
       </c>
       <c r="D935" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E935">
         <v>2.364004227635257</v>
@@ -48516,7 +48522,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48530,7 +48536,7 @@
         <v>2.511890194188259</v>
       </c>
       <c r="D936" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E936">
         <v>2.341890194188259</v>
@@ -48566,7 +48572,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -48580,7 +48586,7 @@
         <v>2.469776160741262</v>
       </c>
       <c r="D937" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E937">
         <v>2.341890194188259</v>
@@ -48616,7 +48622,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -48630,7 +48636,7 @@
         <v>2.585546222284397</v>
       </c>
       <c r="D938" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E938">
         <v>2.376478194766136</v>
@@ -48680,7 +48686,7 @@
         <v>2.507789519639486</v>
       </c>
       <c r="D939" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E939">
         <v>2.376478194766136</v>
@@ -48730,7 +48736,7 @@
         <v>2.488816330219128</v>
       </c>
       <c r="D940" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E940">
         <v>2.376478194766136</v>
@@ -48780,7 +48786,7 @@
         <v>2.524234897411047</v>
       </c>
       <c r="D941" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E941">
         <v>2.387599843443681</v>
@@ -48830,7 +48836,7 @@
         <v>2.592366497323944</v>
       </c>
       <c r="D942" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E942">
         <v>2.382746352302482</v>
@@ -48880,7 +48886,7 @@
         <v>2.51467474967941</v>
       </c>
       <c r="D943" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E943">
         <v>2.382746352302482</v>
@@ -48930,7 +48936,7 @@
         <v>2.495441740257546</v>
       </c>
       <c r="D944" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E944">
         <v>2.382746352302482</v>
@@ -48980,7 +48986,7 @@
         <v>2.530438099947015</v>
       </c>
       <c r="D945" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E945">
         <v>2.39812984759155</v>
@@ -49030,7 +49036,7 @@
         <v>2.523049937079764</v>
       </c>
       <c r="D946" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E946">
         <v>2.390370933284879</v>
@@ -49080,7 +49086,7 @@
         <v>2.503500882850339</v>
       </c>
       <c r="D947" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E947">
         <v>2.390370933284879</v>
@@ -49130,7 +49136,7 @@
         <v>2.537983669727523</v>
       </c>
       <c r="D948" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E948">
         <v>2.41440277439149</v>
@@ -49180,7 +49186,7 @@
         <v>2.526835385892296</v>
       </c>
       <c r="D949" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E949">
         <v>2.393817120175534</v>
@@ -49230,7 +49236,7 @@
         <v>2.50714348453787</v>
       </c>
       <c r="D950" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E950">
         <v>2.393817120175534</v>
@@ -49280,7 +49286,7 @@
         <v>2.541394144836927</v>
       </c>
       <c r="D951" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E951">
         <v>2.417759681829017</v>
@@ -49330,7 +49336,7 @@
         <v>2.345028607844837</v>
       </c>
       <c r="D952" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E952">
         <v>2.42987455852205</v>
@@ -49380,7 +49386,7 @@
         <v>2.534209390950705</v>
       </c>
       <c r="D953" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E953">
         <v>2.434239225254452</v>
@@ -49480,7 +49486,7 @@
         <v>2.548037705998041</v>
       </c>
       <c r="D955" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E955">
         <v>2.424298893861947</v>
@@ -49530,7 +49536,7 @@
         <v>2.505545164573978</v>
       </c>
       <c r="D956" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E956">
         <v>2.429283976710074</v>
@@ -49580,7 +49586,7 @@
         <v>2.351776518134136</v>
       </c>
       <c r="D957" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E957">
         <v>2.469254142406326</v>
@@ -49630,7 +49636,7 @@
         <v>2.537683733866443</v>
       </c>
       <c r="D958" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E958">
         <v>2.437582460890351</v>
@@ -49730,7 +49736,7 @@
         <v>2.551167892304201</v>
       </c>
       <c r="D960" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E960">
         <v>2.427379914938167</v>
@@ -49780,7 +49786,7 @@
         <v>2.508642574060178</v>
       </c>
       <c r="D961" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E961">
         <v>2.432430551426213</v>
@@ -49830,7 +49836,7 @@
         <v>2.354955869670236</v>
       </c>
       <c r="D962" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E962">
         <v>2.472531824402305</v>
@@ -49880,7 +49886,7 @@
         <v>2.374955869670236</v>
       </c>
       <c r="D963" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E963">
         <v>2.302531824402305</v>
@@ -49930,7 +49936,7 @@
         <v>2.547057903948727</v>
       </c>
       <c r="D964" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E964">
         <v>2.446602888705379</v>
@@ -50030,7 +50036,7 @@
         <v>2.559613488934938</v>
       </c>
       <c r="D966" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E966">
         <v>2.435692858218683</v>
@@ -50080,7 +50086,7 @@
         <v>2.516999735124102</v>
       </c>
       <c r="D967" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E967">
         <v>2.440920365840357</v>
@@ -50130,7 +50136,7 @@
         <v>2.363534119651194</v>
       </c>
       <c r="D968" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E968">
         <v>2.481375381083705</v>
@@ -50180,7 +50186,7 @@
         <v>2.383534119651195</v>
       </c>
       <c r="D969" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E969">
         <v>2.414840996556613</v>
@@ -50230,7 +50236,7 @@
         <v>2.564343447930323</v>
       </c>
       <c r="D970" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E970">
         <v>2.427963610615813</v>
@@ -50280,7 +50286,7 @@
         <v>2.543236148008424</v>
       </c>
       <c r="D971" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E971">
         <v>2.427963610615813</v>
@@ -50380,7 +50386,7 @@
         <v>2.575186785635339</v>
       </c>
       <c r="D973" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E973">
         <v>2.451021548164626</v>
@@ -50430,7 +50436,7 @@
         <v>2.532409960654864</v>
       </c>
       <c r="D974" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E974">
         <v>2.456575198125576</v>
@@ -50480,7 +50486,7 @@
         <v>2.37935202310605</v>
       </c>
       <c r="D975" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E975">
         <v>2.464905673067</v>
@@ -50530,7 +50536,7 @@
         <v>2.399352023106051</v>
       </c>
       <c r="D976" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E976">
         <v>2.447963610615814</v>
@@ -50580,7 +50586,7 @@
         <v>2.947313892359365</v>
       </c>
       <c r="D977" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E977">
         <v>2.80175874695094</v>
@@ -50630,7 +50636,7 @@
         <v>2.55309257246083</v>
       </c>
       <c r="D978" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E978">
         <v>2.899758008686105</v>
@@ -50680,7 +50686,7 @@
         <v>3.072869037767791</v>
       </c>
       <c r="D979" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E979">
         <v>2.755756532156437</v>
@@ -50730,7 +50736,7 @@
         <v>2.994646241339586</v>
       </c>
       <c r="D980" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E980">
         <v>2.755756532156437</v>
@@ -50780,7 +50786,7 @@
         <v>2.669091095931161</v>
       </c>
       <c r="D981" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E981">
         <v>2.697313892359365</v>
@@ -50830,7 +50836,7 @@
         <v>2.666646979604421</v>
       </c>
       <c r="D982" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E982">
         <v>2.697313892359365</v>
@@ -50880,7 +50886,7 @@
         <v>1.297829535910621</v>
       </c>
       <c r="D983" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E983">
         <v>0.8616678599075076</v>
@@ -50930,7 +50936,7 @@
         <v>0.6201465518963349</v>
       </c>
       <c r="D984" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E984">
         <v>1.150592131893589</v>
@@ -50980,7 +50986,7 @@
         <v>1.478357895886811</v>
       </c>
       <c r="D985" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E985">
         <v>1.02817966388791</v>
@@ -51080,10 +51086,10 @@
         <v>0.7719288718853452</v>
       </c>
       <c r="D987" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E987">
-        <v>0.9677340838906572</v>
+        <v>1.277377619892856</v>
       </c>
       <c r="F987">
         <v>1</v>
@@ -51092,10 +51098,10 @@
         <v>0.01742807112811465</v>
       </c>
       <c r="H987">
-        <v>0.01685226591610934</v>
+        <v>0.01684262238010715</v>
       </c>
       <c r="I987">
-        <v>0.195805212005312</v>
+        <v>0.5054487480075105</v>
       </c>
       <c r="J987">
         <v>1.330362800018315</v>
@@ -51107,10 +51113,10 @@
         <v>9.1</v>
       </c>
       <c r="M987">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N987">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O987">
         <v>1</v>
@@ -51130,7 +51136,7 @@
         <v>0.5600712707795941</v>
       </c>
       <c r="D988" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E988">
         <v>1.088924749687181</v>
@@ -51180,7 +51186,7 @@
         <v>1.41276333099256</v>
       </c>
       <c r="D989" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E989">
         <v>0.9632219394295252</v>
@@ -51280,10 +51286,10 @@
         <v>0.7054851864099394</v>
       </c>
       <c r="D991" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E991">
-        <v>0.9043684605219404</v>
+        <v>1.215285677395871</v>
       </c>
       <c r="F991">
         <v>1</v>
@@ -51292,10 +51298,10 @@
         <v>0.01749451481359006</v>
       </c>
       <c r="H991">
-        <v>0.01691563153947806</v>
+        <v>0.01690471432260413</v>
       </c>
       <c r="I991">
-        <v>0.198883274112001</v>
+        <v>0.5098004909859313</v>
       </c>
       <c r="J991">
         <v>1.340976807282757</v>
@@ -51307,10 +51313,10 @@
         <v>9.1</v>
       </c>
       <c r="M991">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N991">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O991">
         <v>1</v>
@@ -51330,7 +51336,7 @@
         <v>1.488608161168904</v>
       </c>
       <c r="D992" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E992">
         <v>1.058608161168903</v>
@@ -51380,10 +51386,10 @@
         <v>0.7756689823198943</v>
       </c>
       <c r="D993" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E993">
-        <v>0.9286081611689037</v>
+        <v>1.239038147879077</v>
       </c>
       <c r="F993">
         <v>1</v>
@@ -51392,10 +51398,10 @@
         <v>0.01644433101768011</v>
       </c>
       <c r="H993">
-        <v>0.0168913918388311</v>
+        <v>0.01688096185212093</v>
       </c>
       <c r="I993">
-        <v>0.1529391788490093</v>
+        <v>0.4633691655591825</v>
       </c>
       <c r="J993">
         <v>1.336916555918107</v>
@@ -51407,10 +51413,10 @@
         <v>8.609999999999999</v>
       </c>
       <c r="M993">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N993">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O993">
         <v>1</v>
@@ -51430,10 +51436,10 @@
         <v>0.730902359952653</v>
       </c>
       <c r="D994" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E994">
-        <v>0.9286081611689037</v>
+        <v>1.239038147879077</v>
       </c>
       <c r="F994">
         <v>1</v>
@@ -51442,10 +51448,10 @@
         <v>0.01746909764004734</v>
       </c>
       <c r="H994">
-        <v>0.0168913918388311</v>
+        <v>0.01688096185212093</v>
       </c>
       <c r="I994">
-        <v>0.1977058012162507</v>
+        <v>0.5081357879264239</v>
       </c>
       <c r="J994">
         <v>1.336916555918107</v>
@@ -51457,10 +51463,10 @@
         <v>9.1</v>
       </c>
       <c r="M994">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N994">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O994">
         <v>1</v>
@@ -51480,10 +51486,10 @@
         <v>1.462100210182946</v>
       </c>
       <c r="D995" t="s">
-        <v>193</v>
+        <v>347</v>
       </c>
       <c r="E995">
-        <v>0.7496494525413828</v>
+        <v>1.032100210182945</v>
       </c>
       <c r="F995">
         <v>-1</v>
@@ -51492,10 +51498,10 @@
         <v>0.01747789978981706</v>
       </c>
       <c r="H995">
-        <v>0.01647035054745861</v>
+        <v>0.01704789978981705</v>
       </c>
       <c r="I995">
-        <v>0.7124507576415633</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J995">
         <v>1.341356748713074</v>
@@ -51507,10 +51513,10 @@
         <v>9.470000000000001</v>
       </c>
       <c r="M995">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="N995">
-        <v>8.609999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O995">
         <v>1</v>
@@ -51530,10 +51536,10 @@
         <v>0.7031067530561543</v>
       </c>
       <c r="D996" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E996">
-        <v>0.9021002101829456</v>
+        <v>1.213063020028516</v>
       </c>
       <c r="F996">
         <v>1</v>
@@ -51542,10 +51548,10 @@
         <v>0.01749689324694385</v>
       </c>
       <c r="H996">
-        <v>0.01691789978981706</v>
+        <v>0.01690693697997148</v>
       </c>
       <c r="I996">
-        <v>0.1989934571267913</v>
+        <v>0.5099562669723614</v>
       </c>
       <c r="J996">
         <v>1.341356748713074</v>
@@ -51557,10 +51563,10 @@
         <v>9.1</v>
       </c>
       <c r="M996">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N996">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O996">
         <v>1</v>
@@ -51630,10 +51636,10 @@
         <v>0.6897950523407328</v>
       </c>
       <c r="D998" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E998">
-        <v>0.8894051856987506</v>
+        <v>1.200623171915861</v>
       </c>
       <c r="F998">
         <v>1</v>
@@ -51642,10 +51648,10 @@
         <v>0.01751020494765927</v>
       </c>
       <c r="H998">
-        <v>0.01693059481430125</v>
+        <v>0.01691937682808414</v>
       </c>
       <c r="I998">
-        <v>0.1996101333580178</v>
+        <v>0.5108281195751285</v>
       </c>
       <c r="J998">
         <v>1.343483218475921</v>
@@ -51657,10 +51663,10 @@
         <v>9.1</v>
       </c>
       <c r="M998">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N998">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O998">
         <v>1</v>
@@ -51716,7 +51722,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51730,10 +51736,10 @@
         <v>0.6867118341980269</v>
       </c>
       <c r="D1000" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1000">
-        <v>0.8864648003454043</v>
+        <v>1.197741889785697</v>
       </c>
       <c r="F1000">
         <v>1</v>
@@ -51742,10 +51748,10 @@
         <v>0.01751328816580197</v>
       </c>
       <c r="H1000">
-        <v>0.0169335351996546</v>
+        <v>0.01692225811021431</v>
       </c>
       <c r="I1000">
-        <v>0.1997529661473774</v>
+        <v>0.5110300555876703</v>
       </c>
       <c r="J1000">
         <v>1.343975745335778</v>
@@ -51757,16 +51763,16 @@
         <v>9.1</v>
       </c>
       <c r="M1000">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N1000">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O1000">
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51780,10 +51786,10 @@
         <v>1.460084502779063</v>
       </c>
       <c r="D1001" t="s">
-        <v>193</v>
+        <v>347</v>
       </c>
       <c r="E1001">
-        <v>0.7476708854749239</v>
+        <v>1.030084502779061</v>
       </c>
       <c r="F1001">
         <v>-1</v>
@@ -51792,10 +51798,10 @@
         <v>0.01747991549722094</v>
       </c>
       <c r="H1001">
-        <v>0.01647232911452507</v>
+        <v>0.01704991549722094</v>
       </c>
       <c r="I1001">
-        <v>0.7124136173041391</v>
+        <v>0.4300000000000015</v>
       </c>
       <c r="J1001">
         <v>1.341694388144211</v>
@@ -51807,10 +51813,10 @@
         <v>9.470000000000001</v>
       </c>
       <c r="M1001">
-        <v>5.86</v>
+        <v>5.97</v>
       </c>
       <c r="N1001">
-        <v>8.609999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O1001">
         <v>1</v>
@@ -51830,10 +51836,10 @@
         <v>0.7009931302172401</v>
       </c>
       <c r="D1002" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1002">
-        <v>0.9000845027790625</v>
+        <v>1.211087829356368</v>
       </c>
       <c r="F1002">
         <v>1</v>
@@ -51842,10 +51848,10 @@
         <v>0.01749900686978276</v>
       </c>
       <c r="H1002">
-        <v>0.01691991549722094</v>
+        <v>0.01690891217064363</v>
       </c>
       <c r="I1002">
-        <v>0.1990913725618224</v>
+        <v>0.5100946991391284</v>
       </c>
       <c r="J1002">
         <v>1.341694388144211</v>
@@ -51857,10 +51863,10 @@
         <v>9.1</v>
       </c>
       <c r="M1002">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N1002">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O1002">
         <v>1</v>
@@ -51930,10 +51936,10 @@
         <v>0.6936578188804567</v>
       </c>
       <c r="D1004" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1004">
-        <v>0.8930890061847165</v>
+        <v>1.204232945758894</v>
       </c>
       <c r="F1004">
         <v>1</v>
@@ -51942,10 +51948,10 @@
         <v>0.01750634218111954</v>
       </c>
       <c r="H1004">
-        <v>0.01692691099381528</v>
+        <v>0.01691576705424111</v>
       </c>
       <c r="I1004">
-        <v>0.1994311873042598</v>
+        <v>0.5105751268784369</v>
       </c>
       <c r="J1004">
         <v>1.342866163118138</v>
@@ -51957,10 +51963,10 @@
         <v>9.1</v>
       </c>
       <c r="M1004">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N1004">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O1004">
         <v>1</v>
@@ -51980,10 +51986,10 @@
         <v>0.6837427575297426</v>
       </c>
       <c r="D1005" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1005">
-        <v>0.8836332687623916</v>
+        <v>1.194967273410384</v>
       </c>
       <c r="F1005">
         <v>1</v>
@@ -51992,10 +51998,10 @@
         <v>0.01751625724247026</v>
       </c>
       <c r="H1005">
-        <v>0.01693636673123761</v>
+        <v>0.01692503272658962</v>
       </c>
       <c r="I1005">
-        <v>0.199890511232649</v>
+        <v>0.5112245158806417</v>
       </c>
       <c r="J1005">
         <v>1.344450038733268</v>
@@ -52007,10 +52013,10 @@
         <v>9.1</v>
       </c>
       <c r="M1005">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N1005">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O1005">
         <v>1</v>
@@ -52030,10 +52036,10 @@
         <v>0.6537674584469055</v>
       </c>
       <c r="D1006" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1006">
-        <v>0.8550466017456912</v>
+        <v>1.166955212765879</v>
       </c>
       <c r="F1006">
         <v>1</v>
@@ -52042,10 +52048,10 @@
         <v>0.0175462325415531</v>
       </c>
       <c r="H1006">
-        <v>0.01696495339825431</v>
+        <v>0.01695304478723412</v>
       </c>
       <c r="I1006">
-        <v>0.2012791432987857</v>
+        <v>0.5131877543189738</v>
       </c>
       <c r="J1006">
         <v>1.349238425168226</v>
@@ -52057,10 +52063,10 @@
         <v>9.1</v>
       </c>
       <c r="M1006">
-        <v>5.97</v>
+        <v>5.85</v>
       </c>
       <c r="N1006">
-        <v>8.91</v>
+        <v>9.06</v>
       </c>
       <c r="O1006">
         <v>1</v>
@@ -52074,49 +52080,49 @@
         <v>0</v>
       </c>
       <c r="B1007" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C1007">
-        <v>0.9710227407769887</v>
+        <v>0.6424229975026066</v>
       </c>
       <c r="D1007" t="s">
-        <v>193</v>
+        <v>346</v>
       </c>
       <c r="E1007">
-        <v>0.6882475062965234</v>
+        <v>1.156353759647005</v>
       </c>
       <c r="F1007">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1007">
-        <v>0.01640897725922301</v>
+        <v>0.01755757700249739</v>
       </c>
       <c r="H1007">
-        <v>0.01653175249370347</v>
+        <v>0.016963646240353</v>
       </c>
       <c r="I1007">
-        <v>0.2827752344804653</v>
+        <v>0.5139307621443985</v>
       </c>
       <c r="J1007">
-        <v>1.351834896536429</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1007">
-        <v>5.71</v>
+        <v>6.26</v>
       </c>
       <c r="L1007">
-        <v>8.69</v>
+        <v>9.1</v>
       </c>
       <c r="M1007">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N1007">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O1007">
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>348</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52124,13 +52130,13 @@
         <v>0</v>
       </c>
       <c r="B1008" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1008">
         <v>0.5002997890366885</v>
       </c>
       <c r="D1008" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1008">
         <v>0.8376088036369964</v>
@@ -52166,7 +52172,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>194</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52174,13 +52180,13 @@
         <v>0</v>
       </c>
       <c r="B1009" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1009">
         <v>0.4969577705448094</v>
       </c>
       <c r="D1009" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1009">
         <v>0.8340775026818612</v>
@@ -52216,7 +52222,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52224,13 +52230,13 @@
         <v>0</v>
       </c>
       <c r="B1010" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1010">
         <v>0.4920648074520191</v>
       </c>
       <c r="D1010" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1010">
         <v>0.8289074160156744</v>
@@ -52274,13 +52280,13 @@
         <v>0</v>
       </c>
       <c r="B1011" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1011">
         <v>0.5046197380717317</v>
       </c>
       <c r="D1011" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1011">
         <v>0.8421734223519017</v>
@@ -52316,7 +52322,7 @@
         <v>1</v>
       </c>
       <c r="P1011" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1012" spans="1:16">
@@ -52324,13 +52330,13 @@
         <v>0</v>
       </c>
       <c r="B1012" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1012">
         <v>0.5044756313746497</v>
       </c>
       <c r="D1012" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1012">
         <v>0.8420211538595854</v>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3066" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="469">
   <si>
     <t>trade_time</t>
   </si>
@@ -595,9 +595,6 @@
     <t>2021-10-12</t>
   </si>
   <si>
-    <t>2021-10-08</t>
-  </si>
-  <si>
     <t>2021-10-19</t>
   </si>
   <si>
@@ -1055,6 +1052,9 @@
   </si>
   <si>
     <t>2021-09-14</t>
+  </si>
+  <si>
+    <t>2021-10-08</t>
   </si>
   <si>
     <t>2021-09-28</t>
@@ -1778,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1018"/>
+  <dimension ref="A1:P1017"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1839,7 +1839,7 @@
         <v>5.028606163154461</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E2">
         <v>4.601827608720447</v>
@@ -1889,7 +1889,7 @@
         <v>5.040216885937453</v>
       </c>
       <c r="D3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E3">
         <v>4.601827608720447</v>
@@ -1939,7 +1939,7 @@
         <v>1.215042657100271</v>
       </c>
       <c r="D4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E4">
         <v>1.076505618462547</v>
@@ -1989,7 +1989,7 @@
         <v>0.9371889532364994</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5">
         <v>1.106505618462547</v>
@@ -2039,7 +2039,7 @@
         <v>0.9964574725553605</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E6">
         <v>1.106505618462547</v>
@@ -2089,7 +2089,7 @@
         <v>1.217920433917637</v>
       </c>
       <c r="D7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E7">
         <v>1.057140807329312</v>
@@ -2139,7 +2139,7 @@
         <v>0.9443593223263207</v>
       </c>
       <c r="D8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E8">
         <v>1.113675987552369</v>
@@ -2189,7 +2189,7 @@
         <v>2.850211426818262</v>
       </c>
       <c r="D9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E9">
         <v>2.672419106455101</v>
@@ -2239,7 +2239,7 @@
         <v>2.543527980245384</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E10">
         <v>2.701305198692955</v>
@@ -2289,7 +2289,7 @@
         <v>2.517978577322106</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E11">
         <v>2.701305198692955</v>
@@ -2339,7 +2339,7 @@
         <v>2.834636854035667</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E12">
         <v>2.682429174398827</v>
@@ -2389,7 +2389,7 @@
         <v>2.827973543350242</v>
       </c>
       <c r="D13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E13">
         <v>2.682429174398827</v>
@@ -2439,7 +2439,7 @@
         <v>2.72973410868421</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E14">
         <v>2.560228587981063</v>
@@ -2489,7 +2489,7 @@
         <v>2.488324529492481</v>
       </c>
       <c r="D15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E15">
         <v>2.59070829553815</v>
@@ -2539,7 +2539,7 @@
         <v>2.403556997401141</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E16">
         <v>2.59070829553815</v>
@@ -2589,7 +2589,7 @@
         <v>2.724996120072402</v>
       </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E17">
         <v>2.564501640775549</v>
@@ -2639,7 +2639,7 @@
         <v>2.694021933218462</v>
       </c>
       <c r="D18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E18">
         <v>2.674021933218462</v>
@@ -2689,7 +2689,7 @@
         <v>2.608852577284488</v>
       </c>
       <c r="D19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E19">
         <v>2.447661659270211</v>
@@ -2739,7 +2739,7 @@
         <v>2.376077393192739</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E20">
         <v>2.47974032888285</v>
@@ -2789,7 +2789,7 @@
         <v>2.288751521812516</v>
       </c>
       <c r="D21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E21">
         <v>2.47974032888285</v>
@@ -2839,7 +2839,7 @@
         <v>2.614987530650434</v>
       </c>
       <c r="D22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E22">
         <v>2.44617844866471</v>
@@ -2889,7 +2889,7 @@
         <v>2.522977458670185</v>
       </c>
       <c r="D23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E23">
         <v>2.36769329484631</v>
@@ -2925,7 +2925,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2939,7 +2939,7 @@
         <v>2.296336211622314</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E24">
         <v>2.400907878726334</v>
@@ -2975,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2989,7 +2989,7 @@
         <v>2.207192877414276</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E25">
         <v>2.400907878726334</v>
@@ -3025,7 +3025,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3039,7 +3039,7 @@
         <v>2.536836629054347</v>
       </c>
       <c r="D26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E26">
         <v>2.362120792878222</v>
@@ -3075,7 +3075,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3089,7 +3089,7 @@
         <v>2.419036917127896</v>
       </c>
       <c r="D27" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E27">
         <v>2.270902102722273</v>
@@ -3139,7 +3139,7 @@
         <v>2.199819994475903</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E28">
         <v>2.305491561490423</v>
@@ -3189,7 +3189,7 @@
         <v>2.108476860446864</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E29">
         <v>2.305491561490423</v>
@@ -3239,7 +3239,7 @@
         <v>2.442245236751312</v>
       </c>
       <c r="D30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E30">
         <v>2.260380051156934</v>
@@ -3289,7 +3289,7 @@
         <v>1.962237985766278</v>
       </c>
       <c r="D31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E31">
         <v>2.333650929502008</v>
@@ -3339,7 +3339,7 @@
         <v>2.093297693568075</v>
       </c>
       <c r="D32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E32">
         <v>2.333650929502008</v>
@@ -3439,7 +3439,7 @@
         <v>2.51400416543594</v>
       </c>
       <c r="D34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E34">
         <v>2.613650929502008</v>
@@ -3489,7 +3489,7 @@
         <v>2.07288858017555</v>
       </c>
       <c r="D35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E35">
         <v>2.313294552836596</v>
@@ -3589,7 +3589,7 @@
         <v>2.493700525497641</v>
       </c>
       <c r="D37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37">
         <v>2.433294552836596</v>
@@ -3639,7 +3639,7 @@
         <v>2.470046771548235</v>
       </c>
       <c r="D38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E38">
         <v>2.433294552836596</v>
@@ -3689,7 +3689,7 @@
         <v>2.057053876296721</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E39">
         <v>2.258557238944802</v>
@@ -3739,7 +3739,7 @@
         <v>2.018009459771084</v>
       </c>
       <c r="D40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E40">
         <v>2.258557238944802</v>
@@ -3839,7 +3839,7 @@
         <v>2.439105018118521</v>
       </c>
       <c r="D42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42">
         <v>2.379105018118521</v>
@@ -3889,7 +3889,7 @@
         <v>2.414175005555058</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E43">
         <v>2.379105018118521</v>
@@ -3939,7 +3939,7 @@
         <v>2.013779087468848</v>
       </c>
       <c r="D44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E44">
         <v>2.203780066898736</v>
@@ -3989,7 +3989,7 @@
         <v>1.999296599035713</v>
       </c>
       <c r="D45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E45">
         <v>2.203780066898736</v>
@@ -4039,7 +4039,7 @@
         <v>1.963090377952877</v>
       </c>
       <c r="D46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E46">
         <v>2.203780066898736</v>
@@ -4239,7 +4239,7 @@
         <v>1.955311973767153</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E50">
         <v>2.149398606925594</v>
@@ -4289,7 +4289,7 @@
         <v>1.941956562224654</v>
       </c>
       <c r="D51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E51">
         <v>2.149398606925594</v>
@@ -4339,7 +4339,7 @@
         <v>1.908568033368406</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E52">
         <v>2.149398606925594</v>
@@ -4439,7 +4439,7 @@
         <v>2.330229180482781</v>
       </c>
       <c r="D54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E54">
         <v>2.239431724239342</v>
@@ -4489,7 +4489,7 @@
         <v>2.395278856453404</v>
       </c>
       <c r="D55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E55">
         <v>2.239431724239342</v>
@@ -4539,7 +4539,7 @@
         <v>2.358568033368406</v>
       </c>
       <c r="D56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E56">
         <v>2.239431724239342</v>
@@ -4589,7 +4589,7 @@
         <v>1.889864833308684</v>
       </c>
       <c r="D57" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E57">
         <v>2.093583493551073</v>
@@ -4639,7 +4639,7 @@
         <v>1.87777105338948</v>
       </c>
       <c r="D58" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E58">
         <v>2.093583493551073</v>
@@ -4689,7 +4689,7 @@
         <v>1.847536603591471</v>
       </c>
       <c r="D59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E59">
         <v>2.093583493551073</v>
@@ -4739,7 +4739,7 @@
         <v>1.937653828490475</v>
       </c>
       <c r="D60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E60">
         <v>2.093583493551073</v>
@@ -4789,7 +4789,7 @@
         <v>1.933466268652069</v>
       </c>
       <c r="D61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E61">
         <v>2.128524881101571</v>
@@ -4839,7 +4839,7 @@
         <v>2.26951315861167</v>
       </c>
       <c r="D62" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E62">
         <v>2.148759330899581</v>
@@ -4889,7 +4889,7 @@
         <v>2.331724163429878</v>
       </c>
       <c r="D63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E63">
         <v>2.148759330899581</v>
@@ -4939,7 +4939,7 @@
         <v>2.297536603591471</v>
       </c>
       <c r="D64" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E64">
         <v>2.148759330899581</v>
@@ -4989,7 +4989,7 @@
         <v>1.775456318615009</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E65">
         <v>2.014299333031558</v>
@@ -5039,7 +5039,7 @@
         <v>1.750249619911568</v>
       </c>
       <c r="D66" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E66">
         <v>2.014299333031558</v>
@@ -5089,7 +5089,7 @@
         <v>1.837852969263289</v>
       </c>
       <c r="D67" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E67">
         <v>2.014299333031558</v>
@@ -5139,7 +5139,7 @@
         <v>1.689340672772246</v>
       </c>
       <c r="D68" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E68">
         <v>2.014299333031558</v>
@@ -5189,7 +5189,7 @@
         <v>1.837687610300537</v>
       </c>
       <c r="D69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E69">
         <v>2.031489284976398</v>
@@ -5239,7 +5239,7 @@
         <v>2.172728950041225</v>
       </c>
       <c r="D70" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E70">
         <v>2.049092634328118</v>
@@ -5289,7 +5289,7 @@
         <v>2.230414978874321</v>
       </c>
       <c r="D71" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E71">
         <v>2.049092634328118</v>
@@ -5339,7 +5339,7 @@
         <v>2.200249619911569</v>
       </c>
       <c r="D72" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E72">
         <v>2.049092634328118</v>
@@ -5389,7 +5389,7 @@
         <v>1.657250003319568</v>
       </c>
       <c r="D73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E73">
         <v>1.914330752922327</v>
@@ -5439,7 +5439,7 @@
         <v>1.742450261803278</v>
       </c>
       <c r="D74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E74">
         <v>1.914330752922327</v>
@@ -5489,7 +5489,7 @@
         <v>1.588410856315811</v>
       </c>
       <c r="D75" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E75">
         <v>1.914330752922327</v>
@@ -5539,7 +5539,7 @@
         <v>2.080209951622827</v>
       </c>
       <c r="D76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E76">
         <v>1.829850132561424</v>
@@ -5589,7 +5589,7 @@
         <v>2.133570416893503</v>
       </c>
       <c r="D77" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E77">
         <v>1.829850132561424</v>
@@ -5639,7 +5639,7 @@
         <v>2.107250003319568</v>
       </c>
       <c r="D78" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E78">
         <v>1.829850132561424</v>
@@ -5689,7 +5689,7 @@
         <v>1.545168899465309</v>
       </c>
       <c r="D79" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E79">
         <v>1.804468343102783</v>
@@ -5739,7 +5739,7 @@
         <v>1.627473005394645</v>
       </c>
       <c r="D80" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E80">
         <v>1.804468343102783</v>
@@ -5789,7 +5789,7 @@
         <v>1.466772449032118</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E81">
         <v>1.804468343102783</v>
@@ -5839,7 +5839,7 @@
         <v>1.551629720651176</v>
       </c>
       <c r="D82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E82">
         <v>1.826938488872376</v>
@@ -5889,7 +5889,7 @@
         <v>1.968708078279442</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E83">
         <v>1.716320952429977</v>
@@ -5939,7 +5939,7 @@
         <v>2.016855468952246</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E84">
         <v>1.716320952429977</v>
@@ -5989,7 +5989,7 @@
         <v>1.995168899465309</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E85">
         <v>1.716320952429977</v>
@@ -6139,7 +6139,7 @@
         <v>1.313264500703522</v>
       </c>
       <c r="D88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E88">
         <v>1.590411561109409</v>
@@ -6189,7 +6189,7 @@
         <v>1.732793914578037</v>
       </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E89">
         <v>1.476117440297638</v>
@@ -6239,7 +6239,7 @@
         <v>1.769911552142724</v>
       </c>
       <c r="D90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E90">
         <v>1.476117440297638</v>
@@ -6289,7 +6289,7 @@
         <v>1.75802920764078</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E91">
         <v>1.476117440297638</v>
@@ -6339,7 +6339,7 @@
         <v>1.258237544033932</v>
       </c>
       <c r="D92" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E92">
         <v>1.56590422061944</v>
@@ -6375,7 +6375,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6389,7 +6389,7 @@
         <v>1.678332787797079</v>
       </c>
       <c r="D93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E93">
         <v>1.525332758040558</v>
@@ -6425,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6439,7 +6439,7 @@
         <v>1.712904190862917</v>
       </c>
       <c r="D94" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E94">
         <v>1.525332758040558</v>
@@ -6475,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6489,7 +6489,7 @@
         <v>1.703285165915505</v>
       </c>
       <c r="D95" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E95">
         <v>1.525332758040558</v>
@@ -6525,7 +6525,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6539,7 +6539,7 @@
         <v>0.5938182775466023</v>
       </c>
       <c r="D96" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E96">
         <v>0.8343117874589812</v>
@@ -6589,7 +6589,7 @@
         <v>0.956860945497624</v>
       </c>
       <c r="D97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E97">
         <v>0.585265392082662</v>
@@ -6639,7 +6639,7 @@
         <v>0.5810056569512305</v>
       </c>
       <c r="D98" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E98">
         <v>0.7840483249022538</v>
@@ -6689,7 +6689,7 @@
         <v>0.5553058141248099</v>
       </c>
       <c r="D99" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E99">
         <v>0.7944238789149818</v>
@@ -6739,7 +6739,7 @@
         <v>0.9198221732781962</v>
       </c>
       <c r="D100" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E100">
         <v>0.5506827718671756</v>
@@ -6789,7 +6789,7 @@
         <v>0.5443598690524336</v>
       </c>
       <c r="D101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E101">
         <v>0.7488762282058206</v>
@@ -6839,7 +6839,7 @@
         <v>0.4093999017952683</v>
       </c>
       <c r="D102" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E102">
         <v>0.6433070411450998</v>
@@ -6889,7 +6889,7 @@
         <v>0.7794993953490197</v>
       </c>
       <c r="D103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E103">
         <v>0.8895325598669377</v>
@@ -6939,7 +6939,7 @@
         <v>0.405525926963354</v>
       </c>
       <c r="D104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E104">
         <v>0.615625420517107</v>
@@ -6989,7 +6989,7 @@
         <v>0.3689689640067657</v>
       </c>
       <c r="D105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E105">
         <v>0.6014321412927224</v>
@@ -7039,7 +7039,7 @@
         <v>0.740615559771812</v>
       </c>
       <c r="D106" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E106">
         <v>0.3833598860468914</v>
@@ -7089,7 +7089,7 @@
         <v>0.3670546519758249</v>
       </c>
       <c r="D107" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E107">
         <v>0.5787012477408719</v>
@@ -7139,7 +7139,7 @@
         <v>0.2652632672207957</v>
       </c>
       <c r="D108" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E108">
         <v>0.494022669621538</v>
@@ -7189,7 +7189,7 @@
         <v>0.6408781932199989</v>
       </c>
       <c r="D109" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E109">
         <v>0.2902364032186728</v>
@@ -7239,7 +7239,7 @@
         <v>0.2683755068197868</v>
       </c>
       <c r="D110" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E110">
         <v>0.4839904328189908</v>
@@ -7289,7 +7289,7 @@
         <v>0.5427390896188848</v>
       </c>
       <c r="D111" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E111">
         <v>0.4852417760190972</v>
@@ -7339,7 +7339,7 @@
         <v>0.2319266556591515</v>
       </c>
       <c r="D112" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E112">
         <v>0.4594954647898355</v>
@@ -7389,7 +7389,7 @@
         <v>0.6088172173048463</v>
       </c>
       <c r="D113" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E113">
         <v>0.2603014867143392</v>
@@ -7439,7 +7439,7 @@
         <v>0.2366547004103658</v>
       </c>
       <c r="D114" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E114">
         <v>0.4535452620560614</v>
@@ -7539,7 +7539,7 @@
         <v>0.1698091881469042</v>
       </c>
       <c r="D116" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E116">
         <v>0.4494895079522143</v>
@@ -7589,7 +7589,7 @@
         <v>0.2222657318159307</v>
       </c>
       <c r="D117" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E117">
         <v>0.4494895079522143</v>
@@ -7639,7 +7639,7 @@
         <v>0.5995259716699124</v>
       </c>
       <c r="D118" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E118">
         <v>0.251626371426549</v>
@@ -7689,7 +7689,7 @@
         <v>0.2274620356309747</v>
       </c>
       <c r="D119" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E119">
         <v>0.4447222754849562</v>
@@ -7739,7 +7739,7 @@
         <v>0.1319562177001394</v>
       </c>
       <c r="D120" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E120">
         <v>0.4134136722682085</v>
@@ -7789,7 +7789,7 @@
         <v>0.1874338904658561</v>
       </c>
       <c r="D121" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E121">
         <v>0.4134136722682085</v>
@@ -7839,7 +7839,7 @@
         <v>0.5660269813919063</v>
       </c>
       <c r="D122" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E122">
         <v>0.2203487996019922</v>
@@ -7889,7 +7889,7 @@
         <v>0.1943184723055209</v>
       </c>
       <c r="D123" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E123">
         <v>0.4129115632315719</v>
@@ -7939,7 +7939,7 @@
         <v>0.4849216723303957</v>
       </c>
       <c r="D124" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E124">
         <v>0.4323589087008166</v>
@@ -7989,7 +7989,7 @@
         <v>0.08200931527144117</v>
       </c>
       <c r="D125" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E125">
         <v>0.3658116948361627</v>
@@ -8039,7 +8039,7 @@
         <v>0.1414733605314673</v>
       </c>
       <c r="D126" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E126">
         <v>0.3658116948361627</v>
@@ -8089,7 +8089,7 @@
         <v>0.5218251452050078</v>
       </c>
       <c r="D127" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E127">
         <v>0.1790781196609093</v>
@@ -8139,7 +8139,7 @@
         <v>0.1505856211179522</v>
       </c>
       <c r="D128" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E128">
         <v>0.3709374057914925</v>
@@ -8239,7 +8239,7 @@
         <v>0.1301209626132955</v>
       </c>
       <c r="D130" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E130">
         <v>0.3249118201990129</v>
@@ -8289,7 +8289,7 @@
         <v>0.0390946684846778</v>
       </c>
       <c r="D131" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E131">
         <v>0.3249118201990129</v>
@@ -8339,7 +8339,7 @@
         <v>0.4838466901847962</v>
       </c>
       <c r="D132" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E132">
         <v>0.1436181298277148</v>
@@ -8389,7 +8389,7 @@
         <v>0.1130101205276635</v>
       </c>
       <c r="D133" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E133">
         <v>0.3348729843134146</v>
@@ -8489,7 +8489,7 @@
         <v>0.1185053657063797</v>
       </c>
       <c r="D135" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E135">
         <v>0.3133247628422371</v>
@@ -8539,7 +8539,7 @@
         <v>0.02693682012510568</v>
       </c>
       <c r="D136" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E136">
         <v>0.3133247628422371</v>
@@ -8589,7 +8589,7 @@
         <v>0.4730872797820762</v>
       </c>
       <c r="D137" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E137">
         <v>0.1335722081784905</v>
@@ -8639,7 +8639,7 @@
         <v>0.1023648683255027</v>
       </c>
       <c r="D138" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E138">
         <v>0.3246558253633509</v>
@@ -8689,7 +8689,7 @@
         <v>0.4703213566239093</v>
       </c>
       <c r="D139" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E139">
         <v>0.5140571365749054</v>
@@ -8739,7 +8739,7 @@
         <v>0.1082747062549414</v>
       </c>
       <c r="D140" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E140">
         <v>0.3031192401462075</v>
@@ -8789,7 +8789,7 @@
         <v>0.01622856232089642</v>
       </c>
       <c r="D141" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E141">
         <v>0.3031192401462075</v>
@@ -8839,7 +8839,7 @@
         <v>0.4636107229929056</v>
       </c>
       <c r="D142" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E142">
         <v>0.1247240702745431</v>
@@ -8889,7 +8889,7 @@
         <v>0.0929888585579679</v>
       </c>
       <c r="D143" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E143">
         <v>0.3156568669269504</v>
@@ -8939,7 +8939,7 @@
         <v>0.4619256803173224</v>
       </c>
       <c r="D144" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E144">
         <v>0.4194382225775701</v>
@@ -8989,7 +8989,7 @@
         <v>0.1029539075611501</v>
       </c>
       <c r="D145" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E145">
         <v>0.2978115146678801</v>
@@ -9039,7 +9039,7 @@
         <v>0.01065937253329263</v>
       </c>
       <c r="D146" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E146">
         <v>0.2978115146678801</v>
@@ -9089,7 +9089,7 @@
         <v>0.4586821207630312</v>
       </c>
       <c r="D147" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E147">
         <v>0.1201222984312649</v>
@@ -9139,7 +9139,7 @@
         <v>0.08811254918994837</v>
       </c>
       <c r="D148" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E148">
         <v>0.3109766557908884</v>
@@ -9189,7 +9189,7 @@
         <v>0.4575592263523935</v>
       </c>
       <c r="D149" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E149">
         <v>0.3255657258466043</v>
@@ -9239,7 +9239,7 @@
         <v>0.02638546696888966</v>
       </c>
       <c r="D150" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E150">
         <v>0.3127992948107261</v>
@@ -9289,7 +9289,7 @@
         <v>0.4725993451813872</v>
       </c>
       <c r="D151" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E151">
         <v>0.1331166299836823</v>
@@ -9339,7 +9339,7 @@
         <v>0.101882110749755</v>
       </c>
       <c r="D152" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E152">
         <v>0.3241924816311323</v>
@@ -9439,7 +9439,7 @@
         <v>0.08340592620937315</v>
       </c>
       <c r="D154" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E154">
         <v>0.3671427371854588</v>
@@ -9489,7 +9489,7 @@
         <v>0.5230611131007823</v>
       </c>
       <c r="D155" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E155">
         <v>0.18023212682089</v>
@@ -9539,7 +9539,7 @@
         <v>0.1518084752959998</v>
       </c>
       <c r="D156" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E156">
         <v>0.3721110835280639</v>
@@ -9639,7 +9639,7 @@
         <v>0.1326336220486173</v>
       </c>
       <c r="D158" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E158">
         <v>0.4140592735956314</v>
@@ -9689,7 +9689,7 @@
         <v>0.5666264683387991</v>
       </c>
       <c r="D159" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E159">
         <v>0.2209085327725662</v>
@@ -9739,7 +9739,7 @@
         <v>0.2697669895764108</v>
       </c>
       <c r="D160" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E160">
         <v>0.4134808373084624</v>
@@ -9839,7 +9839,7 @@
         <v>0.5970514875023341</v>
       </c>
       <c r="D162" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E162">
         <v>0.2493159777210128</v>
@@ -9889,7 +9889,7 @@
         <v>0.2989007612422894</v>
       </c>
       <c r="D163" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E163">
         <v>0.4423725000685295</v>
@@ -9989,7 +9989,7 @@
         <v>0.8264673601681558</v>
       </c>
       <c r="D165" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E165">
         <v>0.9378275992619312</v>
@@ -10025,7 +10025,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10039,7 +10039,7 @@
         <v>0.8485077188088193</v>
       </c>
       <c r="D166" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E166">
         <v>0.9378275992619312</v>
@@ -10075,7 +10075,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10089,7 +10089,7 @@
         <v>1.04238664288683</v>
       </c>
       <c r="D167" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E167">
         <v>0.885879418334687</v>
@@ -10125,7 +10125,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10139,7 +10139,7 @@
         <v>0.8582684061162329</v>
       </c>
       <c r="D168" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E168">
         <v>0.9701707084932139</v>
@@ -10189,7 +10189,7 @@
         <v>0.8811218596817048</v>
       </c>
       <c r="D169" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E169">
         <v>0.9701707084932139</v>
@@ -10239,7 +10239,7 @@
         <v>1.072561498985289</v>
       </c>
       <c r="D170" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E170">
         <v>0.9147894601056654</v>
@@ -10289,7 +10289,7 @@
         <v>0.890454471710437</v>
       </c>
       <c r="D171" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E171">
         <v>1.002905400205501</v>
@@ -10325,7 +10325,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10339,7 +10339,7 @@
         <v>0.9141308644530337</v>
       </c>
       <c r="D172" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E172">
         <v>1.002905400205501</v>
@@ -10375,7 +10375,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10389,7 +10389,7 @@
         <v>1.063379316961259</v>
       </c>
       <c r="D173" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E173">
         <v>0.9440495197367609</v>
@@ -10425,7 +10425,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10439,7 +10439,7 @@
         <v>1.103101686225244</v>
       </c>
       <c r="D174" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E174">
         <v>0.9440495197367609</v>
@@ -10475,7 +10475,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10489,7 +10489,7 @@
         <v>0.8952216225869147</v>
       </c>
       <c r="D175" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E175">
         <v>1.007753809335554</v>
@@ -10539,7 +10539,7 @@
         <v>0.9190199027098753</v>
       </c>
       <c r="D176" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E176">
         <v>1.007753809335554</v>
@@ -10589,7 +10589,7 @@
         <v>1.066108600501315</v>
       </c>
       <c r="D177" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E177">
         <v>0.9483832932608314</v>
@@ -10639,7 +10639,7 @@
         <v>1.068132924795474</v>
       </c>
       <c r="D178" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E178">
         <v>0.9483832932608314</v>
@@ -10689,7 +10689,7 @@
         <v>1.107625062340992</v>
       </c>
       <c r="D179" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E179">
         <v>0.9483832932608314</v>
@@ -10789,7 +10789,7 @@
         <v>0.9002742157630061</v>
       </c>
       <c r="D181" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E181">
         <v>1.012892526258966</v>
@@ -10839,7 +10839,7 @@
         <v>0.924201681506946</v>
       </c>
       <c r="D182" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E182">
         <v>1.012892526258966</v>
@@ -10889,7 +10889,7 @@
         <v>1.071304733256273</v>
       </c>
       <c r="D183" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E183">
         <v>0.9529765597845508</v>
@@ -10939,7 +10939,7 @@
         <v>1.073171164013679</v>
       </c>
       <c r="D184" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E184">
         <v>0.9529765597845508</v>
@@ -10989,7 +10989,7 @@
         <v>1.112419284275125</v>
       </c>
       <c r="D185" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E185">
         <v>0.9529765597845508</v>
@@ -11139,7 +11139,7 @@
         <v>1.074651024327075</v>
       </c>
       <c r="D188" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E188">
         <v>0.9559346071399553</v>
@@ -11189,7 +11189,7 @@
         <v>1.076415772206639</v>
       </c>
       <c r="D189" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E189">
         <v>0.9559346071399553</v>
@@ -11239,7 +11239,7 @@
         <v>1.115506746202329</v>
       </c>
       <c r="D190" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E190">
         <v>0.9559346071399553</v>
@@ -11339,7 +11339,7 @@
         <v>1.1321100696318</v>
       </c>
       <c r="D192" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E192">
         <v>0.9718419828807665</v>
@@ -11439,7 +11439,7 @@
         <v>1.161282995049877</v>
       </c>
       <c r="D194" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E194">
         <v>0.9997920910657498</v>
@@ -11489,7 +11489,7 @@
         <v>1.18828947410149</v>
       </c>
       <c r="D195" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E195">
         <v>1.025666562013403</v>
@@ -11539,7 +11539,7 @@
         <v>1.215609088742732</v>
       </c>
       <c r="D196" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E196">
         <v>1.051841043106808</v>
@@ -11589,7 +11589,7 @@
         <v>1.240067525701835</v>
       </c>
       <c r="D197" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E197">
         <v>1.075274276121518</v>
@@ -11625,7 +11625,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11675,7 +11675,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11725,7 +11725,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11739,7 +11739,7 @@
         <v>1.268045594928877</v>
       </c>
       <c r="D200" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E200">
         <v>1.102079611907905</v>
@@ -11889,7 +11889,7 @@
         <v>1.286712805706288</v>
       </c>
       <c r="D203" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E203">
         <v>1.119964364748539</v>
@@ -11989,7 +11989,7 @@
         <v>1.302282242677217</v>
       </c>
       <c r="D205" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E205">
         <v>1.13488119058895</v>
@@ -12089,7 +12089,7 @@
         <v>1.311299224369049</v>
       </c>
       <c r="D207" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E207">
         <v>1.143520214964358</v>
@@ -13475,7 +13475,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13525,7 +13525,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13575,7 +13575,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13589,7 +13589,7 @@
         <v>0.8200792964932733</v>
       </c>
       <c r="D237" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E237">
         <v>0.8219030850898417</v>
@@ -13625,7 +13625,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13639,7 +13639,7 @@
         <v>0.937074891230151</v>
       </c>
       <c r="D238" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E238">
         <v>0.8219030850898417</v>
@@ -13675,7 +13675,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13789,7 +13789,7 @@
         <v>0.8190773400228082</v>
       </c>
       <c r="D241" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E241">
         <v>0.8460555597919894</v>
@@ -13839,7 +13839,7 @@
         <v>0.9360555597919893</v>
       </c>
       <c r="D242" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E242">
         <v>0.8460555597919894</v>
@@ -14125,7 +14125,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14175,7 +14175,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14225,7 +14225,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14275,7 +14275,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14289,7 +14289,7 @@
         <v>0.7963991260233625</v>
       </c>
       <c r="D251" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E251">
         <v>0.848389834527401</v>
@@ -14325,7 +14325,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14339,7 +14339,7 @@
         <v>0.8040407192610317</v>
       </c>
       <c r="D252" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E252">
         <v>0.848389834527401</v>
@@ -14375,7 +14375,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14925,7 +14925,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14975,7 +14975,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15025,7 +15025,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15075,7 +15075,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15125,7 +15125,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15175,7 +15175,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15225,7 +15225,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15275,7 +15275,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15325,7 +15325,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15339,7 +15339,7 @@
         <v>0.709400862280603</v>
       </c>
       <c r="D272" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E272">
         <v>0.7643754237703098</v>
@@ -15375,7 +15375,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15389,7 +15389,7 @@
         <v>0.7145280548320647</v>
       </c>
       <c r="D273" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E273">
         <v>0.7643754237703098</v>
@@ -15425,7 +15425,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15439,7 +15439,7 @@
         <v>0.749400862280603</v>
       </c>
       <c r="D274" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E274">
         <v>0.7643754237703098</v>
@@ -15475,7 +15475,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15525,7 +15525,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15575,7 +15575,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15625,7 +15625,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15639,7 +15639,7 @@
         <v>0.6652568429569481</v>
       </c>
       <c r="D278" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E278">
         <v>0.7257163014198733</v>
@@ -15675,7 +15675,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15689,7 +15689,7 @@
         <v>0.669108196799634</v>
       </c>
       <c r="D279" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E279">
         <v>0.7257163014198733</v>
@@ -15725,7 +15725,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15739,7 +15739,7 @@
         <v>0.7052568429569481</v>
       </c>
       <c r="D280" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E280">
         <v>0.7257163014198733</v>
@@ -15775,7 +15775,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -16239,7 +16239,7 @@
         <v>0.5098981945395424</v>
       </c>
       <c r="D290" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E290">
         <v>0.4597052829411883</v>
@@ -16289,7 +16289,7 @@
         <v>0.4670290224146925</v>
       </c>
       <c r="D291" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E291">
         <v>0.4597052829411883</v>
@@ -16339,7 +16339,7 @@
         <v>0.4288915341107993</v>
       </c>
       <c r="D292" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E292">
         <v>0.4597052829411883</v>
@@ -16639,7 +16639,7 @@
         <v>0.3683952712899403</v>
       </c>
       <c r="D298" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E298">
         <v>0.375715173934144</v>
@@ -16789,7 +16789,7 @@
         <v>0.3328925326816705</v>
       </c>
       <c r="D301" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E301">
         <v>0.3761370628624148</v>
@@ -17189,7 +17189,7 @@
         <v>0.2591964526318904</v>
       </c>
       <c r="D309" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E309">
         <v>0.1842681443037231</v>
@@ -17239,7 +17239,7 @@
         <v>0.1964622097836042</v>
       </c>
       <c r="D310" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E310">
         <v>0.1842681443037231</v>
@@ -17289,7 +17289,7 @@
         <v>0.2493398359755563</v>
       </c>
       <c r="D311" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E311">
         <v>0.1842681443037231</v>
@@ -17339,7 +17339,7 @@
         <v>0.2221683550801181</v>
       </c>
       <c r="D312" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E312">
         <v>0.1904669351684678</v>
@@ -17389,7 +17389,7 @@
         <v>0.1768500318498596</v>
       </c>
       <c r="D313" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E313">
         <v>0.1904669351684678</v>
@@ -17439,7 +17439,7 @@
         <v>0.2296162252126424</v>
       </c>
       <c r="D314" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E314">
         <v>0.1904669351684678</v>
@@ -17489,7 +17489,7 @@
         <v>0.2053553502696301</v>
       </c>
       <c r="D315" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E315">
         <v>0.1123646202766642</v>
@@ -17539,7 +17539,7 @@
         <v>0.1596958936084336</v>
       </c>
       <c r="D316" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E316">
         <v>0.1123646202766642</v>
@@ -17589,7 +17589,7 @@
         <v>0.1543584402719747</v>
       </c>
       <c r="D317" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E317">
         <v>0.1123646202766642</v>
@@ -17689,7 +17689,7 @@
         <v>0.1340998453989064</v>
       </c>
       <c r="D319" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E319">
         <v>0.08288478726310178</v>
@@ -17739,7 +17739,7 @@
         <v>0.129053256246646</v>
       </c>
       <c r="D320" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E320">
         <v>0.08288478726310178</v>
@@ -17839,7 +17839,7 @@
         <v>0.1049880441022522</v>
       </c>
       <c r="D322" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E322">
         <v>0.1511669874093613</v>
@@ -17889,7 +17889,7 @@
         <v>0.100272270873818</v>
       </c>
       <c r="D323" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E323">
         <v>0.1511669874093613</v>
@@ -18189,7 +18189,7 @@
         <v>0.02103995734812436</v>
       </c>
       <c r="D329" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E329">
         <v>0.06193314098385727</v>
@@ -18239,7 +18239,7 @@
         <v>0.0172781396509869</v>
       </c>
       <c r="D330" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E330">
         <v>0.06193314098385727</v>
@@ -18289,7 +18289,7 @@
         <v>-0.03024549574328894</v>
       </c>
       <c r="D331" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E331">
         <v>0.06193314098385727</v>
@@ -18489,7 +18489,7 @@
         <v>-0.02692077305540685</v>
       </c>
       <c r="D335" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E335">
         <v>0.02601619170547753</v>
@@ -18539,7 +18539,7 @@
         <v>-0.03013758245250386</v>
       </c>
       <c r="D336" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E336">
         <v>0.02601619170547753</v>
@@ -18589,7 +18589,7 @@
         <v>-0.07657120124669881</v>
       </c>
       <c r="D337" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E337">
         <v>0.02601619170547753</v>
@@ -18739,7 +18739,7 @@
         <v>-0.0666863454204627</v>
       </c>
       <c r="D340" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E340">
         <v>0.05932763892745285</v>
@@ -18789,7 +18789,7 @@
         <v>-0.06945127331341183</v>
       </c>
       <c r="D341" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E341">
         <v>0.05932763892745285</v>
@@ -18839,7 +18839,7 @@
         <v>-0.1149811290993101</v>
       </c>
       <c r="D342" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E342">
         <v>0.05932763892745285</v>
@@ -18989,7 +18989,7 @@
         <v>-0.1222098013248543</v>
       </c>
       <c r="D345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E345">
         <v>0.03478777543614875</v>
@@ -19039,7 +19039,7 @@
         <v>-0.124343780855253</v>
       </c>
       <c r="D346" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E346">
         <v>0.03478777543614875</v>
@@ -19089,7 +19089,7 @@
         <v>-0.1686117399160514</v>
       </c>
       <c r="D347" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E347">
         <v>0.03478777543614875</v>
@@ -19239,7 +19239,7 @@
         <v>-0.1678666819248154</v>
       </c>
       <c r="D350" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E350">
         <v>-0.008923499456428452</v>
@@ -19289,7 +19289,7 @@
         <v>-0.1694818332665786</v>
       </c>
       <c r="D351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E351">
         <v>-0.008923499456428452</v>
@@ -19339,7 +19339,7 @@
         <v>-0.2127121359501061</v>
       </c>
       <c r="D352" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E352">
         <v>-0.008923499456428452</v>
@@ -19489,7 +19489,7 @@
         <v>-0.2230704748734498</v>
       </c>
       <c r="D355" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E355">
         <v>-0.06177485804645588</v>
@@ -19539,7 +19539,7 @@
         <v>-0.2240583103862512</v>
       </c>
       <c r="D356" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E356">
         <v>-0.06177485804645588</v>
@@ -19589,7 +19589,7 @@
         <v>-0.2660339814118542</v>
       </c>
       <c r="D357" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E357">
         <v>-0.06177485804645588</v>
@@ -19739,7 +19739,7 @@
         <v>-0.2547475324515673</v>
       </c>
       <c r="D360" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E360">
         <v>-0.09210204101187003</v>
@@ -19789,7 +19789,7 @@
         <v>-0.2553754014009808</v>
       </c>
       <c r="D361" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E361">
         <v>-0.09210204101187003</v>
@@ -19839,7 +19839,7 @@
         <v>-0.2966311392998087</v>
       </c>
       <c r="D362" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E362">
         <v>-0.09210204101187003</v>
@@ -19889,7 +19889,7 @@
         <v>0.1392877125289997</v>
       </c>
       <c r="D363" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E363">
         <v>0.06960164700370619</v>
@@ -20039,7 +20039,7 @@
         <v>-0.2851514146282588</v>
       </c>
       <c r="D366" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E366">
         <v>-0.1212103032094403</v>
@@ -20089,7 +20089,7 @@
         <v>-0.2854337849165738</v>
       </c>
       <c r="D367" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E367">
         <v>-0.1212103032094403</v>
@@ -20139,7 +20139,7 @@
         <v>-0.3259985254932039</v>
       </c>
       <c r="D368" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E368">
         <v>-0.1212103032094403</v>
@@ -20189,7 +20189,7 @@
         <v>0.1121660676327467</v>
       </c>
       <c r="D369" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E369">
         <v>-0.02205741407438655</v>
@@ -20289,7 +20289,7 @@
         <v>-0.3208678237650178</v>
       </c>
       <c r="D371" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E371">
         <v>-0.1554047062750312</v>
@@ -20339,7 +20339,7 @@
         <v>-0.3207443257676879</v>
       </c>
       <c r="D372" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E372">
         <v>-0.1554047062750312</v>
@@ -20389,7 +20389,7 @@
         <v>-0.3604973297730281</v>
       </c>
       <c r="D373" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E373">
         <v>-0.1554047062750312</v>
@@ -20439,7 +20439,7 @@
         <v>0.08030540720961454</v>
       </c>
       <c r="D374" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E374">
         <v>-0.1700650867823734</v>
@@ -20539,7 +20539,7 @@
         <v>-0.345691858448542</v>
       </c>
       <c r="D376" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E376">
         <v>-0.1791708985714733</v>
@@ -20589,7 +20589,7 @@
         <v>-0.3452862691479899</v>
       </c>
       <c r="D377" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E377">
         <v>-0.1791708985714733</v>
@@ -20639,7 +20639,7 @@
         <v>-0.3844750905468866</v>
       </c>
       <c r="D378" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E378">
         <v>-0.1791708985714733</v>
@@ -20789,7 +20789,7 @@
         <v>-0.3598244404072002</v>
       </c>
       <c r="D381" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E381">
         <v>-0.1927012398216661</v>
@@ -20839,7 +20839,7 @@
         <v>-0.3592582535843913</v>
       </c>
       <c r="D382" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E382">
         <v>-0.1927012398216661</v>
@@ -20889,7 +20889,7 @@
         <v>-0.3981258799387728</v>
       </c>
       <c r="D383" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E383">
         <v>-0.1927012398216661</v>
@@ -20939,7 +20939,7 @@
         <v>0.04555433440948597</v>
       </c>
       <c r="D384" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E384">
         <v>-0.07331329194489644</v>
@@ -20989,7 +20989,7 @@
         <v>-0.03472875900191852</v>
       </c>
       <c r="D385" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E385">
         <v>-0.07331329194489644</v>
@@ -21089,7 +21089,7 @@
         <v>-0.3763080661355378</v>
       </c>
       <c r="D387" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E387">
         <v>-0.2084824383172617</v>
@@ -21139,7 +21139,7 @@
         <v>-0.3755545653839976</v>
       </c>
       <c r="D388" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E388">
         <v>-0.2084824383172617</v>
@@ -21189,7 +21189,7 @@
         <v>-0.4140475638809171</v>
       </c>
       <c r="D389" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E389">
         <v>-0.2084824383172617</v>
@@ -21239,7 +21239,7 @@
         <v>0.03085019100409347</v>
       </c>
       <c r="D390" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E390">
         <v>-0.09764280749282594</v>
@@ -21289,7 +21289,7 @@
         <v>-0.04952655937167627</v>
       </c>
       <c r="D391" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E391">
         <v>-0.09764280749282594</v>
@@ -21389,7 +21389,7 @@
         <v>-0.4007277092358548</v>
       </c>
       <c r="D393" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E393">
         <v>-0.2318614716263721</v>
@@ -21439,7 +21439,7 @@
         <v>-0.3996967125399919</v>
       </c>
       <c r="D394" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E394">
         <v>-0.2318614716263721</v>
@@ -21489,7 +21489,7 @@
         <v>-0.4376347191482681</v>
       </c>
       <c r="D395" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E395">
         <v>-0.2318614716263721</v>
@@ -21539,7 +21539,7 @@
         <v>0.009066759374833921</v>
       </c>
       <c r="D396" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E396">
         <v>-0.1304177422772348</v>
@@ -21589,7 +21589,7 @@
         <v>-0.07144873897309711</v>
       </c>
       <c r="D397" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E397">
         <v>-0.1304177422772348</v>
@@ -21689,7 +21689,7 @@
         <v>-0.4077205864393338</v>
       </c>
       <c r="D399" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E399">
         <v>-0.2385563569035662</v>
@@ -21739,7 +21739,7 @@
         <v>-0.406610125229796</v>
       </c>
       <c r="D400" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E400">
         <v>-0.2385563569035662</v>
@@ -21789,7 +21789,7 @@
         <v>-0.4443892028107195</v>
       </c>
       <c r="D401" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E401">
         <v>-0.2385563569035662</v>
@@ -21839,7 +21839,7 @@
         <v>0.002828795051275534</v>
       </c>
       <c r="D402" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E402">
         <v>0.005604948075121463</v>
@@ -21889,7 +21889,7 @@
         <v>-0.07772643555349301</v>
       </c>
       <c r="D403" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E403">
         <v>0.005604948075121463</v>
@@ -21939,7 +21939,7 @@
         <v>0.4861229225744816</v>
       </c>
       <c r="D404" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E404">
         <v>0.1770614712898908</v>
@@ -21989,7 +21989,7 @@
         <v>0.4461229225744816</v>
       </c>
       <c r="D405" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E405">
         <v>0.1770614712898908</v>
@@ -22039,7 +22039,7 @@
         <v>0.4906257158146907</v>
       </c>
       <c r="D406" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E406">
         <v>0.1770614712898908</v>
@@ -22089,7 +22089,7 @@
         <v>0.4546033698930207</v>
       </c>
       <c r="D407" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E407">
         <v>0.1770614712898908</v>
@@ -22139,7 +22139,7 @@
         <v>0.4875866104517694</v>
       </c>
       <c r="D408" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E408">
         <v>0.1770614712898908</v>
@@ -22189,7 +22189,7 @@
         <v>-0.02241338954823124</v>
       </c>
       <c r="D409" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E409">
         <v>0.3145475050888473</v>
@@ -22239,7 +22239,7 @@
         <v>0.05951957268676189</v>
       </c>
       <c r="D410" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E410">
         <v>0.3145475050888473</v>
@@ -22289,7 +22289,7 @@
         <v>0.1380000200053004</v>
       </c>
       <c r="D411" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E411">
         <v>0.3145475050888473</v>
@@ -22339,7 +22339,7 @@
         <v>0.1180000200053</v>
       </c>
       <c r="D412" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E412">
         <v>0.03700560648571827</v>
@@ -22389,7 +22389,7 @@
         <v>0.1260111929661347</v>
       </c>
       <c r="D413" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E413">
         <v>0.03700560648571827</v>
@@ -22439,7 +22439,7 @@
         <v>0.4959765202796076</v>
       </c>
       <c r="D414" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E414">
         <v>0.1876054484520644</v>
@@ -22489,7 +22489,7 @@
         <v>0.4559765202796076</v>
       </c>
       <c r="D415" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E415">
         <v>0.1876054484520644</v>
@@ -22539,7 +22539,7 @@
         <v>0.5004479326354057</v>
       </c>
       <c r="D416" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E416">
         <v>0.1876054484520644</v>
@@ -22589,7 +22589,7 @@
         <v>0.4646766337890256</v>
       </c>
       <c r="D417" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E417">
         <v>0.1876054484520644</v>
@@ -22639,7 +22639,7 @@
         <v>0.4978481596542412</v>
       </c>
       <c r="D418" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E418">
         <v>0.1876054484520644</v>
@@ -22689,7 +22689,7 @@
         <v>-0.01215184034575945</v>
       </c>
       <c r="D419" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E419">
         <v>0.3252483866730769</v>
@@ -22739,7 +22739,7 @@
         <v>0.07053426311510336</v>
       </c>
       <c r="D420" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E420">
         <v>0.3252483866730769</v>
@@ -22789,7 +22789,7 @@
         <v>0.1292343766245203</v>
       </c>
       <c r="D421" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E421">
         <v>0.1050056754708999</v>
@@ -22839,7 +22839,7 @@
         <v>0.1371200260477101</v>
       </c>
       <c r="D422" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E422">
         <v>0.1050056754708999</v>
@@ -22889,7 +22889,7 @@
         <v>0.2644553699245202</v>
       </c>
       <c r="D423" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E423">
         <v>0.5136446756246755</v>
@@ -22939,7 +22939,7 @@
         <v>0.3066175087844885</v>
       </c>
       <c r="D424" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E424">
         <v>0.4518878839146296</v>
@@ -22989,7 +22989,7 @@
         <v>0.5375636061946913</v>
       </c>
       <c r="D425" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E425">
         <v>0.3814825367647066</v>
@@ -23039,7 +23039,7 @@
         <v>0.5533747315851132</v>
       </c>
       <c r="D426" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E426">
         <v>0.5155368704450822</v>
@@ -23089,7 +23089,7 @@
         <v>0.5455368704450816</v>
       </c>
       <c r="D427" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E427">
         <v>0.5155368704450822</v>
@@ -23139,7 +23139,7 @@
         <v>0.5472936621551279</v>
       </c>
       <c r="D428" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E428">
         <v>0.5155368704450822</v>
@@ -23189,7 +23189,7 @@
         <v>0.269705945999557</v>
       </c>
       <c r="D429" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E429">
         <v>0.5187456626377447</v>
@@ -23239,7 +23239,7 @@
         <v>0.3323781443528233</v>
       </c>
       <c r="D430" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E430">
         <v>0.4558019743357367</v>
@@ -23289,7 +23289,7 @@
         <v>0.5426496343015641</v>
       </c>
       <c r="D431" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E431">
         <v>0.3865536059653829</v>
@@ -23339,7 +23339,7 @@
         <v>0.5580568692246759</v>
       </c>
       <c r="D432" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E432">
         <v>0.4290171525864865</v>
@@ -23389,7 +23389,7 @@
         <v>0.5502489258970371</v>
       </c>
       <c r="D433" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E433">
         <v>0.4290171525864865</v>
@@ -23439,7 +23439,7 @@
         <v>0.5519608408884942</v>
       </c>
       <c r="D434" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E434">
         <v>0.4290171525864865</v>
@@ -23489,7 +23489,7 @@
         <v>0.2827549913852314</v>
       </c>
       <c r="D435" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E435">
         <v>0.5314229403486141</v>
@@ -23539,7 +23539,7 @@
         <v>0.3656874271108617</v>
       </c>
       <c r="D436" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E436">
         <v>0.5314229403486141</v>
@@ -23589,7 +23589,7 @@
         <v>0.5414229403486139</v>
       </c>
       <c r="D437" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E437">
         <v>0.3827549913852311</v>
@@ -23639,7 +23639,7 @@
         <v>0.3456874271108612</v>
       </c>
       <c r="D438" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E438">
         <v>0.4688881964888916</v>
@@ -23689,7 +23689,7 @@
         <v>0.5552897352449522</v>
       </c>
       <c r="D439" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E439">
         <v>0.3991565301412905</v>
@@ -23739,7 +23739,7 @@
         <v>0.5696931974460888</v>
       </c>
       <c r="D440" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E440">
         <v>0.4410252484827053</v>
@@ -23789,7 +23789,7 @@
         <v>0.5619596076534119</v>
       </c>
       <c r="D441" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E441">
         <v>0.4410252484827053</v>
@@ -23839,7 +23839,7 @@
         <v>0.5635599923424266</v>
       </c>
       <c r="D442" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E442">
         <v>0.4410252484827053</v>
@@ -23889,7 +23889,7 @@
         <v>0.2818837012820081</v>
       </c>
       <c r="D443" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E443">
         <v>0.5305764733252545</v>
@@ -23939,7 +23939,7 @@
         <v>0.364798760851734</v>
       </c>
       <c r="D444" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E444">
         <v>0.5305764733252545</v>
@@ -23989,7 +23989,7 @@
         <v>0.5405764733252543</v>
       </c>
       <c r="D445" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E445">
         <v>0.3818837012820078</v>
@@ -24039,7 +24039,7 @@
         <v>0.3447987608517336</v>
       </c>
       <c r="D446" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E446">
         <v>0.4680144240776825</v>
@@ -24089,7 +24089,7 @@
         <v>0.5544457505295792</v>
       </c>
       <c r="D447" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E447">
         <v>0.3983150277339043</v>
@@ -24139,7 +24139,7 @@
         <v>0.5689162350463484</v>
       </c>
       <c r="D448" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E448">
         <v>0.4402234630031003</v>
@@ -24189,7 +24189,7 @@
         <v>0.5611776806376989</v>
       </c>
       <c r="D449" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E449">
         <v>0.4402234630031003</v>
@@ -24239,7 +24239,7 @@
         <v>0.5627855122506729</v>
       </c>
       <c r="D450" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E450">
         <v>0.4402234630031003</v>
@@ -24289,7 +24289,7 @@
         <v>0.362536241667339</v>
       </c>
       <c r="D451" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E451">
         <v>0.5284213922026888</v>
@@ -24339,7 +24339,7 @@
         <v>0.5384213922026886</v>
       </c>
       <c r="D452" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E452">
         <v>0.3796654212995421</v>
@@ -24389,7 +24389,7 @@
         <v>0.3425362416673385</v>
       </c>
       <c r="D453" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E453">
         <v>0.4657898242092271</v>
@@ -24439,7 +24439,7 @@
         <v>0.5522969892930032</v>
       </c>
       <c r="D454" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E454">
         <v>0.3961725863833179</v>
@@ -24489,7 +24489,7 @@
         <v>0.5669381107315008</v>
       </c>
       <c r="D455" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E455">
         <v>0.4381821398283536</v>
@@ -24539,7 +24539,7 @@
         <v>0.5591869165508712</v>
       </c>
       <c r="D456" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E456">
         <v>0.4381821398283536</v>
@@ -24589,7 +24589,7 @@
         <v>0.5608137078218149</v>
       </c>
       <c r="D457" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E457">
         <v>0.4381821398283536</v>
@@ -24639,7 +24639,7 @@
         <v>0.3787781087183184</v>
       </c>
       <c r="D458" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E458">
         <v>0.5438919974104648</v>
@@ -24689,7 +24689,7 @@
         <v>0.5538919974104646</v>
       </c>
       <c r="D459" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E459">
         <v>0.3955897099444972</v>
@@ -24739,7 +24739,7 @@
         <v>0.3587781087183179</v>
       </c>
       <c r="D460" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E460">
         <v>0.4817594811978996</v>
@@ -24789,7 +24789,7 @@
         <v>0.5677222261570618</v>
       </c>
       <c r="D461" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E461">
         <v>0.4115524549036591</v>
@@ -24839,7 +24839,7 @@
         <v>0.5811384023151787</v>
       </c>
       <c r="D462" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E462">
         <v>0.4528361148492088</v>
@@ -24889,7 +24889,7 @@
         <v>0.5734779448219838</v>
       </c>
       <c r="D463" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E463">
         <v>0.4528361148492088</v>
@@ -24939,7 +24939,7 @@
         <v>0.5749686310617745</v>
       </c>
       <c r="D464" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E464">
         <v>0.4528361148492088</v>
@@ -24989,7 +24989,7 @@
         <v>0.5759260480051562</v>
       </c>
       <c r="D465" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E465">
         <v>0.4182699203806752</v>
@@ -25039,7 +25039,7 @@
         <v>0.381910631043537</v>
       </c>
       <c r="D466" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E466">
         <v>0.5045043076182258</v>
@@ -25089,7 +25089,7 @@
         <v>0.5896916607676044</v>
       </c>
       <c r="D467" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E467">
         <v>0.4334572735300526</v>
@@ -25139,7 +25139,7 @@
         <v>0.6013632053537075</v>
       </c>
       <c r="D468" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E468">
         <v>0.4737070777292249</v>
@@ -25189,7 +25189,7 @@
         <v>0.5938319798288108</v>
       </c>
       <c r="D469" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E469">
         <v>0.4737070777292249</v>
@@ -25239,7 +25239,7 @@
         <v>0.5951288181161551</v>
       </c>
       <c r="D470" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E470">
         <v>0.4737070777292249</v>
@@ -25289,7 +25289,7 @@
         <v>0.8275182606108249</v>
       </c>
       <c r="D471" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E471">
         <v>0.7045523383049392</v>
@@ -25339,7 +25339,7 @@
         <v>0.8516663182579531</v>
       </c>
       <c r="D472" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E472">
         <v>0.7320070951991022</v>
@@ -25389,7 +25389,7 @@
         <v>0.8457344736461829</v>
       </c>
       <c r="D473" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E473">
         <v>0.7320070951991022</v>
@@ -25439,7 +25439,7 @@
         <v>0.844632240563838</v>
       </c>
       <c r="D474" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E474">
         <v>0.7320070951991022</v>
@@ -25489,7 +25489,7 @@
         <v>0.6727685513402974</v>
       </c>
       <c r="D475" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E475">
         <v>0.7664959297873786</v>
@@ -25539,7 +25539,7 @@
         <v>1.961867488267962</v>
       </c>
       <c r="D476" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E476">
         <v>2.359173157777273</v>
@@ -25589,7 +25589,7 @@
         <v>2.029355876327454</v>
       </c>
       <c r="D477" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E477">
         <v>2.359173157777273</v>
@@ -25639,7 +25639,7 @@
         <v>2.417392420037491</v>
       </c>
       <c r="D478" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E478">
         <v>2.467575138587673</v>
@@ -25689,7 +25689,7 @@
         <v>1.940717323096565</v>
       </c>
       <c r="D479" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E479">
         <v>2.336812591587031</v>
@@ -25739,7 +25739,7 @@
         <v>2.007313836721119</v>
       </c>
       <c r="D480" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E480">
         <v>2.336812591587031</v>
@@ -25839,7 +25839,7 @@
         <v>1.900096592997466</v>
       </c>
       <c r="D482" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E482">
         <v>2.293867181150936</v>
@@ -25889,7 +25889,7 @@
         <v>1.964980184268443</v>
       </c>
       <c r="D483" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E483">
         <v>2.293867181150936</v>
@@ -26039,7 +26039,7 @@
         <v>1.861852628646782</v>
       </c>
       <c r="D486" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E486">
         <v>2.25343455618982</v>
@@ -26089,7 +26089,7 @@
         <v>1.925123522625862</v>
       </c>
       <c r="D487" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E487">
         <v>2.25343455618982</v>
@@ -26139,7 +26139,7 @@
         <v>2.430110142764237</v>
       </c>
       <c r="D488" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E488">
         <v>2.50019042193399</v>
@@ -26189,7 +26189,7 @@
         <v>2.430163662210739</v>
       </c>
       <c r="D489" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E489">
         <v>2.50019042193399</v>
@@ -26239,7 +26239,7 @@
         <v>1.831459736592777</v>
       </c>
       <c r="D490" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E490">
         <v>2.221302311879713</v>
@@ -26289,7 +26289,7 @@
         <v>1.903030398449984</v>
       </c>
       <c r="D491" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E491">
         <v>2.221302311879713</v>
@@ -26339,7 +26339,7 @@
         <v>1.893449002593677</v>
       </c>
       <c r="D492" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E492">
         <v>2.221302311879713</v>
@@ -26389,7 +26389,7 @@
         <v>2.398160988165298</v>
       </c>
       <c r="D493" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E493">
         <v>2.478318412878362</v>
@@ -26439,7 +26439,7 @@
         <v>2.399313045878813</v>
       </c>
       <c r="D494" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E494">
         <v>2.478318412878362</v>
@@ -26489,7 +26489,7 @@
         <v>2.402454369593227</v>
       </c>
       <c r="D495" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E495">
         <v>2.478318412878362</v>
@@ -26539,7 +26539,7 @@
         <v>2.395487738671498</v>
       </c>
       <c r="D496" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E496">
         <v>2.178404138073476</v>
@@ -26589,7 +26589,7 @@
         <v>2.392346507442251</v>
       </c>
       <c r="D497" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E497">
         <v>2.081770201129994</v>
@@ -26639,7 +26639,7 @@
         <v>2.396288876811025</v>
       </c>
       <c r="D498" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E498">
         <v>2.081770201129994</v>
@@ -26689,7 +26689,7 @@
         <v>2.352451083881302</v>
       </c>
       <c r="D499" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E499">
         <v>2.137017856475825</v>
@@ -26739,7 +26739,7 @@
         <v>2.350579370492474</v>
       </c>
       <c r="D500" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E500">
         <v>2.036194510658961</v>
@@ -26789,7 +26789,7 @@
         <v>2.354140884509123</v>
       </c>
       <c r="D501" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E501">
         <v>2.036194510658961</v>
@@ -26839,7 +26839,7 @@
         <v>2.299604104293275</v>
       </c>
       <c r="D502" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E502">
         <v>2.086197457225981</v>
@@ -26889,7 +26889,7 @@
         <v>2.299291298856895</v>
       </c>
       <c r="D503" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E503">
         <v>1.980229715166035</v>
@@ -26939,7 +26939,7 @@
         <v>2.30238514048781</v>
       </c>
       <c r="D504" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E504">
         <v>1.980229715166035</v>
@@ -26989,7 +26989,7 @@
         <v>1.834447701575086</v>
       </c>
       <c r="D505" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E505">
         <v>2.020009773964153</v>
@@ -27039,7 +27039,7 @@
         <v>2.24888552042234</v>
       </c>
       <c r="D506" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E506">
         <v>2.037423833798475</v>
@@ -27075,7 +27075,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27089,7 +27089,7 @@
         <v>2.250068838403982</v>
       </c>
       <c r="D507" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E507">
         <v>1.926518884459057</v>
@@ -27125,7 +27125,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27139,7 +27139,7 @@
         <v>2.252713843009491</v>
       </c>
       <c r="D508" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E508">
         <v>1.926518884459057</v>
@@ -27175,7 +27175,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27189,7 +27189,7 @@
         <v>1.784477179413162</v>
       </c>
       <c r="D509" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E509">
         <v>1.954198810770938</v>
@@ -27225,7 +27225,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27239,7 +27239,7 @@
         <v>2.18954595312629</v>
       </c>
       <c r="D510" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E510">
         <v>1.980359825130297</v>
@@ -27289,7 +27289,7 @@
         <v>2.19247970082168</v>
       </c>
       <c r="D511" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E511">
         <v>1.863678457735511</v>
@@ -27339,7 +27339,7 @@
         <v>2.194599576513064</v>
       </c>
       <c r="D512" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E512">
         <v>1.863678457735511</v>
@@ -27439,7 +27439,7 @@
         <v>2.12798379490697</v>
       </c>
       <c r="D514" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E514">
         <v>1.793301466175083</v>
@@ -27489,7 +27489,7 @@
         <v>2.129515562033781</v>
       </c>
       <c r="D515" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E515">
         <v>1.793301466175083</v>
@@ -27539,7 +27539,7 @@
         <v>1.660536740118322</v>
       </c>
       <c r="D516" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E516">
         <v>1.821856726399725</v>
@@ -27589,7 +27589,7 @@
         <v>1.723388493526535</v>
       </c>
       <c r="D517" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E517">
         <v>1.821856726399725</v>
@@ -27639,7 +27639,7 @@
         <v>2.053274487460548</v>
       </c>
       <c r="D518" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E518">
         <v>1.711779759873364</v>
@@ -27675,7 +27675,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27725,7 +27725,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27775,7 +27775,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27789,7 +27789,7 @@
         <v>1.978172341647824</v>
       </c>
       <c r="D521" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E521">
         <v>1.629829394077717</v>
@@ -27825,7 +27825,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27839,7 +27839,7 @@
         <v>1.508448517052806</v>
       </c>
       <c r="D522" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E522">
         <v>1.687122875108891</v>
@@ -27875,7 +27875,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27889,7 +27889,7 @@
         <v>1.577675225918856</v>
       </c>
       <c r="D523" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E523">
         <v>1.687122875108891</v>
@@ -27925,7 +27925,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27939,7 +27939,7 @@
         <v>1.898217593290899</v>
       </c>
       <c r="D524" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E524">
         <v>1.542583939183686</v>
@@ -27989,7 +27989,7 @@
         <v>1.427278650939697</v>
       </c>
       <c r="D525" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E525">
         <v>1.591409997284986</v>
@@ -28039,7 +28039,7 @@
         <v>1.499907689523063</v>
       </c>
       <c r="D526" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E526">
         <v>1.591409997284986</v>
@@ -28089,7 +28089,7 @@
         <v>1.773958940747064</v>
       </c>
       <c r="D527" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E527">
         <v>1.657280312655916</v>
@@ -28125,7 +28125,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28139,7 +28139,7 @@
         <v>1.803626803556179</v>
       </c>
       <c r="D528" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E528">
         <v>1.657280312655916</v>
@@ -28175,7 +28175,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28189,7 +28189,7 @@
         <v>1.61628390108326</v>
       </c>
       <c r="D529" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E529">
         <v>1.744291077937949</v>
@@ -28225,7 +28225,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28239,7 +28239,7 @@
         <v>1.593294666365293</v>
       </c>
       <c r="D530" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E530">
         <v>1.744291077937949</v>
@@ -28275,7 +28275,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28325,7 +28325,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28339,7 +28339,7 @@
         <v>1.804291077937949</v>
       </c>
       <c r="D532" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E532">
         <v>1.703958940747064</v>
@@ -28375,7 +28375,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28389,7 +28389,7 @@
         <v>1.761078645636388</v>
       </c>
       <c r="D533" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E533">
         <v>1.61323205942485</v>
@@ -28439,7 +28439,7 @@
         <v>1.572644764755269</v>
       </c>
       <c r="D534" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E534">
         <v>1.701470175416108</v>
@@ -28489,7 +28489,7 @@
         <v>1.550882880746527</v>
       </c>
       <c r="D535" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E535">
         <v>1.701470175416108</v>
@@ -28539,7 +28539,7 @@
         <v>1.721861705195829</v>
       </c>
       <c r="D536" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E536">
         <v>1.652644764755269</v>
@@ -28639,7 +28639,7 @@
         <v>1.761470175416108</v>
       </c>
       <c r="D538" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E538">
         <v>1.661274410526249</v>
@@ -28689,7 +28689,7 @@
         <v>1.581861705195828</v>
       </c>
       <c r="D539" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E539">
         <v>1.581078645636387</v>
@@ -28739,7 +28739,7 @@
         <v>1.751751519300945</v>
       </c>
       <c r="D540" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E540">
         <v>1.603576092096812</v>
@@ -28775,7 +28775,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28789,7 +28789,7 @@
         <v>1.563078481334303</v>
       </c>
       <c r="D541" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E541">
         <v>1.652580870571793</v>
@@ -28825,7 +28825,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28839,7 +28839,7 @@
         <v>1.541585649046775</v>
       </c>
       <c r="D542" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E542">
         <v>1.652580870571793</v>
@@ -28875,7 +28875,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28889,7 +28889,7 @@
         <v>1.712415000317624</v>
       </c>
       <c r="D543" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E543">
         <v>1.643078481334303</v>
@@ -28925,7 +28925,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28975,7 +28975,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28989,7 +28989,7 @@
         <v>1.752083259809285</v>
       </c>
       <c r="D545" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E545">
         <v>1.631585649046776</v>
@@ -29025,7 +29025,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29039,7 +29039,7 @@
         <v>1.572415000317624</v>
       </c>
       <c r="D546" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E546">
         <v>1.572415000317624</v>
@@ -29075,7 +29075,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29089,7 +29089,7 @@
         <v>1.550696711215447</v>
       </c>
       <c r="D547" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E547">
         <v>1.640315179547803</v>
@@ -29125,7 +29125,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29139,7 +29139,7 @@
         <v>1.529552116212513</v>
       </c>
       <c r="D548" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E548">
         <v>1.640315179547803</v>
@@ -29175,7 +29175,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29189,7 +29189,7 @@
         <v>1.700188002325254</v>
       </c>
       <c r="D549" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E549">
         <v>1.630696711215447</v>
@@ -29225,7 +29225,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29239,7 +29239,7 @@
         <v>1.739933647880158</v>
       </c>
       <c r="D550" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E550">
         <v>1.619552116212513</v>
@@ -29275,7 +29275,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29289,7 +29289,7 @@
         <v>1.560188002325254</v>
       </c>
       <c r="D551" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E551">
         <v>1.569552116212513</v>
@@ -29325,7 +29325,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29339,7 +29339,7 @@
         <v>1.454006350364605</v>
       </c>
       <c r="D552" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E552">
         <v>1.544531290829937</v>
@@ -29389,7 +29389,7 @@
         <v>1.4355811717606</v>
       </c>
       <c r="D553" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E553">
         <v>1.544531290829937</v>
@@ -29439,7 +29439,7 @@
         <v>1.604706270985048</v>
       </c>
       <c r="D554" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E554">
         <v>1.534006350364605</v>
@@ -29489,7 +29489,7 @@
         <v>1.645056231295269</v>
       </c>
       <c r="D555" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E555">
         <v>1.525581171760601</v>
@@ -29539,7 +29539,7 @@
         <v>1.464706270985047</v>
       </c>
       <c r="D556" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E556">
         <v>1.556106112225933</v>
@@ -29589,7 +29589,7 @@
         <v>1.381264364482504</v>
       </c>
       <c r="D557" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E557">
         <v>1.47247126106548</v>
@@ -29639,7 +29639,7 @@
         <v>1.364885054231434</v>
       </c>
       <c r="D558" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E558">
         <v>1.47247126106548</v>
@@ -29689,7 +29689,7 @@
         <v>1.532873559926473</v>
       </c>
       <c r="D559" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E559">
         <v>1.461264364482504</v>
@@ -29739,7 +29739,7 @@
         <v>1.573678157648457</v>
       </c>
       <c r="D560" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E560">
         <v>1.454885054231434</v>
@@ -29789,7 +29789,7 @@
         <v>1.392873559926473</v>
       </c>
       <c r="D561" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E561">
         <v>1.486091950814411</v>
@@ -29839,7 +29839,7 @@
         <v>1.323846162601001</v>
       </c>
       <c r="D562" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E562">
         <v>1.430640622329638</v>
@@ -29889,7 +29889,7 @@
         <v>1.491174879041532</v>
       </c>
       <c r="D563" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E563">
         <v>1.419037852193957</v>
@@ -29989,7 +29989,7 @@
         <v>1.53224339246532</v>
       </c>
       <c r="D565" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E565">
         <v>1.413846162601002</v>
@@ -30039,7 +30039,7 @@
         <v>1.351174879041532</v>
       </c>
       <c r="D566" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E566">
         <v>1.445448932736684</v>
@@ -30089,7 +30089,7 @@
         <v>1.290817037379022</v>
       </c>
       <c r="D567" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E567">
         <v>1.43889565831837</v>
@@ -30139,7 +30139,7 @@
         <v>1.457614738944602</v>
       </c>
       <c r="D568" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E568">
         <v>1.385052900197065</v>
@@ -30239,7 +30239,7 @@
         <v>1.49889565831837</v>
       </c>
       <c r="D570" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E570">
         <v>1.380817037379023</v>
@@ -30289,7 +30289,7 @@
         <v>1.317614738944601</v>
       </c>
       <c r="D571" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E571">
         <v>1.412738416439675</v>
@@ -30339,7 +30339,7 @@
         <v>1.465300255187212</v>
       </c>
       <c r="D572" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E572">
         <v>1.414659795500328</v>
@@ -30389,7 +30389,7 @@
         <v>1.263583293912756</v>
       </c>
       <c r="D573" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E573">
         <v>1.411399209931207</v>
@@ -30439,7 +30439,7 @@
         <v>1.429943153943507</v>
       </c>
       <c r="D574" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E574">
         <v>1.357031041968109</v>
@@ -30539,7 +30539,7 @@
         <v>1.471399209931207</v>
       </c>
       <c r="D576" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E576">
         <v>1.353583293912756</v>
@@ -30589,7 +30589,7 @@
         <v>1.438679489869704</v>
       </c>
       <c r="D577" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E577">
         <v>1.390135545857402</v>
@@ -30639,7 +30639,7 @@
         <v>1.397526326513801</v>
       </c>
       <c r="D578" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E578">
         <v>1.324203874950685</v>
@@ -30739,7 +30739,7 @@
         <v>1.407493681203151</v>
       </c>
       <c r="D580" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E580">
         <v>1.335799810110941</v>
@@ -30789,7 +30789,7 @@
         <v>1.358411271518721</v>
       </c>
       <c r="D581" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E581">
         <v>1.284593692677185</v>
@@ -30839,7 +30839,7 @@
         <v>1.361730508546035</v>
       </c>
       <c r="D582" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E582">
         <v>1.30077611383565</v>
@@ -30939,7 +30939,7 @@
         <v>1.369864008043327</v>
       </c>
       <c r="D584" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E584">
         <v>1.299407955147164</v>
@@ -30989,7 +30989,7 @@
         <v>1.334364057726781</v>
       </c>
       <c r="D585" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E585">
         <v>1.260242083773956</v>
@@ -31039,7 +31039,7 @@
         <v>1.337150603309337</v>
       </c>
       <c r="D586" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E586">
         <v>1.27612010982113</v>
@@ -31139,7 +31139,7 @@
         <v>1.194364057726781</v>
       </c>
       <c r="D588" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E588">
         <v>1.292608005632433</v>
@@ -31189,7 +31189,7 @@
         <v>1.346729979585258</v>
       </c>
       <c r="D589" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E589">
         <v>1.277034914467322</v>
@@ -31239,7 +31239,7 @@
         <v>1.323737513794956</v>
       </c>
       <c r="D590" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E590">
         <v>1.249481026627804</v>
@@ -31275,7 +31275,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31325,7 +31325,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31339,7 +31339,7 @@
         <v>1.183737513794956</v>
       </c>
       <c r="D592" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E592">
         <v>1.282250488129261</v>
@@ -31375,7 +31375,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31389,7 +31389,7 @@
         <v>1.336506975296414</v>
       </c>
       <c r="D593" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E593">
         <v>1.244597045756811</v>
@@ -31425,7 +31425,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31439,7 +31439,7 @@
         <v>1.107789411132176</v>
       </c>
       <c r="D594" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E594">
         <v>1.128853532923964</v>
@@ -31475,7 +31475,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31489,7 +31489,7 @@
         <v>1.314314361428908</v>
       </c>
       <c r="D595" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E595">
         <v>1.239938593852058</v>
@@ -31589,7 +31589,7 @@
         <v>1.356502245217332</v>
       </c>
       <c r="D597" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E597">
         <v>1.23978407089997</v>
@@ -31639,7 +31639,7 @@
         <v>1.174314361428907</v>
       </c>
       <c r="D598" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E598">
         <v>1.273065896582606</v>
@@ -31689,7 +31689,7 @@
         <v>1.327441664159455</v>
       </c>
       <c r="D599" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E599">
         <v>1.236038676361065</v>
@@ -31739,7 +31739,7 @@
         <v>1.099320502043702</v>
       </c>
       <c r="D600" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E600">
         <v>1.151508385832127</v>
@@ -31789,7 +31789,7 @@
         <v>1.304586839884553</v>
       </c>
       <c r="D601" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E601">
         <v>1.230087939123598</v>
@@ -31889,7 +31889,7 @@
         <v>1.34683629026503</v>
       </c>
       <c r="D603" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E603">
         <v>1.230210465835747</v>
@@ -31939,7 +31939,7 @@
         <v>1.164586839884553</v>
       </c>
       <c r="D604" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E604">
         <v>1.263584641406464</v>
@@ -31989,7 +31989,7 @@
         <v>1.318083542167419</v>
       </c>
       <c r="D605" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E605">
         <v>1.227203870401477</v>
@@ -32039,7 +32039,7 @@
         <v>1.090578045972193</v>
       </c>
       <c r="D606" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E606">
         <v>1.168451122303864</v>
@@ -32089,7 +32089,7 @@
         <v>1.288015597086421</v>
       </c>
       <c r="D607" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E607">
         <v>1.213306933758401</v>
@@ -32125,7 +32125,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32175,7 +32175,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32189,7 +32189,7 @@
         <v>1.330369928750431</v>
       </c>
       <c r="D609" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E609">
         <v>1.213901426246447</v>
@@ -32225,7 +32225,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32239,7 +32239,7 @@
         <v>1.148015597086421</v>
       </c>
       <c r="D610" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E610">
         <v>1.247432923742462</v>
@@ -32275,7 +32275,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32289,7 +32289,7 @@
         <v>1.302141587070481</v>
       </c>
       <c r="D611" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E611">
         <v>1.212153406214566</v>
@@ -32325,7 +32325,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32375,7 +32375,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32439,7 +32439,7 @@
         <v>1.316010539200704</v>
       </c>
       <c r="D614" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E614">
         <v>1.199679228316622</v>
@@ -32489,7 +32489,7 @@
         <v>1.13356474645676</v>
       </c>
       <c r="D615" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E615">
         <v>1.233347917432539</v>
@@ -32539,7 +32539,7 @@
         <v>1.288239502920428</v>
       </c>
       <c r="D616" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E616">
         <v>1.199028741243956</v>
@@ -32589,7 +32589,7 @@
         <v>1.062697430359874</v>
       </c>
       <c r="D617" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E617">
         <v>1.173703497707623</v>
@@ -32689,7 +32689,7 @@
         <v>1.289689339635371</v>
       </c>
       <c r="D619" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E619">
         <v>1.173609505180258</v>
@@ -32739,7 +32739,7 @@
         <v>1.107075895938781</v>
       </c>
       <c r="D620" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E620">
         <v>1.207529670725142</v>
@@ -32789,7 +32789,7 @@
         <v>1.262756558118322</v>
       </c>
       <c r="D621" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E621">
         <v>1.174970829539336</v>
@@ -32939,7 +32939,7 @@
         <v>1.276835319137715</v>
       </c>
       <c r="D624" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E624">
         <v>1.160878293795636</v>
@@ -32989,7 +32989,7 @@
         <v>1.094140002699101</v>
       </c>
       <c r="D625" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E625">
         <v>1.194921268453555</v>
@@ -33089,7 +33089,7 @@
         <v>1.101308040374834</v>
       </c>
       <c r="D627" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E627">
         <v>1.125351015032754</v>
@@ -33139,7 +33139,7 @@
         <v>1.261511807017353</v>
       </c>
       <c r="D628" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E628">
         <v>1.145701184657316</v>
@@ -33189,7 +33189,7 @@
         <v>1.078718888590712</v>
       </c>
       <c r="D629" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E629">
         <v>1.179890562297277</v>
@@ -33239,7 +33239,7 @@
         <v>1.087594961056931</v>
       </c>
       <c r="D630" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E630">
         <v>1.158991420270251</v>
@@ -33289,7 +33289,7 @@
         <v>1.226836158897406</v>
       </c>
       <c r="D631" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E631">
         <v>1.111356832538514</v>
@@ -33339,7 +33339,7 @@
         <v>1.043822376470001</v>
       </c>
       <c r="D632" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E632">
         <v>1.145877506179622</v>
@@ -33389,7 +33389,7 @@
         <v>1.056563568949589</v>
       </c>
       <c r="D633" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E633">
         <v>1.128070460163292</v>
@@ -33439,7 +33439,7 @@
         <v>1.201158127400802</v>
       </c>
       <c r="D634" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E634">
         <v>1.085924132553024</v>
@@ -33489,7 +33489,7 @@
         <v>1.017980790632654</v>
       </c>
       <c r="D635" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E635">
         <v>1.120690137705246</v>
@@ -33539,7 +33539,7 @@
         <v>1.168551502583454</v>
       </c>
       <c r="D636" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E636">
         <v>1.053629035998263</v>
@@ -33575,7 +33575,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33589,7 +33589,7 @@
         <v>0.9851664803069156</v>
       </c>
       <c r="D637" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E637">
         <v>1.088706569413071</v>
@@ -33625,7 +33625,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33639,7 +33639,7 @@
         <v>1.162722274727682</v>
       </c>
       <c r="D638" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E638">
         <v>1.047855501402259</v>
@@ -33689,7 +33689,7 @@
         <v>0.979300123611297</v>
       </c>
       <c r="D639" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E639">
         <v>1.082988728076835</v>
@@ -33739,7 +33739,7 @@
         <v>0.9086593724975383</v>
       </c>
       <c r="D640" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E640">
         <v>1.014136350408994</v>
@@ -33889,7 +33889,7 @@
         <v>0.7992043433997962</v>
       </c>
       <c r="D643" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E643">
         <v>1.019738497970907</v>
@@ -33925,7 +33925,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33939,7 +33939,7 @@
         <v>1.313286431175834</v>
       </c>
       <c r="D644" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E644">
         <v>1.130272652542017</v>
@@ -33975,7 +33975,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33989,7 +33989,7 @@
         <v>0.7800006615139132</v>
       </c>
       <c r="D645" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E645">
         <v>0.9989795883266597</v>
@@ -34025,7 +34025,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34075,7 +34075,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34089,7 +34089,7 @@
         <v>0.7633805417349455</v>
       </c>
       <c r="D647" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E647">
         <v>0.9810134729317896</v>
@@ -34125,7 +34125,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34139,7 +34139,7 @@
         <v>1.274182985696595</v>
       </c>
       <c r="D648" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E648">
         <v>0.9863695750502357</v>
@@ -34175,7 +34175,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34189,7 +34189,7 @@
         <v>1.137753720442226</v>
       </c>
       <c r="D649" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E649">
         <v>0.9863695750502357</v>
@@ -34225,7 +34225,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34239,7 +34239,7 @@
         <v>0.7497456373466673</v>
       </c>
       <c r="D650" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E650">
         <v>0.9662743333289678</v>
@@ -34275,7 +34275,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34289,7 +34289,7 @@
         <v>1.259299815413615</v>
       </c>
       <c r="D651" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E651">
         <v>0.9151278686163851</v>
@@ -34325,7 +34325,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34339,7 +34339,7 @@
         <v>1.122102386531737</v>
       </c>
       <c r="D652" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E652">
         <v>0.9151278686163851</v>
@@ -34375,7 +34375,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34389,7 +34389,7 @@
         <v>0.7499733438090663</v>
       </c>
       <c r="D653" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E653">
         <v>0.9665204808076879</v>
@@ -34439,7 +34439,7 @@
         <v>1.259548368242291</v>
       </c>
       <c r="D654" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E654">
         <v>0.9153916553281078</v>
@@ -34489,7 +34489,7 @@
         <v>1.122363767893505</v>
       </c>
       <c r="D655" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E655">
         <v>0.9153916553281078</v>
@@ -34539,7 +34539,7 @@
         <v>0.7430600171819424</v>
       </c>
       <c r="D656" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E656">
         <v>0.9590472720945642</v>
@@ -34589,7 +34589,7 @@
         <v>1.252002131430993</v>
       </c>
       <c r="D657" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E657">
         <v>0.9073829072283761</v>
@@ -34639,7 +34639,7 @@
         <v>1.114428047891947</v>
       </c>
       <c r="D658" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E658">
         <v>0.9073829072283761</v>
@@ -34689,7 +34689,7 @@
         <v>0.7298791026179612</v>
       </c>
       <c r="D659" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E659">
         <v>0.9447988890975849</v>
@@ -34739,7 +34739,7 @@
         <v>1.237614513421014</v>
       </c>
       <c r="D660" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E660">
         <v>0.8921134674693985</v>
@@ -34789,7 +34789,7 @@
         <v>1.099297843145969</v>
       </c>
       <c r="D661" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E661">
         <v>0.8921134674693985</v>
@@ -34839,7 +34839,7 @@
         <v>0.7205518880005681</v>
       </c>
       <c r="D662" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E662">
         <v>0.9347163014654027</v>
@@ -34889,7 +34889,7 @@
         <v>1.227433398873859</v>
       </c>
       <c r="D663" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E663">
         <v>0.8813083491274183</v>
@@ -34939,7 +34939,7 @@
         <v>1.088591251718961</v>
       </c>
       <c r="D664" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E664">
         <v>0.8813083491274183</v>
@@ -34989,7 +34989,7 @@
         <v>0.7334671047121053</v>
       </c>
       <c r="D665" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E665">
         <v>0.9486774688261139</v>
@@ -35025,7 +35025,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35039,7 +35039,7 @@
         <v>1.241530994580115</v>
       </c>
       <c r="D666" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E666">
         <v>0.8962699910221215</v>
@@ -35075,7 +35075,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35089,7 +35089,7 @@
         <v>1.10341646526812</v>
       </c>
       <c r="D667" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E667">
         <v>0.8962699910221215</v>
@@ -35125,7 +35125,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35139,7 +35139,7 @@
         <v>0.8045700379682295</v>
       </c>
       <c r="D668" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E668">
         <v>1.004863742954274</v>
@@ -35175,7 +35175,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35189,7 +35189,7 @@
         <v>1.234863742954274</v>
       </c>
       <c r="D669" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E669">
         <v>0.9443867707027893</v>
@@ -35225,7 +35225,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35239,7 +35239,7 @@
         <v>1.096405097429334</v>
       </c>
       <c r="D670" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E670">
         <v>0.9443867707027893</v>
@@ -35275,7 +35275,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35289,7 +35289,7 @@
         <v>0.7207520002925669</v>
       </c>
       <c r="D671" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E671">
         <v>0.903356547088833</v>
@@ -35325,7 +35325,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35339,7 +35339,7 @@
         <v>0.7297853816033166</v>
       </c>
       <c r="D672" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E672">
         <v>0.903356547088833</v>
@@ -35375,7 +35375,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35389,7 +35389,7 @@
         <v>0.7096588204869674</v>
       </c>
       <c r="D673" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E673">
         <v>0.943356547088833</v>
@@ -35425,7 +35425,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35439,7 +35439,7 @@
         <v>0.8405874255868655</v>
       </c>
       <c r="D674" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E674">
         <v>0.9485506684719898</v>
@@ -35489,7 +35489,7 @@
         <v>0.7932418398819072</v>
       </c>
       <c r="D675" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E675">
         <v>0.9485506684719898</v>
@@ -35539,7 +35539,7 @@
         <v>0.803058054307523</v>
       </c>
       <c r="D676" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E676">
         <v>0.9897859828323181</v>
@@ -35589,7 +35589,7 @@
         <v>0.8230580543075225</v>
       </c>
       <c r="D677" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E677">
         <v>0.9897859828323181</v>
@@ -35639,7 +35639,7 @@
         <v>0.8318227399471945</v>
       </c>
       <c r="D678" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E678">
         <v>0.9571315685372763</v>
@@ -35889,7 +35889,7 @@
         <v>0.777997561282735</v>
       </c>
       <c r="D683" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E683">
         <v>0.9334019652872323</v>
@@ -35939,7 +35939,7 @@
         <v>0.7885305913164626</v>
       </c>
       <c r="D684" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E684">
         <v>0.9750195813052205</v>
@@ -35989,7 +35989,7 @@
         <v>0.8085305913164622</v>
       </c>
       <c r="D685" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E685">
         <v>0.9750195813052205</v>
@@ -36039,7 +36039,7 @@
         <v>0.8169129752984747</v>
       </c>
       <c r="D686" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E686">
         <v>0.9423173793029713</v>
@@ -36189,7 +36189,7 @@
         <v>1.044210773296226</v>
       </c>
       <c r="D689" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E689">
         <v>1.03610416728948</v>
@@ -36239,7 +36239,7 @@
         <v>0.7528694316436244</v>
       </c>
       <c r="D690" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E690">
         <v>0.9084313787806551</v>
@@ -36289,7 +36289,7 @@
         <v>0.764584035171354</v>
       </c>
       <c r="D691" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E691">
         <v>0.950679167328778</v>
@@ -36339,7 +36339,7 @@
         <v>0.8145840351713538</v>
       </c>
       <c r="D692" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E692">
         <v>0.950679167328778</v>
@@ -36389,7 +36389,7 @@
         <v>0.7923362466232318</v>
       </c>
       <c r="D693" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E693">
         <v>0.9178981937602617</v>
@@ -36589,7 +36589,7 @@
         <v>0.7253017663654795</v>
       </c>
       <c r="D697" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E697">
         <v>0.9239756921847437</v>
@@ -36639,7 +36639,7 @@
         <v>0.7383126550943753</v>
       </c>
       <c r="D698" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E698">
         <v>0.9239756921847437</v>
@@ -36689,7 +36689,7 @@
         <v>0.7653735144389637</v>
       </c>
       <c r="D699" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E699">
         <v>0.8911082996028163</v>
@@ -36889,7 +36889,7 @@
         <v>0.71847767572971</v>
       </c>
       <c r="D703" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E703">
         <v>0.9038144796068437</v>
@@ -36939,7 +36939,7 @@
         <v>0.7450165619331228</v>
       </c>
       <c r="D704" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E704">
         <v>1.017804067975443</v>
@@ -37039,7 +37039,7 @@
         <v>1.023814479606843</v>
       </c>
       <c r="D706" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E706">
         <v>1.07328600503483</v>
@@ -37089,7 +37089,7 @@
         <v>0.98328600503483</v>
       </c>
       <c r="D707" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E707">
         <v>1.07328600503483</v>
@@ -37139,7 +37139,7 @@
         <v>0.6881995922217432</v>
       </c>
       <c r="D708" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E708">
         <v>0.8730384013043384</v>
@@ -37189,7 +37189,7 @@
         <v>0.7139416867538939</v>
       </c>
       <c r="D709" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E709">
         <v>0.9885219740565545</v>
@@ -37239,7 +37239,7 @@
         <v>0.9930384013043376</v>
       </c>
       <c r="D710" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E710">
         <v>0.9930384013043376</v>
@@ -37289,7 +37289,7 @@
         <v>0.9518127340199696</v>
       </c>
       <c r="D711" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E711">
         <v>0.9930384013043376</v>
@@ -37339,7 +37339,7 @@
         <v>0.6656441408663709</v>
       </c>
       <c r="D712" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E712">
         <v>0.8501119721306205</v>
@@ -37375,7 +37375,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37389,7 +37389,7 @@
         <v>0.6907926708891701</v>
       </c>
       <c r="D713" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E713">
         <v>0.9667084783378717</v>
@@ -37425,7 +37425,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37439,7 +37439,7 @@
         <v>0.742537707119221</v>
       </c>
       <c r="D714" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E714">
         <v>0.9667084783378717</v>
@@ -37475,7 +37475,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37489,7 +37489,7 @@
         <v>0.9701119721306197</v>
       </c>
       <c r="D715" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E715">
         <v>0.9732184058777698</v>
@@ -37525,7 +37525,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37539,7 +37539,7 @@
         <v>0.9776862371420201</v>
       </c>
       <c r="D716" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E716">
         <v>0.9732184058777698</v>
@@ -37575,7 +37575,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37589,7 +37589,7 @@
         <v>0.6508193548090921</v>
       </c>
       <c r="D717" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E717">
         <v>0.8350433573552944</v>
@@ -37639,7 +37639,7 @@
         <v>0.6755777588830156</v>
       </c>
       <c r="D718" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E718">
         <v>0.9523713497166879</v>
@@ -37689,7 +37689,7 @@
         <v>0.7276641553183332</v>
       </c>
       <c r="D719" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E719">
         <v>0.9523713497166879</v>
@@ -37739,7 +37739,7 @@
         <v>0.9550433573552937</v>
       </c>
       <c r="D720" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E720">
         <v>0.9345089558275728</v>
@@ -37789,7 +37789,7 @@
         <v>0.9624225593922562</v>
       </c>
       <c r="D721" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E721">
         <v>0.9345089558275728</v>
@@ -37839,7 +37839,7 @@
         <v>0.6242673164036452</v>
       </c>
       <c r="D722" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E722">
         <v>0.8080546077918633</v>
@@ -37889,7 +37889,7 @@
         <v>0.6483269826247939</v>
       </c>
       <c r="D723" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E723">
         <v>0.9266927336272097</v>
@@ -37939,7 +37939,7 @@
         <v>0.7010247746812892</v>
       </c>
       <c r="D724" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E724">
         <v>0.9266927336272097</v>
@@ -38089,7 +38089,7 @@
         <v>0.6355734784869522</v>
       </c>
       <c r="D727" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E727">
         <v>0.9146750085742434</v>
@@ -38139,7 +38139,7 @@
         <v>0.6885574068542324</v>
       </c>
       <c r="D728" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E728">
         <v>0.9146750085742434</v>
@@ -38189,7 +38189,7 @@
         <v>0.9154237335015001</v>
       </c>
       <c r="D729" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E729">
         <v>0.8587071518396838</v>
@@ -38239,7 +38239,7 @@
         <v>0.9222900601487689</v>
       </c>
       <c r="D730" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E730">
         <v>0.8587071518396838</v>
@@ -38289,7 +38289,7 @@
         <v>0.6415632406536673</v>
       </c>
       <c r="D731" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E731">
         <v>0.8890838888081336</v>
@@ -38339,7 +38339,7 @@
         <v>0.6084155554698558</v>
       </c>
       <c r="D732" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E732">
         <v>0.8890838888081336</v>
@@ -38389,7 +38389,7 @@
         <v>0.6718974073228061</v>
       </c>
       <c r="D733" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E733">
         <v>0.8890838888081336</v>
@@ -38439,7 +38439,7 @@
         <v>0.8885269443595689</v>
       </c>
       <c r="D734" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E734">
         <v>0.8153792591757565</v>
@@ -38489,7 +38489,7 @@
         <v>0.895045092506618</v>
       </c>
       <c r="D735" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E735">
         <v>0.8153792591757565</v>
@@ -38539,7 +38539,7 @@
         <v>0.6125179249261947</v>
       </c>
       <c r="D736" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E736">
         <v>0.862145961918932</v>
@@ -38589,7 +38589,7 @@
         <v>0.5798283677507028</v>
       </c>
       <c r="D737" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E737">
         <v>0.862145961918932</v>
@@ -38639,7 +38639,7 @@
         <v>0.6436767220103095</v>
       </c>
       <c r="D738" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E738">
         <v>0.862145961918932</v>
@@ -38689,7 +38689,7 @@
         <v>0.8602146334454073</v>
       </c>
       <c r="D739" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E739">
         <v>0.7909871648348172</v>
@@ -38739,7 +38739,7 @@
         <v>0.8663662791858018</v>
       </c>
       <c r="D740" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E740">
         <v>0.7909871648348172</v>
@@ -38789,7 +38789,7 @@
         <v>0.8640629877050143</v>
       </c>
       <c r="D741" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E741">
         <v>0.7909871648348172</v>
@@ -38839,7 +38839,7 @@
         <v>0.5868517408115368</v>
       </c>
       <c r="D742" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E742">
         <v>0.8383419930554954</v>
@@ -38889,7 +38889,7 @@
         <v>0.6187392308200419</v>
       </c>
       <c r="D743" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E743">
         <v>0.8383419930554954</v>
@@ -38939,7 +38939,7 @@
         <v>0.8351961763746525</v>
       </c>
       <c r="D744" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E744">
         <v>0.749997557492379</v>
@@ -38989,7 +38989,7 @@
         <v>0.8410239585930954</v>
       </c>
       <c r="D745" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E745">
         <v>0.749997557492379</v>
@@ -39039,7 +39039,7 @@
         <v>0.8393683941562111</v>
       </c>
       <c r="D746" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E746">
         <v>0.749997557492379</v>
@@ -39089,7 +39089,7 @@
         <v>0.5558537772765639</v>
       </c>
       <c r="D747" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E747">
         <v>0.8095930931208519</v>
@@ -39139,7 +39139,7 @@
         <v>0.5886213356504157</v>
       </c>
       <c r="D748" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E748">
         <v>0.8095930931208519</v>
@@ -39189,7 +39189,7 @@
         <v>0.8049804958310984</v>
       </c>
       <c r="D749" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E749">
         <v>0.7741072143856336</v>
@@ -39239,7 +39239,7 @@
         <v>0.8104171365538315</v>
       </c>
       <c r="D750" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E750">
         <v>0.7741072143856336</v>
@@ -39289,7 +39289,7 @@
         <v>0.809543855108366</v>
       </c>
       <c r="D751" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E751">
         <v>0.7741072143856336</v>
@@ -39339,7 +39339,7 @@
         <v>0.4884465484383016</v>
       </c>
       <c r="D752" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E752">
         <v>0.7470766095926207</v>
@@ -39389,7 +39389,7 @@
         <v>0.5569813576358316</v>
       </c>
       <c r="D753" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E753">
         <v>0.7470766095926207</v>
@@ -39589,7 +39589,7 @@
         <v>0.4354740041875989</v>
       </c>
       <c r="D757" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E757">
         <v>0.6979474991519057</v>
@@ -39625,7 +39625,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39639,7 +39639,7 @@
         <v>0.5056798715633839</v>
       </c>
       <c r="D758" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E758">
         <v>0.6979474991519057</v>
@@ -39675,7 +39675,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39689,7 +39689,7 @@
         <v>0.5198033919888561</v>
       </c>
       <c r="D759" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E759">
         <v>0.6979474991519057</v>
@@ -39725,7 +39725,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39775,7 +39775,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39789,7 +39789,7 @@
         <v>0.687638698088227</v>
       </c>
       <c r="D761" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E761">
         <v>0.6759886726270619</v>
@@ -39825,7 +39825,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39839,7 +39839,7 @@
         <v>0.6915563511379128</v>
       </c>
       <c r="D762" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E762">
         <v>0.6759886726270619</v>
@@ -39875,7 +39875,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39889,7 +39889,7 @@
         <v>0.6937210450385409</v>
       </c>
       <c r="D763" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E763">
         <v>0.6759886726270619</v>
@@ -39925,7 +39925,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39939,7 +39939,7 @@
         <v>0.7159886726270619</v>
       </c>
       <c r="D764" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E764">
         <v>0.6759886726270619</v>
@@ -39975,7 +39975,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -39989,7 +39989,7 @@
         <v>0.4606014325671115</v>
       </c>
       <c r="D765" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E765">
         <v>0.6547779191359311</v>
@@ -40039,7 +40039,7 @@
         <v>0.4756059648296436</v>
       </c>
       <c r="D766" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E766">
         <v>0.6547779191359311</v>
@@ -40139,7 +40139,7 @@
         <v>0.6422665884796004</v>
       </c>
       <c r="D768" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E768">
         <v>0.5897824513984631</v>
@@ -40189,7 +40189,7 @@
         <v>0.6455969003045796</v>
       </c>
       <c r="D769" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E769">
         <v>0.5897824513984631</v>
@@ -40239,7 +40239,7 @@
         <v>0.6489362766546218</v>
       </c>
       <c r="D770" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E770">
         <v>0.5897824513984631</v>
@@ -40289,7 +40289,7 @@
         <v>0.6731127632234415</v>
       </c>
       <c r="D771" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E771">
         <v>0.5897824513984631</v>
@@ -40339,7 +40339,7 @@
         <v>0.4311736090828546</v>
       </c>
       <c r="D772" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E772">
         <v>0.6265962249848842</v>
@@ -40389,7 +40389,7 @@
         <v>0.4467532779607151</v>
       </c>
       <c r="D773" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E773">
         <v>0.6265962249848842</v>
@@ -40489,7 +40489,7 @@
         <v>0.6126470527902352</v>
       </c>
       <c r="D775" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E775">
         <v>0.5324899998144046</v>
@@ -40539,7 +40539,7 @@
         <v>0.6155939402049952</v>
       </c>
       <c r="D776" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E776">
         <v>0.5324899998144046</v>
@@ -40589,7 +40589,7 @@
         <v>0.619700165375475</v>
       </c>
       <c r="D777" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E777">
         <v>0.5324899998144046</v>
@@ -40639,7 +40639,7 @@
         <v>0.6451227812775038</v>
       </c>
       <c r="D778" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E778">
         <v>0.4344945693741815</v>
@@ -40689,7 +40689,7 @@
         <v>0.4145254252315729</v>
       </c>
       <c r="D779" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E779">
         <v>0.6106530130882168</v>
@@ -40739,7 +40739,7 @@
         <v>0.4304304657807938</v>
       </c>
       <c r="D780" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E780">
         <v>0.6106530130882168</v>
@@ -40839,7 +40839,7 @@
         <v>0.5958904117151667</v>
       </c>
       <c r="D782" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E782">
         <v>0.5161129590225899</v>
@@ -40889,7 +40889,7 @@
         <v>0.598620384682353</v>
       </c>
       <c r="D783" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E783">
         <v>0.5161129590225899</v>
@@ -40939,7 +40939,7 @@
         <v>0.6031604387479801</v>
       </c>
       <c r="D784" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E784">
         <v>0.5161129590225899</v>
@@ -40989,7 +40989,7 @@
         <v>0.6292880266046232</v>
       </c>
       <c r="D785" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E785">
         <v>0.420178215834317</v>
@@ -41039,7 +41039,7 @@
         <v>0.4227821175677198</v>
       </c>
       <c r="D786" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E786">
         <v>0.6031825334382379</v>
@@ -41075,7 +41075,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41125,7 +41125,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41139,7 +41139,7 @@
         <v>0.5880387851442697</v>
       </c>
       <c r="D788" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E788">
         <v>0.508439201014788</v>
@@ -41175,7 +41175,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41189,7 +41189,7 @@
         <v>0.5906671189325454</v>
       </c>
       <c r="D789" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E789">
         <v>0.508439201014788</v>
@@ -41225,7 +41225,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41239,7 +41239,7 @@
         <v>0.5954104513559946</v>
       </c>
       <c r="D790" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E790">
         <v>0.508439201014788</v>
@@ -41275,7 +41275,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41289,7 +41289,7 @@
         <v>0.6218683665441</v>
       </c>
       <c r="D791" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E791">
         <v>0.4134700300261724</v>
@@ -41325,7 +41325,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41339,7 +41339,7 @@
         <v>0.4183317969287206</v>
       </c>
       <c r="D792" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E792">
         <v>0.5988357086280525</v>
@@ -41439,7 +41439,7 @@
         <v>0.5834701835580542</v>
       </c>
       <c r="D794" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E794">
         <v>0.5039740952573863</v>
@@ -41489,7 +41489,7 @@
         <v>0.5860393768727219</v>
       </c>
       <c r="D795" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E795">
         <v>0.5039740952573863</v>
@@ -41539,7 +41539,7 @@
         <v>0.5909009902433873</v>
       </c>
       <c r="D796" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E796">
         <v>0.5039740952573863</v>
@@ -41589,7 +41589,7 @@
         <v>0.6175511119707178</v>
       </c>
       <c r="D797" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E797">
         <v>0.4095667587680469</v>
@@ -41639,7 +41639,7 @@
         <v>0.4068527587148587</v>
       </c>
       <c r="D798" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E798">
         <v>0.5876236247912567</v>
@@ -41739,7 +41739,7 @@
         <v>0.5716860546275448</v>
       </c>
       <c r="D800" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E800">
         <v>0.492456920703944</v>
@@ -41789,7 +41789,7 @@
         <v>0.5741027025838896</v>
       </c>
       <c r="D801" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E801">
         <v>0.492456920703944</v>
@@ -41839,7 +41839,7 @@
         <v>0.5792694066712016</v>
       </c>
       <c r="D802" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E802">
         <v>0.492456920703944</v>
@@ -41889,7 +41889,7 @@
         <v>0.6064153008130848</v>
       </c>
       <c r="D803" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E803">
         <v>0.3994987651186794</v>
@@ -41939,7 +41939,7 @@
         <v>0.3579570329658832</v>
       </c>
       <c r="D804" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E804">
         <v>0.3699362230204524</v>
@@ -41989,7 +41989,7 @@
         <v>0.3977542302305785</v>
       </c>
       <c r="D805" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E805">
         <v>0.5787366899926578</v>
@@ -42089,7 +42089,7 @@
         <v>0.5623457047882017</v>
       </c>
       <c r="D807" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E807">
         <v>0.4833281645502812</v>
@@ -42139,7 +42139,7 @@
         <v>0.5646414420670132</v>
       </c>
       <c r="D808" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E808">
         <v>0.4833281645502812</v>
@@ -42189,7 +42189,7 @@
         <v>0.57004996750939</v>
       </c>
       <c r="D809" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E809">
         <v>0.4833281645502812</v>
@@ -42239,7 +42239,7 @@
         <v>0.5975888213532521</v>
       </c>
       <c r="D810" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E810">
         <v>0.3915186604015704</v>
@@ -42289,7 +42289,7 @@
         <v>0.3495537408774121</v>
       </c>
       <c r="D811" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E811">
         <v>0.4216840692788968</v>
@@ -42389,7 +42389,7 @@
         <v>0.5721210895999382</v>
       </c>
       <c r="D813" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E813">
         <v>0.4928821005151498</v>
@@ -42439,7 +42439,7 @@
         <v>0.5745433690769604</v>
       </c>
       <c r="D814" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E814">
         <v>0.4928821005151498</v>
@@ -42489,7 +42489,7 @@
         <v>0.5796988101229168</v>
       </c>
       <c r="D815" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E815">
         <v>0.4928821005151498</v>
@@ -42539,7 +42539,7 @@
         <v>0.6068264018225955</v>
       </c>
       <c r="D816" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E816">
         <v>0.3998704454834425</v>
@@ -42639,7 +42639,7 @@
         <v>0.6148946886098487</v>
       </c>
       <c r="D818" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E818">
         <v>0.5346867183177162</v>
@@ -42689,7 +42689,7 @@
         <v>0.6178706716339253</v>
       </c>
       <c r="D819" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E819">
         <v>0.5346867183177162</v>
@@ -42739,7 +42739,7 @@
         <v>0.6219187055857738</v>
       </c>
       <c r="D820" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E820">
         <v>0.5346867183177162</v>
@@ -42789,7 +42789,7 @@
         <v>0.6472467607575272</v>
       </c>
       <c r="D821" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E821">
         <v>0.4364148795889973</v>
@@ -42875,7 +42875,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42889,7 +42889,7 @@
         <v>0.6279001693216664</v>
       </c>
       <c r="D823" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E823">
         <v>0.5473975764891374</v>
@@ -42925,7 +42925,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -42939,7 +42939,7 @@
         <v>0.6310445080831126</v>
       </c>
       <c r="D824" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E824">
         <v>0.5473975764891374</v>
@@ -42975,7 +42975,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -42989,7 +42989,7 @@
         <v>0.6347558305602217</v>
       </c>
       <c r="D825" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E825">
         <v>0.5473975764891374</v>
@@ -43025,7 +43025,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43039,7 +43039,7 @@
         <v>0.6595367295855228</v>
       </c>
       <c r="D826" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E826">
         <v>0.4475263582554048</v>
@@ -43075,7 +43075,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43089,7 +43089,7 @@
         <v>1.962686724385328</v>
       </c>
       <c r="D827" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E827">
         <v>2.151981906363921</v>
@@ -43189,7 +43189,7 @@
         <v>1.958001051354043</v>
       </c>
       <c r="D829" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E829">
         <v>2.26470804772295</v>
@@ -43239,7 +43239,7 @@
         <v>2.365152550575952</v>
       </c>
       <c r="D830" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E830">
         <v>2.343253550057224</v>
@@ -43289,7 +43289,7 @@
         <v>2.013095064260612</v>
       </c>
       <c r="D831" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E831">
         <v>2.265466103249754</v>
@@ -43389,7 +43389,7 @@
         <v>2.011324180903594</v>
       </c>
       <c r="D833" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E833">
         <v>2.263769006699277</v>
@@ -43489,7 +43489,7 @@
         <v>2.024694880188124</v>
       </c>
       <c r="D835" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E835">
         <v>2.260773155550828</v>
@@ -43539,7 +43539,7 @@
         <v>2.027479225115583</v>
       </c>
       <c r="D836" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E836">
         <v>2.260773155550828</v>
@@ -43589,7 +43589,7 @@
         <v>2.544904144922141</v>
       </c>
       <c r="D837" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E837">
         <v>2.400982420284845</v>
@@ -43639,7 +43639,7 @@
         <v>2.403976029946321</v>
       </c>
       <c r="D838" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E838">
         <v>2.400982420284845</v>
@@ -43689,7 +43689,7 @@
         <v>2.412838650236485</v>
       </c>
       <c r="D839" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E839">
         <v>2.400982420284845</v>
@@ -43739,7 +43739,7 @@
         <v>2.021712430063359</v>
       </c>
       <c r="D840" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E840">
         <v>2.258015513224412</v>
@@ -43989,7 +43989,7 @@
         <v>2.019211875698086</v>
       </c>
       <c r="D845" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E845">
         <v>2.255703442856522</v>
@@ -44239,7 +44239,7 @@
         <v>2.018121327597043</v>
       </c>
       <c r="D850" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E850">
         <v>2.254695096873648</v>
@@ -44289,7 +44289,7 @@
         <v>2.537967230127533</v>
       </c>
       <c r="D851" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E851">
         <v>2.358275425066553</v>
@@ -44339,7 +44339,7 @@
         <v>2.397072148079306</v>
       </c>
       <c r="D852" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E852">
         <v>2.358275425066553</v>
@@ -44389,7 +44389,7 @@
         <v>2.442596737838175</v>
       </c>
       <c r="D853" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E853">
         <v>2.358275425066553</v>
@@ -44439,7 +44439,7 @@
         <v>2.40633116350059</v>
       </c>
       <c r="D854" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E854">
         <v>2.358275425066553</v>
@@ -44489,7 +44489,7 @@
         <v>2.021368606041688</v>
       </c>
       <c r="D855" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E855">
         <v>2.257697605586285</v>
@@ -44525,7 +44525,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44539,7 +44539,7 @@
         <v>2.541394006375651</v>
       </c>
       <c r="D856" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E856">
         <v>2.352254605738086</v>
@@ -44575,7 +44575,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44589,7 +44589,7 @@
         <v>2.40048260634529</v>
       </c>
       <c r="D857" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E857">
         <v>2.352254605738086</v>
@@ -44625,7 +44625,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44639,7 +44639,7 @@
         <v>2.445925606193489</v>
       </c>
       <c r="D858" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E858">
         <v>2.352254605738086</v>
@@ -44675,7 +44675,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44689,7 +44689,7 @@
         <v>2.409545805980967</v>
       </c>
       <c r="D859" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E859">
         <v>2.352254605738086</v>
@@ -44725,7 +44725,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44739,7 +44739,7 @@
         <v>2.025854940315086</v>
       </c>
       <c r="D860" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E860">
         <v>2.261845773959677</v>
@@ -44789,7 +44789,7 @@
         <v>2.546128328975719</v>
       </c>
       <c r="D861" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E861">
         <v>2.405581551654453</v>
@@ -44839,7 +44839,7 @@
         <v>2.467996217823106</v>
       </c>
       <c r="D862" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E862">
         <v>2.405581551654453</v>
@@ -44889,7 +44889,7 @@
         <v>2.450524662433555</v>
       </c>
       <c r="D863" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E863">
         <v>2.405581551654453</v>
@@ -44939,7 +44939,7 @@
         <v>2.413987051467698</v>
       </c>
       <c r="D864" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E864">
         <v>2.405581551654453</v>
@@ -44989,7 +44989,7 @@
         <v>2.419317329349228</v>
       </c>
       <c r="D865" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E865">
         <v>2.405581551654453</v>
@@ -45039,7 +45039,7 @@
         <v>2.077206228244958</v>
       </c>
       <c r="D866" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E866">
         <v>2.263969424227638</v>
@@ -45089,7 +45089,7 @@
         <v>2.028151714246195</v>
       </c>
       <c r="D867" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E867">
         <v>2.263969424227638</v>
@@ -45139,7 +45139,7 @@
         <v>2.548552060259804</v>
       </c>
       <c r="D868" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E868">
         <v>2.429642340235061</v>
@@ -45189,7 +45189,7 @@
         <v>2.470443032262278</v>
       </c>
       <c r="D869" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E869">
         <v>2.429642340235061</v>
@@ -45239,7 +45239,7 @@
         <v>2.452879144252381</v>
       </c>
       <c r="D870" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E870">
         <v>2.429642340235061</v>
@@ -45289,7 +45289,7 @@
         <v>2.421533312237536</v>
       </c>
       <c r="D871" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E871">
         <v>2.429642340235061</v>
@@ -45339,7 +45339,7 @@
         <v>2.078439011686218</v>
       </c>
       <c r="D872" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E872">
         <v>2.26511504116295</v>
@@ -45389,7 +45389,7 @@
         <v>2.029390723866451</v>
       </c>
       <c r="D873" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E873">
         <v>2.26511504116295</v>
@@ -45639,7 +45639,7 @@
         <v>2.551608670550823</v>
       </c>
       <c r="D878" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E878">
         <v>2.394327927360752</v>
@@ -45689,7 +45689,7 @@
         <v>2.473528753127496</v>
       </c>
       <c r="D879" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E879">
         <v>2.394327927360752</v>
@@ -45739,7 +45739,7 @@
         <v>2.455848422820799</v>
       </c>
       <c r="D880" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E880">
         <v>2.394327927360752</v>
@@ -45789,7 +45789,7 @@
         <v>2.493367886072415</v>
       </c>
       <c r="D881" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E881">
         <v>2.394327927360752</v>
@@ -45839,7 +45839,7 @@
         <v>2.451447803495741</v>
       </c>
       <c r="D882" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E882">
         <v>2.394327927360752</v>
@@ -45889,7 +45889,7 @@
         <v>2.550180575011903</v>
       </c>
       <c r="D883" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E883">
         <v>2.413975480844273</v>
@@ -45939,7 +45939,7 @@
         <v>2.472087056678682</v>
       </c>
       <c r="D884" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E884">
         <v>2.413975480844273</v>
@@ -45989,7 +45989,7 @@
         <v>2.454461130011562</v>
       </c>
       <c r="D885" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E885">
         <v>2.413975480844273</v>
@@ -46039,7 +46039,7 @@
         <v>2.492068999177492</v>
       </c>
       <c r="D886" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E886">
         <v>2.413975480844273</v>
@@ -46089,7 +46089,7 @@
         <v>2.450162517510712</v>
       </c>
       <c r="D887" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E887">
         <v>2.413975480844273</v>
@@ -46139,7 +46139,7 @@
         <v>2.549221397041758</v>
       </c>
       <c r="D888" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E888">
         <v>2.384991297253062</v>
@@ -46189,7 +46189,7 @@
         <v>2.471118743680251</v>
       </c>
       <c r="D889" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E889">
         <v>2.384991297253062</v>
@@ -46239,7 +46239,7 @@
         <v>2.453529357126279</v>
       </c>
       <c r="D890" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E890">
         <v>2.384991297253062</v>
@@ -46289,7 +46289,7 @@
         <v>2.491196603976075</v>
       </c>
       <c r="D891" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E891">
         <v>2.384991297253062</v>
@@ -46339,7 +46339,7 @@
         <v>2.546894368399535</v>
       </c>
       <c r="D892" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E892">
         <v>2.370017708251004</v>
@@ -46389,7 +46389,7 @@
         <v>2.468769552860483</v>
       </c>
       <c r="D893" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E893">
         <v>2.370017708251004</v>
@@ -46439,7 +46439,7 @@
         <v>2.485643261633848</v>
       </c>
       <c r="D894" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E894">
         <v>2.370017708251004</v>
@@ -46489,7 +46489,7 @@
         <v>2.48908011602053</v>
       </c>
       <c r="D895" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E895">
         <v>2.370017708251004</v>
@@ -46539,7 +46539,7 @@
         <v>2.546210539230263</v>
       </c>
       <c r="D896" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E896">
         <v>2.35126116481272</v>
@@ -46589,7 +46589,7 @@
         <v>2.468079211032456</v>
       </c>
       <c r="D897" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E897">
         <v>2.35126116481272</v>
@@ -46639,7 +46639,7 @@
         <v>2.484998508417106</v>
       </c>
       <c r="D898" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E898">
         <v>2.35126116481272</v>
@@ -46689,7 +46689,7 @@
         <v>2.48845815710943</v>
       </c>
       <c r="D899" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E899">
         <v>2.35126116481272</v>
@@ -46989,7 +46989,7 @@
         <v>2.486934855642235</v>
       </c>
       <c r="D905" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E905">
         <v>2.316934855642235</v>
@@ -47239,7 +47239,7 @@
         <v>2.490094687204029</v>
       </c>
       <c r="D910" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E910">
         <v>2.351980495447003</v>
@@ -47539,7 +47539,7 @@
         <v>2.493632488343625</v>
       </c>
       <c r="D916" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E916">
         <v>2.323632488343625</v>
@@ -47789,7 +47789,7 @@
         <v>2.496950334223138</v>
       </c>
       <c r="D921" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E921">
         <v>2.326950334223138</v>
@@ -48039,7 +48039,7 @@
         <v>2.499807210510219</v>
       </c>
       <c r="D926" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E926">
         <v>2.329807210510219</v>
@@ -48139,7 +48139,7 @@
         <v>2.564547678565647</v>
       </c>
       <c r="D928" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E928">
         <v>2.357179533157952</v>
@@ -48189,7 +48189,7 @@
         <v>2.486590989790082</v>
       </c>
       <c r="D929" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E929">
         <v>2.357179533157952</v>
@@ -48239,7 +48239,7 @@
         <v>2.468417744892343</v>
       </c>
       <c r="D930" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E930">
         <v>2.357179533157952</v>
@@ -48289,7 +48289,7 @@
         <v>2.505136221933517</v>
       </c>
       <c r="D931" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E931">
         <v>2.335136221933517</v>
@@ -48375,7 +48375,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48389,7 +48389,7 @@
         <v>2.571973511934736</v>
       </c>
       <c r="D933" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E933">
         <v>2.364004227635257</v>
@@ -48425,7 +48425,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48439,7 +48439,7 @@
         <v>2.494087545381733</v>
       </c>
       <c r="D934" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E934">
         <v>2.364004227635257</v>
@@ -48475,7 +48475,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48489,7 +48489,7 @@
         <v>2.475631411593743</v>
       </c>
       <c r="D935" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E935">
         <v>2.364004227635257</v>
@@ -48525,7 +48525,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48539,7 +48539,7 @@
         <v>2.511890194188259</v>
       </c>
       <c r="D936" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E936">
         <v>2.341890194188259</v>
@@ -48575,7 +48575,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -48589,7 +48589,7 @@
         <v>2.469776160741262</v>
       </c>
       <c r="D937" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E937">
         <v>2.341890194188259</v>
@@ -48625,7 +48625,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -48639,7 +48639,7 @@
         <v>2.585546222284397</v>
       </c>
       <c r="D938" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E938">
         <v>2.376478194766136</v>
@@ -48689,7 +48689,7 @@
         <v>2.507789519639486</v>
       </c>
       <c r="D939" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E939">
         <v>2.376478194766136</v>
@@ -48739,7 +48739,7 @@
         <v>2.488816330219128</v>
       </c>
       <c r="D940" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E940">
         <v>2.376478194766136</v>
@@ -48789,7 +48789,7 @@
         <v>2.524234897411047</v>
       </c>
       <c r="D941" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E941">
         <v>2.387599843443681</v>
@@ -48839,7 +48839,7 @@
         <v>2.592366497323944</v>
       </c>
       <c r="D942" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E942">
         <v>2.382746352302482</v>
@@ -48889,7 +48889,7 @@
         <v>2.51467474967941</v>
       </c>
       <c r="D943" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E943">
         <v>2.382746352302482</v>
@@ -48939,7 +48939,7 @@
         <v>2.495441740257546</v>
       </c>
       <c r="D944" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E944">
         <v>2.382746352302482</v>
@@ -48989,7 +48989,7 @@
         <v>2.530438099947015</v>
       </c>
       <c r="D945" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E945">
         <v>2.39812984759155</v>
@@ -49039,7 +49039,7 @@
         <v>2.523049937079764</v>
       </c>
       <c r="D946" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E946">
         <v>2.390370933284879</v>
@@ -49089,7 +49089,7 @@
         <v>2.503500882850339</v>
       </c>
       <c r="D947" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E947">
         <v>2.390370933284879</v>
@@ -49139,7 +49139,7 @@
         <v>2.537983669727523</v>
       </c>
       <c r="D948" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E948">
         <v>2.41440277439149</v>
@@ -49189,7 +49189,7 @@
         <v>2.526835385892296</v>
       </c>
       <c r="D949" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E949">
         <v>2.393817120175534</v>
@@ -49239,7 +49239,7 @@
         <v>2.50714348453787</v>
       </c>
       <c r="D950" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E950">
         <v>2.393817120175534</v>
@@ -49289,7 +49289,7 @@
         <v>2.541394144836927</v>
       </c>
       <c r="D951" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E951">
         <v>2.417759681829017</v>
@@ -49339,7 +49339,7 @@
         <v>2.345028607844837</v>
       </c>
       <c r="D952" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E952">
         <v>2.42987455852205</v>
@@ -49389,7 +49389,7 @@
         <v>2.534209390950705</v>
       </c>
       <c r="D953" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E953">
         <v>2.434239225254452</v>
@@ -49489,7 +49489,7 @@
         <v>2.548037705998041</v>
       </c>
       <c r="D955" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E955">
         <v>2.424298893861947</v>
@@ -49539,7 +49539,7 @@
         <v>2.505545164573978</v>
       </c>
       <c r="D956" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E956">
         <v>2.429283976710074</v>
@@ -49589,7 +49589,7 @@
         <v>2.351776518134136</v>
       </c>
       <c r="D957" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E957">
         <v>2.469254142406326</v>
@@ -49639,7 +49639,7 @@
         <v>2.537683733866443</v>
       </c>
       <c r="D958" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E958">
         <v>2.437582460890351</v>
@@ -49739,7 +49739,7 @@
         <v>2.551167892304201</v>
       </c>
       <c r="D960" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E960">
         <v>2.427379914938167</v>
@@ -49789,7 +49789,7 @@
         <v>2.508642574060178</v>
       </c>
       <c r="D961" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E961">
         <v>2.432430551426213</v>
@@ -49839,7 +49839,7 @@
         <v>2.354955869670236</v>
       </c>
       <c r="D962" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E962">
         <v>2.472531824402305</v>
@@ -49889,7 +49889,7 @@
         <v>2.374955869670236</v>
       </c>
       <c r="D963" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E963">
         <v>2.302531824402305</v>
@@ -49939,7 +49939,7 @@
         <v>2.547057903948727</v>
       </c>
       <c r="D964" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E964">
         <v>2.446602888705379</v>
@@ -50039,7 +50039,7 @@
         <v>2.559613488934938</v>
       </c>
       <c r="D966" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E966">
         <v>2.435692858218683</v>
@@ -50089,7 +50089,7 @@
         <v>2.516999735124102</v>
       </c>
       <c r="D967" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E967">
         <v>2.440920365840357</v>
@@ -50139,7 +50139,7 @@
         <v>2.363534119651194</v>
       </c>
       <c r="D968" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E968">
         <v>2.481375381083705</v>
@@ -50189,7 +50189,7 @@
         <v>2.383534119651195</v>
       </c>
       <c r="D969" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E969">
         <v>2.414840996556613</v>
@@ -50239,7 +50239,7 @@
         <v>2.564343447930323</v>
       </c>
       <c r="D970" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E970">
         <v>2.427963610615813</v>
@@ -50289,7 +50289,7 @@
         <v>2.543236148008424</v>
       </c>
       <c r="D971" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E971">
         <v>2.427963610615813</v>
@@ -50389,7 +50389,7 @@
         <v>2.575186785635339</v>
       </c>
       <c r="D973" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E973">
         <v>2.451021548164626</v>
@@ -50439,7 +50439,7 @@
         <v>2.532409960654864</v>
       </c>
       <c r="D974" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E974">
         <v>2.456575198125576</v>
@@ -50489,7 +50489,7 @@
         <v>2.37935202310605</v>
       </c>
       <c r="D975" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E975">
         <v>2.464905673067</v>
@@ -50539,7 +50539,7 @@
         <v>2.399352023106051</v>
       </c>
       <c r="D976" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E976">
         <v>2.447963610615814</v>
@@ -50589,7 +50589,7 @@
         <v>2.947313892359365</v>
       </c>
       <c r="D977" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E977">
         <v>2.80175874695094</v>
@@ -50639,7 +50639,7 @@
         <v>2.55309257246083</v>
       </c>
       <c r="D978" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E978">
         <v>2.899758008686105</v>
@@ -50689,7 +50689,7 @@
         <v>3.072869037767791</v>
       </c>
       <c r="D979" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E979">
         <v>2.755756532156437</v>
@@ -50739,7 +50739,7 @@
         <v>2.994646241339586</v>
       </c>
       <c r="D980" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E980">
         <v>2.755756532156437</v>
@@ -50789,7 +50789,7 @@
         <v>2.669091095931161</v>
       </c>
       <c r="D981" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E981">
         <v>2.697313892359365</v>
@@ -50839,7 +50839,7 @@
         <v>2.666646979604421</v>
       </c>
       <c r="D982" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E982">
         <v>2.697313892359365</v>
@@ -50889,7 +50889,7 @@
         <v>1.297829535910621</v>
       </c>
       <c r="D983" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E983">
         <v>0.8616678599075076</v>
@@ -50939,7 +50939,7 @@
         <v>0.6201465518963349</v>
       </c>
       <c r="D984" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E984">
         <v>1.150592131893589</v>
@@ -50989,7 +50989,7 @@
         <v>1.478357895886811</v>
       </c>
       <c r="D985" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E985">
         <v>1.02817966388791</v>
@@ -51039,7 +51039,7 @@
         <v>1.527734083890658</v>
       </c>
       <c r="D986" t="s">
-        <v>193</v>
+        <v>346</v>
       </c>
       <c r="E986">
         <v>0.8140739918926707</v>
@@ -51089,7 +51089,7 @@
         <v>0.7719288718853452</v>
       </c>
       <c r="D987" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E987">
         <v>1.277377619892856</v>
@@ -51139,7 +51139,7 @@
         <v>0.5600712707795941</v>
       </c>
       <c r="D988" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E988">
         <v>1.088924749687181</v>
@@ -51189,7 +51189,7 @@
         <v>1.41276333099256</v>
       </c>
       <c r="D989" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E989">
         <v>0.9632219394295252</v>
@@ -51239,7 +51239,7 @@
         <v>1.464368460521941</v>
       </c>
       <c r="D990" t="s">
-        <v>193</v>
+        <v>346</v>
       </c>
       <c r="E990">
         <v>0.7518759093230418</v>
@@ -51289,7 +51289,7 @@
         <v>0.7054851864099394</v>
       </c>
       <c r="D991" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E991">
         <v>1.215285677395871</v>
@@ -51383,13 +51383,13 @@
         <v>1</v>
       </c>
       <c r="B993" t="s">
+        <v>192</v>
+      </c>
+      <c r="C993">
+        <v>0.730902359952653</v>
+      </c>
+      <c r="D993" t="s">
         <v>193</v>
-      </c>
-      <c r="C993">
-        <v>0.7756689823198943</v>
-      </c>
-      <c r="D993" t="s">
-        <v>194</v>
       </c>
       <c r="E993">
         <v>1.239038147879077</v>
@@ -51398,22 +51398,22 @@
         <v>1</v>
       </c>
       <c r="G993">
-        <v>0.01644433101768011</v>
+        <v>0.01746909764004734</v>
       </c>
       <c r="H993">
         <v>0.01688096185212093</v>
       </c>
       <c r="I993">
-        <v>0.4633691655591825</v>
+        <v>0.5081357879264239</v>
       </c>
       <c r="J993">
         <v>1.336916555918107</v>
       </c>
       <c r="K993">
-        <v>5.86</v>
+        <v>6.26</v>
       </c>
       <c r="L993">
-        <v>8.609999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M993">
         <v>5.85</v>
@@ -51430,96 +51430,96 @@
     </row>
     <row r="994" spans="1:16">
       <c r="A994" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B994" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C994">
-        <v>0.730902359952653</v>
+        <v>1.462100210182946</v>
       </c>
       <c r="D994" t="s">
-        <v>194</v>
+        <v>346</v>
       </c>
       <c r="E994">
-        <v>1.239038147879077</v>
+        <v>0.7496494525413828</v>
       </c>
       <c r="F994">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G994">
-        <v>0.01746909764004734</v>
+        <v>0.01747789978981706</v>
       </c>
       <c r="H994">
-        <v>0.01688096185212093</v>
+        <v>0.01647035054745861</v>
       </c>
       <c r="I994">
-        <v>0.5081357879264239</v>
+        <v>0.7124507576415633</v>
       </c>
       <c r="J994">
-        <v>1.336916555918107</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K994">
-        <v>6.26</v>
+        <v>5.97</v>
       </c>
       <c r="L994">
-        <v>9.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M994">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N994">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O994">
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>190</v>
+        <v>460</v>
       </c>
     </row>
     <row r="995" spans="1:16">
       <c r="A995" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B995" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C995">
-        <v>1.462100210182946</v>
+        <v>0.7031067530561543</v>
       </c>
       <c r="D995" t="s">
         <v>193</v>
       </c>
       <c r="E995">
-        <v>0.7496494525413828</v>
+        <v>1.213063020028516</v>
       </c>
       <c r="F995">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G995">
-        <v>0.01747789978981706</v>
+        <v>0.01749689324694385</v>
       </c>
       <c r="H995">
-        <v>0.01647035054745861</v>
+        <v>0.01690693697997148</v>
       </c>
       <c r="I995">
-        <v>0.7124507576415633</v>
+        <v>0.5099562669723614</v>
       </c>
       <c r="J995">
         <v>1.341356748713074</v>
       </c>
       <c r="K995">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="L995">
-        <v>9.470000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M995">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N995">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O995">
         <v>1</v>
@@ -51530,96 +51530,96 @@
     </row>
     <row r="996" spans="1:16">
       <c r="A996" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B996" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C996">
-        <v>0.7031067530561543</v>
+        <v>1.449405185698751</v>
       </c>
       <c r="D996" t="s">
-        <v>194</v>
+        <v>346</v>
       </c>
       <c r="E996">
-        <v>1.213063020028516</v>
+        <v>0.7371883397310999</v>
       </c>
       <c r="F996">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G996">
-        <v>0.01749689324694385</v>
+        <v>0.01749059481430125</v>
       </c>
       <c r="H996">
-        <v>0.01690693697997148</v>
+        <v>0.0164828116602689</v>
       </c>
       <c r="I996">
-        <v>0.5099562669723614</v>
+        <v>0.7122168459676512</v>
       </c>
       <c r="J996">
-        <v>1.341356748713074</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K996">
-        <v>6.26</v>
+        <v>5.97</v>
       </c>
       <c r="L996">
-        <v>9.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M996">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N996">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O996">
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="997" spans="1:16">
       <c r="A997" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B997" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C997">
-        <v>1.449405185698751</v>
+        <v>0.6897950523407328</v>
       </c>
       <c r="D997" t="s">
         <v>193</v>
       </c>
       <c r="E997">
-        <v>0.7371883397310999</v>
+        <v>1.200623171915861</v>
       </c>
       <c r="F997">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G997">
-        <v>0.01749059481430125</v>
+        <v>0.01751020494765927</v>
       </c>
       <c r="H997">
-        <v>0.0164828116602689</v>
+        <v>0.01691937682808414</v>
       </c>
       <c r="I997">
-        <v>0.7122168459676512</v>
+        <v>0.5108281195751285</v>
       </c>
       <c r="J997">
         <v>1.343483218475921</v>
       </c>
       <c r="K997">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="L997">
-        <v>9.470000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M997">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N997">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O997">
         <v>1</v>
@@ -51630,196 +51630,196 @@
     </row>
     <row r="998" spans="1:16">
       <c r="A998" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B998" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C998">
-        <v>0.6897950523407328</v>
+        <v>1.446464800345405</v>
       </c>
       <c r="D998" t="s">
-        <v>194</v>
+        <v>346</v>
       </c>
       <c r="E998">
-        <v>1.200623171915861</v>
+        <v>0.7343021323323375</v>
       </c>
       <c r="F998">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G998">
-        <v>0.01751020494765927</v>
+        <v>0.0174935351996546</v>
       </c>
       <c r="H998">
-        <v>0.01691937682808414</v>
+        <v>0.01648569786766766</v>
       </c>
       <c r="I998">
-        <v>0.5108281195751285</v>
+        <v>0.7121626680130673</v>
       </c>
       <c r="J998">
-        <v>1.343483218475921</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K998">
-        <v>6.26</v>
+        <v>5.97</v>
       </c>
       <c r="L998">
-        <v>9.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M998">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N998">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O998">
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>461</v>
+        <v>345</v>
       </c>
     </row>
     <row r="999" spans="1:16">
       <c r="A999" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B999" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C999">
-        <v>1.446464800345405</v>
+        <v>0.6867118341980269</v>
       </c>
       <c r="D999" t="s">
         <v>193</v>
       </c>
       <c r="E999">
-        <v>0.7343021323323375</v>
+        <v>1.197741889785697</v>
       </c>
       <c r="F999">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G999">
-        <v>0.0174935351996546</v>
+        <v>0.01751328816580197</v>
       </c>
       <c r="H999">
-        <v>0.01648569786766766</v>
+        <v>0.01692225811021431</v>
       </c>
       <c r="I999">
-        <v>0.7121626680130673</v>
+        <v>0.5110300555876703</v>
       </c>
       <c r="J999">
         <v>1.343975745335778</v>
       </c>
       <c r="K999">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="L999">
-        <v>9.470000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M999">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N999">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O999">
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
       <c r="A1000" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1000" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C1000">
-        <v>0.6867118341980269</v>
+        <v>1.460084502779063</v>
       </c>
       <c r="D1000" t="s">
-        <v>194</v>
+        <v>346</v>
       </c>
       <c r="E1000">
-        <v>1.197741889785697</v>
+        <v>0.7476708854749239</v>
       </c>
       <c r="F1000">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1000">
-        <v>0.01751328816580197</v>
+        <v>0.01747991549722094</v>
       </c>
       <c r="H1000">
-        <v>0.01692225811021431</v>
+        <v>0.01647232911452507</v>
       </c>
       <c r="I1000">
-        <v>0.5110300555876703</v>
+        <v>0.7124136173041391</v>
       </c>
       <c r="J1000">
-        <v>1.343975745335778</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1000">
-        <v>6.26</v>
+        <v>5.97</v>
       </c>
       <c r="L1000">
-        <v>9.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1000">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N1000">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1000">
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
       <c r="A1001" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1001" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C1001">
-        <v>1.460084502779063</v>
+        <v>0.7009931302172401</v>
       </c>
       <c r="D1001" t="s">
         <v>193</v>
       </c>
       <c r="E1001">
-        <v>0.7476708854749239</v>
+        <v>1.211087829356368</v>
       </c>
       <c r="F1001">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1001">
-        <v>0.01747991549722094</v>
+        <v>0.01749900686978276</v>
       </c>
       <c r="H1001">
-        <v>0.01647232911452507</v>
+        <v>0.01690891217064363</v>
       </c>
       <c r="I1001">
-        <v>0.7124136173041391</v>
+        <v>0.5100946991391284</v>
       </c>
       <c r="J1001">
         <v>1.341694388144211</v>
       </c>
       <c r="K1001">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="L1001">
-        <v>9.470000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M1001">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N1001">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O1001">
         <v>1</v>
@@ -51830,96 +51830,96 @@
     </row>
     <row r="1002" spans="1:16">
       <c r="A1002" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1002" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C1002">
-        <v>0.7009931302172401</v>
+        <v>1.453089006184717</v>
       </c>
       <c r="D1002" t="s">
-        <v>194</v>
+        <v>346</v>
       </c>
       <c r="E1002">
-        <v>1.211087829356368</v>
+        <v>0.7408042841277105</v>
       </c>
       <c r="F1002">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1002">
-        <v>0.01749900686978276</v>
+        <v>0.01748691099381528</v>
       </c>
       <c r="H1002">
-        <v>0.01690891217064363</v>
+        <v>0.01647919571587229</v>
       </c>
       <c r="I1002">
-        <v>0.5100946991391284</v>
+        <v>0.7122847220570065</v>
       </c>
       <c r="J1002">
-        <v>1.341694388144211</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K1002">
-        <v>6.26</v>
+        <v>5.97</v>
       </c>
       <c r="L1002">
-        <v>9.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1002">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N1002">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1002">
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
       <c r="A1003" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1003" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C1003">
-        <v>1.453089006184717</v>
+        <v>0.6936578188804567</v>
       </c>
       <c r="D1003" t="s">
         <v>193</v>
       </c>
       <c r="E1003">
-        <v>0.7408042841277105</v>
+        <v>1.204232945758894</v>
       </c>
       <c r="F1003">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1003">
-        <v>0.01748691099381528</v>
+        <v>0.01750634218111954</v>
       </c>
       <c r="H1003">
-        <v>0.01647919571587229</v>
+        <v>0.01691576705424111</v>
       </c>
       <c r="I1003">
-        <v>0.7122847220570065</v>
+        <v>0.5105751268784369</v>
       </c>
       <c r="J1003">
         <v>1.342866163118138</v>
       </c>
       <c r="K1003">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="L1003">
-        <v>9.470000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M1003">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N1003">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O1003">
         <v>1</v>
@@ -51930,34 +51930,34 @@
     </row>
     <row r="1004" spans="1:16">
       <c r="A1004" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1004" t="s">
         <v>192</v>
       </c>
       <c r="C1004">
-        <v>0.6936578188804567</v>
+        <v>0.6837427575297426</v>
       </c>
       <c r="D1004" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E1004">
-        <v>1.204232945758894</v>
+        <v>1.194967273410384</v>
       </c>
       <c r="F1004">
         <v>1</v>
       </c>
       <c r="G1004">
-        <v>0.01750634218111954</v>
+        <v>0.01751625724247026</v>
       </c>
       <c r="H1004">
-        <v>0.01691576705424111</v>
+        <v>0.01692503272658962</v>
       </c>
       <c r="I1004">
-        <v>0.5105751268784369</v>
+        <v>0.5112245158806417</v>
       </c>
       <c r="J1004">
-        <v>1.342866163118138</v>
+        <v>1.344450038733268</v>
       </c>
       <c r="K1004">
         <v>6.26</v>
@@ -51975,7 +51975,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>463</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -51986,28 +51986,28 @@
         <v>192</v>
       </c>
       <c r="C1005">
-        <v>0.6837427575297426</v>
+        <v>0.6537674584469055</v>
       </c>
       <c r="D1005" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E1005">
-        <v>1.194967273410384</v>
+        <v>1.166955212765879</v>
       </c>
       <c r="F1005">
         <v>1</v>
       </c>
       <c r="G1005">
-        <v>0.01751625724247026</v>
+        <v>0.0175462325415531</v>
       </c>
       <c r="H1005">
-        <v>0.01692503272658962</v>
+        <v>0.01695304478723412</v>
       </c>
       <c r="I1005">
-        <v>0.5112245158806417</v>
+        <v>0.5131877543189738</v>
       </c>
       <c r="J1005">
-        <v>1.344450038733268</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1005">
         <v>6.26</v>
@@ -52025,7 +52025,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>191</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52036,28 +52036,28 @@
         <v>192</v>
       </c>
       <c r="C1006">
-        <v>0.6537674584469055</v>
+        <v>0.6424229975026066</v>
       </c>
       <c r="D1006" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E1006">
-        <v>1.166955212765879</v>
+        <v>1.156353759647005</v>
       </c>
       <c r="F1006">
         <v>1</v>
       </c>
       <c r="G1006">
-        <v>0.0175462325415531</v>
+        <v>0.01755757700249739</v>
       </c>
       <c r="H1006">
-        <v>0.01695304478723412</v>
+        <v>0.016963646240353</v>
       </c>
       <c r="I1006">
-        <v>0.5131877543189738</v>
+        <v>0.5139307621443985</v>
       </c>
       <c r="J1006">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1006">
         <v>6.26</v>
@@ -52075,7 +52075,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52083,49 +52083,49 @@
         <v>0</v>
       </c>
       <c r="B1007" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C1007">
-        <v>0.6424229975026066</v>
+        <v>1.15176585526189</v>
       </c>
       <c r="D1007" t="s">
-        <v>194</v>
+        <v>348</v>
       </c>
       <c r="E1007">
-        <v>1.156353759647005</v>
+        <v>0.7013897200842756</v>
       </c>
       <c r="F1007">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1007">
-        <v>0.01755757700249739</v>
+        <v>0.01696823414473811</v>
       </c>
       <c r="H1007">
-        <v>0.016963646240353</v>
+        <v>0.01559861027991572</v>
       </c>
       <c r="I1007">
-        <v>0.5139307621443985</v>
+        <v>0.4503761351776143</v>
       </c>
       <c r="J1007">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1007">
-        <v>6.26</v>
+        <v>5.85</v>
       </c>
       <c r="L1007">
-        <v>9.1</v>
+        <v>9.06</v>
       </c>
       <c r="M1007">
-        <v>5.85</v>
+        <v>5.51</v>
       </c>
       <c r="N1007">
-        <v>9.06</v>
+        <v>8.15</v>
       </c>
       <c r="O1007">
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>465</v>
+        <v>347</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52136,90 +52136,90 @@
         <v>194</v>
       </c>
       <c r="C1008">
-        <v>1.15176585526189</v>
+        <v>0.5002997890366885</v>
       </c>
       <c r="D1008" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1008">
-        <v>0.7013897200842756</v>
+        <v>0.8376088036369964</v>
       </c>
       <c r="F1008">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1008">
-        <v>0.01696823414473811</v>
+        <v>0.01577970021096331</v>
       </c>
       <c r="H1008">
-        <v>0.01559861027991572</v>
+        <v>0.01698239119636301</v>
       </c>
       <c r="I1008">
-        <v>0.4503761351776143</v>
+        <v>0.3373090146003079</v>
       </c>
       <c r="J1008">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1008">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1008">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1008">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1008">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1008">
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>347</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
       <c r="A1009" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1009" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C1009">
-        <v>0.5002997890366885</v>
+        <v>1.149867923161882</v>
       </c>
       <c r="D1009" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1009">
-        <v>0.8376088036369964</v>
+        <v>0.6996020951490545</v>
       </c>
       <c r="F1009">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1009">
-        <v>0.01577970021096331</v>
+        <v>0.01697013207683812</v>
       </c>
       <c r="H1009">
-        <v>0.01698239119636301</v>
+        <v>0.01560039790485095</v>
       </c>
       <c r="I1009">
-        <v>0.3373090146003079</v>
+        <v>0.4502658280128271</v>
       </c>
       <c r="J1009">
         <v>1.352159329374037</v>
       </c>
       <c r="K1009">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1009">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1009">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1009">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1009">
         <v>1</v>
@@ -52230,96 +52230,96 @@
     </row>
     <row r="1010" spans="1:16">
       <c r="A1010" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1010" t="s">
         <v>194</v>
       </c>
       <c r="C1010">
-        <v>1.149867923161882</v>
+        <v>0.4969577705448094</v>
       </c>
       <c r="D1010" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1010">
-        <v>0.6996020951490545</v>
+        <v>0.8340775026818612</v>
       </c>
       <c r="F1010">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1010">
-        <v>0.01697013207683812</v>
+        <v>0.01578304222945519</v>
       </c>
       <c r="H1010">
-        <v>0.01560039790485095</v>
+        <v>0.01698592249731814</v>
       </c>
       <c r="I1010">
-        <v>0.4502658280128271</v>
+        <v>0.3371197321370518</v>
       </c>
       <c r="J1010">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1010">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1010">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1010">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1010">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1010">
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
       <c r="A1011" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1011" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C1011">
-        <v>0.4969577705448094</v>
+        <v>1.146407603130467</v>
       </c>
       <c r="D1011" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1011">
-        <v>0.8340775026818612</v>
+        <v>0.6963428877348496</v>
       </c>
       <c r="F1011">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1011">
-        <v>0.01578304222945519</v>
+        <v>0.01697359239686954</v>
       </c>
       <c r="H1011">
-        <v>0.01698592249731814</v>
+        <v>0.01560365711226515</v>
       </c>
       <c r="I1011">
-        <v>0.3371197321370518</v>
+        <v>0.4500647153956177</v>
       </c>
       <c r="J1011">
         <v>1.352750837071715</v>
       </c>
       <c r="K1011">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1011">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1011">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1011">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1011">
         <v>1</v>
@@ -52330,196 +52330,196 @@
     </row>
     <row r="1012" spans="1:16">
       <c r="A1012" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1012" t="s">
         <v>194</v>
       </c>
       <c r="C1012">
-        <v>1.146407603130467</v>
+        <v>0.4920648074520191</v>
       </c>
       <c r="D1012" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1012">
-        <v>0.6963428877348496</v>
+        <v>0.8289074160156744</v>
       </c>
       <c r="F1012">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1012">
-        <v>0.01697359239686954</v>
+        <v>0.01578793519254798</v>
       </c>
       <c r="H1012">
-        <v>0.01560365711226515</v>
+        <v>0.01699109258398433</v>
       </c>
       <c r="I1012">
-        <v>0.4500647153956177</v>
+        <v>0.3368426085636553</v>
       </c>
       <c r="J1012">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1012">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1012">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1012">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1012">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1012">
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>467</v>
+        <v>346</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
       <c r="A1013" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1013" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C1013">
-        <v>0.4920648074520191</v>
+        <v>1.141341437804305</v>
       </c>
       <c r="D1013" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1013">
-        <v>0.8289074160156744</v>
+        <v>0.6915711662054216</v>
       </c>
       <c r="F1013">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1013">
-        <v>0.01578793519254798</v>
+        <v>0.0169786585621957</v>
       </c>
       <c r="H1013">
-        <v>0.01699109258398433</v>
+        <v>0.01560842883379458</v>
       </c>
       <c r="I1013">
-        <v>0.3368426085636553</v>
+        <v>0.4497702715988829</v>
       </c>
       <c r="J1013">
         <v>1.353616848238581</v>
       </c>
       <c r="K1013">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1013">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1013">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1013">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1013">
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>193</v>
+        <v>346</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
       <c r="A1014" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1014" t="s">
         <v>194</v>
       </c>
       <c r="C1014">
-        <v>1.141341437804305</v>
+        <v>0.5046197380717317</v>
       </c>
       <c r="D1014" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1014">
-        <v>0.6915711662054216</v>
+        <v>0.8421734223519017</v>
       </c>
       <c r="F1014">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1014">
-        <v>0.0169786585621957</v>
+        <v>0.01577538026192827</v>
       </c>
       <c r="H1014">
-        <v>0.01560842883379458</v>
+        <v>0.0169778265776481</v>
       </c>
       <c r="I1014">
-        <v>0.4497702715988829</v>
+        <v>0.3375536842801701</v>
       </c>
       <c r="J1014">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1014">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1014">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1014">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1014">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1014">
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>193</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
       <c r="A1015" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1015" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C1015">
-        <v>0.5046197380717317</v>
+        <v>1.154340790746838</v>
       </c>
       <c r="D1015" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1015">
-        <v>0.8421734223519017</v>
+        <v>0.7038150011991586</v>
       </c>
       <c r="F1015">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1015">
-        <v>0.01577538026192827</v>
+        <v>0.01696565920925316</v>
       </c>
       <c r="H1015">
-        <v>0.0169778265776481</v>
+        <v>0.01559618499880084</v>
       </c>
       <c r="I1015">
-        <v>0.3375536842801701</v>
+        <v>0.4505257895476795</v>
       </c>
       <c r="J1015">
         <v>1.351394736624472</v>
       </c>
       <c r="K1015">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1015">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1015">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1015">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1015">
         <v>1</v>
@@ -52530,151 +52530,101 @@
     </row>
     <row r="1016" spans="1:16">
       <c r="A1016" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1016" t="s">
         <v>194</v>
       </c>
       <c r="C1016">
-        <v>1.154340790746838</v>
+        <v>0.5044756313746497</v>
       </c>
       <c r="D1016" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1016">
-        <v>0.7038150011991586</v>
+        <v>0.8420211538595854</v>
       </c>
       <c r="F1016">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1016">
-        <v>0.01696565920925316</v>
+        <v>0.01577552436862535</v>
       </c>
       <c r="H1016">
-        <v>0.01559618499880084</v>
+        <v>0.01697797884614042</v>
       </c>
       <c r="I1016">
-        <v>0.4505257895476795</v>
+        <v>0.3375455224849357</v>
       </c>
       <c r="J1016">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1016">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1016">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1016">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1016">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1016">
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>468</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
       <c r="A1017" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1017" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C1017">
-        <v>0.5044756313746497</v>
+        <v>1.154191582927735</v>
       </c>
       <c r="D1017" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1017">
-        <v>0.8420211538595854</v>
+        <v>0.7036744652874907</v>
       </c>
       <c r="F1017">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1017">
-        <v>0.01577552436862535</v>
+        <v>0.01696580841707227</v>
       </c>
       <c r="H1017">
-        <v>0.01697797884614042</v>
+        <v>0.01559632553471251</v>
       </c>
       <c r="I1017">
-        <v>0.3375455224849357</v>
+        <v>0.4505171176402447</v>
       </c>
       <c r="J1017">
         <v>1.351420242234575</v>
       </c>
       <c r="K1017">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1017">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1017">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1017">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1017">
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="1018" spans="1:16">
-      <c r="A1018" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1018" t="s">
-        <v>194</v>
-      </c>
-      <c r="C1018">
-        <v>1.154191582927735</v>
-      </c>
-      <c r="D1018" t="s">
-        <v>348</v>
-      </c>
-      <c r="E1018">
-        <v>0.7036744652874907</v>
-      </c>
-      <c r="F1018">
-        <v>-1</v>
-      </c>
-      <c r="G1018">
-        <v>0.01696580841707227</v>
-      </c>
-      <c r="H1018">
-        <v>0.01559632553471251</v>
-      </c>
-      <c r="I1018">
-        <v>0.4505171176402447</v>
-      </c>
-      <c r="J1018">
-        <v>1.351420242234575</v>
-      </c>
-      <c r="K1018">
-        <v>5.85</v>
-      </c>
-      <c r="L1018">
-        <v>9.06</v>
-      </c>
-      <c r="M1018">
-        <v>5.51</v>
-      </c>
-      <c r="N1018">
-        <v>8.15</v>
-      </c>
-      <c r="O1018">
-        <v>1</v>
-      </c>
-      <c r="P1018" t="s">
         <v>192</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3093" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="471">
   <si>
     <t>trade_time</t>
   </si>
@@ -586,7 +586,7 @@
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-09</t>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2021-09-23</t>
@@ -598,10 +598,10 @@
     <t>2021-10-22</t>
   </si>
   <si>
-    <t>2021-10-19</t>
+    <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-30</t>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2021-10-15</t>
@@ -1063,7 +1063,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-10-25</t>
+    <t>2021-10-26</t>
   </si>
   <si>
     <t>2021-10-20</t>
@@ -1414,9 +1414,6 @@
     <t>2021-09-17</t>
   </si>
   <si>
-    <t>2021-09-24</t>
-  </si>
-  <si>
     <t>2021-09-27</t>
   </si>
   <si>
@@ -1424,6 +1421,9 @@
   </si>
   <si>
     <t>2021-09-29</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
   </si>
   <si>
     <t>2021-10-11</t>
@@ -1784,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1027"/>
+  <dimension ref="A1:P1025"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -50992,7 +50992,7 @@
         <v>190</v>
       </c>
       <c r="C985">
-        <v>1.478357895886811</v>
+        <v>1.267644967891206</v>
       </c>
       <c r="D985" t="s">
         <v>347</v>
@@ -51004,22 +51004,22 @@
         <v>-1</v>
       </c>
       <c r="G985">
-        <v>0.01792164210411319</v>
+        <v>0.0170723550321088</v>
       </c>
       <c r="H985">
         <v>0.01731182033611209</v>
       </c>
       <c r="I985">
-        <v>0.4501782319989012</v>
+        <v>0.2394653040032964</v>
       </c>
       <c r="J985">
         <v>1.330362800018315</v>
       </c>
       <c r="K985">
-        <v>6.18</v>
+        <v>5.94</v>
       </c>
       <c r="L985">
-        <v>9.699999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="M985">
         <v>6.12</v>
@@ -51095,7 +51095,7 @@
         <v>0.7719288718853452</v>
       </c>
       <c r="D987" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E987">
         <v>1.277377619892856</v>
@@ -51148,7 +51148,7 @@
         <v>349</v>
       </c>
       <c r="E988">
-        <v>0.7960408799010965</v>
+        <v>0.9022916719036616</v>
       </c>
       <c r="F988">
         <v>1</v>
@@ -51157,10 +51157,10 @@
         <v>0.01503074460809817</v>
       </c>
       <c r="H988">
-        <v>0.01516395912009891</v>
+        <v>0.01489770832809634</v>
       </c>
       <c r="I988">
-        <v>0.02678548799926705</v>
+        <v>0.1330362800018321</v>
       </c>
       <c r="J988">
         <v>1.330362800018315</v>
@@ -51172,10 +51172,10 @@
         <v>7.9</v>
       </c>
       <c r="M988">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="N988">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="O988">
         <v>1</v>
@@ -51239,7 +51239,7 @@
         <v>1</v>
       </c>
       <c r="B990" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C990">
         <v>1.41276333099256</v>
@@ -51345,7 +51345,7 @@
         <v>0.7054851864099394</v>
       </c>
       <c r="D992" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E992">
         <v>1.215285677395871</v>
@@ -51398,7 +51398,7 @@
         <v>349</v>
       </c>
       <c r="E993">
-        <v>0.7387252406731104</v>
+        <v>0.8464619936926976</v>
       </c>
       <c r="F993">
         <v>1</v>
@@ -51407,10 +51407,10 @@
         <v>0.01508763568703558</v>
       </c>
       <c r="H993">
-        <v>0.01522127475932689</v>
+        <v>0.0149535380063073</v>
       </c>
       <c r="I993">
-        <v>0.02636092770868981</v>
+        <v>0.134097680728277</v>
       </c>
       <c r="J993">
         <v>1.340976807282757</v>
@@ -51422,10 +51422,10 @@
         <v>7.9</v>
       </c>
       <c r="M993">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="N993">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="O993">
         <v>1</v>
@@ -51481,7 +51481,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51495,7 +51495,7 @@
         <v>0.730902359952653</v>
       </c>
       <c r="D995" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E995">
         <v>1.239038147879077</v>
@@ -51531,7 +51531,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51548,7 +51548,7 @@
         <v>349</v>
       </c>
       <c r="E996">
-        <v>0.7606505980422238</v>
+        <v>0.8678189158707594</v>
       </c>
       <c r="F996">
         <v>1</v>
@@ -51557,10 +51557,10 @@
         <v>0.01506587273972105</v>
       </c>
       <c r="H996">
-        <v>0.01519934940195778</v>
+        <v>0.01493218108412924</v>
       </c>
       <c r="I996">
-        <v>0.0265233377632752</v>
+        <v>0.1336916555918108</v>
       </c>
       <c r="J996">
         <v>1.336916555918107</v>
@@ -51572,16 +51572,16 @@
         <v>7.9</v>
       </c>
       <c r="M996">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="N996">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="O996">
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51645,7 +51645,7 @@
         <v>0.7031067530561543</v>
       </c>
       <c r="D998" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E998">
         <v>1.213063020028516</v>
@@ -51698,7 +51698,7 @@
         <v>349</v>
       </c>
       <c r="E999">
-        <v>0.7366735569493983</v>
+        <v>0.844463501769229</v>
       </c>
       <c r="F999">
         <v>1</v>
@@ -51707,10 +51707,10 @@
         <v>0.01508967217310208</v>
       </c>
       <c r="H999">
-        <v>0.0152233264430506</v>
+        <v>0.01495553649823077</v>
       </c>
       <c r="I999">
-        <v>0.02634573005147711</v>
+        <v>0.1341356748713078</v>
       </c>
       <c r="J999">
         <v>1.341356748713074</v>
@@ -51722,10 +51722,10 @@
         <v>7.9</v>
       </c>
       <c r="M999">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="N999">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="O999">
         <v>1</v>
@@ -51795,7 +51795,7 @@
         <v>0.6897950523407328</v>
       </c>
       <c r="D1001" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1001">
         <v>1.200623171915861</v>
@@ -51848,7 +51848,7 @@
         <v>349</v>
       </c>
       <c r="E1002">
-        <v>0.7251906202300251</v>
+        <v>0.8332782708166544</v>
       </c>
       <c r="F1002">
         <v>1</v>
@@ -51857,10 +51857,10 @@
         <v>0.01510107005103094</v>
       </c>
       <c r="H1002">
-        <v>0.01523480937976998</v>
+        <v>0.01496672172918335</v>
       </c>
       <c r="I1002">
-        <v>0.02626067126096387</v>
+        <v>0.1343483218475932</v>
       </c>
       <c r="J1002">
         <v>1.343483218475921</v>
@@ -51872,10 +51872,10 @@
         <v>7.9</v>
       </c>
       <c r="M1002">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="N1002">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="O1002">
         <v>1</v>
@@ -51945,7 +51945,7 @@
         <v>0.6867118341980269</v>
       </c>
       <c r="D1004" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1004">
         <v>1.197741889785697</v>
@@ -51998,7 +51998,7 @@
         <v>349</v>
       </c>
       <c r="E1005">
-        <v>0.722530975186797</v>
+        <v>0.8306875795338069</v>
       </c>
       <c r="F1005">
         <v>1</v>
@@ -52007,10 +52007,10 @@
         <v>0.01510370999499977</v>
       </c>
       <c r="H1005">
-        <v>0.01523746902481321</v>
+        <v>0.01496931242046619</v>
       </c>
       <c r="I1005">
-        <v>0.0262409701865689</v>
+        <v>0.1343975745335788</v>
       </c>
       <c r="J1005">
         <v>1.343975745335778</v>
@@ -52022,10 +52022,10 @@
         <v>7.9</v>
       </c>
       <c r="M1005">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="N1005">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="O1005">
         <v>1</v>
@@ -52095,7 +52095,7 @@
         <v>0.7009931302172401</v>
       </c>
       <c r="D1007" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1007">
         <v>1.211087829356368</v>
@@ -52148,7 +52148,7 @@
         <v>349</v>
       </c>
       <c r="E1008">
-        <v>0.7348503040212622</v>
+        <v>0.8426875183614522</v>
       </c>
       <c r="F1008">
         <v>1</v>
@@ -52157,10 +52157,10 @@
         <v>0.01509148192045297</v>
       </c>
       <c r="H1008">
-        <v>0.01522514969597874</v>
+        <v>0.01495731248163855</v>
       </c>
       <c r="I1008">
-        <v>0.02633222447423211</v>
+        <v>0.1341694388144221</v>
       </c>
       <c r="J1008">
         <v>1.341694388144211</v>
@@ -52172,10 +52172,10 @@
         <v>7.9</v>
       </c>
       <c r="M1008">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="N1008">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="O1008">
         <v>1</v>
@@ -52245,7 +52245,7 @@
         <v>0.6936578188804567</v>
       </c>
       <c r="D1010" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1010">
         <v>1.204232945758894</v>
@@ -52298,7 +52298,7 @@
         <v>349</v>
       </c>
       <c r="E1011">
-        <v>0.7285227191620551</v>
+        <v>0.836523981998595</v>
       </c>
       <c r="F1011">
         <v>1</v>
@@ -52307,10 +52307,10 @@
         <v>0.01509776263431322</v>
       </c>
       <c r="H1011">
-        <v>0.01523147728083795</v>
+        <v>0.01496347601800141</v>
       </c>
       <c r="I1011">
-        <v>0.0262853534752745</v>
+        <v>0.1342866163118144</v>
       </c>
       <c r="J1011">
         <v>1.342866163118138</v>
@@ -52322,10 +52322,10 @@
         <v>7.9</v>
       </c>
       <c r="M1011">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="N1011">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="O1011">
         <v>1</v>
@@ -52345,7 +52345,7 @@
         <v>0.6837427575297426</v>
       </c>
       <c r="D1012" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1012">
         <v>1.194967273410384</v>
@@ -52389,43 +52389,43 @@
         <v>0</v>
       </c>
       <c r="B1013" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C1013">
-        <v>0.6537674584469055</v>
+        <v>1.156353759647005</v>
       </c>
       <c r="D1013" t="s">
-        <v>194</v>
+        <v>350</v>
       </c>
       <c r="E1013">
-        <v>1.166955212765879</v>
+        <v>0.705710977035042</v>
       </c>
       <c r="F1013">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1013">
-        <v>0.0175462325415531</v>
+        <v>0.016963646240353</v>
       </c>
       <c r="H1013">
-        <v>0.01695304478723412</v>
+        <v>0.01559428902296496</v>
       </c>
       <c r="I1013">
-        <v>0.5131877543189738</v>
+        <v>0.450642782611963</v>
       </c>
       <c r="J1013">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1013">
-        <v>6.26</v>
+        <v>5.85</v>
       </c>
       <c r="L1013">
-        <v>9.1</v>
+        <v>9.06</v>
       </c>
       <c r="M1013">
-        <v>5.85</v>
+        <v>5.51</v>
       </c>
       <c r="N1013">
-        <v>9.06</v>
+        <v>8.15</v>
       </c>
       <c r="O1013">
         <v>1</v>
@@ -52439,43 +52439,43 @@
         <v>0</v>
       </c>
       <c r="B1014" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C1014">
-        <v>1.156353759647005</v>
+        <v>0.5021328345691742</v>
       </c>
       <c r="D1014" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1014">
-        <v>0.705710977035042</v>
+        <v>0.8395456676775179</v>
       </c>
       <c r="F1014">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1014">
-        <v>0.016963646240353</v>
+        <v>0.01577786716543083</v>
       </c>
       <c r="H1014">
-        <v>0.01559428902296496</v>
+        <v>0.01698045433232248</v>
       </c>
       <c r="I1014">
-        <v>0.450642782611963</v>
+        <v>0.3374128331083437</v>
       </c>
       <c r="J1014">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1014">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1014">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1014">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1014">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1014">
         <v>1</v>
@@ -52486,84 +52486,84 @@
     </row>
     <row r="1015" spans="1:16">
       <c r="A1015" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1015" t="s">
         <v>195</v>
       </c>
       <c r="C1015">
-        <v>0.9765823656082446</v>
+        <v>1.15176585526189</v>
       </c>
       <c r="D1015" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E1015">
-        <v>0.6882475062965234</v>
+        <v>0.7013897200842756</v>
       </c>
       <c r="F1015">
         <v>-1</v>
       </c>
       <c r="G1015">
-        <v>0.01706341763439176</v>
+        <v>0.01696823414473811</v>
       </c>
       <c r="H1015">
-        <v>0.01653175249370347</v>
+        <v>0.01559861027991572</v>
       </c>
       <c r="I1015">
-        <v>0.2883348593117212</v>
+        <v>0.4503761351776143</v>
       </c>
       <c r="J1015">
         <v>1.351834896536429</v>
       </c>
       <c r="K1015">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="L1015">
-        <v>9.02</v>
+        <v>9.06</v>
       </c>
       <c r="M1015">
-        <v>5.86</v>
+        <v>5.51</v>
       </c>
       <c r="N1015">
-        <v>8.609999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="O1015">
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
       <c r="A1016" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1016" t="s">
         <v>196</v>
       </c>
       <c r="C1016">
-        <v>0.5021328345691742</v>
+        <v>0.5002997890366885</v>
       </c>
       <c r="D1016" t="s">
         <v>351</v>
       </c>
       <c r="E1016">
-        <v>0.8395456676775179</v>
+        <v>0.8376088036369964</v>
       </c>
       <c r="F1016">
         <v>1</v>
       </c>
       <c r="G1016">
-        <v>0.01577786716543083</v>
+        <v>0.01577970021096331</v>
       </c>
       <c r="H1016">
-        <v>0.01698045433232248</v>
+        <v>0.01698239119636301</v>
       </c>
       <c r="I1016">
-        <v>0.3374128331083437</v>
+        <v>0.3373090146003079</v>
       </c>
       <c r="J1016">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1016">
         <v>5.65</v>
@@ -52586,34 +52586,34 @@
     </row>
     <row r="1017" spans="1:16">
       <c r="A1017" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1017" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C1017">
-        <v>1.15176585526189</v>
+        <v>1.149867923161882</v>
       </c>
       <c r="D1017" t="s">
         <v>350</v>
       </c>
       <c r="E1017">
-        <v>0.7013897200842756</v>
+        <v>0.6996020951490545</v>
       </c>
       <c r="F1017">
         <v>-1</v>
       </c>
       <c r="G1017">
-        <v>0.01696823414473811</v>
+        <v>0.01697013207683812</v>
       </c>
       <c r="H1017">
-        <v>0.01559861027991572</v>
+        <v>0.01560039790485095</v>
       </c>
       <c r="I1017">
-        <v>0.4503761351776143</v>
+        <v>0.4502658280128271</v>
       </c>
       <c r="J1017">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1017">
         <v>5.85</v>
@@ -52642,28 +52642,28 @@
         <v>196</v>
       </c>
       <c r="C1018">
-        <v>0.5002997890366885</v>
+        <v>0.4969577705448094</v>
       </c>
       <c r="D1018" t="s">
         <v>351</v>
       </c>
       <c r="E1018">
-        <v>0.8376088036369964</v>
+        <v>0.8340775026818612</v>
       </c>
       <c r="F1018">
         <v>1</v>
       </c>
       <c r="G1018">
-        <v>0.01577970021096331</v>
+        <v>0.01578304222945519</v>
       </c>
       <c r="H1018">
-        <v>0.01698239119636301</v>
+        <v>0.01698592249731814</v>
       </c>
       <c r="I1018">
-        <v>0.3373090146003079</v>
+        <v>0.3371197321370518</v>
       </c>
       <c r="J1018">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1018">
         <v>5.65</v>
@@ -52689,31 +52689,31 @@
         <v>1</v>
       </c>
       <c r="B1019" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C1019">
-        <v>1.149867923161882</v>
+        <v>1.146407603130467</v>
       </c>
       <c r="D1019" t="s">
         <v>350</v>
       </c>
       <c r="E1019">
-        <v>0.6996020951490545</v>
+        <v>0.6963428877348496</v>
       </c>
       <c r="F1019">
         <v>-1</v>
       </c>
       <c r="G1019">
-        <v>0.01697013207683812</v>
+        <v>0.01697359239686954</v>
       </c>
       <c r="H1019">
-        <v>0.01560039790485095</v>
+        <v>0.01560365711226515</v>
       </c>
       <c r="I1019">
-        <v>0.4502658280128271</v>
+        <v>0.4500647153956177</v>
       </c>
       <c r="J1019">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1019">
         <v>5.85</v>
@@ -52742,28 +52742,28 @@
         <v>196</v>
       </c>
       <c r="C1020">
-        <v>0.4969577705448094</v>
+        <v>0.4920648074520191</v>
       </c>
       <c r="D1020" t="s">
         <v>351</v>
       </c>
       <c r="E1020">
-        <v>0.8340775026818612</v>
+        <v>0.8289074160156744</v>
       </c>
       <c r="F1020">
         <v>1</v>
       </c>
       <c r="G1020">
-        <v>0.01578304222945519</v>
+        <v>0.01578793519254798</v>
       </c>
       <c r="H1020">
-        <v>0.01698592249731814</v>
+        <v>0.01699109258398433</v>
       </c>
       <c r="I1020">
-        <v>0.3371197321370518</v>
+        <v>0.3368426085636553</v>
       </c>
       <c r="J1020">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1020">
         <v>5.65</v>
@@ -52781,7 +52781,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>195</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52789,31 +52789,31 @@
         <v>1</v>
       </c>
       <c r="B1021" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C1021">
-        <v>1.146407603130467</v>
+        <v>1.141341437804305</v>
       </c>
       <c r="D1021" t="s">
         <v>350</v>
       </c>
       <c r="E1021">
-        <v>0.6963428877348496</v>
+        <v>0.6915711662054216</v>
       </c>
       <c r="F1021">
         <v>-1</v>
       </c>
       <c r="G1021">
-        <v>0.01697359239686954</v>
+        <v>0.0169786585621957</v>
       </c>
       <c r="H1021">
-        <v>0.01560365711226515</v>
+        <v>0.01560842883379458</v>
       </c>
       <c r="I1021">
-        <v>0.4500647153956177</v>
+        <v>0.4497702715988829</v>
       </c>
       <c r="J1021">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1021">
         <v>5.85</v>
@@ -52831,7 +52831,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>195</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52842,28 +52842,28 @@
         <v>196</v>
       </c>
       <c r="C1022">
-        <v>0.4920648074520191</v>
+        <v>0.5046197380717317</v>
       </c>
       <c r="D1022" t="s">
         <v>351</v>
       </c>
       <c r="E1022">
-        <v>0.8289074160156744</v>
+        <v>0.8421734223519017</v>
       </c>
       <c r="F1022">
         <v>1</v>
       </c>
       <c r="G1022">
-        <v>0.01578793519254798</v>
+        <v>0.01577538026192827</v>
       </c>
       <c r="H1022">
-        <v>0.01699109258398433</v>
+        <v>0.0169778265776481</v>
       </c>
       <c r="I1022">
-        <v>0.3368426085636553</v>
+        <v>0.3375536842801701</v>
       </c>
       <c r="J1022">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1022">
         <v>5.65</v>
@@ -52881,7 +52881,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>348</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -52889,31 +52889,31 @@
         <v>1</v>
       </c>
       <c r="B1023" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C1023">
-        <v>1.141341437804305</v>
+        <v>1.154340790746838</v>
       </c>
       <c r="D1023" t="s">
         <v>350</v>
       </c>
       <c r="E1023">
-        <v>0.6915711662054216</v>
+        <v>0.7038150011991586</v>
       </c>
       <c r="F1023">
         <v>-1</v>
       </c>
       <c r="G1023">
-        <v>0.0169786585621957</v>
+        <v>0.01696565920925316</v>
       </c>
       <c r="H1023">
-        <v>0.01560842883379458</v>
+        <v>0.01559618499880084</v>
       </c>
       <c r="I1023">
-        <v>0.4497702715988829</v>
+        <v>0.4505257895476795</v>
       </c>
       <c r="J1023">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1023">
         <v>5.85</v>
@@ -52931,7 +52931,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>348</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -52942,28 +52942,28 @@
         <v>196</v>
       </c>
       <c r="C1024">
-        <v>0.5046197380717317</v>
+        <v>0.5044756313746497</v>
       </c>
       <c r="D1024" t="s">
         <v>351</v>
       </c>
       <c r="E1024">
-        <v>0.8421734223519017</v>
+        <v>0.8420211538595854</v>
       </c>
       <c r="F1024">
         <v>1</v>
       </c>
       <c r="G1024">
-        <v>0.01577538026192827</v>
+        <v>0.01577552436862535</v>
       </c>
       <c r="H1024">
-        <v>0.0169778265776481</v>
+        <v>0.01697797884614042</v>
       </c>
       <c r="I1024">
-        <v>0.3375536842801701</v>
+        <v>0.3375455224849357</v>
       </c>
       <c r="J1024">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1024">
         <v>5.65</v>
@@ -52981,7 +52981,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>470</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -52989,31 +52989,31 @@
         <v>1</v>
       </c>
       <c r="B1025" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C1025">
-        <v>1.154340790746838</v>
+        <v>1.154191582927735</v>
       </c>
       <c r="D1025" t="s">
         <v>350</v>
       </c>
       <c r="E1025">
-        <v>0.7038150011991586</v>
+        <v>0.7036744652874907</v>
       </c>
       <c r="F1025">
         <v>-1</v>
       </c>
       <c r="G1025">
-        <v>0.01696565920925316</v>
+        <v>0.01696580841707227</v>
       </c>
       <c r="H1025">
-        <v>0.01559618499880084</v>
+        <v>0.01559632553471251</v>
       </c>
       <c r="I1025">
-        <v>0.4505257895476795</v>
+        <v>0.4505171176402447</v>
       </c>
       <c r="J1025">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1025">
         <v>5.85</v>
@@ -53031,106 +53031,6 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="1026" spans="1:16">
-      <c r="A1026" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1026">
-        <v>0.5044756313746497</v>
-      </c>
-      <c r="D1026" t="s">
-        <v>351</v>
-      </c>
-      <c r="E1026">
-        <v>0.8420211538595854</v>
-      </c>
-      <c r="F1026">
-        <v>1</v>
-      </c>
-      <c r="G1026">
-        <v>0.01577552436862535</v>
-      </c>
-      <c r="H1026">
-        <v>0.01697797884614042</v>
-      </c>
-      <c r="I1026">
-        <v>0.3375455224849357</v>
-      </c>
-      <c r="J1026">
-        <v>1.351420242234575</v>
-      </c>
-      <c r="K1026">
-        <v>5.65</v>
-      </c>
-      <c r="L1026">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="M1026">
-        <v>5.97</v>
-      </c>
-      <c r="N1026">
-        <v>8.91</v>
-      </c>
-      <c r="O1026">
-        <v>1</v>
-      </c>
-      <c r="P1026" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="1027" spans="1:16">
-      <c r="A1027" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>194</v>
-      </c>
-      <c r="C1027">
-        <v>1.154191582927735</v>
-      </c>
-      <c r="D1027" t="s">
-        <v>350</v>
-      </c>
-      <c r="E1027">
-        <v>0.7036744652874907</v>
-      </c>
-      <c r="F1027">
-        <v>-1</v>
-      </c>
-      <c r="G1027">
-        <v>0.01696580841707227</v>
-      </c>
-      <c r="H1027">
-        <v>0.01559632553471251</v>
-      </c>
-      <c r="I1027">
-        <v>0.4505171176402447</v>
-      </c>
-      <c r="J1027">
-        <v>1.351420242234575</v>
-      </c>
-      <c r="K1027">
-        <v>5.85</v>
-      </c>
-      <c r="L1027">
-        <v>9.06</v>
-      </c>
-      <c r="M1027">
-        <v>5.51</v>
-      </c>
-      <c r="N1027">
-        <v>8.15</v>
-      </c>
-      <c r="O1027">
-        <v>1</v>
-      </c>
-      <c r="P1027" t="s">
         <v>192</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3099" uniqueCount="472">
   <si>
     <t>trade_time</t>
   </si>
@@ -598,13 +598,13 @@
     <t>2021-10-22</t>
   </si>
   <si>
-    <t>2021-09-09</t>
+    <t>2021-09-16</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
   </si>
   <si>
     <t>2021-10-19</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
   </si>
   <si>
     <t>2016-11-30</t>
@@ -1063,13 +1063,13 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-10-26</t>
+    <t>2021-10-27</t>
+  </si>
+  <si>
+    <t>2021-10-18</t>
   </si>
   <si>
     <t>2021-10-20</t>
-  </si>
-  <si>
-    <t>2021-10-18</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1402,16 +1402,19 @@
     <t>2021-09-01</t>
   </si>
   <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
     <t>2021-09-10</t>
   </si>
   <si>
     <t>2021-09-13</t>
   </si>
   <si>
-    <t>2021-09-16</t>
+    <t>2021-09-17</t>
   </si>
   <si>
-    <t>2021-09-17</t>
+    <t>2021-09-24</t>
   </si>
   <si>
     <t>2021-09-27</t>
@@ -1784,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1025"/>
+  <dimension ref="A1:P1029"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51095,7 +51098,7 @@
         <v>0.7719288718853452</v>
       </c>
       <c r="D987" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E987">
         <v>1.277377619892856</v>
@@ -51148,7 +51151,7 @@
         <v>349</v>
       </c>
       <c r="E988">
-        <v>0.9022916719036616</v>
+        <v>0.7717569759069578</v>
       </c>
       <c r="F988">
         <v>1</v>
@@ -51157,10 +51160,10 @@
         <v>0.01503074460809817</v>
       </c>
       <c r="H988">
-        <v>0.01489770832809634</v>
+        <v>0.01428824302409304</v>
       </c>
       <c r="I988">
-        <v>0.1330362800018321</v>
+        <v>0.002501584005128343</v>
       </c>
       <c r="J988">
         <v>1.330362800018315</v>
@@ -51172,10 +51175,10 @@
         <v>7.9</v>
       </c>
       <c r="M988">
-        <v>5.26</v>
+        <v>5.08</v>
       </c>
       <c r="N988">
-        <v>7.9</v>
+        <v>7.53</v>
       </c>
       <c r="O988">
         <v>1</v>
@@ -51239,10 +51242,10 @@
         <v>1</v>
       </c>
       <c r="B990" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C990">
-        <v>1.41276333099256</v>
+        <v>1.204597764740421</v>
       </c>
       <c r="D990" t="s">
         <v>347</v>
@@ -51254,22 +51257,22 @@
         <v>-1</v>
       </c>
       <c r="G990">
-        <v>0.01798723666900744</v>
+        <v>0.01713540223525958</v>
       </c>
       <c r="H990">
         <v>0.01737677806057047</v>
       </c>
       <c r="I990">
-        <v>0.4495413915630344</v>
+        <v>0.2413758253108957</v>
       </c>
       <c r="J990">
         <v>1.340976807282757</v>
       </c>
       <c r="K990">
-        <v>6.18</v>
+        <v>5.94</v>
       </c>
       <c r="L990">
-        <v>9.699999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="M990">
         <v>6.12</v>
@@ -51345,7 +51348,7 @@
         <v>0.7054851864099394</v>
       </c>
       <c r="D992" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E992">
         <v>1.215285677395871</v>
@@ -51398,7 +51401,7 @@
         <v>349</v>
       </c>
       <c r="E993">
-        <v>0.8464619936926976</v>
+        <v>0.7178378190035932</v>
       </c>
       <c r="F993">
         <v>1</v>
@@ -51407,10 +51410,10 @@
         <v>0.01508763568703558</v>
       </c>
       <c r="H993">
-        <v>0.0149535380063073</v>
+        <v>0.01434216218099641</v>
       </c>
       <c r="I993">
-        <v>0.134097680728277</v>
+        <v>0.005473506039172626</v>
       </c>
       <c r="J993">
         <v>1.340976807282757</v>
@@ -51422,10 +51425,10 @@
         <v>7.9</v>
       </c>
       <c r="M993">
-        <v>5.26</v>
+        <v>5.08</v>
       </c>
       <c r="N993">
-        <v>7.9</v>
+        <v>7.53</v>
       </c>
       <c r="O993">
         <v>1</v>
@@ -51481,7 +51484,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>194</v>
+        <v>462</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51495,7 +51498,7 @@
         <v>0.730902359952653</v>
       </c>
       <c r="D995" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E995">
         <v>1.239038147879077</v>
@@ -51531,7 +51534,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>194</v>
+        <v>462</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51548,7 +51551,7 @@
         <v>349</v>
       </c>
       <c r="E996">
-        <v>0.8678189158707594</v>
+        <v>0.7384638959360181</v>
       </c>
       <c r="F996">
         <v>1</v>
@@ -51557,10 +51560,10 @@
         <v>0.01506587273972105</v>
       </c>
       <c r="H996">
-        <v>0.01493218108412924</v>
+        <v>0.01432153610406398</v>
       </c>
       <c r="I996">
-        <v>0.1336916555918108</v>
+        <v>0.004336635657069543</v>
       </c>
       <c r="J996">
         <v>1.336916555918107</v>
@@ -51572,16 +51575,16 @@
         <v>7.9</v>
       </c>
       <c r="M996">
-        <v>5.26</v>
+        <v>5.08</v>
       </c>
       <c r="N996">
-        <v>7.9</v>
+        <v>7.53</v>
       </c>
       <c r="O996">
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>194</v>
+        <v>462</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51631,7 +51634,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51645,7 +51648,7 @@
         <v>0.7031067530561543</v>
       </c>
       <c r="D998" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E998">
         <v>1.213063020028516</v>
@@ -51681,7 +51684,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51698,7 +51701,7 @@
         <v>349</v>
       </c>
       <c r="E999">
-        <v>0.844463501769229</v>
+        <v>0.7159077165375818</v>
       </c>
       <c r="F999">
         <v>1</v>
@@ -51707,10 +51710,10 @@
         <v>0.01508967217310208</v>
       </c>
       <c r="H999">
-        <v>0.01495553649823077</v>
+        <v>0.01434409228346242</v>
       </c>
       <c r="I999">
-        <v>0.1341356748713078</v>
+        <v>0.005579889639660607</v>
       </c>
       <c r="J999">
         <v>1.341356748713074</v>
@@ -51722,16 +51725,16 @@
         <v>7.9</v>
       </c>
       <c r="M999">
-        <v>5.26</v>
+        <v>5.08</v>
       </c>
       <c r="N999">
-        <v>7.9</v>
+        <v>7.53</v>
       </c>
       <c r="O999">
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51739,10 +51742,10 @@
         <v>0</v>
       </c>
       <c r="B1000" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1000">
-        <v>1.449405185698751</v>
+        <v>1.239490555786455</v>
       </c>
       <c r="D1000" t="s">
         <v>348</v>
@@ -51754,22 +51757,22 @@
         <v>-1</v>
       </c>
       <c r="G1000">
-        <v>0.01749059481430125</v>
+        <v>0.01814050944421354</v>
       </c>
       <c r="H1000">
         <v>0.0164828116602689</v>
       </c>
       <c r="I1000">
-        <v>0.7122168459676512</v>
+        <v>0.5023022160553552</v>
       </c>
       <c r="J1000">
         <v>1.343483218475921</v>
       </c>
       <c r="K1000">
-        <v>5.97</v>
+        <v>6.29</v>
       </c>
       <c r="L1000">
-        <v>9.470000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="M1000">
         <v>5.86</v>
@@ -51781,7 +51784,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51789,49 +51792,49 @@
         <v>1</v>
       </c>
       <c r="B1001" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C1001">
-        <v>0.6897950523407328</v>
+        <v>1.449405185698751</v>
       </c>
       <c r="D1001" t="s">
-        <v>195</v>
+        <v>348</v>
       </c>
       <c r="E1001">
-        <v>1.200623171915861</v>
+        <v>0.7371883397310999</v>
       </c>
       <c r="F1001">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1001">
-        <v>0.01751020494765927</v>
+        <v>0.01749059481430125</v>
       </c>
       <c r="H1001">
-        <v>0.01691937682808414</v>
+        <v>0.0164828116602689</v>
       </c>
       <c r="I1001">
-        <v>0.5108281195751285</v>
+        <v>0.7122168459676512</v>
       </c>
       <c r="J1001">
         <v>1.343483218475921</v>
       </c>
       <c r="K1001">
-        <v>6.26</v>
+        <v>5.97</v>
       </c>
       <c r="L1001">
-        <v>9.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1001">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N1001">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1001">
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -51839,143 +51842,143 @@
         <v>2</v>
       </c>
       <c r="B1002" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C1002">
-        <v>0.6989299489690612</v>
+        <v>0.6897950523407328</v>
       </c>
       <c r="D1002" t="s">
-        <v>349</v>
+        <v>196</v>
       </c>
       <c r="E1002">
-        <v>0.8332782708166544</v>
+        <v>1.200623171915861</v>
       </c>
       <c r="F1002">
         <v>1</v>
       </c>
       <c r="G1002">
-        <v>0.01510107005103094</v>
+        <v>0.01751020494765927</v>
       </c>
       <c r="H1002">
-        <v>0.01496672172918335</v>
+        <v>0.01691937682808414</v>
       </c>
       <c r="I1002">
-        <v>0.1343483218475932</v>
+        <v>0.5108281195751285</v>
       </c>
       <c r="J1002">
         <v>1.343483218475921</v>
       </c>
       <c r="K1002">
-        <v>5.36</v>
+        <v>6.26</v>
       </c>
       <c r="L1002">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
       <c r="M1002">
-        <v>5.26</v>
+        <v>5.85</v>
       </c>
       <c r="N1002">
-        <v>7.9</v>
+        <v>9.06</v>
       </c>
       <c r="O1002">
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
       <c r="A1003" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1003" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C1003">
-        <v>1.446464800345405</v>
+        <v>0.6989299489690612</v>
       </c>
       <c r="D1003" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1003">
-        <v>0.7343021323323375</v>
+        <v>0.7051052501423198</v>
       </c>
       <c r="F1003">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1003">
-        <v>0.0174935351996546</v>
+        <v>0.01510107005103094</v>
       </c>
       <c r="H1003">
-        <v>0.01648569786766766</v>
+        <v>0.01435489474985768</v>
       </c>
       <c r="I1003">
-        <v>0.7121626680130673</v>
+        <v>0.006175301173258596</v>
       </c>
       <c r="J1003">
-        <v>1.343975745335778</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K1003">
-        <v>5.97</v>
+        <v>5.36</v>
       </c>
       <c r="L1003">
-        <v>9.470000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="M1003">
-        <v>5.86</v>
+        <v>5.08</v>
       </c>
       <c r="N1003">
-        <v>8.609999999999999</v>
+        <v>7.53</v>
       </c>
       <c r="O1003">
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>347</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
       <c r="A1004" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1004" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C1004">
-        <v>0.6867118341980269</v>
+        <v>1.236392561837954</v>
       </c>
       <c r="D1004" t="s">
-        <v>195</v>
+        <v>348</v>
       </c>
       <c r="E1004">
-        <v>1.197741889785697</v>
+        <v>0.7343021323323375</v>
       </c>
       <c r="F1004">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1004">
-        <v>0.01751328816580197</v>
+        <v>0.01814360743816204</v>
       </c>
       <c r="H1004">
-        <v>0.01692225811021431</v>
+        <v>0.01648569786766766</v>
       </c>
       <c r="I1004">
-        <v>0.5110300555876703</v>
+        <v>0.5020904295056168</v>
       </c>
       <c r="J1004">
         <v>1.343975745335778</v>
       </c>
       <c r="K1004">
-        <v>6.26</v>
+        <v>6.29</v>
       </c>
       <c r="L1004">
-        <v>9.1</v>
+        <v>9.69</v>
       </c>
       <c r="M1004">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N1004">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1004">
         <v>1</v>
@@ -51986,46 +51989,46 @@
     </row>
     <row r="1005" spans="1:16">
       <c r="A1005" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1005" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C1005">
-        <v>0.6962900050002281</v>
+        <v>1.446464800345405</v>
       </c>
       <c r="D1005" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1005">
-        <v>0.8306875795338069</v>
+        <v>0.7343021323323375</v>
       </c>
       <c r="F1005">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1005">
-        <v>0.01510370999499977</v>
+        <v>0.0174935351996546</v>
       </c>
       <c r="H1005">
-        <v>0.01496931242046619</v>
+        <v>0.01648569786766766</v>
       </c>
       <c r="I1005">
-        <v>0.1343975745335788</v>
+        <v>0.7121626680130673</v>
       </c>
       <c r="J1005">
         <v>1.343975745335778</v>
       </c>
       <c r="K1005">
-        <v>5.36</v>
+        <v>5.97</v>
       </c>
       <c r="L1005">
-        <v>7.9</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1005">
-        <v>5.26</v>
+        <v>5.86</v>
       </c>
       <c r="N1005">
-        <v>7.9</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1005">
         <v>1</v>
@@ -52036,296 +52039,296 @@
     </row>
     <row r="1006" spans="1:16">
       <c r="A1006" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1006" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C1006">
-        <v>1.460084502779063</v>
+        <v>0.6867118341980269</v>
       </c>
       <c r="D1006" t="s">
-        <v>348</v>
+        <v>196</v>
       </c>
       <c r="E1006">
-        <v>0.7476708854749239</v>
+        <v>1.197741889785697</v>
       </c>
       <c r="F1006">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1006">
-        <v>0.01747991549722094</v>
+        <v>0.01751328816580197</v>
       </c>
       <c r="H1006">
-        <v>0.01647232911452507</v>
+        <v>0.01692225811021431</v>
       </c>
       <c r="I1006">
-        <v>0.7124136173041391</v>
+        <v>0.5110300555876703</v>
       </c>
       <c r="J1006">
-        <v>1.341694388144211</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K1006">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="L1006">
-        <v>9.470000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M1006">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N1006">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O1006">
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>464</v>
+        <v>347</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
       <c r="A1007" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1007" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C1007">
-        <v>0.7009931302172401</v>
+        <v>0.6962900050002281</v>
       </c>
       <c r="D1007" t="s">
-        <v>195</v>
+        <v>349</v>
       </c>
       <c r="E1007">
-        <v>1.211087829356368</v>
+        <v>0.7026032136942462</v>
       </c>
       <c r="F1007">
         <v>1</v>
       </c>
       <c r="G1007">
-        <v>0.01749900686978276</v>
+        <v>0.01510370999499977</v>
       </c>
       <c r="H1007">
-        <v>0.01690891217064363</v>
+        <v>0.01435739678630575</v>
       </c>
       <c r="I1007">
-        <v>0.5100946991391284</v>
+        <v>0.00631320869401808</v>
       </c>
       <c r="J1007">
-        <v>1.341694388144211</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K1007">
-        <v>6.26</v>
+        <v>5.36</v>
       </c>
       <c r="L1007">
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="M1007">
-        <v>5.85</v>
+        <v>5.08</v>
       </c>
       <c r="N1007">
-        <v>9.06</v>
+        <v>7.53</v>
       </c>
       <c r="O1007">
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>464</v>
+        <v>347</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
       <c r="A1008" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1008" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C1008">
-        <v>0.7085180795470301</v>
+        <v>1.460084502779063</v>
       </c>
       <c r="D1008" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1008">
-        <v>0.8426875183614522</v>
+        <v>0.7476708854749239</v>
       </c>
       <c r="F1008">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1008">
-        <v>0.01509148192045297</v>
+        <v>0.01747991549722094</v>
       </c>
       <c r="H1008">
-        <v>0.01495731248163855</v>
+        <v>0.01647232911452507</v>
       </c>
       <c r="I1008">
-        <v>0.1341694388144221</v>
+        <v>0.7124136173041391</v>
       </c>
       <c r="J1008">
         <v>1.341694388144211</v>
       </c>
       <c r="K1008">
-        <v>5.36</v>
+        <v>5.97</v>
       </c>
       <c r="L1008">
-        <v>7.9</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1008">
-        <v>5.26</v>
+        <v>5.86</v>
       </c>
       <c r="N1008">
-        <v>7.9</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1008">
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>464</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
       <c r="A1009" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1009" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C1009">
-        <v>1.453089006184717</v>
+        <v>0.7009931302172401</v>
       </c>
       <c r="D1009" t="s">
-        <v>348</v>
+        <v>196</v>
       </c>
       <c r="E1009">
-        <v>0.7408042841277105</v>
+        <v>1.211087829356368</v>
       </c>
       <c r="F1009">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1009">
-        <v>0.01748691099381528</v>
+        <v>0.01749900686978276</v>
       </c>
       <c r="H1009">
-        <v>0.01647919571587229</v>
+        <v>0.01690891217064363</v>
       </c>
       <c r="I1009">
-        <v>0.7122847220570065</v>
+        <v>0.5100946991391284</v>
       </c>
       <c r="J1009">
-        <v>1.342866163118138</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1009">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="L1009">
-        <v>9.470000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M1009">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N1009">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O1009">
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>465</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
       <c r="A1010" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1010" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C1010">
-        <v>0.6936578188804567</v>
+        <v>0.7085180795470301</v>
       </c>
       <c r="D1010" t="s">
-        <v>195</v>
+        <v>349</v>
       </c>
       <c r="E1010">
-        <v>1.204232945758894</v>
+        <v>0.7141925082274101</v>
       </c>
       <c r="F1010">
         <v>1</v>
       </c>
       <c r="G1010">
-        <v>0.01750634218111954</v>
+        <v>0.01509148192045297</v>
       </c>
       <c r="H1010">
-        <v>0.01691576705424111</v>
+        <v>0.01434580749177259</v>
       </c>
       <c r="I1010">
-        <v>0.5105751268784369</v>
+        <v>0.005674428680380039</v>
       </c>
       <c r="J1010">
-        <v>1.342866163118138</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1010">
-        <v>6.26</v>
+        <v>5.36</v>
       </c>
       <c r="L1010">
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="M1010">
-        <v>5.85</v>
+        <v>5.08</v>
       </c>
       <c r="N1010">
-        <v>9.06</v>
+        <v>7.53</v>
       </c>
       <c r="O1010">
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>465</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
       <c r="A1011" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1011" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C1011">
-        <v>0.7022373656867806</v>
+        <v>1.453089006184717</v>
       </c>
       <c r="D1011" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1011">
-        <v>0.836523981998595</v>
+        <v>0.7408042841277105</v>
       </c>
       <c r="F1011">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1011">
-        <v>0.01509776263431322</v>
+        <v>0.01748691099381528</v>
       </c>
       <c r="H1011">
-        <v>0.01496347601800141</v>
+        <v>0.01647919571587229</v>
       </c>
       <c r="I1011">
-        <v>0.1342866163118144</v>
+        <v>0.7122847220570065</v>
       </c>
       <c r="J1011">
         <v>1.342866163118138</v>
       </c>
       <c r="K1011">
-        <v>5.36</v>
+        <v>5.97</v>
       </c>
       <c r="L1011">
-        <v>7.9</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1011">
-        <v>5.26</v>
+        <v>5.86</v>
       </c>
       <c r="N1011">
-        <v>7.9</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1011">
         <v>1</v>
@@ -52336,34 +52339,34 @@
     </row>
     <row r="1012" spans="1:16">
       <c r="A1012" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1012" t="s">
         <v>192</v>
       </c>
       <c r="C1012">
-        <v>0.6837427575297426</v>
+        <v>0.6936578188804567</v>
       </c>
       <c r="D1012" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E1012">
-        <v>1.194967273410384</v>
+        <v>1.204232945758894</v>
       </c>
       <c r="F1012">
         <v>1</v>
       </c>
       <c r="G1012">
-        <v>0.01751625724247026</v>
+        <v>0.01750634218111954</v>
       </c>
       <c r="H1012">
-        <v>0.01692503272658962</v>
+        <v>0.01691576705424111</v>
       </c>
       <c r="I1012">
-        <v>0.5112245158806417</v>
+        <v>0.5105751268784369</v>
       </c>
       <c r="J1012">
-        <v>1.344450038733268</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K1012">
         <v>6.26</v>
@@ -52381,7 +52384,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>191</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52392,46 +52395,46 @@
         <v>195</v>
       </c>
       <c r="C1013">
-        <v>1.156353759647005</v>
+        <v>0.5438572811570364</v>
       </c>
       <c r="D1013" t="s">
-        <v>350</v>
+        <v>196</v>
       </c>
       <c r="E1013">
-        <v>0.705710977035042</v>
+        <v>1.194967273410384</v>
       </c>
       <c r="F1013">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1013">
-        <v>0.016963646240353</v>
+        <v>0.01573614271884297</v>
       </c>
       <c r="H1013">
-        <v>0.01559428902296496</v>
+        <v>0.01692503272658962</v>
       </c>
       <c r="I1013">
-        <v>0.450642782611963</v>
+        <v>0.6511099922533479</v>
       </c>
       <c r="J1013">
-        <v>1.35105063937658</v>
+        <v>1.344450038733268</v>
       </c>
       <c r="K1013">
+        <v>5.65</v>
+      </c>
+      <c r="L1013">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M1013">
         <v>5.85</v>
       </c>
-      <c r="L1013">
+      <c r="N1013">
         <v>9.06</v>
       </c>
-      <c r="M1013">
-        <v>5.51</v>
-      </c>
-      <c r="N1013">
-        <v>8.15</v>
-      </c>
       <c r="O1013">
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>466</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52439,31 +52442,31 @@
         <v>0</v>
       </c>
       <c r="B1014" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C1014">
-        <v>0.5021328345691742</v>
+        <v>0.5168028977995238</v>
       </c>
       <c r="D1014" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1014">
-        <v>0.8395456676775179</v>
+        <v>0.8550466017456912</v>
       </c>
       <c r="F1014">
         <v>1</v>
       </c>
       <c r="G1014">
-        <v>0.01577786716543083</v>
+        <v>0.01576319710220048</v>
       </c>
       <c r="H1014">
-        <v>0.01698045433232248</v>
+        <v>0.01696495339825431</v>
       </c>
       <c r="I1014">
-        <v>0.3374128331083437</v>
+        <v>0.3382437039461674</v>
       </c>
       <c r="J1014">
-        <v>1.351834896536429</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1014">
         <v>5.65</v>
@@ -52481,7 +52484,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52489,31 +52492,31 @@
         <v>1</v>
       </c>
       <c r="B1015" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1015">
-        <v>1.15176585526189</v>
+        <v>1.166955212765879</v>
       </c>
       <c r="D1015" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1015">
-        <v>0.7013897200842756</v>
+        <v>0.7156962773230759</v>
       </c>
       <c r="F1015">
         <v>-1</v>
       </c>
       <c r="G1015">
-        <v>0.01696823414473811</v>
+        <v>0.01695304478723412</v>
       </c>
       <c r="H1015">
-        <v>0.01559861027991572</v>
+        <v>0.01558430372267692</v>
       </c>
       <c r="I1015">
-        <v>0.4503761351776143</v>
+        <v>0.4512589354428034</v>
       </c>
       <c r="J1015">
-        <v>1.351834896536429</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1015">
         <v>5.85</v>
@@ -52531,7 +52534,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52539,31 +52542,31 @@
         <v>0</v>
       </c>
       <c r="B1016" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C1016">
-        <v>0.5002997890366885</v>
+        <v>0.5065638875223204</v>
       </c>
       <c r="D1016" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1016">
-        <v>0.8376088036369964</v>
+        <v>0.8442276829218152</v>
       </c>
       <c r="F1016">
         <v>1</v>
       </c>
       <c r="G1016">
-        <v>0.01577970021096331</v>
+        <v>0.01577343611247768</v>
       </c>
       <c r="H1016">
-        <v>0.01698239119636301</v>
+        <v>0.01697577231707819</v>
       </c>
       <c r="I1016">
-        <v>0.3373090146003079</v>
+        <v>0.3376637953994948</v>
       </c>
       <c r="J1016">
-        <v>1.352159329374037</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1016">
         <v>5.65</v>
@@ -52581,7 +52584,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -52589,31 +52592,31 @@
         <v>1</v>
       </c>
       <c r="B1017" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1017">
-        <v>1.149867923161882</v>
+        <v>1.156353759647005</v>
       </c>
       <c r="D1017" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1017">
-        <v>0.6996020951490545</v>
+        <v>0.705710977035042</v>
       </c>
       <c r="F1017">
         <v>-1</v>
       </c>
       <c r="G1017">
-        <v>0.01697013207683812</v>
+        <v>0.016963646240353</v>
       </c>
       <c r="H1017">
-        <v>0.01560039790485095</v>
+        <v>0.01559428902296496</v>
       </c>
       <c r="I1017">
-        <v>0.4502658280128271</v>
+        <v>0.450642782611963</v>
       </c>
       <c r="J1017">
-        <v>1.352159329374037</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1017">
         <v>5.85</v>
@@ -52631,7 +52634,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52639,31 +52642,31 @@
         <v>0</v>
       </c>
       <c r="B1018" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C1018">
-        <v>0.4969577705448094</v>
+        <v>0.5021328345691742</v>
       </c>
       <c r="D1018" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1018">
-        <v>0.8340775026818612</v>
+        <v>0.8395456676775179</v>
       </c>
       <c r="F1018">
         <v>1</v>
       </c>
       <c r="G1018">
-        <v>0.01578304222945519</v>
+        <v>0.01577786716543083</v>
       </c>
       <c r="H1018">
-        <v>0.01698592249731814</v>
+        <v>0.01698045433232248</v>
       </c>
       <c r="I1018">
-        <v>0.3371197321370518</v>
+        <v>0.3374128331083437</v>
       </c>
       <c r="J1018">
-        <v>1.352750837071715</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1018">
         <v>5.65</v>
@@ -52681,7 +52684,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52689,31 +52692,31 @@
         <v>1</v>
       </c>
       <c r="B1019" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1019">
-        <v>1.146407603130467</v>
+        <v>1.15176585526189</v>
       </c>
       <c r="D1019" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1019">
-        <v>0.6963428877348496</v>
+        <v>0.7013897200842756</v>
       </c>
       <c r="F1019">
         <v>-1</v>
       </c>
       <c r="G1019">
-        <v>0.01697359239686954</v>
+        <v>0.01696823414473811</v>
       </c>
       <c r="H1019">
-        <v>0.01560365711226515</v>
+        <v>0.01559861027991572</v>
       </c>
       <c r="I1019">
-        <v>0.4500647153956177</v>
+        <v>0.4503761351776143</v>
       </c>
       <c r="J1019">
-        <v>1.352750837071715</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1019">
         <v>5.85</v>
@@ -52731,7 +52734,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52739,31 +52742,31 @@
         <v>0</v>
       </c>
       <c r="B1020" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C1020">
-        <v>0.4920648074520191</v>
+        <v>0.5002997890366885</v>
       </c>
       <c r="D1020" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1020">
-        <v>0.8289074160156744</v>
+        <v>0.8376088036369964</v>
       </c>
       <c r="F1020">
         <v>1</v>
       </c>
       <c r="G1020">
-        <v>0.01578793519254798</v>
+        <v>0.01577970021096331</v>
       </c>
       <c r="H1020">
-        <v>0.01699109258398433</v>
+        <v>0.01698239119636301</v>
       </c>
       <c r="I1020">
-        <v>0.3368426085636553</v>
+        <v>0.3373090146003079</v>
       </c>
       <c r="J1020">
-        <v>1.353616848238581</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1020">
         <v>5.65</v>
@@ -52781,7 +52784,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>348</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52789,31 +52792,31 @@
         <v>1</v>
       </c>
       <c r="B1021" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1021">
-        <v>1.141341437804305</v>
+        <v>1.149867923161882</v>
       </c>
       <c r="D1021" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1021">
-        <v>0.6915711662054216</v>
+        <v>0.6996020951490545</v>
       </c>
       <c r="F1021">
         <v>-1</v>
       </c>
       <c r="G1021">
-        <v>0.0169786585621957</v>
+        <v>0.01697013207683812</v>
       </c>
       <c r="H1021">
-        <v>0.01560842883379458</v>
+        <v>0.01560039790485095</v>
       </c>
       <c r="I1021">
-        <v>0.4497702715988829</v>
+        <v>0.4502658280128271</v>
       </c>
       <c r="J1021">
-        <v>1.353616848238581</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1021">
         <v>5.85</v>
@@ -52831,7 +52834,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>348</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52839,31 +52842,31 @@
         <v>0</v>
       </c>
       <c r="B1022" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C1022">
-        <v>0.5046197380717317</v>
+        <v>0.4969577705448094</v>
       </c>
       <c r="D1022" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1022">
-        <v>0.8421734223519017</v>
+        <v>0.8340775026818612</v>
       </c>
       <c r="F1022">
         <v>1</v>
       </c>
       <c r="G1022">
-        <v>0.01577538026192827</v>
+        <v>0.01578304222945519</v>
       </c>
       <c r="H1022">
-        <v>0.0169778265776481</v>
+        <v>0.01698592249731814</v>
       </c>
       <c r="I1022">
-        <v>0.3375536842801701</v>
+        <v>0.3371197321370518</v>
       </c>
       <c r="J1022">
-        <v>1.351394736624472</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1022">
         <v>5.65</v>
@@ -52889,31 +52892,31 @@
         <v>1</v>
       </c>
       <c r="B1023" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1023">
-        <v>1.154340790746838</v>
+        <v>1.146407603130467</v>
       </c>
       <c r="D1023" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1023">
-        <v>0.7038150011991586</v>
+        <v>0.6963428877348496</v>
       </c>
       <c r="F1023">
         <v>-1</v>
       </c>
       <c r="G1023">
-        <v>0.01696565920925316</v>
+        <v>0.01697359239686954</v>
       </c>
       <c r="H1023">
-        <v>0.01559618499880084</v>
+        <v>0.01560365711226515</v>
       </c>
       <c r="I1023">
-        <v>0.4505257895476795</v>
+        <v>0.4500647153956177</v>
       </c>
       <c r="J1023">
-        <v>1.351394736624472</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1023">
         <v>5.85</v>
@@ -52939,31 +52942,31 @@
         <v>0</v>
       </c>
       <c r="B1024" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C1024">
-        <v>0.5044756313746497</v>
+        <v>0.4920648074520191</v>
       </c>
       <c r="D1024" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1024">
-        <v>0.8420211538595854</v>
+        <v>0.8289074160156744</v>
       </c>
       <c r="F1024">
         <v>1</v>
       </c>
       <c r="G1024">
-        <v>0.01577552436862535</v>
+        <v>0.01578793519254798</v>
       </c>
       <c r="H1024">
-        <v>0.01697797884614042</v>
+        <v>0.01699109258398433</v>
       </c>
       <c r="I1024">
-        <v>0.3375455224849357</v>
+        <v>0.3368426085636553</v>
       </c>
       <c r="J1024">
-        <v>1.351420242234575</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1024">
         <v>5.65</v>
@@ -52981,7 +52984,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>192</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -52989,31 +52992,31 @@
         <v>1</v>
       </c>
       <c r="B1025" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1025">
-        <v>1.154191582927735</v>
+        <v>1.141341437804305</v>
       </c>
       <c r="D1025" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1025">
-        <v>0.7036744652874907</v>
+        <v>0.6915711662054216</v>
       </c>
       <c r="F1025">
         <v>-1</v>
       </c>
       <c r="G1025">
-        <v>0.01696580841707227</v>
+        <v>0.0169786585621957</v>
       </c>
       <c r="H1025">
-        <v>0.01559632553471251</v>
+        <v>0.01560842883379458</v>
       </c>
       <c r="I1025">
-        <v>0.4505171176402447</v>
+        <v>0.4497702715988829</v>
       </c>
       <c r="J1025">
-        <v>1.351420242234575</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1025">
         <v>5.85</v>
@@ -53031,6 +53034,206 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:16">
+      <c r="A1026" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1026">
+        <v>0.5046197380717317</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>350</v>
+      </c>
+      <c r="E1026">
+        <v>0.8421734223519017</v>
+      </c>
+      <c r="F1026">
+        <v>1</v>
+      </c>
+      <c r="G1026">
+        <v>0.01577538026192827</v>
+      </c>
+      <c r="H1026">
+        <v>0.0169778265776481</v>
+      </c>
+      <c r="I1026">
+        <v>0.3375536842801701</v>
+      </c>
+      <c r="J1026">
+        <v>1.351394736624472</v>
+      </c>
+      <c r="K1026">
+        <v>5.65</v>
+      </c>
+      <c r="L1026">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M1026">
+        <v>5.97</v>
+      </c>
+      <c r="N1026">
+        <v>8.91</v>
+      </c>
+      <c r="O1026">
+        <v>1</v>
+      </c>
+      <c r="P1026" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:16">
+      <c r="A1027" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1027">
+        <v>1.154340790746838</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>351</v>
+      </c>
+      <c r="E1027">
+        <v>0.7038150011991586</v>
+      </c>
+      <c r="F1027">
+        <v>-1</v>
+      </c>
+      <c r="G1027">
+        <v>0.01696565920925316</v>
+      </c>
+      <c r="H1027">
+        <v>0.01559618499880084</v>
+      </c>
+      <c r="I1027">
+        <v>0.4505257895476795</v>
+      </c>
+      <c r="J1027">
+        <v>1.351394736624472</v>
+      </c>
+      <c r="K1027">
+        <v>5.85</v>
+      </c>
+      <c r="L1027">
+        <v>9.06</v>
+      </c>
+      <c r="M1027">
+        <v>5.51</v>
+      </c>
+      <c r="N1027">
+        <v>8.15</v>
+      </c>
+      <c r="O1027">
+        <v>1</v>
+      </c>
+      <c r="P1027" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:16">
+      <c r="A1028" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1028">
+        <v>0.5044756313746497</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>350</v>
+      </c>
+      <c r="E1028">
+        <v>0.8420211538595854</v>
+      </c>
+      <c r="F1028">
+        <v>1</v>
+      </c>
+      <c r="G1028">
+        <v>0.01577552436862535</v>
+      </c>
+      <c r="H1028">
+        <v>0.01697797884614042</v>
+      </c>
+      <c r="I1028">
+        <v>0.3375455224849357</v>
+      </c>
+      <c r="J1028">
+        <v>1.351420242234575</v>
+      </c>
+      <c r="K1028">
+        <v>5.65</v>
+      </c>
+      <c r="L1028">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M1028">
+        <v>5.97</v>
+      </c>
+      <c r="N1028">
+        <v>8.91</v>
+      </c>
+      <c r="O1028">
+        <v>1</v>
+      </c>
+      <c r="P1028" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:16">
+      <c r="A1029" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1029">
+        <v>1.154191582927735</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>351</v>
+      </c>
+      <c r="E1029">
+        <v>0.7036744652874907</v>
+      </c>
+      <c r="F1029">
+        <v>-1</v>
+      </c>
+      <c r="G1029">
+        <v>0.01696580841707227</v>
+      </c>
+      <c r="H1029">
+        <v>0.01559632553471251</v>
+      </c>
+      <c r="I1029">
+        <v>0.4505171176402447</v>
+      </c>
+      <c r="J1029">
+        <v>1.351420242234575</v>
+      </c>
+      <c r="K1029">
+        <v>5.85</v>
+      </c>
+      <c r="L1029">
+        <v>9.06</v>
+      </c>
+      <c r="M1029">
+        <v>5.51</v>
+      </c>
+      <c r="N1029">
+        <v>8.15</v>
+      </c>
+      <c r="O1029">
+        <v>1</v>
+      </c>
+      <c r="P1029" t="s">
         <v>192</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3159" uniqueCount="477">
   <si>
     <t>trade_time</t>
   </si>
@@ -604,10 +604,10 @@
     <t>2021-10-27</t>
   </si>
   <si>
-    <t>2021-10-29</t>
+    <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-10-15</t>
+    <t>2021-10-29</t>
   </si>
   <si>
     <t>2021-10-19</t>
@@ -1072,7 +1072,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-11-01</t>
+    <t>2021-11-02</t>
   </si>
   <si>
     <t>2021-10-18</t>
@@ -1802,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1052"/>
+  <dimension ref="A1:P1049"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51213,7 +51213,7 @@
         <v>0.7692553919018295</v>
       </c>
       <c r="D989" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E989">
         <v>0.6740803279131855</v>
@@ -51263,7 +51263,7 @@
         <v>0.7717569759069578</v>
       </c>
       <c r="D990" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E990">
         <v>0.6740803279131855</v>
@@ -51507,10 +51507,10 @@
         <v>4</v>
       </c>
       <c r="B995" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C995">
-        <v>0.7054851864099394</v>
+        <v>0.5634810388524212</v>
       </c>
       <c r="D995" t="s">
         <v>198</v>
@@ -51522,22 +51522,22 @@
         <v>1</v>
       </c>
       <c r="G995">
-        <v>0.01749451481359006</v>
+        <v>0.01571651896114758</v>
       </c>
       <c r="H995">
         <v>0.01690471432260413</v>
       </c>
       <c r="I995">
-        <v>0.5098004909859313</v>
+        <v>0.6518046385434495</v>
       </c>
       <c r="J995">
         <v>1.340976807282757</v>
       </c>
       <c r="K995">
-        <v>6.26</v>
+        <v>5.65</v>
       </c>
       <c r="L995">
-        <v>9.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M995">
         <v>5.85</v>
@@ -51557,7 +51557,7 @@
         <v>5</v>
       </c>
       <c r="B996" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C996">
         <v>0.6237699334797311</v>
@@ -51566,7 +51566,7 @@
         <v>352</v>
       </c>
       <c r="E996">
-        <v>0.7233113250427659</v>
+        <v>0.6880969184264885</v>
       </c>
       <c r="F996">
         <v>1</v>
@@ -51575,10 +51575,10 @@
         <v>0.01333623006652027</v>
       </c>
       <c r="H996">
-        <v>0.01359668867495724</v>
+        <v>0.01305190308157351</v>
       </c>
       <c r="I996">
-        <v>0.09954139156303476</v>
+        <v>0.06432698494675737</v>
       </c>
       <c r="J996">
         <v>1.340976807282757</v>
@@ -51590,10 +51590,10 @@
         <v>6.98</v>
       </c>
       <c r="M996">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="N996">
-        <v>7.16</v>
+        <v>6.87</v>
       </c>
       <c r="O996">
         <v>1</v>
@@ -51707,10 +51707,10 @@
         <v>2</v>
       </c>
       <c r="B999" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C999">
-        <v>0.730902359952653</v>
+        <v>0.5864214590626977</v>
       </c>
       <c r="D999" t="s">
         <v>198</v>
@@ -51722,22 +51722,22 @@
         <v>1</v>
       </c>
       <c r="G999">
-        <v>0.01746909764004734</v>
+        <v>0.0156935785409373</v>
       </c>
       <c r="H999">
         <v>0.01688096185212093</v>
       </c>
       <c r="I999">
-        <v>0.5081357879264239</v>
+        <v>0.6526166888163791</v>
       </c>
       <c r="J999">
         <v>1.336916555918107</v>
       </c>
       <c r="K999">
-        <v>6.26</v>
+        <v>5.65</v>
       </c>
       <c r="L999">
-        <v>9.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M999">
         <v>5.85</v>
@@ -51757,43 +51757,43 @@
         <v>3</v>
       </c>
       <c r="B1000" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C1000">
-        <v>0.7341272602789486</v>
+        <v>0.6430155249481748</v>
       </c>
       <c r="D1000" t="s">
         <v>352</v>
       </c>
       <c r="E1000">
-        <v>0.7428005315930886</v>
+        <v>0.7068146772175279</v>
       </c>
       <c r="F1000">
         <v>1</v>
       </c>
       <c r="G1000">
-        <v>0.01506587273972105</v>
+        <v>0.01331698447505182</v>
       </c>
       <c r="H1000">
-        <v>0.01357719946840691</v>
+        <v>0.01303318532278247</v>
       </c>
       <c r="I1000">
-        <v>0.008673271314139974</v>
+        <v>0.06379915226935307</v>
       </c>
       <c r="J1000">
         <v>1.336916555918107</v>
       </c>
       <c r="K1000">
-        <v>5.36</v>
+        <v>4.74</v>
       </c>
       <c r="L1000">
-        <v>7.9</v>
+        <v>6.98</v>
       </c>
       <c r="M1000">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="N1000">
-        <v>7.16</v>
+        <v>6.87</v>
       </c>
       <c r="O1000">
         <v>1</v>
@@ -51804,146 +51804,146 @@
     </row>
     <row r="1001" spans="1:16">
       <c r="A1001" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1001" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C1001">
-        <v>0.7384638959360181</v>
+        <v>1.252866050594761</v>
       </c>
       <c r="D1001" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E1001">
-        <v>0.7428005315930886</v>
+        <v>0.7496494525413828</v>
       </c>
       <c r="F1001">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1001">
-        <v>0.01432153610406398</v>
+        <v>0.01812713394940524</v>
       </c>
       <c r="H1001">
-        <v>0.01357719946840691</v>
+        <v>0.01647035054745861</v>
       </c>
       <c r="I1001">
-        <v>0.004336635657070431</v>
+        <v>0.5032165980533785</v>
       </c>
       <c r="J1001">
-        <v>1.336916555918107</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K1001">
-        <v>5.08</v>
+        <v>6.29</v>
       </c>
       <c r="L1001">
-        <v>7.53</v>
+        <v>9.69</v>
       </c>
       <c r="M1001">
-        <v>4.8</v>
+        <v>5.86</v>
       </c>
       <c r="N1001">
-        <v>7.16</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1001">
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
       <c r="A1002" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1002" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C1002">
-        <v>0.6430155249481748</v>
+        <v>1.462100210182946</v>
       </c>
       <c r="D1002" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E1002">
-        <v>0.7428005315930886</v>
+        <v>0.7496494525413828</v>
       </c>
       <c r="F1002">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1002">
-        <v>0.01331698447505182</v>
+        <v>0.01747789978981706</v>
       </c>
       <c r="H1002">
-        <v>0.01357719946840691</v>
+        <v>0.01647035054745861</v>
       </c>
       <c r="I1002">
-        <v>0.09978500664491374</v>
+        <v>0.7124507576415633</v>
       </c>
       <c r="J1002">
-        <v>1.336916555918107</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K1002">
-        <v>4.74</v>
+        <v>5.97</v>
       </c>
       <c r="L1002">
-        <v>6.98</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1002">
-        <v>4.8</v>
+        <v>5.86</v>
       </c>
       <c r="N1002">
-        <v>7.16</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1002">
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
       <c r="A1003" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1003" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C1003">
-        <v>1.252866050594761</v>
+        <v>0.5613343697711297</v>
       </c>
       <c r="D1003" t="s">
-        <v>351</v>
+        <v>198</v>
       </c>
       <c r="E1003">
-        <v>0.7496494525413828</v>
+        <v>1.213063020028516</v>
       </c>
       <c r="F1003">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1003">
-        <v>0.01812713394940524</v>
+        <v>0.01571866563022887</v>
       </c>
       <c r="H1003">
-        <v>0.01647035054745861</v>
+        <v>0.01690693697997148</v>
       </c>
       <c r="I1003">
-        <v>0.5032165980533785</v>
+        <v>0.651728650257386</v>
       </c>
       <c r="J1003">
         <v>1.341356748713074</v>
       </c>
       <c r="K1003">
-        <v>6.29</v>
+        <v>5.65</v>
       </c>
       <c r="L1003">
-        <v>9.69</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1003">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N1003">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="O1003">
         <v>1</v>
@@ -51954,46 +51954,46 @@
     </row>
     <row r="1004" spans="1:16">
       <c r="A1004" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1004" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C1004">
-        <v>1.462100210182946</v>
+        <v>0.6219690111000276</v>
       </c>
       <c r="D1004" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E1004">
-        <v>0.7496494525413828</v>
+        <v>0.6863453884327262</v>
       </c>
       <c r="F1004">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1004">
-        <v>0.01747789978981706</v>
+        <v>0.01333803098889997</v>
       </c>
       <c r="H1004">
-        <v>0.01647035054745861</v>
+        <v>0.01305365461156728</v>
       </c>
       <c r="I1004">
-        <v>0.7124507576415633</v>
+        <v>0.06437637733269863</v>
       </c>
       <c r="J1004">
         <v>1.341356748713074</v>
       </c>
       <c r="K1004">
-        <v>5.97</v>
+        <v>4.74</v>
       </c>
       <c r="L1004">
-        <v>9.470000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="M1004">
-        <v>5.86</v>
+        <v>4.61</v>
       </c>
       <c r="N1004">
-        <v>8.609999999999999</v>
+        <v>6.87</v>
       </c>
       <c r="O1004">
         <v>1</v>
@@ -52004,196 +52004,196 @@
     </row>
     <row r="1005" spans="1:16">
       <c r="A1005" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1005" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C1005">
-        <v>0.7031067530561543</v>
+        <v>1.239490555786455</v>
       </c>
       <c r="D1005" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
       <c r="E1005">
-        <v>1.213063020028516</v>
+        <v>0.7371883397310999</v>
       </c>
       <c r="F1005">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1005">
-        <v>0.01749689324694385</v>
+        <v>0.01814050944421354</v>
       </c>
       <c r="H1005">
-        <v>0.01690693697997148</v>
+        <v>0.0164828116602689</v>
       </c>
       <c r="I1005">
-        <v>0.5099562669723614</v>
+        <v>0.5023022160553552</v>
       </c>
       <c r="J1005">
-        <v>1.341356748713074</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K1005">
-        <v>6.26</v>
+        <v>6.29</v>
       </c>
       <c r="L1005">
-        <v>9.1</v>
+        <v>9.69</v>
       </c>
       <c r="M1005">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N1005">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1005">
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
       <c r="A1006" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1006" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C1006">
-        <v>0.7103278268979212</v>
+        <v>1.449405185698751</v>
       </c>
       <c r="D1006" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E1006">
-        <v>0.7214876061772433</v>
+        <v>0.7371883397310999</v>
       </c>
       <c r="F1006">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1006">
-        <v>0.01508967217310208</v>
+        <v>0.01749059481430125</v>
       </c>
       <c r="H1006">
-        <v>0.01359851239382276</v>
+        <v>0.0164828116602689</v>
       </c>
       <c r="I1006">
-        <v>0.0111597792793221</v>
+        <v>0.7122168459676512</v>
       </c>
       <c r="J1006">
-        <v>1.341356748713074</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K1006">
-        <v>5.36</v>
+        <v>5.97</v>
       </c>
       <c r="L1006">
-        <v>7.9</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1006">
-        <v>4.8</v>
+        <v>5.86</v>
       </c>
       <c r="N1006">
-        <v>7.16</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1006">
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
       <c r="A1007" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1007" t="s">
         <v>196</v>
       </c>
       <c r="C1007">
-        <v>0.6219690111000276</v>
+        <v>0.5493198156110441</v>
       </c>
       <c r="D1007" t="s">
-        <v>352</v>
+        <v>198</v>
       </c>
       <c r="E1007">
-        <v>0.7214876061772433</v>
+        <v>1.200623171915861</v>
       </c>
       <c r="F1007">
         <v>1</v>
       </c>
       <c r="G1007">
-        <v>0.01333803098889997</v>
+        <v>0.01573068018438896</v>
       </c>
       <c r="H1007">
-        <v>0.01359851239382276</v>
+        <v>0.01691937682808414</v>
       </c>
       <c r="I1007">
-        <v>0.09951859507721572</v>
+        <v>0.6513033563048172</v>
       </c>
       <c r="J1007">
-        <v>1.341356748713074</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K1007">
-        <v>4.74</v>
+        <v>5.65</v>
       </c>
       <c r="L1007">
-        <v>6.98</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1007">
-        <v>4.8</v>
+        <v>5.85</v>
       </c>
       <c r="N1007">
-        <v>7.16</v>
+        <v>9.06</v>
       </c>
       <c r="O1007">
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
       <c r="A1008" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1008" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C1008">
-        <v>1.239490555786455</v>
+        <v>0.611889544424133</v>
       </c>
       <c r="D1008" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E1008">
-        <v>0.7371883397310999</v>
+        <v>0.6765423628260026</v>
       </c>
       <c r="F1008">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1008">
-        <v>0.01814050944421354</v>
+        <v>0.01334811045557587</v>
       </c>
       <c r="H1008">
-        <v>0.0164828116602689</v>
+        <v>0.013063457637174</v>
       </c>
       <c r="I1008">
-        <v>0.5023022160553552</v>
+        <v>0.06465281840186954</v>
       </c>
       <c r="J1008">
         <v>1.343483218475921</v>
       </c>
       <c r="K1008">
-        <v>6.29</v>
+        <v>4.74</v>
       </c>
       <c r="L1008">
-        <v>9.69</v>
+        <v>6.98</v>
       </c>
       <c r="M1008">
-        <v>5.86</v>
+        <v>4.61</v>
       </c>
       <c r="N1008">
-        <v>8.609999999999999</v>
+        <v>6.87</v>
       </c>
       <c r="O1008">
         <v>1</v>
@@ -52204,40 +52204,40 @@
     </row>
     <row r="1009" spans="1:16">
       <c r="A1009" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1009" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C1009">
-        <v>1.449405185698751</v>
+        <v>1.236392561837954</v>
       </c>
       <c r="D1009" t="s">
         <v>351</v>
       </c>
       <c r="E1009">
-        <v>0.7371883397310999</v>
+        <v>0.7343021323323375</v>
       </c>
       <c r="F1009">
         <v>-1</v>
       </c>
       <c r="G1009">
-        <v>0.01749059481430125</v>
+        <v>0.01814360743816204</v>
       </c>
       <c r="H1009">
-        <v>0.0164828116602689</v>
+        <v>0.01648569786766766</v>
       </c>
       <c r="I1009">
-        <v>0.7122168459676512</v>
+        <v>0.5020904295056168</v>
       </c>
       <c r="J1009">
-        <v>1.343483218475921</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K1009">
-        <v>5.97</v>
+        <v>6.29</v>
       </c>
       <c r="L1009">
-        <v>9.470000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="M1009">
         <v>5.86</v>
@@ -52249,151 +52249,151 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
       <c r="A1010" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1010" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C1010">
-        <v>0.6897950523407328</v>
+        <v>1.446464800345405</v>
       </c>
       <c r="D1010" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
       <c r="E1010">
-        <v>1.200623171915861</v>
+        <v>0.7343021323323375</v>
       </c>
       <c r="F1010">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1010">
-        <v>0.01751020494765927</v>
+        <v>0.0174935351996546</v>
       </c>
       <c r="H1010">
-        <v>0.01691937682808414</v>
+        <v>0.01648569786766766</v>
       </c>
       <c r="I1010">
-        <v>0.5108281195751285</v>
+        <v>0.7121626680130673</v>
       </c>
       <c r="J1010">
-        <v>1.343483218475921</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K1010">
-        <v>6.26</v>
+        <v>5.97</v>
       </c>
       <c r="L1010">
-        <v>9.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M1010">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N1010">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1010">
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
       <c r="A1011" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1011" t="s">
         <v>196</v>
       </c>
       <c r="C1011">
-        <v>0.611889544424133</v>
+        <v>0.5465370388528523</v>
       </c>
       <c r="D1011" t="s">
-        <v>352</v>
+        <v>198</v>
       </c>
       <c r="E1011">
-        <v>0.7112805513155775</v>
+        <v>1.197741889785697</v>
       </c>
       <c r="F1011">
         <v>1</v>
       </c>
       <c r="G1011">
-        <v>0.01334811045557587</v>
+        <v>0.01573346296114715</v>
       </c>
       <c r="H1011">
-        <v>0.01360871944868442</v>
+        <v>0.01692225811021431</v>
       </c>
       <c r="I1011">
-        <v>0.09939100689144453</v>
+        <v>0.651204850932845</v>
       </c>
       <c r="J1011">
-        <v>1.343483218475921</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K1011">
-        <v>4.74</v>
+        <v>5.65</v>
       </c>
       <c r="L1011">
-        <v>6.98</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1011">
-        <v>4.8</v>
+        <v>5.85</v>
       </c>
       <c r="N1011">
-        <v>7.16</v>
+        <v>9.06</v>
       </c>
       <c r="O1011">
         <v>1</v>
       </c>
       <c r="P1011" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1012" spans="1:16">
       <c r="A1012" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1012" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C1012">
-        <v>1.236392561837954</v>
+        <v>0.6095549671084104</v>
       </c>
       <c r="D1012" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E1012">
-        <v>0.7343021323323375</v>
+        <v>0.6742718140020614</v>
       </c>
       <c r="F1012">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1012">
-        <v>0.01814360743816204</v>
+        <v>0.01335044503289159</v>
       </c>
       <c r="H1012">
-        <v>0.01648569786766766</v>
+        <v>0.01306572818599794</v>
       </c>
       <c r="I1012">
-        <v>0.5020904295056168</v>
+        <v>0.06471684689365098</v>
       </c>
       <c r="J1012">
         <v>1.343975745335778</v>
       </c>
       <c r="K1012">
-        <v>6.29</v>
+        <v>4.74</v>
       </c>
       <c r="L1012">
-        <v>9.69</v>
+        <v>6.98</v>
       </c>
       <c r="M1012">
-        <v>5.86</v>
+        <v>4.61</v>
       </c>
       <c r="N1012">
-        <v>8.609999999999999</v>
+        <v>6.87</v>
       </c>
       <c r="O1012">
         <v>1</v>
@@ -52404,34 +52404,34 @@
     </row>
     <row r="1013" spans="1:16">
       <c r="A1013" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1013" t="s">
         <v>192</v>
       </c>
       <c r="C1013">
-        <v>1.446464800345405</v>
+        <v>1.460084502779063</v>
       </c>
       <c r="D1013" t="s">
         <v>351</v>
       </c>
       <c r="E1013">
-        <v>0.7343021323323375</v>
+        <v>0.7476708854749239</v>
       </c>
       <c r="F1013">
         <v>-1</v>
       </c>
       <c r="G1013">
-        <v>0.0174935351996546</v>
+        <v>0.01747991549722094</v>
       </c>
       <c r="H1013">
-        <v>0.01648569786766766</v>
+        <v>0.01647232911452507</v>
       </c>
       <c r="I1013">
-        <v>0.7121626680130673</v>
+        <v>0.7124136173041391</v>
       </c>
       <c r="J1013">
-        <v>1.343975745335778</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1013">
         <v>5.97</v>
@@ -52449,39 +52449,39 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
       <c r="A1014" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1014" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1014">
-        <v>0.5465370388528523</v>
+        <v>0.5594267069852092</v>
       </c>
       <c r="D1014" t="s">
         <v>198</v>
       </c>
       <c r="E1014">
-        <v>1.197741889785697</v>
+        <v>1.211087829356368</v>
       </c>
       <c r="F1014">
         <v>1</v>
       </c>
       <c r="G1014">
-        <v>0.01573346296114715</v>
+        <v>0.01572057329301479</v>
       </c>
       <c r="H1014">
-        <v>0.01692225811021431</v>
+        <v>0.01690891217064363</v>
       </c>
       <c r="I1014">
-        <v>0.651204850932845</v>
+        <v>0.6516611223711593</v>
       </c>
       <c r="J1014">
-        <v>1.343975745335778</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1014">
         <v>5.65</v>
@@ -52499,39 +52499,39 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
       <c r="A1015" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1015" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1015">
-        <v>0.6095549671084104</v>
+        <v>0.620368600196441</v>
       </c>
       <c r="D1015" t="s">
         <v>352</v>
       </c>
       <c r="E1015">
-        <v>0.7089164223882642</v>
+        <v>0.6847888706551881</v>
       </c>
       <c r="F1015">
         <v>1</v>
       </c>
       <c r="G1015">
-        <v>0.01335044503289159</v>
+        <v>0.01333963139980356</v>
       </c>
       <c r="H1015">
-        <v>0.01361108357761174</v>
+        <v>0.01305521112934481</v>
       </c>
       <c r="I1015">
-        <v>0.09936145527985385</v>
+        <v>0.0644202704587471</v>
       </c>
       <c r="J1015">
-        <v>1.343975745335778</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1015">
         <v>4.74</v>
@@ -52540,16 +52540,16 @@
         <v>6.98</v>
       </c>
       <c r="M1015">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="N1015">
-        <v>7.16</v>
+        <v>6.87</v>
       </c>
       <c r="O1015">
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52557,49 +52557,49 @@
         <v>0</v>
       </c>
       <c r="B1016" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C1016">
-        <v>1.460084502779063</v>
+        <v>0.5528061783825207</v>
       </c>
       <c r="D1016" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E1016">
-        <v>0.7476708854749239</v>
+        <v>0.8930890061847165</v>
       </c>
       <c r="F1016">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1016">
-        <v>0.01747991549722094</v>
+        <v>0.01572719382161748</v>
       </c>
       <c r="H1016">
-        <v>0.01647232911452507</v>
+        <v>0.01692691099381528</v>
       </c>
       <c r="I1016">
-        <v>0.7124136173041391</v>
+        <v>0.3402828278021959</v>
       </c>
       <c r="J1016">
-        <v>1.341694388144211</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K1016">
+        <v>5.65</v>
+      </c>
+      <c r="L1016">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M1016">
         <v>5.97</v>
       </c>
-      <c r="L1016">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="M1016">
-        <v>5.86</v>
-      </c>
       <c r="N1016">
-        <v>8.609999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="O1016">
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>191</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -52607,49 +52607,49 @@
         <v>1</v>
       </c>
       <c r="B1017" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1017">
-        <v>0.5594267069852092</v>
+        <v>1.204232945758894</v>
       </c>
       <c r="D1017" t="s">
-        <v>198</v>
+        <v>354</v>
       </c>
       <c r="E1017">
-        <v>1.211087829356368</v>
+        <v>0.7508074412190604</v>
       </c>
       <c r="F1017">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1017">
-        <v>0.01572057329301479</v>
+        <v>0.01691576705424111</v>
       </c>
       <c r="H1017">
-        <v>0.01690891217064363</v>
+        <v>0.01554919255878094</v>
       </c>
       <c r="I1017">
-        <v>0.6516611223711593</v>
+        <v>0.4534255045398332</v>
       </c>
       <c r="J1017">
-        <v>1.341694388144211</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K1017">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1017">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1017">
-        <v>5.85</v>
+        <v>5.51</v>
       </c>
       <c r="N1017">
-        <v>9.06</v>
+        <v>8.15</v>
       </c>
       <c r="O1017">
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>191</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52657,31 +52657,31 @@
         <v>2</v>
       </c>
       <c r="B1018" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1018">
-        <v>0.620368600196441</v>
+        <v>0.6148143868200258</v>
       </c>
       <c r="D1018" t="s">
         <v>352</v>
       </c>
       <c r="E1018">
-        <v>0.7198669369077892</v>
+        <v>0.6793869880253833</v>
       </c>
       <c r="F1018">
         <v>1</v>
       </c>
       <c r="G1018">
-        <v>0.01333963139980356</v>
+        <v>0.01334518561317997</v>
       </c>
       <c r="H1018">
-        <v>0.01360013306309221</v>
+        <v>0.01306061301197462</v>
       </c>
       <c r="I1018">
-        <v>0.09949833671134822</v>
+        <v>0.06457260120535757</v>
       </c>
       <c r="J1018">
-        <v>1.341694388144211</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K1018">
         <v>4.74</v>
@@ -52690,16 +52690,16 @@
         <v>6.98</v>
       </c>
       <c r="M1018">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="N1018">
-        <v>7.16</v>
+        <v>6.87</v>
       </c>
       <c r="O1018">
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>191</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52707,31 +52707,31 @@
         <v>0</v>
       </c>
       <c r="B1019" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1019">
-        <v>0.5528061783825207</v>
+        <v>0.5438572811570364</v>
       </c>
       <c r="D1019" t="s">
-        <v>198</v>
+        <v>353</v>
       </c>
       <c r="E1019">
-        <v>1.204232945758894</v>
+        <v>0.8836332687623916</v>
       </c>
       <c r="F1019">
         <v>1</v>
       </c>
       <c r="G1019">
-        <v>0.01572719382161748</v>
+        <v>0.01573614271884297</v>
       </c>
       <c r="H1019">
-        <v>0.01691576705424111</v>
+        <v>0.01693636673123761</v>
       </c>
       <c r="I1019">
-        <v>0.651426767376373</v>
+        <v>0.3397759876053552</v>
       </c>
       <c r="J1019">
-        <v>1.342866163118138</v>
+        <v>1.344450038733268</v>
       </c>
       <c r="K1019">
         <v>5.65</v>
@@ -52740,16 +52740,16 @@
         <v>8.140000000000001</v>
       </c>
       <c r="M1019">
-        <v>5.85</v>
+        <v>5.97</v>
       </c>
       <c r="N1019">
-        <v>9.06</v>
+        <v>8.91</v>
       </c>
       <c r="O1019">
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>469</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52757,93 +52757,93 @@
         <v>1</v>
       </c>
       <c r="B1020" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1020">
-        <v>0.6148143868200258</v>
+        <v>1.194967273410384</v>
       </c>
       <c r="D1020" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E1020">
-        <v>0.7142424170329376</v>
+        <v>0.7420802865796947</v>
       </c>
       <c r="F1020">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1020">
-        <v>0.01334518561317997</v>
+        <v>0.01692503272658962</v>
       </c>
       <c r="H1020">
-        <v>0.01360575758296706</v>
+        <v>0.01555791971342031</v>
       </c>
       <c r="I1020">
-        <v>0.0994280302129118</v>
+        <v>0.4528869868306895</v>
       </c>
       <c r="J1020">
-        <v>1.342866163118138</v>
+        <v>1.344450038733268</v>
       </c>
       <c r="K1020">
-        <v>4.74</v>
+        <v>5.85</v>
       </c>
       <c r="L1020">
-        <v>6.98</v>
+        <v>9.06</v>
       </c>
       <c r="M1020">
-        <v>4.8</v>
+        <v>5.51</v>
       </c>
       <c r="N1020">
-        <v>7.16</v>
+        <v>8.15</v>
       </c>
       <c r="O1020">
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>469</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
       <c r="A1021" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1021" t="s">
         <v>197</v>
       </c>
       <c r="C1021">
-        <v>0.5438572811570364</v>
+        <v>0.6073068164043107</v>
       </c>
       <c r="D1021" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E1021">
-        <v>0.8836332687623916</v>
+        <v>0.672085321439635</v>
       </c>
       <c r="F1021">
         <v>1</v>
       </c>
       <c r="G1021">
-        <v>0.01573614271884297</v>
+        <v>0.01335269318359569</v>
       </c>
       <c r="H1021">
-        <v>0.01693636673123761</v>
+        <v>0.01306791467856037</v>
       </c>
       <c r="I1021">
-        <v>0.3397759876053552</v>
+        <v>0.06477850503532423</v>
       </c>
       <c r="J1021">
         <v>1.344450038733268</v>
       </c>
       <c r="K1021">
-        <v>5.65</v>
+        <v>4.74</v>
       </c>
       <c r="L1021">
-        <v>8.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="M1021">
-        <v>5.97</v>
+        <v>4.61</v>
       </c>
       <c r="N1021">
-        <v>8.91</v>
+        <v>6.87</v>
       </c>
       <c r="O1021">
         <v>1</v>
@@ -52854,146 +52854,146 @@
     </row>
     <row r="1022" spans="1:16">
       <c r="A1022" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1022" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1022">
-        <v>1.194967273410384</v>
+        <v>0.5168028977995238</v>
       </c>
       <c r="D1022" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1022">
-        <v>0.7420802865796947</v>
+        <v>0.8550466017456912</v>
       </c>
       <c r="F1022">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1022">
-        <v>0.01692503272658962</v>
+        <v>0.01576319710220048</v>
       </c>
       <c r="H1022">
-        <v>0.01555791971342031</v>
+        <v>0.01696495339825431</v>
       </c>
       <c r="I1022">
-        <v>0.4528869868306895</v>
+        <v>0.3382437039461674</v>
       </c>
       <c r="J1022">
-        <v>1.344450038733268</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1022">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1022">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1022">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1022">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1022">
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>192</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
       <c r="A1023" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1023" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1023">
-        <v>0.6073068164043107</v>
+        <v>1.166955212765879</v>
       </c>
       <c r="D1023" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E1023">
-        <v>0.7066398140803143</v>
+        <v>0.7156962773230759</v>
       </c>
       <c r="F1023">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1023">
-        <v>0.01335269318359569</v>
+        <v>0.01695304478723412</v>
       </c>
       <c r="H1023">
-        <v>0.01361336018591969</v>
+        <v>0.01558430372267692</v>
       </c>
       <c r="I1023">
-        <v>0.09933299767600356</v>
+        <v>0.4512589354428034</v>
       </c>
       <c r="J1023">
-        <v>1.344450038733268</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1023">
-        <v>4.74</v>
+        <v>5.85</v>
       </c>
       <c r="L1023">
-        <v>6.98</v>
+        <v>9.06</v>
       </c>
       <c r="M1023">
-        <v>4.8</v>
+        <v>5.51</v>
       </c>
       <c r="N1023">
-        <v>7.16</v>
+        <v>8.15</v>
       </c>
       <c r="O1023">
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>192</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
       <c r="A1024" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1024" t="s">
         <v>197</v>
       </c>
       <c r="C1024">
-        <v>0.5168028977995238</v>
+        <v>0.5846098647026094</v>
       </c>
       <c r="D1024" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E1024">
-        <v>0.8550466017456912</v>
+        <v>0.6500108599744783</v>
       </c>
       <c r="F1024">
         <v>1</v>
       </c>
       <c r="G1024">
-        <v>0.01576319710220048</v>
+        <v>0.01337539013529739</v>
       </c>
       <c r="H1024">
-        <v>0.01696495339825431</v>
+        <v>0.01308998914002552</v>
       </c>
       <c r="I1024">
-        <v>0.3382437039461674</v>
+        <v>0.06540099527186882</v>
       </c>
       <c r="J1024">
         <v>1.349238425168226</v>
       </c>
       <c r="K1024">
-        <v>5.65</v>
+        <v>4.74</v>
       </c>
       <c r="L1024">
-        <v>8.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="M1024">
-        <v>5.97</v>
+        <v>4.61</v>
       </c>
       <c r="N1024">
-        <v>8.91</v>
+        <v>6.87</v>
       </c>
       <c r="O1024">
         <v>1</v>
@@ -53004,146 +53004,146 @@
     </row>
     <row r="1025" spans="1:16">
       <c r="A1025" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1025" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1025">
-        <v>1.166955212765879</v>
+        <v>0.5065638875223204</v>
       </c>
       <c r="D1025" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1025">
-        <v>0.7156962773230759</v>
+        <v>0.8442276829218152</v>
       </c>
       <c r="F1025">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1025">
-        <v>0.01695304478723412</v>
+        <v>0.01577343611247768</v>
       </c>
       <c r="H1025">
-        <v>0.01558430372267692</v>
+        <v>0.01697577231707819</v>
       </c>
       <c r="I1025">
-        <v>0.4512589354428034</v>
+        <v>0.3376637953994948</v>
       </c>
       <c r="J1025">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1025">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1025">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1025">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1025">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1025">
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
       <c r="A1026" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1026" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1026">
-        <v>0.5846098647026094</v>
+        <v>1.156353759647005</v>
       </c>
       <c r="D1026" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E1026">
-        <v>0.6836555591925162</v>
+        <v>0.705710977035042</v>
       </c>
       <c r="F1026">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1026">
-        <v>0.01337539013529739</v>
+        <v>0.016963646240353</v>
       </c>
       <c r="H1026">
-        <v>0.01363634444080748</v>
+        <v>0.01559428902296496</v>
       </c>
       <c r="I1026">
-        <v>0.09904569448990674</v>
+        <v>0.450642782611963</v>
       </c>
       <c r="J1026">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1026">
-        <v>4.74</v>
+        <v>5.85</v>
       </c>
       <c r="L1026">
-        <v>6.98</v>
+        <v>9.06</v>
       </c>
       <c r="M1026">
-        <v>4.8</v>
+        <v>5.51</v>
       </c>
       <c r="N1026">
-        <v>7.16</v>
+        <v>8.15</v>
       </c>
       <c r="O1026">
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
       <c r="A1027" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1027" t="s">
         <v>197</v>
       </c>
       <c r="C1027">
-        <v>0.5065638875223204</v>
+        <v>0.5760199693550092</v>
       </c>
       <c r="D1027" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E1027">
-        <v>0.8442276829218152</v>
+        <v>0.6416565524739637</v>
       </c>
       <c r="F1027">
         <v>1</v>
       </c>
       <c r="G1027">
-        <v>0.01577343611247768</v>
+        <v>0.01338398003064499</v>
       </c>
       <c r="H1027">
-        <v>0.01697577231707819</v>
+        <v>0.01309834344752604</v>
       </c>
       <c r="I1027">
-        <v>0.3376637953994948</v>
+        <v>0.06563658311895448</v>
       </c>
       <c r="J1027">
         <v>1.35105063937658</v>
       </c>
       <c r="K1027">
-        <v>5.65</v>
+        <v>4.74</v>
       </c>
       <c r="L1027">
-        <v>8.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="M1027">
-        <v>5.97</v>
+        <v>4.61</v>
       </c>
       <c r="N1027">
-        <v>8.91</v>
+        <v>6.87</v>
       </c>
       <c r="O1027">
         <v>1</v>
@@ -53154,146 +53154,146 @@
     </row>
     <row r="1028" spans="1:16">
       <c r="A1028" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1028" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1028">
-        <v>1.156353759647005</v>
+        <v>0.5021328345691742</v>
       </c>
       <c r="D1028" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1028">
-        <v>0.705710977035042</v>
+        <v>0.8395456676775179</v>
       </c>
       <c r="F1028">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1028">
-        <v>0.016963646240353</v>
+        <v>0.01577786716543083</v>
       </c>
       <c r="H1028">
-        <v>0.01559428902296496</v>
+        <v>0.01698045433232248</v>
       </c>
       <c r="I1028">
-        <v>0.450642782611963</v>
+        <v>0.3374128331083437</v>
       </c>
       <c r="J1028">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1028">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1028">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1028">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1028">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1028">
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
       <c r="A1029" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1029" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1029">
-        <v>0.5760199693550092</v>
+        <v>1.15176585526189</v>
       </c>
       <c r="D1029" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E1029">
-        <v>0.6749569309924146</v>
+        <v>0.7013897200842756</v>
       </c>
       <c r="F1029">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1029">
-        <v>0.01338398003064499</v>
+        <v>0.01696823414473811</v>
       </c>
       <c r="H1029">
-        <v>0.01364504306900759</v>
+        <v>0.01559861027991572</v>
       </c>
       <c r="I1029">
-        <v>0.0989369616374054</v>
+        <v>0.4503761351776143</v>
       </c>
       <c r="J1029">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1029">
-        <v>4.74</v>
+        <v>5.85</v>
       </c>
       <c r="L1029">
-        <v>6.98</v>
+        <v>9.06</v>
       </c>
       <c r="M1029">
-        <v>4.8</v>
+        <v>5.51</v>
       </c>
       <c r="N1029">
-        <v>7.16</v>
+        <v>8.15</v>
       </c>
       <c r="O1029">
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
       <c r="A1030" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1030" t="s">
         <v>197</v>
       </c>
       <c r="C1030">
-        <v>0.5021328345691742</v>
+        <v>0.5723025904173253</v>
       </c>
       <c r="D1030" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E1030">
-        <v>0.8395456676775179</v>
+        <v>0.6380411269670603</v>
       </c>
       <c r="F1030">
         <v>1</v>
       </c>
       <c r="G1030">
-        <v>0.01577786716543083</v>
+        <v>0.01338769740958268</v>
       </c>
       <c r="H1030">
-        <v>0.01698045433232248</v>
+        <v>0.01310195887303294</v>
       </c>
       <c r="I1030">
-        <v>0.3374128331083437</v>
+        <v>0.06573853654973494</v>
       </c>
       <c r="J1030">
         <v>1.351834896536429</v>
       </c>
       <c r="K1030">
-        <v>5.65</v>
+        <v>4.74</v>
       </c>
       <c r="L1030">
-        <v>8.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="M1030">
-        <v>5.97</v>
+        <v>4.61</v>
       </c>
       <c r="N1030">
-        <v>8.91</v>
+        <v>6.87</v>
       </c>
       <c r="O1030">
         <v>1</v>
@@ -53304,146 +53304,146 @@
     </row>
     <row r="1031" spans="1:16">
       <c r="A1031" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1031" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1031">
-        <v>1.15176585526189</v>
+        <v>0.5002997890366885</v>
       </c>
       <c r="D1031" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1031">
-        <v>0.7013897200842756</v>
+        <v>0.8376088036369964</v>
       </c>
       <c r="F1031">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1031">
-        <v>0.01696823414473811</v>
+        <v>0.01577970021096331</v>
       </c>
       <c r="H1031">
-        <v>0.01559861027991572</v>
+        <v>0.01698239119636301</v>
       </c>
       <c r="I1031">
-        <v>0.4503761351776143</v>
+        <v>0.3373090146003079</v>
       </c>
       <c r="J1031">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1031">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1031">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1031">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1031">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1031">
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
       <c r="A1032" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1032" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1032">
-        <v>0.5723025904173253</v>
+        <v>1.149867923161882</v>
       </c>
       <c r="D1032" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E1032">
-        <v>0.6711924966251397</v>
+        <v>0.6996020951490545</v>
       </c>
       <c r="F1032">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1032">
-        <v>0.01338769740958268</v>
+        <v>0.01697013207683812</v>
       </c>
       <c r="H1032">
-        <v>0.01364880750337486</v>
+        <v>0.01560039790485095</v>
       </c>
       <c r="I1032">
-        <v>0.09888990620781435</v>
+        <v>0.4502658280128271</v>
       </c>
       <c r="J1032">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1032">
-        <v>4.74</v>
+        <v>5.85</v>
       </c>
       <c r="L1032">
-        <v>6.98</v>
+        <v>9.06</v>
       </c>
       <c r="M1032">
-        <v>4.8</v>
+        <v>5.51</v>
       </c>
       <c r="N1032">
-        <v>7.16</v>
+        <v>8.15</v>
       </c>
       <c r="O1032">
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
       <c r="A1033" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1033" t="s">
         <v>197</v>
       </c>
       <c r="C1033">
-        <v>0.5002997890366885</v>
+        <v>0.5707647787670629</v>
       </c>
       <c r="D1033" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E1033">
-        <v>0.8376088036369964</v>
+        <v>0.6365454915856867</v>
       </c>
       <c r="F1033">
         <v>1</v>
       </c>
       <c r="G1033">
-        <v>0.01577970021096331</v>
+        <v>0.01338923522123294</v>
       </c>
       <c r="H1033">
-        <v>0.01698239119636301</v>
+        <v>0.01310345450841431</v>
       </c>
       <c r="I1033">
-        <v>0.3373090146003079</v>
+        <v>0.06578071281862385</v>
       </c>
       <c r="J1033">
         <v>1.352159329374037</v>
       </c>
       <c r="K1033">
-        <v>5.65</v>
+        <v>4.74</v>
       </c>
       <c r="L1033">
-        <v>8.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="M1033">
-        <v>5.97</v>
+        <v>4.61</v>
       </c>
       <c r="N1033">
-        <v>8.91</v>
+        <v>6.87</v>
       </c>
       <c r="O1033">
         <v>1</v>
@@ -53454,146 +53454,146 @@
     </row>
     <row r="1034" spans="1:16">
       <c r="A1034" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1034" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1034">
-        <v>1.149867923161882</v>
+        <v>0.4969577705448094</v>
       </c>
       <c r="D1034" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1034">
-        <v>0.6996020951490545</v>
+        <v>0.8340775026818612</v>
       </c>
       <c r="F1034">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1034">
-        <v>0.01697013207683812</v>
+        <v>0.01578304222945519</v>
       </c>
       <c r="H1034">
-        <v>0.01560039790485095</v>
+        <v>0.01698592249731814</v>
       </c>
       <c r="I1034">
-        <v>0.4502658280128271</v>
+        <v>0.3371197321370518</v>
       </c>
       <c r="J1034">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1034">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1034">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1034">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1034">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1034">
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
       <c r="A1035" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1035" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1035">
-        <v>0.5707647787670629</v>
+        <v>1.146407603130467</v>
       </c>
       <c r="D1035" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E1035">
-        <v>0.6696352190046202</v>
+        <v>0.6963428877348496</v>
       </c>
       <c r="F1035">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1035">
-        <v>0.01338923522123294</v>
+        <v>0.01697359239686954</v>
       </c>
       <c r="H1035">
-        <v>0.01365036478099538</v>
+        <v>0.01560365711226515</v>
       </c>
       <c r="I1035">
-        <v>0.09887044023755731</v>
+        <v>0.4500647153956177</v>
       </c>
       <c r="J1035">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1035">
-        <v>4.74</v>
+        <v>5.85</v>
       </c>
       <c r="L1035">
-        <v>6.98</v>
+        <v>9.06</v>
       </c>
       <c r="M1035">
-        <v>4.8</v>
+        <v>5.51</v>
       </c>
       <c r="N1035">
-        <v>7.16</v>
+        <v>8.15</v>
       </c>
       <c r="O1035">
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
       <c r="A1036" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1036" t="s">
         <v>197</v>
       </c>
       <c r="C1036">
-        <v>0.4969577705448094</v>
+        <v>0.5679610322800706</v>
       </c>
       <c r="D1036" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E1036">
-        <v>0.8340775026818612</v>
+        <v>0.6338186410993929</v>
       </c>
       <c r="F1036">
         <v>1</v>
       </c>
       <c r="G1036">
-        <v>0.01578304222945519</v>
+        <v>0.01339203896771993</v>
       </c>
       <c r="H1036">
-        <v>0.01698592249731814</v>
+        <v>0.01310618135890061</v>
       </c>
       <c r="I1036">
-        <v>0.3371197321370518</v>
+        <v>0.06585760881932234</v>
       </c>
       <c r="J1036">
         <v>1.352750837071715</v>
       </c>
       <c r="K1036">
-        <v>5.65</v>
+        <v>4.74</v>
       </c>
       <c r="L1036">
-        <v>8.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="M1036">
-        <v>5.97</v>
+        <v>4.61</v>
       </c>
       <c r="N1036">
-        <v>8.91</v>
+        <v>6.87</v>
       </c>
       <c r="O1036">
         <v>1</v>
@@ -53604,84 +53604,84 @@
     </row>
     <row r="1037" spans="1:16">
       <c r="A1037" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1037" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1037">
-        <v>1.146407603130467</v>
+        <v>0.4920648074520191</v>
       </c>
       <c r="D1037" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1037">
-        <v>0.6963428877348496</v>
+        <v>0.8289074160156744</v>
       </c>
       <c r="F1037">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1037">
-        <v>0.01697359239686954</v>
+        <v>0.01578793519254798</v>
       </c>
       <c r="H1037">
-        <v>0.01560365711226515</v>
+        <v>0.01699109258398433</v>
       </c>
       <c r="I1037">
-        <v>0.4500647153956177</v>
+        <v>0.3368426085636553</v>
       </c>
       <c r="J1037">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1037">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1037">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1037">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1037">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1037">
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>474</v>
+        <v>351</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1038" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1038">
-        <v>0.5679610322800706</v>
+        <v>0.5638561393491281</v>
       </c>
       <c r="D1038" t="s">
         <v>352</v>
       </c>
       <c r="E1038">
-        <v>0.6667959820557678</v>
+        <v>0.6298263296201432</v>
       </c>
       <c r="F1038">
         <v>1</v>
       </c>
       <c r="G1038">
-        <v>0.01339203896771993</v>
+        <v>0.01339614386065087</v>
       </c>
       <c r="H1038">
-        <v>0.01365320401794423</v>
+        <v>0.01311017367037986</v>
       </c>
       <c r="I1038">
-        <v>0.09883494977569729</v>
+        <v>0.06597019027101503</v>
       </c>
       <c r="J1038">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1038">
         <v>4.74</v>
@@ -53690,16 +53690,16 @@
         <v>6.98</v>
       </c>
       <c r="M1038">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="N1038">
-        <v>7.16</v>
+        <v>6.87</v>
       </c>
       <c r="O1038">
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>474</v>
+        <v>351</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -53707,31 +53707,31 @@
         <v>0</v>
       </c>
       <c r="B1039" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1039">
-        <v>0.4920648074520191</v>
+        <v>0.5046197380717317</v>
       </c>
       <c r="D1039" t="s">
         <v>353</v>
       </c>
       <c r="E1039">
-        <v>0.8289074160156744</v>
+        <v>0.8421734223519017</v>
       </c>
       <c r="F1039">
         <v>1</v>
       </c>
       <c r="G1039">
-        <v>0.01578793519254798</v>
+        <v>0.01577538026192827</v>
       </c>
       <c r="H1039">
-        <v>0.01699109258398433</v>
+        <v>0.0169778265776481</v>
       </c>
       <c r="I1039">
-        <v>0.3368426085636553</v>
+        <v>0.3375536842801701</v>
       </c>
       <c r="J1039">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1039">
         <v>5.65</v>
@@ -53749,7 +53749,7 @@
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>351</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
@@ -53760,28 +53760,28 @@
         <v>198</v>
       </c>
       <c r="C1040">
-        <v>1.141341437804305</v>
+        <v>1.154340790746838</v>
       </c>
       <c r="D1040" t="s">
         <v>354</v>
       </c>
       <c r="E1040">
-        <v>0.6915711662054216</v>
+        <v>0.7038150011991586</v>
       </c>
       <c r="F1040">
         <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.0169786585621957</v>
+        <v>0.01696565920925316</v>
       </c>
       <c r="H1040">
-        <v>0.01560842883379458</v>
+        <v>0.01559618499880084</v>
       </c>
       <c r="I1040">
-        <v>0.4497702715988829</v>
+        <v>0.4505257895476795</v>
       </c>
       <c r="J1040">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1040">
         <v>5.85</v>
@@ -53799,7 +53799,7 @@
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>351</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
@@ -53807,31 +53807,31 @@
         <v>2</v>
       </c>
       <c r="B1041" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1041">
-        <v>0.5638561393491281</v>
+        <v>0.5743889484000011</v>
       </c>
       <c r="D1041" t="s">
         <v>352</v>
       </c>
       <c r="E1041">
-        <v>0.6626391284548134</v>
+        <v>0.6400702641611824</v>
       </c>
       <c r="F1041">
         <v>1</v>
       </c>
       <c r="G1041">
-        <v>0.01339614386065087</v>
+        <v>0.0133856110516</v>
       </c>
       <c r="H1041">
-        <v>0.01365736087154519</v>
+        <v>0.01309992973583882</v>
       </c>
       <c r="I1041">
-        <v>0.09878298910568528</v>
+        <v>0.0656813157611813</v>
       </c>
       <c r="J1041">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1041">
         <v>4.74</v>
@@ -53840,16 +53840,16 @@
         <v>6.98</v>
       </c>
       <c r="M1041">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="N1041">
-        <v>7.16</v>
+        <v>6.87</v>
       </c>
       <c r="O1041">
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>351</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
@@ -53857,31 +53857,31 @@
         <v>0</v>
       </c>
       <c r="B1042" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1042">
-        <v>0.5046197380717317</v>
+        <v>0.5044756313746497</v>
       </c>
       <c r="D1042" t="s">
         <v>353</v>
       </c>
       <c r="E1042">
-        <v>0.8421734223519017</v>
+        <v>0.8420211538595854</v>
       </c>
       <c r="F1042">
         <v>1</v>
       </c>
       <c r="G1042">
-        <v>0.01577538026192827</v>
+        <v>0.01577552436862535</v>
       </c>
       <c r="H1042">
-        <v>0.0169778265776481</v>
+        <v>0.01697797884614042</v>
       </c>
       <c r="I1042">
-        <v>0.3375536842801701</v>
+        <v>0.3375455224849357</v>
       </c>
       <c r="J1042">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1042">
         <v>5.65</v>
@@ -53899,7 +53899,7 @@
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>475</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
@@ -53910,28 +53910,28 @@
         <v>198</v>
       </c>
       <c r="C1043">
-        <v>1.154340790746838</v>
+        <v>1.154191582927735</v>
       </c>
       <c r="D1043" t="s">
         <v>354</v>
       </c>
       <c r="E1043">
-        <v>0.7038150011991586</v>
+        <v>0.7036744652874907</v>
       </c>
       <c r="F1043">
         <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.01696565920925316</v>
+        <v>0.01696580841707227</v>
       </c>
       <c r="H1043">
-        <v>0.01559618499880084</v>
+        <v>0.01559632553471251</v>
       </c>
       <c r="I1043">
-        <v>0.4505257895476795</v>
+        <v>0.4505171176402447</v>
       </c>
       <c r="J1043">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1043">
         <v>5.85</v>
@@ -53949,39 +53949,39 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>475</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1044" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1044">
-        <v>0.5743889484000011</v>
+        <v>0.5996415176724694</v>
       </c>
       <c r="D1044" t="s">
         <v>352</v>
       </c>
       <c r="E1044">
-        <v>0.6733052642025337</v>
+        <v>0.6646302524198493</v>
       </c>
       <c r="F1044">
         <v>1</v>
       </c>
       <c r="G1044">
-        <v>0.0133856110516</v>
+        <v>0.01336035848232753</v>
       </c>
       <c r="H1044">
-        <v>0.01364669473579747</v>
+        <v>0.01307536974758015</v>
       </c>
       <c r="I1044">
-        <v>0.09891631580253257</v>
+        <v>0.06498873474737987</v>
       </c>
       <c r="J1044">
-        <v>1.351394736624472</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1044">
         <v>4.74</v>
@@ -53990,16 +53990,16 @@
         <v>6.98</v>
       </c>
       <c r="M1044">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="N1044">
-        <v>7.16</v>
+        <v>6.87</v>
       </c>
       <c r="O1044">
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>475</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54007,49 +54007,49 @@
         <v>0</v>
       </c>
       <c r="B1045" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C1045">
-        <v>0.5044756313746497</v>
+        <v>0.8240937125821999</v>
       </c>
       <c r="D1045" t="s">
-        <v>353</v>
+        <v>194</v>
       </c>
       <c r="E1045">
-        <v>0.8420211538595854</v>
+        <v>0.6766682850975805</v>
       </c>
       <c r="F1045">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.01577552436862535</v>
+        <v>0.0157559062874178</v>
       </c>
       <c r="H1045">
-        <v>0.01697797884614042</v>
+        <v>0.01512333171490242</v>
       </c>
       <c r="I1045">
-        <v>0.3375455224849357</v>
+        <v>0.1474254274846194</v>
       </c>
       <c r="J1045">
-        <v>1.351420242234575</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1045">
-        <v>5.65</v>
+        <v>5.54</v>
       </c>
       <c r="L1045">
-        <v>8.140000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1045">
-        <v>5.97</v>
+        <v>5.36</v>
       </c>
       <c r="N1045">
-        <v>8.91</v>
+        <v>7.9</v>
       </c>
       <c r="O1045">
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>193</v>
+        <v>354</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54057,49 +54057,49 @@
         <v>1</v>
       </c>
       <c r="B1046" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1046">
-        <v>1.154191582927735</v>
+        <v>0.5922029237616666</v>
       </c>
       <c r="D1046" t="s">
+        <v>352</v>
+      </c>
+      <c r="E1046">
+        <v>0.657395670578329</v>
+      </c>
+      <c r="F1046">
+        <v>1</v>
+      </c>
+      <c r="G1046">
+        <v>0.01336779707623833</v>
+      </c>
+      <c r="H1046">
+        <v>0.01308260432942167</v>
+      </c>
+      <c r="I1046">
+        <v>0.06519274681666243</v>
+      </c>
+      <c r="J1046">
+        <v>1.347636513974332</v>
+      </c>
+      <c r="K1046">
+        <v>4.74</v>
+      </c>
+      <c r="L1046">
+        <v>6.98</v>
+      </c>
+      <c r="M1046">
+        <v>4.61</v>
+      </c>
+      <c r="N1046">
+        <v>6.87</v>
+      </c>
+      <c r="O1046">
+        <v>1</v>
+      </c>
+      <c r="P1046" t="s">
         <v>354</v>
-      </c>
-      <c r="E1046">
-        <v>0.7036744652874907</v>
-      </c>
-      <c r="F1046">
-        <v>-1</v>
-      </c>
-      <c r="G1046">
-        <v>0.01696580841707227</v>
-      </c>
-      <c r="H1046">
-        <v>0.01559632553471251</v>
-      </c>
-      <c r="I1046">
-        <v>0.4505171176402447</v>
-      </c>
-      <c r="J1046">
-        <v>1.351420242234575</v>
-      </c>
-      <c r="K1046">
-        <v>5.85</v>
-      </c>
-      <c r="L1046">
-        <v>9.06</v>
-      </c>
-      <c r="M1046">
-        <v>5.51</v>
-      </c>
-      <c r="N1046">
-        <v>8.15</v>
-      </c>
-      <c r="O1046">
-        <v>1</v>
-      </c>
-      <c r="P1046" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54107,31 +54107,31 @@
         <v>0</v>
       </c>
       <c r="B1047" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1047">
-        <v>0.5996415176724694</v>
+        <v>0.5865946806561269</v>
       </c>
       <c r="D1047" t="s">
         <v>352</v>
       </c>
       <c r="E1047">
-        <v>0.6988774862506029</v>
+        <v>0.6519412400474138</v>
       </c>
       <c r="F1047">
         <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.01336035848232753</v>
+        <v>0.01337340531934387</v>
       </c>
       <c r="H1047">
-        <v>0.0136211225137494</v>
+        <v>0.01308805875995259</v>
       </c>
       <c r="I1047">
-        <v>0.09923596857813344</v>
+        <v>0.06534655939128697</v>
       </c>
       <c r="J1047">
-        <v>1.346067190364458</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1047">
         <v>4.74</v>
@@ -54140,16 +54140,16 @@
         <v>6.98</v>
       </c>
       <c r="M1047">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="N1047">
-        <v>7.16</v>
+        <v>6.87</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54157,248 +54157,98 @@
         <v>0</v>
       </c>
       <c r="B1048" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C1048">
-        <v>0.8240937125821999</v>
+        <v>0.7946438898107466</v>
       </c>
       <c r="D1048" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1048">
+        <v>0.6677929582202644</v>
+      </c>
+      <c r="F1048">
+        <v>-1</v>
+      </c>
+      <c r="G1048">
+        <v>0.01500535611018925</v>
+      </c>
+      <c r="H1048">
+        <v>0.01439220704177974</v>
+      </c>
+      <c r="I1048">
+        <v>0.1268509315904822</v>
+      </c>
+      <c r="J1048">
+        <v>1.350828157830657</v>
+      </c>
+      <c r="K1048">
+        <v>5.26</v>
+      </c>
+      <c r="L1048">
+        <v>7.9</v>
+      </c>
+      <c r="M1048">
+        <v>5.08</v>
+      </c>
+      <c r="N1048">
+        <v>7.53</v>
+      </c>
+      <c r="O1048">
+        <v>1</v>
+      </c>
+      <c r="P1048" t="s">
         <v>194</v>
-      </c>
-      <c r="E1048">
-        <v>0.6766682850975805</v>
-      </c>
-      <c r="F1048">
-        <v>-1</v>
-      </c>
-      <c r="G1048">
-        <v>0.0157559062874178</v>
-      </c>
-      <c r="H1048">
-        <v>0.01512333171490242</v>
-      </c>
-      <c r="I1048">
-        <v>0.1474254274846194</v>
-      </c>
-      <c r="J1048">
-        <v>1.347636513974332</v>
-      </c>
-      <c r="K1048">
-        <v>5.54</v>
-      </c>
-      <c r="L1048">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="M1048">
-        <v>5.36</v>
-      </c>
-      <c r="N1048">
-        <v>7.9</v>
-      </c>
-      <c r="O1048">
-        <v>1</v>
-      </c>
-      <c r="P1048" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1049" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C1049">
-        <v>0.5922029237616666</v>
+        <v>0.7954040719633015</v>
       </c>
       <c r="D1049" t="s">
-        <v>352</v>
+        <v>195</v>
       </c>
       <c r="E1049">
-        <v>0.6913447329232065</v>
+        <v>0.6685271265348991</v>
       </c>
       <c r="F1049">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.01336779707623833</v>
+        <v>0.0150045959280367</v>
       </c>
       <c r="H1049">
-        <v>0.01362865526707679</v>
+        <v>0.0143914728734651</v>
       </c>
       <c r="I1049">
-        <v>0.09914180916153992</v>
+        <v>0.1268769454284024</v>
       </c>
       <c r="J1049">
-        <v>1.347636513974332</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1049">
-        <v>4.74</v>
+        <v>5.26</v>
       </c>
       <c r="L1049">
-        <v>6.98</v>
+        <v>7.9</v>
       </c>
       <c r="M1049">
-        <v>4.8</v>
+        <v>5.08</v>
       </c>
       <c r="N1049">
-        <v>7.16</v>
+        <v>7.53</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="1050" spans="1:16">
-      <c r="A1050" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1050">
-        <v>0.5865946806561269</v>
-      </c>
-      <c r="D1050" t="s">
-        <v>352</v>
-      </c>
-      <c r="E1050">
-        <v>0.6856654993986089</v>
-      </c>
-      <c r="F1050">
-        <v>1</v>
-      </c>
-      <c r="G1050">
-        <v>0.01337340531934387</v>
-      </c>
-      <c r="H1050">
-        <v>0.01363433450060139</v>
-      </c>
-      <c r="I1050">
-        <v>0.09907081874248203</v>
-      </c>
-      <c r="J1050">
-        <v>1.34881968762529</v>
-      </c>
-      <c r="K1050">
-        <v>4.74</v>
-      </c>
-      <c r="L1050">
-        <v>6.98</v>
-      </c>
-      <c r="M1050">
-        <v>4.8</v>
-      </c>
-      <c r="N1050">
-        <v>7.16</v>
-      </c>
-      <c r="O1050">
-        <v>1</v>
-      </c>
-      <c r="P1050" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="1051" spans="1:16">
-      <c r="A1051" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>200</v>
-      </c>
-      <c r="C1051">
-        <v>0.7946438898107466</v>
-      </c>
-      <c r="D1051" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1051">
-        <v>0.6677929582202644</v>
-      </c>
-      <c r="F1051">
-        <v>-1</v>
-      </c>
-      <c r="G1051">
-        <v>0.01500535611018925</v>
-      </c>
-      <c r="H1051">
-        <v>0.01439220704177974</v>
-      </c>
-      <c r="I1051">
-        <v>0.1268509315904822</v>
-      </c>
-      <c r="J1051">
-        <v>1.350828157830657</v>
-      </c>
-      <c r="K1051">
-        <v>5.26</v>
-      </c>
-      <c r="L1051">
-        <v>7.9</v>
-      </c>
-      <c r="M1051">
-        <v>5.08</v>
-      </c>
-      <c r="N1051">
-        <v>7.53</v>
-      </c>
-      <c r="O1051">
-        <v>1</v>
-      </c>
-      <c r="P1051" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="1052" spans="1:16">
-      <c r="A1052" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>200</v>
-      </c>
-      <c r="C1052">
-        <v>0.7954040719633015</v>
-      </c>
-      <c r="D1052" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1052">
-        <v>0.6685271265348991</v>
-      </c>
-      <c r="F1052">
-        <v>-1</v>
-      </c>
-      <c r="G1052">
-        <v>0.0150045959280367</v>
-      </c>
-      <c r="H1052">
-        <v>0.0143914728734651</v>
-      </c>
-      <c r="I1052">
-        <v>0.1268769454284024</v>
-      </c>
-      <c r="J1052">
-        <v>1.350683636508878</v>
-      </c>
-      <c r="K1052">
-        <v>5.26</v>
-      </c>
-      <c r="L1052">
-        <v>7.9</v>
-      </c>
-      <c r="M1052">
-        <v>5.08</v>
-      </c>
-      <c r="N1052">
-        <v>7.53</v>
-      </c>
-      <c r="O1052">
-        <v>1</v>
-      </c>
-      <c r="P1052" t="s">
         <v>476</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3174" uniqueCount="481">
   <si>
     <t>trade_time</t>
   </si>
@@ -610,9 +610,6 @@
     <t>2021-10-19</t>
   </si>
   <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
     <t>2021-11-04</t>
   </si>
   <si>
@@ -629,6 +626,9 @@
   </si>
   <si>
     <t>2021-10-28</t>
+  </si>
+  <si>
+    <t>2021-11-01</t>
   </si>
   <si>
     <t>2016-11-30</t>
@@ -1084,13 +1084,16 @@
     <t>2021-10-08</t>
   </si>
   <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
     <t>2021-10-18</t>
   </si>
   <si>
     <t>2021-10-20</t>
   </si>
   <si>
-    <t>2021-11-08</t>
+    <t>2021-11-09</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1811,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1059"/>
+  <dimension ref="A1:P1054"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1908,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1958,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2008,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2058,7 +2061,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2108,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2158,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2208,7 +2211,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2508,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2558,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2608,7 +2611,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2658,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2708,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2758,7 +2761,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2808,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2858,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2908,7 +2911,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3158,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3208,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3258,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3308,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3358,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3408,7 +3411,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3458,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3508,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3558,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3608,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3658,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3708,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4008,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4058,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4108,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4158,7 +4161,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4208,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4258,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4308,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4358,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4408,7 +4411,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4458,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4508,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4558,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4608,7 +4611,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4658,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4708,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4758,7 +4761,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4808,7 +4811,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4858,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4908,7 +4911,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4958,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5008,7 +5011,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5458,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5508,7 +5511,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5558,7 +5561,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5608,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5658,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5708,7 +5711,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6108,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6158,7 +6161,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6208,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6258,7 +6261,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6308,7 +6311,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6358,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6608,7 +6611,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6658,7 +6661,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6708,7 +6711,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6758,7 +6761,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6808,7 +6811,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6858,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6908,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6958,7 +6961,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7008,7 +7011,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7058,7 +7061,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7108,7 +7111,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7158,7 +7161,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7208,7 +7211,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7258,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7308,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7358,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7408,7 +7411,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7458,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7508,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7558,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7608,7 +7611,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7658,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7708,7 +7711,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7758,7 +7761,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7808,7 +7811,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7858,7 +7861,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7908,7 +7911,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7958,7 +7961,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8008,7 +8011,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8058,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8108,7 +8111,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8158,7 +8161,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8208,7 +8211,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8258,7 +8261,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8308,7 +8311,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8358,7 +8361,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8408,7 +8411,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8458,7 +8461,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8508,7 +8511,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8558,7 +8561,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8608,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8658,7 +8661,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8708,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8758,7 +8761,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8808,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8858,7 +8861,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8908,7 +8911,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8958,7 +8961,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9008,7 +9011,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9058,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9108,7 +9111,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9158,7 +9161,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9208,7 +9211,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9258,7 +9261,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9508,7 +9511,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9558,7 +9561,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9608,7 +9611,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9658,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9708,7 +9711,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9758,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9808,7 +9811,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9858,7 +9861,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10208,7 +10211,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10258,7 +10261,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10308,7 +10311,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10558,7 +10561,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10608,7 +10611,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10658,7 +10661,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10708,7 +10711,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10758,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10808,7 +10811,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10858,7 +10861,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10908,7 +10911,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10958,7 +10961,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11008,7 +11011,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11058,7 +11061,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11108,7 +11111,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11158,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11558,7 +11561,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11808,7 +11811,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11858,7 +11861,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11908,7 +11911,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11958,7 +11961,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12008,7 +12011,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12058,7 +12061,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12108,7 +12111,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12158,7 +12161,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12208,7 +12211,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12258,7 +12261,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12308,7 +12311,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12358,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12408,7 +12411,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12458,7 +12461,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12508,7 +12511,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12558,7 +12561,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12608,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16458,7 +16461,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16508,7 +16511,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16558,7 +16561,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16608,7 +16611,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16658,7 +16661,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16708,7 +16711,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16908,7 +16911,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16958,7 +16961,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17008,7 +17011,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17058,7 +17061,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17108,7 +17111,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17158,7 +17161,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17408,7 +17411,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17458,7 +17461,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17508,7 +17511,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17558,7 +17561,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17608,7 +17611,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17658,7 +17661,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17708,7 +17711,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17758,7 +17761,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17808,7 +17811,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18958,7 +18961,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19008,7 +19011,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19058,7 +19061,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19108,7 +19111,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19158,7 +19161,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19208,7 +19211,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19258,7 +19261,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19308,7 +19311,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19358,7 +19361,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19408,7 +19411,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -20008,7 +20011,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20058,7 +20061,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20108,7 +20111,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20158,7 +20161,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20208,7 +20211,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20258,7 +20261,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -22008,7 +22011,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22058,7 +22061,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22108,7 +22111,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22158,7 +22161,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22208,7 +22211,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22258,7 +22261,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22308,7 +22311,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22358,7 +22361,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22408,7 +22411,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22458,7 +22461,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22508,7 +22511,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22558,7 +22561,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22608,7 +22611,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22658,7 +22661,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22708,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22758,7 +22761,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22808,7 +22811,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22858,7 +22861,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22908,7 +22911,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23258,7 +23261,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23308,7 +23311,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23358,7 +23361,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23408,7 +23411,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23458,7 +23461,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23508,7 +23511,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23558,7 +23561,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23608,7 +23611,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23658,7 +23661,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23708,7 +23711,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23758,7 +23761,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23808,7 +23811,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23858,7 +23861,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23908,7 +23911,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23958,7 +23961,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24008,7 +24011,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24058,7 +24061,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24108,7 +24111,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24158,7 +24161,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24208,7 +24211,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24258,7 +24261,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24308,7 +24311,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24708,7 +24711,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24758,7 +24761,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24808,7 +24811,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24858,7 +24861,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24908,7 +24911,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24958,7 +24961,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25008,7 +25011,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25608,7 +25611,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25658,7 +25661,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25708,7 +25711,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25758,7 +25761,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25808,7 +25811,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25858,7 +25861,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25908,7 +25911,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25958,7 +25961,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26008,7 +26011,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26058,7 +26061,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26108,7 +26111,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26158,7 +26161,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26208,7 +26211,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26258,7 +26261,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26308,7 +26311,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26358,7 +26361,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26408,7 +26411,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26458,7 +26461,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26508,7 +26511,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26558,7 +26561,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26758,7 +26761,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26808,7 +26811,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26858,7 +26861,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26908,7 +26911,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26958,7 +26961,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27008,7 +27011,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27058,7 +27061,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -28008,7 +28011,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28058,7 +28061,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28108,7 +28111,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29408,7 +29411,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29458,7 +29461,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29508,7 +29511,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29558,7 +29561,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29608,7 +29611,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29658,7 +29661,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29708,7 +29711,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29758,7 +29761,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29808,7 +29811,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29858,7 +29861,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30158,7 +30161,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30208,7 +30211,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30258,7 +30261,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30308,7 +30311,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30358,7 +30361,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30408,7 +30411,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30458,7 +30461,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30508,7 +30511,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30558,7 +30561,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30608,7 +30611,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30658,7 +30661,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30858,7 +30861,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30908,7 +30911,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30958,7 +30961,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31008,7 +31011,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31058,7 +31061,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31108,7 +31111,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31158,7 +31161,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31208,7 +31211,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31258,7 +31261,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31558,7 +31561,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31608,7 +31611,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31658,7 +31661,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31708,7 +31711,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31758,7 +31761,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31808,7 +31811,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31858,7 +31861,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31908,7 +31911,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31958,7 +31961,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32008,7 +32011,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32058,7 +32061,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32108,7 +32111,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32708,7 +32711,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32758,7 +32761,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32808,7 +32811,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32858,7 +32861,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32908,7 +32911,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32958,7 +32961,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33008,7 +33011,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33058,7 +33061,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33108,7 +33111,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33158,7 +33161,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33358,7 +33361,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33408,7 +33411,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33458,7 +33461,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33508,7 +33511,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33558,7 +33561,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34458,7 +34461,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34508,7 +34511,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34558,7 +34561,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34608,7 +34611,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34658,7 +34661,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34708,7 +34711,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34758,7 +34761,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34808,7 +34811,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34858,7 +34861,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35508,7 +35511,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35558,7 +35561,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35608,7 +35611,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35658,7 +35661,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35708,7 +35711,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35758,7 +35761,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35808,7 +35811,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35858,7 +35861,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35908,7 +35911,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36308,7 +36311,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36358,7 +36361,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36408,7 +36411,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36458,7 +36461,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36508,7 +36511,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36558,7 +36561,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36608,7 +36611,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36658,7 +36661,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36708,7 +36711,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36758,7 +36761,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36808,7 +36811,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36858,7 +36861,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36908,7 +36911,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37208,7 +37211,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37258,7 +37261,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37308,7 +37311,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37358,7 +37361,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37658,7 +37661,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37708,7 +37711,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37758,7 +37761,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37808,7 +37811,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37858,7 +37861,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37908,7 +37911,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37958,7 +37961,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38008,7 +38011,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38058,7 +38061,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38108,7 +38111,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38358,7 +38361,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38408,7 +38411,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38458,7 +38461,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38508,7 +38511,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38558,7 +38561,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39158,7 +39161,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39208,7 +39211,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39258,7 +39261,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39308,7 +39311,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39358,7 +39361,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39408,7 +39411,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39458,7 +39461,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39508,7 +39511,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39558,7 +39561,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39608,7 +39611,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40408,7 +40411,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40458,7 +40461,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40508,7 +40511,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40558,7 +40561,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40608,7 +40611,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40658,7 +40661,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40708,7 +40711,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42408,7 +42411,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42458,7 +42461,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42508,7 +42511,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42558,7 +42561,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42608,7 +42611,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43158,7 +43161,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43208,7 +43211,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43258,7 +43261,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43308,7 +43311,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43358,7 +43361,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43408,7 +43411,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43558,7 +43561,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43608,7 +43611,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43658,7 +43661,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43708,7 +43711,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43758,7 +43761,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43808,7 +43811,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43858,7 +43861,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43908,7 +43911,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43958,7 +43961,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44008,7 +44011,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44058,7 +44061,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44108,7 +44111,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44158,7 +44161,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44208,7 +44211,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44258,7 +44261,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44308,7 +44311,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44358,7 +44361,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44408,7 +44411,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44458,7 +44461,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44508,7 +44511,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44808,7 +44811,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44858,7 +44861,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44908,7 +44911,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44958,7 +44961,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45008,7 +45011,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45058,7 +45061,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45108,7 +45111,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45158,7 +45161,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45208,7 +45211,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45258,7 +45261,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45308,7 +45311,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45358,7 +45361,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45408,7 +45411,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45458,7 +45461,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45508,7 +45511,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45558,7 +45561,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45608,7 +45611,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45658,7 +45661,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45958,7 +45961,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46008,7 +46011,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46058,7 +46061,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46108,7 +46111,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46158,7 +46161,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46408,7 +46411,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46458,7 +46461,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46508,7 +46511,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46558,7 +46561,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46808,7 +46811,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46858,7 +46861,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46908,7 +46911,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46958,7 +46961,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47008,7 +47011,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47058,7 +47061,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47108,7 +47111,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47158,7 +47161,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47208,7 +47211,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47258,7 +47261,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47308,7 +47311,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47658,7 +47661,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47708,7 +47711,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47758,7 +47761,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47808,7 +47811,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47858,7 +47861,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47908,7 +47911,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -47958,7 +47961,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48008,7 +48011,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48058,7 +48061,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48108,7 +48111,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48158,7 +48161,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48208,7 +48211,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48258,7 +48261,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48308,7 +48311,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48358,7 +48361,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48908,7 +48911,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48958,7 +48961,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49008,7 +49011,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49058,7 +49061,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49258,7 +49261,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49308,7 +49311,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49358,7 +49361,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49408,7 +49411,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49458,7 +49461,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49508,7 +49511,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49558,7 +49561,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49608,7 +49611,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49658,7 +49661,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50658,7 +50661,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50708,7 +50711,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50758,7 +50761,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50808,7 +50811,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50858,7 +50861,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50908,7 +50911,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50958,7 +50961,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51008,7 +51011,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51058,7 +51061,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51108,7 +51111,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51158,7 +51161,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51208,7 +51211,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51222,7 +51225,7 @@
         <v>0.7692553919018295</v>
       </c>
       <c r="D989" t="s">
-        <v>198</v>
+        <v>356</v>
       </c>
       <c r="E989">
         <v>0.6740803279131855</v>
@@ -51258,7 +51261,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51272,7 +51275,7 @@
         <v>0.7717569759069578</v>
       </c>
       <c r="D990" t="s">
-        <v>198</v>
+        <v>356</v>
       </c>
       <c r="E990">
         <v>0.6740803279131855</v>
@@ -51308,7 +51311,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51358,7 +51361,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51408,7 +51411,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51458,7 +51461,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51508,7 +51511,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51522,7 +51525,7 @@
         <v>0.5634810388524212</v>
       </c>
       <c r="D995" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E995">
         <v>0.9043684605219404</v>
@@ -51558,7 +51561,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51572,7 +51575,7 @@
         <v>1.215285677395871</v>
       </c>
       <c r="D996" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E996">
         <v>0.7612177918720082</v>
@@ -51608,7 +51611,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51619,107 +51622,107 @@
         <v>198</v>
       </c>
       <c r="C997">
-        <v>0.6237699334797311</v>
+        <v>0.5439992376982135</v>
       </c>
       <c r="D997" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E997">
-        <v>0.4351457587906271</v>
+        <v>0.4290141353004202</v>
       </c>
       <c r="F997">
         <v>1</v>
       </c>
       <c r="G997">
-        <v>0.01333623006652027</v>
+        <v>0.01317600076230179</v>
       </c>
       <c r="H997">
-        <v>0.01266485424120937</v>
+        <v>0.01247098586469958</v>
       </c>
       <c r="I997">
-        <v>-0.188624174689104</v>
+        <v>-0.1149851023977932</v>
       </c>
       <c r="J997">
         <v>1.340976807282757</v>
       </c>
       <c r="K997">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="L997">
-        <v>6.98</v>
+        <v>6.86</v>
       </c>
       <c r="M997">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="N997">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="O997">
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="998" spans="1:16">
       <c r="A998" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B998" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C998">
-        <v>0.5439992376982135</v>
+        <v>1.280794863275108</v>
       </c>
       <c r="D998" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E998">
-        <v>0.4351457587906271</v>
+        <v>0.7756689823198943</v>
       </c>
       <c r="F998">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G998">
-        <v>0.01317600076230179</v>
+        <v>0.01809920513672489</v>
       </c>
       <c r="H998">
-        <v>0.01266485424120937</v>
+        <v>0.01644433101768011</v>
       </c>
       <c r="I998">
-        <v>-0.1088534789075863</v>
+        <v>0.5051258809552142</v>
       </c>
       <c r="J998">
-        <v>1.340976807282757</v>
+        <v>1.336916555918107</v>
       </c>
       <c r="K998">
-        <v>4.71</v>
+        <v>6.29</v>
       </c>
       <c r="L998">
-        <v>6.86</v>
+        <v>9.69</v>
       </c>
       <c r="M998">
-        <v>4.56</v>
+        <v>5.86</v>
       </c>
       <c r="N998">
-        <v>6.55</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O998">
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="999" spans="1:16">
       <c r="A999" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B999" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C999">
-        <v>1.280794863275108</v>
+        <v>1.488608161168904</v>
       </c>
       <c r="D999" t="s">
         <v>355</v>
@@ -51731,22 +51734,22 @@
         <v>-1</v>
       </c>
       <c r="G999">
-        <v>0.01809920513672489</v>
+        <v>0.01745139183883109</v>
       </c>
       <c r="H999">
         <v>0.01644433101768011</v>
       </c>
       <c r="I999">
-        <v>0.5051258809552142</v>
+        <v>0.7129391788490098</v>
       </c>
       <c r="J999">
         <v>1.336916555918107</v>
       </c>
       <c r="K999">
-        <v>6.29</v>
+        <v>5.97</v>
       </c>
       <c r="L999">
-        <v>9.69</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M999">
         <v>5.86</v>
@@ -51758,789 +51761,789 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
       <c r="A1000" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1000" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C1000">
-        <v>1.488608161168904</v>
+        <v>0.5864214590626977</v>
       </c>
       <c r="D1000" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E1000">
-        <v>0.7756689823198943</v>
+        <v>0.9286081611689037</v>
       </c>
       <c r="F1000">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1000">
-        <v>0.01745139183883109</v>
+        <v>0.0156935785409373</v>
       </c>
       <c r="H1000">
-        <v>0.01644433101768011</v>
+        <v>0.0168913918388311</v>
       </c>
       <c r="I1000">
-        <v>0.7129391788490098</v>
+        <v>0.3421867021062059</v>
       </c>
       <c r="J1000">
         <v>1.336916555918107</v>
       </c>
       <c r="K1000">
+        <v>5.65</v>
+      </c>
+      <c r="L1000">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M1000">
         <v>5.97</v>
       </c>
-      <c r="L1000">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="M1000">
-        <v>5.86</v>
-      </c>
       <c r="N1000">
-        <v>8.609999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="O1000">
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
       <c r="A1001" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1001" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1001">
-        <v>0.5864214590626977</v>
+        <v>1.239038147879077</v>
       </c>
       <c r="D1001" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E1001">
-        <v>0.9286081611689037</v>
+        <v>0.7835897768912332</v>
       </c>
       <c r="F1001">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1001">
-        <v>0.0156935785409373</v>
+        <v>0.01688096185212093</v>
       </c>
       <c r="H1001">
-        <v>0.0168913918388311</v>
+        <v>0.01551641022310877</v>
       </c>
       <c r="I1001">
-        <v>0.3421867021062059</v>
+        <v>0.4554483709878436</v>
       </c>
       <c r="J1001">
         <v>1.336916555918107</v>
       </c>
       <c r="K1001">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1001">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1001">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1001">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1001">
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
       <c r="A1002" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1002" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1002">
-        <v>1.239038147879077</v>
+        <v>0.5631230216257181</v>
       </c>
       <c r="D1002" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E1002">
-        <v>0.7835897768912332</v>
+        <v>0.4472446639277008</v>
       </c>
       <c r="F1002">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1002">
-        <v>0.01688096185212093</v>
+        <v>0.01315687697837428</v>
       </c>
       <c r="H1002">
-        <v>0.01551641022310877</v>
+        <v>0.0124527553360723</v>
       </c>
       <c r="I1002">
-        <v>0.4554483709878436</v>
+        <v>-0.1158783576980174</v>
       </c>
       <c r="J1002">
         <v>1.336916555918107</v>
       </c>
       <c r="K1002">
-        <v>5.85</v>
+        <v>4.71</v>
       </c>
       <c r="L1002">
-        <v>9.06</v>
+        <v>6.86</v>
       </c>
       <c r="M1002">
-        <v>5.51</v>
+        <v>4.49</v>
       </c>
       <c r="N1002">
-        <v>8.15</v>
+        <v>6.45</v>
       </c>
       <c r="O1002">
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
       <c r="A1003" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1003" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C1003">
-        <v>0.6430155249481748</v>
+        <v>1.252866050594761</v>
       </c>
       <c r="D1003" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E1003">
-        <v>0.4536605050134339</v>
+        <v>0.7496494525413828</v>
       </c>
       <c r="F1003">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1003">
-        <v>0.01331698447505182</v>
+        <v>0.01812713394940524</v>
       </c>
       <c r="H1003">
-        <v>0.01264633949498657</v>
+        <v>0.01647035054745861</v>
       </c>
       <c r="I1003">
-        <v>-0.1893550199347409</v>
+        <v>0.5032165980533785</v>
       </c>
       <c r="J1003">
-        <v>1.336916555918107</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K1003">
-        <v>4.74</v>
+        <v>6.29</v>
       </c>
       <c r="L1003">
-        <v>6.98</v>
+        <v>9.69</v>
       </c>
       <c r="M1003">
-        <v>4.56</v>
+        <v>5.86</v>
       </c>
       <c r="N1003">
-        <v>6.55</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1003">
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
       <c r="A1004" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1004" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C1004">
-        <v>0.5631230216257181</v>
+        <v>0.5613343697711297</v>
       </c>
       <c r="D1004" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E1004">
-        <v>0.4536605050134339</v>
+        <v>0.9021002101829456</v>
       </c>
       <c r="F1004">
         <v>1</v>
       </c>
       <c r="G1004">
-        <v>0.01315687697837428</v>
+        <v>0.01571866563022887</v>
       </c>
       <c r="H1004">
-        <v>0.01264633949498657</v>
+        <v>0.01691789978981706</v>
       </c>
       <c r="I1004">
-        <v>-0.1094625166122842</v>
+        <v>0.3407658404118159</v>
       </c>
       <c r="J1004">
-        <v>1.336916555918107</v>
+        <v>1.341356748713074</v>
       </c>
       <c r="K1004">
-        <v>4.71</v>
+        <v>5.65</v>
       </c>
       <c r="L1004">
-        <v>6.86</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1004">
-        <v>4.56</v>
+        <v>5.97</v>
       </c>
       <c r="N1004">
-        <v>6.55</v>
+        <v>8.91</v>
       </c>
       <c r="O1004">
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
       <c r="A1005" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1005" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C1005">
-        <v>1.252866050594761</v>
+        <v>1.213063020028516</v>
       </c>
       <c r="D1005" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E1005">
-        <v>0.7496494525413828</v>
+        <v>0.7591243145909603</v>
       </c>
       <c r="F1005">
         <v>-1</v>
       </c>
       <c r="G1005">
-        <v>0.01812713394940524</v>
+        <v>0.01690693697997148</v>
       </c>
       <c r="H1005">
-        <v>0.01647035054745861</v>
+        <v>0.01554087568540904</v>
       </c>
       <c r="I1005">
-        <v>0.5032165980533785</v>
+        <v>0.4539387054375554</v>
       </c>
       <c r="J1005">
         <v>1.341356748713074</v>
       </c>
       <c r="K1005">
-        <v>6.29</v>
+        <v>5.85</v>
       </c>
       <c r="L1005">
-        <v>9.69</v>
+        <v>9.06</v>
       </c>
       <c r="M1005">
-        <v>5.86</v>
+        <v>5.51</v>
       </c>
       <c r="N1005">
-        <v>8.609999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="O1005">
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
       <c r="A1006" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1006" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1006">
-        <v>0.5613343697711297</v>
+        <v>0.5422097135614194</v>
       </c>
       <c r="D1006" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E1006">
-        <v>0.9021002101829456</v>
+        <v>0.427308198278296</v>
       </c>
       <c r="F1006">
         <v>1</v>
       </c>
       <c r="G1006">
-        <v>0.01571866563022887</v>
+        <v>0.01317779028643858</v>
       </c>
       <c r="H1006">
-        <v>0.01691789978981706</v>
+        <v>0.01247269180172171</v>
       </c>
       <c r="I1006">
-        <v>0.3407658404118159</v>
+        <v>-0.1149015152831234</v>
       </c>
       <c r="J1006">
         <v>1.341356748713074</v>
       </c>
       <c r="K1006">
-        <v>5.65</v>
+        <v>4.71</v>
       </c>
       <c r="L1006">
-        <v>8.140000000000001</v>
+        <v>6.86</v>
       </c>
       <c r="M1006">
-        <v>5.97</v>
+        <v>4.49</v>
       </c>
       <c r="N1006">
-        <v>8.91</v>
+        <v>6.45</v>
       </c>
       <c r="O1006">
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
       <c r="A1007" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1007" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C1007">
-        <v>1.213063020028516</v>
+        <v>1.239490555786455</v>
       </c>
       <c r="D1007" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E1007">
-        <v>0.7591243145909603</v>
+        <v>0.7371883397310999</v>
       </c>
       <c r="F1007">
         <v>-1</v>
       </c>
       <c r="G1007">
-        <v>0.01690693697997148</v>
+        <v>0.01814050944421354</v>
       </c>
       <c r="H1007">
-        <v>0.01554087568540904</v>
+        <v>0.0164828116602689</v>
       </c>
       <c r="I1007">
-        <v>0.4539387054375554</v>
+        <v>0.5023022160553552</v>
       </c>
       <c r="J1007">
-        <v>1.341356748713074</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K1007">
-        <v>5.85</v>
+        <v>6.29</v>
       </c>
       <c r="L1007">
-        <v>9.06</v>
+        <v>9.69</v>
       </c>
       <c r="M1007">
-        <v>5.51</v>
+        <v>5.86</v>
       </c>
       <c r="N1007">
-        <v>8.15</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1007">
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
       <c r="A1008" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1008" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1008">
-        <v>0.6219690111000276</v>
+        <v>0.5493198156110441</v>
       </c>
       <c r="D1008" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E1008">
-        <v>0.4334132258683807</v>
+        <v>0.8894051856987506</v>
       </c>
       <c r="F1008">
         <v>1</v>
       </c>
       <c r="G1008">
-        <v>0.01333803098889997</v>
+        <v>0.01573068018438896</v>
       </c>
       <c r="H1008">
-        <v>0.01266658677413162</v>
+        <v>0.01693059481430125</v>
       </c>
       <c r="I1008">
-        <v>-0.1885557852316468</v>
+        <v>0.3400853700877065</v>
       </c>
       <c r="J1008">
-        <v>1.341356748713074</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K1008">
-        <v>4.74</v>
+        <v>5.65</v>
       </c>
       <c r="L1008">
-        <v>6.98</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1008">
-        <v>4.56</v>
+        <v>5.97</v>
       </c>
       <c r="N1008">
-        <v>6.55</v>
+        <v>8.91</v>
       </c>
       <c r="O1008">
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
       <c r="A1009" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1009" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C1009">
-        <v>0.5422097135614194</v>
+        <v>1.200623171915861</v>
       </c>
       <c r="D1009" t="s">
         <v>358</v>
       </c>
       <c r="E1009">
-        <v>0.4334132258683807</v>
+        <v>0.7474074661976742</v>
       </c>
       <c r="F1009">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1009">
-        <v>0.01317779028643858</v>
+        <v>0.01691937682808414</v>
       </c>
       <c r="H1009">
-        <v>0.01266658677413162</v>
+        <v>0.01555259253380233</v>
       </c>
       <c r="I1009">
-        <v>-0.1087964876930387</v>
+        <v>0.4532157057181871</v>
       </c>
       <c r="J1009">
-        <v>1.341356748713074</v>
+        <v>1.343483218475921</v>
       </c>
       <c r="K1009">
-        <v>4.71</v>
+        <v>5.85</v>
       </c>
       <c r="L1009">
-        <v>6.86</v>
+        <v>9.06</v>
       </c>
       <c r="M1009">
-        <v>4.56</v>
+        <v>5.51</v>
       </c>
       <c r="N1009">
-        <v>6.55</v>
+        <v>8.15</v>
       </c>
       <c r="O1009">
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
       <c r="A1010" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1010" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C1010">
-        <v>1.239490555786455</v>
+        <v>0.5321940409784105</v>
       </c>
       <c r="D1010" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E1010">
-        <v>0.7371883397310999</v>
+        <v>0.417760349043113</v>
       </c>
       <c r="F1010">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1010">
-        <v>0.01814050944421354</v>
+        <v>0.01318780595902159</v>
       </c>
       <c r="H1010">
-        <v>0.0164828116602689</v>
+        <v>0.01248223965095689</v>
       </c>
       <c r="I1010">
-        <v>0.5023022160553552</v>
+        <v>-0.1144336919352975</v>
       </c>
       <c r="J1010">
         <v>1.343483218475921</v>
       </c>
       <c r="K1010">
-        <v>6.29</v>
+        <v>4.71</v>
       </c>
       <c r="L1010">
-        <v>9.69</v>
+        <v>6.86</v>
       </c>
       <c r="M1010">
-        <v>5.86</v>
+        <v>4.49</v>
       </c>
       <c r="N1010">
-        <v>8.609999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="O1010">
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
       <c r="A1011" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1011" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C1011">
-        <v>0.5493198156110441</v>
+        <v>1.236392561837954</v>
       </c>
       <c r="D1011" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E1011">
-        <v>0.8894051856987506</v>
+        <v>0.7343021323323375</v>
       </c>
       <c r="F1011">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1011">
-        <v>0.01573068018438896</v>
+        <v>0.01814360743816204</v>
       </c>
       <c r="H1011">
-        <v>0.01693059481430125</v>
+        <v>0.01648569786766766</v>
       </c>
       <c r="I1011">
-        <v>0.3400853700877065</v>
+        <v>0.5020904295056168</v>
       </c>
       <c r="J1011">
-        <v>1.343483218475921</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K1011">
-        <v>5.65</v>
+        <v>6.29</v>
       </c>
       <c r="L1011">
-        <v>8.140000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="M1011">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="N1011">
-        <v>8.91</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O1011">
         <v>1</v>
       </c>
       <c r="P1011" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1012" spans="1:16">
       <c r="A1012" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1012" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1012">
-        <v>1.200623171915861</v>
+        <v>0.5465370388528523</v>
       </c>
       <c r="D1012" t="s">
         <v>357</v>
       </c>
       <c r="E1012">
-        <v>0.7474074661976742</v>
+        <v>0.8864648003454043</v>
       </c>
       <c r="F1012">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1012">
-        <v>0.01691937682808414</v>
+        <v>0.01573346296114715</v>
       </c>
       <c r="H1012">
-        <v>0.01555259253380233</v>
+        <v>0.0169335351996546</v>
       </c>
       <c r="I1012">
-        <v>0.4532157057181871</v>
+        <v>0.339927761492552</v>
       </c>
       <c r="J1012">
-        <v>1.343483218475921</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K1012">
-        <v>5.85</v>
+        <v>5.65</v>
       </c>
       <c r="L1012">
-        <v>9.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1012">
-        <v>5.51</v>
+        <v>5.97</v>
       </c>
       <c r="N1012">
-        <v>8.15</v>
+        <v>8.91</v>
       </c>
       <c r="O1012">
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
       <c r="A1013" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1013" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C1013">
-        <v>0.5321940409784105</v>
+        <v>1.197741889785697</v>
       </c>
       <c r="D1013" t="s">
         <v>358</v>
       </c>
       <c r="E1013">
-        <v>0.4237165237497988</v>
+        <v>0.7446936431998621</v>
       </c>
       <c r="F1013">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1013">
-        <v>0.01318780595902159</v>
+        <v>0.01692225811021431</v>
       </c>
       <c r="H1013">
-        <v>0.0126762834762502</v>
+        <v>0.01555530635680014</v>
       </c>
       <c r="I1013">
-        <v>-0.1084775172286117</v>
+        <v>0.4530482465858352</v>
       </c>
       <c r="J1013">
-        <v>1.343483218475921</v>
+        <v>1.343975745335778</v>
       </c>
       <c r="K1013">
-        <v>4.71</v>
+        <v>5.85</v>
       </c>
       <c r="L1013">
-        <v>6.86</v>
+        <v>9.06</v>
       </c>
       <c r="M1013">
-        <v>4.56</v>
+        <v>5.51</v>
       </c>
       <c r="N1013">
-        <v>6.55</v>
+        <v>8.15</v>
       </c>
       <c r="O1013">
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
       <c r="A1014" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1014" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C1014">
-        <v>1.236392561837954</v>
+        <v>0.5298742394684846</v>
       </c>
       <c r="D1014" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E1014">
-        <v>0.7343021323323375</v>
+        <v>0.415548903442355</v>
       </c>
       <c r="F1014">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1014">
-        <v>0.01814360743816204</v>
+        <v>0.01319012576053151</v>
       </c>
       <c r="H1014">
-        <v>0.01648569786766766</v>
+        <v>0.01248445109655765</v>
       </c>
       <c r="I1014">
-        <v>0.5020904295056168</v>
+        <v>-0.1143253360261296</v>
       </c>
       <c r="J1014">
         <v>1.343975745335778</v>
       </c>
       <c r="K1014">
-        <v>6.29</v>
+        <v>4.71</v>
       </c>
       <c r="L1014">
-        <v>9.69</v>
+        <v>6.86</v>
       </c>
       <c r="M1014">
-        <v>5.86</v>
+        <v>4.49</v>
       </c>
       <c r="N1014">
-        <v>8.609999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="O1014">
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
       <c r="A1015" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1015" t="s">
         <v>196</v>
       </c>
       <c r="C1015">
-        <v>0.5465370388528523</v>
+        <v>0.5594267069852092</v>
       </c>
       <c r="D1015" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E1015">
-        <v>0.8864648003454043</v>
+        <v>0.9000845027790625</v>
       </c>
       <c r="F1015">
         <v>1</v>
       </c>
       <c r="G1015">
-        <v>0.01573346296114715</v>
+        <v>0.01572057329301479</v>
       </c>
       <c r="H1015">
-        <v>0.0169335351996546</v>
+        <v>0.01691991549722094</v>
       </c>
       <c r="I1015">
-        <v>0.339927761492552</v>
+        <v>0.3406577957938532</v>
       </c>
       <c r="J1015">
-        <v>1.343975745335778</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1015">
         <v>5.65</v>
@@ -52558,39 +52561,39 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>472</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
       <c r="A1016" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1016" t="s">
         <v>197</v>
       </c>
       <c r="C1016">
-        <v>1.197741889785697</v>
+        <v>1.211087829356368</v>
       </c>
       <c r="D1016" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1016">
-        <v>0.7446936431998621</v>
+        <v>0.7572639213254</v>
       </c>
       <c r="F1016">
         <v>-1</v>
       </c>
       <c r="G1016">
-        <v>0.01692225811021431</v>
+        <v>0.01690891217064363</v>
       </c>
       <c r="H1016">
-        <v>0.01555530635680014</v>
+        <v>0.0155427360786746</v>
       </c>
       <c r="I1016">
-        <v>0.4530482465858352</v>
+        <v>0.4538239080309685</v>
       </c>
       <c r="J1016">
-        <v>1.343975745335778</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1016">
         <v>5.85</v>
@@ -52608,39 +52611,39 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>472</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
       <c r="A1017" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1017" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1017">
-        <v>0.5298742394684846</v>
+        <v>0.540619431840768</v>
       </c>
       <c r="D1017" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E1017">
-        <v>0.4214706012688509</v>
+        <v>0.4257921972324938</v>
       </c>
       <c r="F1017">
         <v>1</v>
       </c>
       <c r="G1017">
-        <v>0.01319012576053151</v>
+        <v>0.01317938056815923</v>
       </c>
       <c r="H1017">
-        <v>0.01267852939873115</v>
+        <v>0.01247420780276751</v>
       </c>
       <c r="I1017">
-        <v>-0.1084036381996336</v>
+        <v>-0.1148272346082742</v>
       </c>
       <c r="J1017">
-        <v>1.343975745335778</v>
+        <v>1.341694388144211</v>
       </c>
       <c r="K1017">
         <v>4.71</v>
@@ -52649,16 +52652,16 @@
         <v>6.86</v>
       </c>
       <c r="M1017">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="N1017">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="O1017">
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>472</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52669,28 +52672,28 @@
         <v>196</v>
       </c>
       <c r="C1018">
-        <v>0.5594267069852092</v>
+        <v>0.5528061783825207</v>
       </c>
       <c r="D1018" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E1018">
-        <v>0.9000845027790625</v>
+        <v>0.8930890061847165</v>
       </c>
       <c r="F1018">
         <v>1</v>
       </c>
       <c r="G1018">
-        <v>0.01572057329301479</v>
+        <v>0.01572719382161748</v>
       </c>
       <c r="H1018">
-        <v>0.01691991549722094</v>
+        <v>0.01692691099381528</v>
       </c>
       <c r="I1018">
-        <v>0.3406577957938532</v>
+        <v>0.3402828278021959</v>
       </c>
       <c r="J1018">
-        <v>1.341694388144211</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K1018">
         <v>5.65</v>
@@ -52708,7 +52711,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>191</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52719,28 +52722,28 @@
         <v>197</v>
       </c>
       <c r="C1019">
-        <v>1.211087829356368</v>
+        <v>1.204232945758894</v>
       </c>
       <c r="D1019" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1019">
-        <v>0.7572639213254</v>
+        <v>0.7508074412190604</v>
       </c>
       <c r="F1019">
         <v>-1</v>
       </c>
       <c r="G1019">
-        <v>0.01690891217064363</v>
+        <v>0.01691576705424111</v>
       </c>
       <c r="H1019">
-        <v>0.0155427360786746</v>
+        <v>0.01554919255878094</v>
       </c>
       <c r="I1019">
-        <v>0.4538239080309685</v>
+        <v>0.4534255045398332</v>
       </c>
       <c r="J1019">
-        <v>1.341694388144211</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K1019">
         <v>5.85</v>
@@ -52758,7 +52761,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>191</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52766,31 +52769,31 @@
         <v>2</v>
       </c>
       <c r="B1020" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1020">
-        <v>0.540619431840768</v>
+        <v>0.5351003717135701</v>
       </c>
       <c r="D1020" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E1020">
-        <v>0.4318735900623993</v>
+        <v>0.4205309275995601</v>
       </c>
       <c r="F1020">
         <v>1</v>
       </c>
       <c r="G1020">
-        <v>0.01317938056815923</v>
+        <v>0.01318489962828643</v>
       </c>
       <c r="H1020">
-        <v>0.0126681264099376</v>
+        <v>0.01247946907240044</v>
       </c>
       <c r="I1020">
-        <v>-0.1087458417783687</v>
+        <v>-0.1145694441140099</v>
       </c>
       <c r="J1020">
-        <v>1.341694388144211</v>
+        <v>1.342866163118138</v>
       </c>
       <c r="K1020">
         <v>4.71</v>
@@ -52799,16 +52802,16 @@
         <v>6.86</v>
       </c>
       <c r="M1020">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="N1020">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="O1020">
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>191</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52816,49 +52819,49 @@
         <v>0</v>
       </c>
       <c r="B1021" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1021">
-        <v>0.5528061783825207</v>
+        <v>1.194967273410384</v>
       </c>
       <c r="D1021" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E1021">
-        <v>0.8930890061847165</v>
+        <v>0.7420802865796947</v>
       </c>
       <c r="F1021">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1021">
-        <v>0.01572719382161748</v>
+        <v>0.01692503272658962</v>
       </c>
       <c r="H1021">
-        <v>0.01692691099381528</v>
+        <v>0.01555791971342031</v>
       </c>
       <c r="I1021">
-        <v>0.3402828278021959</v>
+        <v>0.4528869868306895</v>
       </c>
       <c r="J1021">
-        <v>1.342866163118138</v>
+        <v>1.344450038733268</v>
       </c>
       <c r="K1021">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1021">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1021">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1021">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1021">
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>473</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52866,631 +52869,631 @@
         <v>1</v>
       </c>
       <c r="B1022" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1022">
-        <v>1.204232945758894</v>
+        <v>0.5276403175663091</v>
       </c>
       <c r="D1022" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E1022">
-        <v>0.7508074412190604</v>
+        <v>0.4134193260876273</v>
       </c>
       <c r="F1022">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1022">
-        <v>0.01691576705424111</v>
+        <v>0.01319235968243369</v>
       </c>
       <c r="H1022">
-        <v>0.01554919255878094</v>
+        <v>0.01248658067391237</v>
       </c>
       <c r="I1022">
-        <v>0.4534255045398332</v>
+        <v>-0.1142209914786818</v>
       </c>
       <c r="J1022">
-        <v>1.342866163118138</v>
+        <v>1.344450038733268</v>
       </c>
       <c r="K1022">
-        <v>5.85</v>
+        <v>4.71</v>
       </c>
       <c r="L1022">
-        <v>9.06</v>
+        <v>6.86</v>
       </c>
       <c r="M1022">
-        <v>5.51</v>
+        <v>4.49</v>
       </c>
       <c r="N1022">
-        <v>8.15</v>
+        <v>6.45</v>
       </c>
       <c r="O1022">
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>473</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
       <c r="A1023" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1023" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C1023">
-        <v>0.5351003717135701</v>
+        <v>0.5168028977995238</v>
       </c>
       <c r="D1023" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E1023">
-        <v>0.4265302961812907</v>
+        <v>0.8550466017456912</v>
       </c>
       <c r="F1023">
         <v>1</v>
       </c>
       <c r="G1023">
-        <v>0.01318489962828643</v>
+        <v>0.01576319710220048</v>
       </c>
       <c r="H1023">
-        <v>0.01267346970381871</v>
+        <v>0.01696495339825431</v>
       </c>
       <c r="I1023">
-        <v>-0.1085700755322794</v>
+        <v>0.3382437039461674</v>
       </c>
       <c r="J1023">
-        <v>1.342866163118138</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1023">
-        <v>4.71</v>
+        <v>5.65</v>
       </c>
       <c r="L1023">
-        <v>6.86</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1023">
-        <v>4.56</v>
+        <v>5.97</v>
       </c>
       <c r="N1023">
-        <v>6.55</v>
+        <v>8.91</v>
       </c>
       <c r="O1023">
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
       <c r="A1024" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1024" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1024">
-        <v>0.5438572811570364</v>
+        <v>1.166955212765879</v>
       </c>
       <c r="D1024" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E1024">
-        <v>0.8836332687623916</v>
+        <v>0.7156962773230759</v>
       </c>
       <c r="F1024">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1024">
-        <v>0.01573614271884297</v>
+        <v>0.01695304478723412</v>
       </c>
       <c r="H1024">
-        <v>0.01693636673123761</v>
+        <v>0.01558430372267692</v>
       </c>
       <c r="I1024">
-        <v>0.3397759876053552</v>
+        <v>0.4512589354428034</v>
       </c>
       <c r="J1024">
-        <v>1.344450038733268</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1024">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1024">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1024">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1024">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1024">
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>192</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
       <c r="A1025" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1025" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1025">
-        <v>1.194967273410384</v>
+        <v>0.5050870174576563</v>
       </c>
       <c r="D1025" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E1025">
-        <v>0.7420802865796947</v>
+        <v>0.3919194709946652</v>
       </c>
       <c r="F1025">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1025">
-        <v>0.01692503272658962</v>
+        <v>0.01321491298254234</v>
       </c>
       <c r="H1025">
-        <v>0.01555791971342031</v>
+        <v>0.01250808052900534</v>
       </c>
       <c r="I1025">
-        <v>0.4528869868306895</v>
+        <v>-0.1131675464629911</v>
       </c>
       <c r="J1025">
-        <v>1.344450038733268</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1025">
-        <v>5.85</v>
+        <v>4.71</v>
       </c>
       <c r="L1025">
-        <v>9.06</v>
+        <v>6.86</v>
       </c>
       <c r="M1025">
-        <v>5.51</v>
+        <v>4.49</v>
       </c>
       <c r="N1025">
-        <v>8.15</v>
+        <v>6.45</v>
       </c>
       <c r="O1025">
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>192</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
       <c r="A1026" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1026" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C1026">
-        <v>0.5276403175663091</v>
+        <v>0.5065638875223204</v>
       </c>
       <c r="D1026" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E1026">
-        <v>0.4193078233762986</v>
+        <v>0.8442276829218152</v>
       </c>
       <c r="F1026">
         <v>1</v>
       </c>
       <c r="G1026">
-        <v>0.01319235968243369</v>
+        <v>0.01577343611247768</v>
       </c>
       <c r="H1026">
-        <v>0.0126806921766237</v>
+        <v>0.01697577231707819</v>
       </c>
       <c r="I1026">
-        <v>-0.1083324941900106</v>
+        <v>0.3376637953994948</v>
       </c>
       <c r="J1026">
-        <v>1.344450038733268</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1026">
-        <v>4.71</v>
+        <v>5.65</v>
       </c>
       <c r="L1026">
-        <v>6.86</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1026">
-        <v>4.56</v>
+        <v>5.97</v>
       </c>
       <c r="N1026">
-        <v>6.55</v>
+        <v>8.91</v>
       </c>
       <c r="O1026">
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>192</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
       <c r="A1027" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1027" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1027">
-        <v>0.5168028977995238</v>
+        <v>1.156353759647005</v>
       </c>
       <c r="D1027" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E1027">
-        <v>0.8550466017456912</v>
+        <v>0.705710977035042</v>
       </c>
       <c r="F1027">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1027">
-        <v>0.01576319710220048</v>
+        <v>0.016963646240353</v>
       </c>
       <c r="H1027">
-        <v>0.01696495339825431</v>
+        <v>0.01559428902296496</v>
       </c>
       <c r="I1027">
-        <v>0.3382437039461674</v>
+        <v>0.450642782611963</v>
       </c>
       <c r="J1027">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1027">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1027">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1027">
-        <v>5.97</v>
+        <v>5.51</v>
       </c>
       <c r="N1027">
-        <v>8.91</v>
+        <v>8.15</v>
       </c>
       <c r="O1027">
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
       <c r="A1028" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1028" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1028">
-        <v>1.166955212765879</v>
+        <v>0.4965514885363067</v>
       </c>
       <c r="D1028" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E1028">
-        <v>0.7156962773230759</v>
+        <v>0.3837826291991542</v>
       </c>
       <c r="F1028">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1028">
-        <v>0.01695304478723412</v>
+        <v>0.01322344851146369</v>
       </c>
       <c r="H1028">
-        <v>0.01558430372267692</v>
+        <v>0.01251621737080085</v>
       </c>
       <c r="I1028">
-        <v>0.4512589354428034</v>
+        <v>-0.1127688593371525</v>
       </c>
       <c r="J1028">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1028">
-        <v>5.85</v>
+        <v>4.71</v>
       </c>
       <c r="L1028">
-        <v>9.06</v>
+        <v>6.86</v>
       </c>
       <c r="M1028">
-        <v>5.51</v>
+        <v>4.49</v>
       </c>
       <c r="N1028">
-        <v>8.15</v>
+        <v>6.45</v>
       </c>
       <c r="O1028">
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
       <c r="A1029" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1029" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C1029">
-        <v>0.5050870174576563</v>
+        <v>0.5021328345691742</v>
       </c>
       <c r="D1029" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E1029">
-        <v>0.3974727812328904</v>
+        <v>0.8395456676775179</v>
       </c>
       <c r="F1029">
         <v>1</v>
       </c>
       <c r="G1029">
-        <v>0.01321491298254234</v>
+        <v>0.01577786716543083</v>
       </c>
       <c r="H1029">
-        <v>0.01270252721876711</v>
+        <v>0.01698045433232248</v>
       </c>
       <c r="I1029">
-        <v>-0.1076142362247658</v>
+        <v>0.3374128331083437</v>
       </c>
       <c r="J1029">
-        <v>1.349238425168226</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1029">
-        <v>4.71</v>
+        <v>5.65</v>
       </c>
       <c r="L1029">
-        <v>6.86</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M1029">
-        <v>4.56</v>
+        <v>5.97</v>
       </c>
       <c r="N1029">
-        <v>6.55</v>
+        <v>8.91</v>
       </c>
       <c r="O1029">
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
       <c r="A1030" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1030" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1030">
-        <v>0.5065638875223204</v>
+        <v>1.15176585526189</v>
       </c>
       <c r="D1030" t="s">
-        <v>356</v>
+        <v>194</v>
       </c>
       <c r="E1030">
-        <v>0.8442276829218152</v>
+        <v>0.654164954564739</v>
       </c>
       <c r="F1030">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1030">
-        <v>0.01577343611247768</v>
+        <v>0.01696823414473811</v>
       </c>
       <c r="H1030">
-        <v>0.01697577231707819</v>
+        <v>0.01514583504543526</v>
       </c>
       <c r="I1030">
-        <v>0.3376637953994948</v>
+        <v>0.4976009006971509</v>
       </c>
       <c r="J1030">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1030">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="L1030">
-        <v>8.140000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="M1030">
-        <v>5.97</v>
+        <v>5.36</v>
       </c>
       <c r="N1030">
-        <v>8.91</v>
+        <v>7.9</v>
       </c>
       <c r="O1030">
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
       <c r="A1031" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1031" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1031">
-        <v>1.156353759647005</v>
+        <v>0.4928576373134188</v>
       </c>
       <c r="D1031" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E1031">
-        <v>0.705710977035042</v>
+        <v>0.380261314551432</v>
       </c>
       <c r="F1031">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1031">
-        <v>0.016963646240353</v>
+        <v>0.01322714236268658</v>
       </c>
       <c r="H1031">
-        <v>0.01559428902296496</v>
+        <v>0.01251973868544857</v>
       </c>
       <c r="I1031">
-        <v>0.450642782611963</v>
+        <v>-0.1125963227619868</v>
       </c>
       <c r="J1031">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1031">
-        <v>5.85</v>
+        <v>4.71</v>
       </c>
       <c r="L1031">
-        <v>9.06</v>
+        <v>6.86</v>
       </c>
       <c r="M1031">
-        <v>5.51</v>
+        <v>4.49</v>
       </c>
       <c r="N1031">
-        <v>8.15</v>
+        <v>6.45</v>
       </c>
       <c r="O1031">
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
       <c r="A1032" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1032" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C1032">
-        <v>0.4965514885363067</v>
+        <v>1.149867923161882</v>
       </c>
       <c r="D1032" t="s">
-        <v>358</v>
+        <v>194</v>
       </c>
       <c r="E1032">
-        <v>0.3892090844427933</v>
+        <v>0.6524259945551591</v>
       </c>
       <c r="F1032">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1032">
-        <v>0.01322344851146369</v>
+        <v>0.01697013207683812</v>
       </c>
       <c r="H1032">
-        <v>0.01271079091555721</v>
+        <v>0.01514757400544484</v>
       </c>
       <c r="I1032">
-        <v>-0.1073424040935134</v>
+        <v>0.4974419286067224</v>
       </c>
       <c r="J1032">
-        <v>1.35105063937658</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1032">
-        <v>4.71</v>
+        <v>5.85</v>
       </c>
       <c r="L1032">
-        <v>6.86</v>
+        <v>9.06</v>
       </c>
       <c r="M1032">
-        <v>4.56</v>
+        <v>5.36</v>
       </c>
       <c r="N1032">
-        <v>6.55</v>
+        <v>7.9</v>
       </c>
       <c r="O1032">
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
       <c r="A1033" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1033" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1033">
-        <v>0.5021328345691742</v>
+        <v>0.4913295586482835</v>
       </c>
       <c r="D1033" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E1033">
-        <v>0.8395456676775179</v>
+        <v>0.3788046111105716</v>
       </c>
       <c r="F1033">
         <v>1</v>
       </c>
       <c r="G1033">
-        <v>0.01577786716543083</v>
+        <v>0.01322867044135172</v>
       </c>
       <c r="H1033">
-        <v>0.01698045433232248</v>
+        <v>0.01252119538888943</v>
       </c>
       <c r="I1033">
-        <v>0.3374128331083437</v>
+        <v>-0.1125249475377119</v>
       </c>
       <c r="J1033">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1033">
-        <v>5.65</v>
+        <v>4.71</v>
       </c>
       <c r="L1033">
-        <v>8.140000000000001</v>
+        <v>6.86</v>
       </c>
       <c r="M1033">
-        <v>5.97</v>
+        <v>4.49</v>
       </c>
       <c r="N1033">
-        <v>8.91</v>
+        <v>6.45</v>
       </c>
       <c r="O1033">
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
       <c r="A1034" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1034" t="s">
         <v>197</v>
       </c>
       <c r="C1034">
-        <v>1.15176585526189</v>
+        <v>1.146407603130467</v>
       </c>
       <c r="D1034" t="s">
-        <v>357</v>
+        <v>194</v>
       </c>
       <c r="E1034">
-        <v>0.7013897200842756</v>
+        <v>0.6492555132956062</v>
       </c>
       <c r="F1034">
         <v>-1</v>
       </c>
       <c r="G1034">
-        <v>0.01696823414473811</v>
+        <v>0.01697359239686954</v>
       </c>
       <c r="H1034">
-        <v>0.01559861027991572</v>
+        <v>0.01515074448670439</v>
       </c>
       <c r="I1034">
-        <v>0.4503761351776143</v>
+        <v>0.4971520898348611</v>
       </c>
       <c r="J1034">
-        <v>1.351834896536429</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1034">
         <v>5.85</v>
@@ -53499,48 +53502,48 @@
         <v>9.06</v>
       </c>
       <c r="M1034">
-        <v>5.51</v>
+        <v>5.36</v>
       </c>
       <c r="N1034">
-        <v>8.15</v>
+        <v>7.9</v>
       </c>
       <c r="O1034">
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
       <c r="A1035" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1035" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1035">
-        <v>0.4928576373134188</v>
+        <v>0.4885435573922221</v>
       </c>
       <c r="D1035" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E1035">
-        <v>0.3856328717938826</v>
+        <v>0.3761487415479987</v>
       </c>
       <c r="F1035">
         <v>1</v>
       </c>
       <c r="G1035">
-        <v>0.01322714236268658</v>
+        <v>0.01323145644260778</v>
       </c>
       <c r="H1035">
-        <v>0.01271436712820612</v>
+        <v>0.012523851258452</v>
       </c>
       <c r="I1035">
-        <v>-0.1072247655195362</v>
+        <v>-0.1123948158442234</v>
       </c>
       <c r="J1035">
-        <v>1.351834896536429</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1035">
         <v>4.71</v>
@@ -53549,16 +53552,16 @@
         <v>6.86</v>
       </c>
       <c r="M1035">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="N1035">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="O1035">
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53566,49 +53569,49 @@
         <v>0</v>
       </c>
       <c r="B1036" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C1036">
-        <v>0.5002997890366885</v>
+        <v>0.8389074160156742</v>
       </c>
       <c r="D1036" t="s">
-        <v>356</v>
+        <v>193</v>
       </c>
       <c r="E1036">
-        <v>0.8376088036369964</v>
+        <v>0.6263585300264847</v>
       </c>
       <c r="F1036">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1036">
-        <v>0.01577970021096331</v>
+        <v>0.01700109258398433</v>
       </c>
       <c r="H1036">
-        <v>0.01698239119636301</v>
+        <v>0.01757364146997352</v>
       </c>
       <c r="I1036">
-        <v>0.3373090146003079</v>
+        <v>0.2125488859891895</v>
       </c>
       <c r="J1036">
-        <v>1.352159329374037</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1036">
-        <v>5.65</v>
+        <v>5.97</v>
       </c>
       <c r="L1036">
-        <v>8.140000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="M1036">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="N1036">
-        <v>8.91</v>
+        <v>9.1</v>
       </c>
       <c r="O1036">
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>477</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -53616,99 +53619,99 @@
         <v>1</v>
       </c>
       <c r="B1037" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1037">
-        <v>1.149867923161882</v>
+        <v>0.412260351408773</v>
       </c>
       <c r="D1037" t="s">
-        <v>194</v>
+        <v>359</v>
       </c>
       <c r="E1037">
-        <v>0.6524259945551591</v>
+        <v>0.372260351408773</v>
       </c>
       <c r="F1037">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1037">
-        <v>0.01697013207683812</v>
+        <v>0.01256773964859123</v>
       </c>
       <c r="H1037">
-        <v>0.01514757400544484</v>
+        <v>0.01252773964859123</v>
       </c>
       <c r="I1037">
-        <v>0.4974419286067224</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J1037">
-        <v>1.352159329374037</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1037">
-        <v>5.85</v>
+        <v>4.49</v>
       </c>
       <c r="L1037">
-        <v>9.06</v>
+        <v>6.49</v>
       </c>
       <c r="M1037">
-        <v>5.36</v>
+        <v>4.49</v>
       </c>
       <c r="N1037">
-        <v>7.9</v>
+        <v>6.45</v>
       </c>
       <c r="O1037">
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>477</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1038" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1038">
+        <v>0.4222376325561195</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>359</v>
+      </c>
+      <c r="E1038">
+        <v>0.3822376325561194</v>
+      </c>
+      <c r="F1038">
+        <v>1</v>
+      </c>
+      <c r="G1038">
+        <v>0.01255776236744388</v>
+      </c>
+      <c r="H1038">
+        <v>0.01251776236744388</v>
+      </c>
+      <c r="I1038">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="J1038">
+        <v>1.351394736624472</v>
+      </c>
+      <c r="K1038">
+        <v>4.49</v>
+      </c>
+      <c r="L1038">
+        <v>6.49</v>
+      </c>
+      <c r="M1038">
+        <v>4.49</v>
+      </c>
+      <c r="N1038">
+        <v>6.45</v>
+      </c>
+      <c r="O1038">
+        <v>1</v>
+      </c>
+      <c r="P1038" t="s">
         <v>199</v>
-      </c>
-      <c r="C1038">
-        <v>0.4913295586482835</v>
-      </c>
-      <c r="D1038" t="s">
-        <v>358</v>
-      </c>
-      <c r="E1038">
-        <v>0.3841534580543895</v>
-      </c>
-      <c r="F1038">
-        <v>1</v>
-      </c>
-      <c r="G1038">
-        <v>0.01322867044135172</v>
-      </c>
-      <c r="H1038">
-        <v>0.01271584654194561</v>
-      </c>
-      <c r="I1038">
-        <v>-0.107176100593894</v>
-      </c>
-      <c r="J1038">
-        <v>1.352159329374037</v>
-      </c>
-      <c r="K1038">
-        <v>4.71</v>
-      </c>
-      <c r="L1038">
-        <v>6.86</v>
-      </c>
-      <c r="M1038">
-        <v>4.56</v>
-      </c>
-      <c r="N1038">
-        <v>6.55</v>
-      </c>
-      <c r="O1038">
-        <v>1</v>
-      </c>
-      <c r="P1038" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -53716,449 +53719,449 @@
         <v>0</v>
       </c>
       <c r="B1039" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C1039">
-        <v>0.4969577705448094</v>
+        <v>0.4221231123667568</v>
       </c>
       <c r="D1039" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E1039">
-        <v>0.8340775026818612</v>
+        <v>0.3821231123667568</v>
       </c>
       <c r="F1039">
         <v>1</v>
       </c>
       <c r="G1039">
-        <v>0.01578304222945519</v>
+        <v>0.01255787688763324</v>
       </c>
       <c r="H1039">
-        <v>0.01698592249731814</v>
+        <v>0.01251787688763324</v>
       </c>
       <c r="I1039">
-        <v>0.3371197321370518</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J1039">
-        <v>1.352750837071715</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1039">
-        <v>5.65</v>
+        <v>4.49</v>
       </c>
       <c r="L1039">
-        <v>8.140000000000001</v>
+        <v>6.49</v>
       </c>
       <c r="M1039">
-        <v>5.97</v>
+        <v>4.49</v>
       </c>
       <c r="N1039">
-        <v>8.91</v>
+        <v>6.45</v>
       </c>
       <c r="O1039">
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>478</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1040" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1040">
+        <v>0.4461583152635837</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>359</v>
+      </c>
+      <c r="E1040">
+        <v>0.4061583152635837</v>
+      </c>
+      <c r="F1040">
+        <v>1</v>
+      </c>
+      <c r="G1040">
+        <v>0.01253384168473642</v>
+      </c>
+      <c r="H1040">
+        <v>0.01249384168473642</v>
+      </c>
+      <c r="I1040">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="J1040">
+        <v>1.346067190364458</v>
+      </c>
+      <c r="K1040">
+        <v>4.49</v>
+      </c>
+      <c r="L1040">
+        <v>6.49</v>
+      </c>
+      <c r="M1040">
+        <v>4.49</v>
+      </c>
+      <c r="N1040">
+        <v>6.45</v>
+      </c>
+      <c r="O1040">
+        <v>1</v>
+      </c>
+      <c r="P1040" t="s">
         <v>197</v>
-      </c>
-      <c r="C1040">
-        <v>1.146407603130467</v>
-      </c>
-      <c r="D1040" t="s">
-        <v>194</v>
-      </c>
-      <c r="E1040">
-        <v>0.6492555132956062</v>
-      </c>
-      <c r="F1040">
-        <v>-1</v>
-      </c>
-      <c r="G1040">
-        <v>0.01697359239686954</v>
-      </c>
-      <c r="H1040">
-        <v>0.01515074448670439</v>
-      </c>
-      <c r="I1040">
-        <v>0.4971520898348611</v>
-      </c>
-      <c r="J1040">
-        <v>1.352750837071715</v>
-      </c>
-      <c r="K1040">
-        <v>5.85</v>
-      </c>
-      <c r="L1040">
-        <v>9.06</v>
-      </c>
-      <c r="M1040">
-        <v>5.36</v>
-      </c>
-      <c r="N1040">
-        <v>7.9</v>
-      </c>
-      <c r="O1040">
-        <v>1</v>
-      </c>
-      <c r="P1040" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1041" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C1041">
-        <v>0.4885435573922221</v>
+        <v>0.8240937125821999</v>
       </c>
       <c r="D1041" t="s">
+        <v>356</v>
+      </c>
+      <c r="E1041">
+        <v>0.5922029237616666</v>
+      </c>
+      <c r="F1041">
+        <v>-1</v>
+      </c>
+      <c r="G1041">
+        <v>0.0157559062874178</v>
+      </c>
+      <c r="H1041">
+        <v>0.01336779707623833</v>
+      </c>
+      <c r="I1041">
+        <v>0.2318907888205333</v>
+      </c>
+      <c r="J1041">
+        <v>1.347636513974332</v>
+      </c>
+      <c r="K1041">
+        <v>5.54</v>
+      </c>
+      <c r="L1041">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="M1041">
+        <v>4.74</v>
+      </c>
+      <c r="N1041">
+        <v>6.98</v>
+      </c>
+      <c r="O1041">
+        <v>1</v>
+      </c>
+      <c r="P1041" t="s">
         <v>358</v>
-      </c>
-      <c r="E1041">
-        <v>0.381456182952979</v>
-      </c>
-      <c r="F1041">
-        <v>1</v>
-      </c>
-      <c r="G1041">
-        <v>0.01323145644260778</v>
-      </c>
-      <c r="H1041">
-        <v>0.01271854381704702</v>
-      </c>
-      <c r="I1041">
-        <v>-0.1070873744392431</v>
-      </c>
-      <c r="J1041">
-        <v>1.352750837071715</v>
-      </c>
-      <c r="K1041">
-        <v>4.71</v>
-      </c>
-      <c r="L1041">
-        <v>6.86</v>
-      </c>
-      <c r="M1041">
-        <v>4.56</v>
-      </c>
-      <c r="N1041">
-        <v>6.55</v>
-      </c>
-      <c r="O1041">
-        <v>1</v>
-      </c>
-      <c r="P1041" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1042" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C1042">
-        <v>0.8389074160156742</v>
+        <v>0.8114319364950138</v>
       </c>
       <c r="D1042" t="s">
-        <v>193</v>
+        <v>356</v>
       </c>
       <c r="E1042">
-        <v>0.6263585300264847</v>
+        <v>0.5922029237616666</v>
       </c>
       <c r="F1042">
         <v>-1</v>
       </c>
       <c r="G1042">
-        <v>0.01700109258398433</v>
+        <v>0.01498856806350499</v>
       </c>
       <c r="H1042">
-        <v>0.01757364146997352</v>
+        <v>0.01336779707623833</v>
       </c>
       <c r="I1042">
-        <v>0.2125488859891895</v>
+        <v>0.2192290127333472</v>
       </c>
       <c r="J1042">
-        <v>1.353616848238581</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1042">
-        <v>5.97</v>
+        <v>5.26</v>
       </c>
       <c r="L1042">
-        <v>8.92</v>
+        <v>7.9</v>
       </c>
       <c r="M1042">
-        <v>6.26</v>
+        <v>4.74</v>
       </c>
       <c r="N1042">
-        <v>9.1</v>
+        <v>6.98</v>
       </c>
       <c r="O1042">
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1043" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C1043">
-        <v>0.4920648074520191</v>
+        <v>0.4391120522552487</v>
       </c>
       <c r="D1043" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E1043">
-        <v>0.8289074160156744</v>
+        <v>0.3991120522552487</v>
       </c>
       <c r="F1043">
         <v>1</v>
       </c>
       <c r="G1043">
-        <v>0.01578793519254798</v>
+        <v>0.01254088794774475</v>
       </c>
       <c r="H1043">
-        <v>0.01699109258398433</v>
+        <v>0.01250088794774475</v>
       </c>
       <c r="I1043">
-        <v>0.3368426085636553</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J1043">
-        <v>1.353616848238581</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1043">
-        <v>5.65</v>
+        <v>4.49</v>
       </c>
       <c r="L1043">
-        <v>8.140000000000001</v>
+        <v>6.49</v>
       </c>
       <c r="M1043">
-        <v>5.97</v>
+        <v>4.49</v>
       </c>
       <c r="N1043">
-        <v>8.91</v>
+        <v>6.45</v>
       </c>
       <c r="O1043">
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1044" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C1044">
-        <v>0.4844646447962857</v>
+        <v>0.8052084430909758</v>
       </c>
       <c r="D1044" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E1044">
-        <v>0.3775071720320726</v>
+        <v>0.5865946806561269</v>
       </c>
       <c r="F1044">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1044">
-        <v>0.01323553535520372</v>
+        <v>0.01499479155690902</v>
       </c>
       <c r="H1044">
-        <v>0.01272249282796793</v>
+        <v>0.01337340531934387</v>
       </c>
       <c r="I1044">
-        <v>-0.1069574727642131</v>
+        <v>0.218613762434849</v>
       </c>
       <c r="J1044">
-        <v>1.353616848238581</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1044">
-        <v>4.71</v>
+        <v>5.26</v>
       </c>
       <c r="L1044">
-        <v>6.86</v>
+        <v>7.9</v>
       </c>
       <c r="M1044">
-        <v>4.56</v>
+        <v>4.74</v>
       </c>
       <c r="N1044">
-        <v>6.55</v>
+        <v>6.98</v>
       </c>
       <c r="O1044">
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>355</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1045" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C1045">
-        <v>0.5046197380717317</v>
+        <v>0.4337996025624484</v>
       </c>
       <c r="D1045" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E1045">
-        <v>0.8421734223519017</v>
+        <v>0.3937996025624484</v>
       </c>
       <c r="F1045">
         <v>1</v>
       </c>
       <c r="G1045">
-        <v>0.01577538026192827</v>
+        <v>0.01254620039743755</v>
       </c>
       <c r="H1045">
-        <v>0.0169778265776481</v>
+        <v>0.01250620039743755</v>
       </c>
       <c r="I1045">
-        <v>0.3375536842801701</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J1045">
-        <v>1.351394736624472</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1045">
-        <v>5.65</v>
+        <v>4.49</v>
       </c>
       <c r="L1045">
-        <v>8.140000000000001</v>
+        <v>6.49</v>
       </c>
       <c r="M1045">
-        <v>5.97</v>
+        <v>4.49</v>
       </c>
       <c r="N1045">
-        <v>8.91</v>
+        <v>6.45</v>
       </c>
       <c r="O1045">
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1046" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C1046">
-        <v>1.154340790746838</v>
+        <v>0.7946438898107466</v>
       </c>
       <c r="D1046" t="s">
+        <v>356</v>
+      </c>
+      <c r="E1046">
+        <v>0.5770745318826878</v>
+      </c>
+      <c r="F1046">
+        <v>-1</v>
+      </c>
+      <c r="G1046">
+        <v>0.01500535611018925</v>
+      </c>
+      <c r="H1046">
+        <v>0.01338292546811731</v>
+      </c>
+      <c r="I1046">
+        <v>0.2175693579280589</v>
+      </c>
+      <c r="J1046">
+        <v>1.350828157830657</v>
+      </c>
+      <c r="K1046">
+        <v>5.26</v>
+      </c>
+      <c r="L1046">
+        <v>7.9</v>
+      </c>
+      <c r="M1046">
+        <v>4.74</v>
+      </c>
+      <c r="N1046">
+        <v>6.98</v>
+      </c>
+      <c r="O1046">
+        <v>1</v>
+      </c>
+      <c r="P1046" t="s">
         <v>194</v>
-      </c>
-      <c r="E1046">
-        <v>0.6565242116928287</v>
-      </c>
-      <c r="F1046">
-        <v>-1</v>
-      </c>
-      <c r="G1046">
-        <v>0.01696565920925316</v>
-      </c>
-      <c r="H1046">
-        <v>0.01514347578830717</v>
-      </c>
-      <c r="I1046">
-        <v>0.4978165790540094</v>
-      </c>
-      <c r="J1046">
-        <v>1.351394736624472</v>
-      </c>
-      <c r="K1046">
-        <v>5.85</v>
-      </c>
-      <c r="L1046">
-        <v>9.06</v>
-      </c>
-      <c r="M1046">
-        <v>5.36</v>
-      </c>
-      <c r="N1046">
-        <v>7.9</v>
-      </c>
-      <c r="O1046">
-        <v>1</v>
-      </c>
-      <c r="P1046" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1047" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C1047">
-        <v>0.4949307904987359</v>
+        <v>0.4247815713403513</v>
       </c>
       <c r="D1047" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E1047">
-        <v>0.3876400009924064</v>
+        <v>0.3847815713403513</v>
       </c>
       <c r="F1047">
         <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.01322506920950126</v>
+        <v>0.01255521842865965</v>
       </c>
       <c r="H1047">
-        <v>0.01271235999900759</v>
+        <v>0.01251521842865965</v>
       </c>
       <c r="I1047">
-        <v>-0.1072907895063295</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J1047">
-        <v>1.351394736624472</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1047">
-        <v>4.71</v>
+        <v>4.49</v>
       </c>
       <c r="L1047">
-        <v>6.86</v>
+        <v>6.49</v>
       </c>
       <c r="M1047">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="N1047">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54166,81 +54169,81 @@
         <v>0</v>
       </c>
       <c r="B1048" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C1048">
-        <v>0.4948106590751502</v>
+        <v>0.7954040719633015</v>
       </c>
       <c r="D1048" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E1048">
-        <v>0.3875236954103372</v>
+        <v>0.577759562947918</v>
       </c>
       <c r="F1048">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.01322518934092485</v>
+        <v>0.0150045959280367</v>
       </c>
       <c r="H1048">
-        <v>0.01271247630458966</v>
+        <v>0.01338224043705208</v>
       </c>
       <c r="I1048">
-        <v>-0.1072869636648131</v>
+        <v>0.2176445090153836</v>
       </c>
       <c r="J1048">
-        <v>1.351420242234575</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1048">
-        <v>4.71</v>
+        <v>5.26</v>
       </c>
       <c r="L1048">
-        <v>6.86</v>
+        <v>7.9</v>
       </c>
       <c r="M1048">
-        <v>4.56</v>
+        <v>4.74</v>
       </c>
       <c r="N1048">
-        <v>6.55</v>
+        <v>6.98</v>
       </c>
       <c r="O1048">
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1049" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C1049">
-        <v>0.4461583152635837</v>
+        <v>0.4254304720751367</v>
       </c>
       <c r="D1049" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E1049">
-        <v>0.4119336119380721</v>
+        <v>0.3854304720751367</v>
       </c>
       <c r="F1049">
         <v>1</v>
       </c>
       <c r="G1049">
-        <v>0.01253384168473642</v>
+        <v>0.01255456952792486</v>
       </c>
       <c r="H1049">
-        <v>0.01268806638806193</v>
+        <v>0.01251456952792486</v>
       </c>
       <c r="I1049">
-        <v>-0.03422470332551164</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J1049">
-        <v>1.346067190364458</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1049">
         <v>4.49</v>
@@ -54249,16 +54252,16 @@
         <v>6.49</v>
       </c>
       <c r="M1049">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="N1049">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>197</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -54266,149 +54269,149 @@
         <v>0</v>
       </c>
       <c r="B1050" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1050">
+        <v>0.4167478384678054</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>359</v>
+      </c>
+      <c r="E1050">
+        <v>0.3767478384678054</v>
+      </c>
+      <c r="F1050">
+        <v>1</v>
+      </c>
+      <c r="G1050">
+        <v>0.01256325216153219</v>
+      </c>
+      <c r="H1050">
+        <v>0.0125232521615322</v>
+      </c>
+      <c r="I1050">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="J1050">
+        <v>1.352617407913629</v>
+      </c>
+      <c r="K1050">
+        <v>4.49</v>
+      </c>
+      <c r="L1050">
+        <v>6.49</v>
+      </c>
+      <c r="M1050">
+        <v>4.49</v>
+      </c>
+      <c r="N1050">
+        <v>6.45</v>
+      </c>
+      <c r="O1050">
+        <v>1</v>
+      </c>
+      <c r="P1050" t="s">
         <v>202</v>
-      </c>
-      <c r="C1050">
-        <v>0.8240937125821999</v>
-      </c>
-      <c r="D1050" t="s">
-        <v>198</v>
-      </c>
-      <c r="E1050">
-        <v>0.5922029237616666</v>
-      </c>
-      <c r="F1050">
-        <v>-1</v>
-      </c>
-      <c r="G1050">
-        <v>0.0157559062874178</v>
-      </c>
-      <c r="H1050">
-        <v>0.01336779707623833</v>
-      </c>
-      <c r="I1050">
-        <v>0.2318907888205333</v>
-      </c>
-      <c r="J1050">
-        <v>1.347636513974332</v>
-      </c>
-      <c r="K1050">
-        <v>5.54</v>
-      </c>
-      <c r="L1050">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="M1050">
-        <v>4.74</v>
-      </c>
-      <c r="N1050">
-        <v>6.98</v>
-      </c>
-      <c r="O1050">
-        <v>1</v>
-      </c>
-      <c r="P1050" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1051" t="s">
         <v>203</v>
       </c>
       <c r="C1051">
-        <v>0.8114319364950138</v>
+        <v>0.6665982265956414</v>
       </c>
       <c r="D1051" t="s">
         <v>198</v>
       </c>
       <c r="E1051">
-        <v>0.5922029237616666</v>
+        <v>0.4757007566940814</v>
       </c>
       <c r="F1051">
         <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.01498856806350499</v>
+        <v>0.01373340177340436</v>
       </c>
       <c r="H1051">
-        <v>0.01336779707623833</v>
+        <v>0.01324429924330592</v>
       </c>
       <c r="I1051">
-        <v>0.2192290127333472</v>
+        <v>0.19089746990156</v>
       </c>
       <c r="J1051">
-        <v>1.347636513974332</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1051">
-        <v>5.26</v>
+        <v>4.82</v>
       </c>
       <c r="L1051">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="M1051">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="N1051">
-        <v>6.98</v>
+        <v>6.86</v>
       </c>
       <c r="O1051">
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>357</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1052" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C1052">
-        <v>0.8052084430909758</v>
+        <v>0.4039058168909611</v>
       </c>
       <c r="D1052" t="s">
-        <v>198</v>
+        <v>359</v>
       </c>
       <c r="E1052">
-        <v>0.5865946806561269</v>
+        <v>0.363905816890961</v>
       </c>
       <c r="F1052">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1052">
-        <v>0.01499479155690902</v>
+        <v>0.01257609418310904</v>
       </c>
       <c r="H1052">
-        <v>0.01337340531934387</v>
+        <v>0.01253609418310904</v>
       </c>
       <c r="I1052">
-        <v>0.218613762434849</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J1052">
-        <v>1.34881968762529</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1052">
-        <v>5.26</v>
+        <v>4.49</v>
       </c>
       <c r="L1052">
-        <v>7.9</v>
+        <v>6.49</v>
       </c>
       <c r="M1052">
-        <v>4.74</v>
+        <v>4.49</v>
       </c>
       <c r="N1052">
-        <v>6.98</v>
+        <v>6.45</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -54416,349 +54419,99 @@
         <v>0</v>
       </c>
       <c r="B1053" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C1053">
-        <v>0.7946438898107466</v>
+        <v>0.6493738814716474</v>
       </c>
       <c r="D1053" t="s">
         <v>198</v>
       </c>
       <c r="E1053">
-        <v>0.5770745318826878</v>
+        <v>0.4714481211940544</v>
       </c>
       <c r="F1053">
         <v>-1</v>
       </c>
       <c r="G1053">
-        <v>0.01500535611018925</v>
+        <v>0.01367062611852835</v>
       </c>
       <c r="H1053">
-        <v>0.01338292546811731</v>
+        <v>0.01324855187880595</v>
       </c>
       <c r="I1053">
-        <v>0.2175693579280589</v>
+        <v>0.177925760277593</v>
       </c>
       <c r="J1053">
-        <v>1.350828157830657</v>
+        <v>1.356380441360074</v>
       </c>
       <c r="K1053">
-        <v>5.26</v>
+        <v>4.8</v>
       </c>
       <c r="L1053">
-        <v>7.9</v>
+        <v>7.16</v>
       </c>
       <c r="M1053">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="N1053">
-        <v>6.98</v>
+        <v>6.86</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1054" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1054">
+        <v>0.3998518182932695</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>359</v>
+      </c>
+      <c r="E1054">
+        <v>0.3598518182932695</v>
+      </c>
+      <c r="F1054">
+        <v>1</v>
+      </c>
+      <c r="G1054">
+        <v>0.01258014818170673</v>
+      </c>
+      <c r="H1054">
+        <v>0.01254014818170673</v>
+      </c>
+      <c r="I1054">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="J1054">
+        <v>1.356380441360074</v>
+      </c>
+      <c r="K1054">
+        <v>4.49</v>
+      </c>
+      <c r="L1054">
+        <v>6.49</v>
+      </c>
+      <c r="M1054">
+        <v>4.49</v>
+      </c>
+      <c r="N1054">
+        <v>6.45</v>
+      </c>
+      <c r="O1054">
+        <v>1</v>
+      </c>
+      <c r="P1054" t="s">
         <v>203</v>
-      </c>
-      <c r="C1054">
-        <v>0.7954040719633015</v>
-      </c>
-      <c r="D1054" t="s">
-        <v>198</v>
-      </c>
-      <c r="E1054">
-        <v>0.577759562947918</v>
-      </c>
-      <c r="F1054">
-        <v>-1</v>
-      </c>
-      <c r="G1054">
-        <v>0.0150045959280367</v>
-      </c>
-      <c r="H1054">
-        <v>0.01338224043705208</v>
-      </c>
-      <c r="I1054">
-        <v>0.2176445090153836</v>
-      </c>
-      <c r="J1054">
-        <v>1.350683636508878</v>
-      </c>
-      <c r="K1054">
-        <v>5.26</v>
-      </c>
-      <c r="L1054">
-        <v>7.9</v>
-      </c>
-      <c r="M1054">
-        <v>4.74</v>
-      </c>
-      <c r="N1054">
-        <v>6.98</v>
-      </c>
-      <c r="O1054">
-        <v>1</v>
-      </c>
-      <c r="P1054" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="1055" spans="1:16">
-      <c r="A1055" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>201</v>
-      </c>
-      <c r="C1055">
-        <v>0.4254304720751367</v>
-      </c>
-      <c r="D1055" t="s">
-        <v>358</v>
-      </c>
-      <c r="E1055">
-        <v>0.3908826175195159</v>
-      </c>
-      <c r="F1055">
-        <v>1</v>
-      </c>
-      <c r="G1055">
-        <v>0.01255456952792486</v>
-      </c>
-      <c r="H1055">
-        <v>0.01270911738248048</v>
-      </c>
-      <c r="I1055">
-        <v>-0.03454785455562082</v>
-      </c>
-      <c r="J1055">
-        <v>1.350683636508878</v>
-      </c>
-      <c r="K1055">
-        <v>4.49</v>
-      </c>
-      <c r="L1055">
-        <v>6.49</v>
-      </c>
-      <c r="M1055">
-        <v>4.56</v>
-      </c>
-      <c r="N1055">
-        <v>6.55</v>
-      </c>
-      <c r="O1055">
-        <v>1</v>
-      </c>
-      <c r="P1055" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="1056" spans="1:16">
-      <c r="A1056" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>201</v>
-      </c>
-      <c r="C1056">
-        <v>0.4167478384678054</v>
-      </c>
-      <c r="D1056" t="s">
-        <v>358</v>
-      </c>
-      <c r="E1056">
-        <v>0.3820646199138515</v>
-      </c>
-      <c r="F1056">
-        <v>1</v>
-      </c>
-      <c r="G1056">
-        <v>0.01256325216153219</v>
-      </c>
-      <c r="H1056">
-        <v>0.01271793538008615</v>
-      </c>
-      <c r="I1056">
-        <v>-0.03468321855395384</v>
-      </c>
-      <c r="J1056">
-        <v>1.352617407913629</v>
-      </c>
-      <c r="K1056">
-        <v>4.49</v>
-      </c>
-      <c r="L1056">
-        <v>6.49</v>
-      </c>
-      <c r="M1056">
-        <v>4.56</v>
-      </c>
-      <c r="N1056">
-        <v>6.55</v>
-      </c>
-      <c r="O1056">
-        <v>1</v>
-      </c>
-      <c r="P1056" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="1057" spans="1:16">
-      <c r="A1057" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>204</v>
-      </c>
-      <c r="C1057">
-        <v>0.6665982265956414</v>
-      </c>
-      <c r="D1057" t="s">
-        <v>198</v>
-      </c>
-      <c r="E1057">
-        <v>0.5550364303035975</v>
-      </c>
-      <c r="F1057">
-        <v>-1</v>
-      </c>
-      <c r="G1057">
-        <v>0.01373340177340436</v>
-      </c>
-      <c r="H1057">
-        <v>0.0134049635696964</v>
-      </c>
-      <c r="I1057">
-        <v>0.1115617962920439</v>
-      </c>
-      <c r="J1057">
-        <v>1.355477546349452</v>
-      </c>
-      <c r="K1057">
-        <v>4.82</v>
-      </c>
-      <c r="L1057">
-        <v>7.2</v>
-      </c>
-      <c r="M1057">
-        <v>4.74</v>
-      </c>
-      <c r="N1057">
-        <v>6.98</v>
-      </c>
-      <c r="O1057">
-        <v>1</v>
-      </c>
-      <c r="P1057" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1058" spans="1:16">
-      <c r="A1058" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>201</v>
-      </c>
-      <c r="C1058">
-        <v>0.4039058168909611</v>
-      </c>
-      <c r="D1058" t="s">
-        <v>358</v>
-      </c>
-      <c r="E1058">
-        <v>0.3690223886464992</v>
-      </c>
-      <c r="F1058">
-        <v>1</v>
-      </c>
-      <c r="G1058">
-        <v>0.01257609418310904</v>
-      </c>
-      <c r="H1058">
-        <v>0.0127309776113535</v>
-      </c>
-      <c r="I1058">
-        <v>-0.03488342824446189</v>
-      </c>
-      <c r="J1058">
-        <v>1.355477546349452</v>
-      </c>
-      <c r="K1058">
-        <v>4.49</v>
-      </c>
-      <c r="L1058">
-        <v>6.49</v>
-      </c>
-      <c r="M1058">
-        <v>4.56</v>
-      </c>
-      <c r="N1058">
-        <v>6.55</v>
-      </c>
-      <c r="O1058">
-        <v>1</v>
-      </c>
-      <c r="P1058" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1059" spans="1:16">
-      <c r="A1059" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>201</v>
-      </c>
-      <c r="C1059">
-        <v>0.3998518182932695</v>
-      </c>
-      <c r="D1059" t="s">
-        <v>358</v>
-      </c>
-      <c r="E1059">
-        <v>0.3649051873980653</v>
-      </c>
-      <c r="F1059">
-        <v>1</v>
-      </c>
-      <c r="G1059">
-        <v>0.01258014818170673</v>
-      </c>
-      <c r="H1059">
-        <v>0.01273509481260193</v>
-      </c>
-      <c r="I1059">
-        <v>-0.03494663089520422</v>
-      </c>
-      <c r="J1059">
-        <v>1.356380441360074</v>
-      </c>
-      <c r="K1059">
-        <v>4.49</v>
-      </c>
-      <c r="L1059">
-        <v>6.49</v>
-      </c>
-      <c r="M1059">
-        <v>4.56</v>
-      </c>
-      <c r="N1059">
-        <v>6.55</v>
-      </c>
-      <c r="O1059">
-        <v>1</v>
-      </c>
-      <c r="P1059" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3213" uniqueCount="486">
   <si>
     <t>trade_time</t>
   </si>
@@ -619,16 +619,10 @@
     <t>2021-11-08</t>
   </si>
   <si>
-    <t>2021-09-30</t>
+    <t>2021-11-15</t>
   </si>
   <si>
     <t>2021-10-11</t>
-  </si>
-  <si>
-    <t>2021-11-15</t>
-  </si>
-  <si>
-    <t>2021-11-09</t>
   </si>
   <si>
     <t>2021-11-10</t>
@@ -638,6 +632,12 @@
   </si>
   <si>
     <t>2021-10-26</t>
+  </si>
+  <si>
+    <t>2021-11-16</t>
+  </si>
+  <si>
+    <t>2021-10-25</t>
   </si>
   <si>
     <t>2021-10-28</t>
@@ -1108,7 +1108,10 @@
     <t>2021-10-20</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-09</t>
+  </si>
+  <si>
+    <t>2021-11-17</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1468,7 +1471,7 @@
     <t>2021-09-29</t>
   </si>
   <si>
-    <t>2021-10-25</t>
+    <t>2021-09-30</t>
   </si>
 </sst>
 </file>
@@ -1826,7 +1829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1058"/>
+  <dimension ref="A1:P1067"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1923,7 +1926,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1973,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2023,7 +2026,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2073,7 +2076,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2123,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2173,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2223,7 +2226,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2523,7 +2526,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2573,7 +2576,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2623,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2673,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2723,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2773,7 +2776,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2823,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2873,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2923,7 +2926,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3173,7 +3176,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3223,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3273,7 +3276,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3323,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3373,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3423,7 +3426,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3473,7 +3476,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3523,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3573,7 +3576,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3623,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3673,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3723,7 +3726,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4023,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4073,7 +4076,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4123,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4173,7 +4176,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4223,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4273,7 +4276,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4323,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4373,7 +4376,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4423,7 +4426,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4473,7 +4476,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4523,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4573,7 +4576,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4623,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4673,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4723,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4773,7 +4776,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4823,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4873,7 +4876,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4923,7 +4926,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4973,7 +4976,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5023,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5473,7 +5476,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5523,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5573,7 +5576,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5623,7 +5626,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5673,7 +5676,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5723,7 +5726,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6123,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6173,7 +6176,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6223,7 +6226,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6273,7 +6276,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6323,7 +6326,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6373,7 +6376,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6623,7 +6626,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6673,7 +6676,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6723,7 +6726,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6773,7 +6776,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6823,7 +6826,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6873,7 +6876,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6923,7 +6926,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6973,7 +6976,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7023,7 +7026,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7073,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7123,7 +7126,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7173,7 +7176,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7223,7 +7226,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7273,7 +7276,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7323,7 +7326,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7373,7 +7376,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7423,7 +7426,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7473,7 +7476,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7523,7 +7526,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7573,7 +7576,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7623,7 +7626,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7673,7 +7676,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7723,7 +7726,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7773,7 +7776,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7823,7 +7826,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7873,7 +7876,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7923,7 +7926,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7973,7 +7976,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8023,7 +8026,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8073,7 +8076,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8123,7 +8126,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8173,7 +8176,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8223,7 +8226,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8273,7 +8276,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8323,7 +8326,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8373,7 +8376,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8423,7 +8426,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8473,7 +8476,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8523,7 +8526,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8573,7 +8576,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8623,7 +8626,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8673,7 +8676,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8723,7 +8726,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8773,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8823,7 +8826,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8873,7 +8876,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8923,7 +8926,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8973,7 +8976,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9023,7 +9026,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9073,7 +9076,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9123,7 +9126,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9173,7 +9176,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9223,7 +9226,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9273,7 +9276,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9523,7 +9526,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9573,7 +9576,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9623,7 +9626,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9673,7 +9676,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9723,7 +9726,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9773,7 +9776,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9823,7 +9826,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9873,7 +9876,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10223,7 +10226,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10273,7 +10276,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10323,7 +10326,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10573,7 +10576,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10623,7 +10626,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10673,7 +10676,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10723,7 +10726,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10773,7 +10776,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10823,7 +10826,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10873,7 +10876,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10923,7 +10926,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10973,7 +10976,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11023,7 +11026,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11073,7 +11076,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11123,7 +11126,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11173,7 +11176,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11573,7 +11576,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11823,7 +11826,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11873,7 +11876,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11923,7 +11926,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11973,7 +11976,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12023,7 +12026,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12073,7 +12076,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12123,7 +12126,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12173,7 +12176,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12223,7 +12226,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12273,7 +12276,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12323,7 +12326,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12373,7 +12376,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12423,7 +12426,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12473,7 +12476,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12523,7 +12526,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12573,7 +12576,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12623,7 +12626,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16473,7 +16476,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16523,7 +16526,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16573,7 +16576,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16623,7 +16626,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16673,7 +16676,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16723,7 +16726,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16923,7 +16926,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16973,7 +16976,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17023,7 +17026,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17073,7 +17076,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17123,7 +17126,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17173,7 +17176,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17423,7 +17426,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17473,7 +17476,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17523,7 +17526,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17573,7 +17576,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17623,7 +17626,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17673,7 +17676,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17723,7 +17726,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17773,7 +17776,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17823,7 +17826,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18973,7 +18976,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19023,7 +19026,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19073,7 +19076,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19123,7 +19126,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19173,7 +19176,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19223,7 +19226,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19273,7 +19276,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19323,7 +19326,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19373,7 +19376,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19423,7 +19426,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -20023,7 +20026,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20073,7 +20076,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20123,7 +20126,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20173,7 +20176,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20223,7 +20226,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20273,7 +20276,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -22023,7 +22026,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22073,7 +22076,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22123,7 +22126,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22173,7 +22176,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22223,7 +22226,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22273,7 +22276,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22323,7 +22326,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22373,7 +22376,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22423,7 +22426,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22473,7 +22476,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22523,7 +22526,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22573,7 +22576,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22623,7 +22626,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22673,7 +22676,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22723,7 +22726,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22773,7 +22776,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22823,7 +22826,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22873,7 +22876,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22923,7 +22926,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23273,7 +23276,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23323,7 +23326,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23373,7 +23376,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23423,7 +23426,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23473,7 +23476,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23523,7 +23526,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23573,7 +23576,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23623,7 +23626,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23673,7 +23676,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23723,7 +23726,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23773,7 +23776,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23823,7 +23826,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23873,7 +23876,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23923,7 +23926,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23973,7 +23976,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24023,7 +24026,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24073,7 +24076,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24123,7 +24126,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24173,7 +24176,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24223,7 +24226,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24273,7 +24276,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24323,7 +24326,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24723,7 +24726,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24773,7 +24776,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24823,7 +24826,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24873,7 +24876,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24923,7 +24926,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24973,7 +24976,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25023,7 +25026,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25623,7 +25626,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25673,7 +25676,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25723,7 +25726,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25773,7 +25776,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25823,7 +25826,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25873,7 +25876,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25923,7 +25926,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25973,7 +25976,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26023,7 +26026,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26073,7 +26076,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26123,7 +26126,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26173,7 +26176,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26223,7 +26226,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26273,7 +26276,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26323,7 +26326,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26373,7 +26376,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26423,7 +26426,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26473,7 +26476,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26523,7 +26526,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26573,7 +26576,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26773,7 +26776,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26823,7 +26826,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26873,7 +26876,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26923,7 +26926,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26973,7 +26976,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27023,7 +27026,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27073,7 +27076,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -28023,7 +28026,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28073,7 +28076,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28123,7 +28126,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29423,7 +29426,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29473,7 +29476,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29523,7 +29526,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29573,7 +29576,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29623,7 +29626,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29673,7 +29676,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29723,7 +29726,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29773,7 +29776,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29823,7 +29826,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29873,7 +29876,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30173,7 +30176,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30223,7 +30226,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30273,7 +30276,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30323,7 +30326,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30373,7 +30376,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30423,7 +30426,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30473,7 +30476,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30523,7 +30526,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30573,7 +30576,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30623,7 +30626,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30673,7 +30676,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30873,7 +30876,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30923,7 +30926,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30973,7 +30976,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31023,7 +31026,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31073,7 +31076,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31123,7 +31126,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31173,7 +31176,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31223,7 +31226,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31273,7 +31276,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31573,7 +31576,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31623,7 +31626,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31673,7 +31676,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31723,7 +31726,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31773,7 +31776,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31823,7 +31826,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31873,7 +31876,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31923,7 +31926,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31973,7 +31976,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32023,7 +32026,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32073,7 +32076,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32123,7 +32126,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32723,7 +32726,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32773,7 +32776,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32823,7 +32826,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32873,7 +32876,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32923,7 +32926,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32973,7 +32976,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33023,7 +33026,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33073,7 +33076,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33123,7 +33126,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33173,7 +33176,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33373,7 +33376,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33423,7 +33426,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33473,7 +33476,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33523,7 +33526,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33573,7 +33576,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34473,7 +34476,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34523,7 +34526,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34573,7 +34576,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34623,7 +34626,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34673,7 +34676,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34723,7 +34726,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34773,7 +34776,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34823,7 +34826,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34873,7 +34876,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35523,7 +35526,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35573,7 +35576,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35623,7 +35626,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35673,7 +35676,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35723,7 +35726,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35773,7 +35776,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35823,7 +35826,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35873,7 +35876,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35923,7 +35926,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36323,7 +36326,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36373,7 +36376,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36423,7 +36426,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36473,7 +36476,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36523,7 +36526,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36573,7 +36576,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36623,7 +36626,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36673,7 +36676,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36723,7 +36726,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36773,7 +36776,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36823,7 +36826,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36873,7 +36876,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36923,7 +36926,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37223,7 +37226,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37273,7 +37276,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37323,7 +37326,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37373,7 +37376,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37673,7 +37676,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37723,7 +37726,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37773,7 +37776,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37823,7 +37826,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37873,7 +37876,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37923,7 +37926,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37973,7 +37976,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38023,7 +38026,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38073,7 +38076,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38123,7 +38126,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38373,7 +38376,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38423,7 +38426,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38473,7 +38476,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38523,7 +38526,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38573,7 +38576,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39173,7 +39176,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39223,7 +39226,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39273,7 +39276,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39323,7 +39326,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39373,7 +39376,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39423,7 +39426,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39473,7 +39476,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39523,7 +39526,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39573,7 +39576,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39623,7 +39626,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40423,7 +40426,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40473,7 +40476,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40523,7 +40526,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40573,7 +40576,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40623,7 +40626,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40673,7 +40676,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40723,7 +40726,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42423,7 +42426,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42473,7 +42476,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42523,7 +42526,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42573,7 +42576,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42623,7 +42626,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43173,7 +43176,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43223,7 +43226,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43273,7 +43276,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43323,7 +43326,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43373,7 +43376,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43423,7 +43426,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43573,7 +43576,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43623,7 +43626,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43673,7 +43676,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43723,7 +43726,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43773,7 +43776,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43823,7 +43826,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43873,7 +43876,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43923,7 +43926,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43973,7 +43976,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44023,7 +44026,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44073,7 +44076,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44123,7 +44126,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44173,7 +44176,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44223,7 +44226,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44273,7 +44276,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44323,7 +44326,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44373,7 +44376,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44423,7 +44426,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44473,7 +44476,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44523,7 +44526,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44823,7 +44826,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44873,7 +44876,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44923,7 +44926,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44973,7 +44976,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45023,7 +45026,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45073,7 +45076,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45123,7 +45126,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45173,7 +45176,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45223,7 +45226,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45273,7 +45276,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45323,7 +45326,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45373,7 +45376,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45423,7 +45426,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45473,7 +45476,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45523,7 +45526,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45573,7 +45576,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45623,7 +45626,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45673,7 +45676,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45973,7 +45976,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46023,7 +46026,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46073,7 +46076,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46123,7 +46126,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46173,7 +46176,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46423,7 +46426,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46473,7 +46476,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46523,7 +46526,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46573,7 +46576,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46823,7 +46826,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46873,7 +46876,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46923,7 +46926,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46973,7 +46976,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47023,7 +47026,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47073,7 +47076,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47123,7 +47126,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47173,7 +47176,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47223,7 +47226,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47273,7 +47276,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47323,7 +47326,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47673,7 +47676,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47723,7 +47726,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47773,7 +47776,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47823,7 +47826,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47873,7 +47876,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47923,7 +47926,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -47973,7 +47976,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48023,7 +48026,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48073,7 +48076,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48123,7 +48126,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48173,7 +48176,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48223,7 +48226,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48273,7 +48276,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48323,7 +48326,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48373,7 +48376,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48923,7 +48926,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48973,7 +48976,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49023,7 +49026,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49073,7 +49076,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49273,7 +49276,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49323,7 +49326,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49373,7 +49376,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49423,7 +49426,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49473,7 +49476,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49523,7 +49526,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49573,7 +49576,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49623,7 +49626,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49673,7 +49676,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50673,7 +50676,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50723,7 +50726,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50773,7 +50776,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50823,7 +50826,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50873,7 +50876,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50923,7 +50926,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50973,7 +50976,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51023,7 +51026,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51073,7 +51076,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51123,7 +51126,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51173,7 +51176,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51223,7 +51226,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51273,7 +51276,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51323,7 +51326,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51373,7 +51376,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51423,7 +51426,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51473,7 +51476,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51523,7 +51526,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51573,7 +51576,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51623,7 +51626,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51637,7 +51640,7 @@
         <v>0.5439992376982135</v>
       </c>
       <c r="D997" t="s">
-        <v>204</v>
+        <v>364</v>
       </c>
       <c r="E997">
         <v>0.4290141353004202</v>
@@ -51673,7 +51676,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51723,7 +51726,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51773,7 +51776,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51787,10 +51790,10 @@
         <v>0.4872446639277008</v>
       </c>
       <c r="D1000" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1000">
-        <v>0.2611513128745981</v>
+        <v>0.4583196307031319</v>
       </c>
       <c r="F1000">
         <v>1</v>
@@ -51799,10 +51802,10 @@
         <v>0.0124927553360723</v>
       </c>
       <c r="H1000">
-        <v>0.0118388486871254</v>
+        <v>0.01166168036929687</v>
       </c>
       <c r="I1000">
-        <v>-0.2260933510531027</v>
+        <v>-0.02892503322456896</v>
       </c>
       <c r="J1000">
         <v>1.336916555918107</v>
@@ -51814,16 +51817,16 @@
         <v>6.49</v>
       </c>
       <c r="M1000">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1000">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1000">
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51873,7 +51876,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -51923,7 +51926,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -51937,10 +51940,10 @@
         <v>0.4673081982782961</v>
       </c>
       <c r="D1003" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1003">
-        <v>0.2419252780723875</v>
+        <v>0.4397152228922172</v>
       </c>
       <c r="F1003">
         <v>1</v>
@@ -51949,10 +51952,10 @@
         <v>0.0125126918017217</v>
       </c>
       <c r="H1003">
-        <v>0.01185807472192761</v>
+        <v>0.01168028477710778</v>
       </c>
       <c r="I1003">
-        <v>-0.2253829202059086</v>
+        <v>-0.02759297538607886</v>
       </c>
       <c r="J1003">
         <v>1.341356748713074</v>
@@ -51964,16 +51967,16 @@
         <v>6.49</v>
       </c>
       <c r="M1003">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1003">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1003">
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52023,7 +52026,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52073,7 +52076,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52087,10 +52090,10 @@
         <v>0.457760349043113</v>
       </c>
       <c r="D1006" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1006">
-        <v>0.2327176639992601</v>
+        <v>0.4308053145858883</v>
       </c>
       <c r="F1006">
         <v>1</v>
@@ -52099,10 +52102,10 @@
         <v>0.01252223965095689</v>
       </c>
       <c r="H1006">
-        <v>0.01186728233600074</v>
+        <v>0.01168919468541411</v>
       </c>
       <c r="I1006">
-        <v>-0.2250426850438529</v>
+        <v>-0.02695503445722469</v>
       </c>
       <c r="J1006">
         <v>1.343483218475921</v>
@@ -52114,16 +52117,16 @@
         <v>6.49</v>
       </c>
       <c r="M1006">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1006">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1006">
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52173,7 +52176,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52223,7 +52226,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52237,10 +52240,10 @@
         <v>0.455548903442355</v>
       </c>
       <c r="D1009" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1009">
-        <v>0.2305850226960793</v>
+        <v>0.4287416270430882</v>
       </c>
       <c r="F1009">
         <v>1</v>
@@ -52249,10 +52252,10 @@
         <v>0.01252445109655764</v>
       </c>
       <c r="H1009">
-        <v>0.01186941497730392</v>
+        <v>0.01169125837295691</v>
       </c>
       <c r="I1009">
-        <v>-0.2249638807462757</v>
+        <v>-0.02680727639926683</v>
       </c>
       <c r="J1009">
         <v>1.343975745335778</v>
@@ -52264,16 +52267,16 @@
         <v>6.49</v>
       </c>
       <c r="M1009">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1009">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1009">
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52331,43 +52334,43 @@
         <v>1</v>
       </c>
       <c r="B1011" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C1011">
-        <v>0.4657921972324939</v>
+        <v>0.4318735900623993</v>
       </c>
       <c r="D1011" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1011">
-        <v>0.2404632993355671</v>
+        <v>0.4383005136757561</v>
       </c>
       <c r="F1011">
         <v>1</v>
       </c>
       <c r="G1011">
-        <v>0.01251420780276751</v>
+        <v>0.0126681264099376</v>
       </c>
       <c r="H1011">
-        <v>0.01185953670066443</v>
+        <v>0.01168169948632424</v>
       </c>
       <c r="I1011">
-        <v>-0.2253288978969268</v>
+        <v>0.006426923613356728</v>
       </c>
       <c r="J1011">
         <v>1.341694388144211</v>
       </c>
       <c r="K1011">
-        <v>4.49</v>
+        <v>4.56</v>
       </c>
       <c r="L1011">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="M1011">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1011">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1011">
         <v>1</v>
@@ -52423,7 +52426,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52437,10 +52440,10 @@
         <v>0.4265302961812907</v>
       </c>
       <c r="D1013" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1013">
-        <v>0.2353895136984621</v>
+        <v>0.4333907765350009</v>
       </c>
       <c r="F1013">
         <v>1</v>
@@ -52449,10 +52452,10 @@
         <v>0.01267346970381871</v>
       </c>
       <c r="H1013">
-        <v>0.01186461048630154</v>
+        <v>0.011686609223465</v>
       </c>
       <c r="I1013">
-        <v>-0.1911407824828286</v>
+        <v>0.00686048035371023</v>
       </c>
       <c r="J1013">
         <v>1.342866163118138</v>
@@ -52464,16 +52467,16 @@
         <v>6.55</v>
       </c>
       <c r="M1013">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1013">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1013">
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52481,43 +52484,43 @@
         <v>0</v>
       </c>
       <c r="B1014" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C1014">
-        <v>1.020522269537055</v>
+        <v>1.194967273410384</v>
       </c>
       <c r="D1014" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E1014">
-        <v>0.6837427575297426</v>
+        <v>0.6937477923896846</v>
       </c>
       <c r="F1014">
         <v>-1</v>
       </c>
       <c r="G1014">
-        <v>0.01701947773046295</v>
+        <v>0.01692503272658962</v>
       </c>
       <c r="H1014">
-        <v>0.01751625724247026</v>
+        <v>0.01510625220761032</v>
       </c>
       <c r="I1014">
-        <v>0.3367795120073129</v>
+        <v>0.5012194810206996</v>
       </c>
       <c r="J1014">
         <v>1.344450038733268</v>
       </c>
       <c r="K1014">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="L1014">
-        <v>9.02</v>
+        <v>9.06</v>
       </c>
       <c r="M1014">
-        <v>6.26</v>
+        <v>5.36</v>
       </c>
       <c r="N1014">
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="O1014">
         <v>1</v>
@@ -52531,43 +52534,43 @@
         <v>1</v>
       </c>
       <c r="B1015" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1015">
-        <v>1.194967273410384</v>
+        <v>0.4193078233762986</v>
       </c>
       <c r="D1015" t="s">
-        <v>194</v>
+        <v>365</v>
       </c>
       <c r="E1015">
-        <v>0.6937477923896846</v>
+        <v>0.4267543377076066</v>
       </c>
       <c r="F1015">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1015">
-        <v>0.01692503272658962</v>
+        <v>0.0126806921766237</v>
       </c>
       <c r="H1015">
-        <v>0.01510625220761032</v>
+        <v>0.01169324566229239</v>
       </c>
       <c r="I1015">
-        <v>0.5012194810206996</v>
+        <v>0.007446514331308052</v>
       </c>
       <c r="J1015">
         <v>1.344450038733268</v>
       </c>
       <c r="K1015">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L1015">
-        <v>9.06</v>
+        <v>6.55</v>
       </c>
       <c r="M1015">
-        <v>5.36</v>
+        <v>4.19</v>
       </c>
       <c r="N1015">
-        <v>7.9</v>
+        <v>6.06</v>
       </c>
       <c r="O1015">
         <v>1</v>
@@ -52578,352 +52581,352 @@
     </row>
     <row r="1016" spans="1:16">
       <c r="A1016" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1016" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C1016">
-        <v>0.4193078233762986</v>
+        <v>1.166955212765879</v>
       </c>
       <c r="D1016" t="s">
-        <v>364</v>
+        <v>194</v>
       </c>
       <c r="E1016">
-        <v>0.22853133228495</v>
+        <v>0.6680820410983088</v>
       </c>
       <c r="F1016">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1016">
-        <v>0.0126806921766237</v>
+        <v>0.01695304478723412</v>
       </c>
       <c r="H1016">
-        <v>0.01187146866771505</v>
+        <v>0.01513191795890169</v>
       </c>
       <c r="I1016">
-        <v>-0.1907764910913485</v>
+        <v>0.4988731716675705</v>
       </c>
       <c r="J1016">
-        <v>1.344450038733268</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1016">
-        <v>4.56</v>
+        <v>5.85</v>
       </c>
       <c r="L1016">
-        <v>6.55</v>
+        <v>9.06</v>
       </c>
       <c r="M1016">
-        <v>4.33</v>
+        <v>5.36</v>
       </c>
       <c r="N1016">
-        <v>6.05</v>
+        <v>7.9</v>
       </c>
       <c r="O1016">
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>192</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
       <c r="A1017" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1017" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1017">
-        <v>1.166955212765879</v>
+        <v>0.3974727812328904</v>
       </c>
       <c r="D1017" t="s">
-        <v>194</v>
+        <v>365</v>
       </c>
       <c r="E1017">
-        <v>0.6680820410983088</v>
+        <v>0.4066909985451321</v>
       </c>
       <c r="F1017">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1017">
-        <v>0.01695304478723412</v>
+        <v>0.01270252721876711</v>
       </c>
       <c r="H1017">
-        <v>0.01513191795890169</v>
+        <v>0.01171330900145487</v>
       </c>
       <c r="I1017">
-        <v>0.4988731716675705</v>
+        <v>0.009218217312241705</v>
       </c>
       <c r="J1017">
         <v>1.349238425168226</v>
       </c>
       <c r="K1017">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L1017">
-        <v>9.06</v>
+        <v>6.55</v>
       </c>
       <c r="M1017">
-        <v>5.36</v>
+        <v>4.19</v>
       </c>
       <c r="N1017">
-        <v>7.9</v>
+        <v>6.06</v>
       </c>
       <c r="O1017">
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
       <c r="A1018" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1018" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C1018">
-        <v>0.3974727812328904</v>
+        <v>1.156353759647005</v>
       </c>
       <c r="D1018" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E1018">
-        <v>0.2077976190215818</v>
+        <v>0.5760199693550092</v>
       </c>
       <c r="F1018">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1018">
-        <v>0.01270252721876711</v>
+        <v>0.016963646240353</v>
       </c>
       <c r="H1018">
-        <v>0.01189220238097842</v>
+        <v>0.01338398003064499</v>
       </c>
       <c r="I1018">
-        <v>-0.1896751622113086</v>
+        <v>0.5803337902919958</v>
       </c>
       <c r="J1018">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1018">
-        <v>4.56</v>
+        <v>5.85</v>
       </c>
       <c r="L1018">
-        <v>6.55</v>
+        <v>9.06</v>
       </c>
       <c r="M1018">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1018">
-        <v>6.05</v>
+        <v>6.98</v>
       </c>
       <c r="O1018">
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
       <c r="A1019" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1019" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1019">
-        <v>1.156353759647005</v>
+        <v>0.3892090844427933</v>
       </c>
       <c r="D1019" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E1019">
-        <v>0.5760199693550092</v>
+        <v>0.399097821012127</v>
       </c>
       <c r="F1019">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1019">
-        <v>0.016963646240353</v>
+        <v>0.01271079091555721</v>
       </c>
       <c r="H1019">
-        <v>0.01338398003064499</v>
+        <v>0.01172090217898787</v>
       </c>
       <c r="I1019">
-        <v>0.5803337902919958</v>
+        <v>0.009888736569333645</v>
       </c>
       <c r="J1019">
         <v>1.35105063937658</v>
       </c>
       <c r="K1019">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L1019">
-        <v>9.06</v>
+        <v>6.55</v>
       </c>
       <c r="M1019">
-        <v>4.74</v>
+        <v>4.19</v>
       </c>
       <c r="N1019">
-        <v>6.98</v>
+        <v>6.06</v>
       </c>
       <c r="O1019">
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
       <c r="A1020" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1020" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C1020">
-        <v>0.3892090844427933</v>
+        <v>1.15176585526189</v>
       </c>
       <c r="D1020" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E1020">
-        <v>0.1999507314994062</v>
+        <v>0.5723025904173253</v>
       </c>
       <c r="F1020">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1020">
-        <v>0.01271079091555721</v>
+        <v>0.01696823414473811</v>
       </c>
       <c r="H1020">
-        <v>0.01190004926850059</v>
+        <v>0.01338769740958268</v>
       </c>
       <c r="I1020">
-        <v>-0.1892583529433871</v>
+        <v>0.5794632648445646</v>
       </c>
       <c r="J1020">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1020">
-        <v>4.56</v>
+        <v>5.85</v>
       </c>
       <c r="L1020">
-        <v>6.55</v>
+        <v>9.06</v>
       </c>
       <c r="M1020">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1020">
-        <v>6.05</v>
+        <v>6.98</v>
       </c>
       <c r="O1020">
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
       <c r="A1021" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1021" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1021">
-        <v>1.15176585526189</v>
+        <v>0.3856328717938826</v>
       </c>
       <c r="D1021" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E1021">
-        <v>0.5723025904173253</v>
+        <v>0.39581178351236</v>
       </c>
       <c r="F1021">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1021">
-        <v>0.01696823414473811</v>
+        <v>0.01271436712820612</v>
       </c>
       <c r="H1021">
-        <v>0.01338769740958268</v>
+        <v>0.01172418821648764</v>
       </c>
       <c r="I1021">
-        <v>0.5794632648445646</v>
+        <v>0.0101789117184774</v>
       </c>
       <c r="J1021">
         <v>1.351834896536429</v>
       </c>
       <c r="K1021">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L1021">
-        <v>9.06</v>
+        <v>6.55</v>
       </c>
       <c r="M1021">
-        <v>4.74</v>
+        <v>4.19</v>
       </c>
       <c r="N1021">
-        <v>6.98</v>
+        <v>6.06</v>
       </c>
       <c r="O1021">
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
       <c r="A1022" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1022" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C1022">
-        <v>0.3856328717938826</v>
+        <v>0.3535915959279903</v>
       </c>
       <c r="D1022" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1022">
-        <v>0.1965548979972604</v>
+        <v>0.39581178351236</v>
       </c>
       <c r="F1022">
         <v>1</v>
       </c>
       <c r="G1022">
-        <v>0.01271436712820612</v>
+        <v>0.01200640840407201</v>
       </c>
       <c r="H1022">
-        <v>0.01190344510200274</v>
+        <v>0.01172418821648764</v>
       </c>
       <c r="I1022">
-        <v>-0.1890779737966222</v>
+        <v>0.04222018758436974</v>
       </c>
       <c r="J1022">
         <v>1.351834896536429</v>
       </c>
       <c r="K1022">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1022">
-        <v>6.55</v>
+        <v>6.18</v>
       </c>
       <c r="M1022">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1022">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1022">
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -52973,7 +52976,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -52981,49 +52984,49 @@
         <v>1</v>
       </c>
       <c r="B1024" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1024">
-        <v>1.149867923161882</v>
+        <v>0.3841534580543895</v>
       </c>
       <c r="D1024" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E1024">
-        <v>0.5707647787670629</v>
+        <v>0.3944524099227822</v>
       </c>
       <c r="F1024">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1024">
-        <v>0.01697013207683812</v>
+        <v>0.01271584654194561</v>
       </c>
       <c r="H1024">
-        <v>0.01338923522123294</v>
+        <v>0.01172554759007722</v>
       </c>
       <c r="I1024">
-        <v>0.5791031443948187</v>
+        <v>0.01029895186839269</v>
       </c>
       <c r="J1024">
         <v>1.352159329374037</v>
       </c>
       <c r="K1024">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L1024">
-        <v>9.06</v>
+        <v>6.55</v>
       </c>
       <c r="M1024">
-        <v>4.74</v>
+        <v>4.19</v>
       </c>
       <c r="N1024">
-        <v>6.98</v>
+        <v>6.06</v>
       </c>
       <c r="O1024">
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53031,293 +53034,293 @@
         <v>2</v>
       </c>
       <c r="B1025" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C1025">
-        <v>0.3841534580543895</v>
+        <v>0.3521932903978984</v>
       </c>
       <c r="D1025" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1025">
-        <v>0.1951501038104171</v>
+        <v>0.3944524099227822</v>
       </c>
       <c r="F1025">
         <v>1</v>
       </c>
       <c r="G1025">
-        <v>0.01271584654194561</v>
+        <v>0.0120078067096021</v>
       </c>
       <c r="H1025">
-        <v>0.01190484989618958</v>
+        <v>0.01172554759007722</v>
       </c>
       <c r="I1025">
-        <v>-0.1890033542439724</v>
+        <v>0.04225911952488381</v>
       </c>
       <c r="J1025">
         <v>1.352159329374037</v>
       </c>
       <c r="K1025">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1025">
-        <v>6.55</v>
+        <v>6.18</v>
       </c>
       <c r="M1025">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1025">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1025">
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
       <c r="A1026" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1026" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C1026">
-        <v>0.3521932903978984</v>
+        <v>0.844077502681861</v>
       </c>
       <c r="D1026" t="s">
-        <v>364</v>
+        <v>196</v>
       </c>
       <c r="E1026">
-        <v>0.1951501038104171</v>
+        <v>0.4969577705448094</v>
       </c>
       <c r="F1026">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1026">
-        <v>0.0120078067096021</v>
+        <v>0.01699592249731814</v>
       </c>
       <c r="H1026">
-        <v>0.01190484989618958</v>
+        <v>0.01578304222945519</v>
       </c>
       <c r="I1026">
-        <v>-0.1570431865874813</v>
+        <v>0.3471197321370516</v>
       </c>
       <c r="J1026">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1026">
-        <v>4.31</v>
+        <v>5.97</v>
       </c>
       <c r="L1026">
-        <v>6.18</v>
+        <v>8.92</v>
       </c>
       <c r="M1026">
-        <v>4.33</v>
+        <v>5.65</v>
       </c>
       <c r="N1026">
-        <v>6.05</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O1026">
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
       <c r="A1027" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1027" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C1027">
-        <v>0.844077502681861</v>
+        <v>0.2702587750308671</v>
       </c>
       <c r="D1027" t="s">
-        <v>196</v>
+        <v>365</v>
       </c>
       <c r="E1027">
-        <v>0.4969577705448094</v>
+        <v>0.3919739926695129</v>
       </c>
       <c r="F1027">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1027">
-        <v>0.01699592249731814</v>
+        <v>0.01230974122496913</v>
       </c>
       <c r="H1027">
-        <v>0.01578304222945519</v>
+        <v>0.01172802600733049</v>
       </c>
       <c r="I1027">
-        <v>0.3471197321370516</v>
+        <v>0.1217152176386458</v>
       </c>
       <c r="J1027">
         <v>1.352750837071715</v>
       </c>
       <c r="K1027">
-        <v>5.97</v>
+        <v>4.45</v>
       </c>
       <c r="L1027">
-        <v>8.92</v>
+        <v>6.29</v>
       </c>
       <c r="M1027">
-        <v>5.65</v>
+        <v>4.19</v>
       </c>
       <c r="N1027">
-        <v>8.140000000000001</v>
+        <v>6.06</v>
       </c>
       <c r="O1027">
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>201</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
       <c r="A1028" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1028" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C1028">
-        <v>0.381456182952979</v>
+        <v>0.3496438922209082</v>
       </c>
       <c r="D1028" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1028">
-        <v>0.1925888754794727</v>
+        <v>0.3919739926695129</v>
       </c>
       <c r="F1028">
         <v>1</v>
       </c>
       <c r="G1028">
-        <v>0.01271854381704702</v>
+        <v>0.01201035610777909</v>
       </c>
       <c r="H1028">
-        <v>0.01190741112452053</v>
+        <v>0.01172802600733049</v>
       </c>
       <c r="I1028">
-        <v>-0.1888673074735063</v>
+        <v>0.04233010044860475</v>
       </c>
       <c r="J1028">
         <v>1.352750837071715</v>
       </c>
       <c r="K1028">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1028">
-        <v>6.55</v>
+        <v>6.18</v>
       </c>
       <c r="M1028">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1028">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1028">
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>201</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
       <c r="A1029" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1029" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C1029">
-        <v>0.3496438922209082</v>
+        <v>0.8389074160156742</v>
       </c>
       <c r="D1029" t="s">
-        <v>364</v>
+        <v>196</v>
       </c>
       <c r="E1029">
-        <v>0.1925888754794727</v>
+        <v>0.4920648074520191</v>
       </c>
       <c r="F1029">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1029">
-        <v>0.01201035610777909</v>
+        <v>0.01700109258398433</v>
       </c>
       <c r="H1029">
-        <v>0.01190741112452053</v>
+        <v>0.01578793519254798</v>
       </c>
       <c r="I1029">
-        <v>-0.1570550167414355</v>
+        <v>0.3468426085636551</v>
       </c>
       <c r="J1029">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1029">
-        <v>4.31</v>
+        <v>5.97</v>
       </c>
       <c r="L1029">
-        <v>6.18</v>
+        <v>8.92</v>
       </c>
       <c r="M1029">
-        <v>4.33</v>
+        <v>5.65</v>
       </c>
       <c r="N1029">
-        <v>6.05</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O1029">
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>201</v>
+        <v>360</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
       <c r="A1030" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1030" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C1030">
-        <v>0.8389074160156742</v>
+        <v>0.7909626607582627</v>
       </c>
       <c r="D1030" t="s">
-        <v>196</v>
+        <v>361</v>
       </c>
       <c r="E1030">
-        <v>0.4920648074520191</v>
+        <v>0.5638561393491281</v>
       </c>
       <c r="F1030">
         <v>-1</v>
       </c>
       <c r="G1030">
-        <v>0.01700109258398433</v>
+        <v>0.01578903733924173</v>
       </c>
       <c r="H1030">
-        <v>0.01578793519254798</v>
+        <v>0.01339614386065087</v>
       </c>
       <c r="I1030">
-        <v>0.3468426085636551</v>
+        <v>0.2271065214091346</v>
       </c>
       <c r="J1030">
         <v>1.353616848238581</v>
       </c>
       <c r="K1030">
-        <v>5.97</v>
+        <v>5.54</v>
       </c>
       <c r="L1030">
-        <v>8.92</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1030">
-        <v>5.65</v>
+        <v>4.74</v>
       </c>
       <c r="N1030">
-        <v>8.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="O1030">
         <v>1</v>
@@ -53328,46 +53331,46 @@
     </row>
     <row r="1031" spans="1:16">
       <c r="A1031" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1031" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C1031">
-        <v>0.372260351408773</v>
+        <v>0.2664050253383161</v>
       </c>
       <c r="D1031" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1031">
-        <v>0.1888390471269457</v>
+        <v>0.3883454058803464</v>
       </c>
       <c r="F1031">
         <v>1</v>
       </c>
       <c r="G1031">
-        <v>0.01252773964859123</v>
+        <v>0.01231359497466168</v>
       </c>
       <c r="H1031">
-        <v>0.01191116095287305</v>
+        <v>0.01173165459411965</v>
       </c>
       <c r="I1031">
-        <v>-0.1834213042818273</v>
+        <v>0.1219403805420303</v>
       </c>
       <c r="J1031">
         <v>1.353616848238581</v>
       </c>
       <c r="K1031">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="L1031">
-        <v>6.45</v>
+        <v>6.29</v>
       </c>
       <c r="M1031">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1031">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1031">
         <v>1</v>
@@ -53378,19 +53381,19 @@
     </row>
     <row r="1032" spans="1:16">
       <c r="A1032" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1032" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C1032">
         <v>0.3459113840917176</v>
       </c>
       <c r="D1032" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1032">
-        <v>0.1888390471269457</v>
+        <v>0.3883454058803464</v>
       </c>
       <c r="F1032">
         <v>1</v>
@@ -53399,10 +53402,10 @@
         <v>0.01201408861590828</v>
       </c>
       <c r="H1032">
-        <v>0.01191116095287305</v>
+        <v>0.01173165459411965</v>
       </c>
       <c r="I1032">
-        <v>-0.157072336964772</v>
+        <v>0.04243402178862876</v>
       </c>
       <c r="J1032">
         <v>1.353616848238581</v>
@@ -53414,10 +53417,10 @@
         <v>6.18</v>
       </c>
       <c r="M1032">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1032">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1032">
         <v>1</v>
@@ -53431,43 +53434,43 @@
         <v>0</v>
       </c>
       <c r="B1033" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C1033">
-        <v>0.276293422021098</v>
+        <v>0.8032731591004225</v>
       </c>
       <c r="D1033" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E1033">
-        <v>0.1984607904160347</v>
+        <v>0.5743889484000011</v>
       </c>
       <c r="F1033">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1033">
-        <v>0.0123037065779789</v>
+        <v>0.01577672684089958</v>
       </c>
       <c r="H1033">
-        <v>0.01190153920958397</v>
+        <v>0.0133856110516</v>
       </c>
       <c r="I1033">
-        <v>-0.07783263160506326</v>
+        <v>0.2288842107004214</v>
       </c>
       <c r="J1033">
         <v>1.351394736624472</v>
       </c>
       <c r="K1033">
-        <v>4.45</v>
+        <v>5.54</v>
       </c>
       <c r="L1033">
-        <v>6.29</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1033">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1033">
-        <v>6.05</v>
+        <v>6.98</v>
       </c>
       <c r="O1033">
         <v>1</v>
@@ -53484,40 +53487,40 @@
         <v>203</v>
       </c>
       <c r="C1034">
-        <v>0.3554886851485248</v>
+        <v>0.276293422021098</v>
       </c>
       <c r="D1034" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1034">
-        <v>0.1984607904160347</v>
+        <v>0.3976560535434599</v>
       </c>
       <c r="F1034">
         <v>1</v>
       </c>
       <c r="G1034">
-        <v>0.01200451131485147</v>
+        <v>0.0123037065779789</v>
       </c>
       <c r="H1034">
-        <v>0.01190153920958397</v>
+        <v>0.01172234394645654</v>
       </c>
       <c r="I1034">
-        <v>-0.1570278947324901</v>
+        <v>0.1213626315223619</v>
       </c>
       <c r="J1034">
         <v>1.351394736624472</v>
       </c>
       <c r="K1034">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1034">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1034">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1034">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1034">
         <v>1</v>
@@ -53528,96 +53531,96 @@
     </row>
     <row r="1035" spans="1:16">
       <c r="A1035" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1035" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1035">
-        <v>0.8031318580204516</v>
+        <v>0.3554886851485248</v>
       </c>
       <c r="D1035" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E1035">
-        <v>0.5742680518081134</v>
+        <v>0.3976560535434599</v>
       </c>
       <c r="F1035">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1035">
-        <v>0.01577686814197955</v>
+        <v>0.01200451131485147</v>
       </c>
       <c r="H1035">
-        <v>0.01338573194819189</v>
+        <v>0.01172234394645654</v>
       </c>
       <c r="I1035">
-        <v>0.2288638062123383</v>
+        <v>0.04216736839493507</v>
       </c>
       <c r="J1035">
-        <v>1.351420242234575</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1035">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1035">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1035">
-        <v>4.74</v>
+        <v>4.19</v>
       </c>
       <c r="N1035">
-        <v>6.98</v>
+        <v>6.06</v>
       </c>
       <c r="O1035">
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
       <c r="A1036" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1036" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1036">
-        <v>0.7915295258461343</v>
+        <v>0.8031318580204516</v>
       </c>
       <c r="D1036" t="s">
-        <v>361</v>
+        <v>198</v>
       </c>
       <c r="E1036">
-        <v>0.5742680518081134</v>
+        <v>0.4948106590751502</v>
       </c>
       <c r="F1036">
         <v>-1</v>
       </c>
       <c r="G1036">
-        <v>0.01500847047415387</v>
+        <v>0.01577686814197955</v>
       </c>
       <c r="H1036">
-        <v>0.01338573194819189</v>
+        <v>0.01322518934092485</v>
       </c>
       <c r="I1036">
-        <v>0.217261474038021</v>
+        <v>0.3083211989453014</v>
       </c>
       <c r="J1036">
         <v>1.351420242234575</v>
       </c>
       <c r="K1036">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1036">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1036">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="N1036">
-        <v>6.98</v>
+        <v>6.86</v>
       </c>
       <c r="O1036">
         <v>1</v>
@@ -53628,46 +53631,46 @@
     </row>
     <row r="1037" spans="1:16">
       <c r="A1037" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1037" t="s">
         <v>205</v>
       </c>
       <c r="C1037">
-        <v>0.2761799220561398</v>
+        <v>0.7915295258461343</v>
       </c>
       <c r="D1037" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
       <c r="E1037">
-        <v>0.1983503511242883</v>
+        <v>0.4948106590751502</v>
       </c>
       <c r="F1037">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1037">
-        <v>0.01230382007794386</v>
+        <v>0.01500847047415387</v>
       </c>
       <c r="H1037">
-        <v>0.01190164964887571</v>
+        <v>0.01322518934092485</v>
       </c>
       <c r="I1037">
-        <v>-0.0778295709318515</v>
+        <v>0.2967188667709841</v>
       </c>
       <c r="J1037">
         <v>1.351420242234575</v>
       </c>
       <c r="K1037">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1037">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1037">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="N1037">
-        <v>6.05</v>
+        <v>6.86</v>
       </c>
       <c r="O1037">
         <v>1</v>
@@ -53678,46 +53681,46 @@
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1038" t="s">
         <v>203</v>
       </c>
       <c r="C1038">
-        <v>0.3553787559689807</v>
+        <v>0.2761799220561398</v>
       </c>
       <c r="D1038" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1038">
-        <v>0.1983503511242883</v>
+        <v>0.3975491850371284</v>
       </c>
       <c r="F1038">
         <v>1</v>
       </c>
       <c r="G1038">
-        <v>0.01200462124403102</v>
+        <v>0.01230382007794386</v>
       </c>
       <c r="H1038">
-        <v>0.01190164964887571</v>
+        <v>0.01172245081496287</v>
       </c>
       <c r="I1038">
-        <v>-0.1570284048446924</v>
+        <v>0.1213692629809886</v>
       </c>
       <c r="J1038">
         <v>1.351420242234575</v>
       </c>
       <c r="K1038">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1038">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1038">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1038">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1038">
         <v>1</v>
@@ -53728,63 +53731,63 @@
     </row>
     <row r="1039" spans="1:16">
       <c r="A1039" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1039" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1039">
-        <v>0.8327877653809024</v>
+        <v>0.3553787559689807</v>
       </c>
       <c r="D1039" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="E1039">
-        <v>0.5200235333834033</v>
+        <v>0.3975491850371284</v>
       </c>
       <c r="F1039">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1039">
-        <v>0.0157472122346191</v>
+        <v>0.01200462124403102</v>
       </c>
       <c r="H1039">
-        <v>0.0131999764666166</v>
+        <v>0.01172245081496287</v>
       </c>
       <c r="I1039">
-        <v>0.312764231997499</v>
+        <v>0.04217042906814772</v>
       </c>
       <c r="J1039">
-        <v>1.346067190364458</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1039">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1039">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1039">
-        <v>4.71</v>
+        <v>4.19</v>
       </c>
       <c r="N1039">
-        <v>6.86</v>
+        <v>6.06</v>
       </c>
       <c r="O1039">
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1040" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1040">
-        <v>0.8196865786829521</v>
+        <v>0.8327877653809024</v>
       </c>
       <c r="D1040" t="s">
         <v>198</v>
@@ -53796,22 +53799,22 @@
         <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.01498031342131705</v>
+        <v>0.0157472122346191</v>
       </c>
       <c r="H1040">
         <v>0.0131999764666166</v>
       </c>
       <c r="I1040">
-        <v>0.2996630452995488</v>
+        <v>0.312764231997499</v>
       </c>
       <c r="J1040">
         <v>1.346067190364458</v>
       </c>
       <c r="K1040">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1040">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1040">
         <v>4.71</v>
@@ -53828,46 +53831,46 @@
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1041" t="s">
         <v>205</v>
       </c>
       <c r="C1041">
-        <v>0.3000010028781626</v>
+        <v>0.8196865786829521</v>
       </c>
       <c r="D1041" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
       <c r="E1041">
-        <v>0.2215290657218967</v>
+        <v>0.5200235333834033</v>
       </c>
       <c r="F1041">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1041">
-        <v>0.01227999899712184</v>
+        <v>0.01498031342131705</v>
       </c>
       <c r="H1041">
-        <v>0.0118784709342781</v>
+        <v>0.0131999764666166</v>
       </c>
       <c r="I1041">
-        <v>-0.07847193715626588</v>
+        <v>0.2996630452995488</v>
       </c>
       <c r="J1041">
         <v>1.346067190364458</v>
       </c>
       <c r="K1041">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1041">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1041">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="N1041">
-        <v>6.05</v>
+        <v>6.86</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -53878,146 +53881,146 @@
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1042" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C1042">
-        <v>0.8240937125821999</v>
+        <v>0.3000010028781626</v>
       </c>
       <c r="D1042" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="E1042">
-        <v>0.5126320191808968</v>
+        <v>0.4199784723729207</v>
       </c>
       <c r="F1042">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1042">
-        <v>0.0157559062874178</v>
+        <v>0.01227999899712184</v>
       </c>
       <c r="H1042">
-        <v>0.0132073679808191</v>
+        <v>0.01170002152762708</v>
       </c>
       <c r="I1042">
-        <v>0.311461693401303</v>
+        <v>0.1199774694947582</v>
       </c>
       <c r="J1042">
-        <v>1.347636513974332</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1042">
-        <v>5.54</v>
+        <v>4.45</v>
       </c>
       <c r="L1042">
-        <v>8.289999999999999</v>
+        <v>6.29</v>
       </c>
       <c r="M1042">
-        <v>4.71</v>
+        <v>4.19</v>
       </c>
       <c r="N1042">
-        <v>6.86</v>
+        <v>6.06</v>
       </c>
       <c r="O1042">
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>363</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1043" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C1043">
-        <v>0.8114319364950138</v>
+        <v>0.2215290657218967</v>
       </c>
       <c r="D1043" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="E1043">
-        <v>0.5126320191808968</v>
+        <v>0.4199784723729207</v>
       </c>
       <c r="F1043">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1043">
-        <v>0.01498856806350499</v>
+        <v>0.0118784709342781</v>
       </c>
       <c r="H1043">
-        <v>0.0132073679808191</v>
+        <v>0.01170002152762708</v>
       </c>
       <c r="I1043">
-        <v>0.2987999173141169</v>
+        <v>0.1984494066510241</v>
       </c>
       <c r="J1043">
-        <v>1.347636513974332</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1043">
-        <v>5.26</v>
+        <v>4.33</v>
       </c>
       <c r="L1043">
-        <v>7.9</v>
+        <v>6.05</v>
       </c>
       <c r="M1043">
-        <v>4.71</v>
+        <v>4.19</v>
       </c>
       <c r="N1043">
-        <v>6.86</v>
+        <v>6.06</v>
       </c>
       <c r="O1043">
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>363</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1044" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C1044">
-        <v>0.2930175128142221</v>
+        <v>0.8240937125821999</v>
       </c>
       <c r="D1044" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
       <c r="E1044">
-        <v>0.2147338944911423</v>
+        <v>0.5126320191808968</v>
       </c>
       <c r="F1044">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1044">
-        <v>0.01228698248718578</v>
+        <v>0.0157559062874178</v>
       </c>
       <c r="H1044">
-        <v>0.01188526610550886</v>
+        <v>0.0132073679808191</v>
       </c>
       <c r="I1044">
-        <v>-0.07828361832307973</v>
+        <v>0.311461693401303</v>
       </c>
       <c r="J1044">
         <v>1.347636513974332</v>
       </c>
       <c r="K1044">
-        <v>4.45</v>
+        <v>5.54</v>
       </c>
       <c r="L1044">
-        <v>6.29</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1044">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="N1044">
-        <v>6.05</v>
+        <v>6.86</v>
       </c>
       <c r="O1044">
         <v>1</v>
@@ -54028,46 +54031,46 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1045" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C1045">
-        <v>0.3716866247706294</v>
+        <v>0.8114319364950138</v>
       </c>
       <c r="D1045" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
       <c r="E1045">
-        <v>0.2147338944911423</v>
+        <v>0.5126320191808968</v>
       </c>
       <c r="F1045">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.01198831337522937</v>
+        <v>0.01498856806350499</v>
       </c>
       <c r="H1045">
-        <v>0.01188526610550886</v>
+        <v>0.0132073679808191</v>
       </c>
       <c r="I1045">
-        <v>-0.1569527302794871</v>
+        <v>0.2987999173141169</v>
       </c>
       <c r="J1045">
         <v>1.347636513974332</v>
       </c>
       <c r="K1045">
-        <v>4.31</v>
+        <v>5.26</v>
       </c>
       <c r="L1045">
-        <v>6.18</v>
+        <v>7.9</v>
       </c>
       <c r="M1045">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="N1045">
-        <v>6.05</v>
+        <v>6.86</v>
       </c>
       <c r="O1045">
         <v>1</v>
@@ -54078,102 +54081,102 @@
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1046" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C1046">
-        <v>0.8052084430909758</v>
+        <v>0.2930175128142221</v>
       </c>
       <c r="D1046" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="E1046">
-        <v>0.5070592712848851</v>
+        <v>0.413403006447548</v>
       </c>
       <c r="F1046">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1046">
-        <v>0.01499479155690902</v>
+        <v>0.01228698248718578</v>
       </c>
       <c r="H1046">
-        <v>0.01321294072871512</v>
+        <v>0.01170659699355245</v>
       </c>
       <c r="I1046">
-        <v>0.2981491718060907</v>
+        <v>0.120385493633326</v>
       </c>
       <c r="J1046">
-        <v>1.34881968762529</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1046">
-        <v>5.26</v>
+        <v>4.45</v>
       </c>
       <c r="L1046">
-        <v>7.9</v>
+        <v>6.29</v>
       </c>
       <c r="M1046">
-        <v>4.71</v>
+        <v>4.19</v>
       </c>
       <c r="N1046">
-        <v>6.86</v>
+        <v>6.06</v>
       </c>
       <c r="O1046">
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>206</v>
+        <v>363</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1047" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C1047">
-        <v>0.2877523900674603</v>
+        <v>0.3716866247706294</v>
       </c>
       <c r="D1047" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1047">
-        <v>0.2096107525824946</v>
+        <v>0.413403006447548</v>
       </c>
       <c r="F1047">
         <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.01229224760993254</v>
+        <v>0.01198831337522937</v>
       </c>
       <c r="H1047">
-        <v>0.01189038924741751</v>
+        <v>0.01170659699355245</v>
       </c>
       <c r="I1047">
-        <v>-0.07814163748496572</v>
+        <v>0.0417163816769186</v>
       </c>
       <c r="J1047">
-        <v>1.34881968762529</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1047">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1047">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1047">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1047">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>206</v>
+        <v>363</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54181,31 +54184,31 @@
         <v>0</v>
       </c>
       <c r="B1048" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C1048">
-        <v>0.7946438898107466</v>
+        <v>0.8052084430909758</v>
       </c>
       <c r="D1048" t="s">
         <v>198</v>
       </c>
       <c r="E1048">
-        <v>0.4975993766176074</v>
+        <v>0.5070592712848851</v>
       </c>
       <c r="F1048">
         <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.01500535611018925</v>
+        <v>0.01499479155690902</v>
       </c>
       <c r="H1048">
-        <v>0.01322240062338239</v>
+        <v>0.01321294072871512</v>
       </c>
       <c r="I1048">
-        <v>0.2970445131931392</v>
+        <v>0.2981491718060907</v>
       </c>
       <c r="J1048">
-        <v>1.350828157830657</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1048">
         <v>5.26</v>
@@ -54223,7 +54226,7 @@
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
@@ -54231,49 +54234,49 @@
         <v>1</v>
       </c>
       <c r="B1049" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C1049">
-        <v>0.6890082792562344</v>
+        <v>0.2877523900674603</v>
       </c>
       <c r="D1049" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="E1049">
-        <v>0.4975993766176074</v>
+        <v>0.4084455088500345</v>
       </c>
       <c r="F1049">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1049">
-        <v>0.01371099172074377</v>
+        <v>0.01229224760993254</v>
       </c>
       <c r="H1049">
-        <v>0.01322240062338239</v>
+        <v>0.01171155449114997</v>
       </c>
       <c r="I1049">
-        <v>0.191408902638627</v>
+        <v>0.1206931187825742</v>
       </c>
       <c r="J1049">
-        <v>1.350828157830657</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1049">
-        <v>4.82</v>
+        <v>4.45</v>
       </c>
       <c r="L1049">
-        <v>7.2</v>
+        <v>6.29</v>
       </c>
       <c r="M1049">
-        <v>4.71</v>
+        <v>4.19</v>
       </c>
       <c r="N1049">
-        <v>6.86</v>
+        <v>6.06</v>
       </c>
       <c r="O1049">
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -54281,49 +54284,49 @@
         <v>2</v>
       </c>
       <c r="B1050" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C1050">
-        <v>0.2788146976535772</v>
+        <v>0.2096107525824946</v>
       </c>
       <c r="D1050" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1050">
-        <v>0.2009140765932562</v>
+        <v>0.4084455088500345</v>
       </c>
       <c r="F1050">
         <v>1</v>
       </c>
       <c r="G1050">
-        <v>0.01230118530234642</v>
+        <v>0.01189038924741751</v>
       </c>
       <c r="H1050">
-        <v>0.01189908592340675</v>
+        <v>0.01171155449114997</v>
       </c>
       <c r="I1050">
-        <v>-0.07790062106032103</v>
+        <v>0.1988347562675399</v>
       </c>
       <c r="J1050">
-        <v>1.350828157830657</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1050">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="L1050">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="M1050">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1050">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1050">
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -54331,37 +54334,37 @@
         <v>0</v>
       </c>
       <c r="B1051" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C1051">
-        <v>0.6897048720272076</v>
+        <v>0.685527947714454</v>
       </c>
       <c r="D1051" t="s">
         <v>198</v>
       </c>
       <c r="E1051">
-        <v>0.4982800720431841</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1051">
         <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.01371029512797279</v>
+        <v>0.01527447205228555</v>
       </c>
       <c r="H1051">
-        <v>0.01322171992795682</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1051">
-        <v>0.1914247999840235</v>
+        <v>0.1879285710968466</v>
       </c>
       <c r="J1051">
-        <v>1.350683636508878</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1051">
-        <v>4.82</v>
+        <v>5.4</v>
       </c>
       <c r="L1051">
-        <v>7.2</v>
+        <v>7.98</v>
       </c>
       <c r="M1051">
         <v>4.71</v>
@@ -54373,7 +54376,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>484</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -54381,149 +54384,149 @@
         <v>1</v>
       </c>
       <c r="B1052" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C1052">
-        <v>0.2794578175354925</v>
+        <v>0.6890082792562344</v>
       </c>
       <c r="D1052" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
       <c r="E1052">
-        <v>0.2015398539165574</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1052">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.01230054218246451</v>
+        <v>0.01371099172074377</v>
       </c>
       <c r="H1052">
-        <v>0.01189846014608344</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1052">
-        <v>-0.0779179636189351</v>
+        <v>0.191408902638627</v>
       </c>
       <c r="J1052">
-        <v>1.350683636508878</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1052">
-        <v>4.45</v>
+        <v>4.82</v>
       </c>
       <c r="L1052">
-        <v>6.29</v>
+        <v>7.2</v>
       </c>
       <c r="M1052">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="N1052">
-        <v>6.05</v>
+        <v>6.86</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>484</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1053" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C1053">
-        <v>0.6674364420145809</v>
+        <v>0.2788146976535772</v>
       </c>
       <c r="D1053" t="s">
-        <v>199</v>
+        <v>365</v>
       </c>
       <c r="E1053">
-        <v>0.4167478384678054</v>
+        <v>0.4000300186895478</v>
       </c>
       <c r="F1053">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.01365256355798542</v>
+        <v>0.01230118530234642</v>
       </c>
       <c r="H1053">
-        <v>0.01256325216153219</v>
+        <v>0.01171996998131045</v>
       </c>
       <c r="I1053">
-        <v>0.2506886035467755</v>
+        <v>0.1212153210359705</v>
       </c>
       <c r="J1053">
-        <v>1.352617407913629</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1053">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1053">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1053">
-        <v>4.49</v>
+        <v>4.19</v>
       </c>
       <c r="N1053">
-        <v>6.49</v>
+        <v>6.06</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1054" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C1054">
-        <v>0.2708525347843507</v>
+        <v>0.2009140765932562</v>
       </c>
       <c r="D1054" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E1054">
-        <v>0.193166623733986</v>
+        <v>0.4000300186895478</v>
       </c>
       <c r="F1054">
         <v>1</v>
       </c>
       <c r="G1054">
-        <v>0.01230914746521565</v>
+        <v>0.01189908592340675</v>
       </c>
       <c r="H1054">
-        <v>0.01190683337626602</v>
+        <v>0.01171996998131045</v>
       </c>
       <c r="I1054">
-        <v>-0.07768591105036471</v>
+        <v>0.1991159420962916</v>
       </c>
       <c r="J1054">
-        <v>1.352617407913629</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1054">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="L1054">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="M1054">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="N1054">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54531,49 +54534,49 @@
         <v>0</v>
       </c>
       <c r="B1055" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C1055">
-        <v>0.653707777522631</v>
+        <v>0.6897048720272076</v>
       </c>
       <c r="D1055" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E1055">
-        <v>0.4039058168909611</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1055">
         <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.01366629222247737</v>
+        <v>0.01371029512797279</v>
       </c>
       <c r="H1055">
-        <v>0.01257609418310904</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1055">
-        <v>0.2498019606316699</v>
+        <v>0.1914247999840235</v>
       </c>
       <c r="J1055">
-        <v>1.355477546349452</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1055">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="L1055">
-        <v>7.16</v>
+        <v>7.2</v>
       </c>
       <c r="M1055">
-        <v>4.49</v>
+        <v>4.71</v>
       </c>
       <c r="N1055">
-        <v>6.49</v>
+        <v>6.86</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54581,148 +54584,598 @@
         <v>1</v>
       </c>
       <c r="B1056" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C1056">
-        <v>0.2581249187449384</v>
+        <v>0.6767185447573851</v>
       </c>
       <c r="D1056" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
       <c r="E1056">
-        <v>0.1807822243068724</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1056">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.01232187508125506</v>
+        <v>0.01364328145524261</v>
       </c>
       <c r="H1056">
-        <v>0.01191921777569313</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1056">
-        <v>-0.07734269443806596</v>
+        <v>0.178438472714201</v>
       </c>
       <c r="J1056">
-        <v>1.355477546349452</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1056">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1056">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1056">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="N1056">
-        <v>6.05</v>
+        <v>6.86</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1057" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C1057">
-        <v>0.6493738814716474</v>
+        <v>0.2794578175354925</v>
       </c>
       <c r="D1057" t="s">
-        <v>199</v>
+        <v>365</v>
       </c>
       <c r="E1057">
-        <v>0.3998518182932695</v>
+        <v>0.4006355630277998</v>
       </c>
       <c r="F1057">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1057">
-        <v>0.01367062611852835</v>
+        <v>0.01230054218246451</v>
       </c>
       <c r="H1057">
-        <v>0.01258014818170673</v>
+        <v>0.0117193644369722</v>
       </c>
       <c r="I1057">
-        <v>0.2495220631783779</v>
+        <v>0.1211777454923073</v>
       </c>
       <c r="J1057">
-        <v>1.356380441360074</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1057">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1057">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1057">
-        <v>4.49</v>
+        <v>4.19</v>
       </c>
       <c r="N1057">
-        <v>6.49</v>
+        <v>6.06</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1058" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1058">
+        <v>0.2015398539165574</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1058">
+        <v>0.4006355630277998</v>
+      </c>
+      <c r="F1058">
+        <v>1</v>
+      </c>
+      <c r="G1058">
+        <v>0.01189846014608344</v>
+      </c>
+      <c r="H1058">
+        <v>0.0117193644369722</v>
+      </c>
+      <c r="I1058">
+        <v>0.1990957091112424</v>
+      </c>
+      <c r="J1058">
+        <v>1.350683636508878</v>
+      </c>
+      <c r="K1058">
+        <v>4.33</v>
+      </c>
+      <c r="L1058">
+        <v>6.05</v>
+      </c>
+      <c r="M1058">
+        <v>4.19</v>
+      </c>
+      <c r="N1058">
+        <v>6.06</v>
+      </c>
+      <c r="O1058">
+        <v>1</v>
+      </c>
+      <c r="P1058" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:16">
+      <c r="A1059" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1059">
+        <v>0.6674364420145809</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1059">
+        <v>0.4167478384678054</v>
+      </c>
+      <c r="F1059">
+        <v>-1</v>
+      </c>
+      <c r="G1059">
+        <v>0.01365256355798542</v>
+      </c>
+      <c r="H1059">
+        <v>0.01256325216153219</v>
+      </c>
+      <c r="I1059">
+        <v>0.2506886035467755</v>
+      </c>
+      <c r="J1059">
+        <v>1.352617407913629</v>
+      </c>
+      <c r="K1059">
+        <v>4.8</v>
+      </c>
+      <c r="L1059">
+        <v>7.16</v>
+      </c>
+      <c r="M1059">
+        <v>4.49</v>
+      </c>
+      <c r="N1059">
+        <v>6.49</v>
+      </c>
+      <c r="O1059">
+        <v>1</v>
+      </c>
+      <c r="P1059" t="s">
         <v>205</v>
       </c>
-      <c r="C1058">
+    </row>
+    <row r="1060" spans="1:16">
+      <c r="A1060" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1060">
+        <v>0.2708525347843507</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1060">
+        <v>0.3925330608418935</v>
+      </c>
+      <c r="F1060">
+        <v>1</v>
+      </c>
+      <c r="G1060">
+        <v>0.01230914746521565</v>
+      </c>
+      <c r="H1060">
+        <v>0.01172746693915811</v>
+      </c>
+      <c r="I1060">
+        <v>0.1216805260575429</v>
+      </c>
+      <c r="J1060">
+        <v>1.352617407913629</v>
+      </c>
+      <c r="K1060">
+        <v>4.45</v>
+      </c>
+      <c r="L1060">
+        <v>6.29</v>
+      </c>
+      <c r="M1060">
+        <v>4.19</v>
+      </c>
+      <c r="N1060">
+        <v>6.06</v>
+      </c>
+      <c r="O1060">
+        <v>1</v>
+      </c>
+      <c r="P1060" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:16">
+      <c r="A1061" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1061">
+        <v>0.193166623733986</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1061">
+        <v>0.3925330608418935</v>
+      </c>
+      <c r="F1061">
+        <v>1</v>
+      </c>
+      <c r="G1061">
+        <v>0.01190683337626602</v>
+      </c>
+      <c r="H1061">
+        <v>0.01172746693915811</v>
+      </c>
+      <c r="I1061">
+        <v>0.1993664371079076</v>
+      </c>
+      <c r="J1061">
+        <v>1.352617407913629</v>
+      </c>
+      <c r="K1061">
+        <v>4.33</v>
+      </c>
+      <c r="L1061">
+        <v>6.05</v>
+      </c>
+      <c r="M1061">
+        <v>4.19</v>
+      </c>
+      <c r="N1061">
+        <v>6.06</v>
+      </c>
+      <c r="O1061">
+        <v>1</v>
+      </c>
+      <c r="P1061" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:16">
+      <c r="A1062" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1062">
+        <v>0.653707777522631</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1062">
+        <v>0.4039058168909611</v>
+      </c>
+      <c r="F1062">
+        <v>-1</v>
+      </c>
+      <c r="G1062">
+        <v>0.01366629222247737</v>
+      </c>
+      <c r="H1062">
+        <v>0.01257609418310904</v>
+      </c>
+      <c r="I1062">
+        <v>0.2498019606316699</v>
+      </c>
+      <c r="J1062">
+        <v>1.355477546349452</v>
+      </c>
+      <c r="K1062">
+        <v>4.8</v>
+      </c>
+      <c r="L1062">
+        <v>7.16</v>
+      </c>
+      <c r="M1062">
+        <v>4.49</v>
+      </c>
+      <c r="N1062">
+        <v>6.49</v>
+      </c>
+      <c r="O1062">
+        <v>1</v>
+      </c>
+      <c r="P1062" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:16">
+      <c r="A1063" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1063">
+        <v>0.2581249187449384</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1063">
+        <v>0.3805490807957952</v>
+      </c>
+      <c r="F1063">
+        <v>1</v>
+      </c>
+      <c r="G1063">
+        <v>0.01232187508125506</v>
+      </c>
+      <c r="H1063">
+        <v>0.0117394509192042</v>
+      </c>
+      <c r="I1063">
+        <v>0.1224241620508568</v>
+      </c>
+      <c r="J1063">
+        <v>1.355477546349452</v>
+      </c>
+      <c r="K1063">
+        <v>4.45</v>
+      </c>
+      <c r="L1063">
+        <v>6.29</v>
+      </c>
+      <c r="M1063">
+        <v>4.19</v>
+      </c>
+      <c r="N1063">
+        <v>6.06</v>
+      </c>
+      <c r="O1063">
+        <v>1</v>
+      </c>
+      <c r="P1063" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:16">
+      <c r="A1064" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1064">
+        <v>0.1807822243068724</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1064">
+        <v>0.3805490807957952</v>
+      </c>
+      <c r="F1064">
+        <v>1</v>
+      </c>
+      <c r="G1064">
+        <v>0.01191921777569313</v>
+      </c>
+      <c r="H1064">
+        <v>0.0117394509192042</v>
+      </c>
+      <c r="I1064">
+        <v>0.1997668564889228</v>
+      </c>
+      <c r="J1064">
+        <v>1.355477546349452</v>
+      </c>
+      <c r="K1064">
+        <v>4.33</v>
+      </c>
+      <c r="L1064">
+        <v>6.05</v>
+      </c>
+      <c r="M1064">
+        <v>4.19</v>
+      </c>
+      <c r="N1064">
+        <v>6.06</v>
+      </c>
+      <c r="O1064">
+        <v>1</v>
+      </c>
+      <c r="P1064" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:16">
+      <c r="A1065" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1065">
+        <v>0.6493738814716474</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1065">
+        <v>0.3998518182932695</v>
+      </c>
+      <c r="F1065">
+        <v>-1</v>
+      </c>
+      <c r="G1065">
+        <v>0.01367062611852835</v>
+      </c>
+      <c r="H1065">
+        <v>0.01258014818170673</v>
+      </c>
+      <c r="I1065">
+        <v>0.2495220631783779</v>
+      </c>
+      <c r="J1065">
+        <v>1.356380441360074</v>
+      </c>
+      <c r="K1065">
+        <v>4.8</v>
+      </c>
+      <c r="L1065">
+        <v>7.16</v>
+      </c>
+      <c r="M1065">
+        <v>4.49</v>
+      </c>
+      <c r="N1065">
+        <v>6.49</v>
+      </c>
+      <c r="O1065">
+        <v>1</v>
+      </c>
+      <c r="P1065" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:16">
+      <c r="A1066" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1066">
         <v>0.2541070359476727</v>
       </c>
-      <c r="D1058" t="s">
-        <v>364</v>
-      </c>
-      <c r="E1058">
+      <c r="D1066" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1066">
+        <v>0.3767659507012908</v>
+      </c>
+      <c r="F1066">
+        <v>1</v>
+      </c>
+      <c r="G1066">
+        <v>0.01232589296405233</v>
+      </c>
+      <c r="H1066">
+        <v>0.01174323404929871</v>
+      </c>
+      <c r="I1066">
+        <v>0.1226589147536181</v>
+      </c>
+      <c r="J1066">
+        <v>1.356380441360074</v>
+      </c>
+      <c r="K1066">
+        <v>4.45</v>
+      </c>
+      <c r="L1066">
+        <v>6.29</v>
+      </c>
+      <c r="M1066">
+        <v>4.19</v>
+      </c>
+      <c r="N1066">
+        <v>6.06</v>
+      </c>
+      <c r="O1066">
+        <v>1</v>
+      </c>
+      <c r="P1066" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:16">
+      <c r="A1067" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1067">
         <v>0.1768726889108816</v>
       </c>
-      <c r="F1058">
-        <v>1</v>
-      </c>
-      <c r="G1058">
-        <v>0.01232589296405233</v>
-      </c>
-      <c r="H1058">
+      <c r="D1067" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1067">
+        <v>0.3767659507012908</v>
+      </c>
+      <c r="F1067">
+        <v>1</v>
+      </c>
+      <c r="G1067">
         <v>0.01192312731108912</v>
       </c>
-      <c r="I1058">
-        <v>-0.07723434703679111</v>
-      </c>
-      <c r="J1058">
+      <c r="H1067">
+        <v>0.01174323404929871</v>
+      </c>
+      <c r="I1067">
+        <v>0.1998932617904092</v>
+      </c>
+      <c r="J1067">
         <v>1.356380441360074</v>
       </c>
-      <c r="K1058">
-        <v>4.45</v>
-      </c>
-      <c r="L1058">
-        <v>6.29</v>
-      </c>
-      <c r="M1058">
+      <c r="K1067">
         <v>4.33</v>
       </c>
-      <c r="N1058">
+      <c r="L1067">
         <v>6.05</v>
       </c>
-      <c r="O1058">
-        <v>1</v>
-      </c>
-      <c r="P1058" t="s">
+      <c r="M1067">
+        <v>4.19</v>
+      </c>
+      <c r="N1067">
+        <v>6.06</v>
+      </c>
+      <c r="O1067">
+        <v>1</v>
+      </c>
+      <c r="P1067" t="s">
         <v>208</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3234" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="492">
   <si>
     <t>trade_time</t>
   </si>
@@ -622,9 +622,6 @@
     <t>2021-11-15</t>
   </si>
   <si>
-    <t>2021-11-09</t>
-  </si>
-  <si>
     <t>2021-10-11</t>
   </si>
   <si>
@@ -632,6 +629,9 @@
   </si>
   <si>
     <t>2021-10-26</t>
+  </si>
+  <si>
+    <t>2021-11-09</t>
   </si>
   <si>
     <t>2021-11-10</t>
@@ -646,10 +646,10 @@
     <t>2021-11-01</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-03</t>
   </si>
   <si>
-    <t>2021-11-03</t>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2016-11-30</t>
@@ -1127,6 +1127,9 @@
   </si>
   <si>
     <t>2021-11-24</t>
+  </si>
+  <si>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1844,7 +1847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1074"/>
+  <dimension ref="A1:P1075"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1941,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1991,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2041,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2091,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2141,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2191,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2241,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2541,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2591,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2641,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2691,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2741,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2791,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2841,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2891,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2941,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3191,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3241,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3291,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3341,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3391,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3441,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3491,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3541,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3591,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3641,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3691,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3741,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4041,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4091,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4141,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4191,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4241,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4291,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4341,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4391,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4441,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4491,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4541,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4591,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4641,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4691,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4741,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4791,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4841,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4891,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4941,7 +4944,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4991,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5041,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5491,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5541,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5591,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5641,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5691,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5741,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6141,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6191,7 +6194,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6241,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6291,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6341,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6391,7 +6394,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6641,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6691,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6741,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6791,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6841,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6891,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6941,7 +6944,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6991,7 +6994,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7041,7 +7044,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7091,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7141,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7191,7 +7194,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7241,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7291,7 +7294,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7341,7 +7344,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7391,7 +7394,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7441,7 +7444,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7491,7 +7494,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7541,7 +7544,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7591,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7641,7 +7644,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7691,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7741,7 +7744,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7791,7 +7794,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7841,7 +7844,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7891,7 +7894,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7941,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7991,7 +7994,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8041,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8091,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8141,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8191,7 +8194,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8241,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8291,7 +8294,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8341,7 +8344,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8391,7 +8394,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8441,7 +8444,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8491,7 +8494,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8541,7 +8544,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8591,7 +8594,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8641,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8691,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8741,7 +8744,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8791,7 +8794,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8841,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8891,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8941,7 +8944,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8991,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9041,7 +9044,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9091,7 +9094,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9141,7 +9144,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9191,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9241,7 +9244,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9291,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9541,7 +9544,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9591,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9641,7 +9644,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9691,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9741,7 +9744,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9791,7 +9794,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9841,7 +9844,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9891,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10241,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10291,7 +10294,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10341,7 +10344,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10591,7 +10594,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10641,7 +10644,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10691,7 +10694,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10741,7 +10744,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10791,7 +10794,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10841,7 +10844,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10891,7 +10894,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10941,7 +10944,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10991,7 +10994,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11041,7 +11044,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11091,7 +11094,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11141,7 +11144,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11191,7 +11194,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11591,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11841,7 +11844,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11891,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11941,7 +11944,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11991,7 +11994,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12041,7 +12044,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12091,7 +12094,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12141,7 +12144,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12191,7 +12194,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12241,7 +12244,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12291,7 +12294,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12341,7 +12344,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12391,7 +12394,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12441,7 +12444,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12491,7 +12494,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12541,7 +12544,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12591,7 +12594,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12641,7 +12644,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16491,7 +16494,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16541,7 +16544,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16591,7 +16594,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16641,7 +16644,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16691,7 +16694,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16741,7 +16744,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16941,7 +16944,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16991,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17041,7 +17044,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17091,7 +17094,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17141,7 +17144,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17191,7 +17194,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17441,7 +17444,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17491,7 +17494,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17541,7 +17544,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17591,7 +17594,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17641,7 +17644,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17691,7 +17694,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17741,7 +17744,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17791,7 +17794,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17841,7 +17844,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18991,7 +18994,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19041,7 +19044,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19091,7 +19094,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19141,7 +19144,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19191,7 +19194,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19241,7 +19244,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19291,7 +19294,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19341,7 +19344,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19391,7 +19394,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19441,7 +19444,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -20041,7 +20044,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20091,7 +20094,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20141,7 +20144,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20191,7 +20194,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20241,7 +20244,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20291,7 +20294,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -22041,7 +22044,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22091,7 +22094,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22141,7 +22144,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22191,7 +22194,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22241,7 +22244,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22291,7 +22294,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22341,7 +22344,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22391,7 +22394,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22441,7 +22444,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22491,7 +22494,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22541,7 +22544,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22591,7 +22594,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22641,7 +22644,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22691,7 +22694,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22741,7 +22744,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22791,7 +22794,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22841,7 +22844,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22891,7 +22894,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22941,7 +22944,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23291,7 +23294,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23341,7 +23344,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23391,7 +23394,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23441,7 +23444,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23491,7 +23494,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23541,7 +23544,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23591,7 +23594,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23641,7 +23644,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23691,7 +23694,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23741,7 +23744,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23791,7 +23794,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23841,7 +23844,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23891,7 +23894,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23941,7 +23944,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23991,7 +23994,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24041,7 +24044,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24091,7 +24094,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24141,7 +24144,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24191,7 +24194,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24241,7 +24244,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24291,7 +24294,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24341,7 +24344,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24741,7 +24744,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24791,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24841,7 +24844,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24891,7 +24894,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24941,7 +24944,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24991,7 +24994,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25041,7 +25044,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25641,7 +25644,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25691,7 +25694,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25741,7 +25744,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25791,7 +25794,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25841,7 +25844,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25891,7 +25894,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25941,7 +25944,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25991,7 +25994,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26041,7 +26044,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26091,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26141,7 +26144,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26191,7 +26194,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26241,7 +26244,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26291,7 +26294,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26341,7 +26344,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26391,7 +26394,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26441,7 +26444,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26491,7 +26494,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26541,7 +26544,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26591,7 +26594,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26791,7 +26794,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26841,7 +26844,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26891,7 +26894,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26941,7 +26944,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26991,7 +26994,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27041,7 +27044,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27091,7 +27094,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -28041,7 +28044,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28091,7 +28094,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28141,7 +28144,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29441,7 +29444,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29491,7 +29494,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29541,7 +29544,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29591,7 +29594,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29641,7 +29644,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29691,7 +29694,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29741,7 +29744,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29791,7 +29794,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29841,7 +29844,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29891,7 +29894,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30191,7 +30194,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30241,7 +30244,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30291,7 +30294,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30341,7 +30344,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30391,7 +30394,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30441,7 +30444,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30491,7 +30494,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30541,7 +30544,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30591,7 +30594,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30641,7 +30644,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30691,7 +30694,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30891,7 +30894,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30941,7 +30944,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30991,7 +30994,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31041,7 +31044,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31091,7 +31094,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31141,7 +31144,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31191,7 +31194,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31241,7 +31244,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31291,7 +31294,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31591,7 +31594,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31641,7 +31644,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31691,7 +31694,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31741,7 +31744,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31791,7 +31794,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31841,7 +31844,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31891,7 +31894,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31941,7 +31944,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31991,7 +31994,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32041,7 +32044,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32091,7 +32094,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32141,7 +32144,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32741,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32791,7 +32794,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32841,7 +32844,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32891,7 +32894,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32941,7 +32944,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32991,7 +32994,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33041,7 +33044,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33091,7 +33094,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33141,7 +33144,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33191,7 +33194,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33391,7 +33394,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33441,7 +33444,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33491,7 +33494,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33541,7 +33544,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33591,7 +33594,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34491,7 +34494,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34541,7 +34544,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34591,7 +34594,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34641,7 +34644,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34691,7 +34694,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34741,7 +34744,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34791,7 +34794,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34841,7 +34844,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34891,7 +34894,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35541,7 +35544,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35591,7 +35594,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35641,7 +35644,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35691,7 +35694,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35741,7 +35744,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35791,7 +35794,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35841,7 +35844,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35891,7 +35894,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35941,7 +35944,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36341,7 +36344,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36391,7 +36394,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36441,7 +36444,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36491,7 +36494,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36541,7 +36544,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36591,7 +36594,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36641,7 +36644,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36691,7 +36694,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36741,7 +36744,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36791,7 +36794,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36841,7 +36844,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36891,7 +36894,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36941,7 +36944,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37241,7 +37244,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37291,7 +37294,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37341,7 +37344,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37391,7 +37394,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37691,7 +37694,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37741,7 +37744,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37791,7 +37794,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37841,7 +37844,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37891,7 +37894,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37941,7 +37944,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37991,7 +37994,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38041,7 +38044,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38091,7 +38094,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38141,7 +38144,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38391,7 +38394,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38441,7 +38444,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38491,7 +38494,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38541,7 +38544,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38591,7 +38594,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39191,7 +39194,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39241,7 +39244,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39291,7 +39294,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39341,7 +39344,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39391,7 +39394,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39441,7 +39444,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39491,7 +39494,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39541,7 +39544,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39591,7 +39594,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39641,7 +39644,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40441,7 +40444,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40491,7 +40494,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40541,7 +40544,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40591,7 +40594,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40641,7 +40644,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40691,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40741,7 +40744,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42441,7 +42444,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42491,7 +42494,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42541,7 +42544,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42591,7 +42594,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42641,7 +42644,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43191,7 +43194,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43241,7 +43244,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43291,7 +43294,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43341,7 +43344,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43391,7 +43394,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43441,7 +43444,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43591,7 +43594,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43641,7 +43644,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43691,7 +43694,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43741,7 +43744,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43791,7 +43794,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43841,7 +43844,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43891,7 +43894,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43941,7 +43944,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43991,7 +43994,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44041,7 +44044,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44091,7 +44094,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44141,7 +44144,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44191,7 +44194,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44241,7 +44244,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44291,7 +44294,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44341,7 +44344,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44391,7 +44394,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44441,7 +44444,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44491,7 +44494,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44541,7 +44544,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44841,7 +44844,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44891,7 +44894,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44941,7 +44944,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44991,7 +44994,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45041,7 +45044,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45091,7 +45094,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45141,7 +45144,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45191,7 +45194,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45241,7 +45244,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45291,7 +45294,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45341,7 +45344,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45391,7 +45394,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45441,7 +45444,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45491,7 +45494,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45541,7 +45544,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45591,7 +45594,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45641,7 +45644,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45691,7 +45694,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45991,7 +45994,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46041,7 +46044,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46091,7 +46094,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46141,7 +46144,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46191,7 +46194,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46441,7 +46444,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46491,7 +46494,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46541,7 +46544,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46591,7 +46594,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46841,7 +46844,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46891,7 +46894,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46941,7 +46944,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46991,7 +46994,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47041,7 +47044,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47091,7 +47094,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47141,7 +47144,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47191,7 +47194,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47241,7 +47244,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47291,7 +47294,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47341,7 +47344,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47691,7 +47694,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47741,7 +47744,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47791,7 +47794,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47841,7 +47844,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47891,7 +47894,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47941,7 +47944,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -47991,7 +47994,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48041,7 +48044,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48091,7 +48094,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48141,7 +48144,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48191,7 +48194,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48241,7 +48244,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48291,7 +48294,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48341,7 +48344,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48391,7 +48394,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48941,7 +48944,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48991,7 +48994,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49041,7 +49044,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49091,7 +49094,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49291,7 +49294,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49341,7 +49344,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49391,7 +49394,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49441,7 +49444,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49491,7 +49494,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49541,7 +49544,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49591,7 +49594,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49641,7 +49644,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49691,7 +49694,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50691,7 +50694,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50741,7 +50744,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50791,7 +50794,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50841,7 +50844,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50891,7 +50894,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50941,7 +50944,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50991,7 +50994,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51041,7 +51044,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51091,7 +51094,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51141,7 +51144,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51191,7 +51194,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51241,7 +51244,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51291,7 +51294,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51341,7 +51344,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51391,7 +51394,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51441,7 +51444,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51491,7 +51494,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51541,7 +51544,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51591,7 +51594,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51641,7 +51644,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51655,7 +51658,7 @@
         <v>0.5439992376982135</v>
       </c>
       <c r="D997" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E997">
         <v>0.4290141353004202</v>
@@ -51691,7 +51694,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51741,7 +51744,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51791,7 +51794,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51841,7 +51844,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51891,7 +51894,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -51941,7 +51944,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -51991,7 +51994,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52041,7 +52044,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52091,7 +52094,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52141,7 +52144,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52191,7 +52194,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52241,7 +52244,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52291,7 +52294,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52441,7 +52444,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52455,10 +52458,10 @@
         <v>0.4265302961812907</v>
       </c>
       <c r="D1013" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1013">
-        <v>0.5593901451167325</v>
+        <v>0.62396274632209</v>
       </c>
       <c r="F1013">
         <v>1</v>
@@ -52467,10 +52470,10 @@
         <v>0.01267346970381871</v>
       </c>
       <c r="H1013">
-        <v>0.01200060985488327</v>
+        <v>0.01171603725367791</v>
       </c>
       <c r="I1013">
-        <v>0.1328598489354418</v>
+        <v>0.1974324501407994</v>
       </c>
       <c r="J1013">
         <v>1.342866163118138</v>
@@ -52482,110 +52485,110 @@
         <v>6.55</v>
       </c>
       <c r="M1013">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1013">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1013">
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
       <c r="A1014" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1014" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C1014">
-        <v>0.3922468369608252</v>
+        <v>1.194967273410384</v>
       </c>
       <c r="D1014" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E1014">
-        <v>0.5593901451167325</v>
+        <v>0.6073068164043107</v>
       </c>
       <c r="F1014">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1014">
-        <v>0.01196775316303917</v>
+        <v>0.01692503272658962</v>
       </c>
       <c r="H1014">
-        <v>0.01200060985488327</v>
+        <v>0.01335269318359569</v>
       </c>
       <c r="I1014">
-        <v>0.1671433081559073</v>
+        <v>0.5876604570060735</v>
       </c>
       <c r="J1014">
-        <v>1.342866163118138</v>
+        <v>1.344450038733268</v>
       </c>
       <c r="K1014">
-        <v>4.31</v>
+        <v>5.85</v>
       </c>
       <c r="L1014">
-        <v>6.18</v>
+        <v>9.06</v>
       </c>
       <c r="M1014">
-        <v>4.26</v>
+        <v>4.74</v>
       </c>
       <c r="N1014">
-        <v>6.28</v>
+        <v>6.98</v>
       </c>
       <c r="O1014">
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>485</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
       <c r="A1015" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1015" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1015">
-        <v>1.194967273410384</v>
+        <v>0.4193078233762986</v>
       </c>
       <c r="D1015" t="s">
-        <v>194</v>
+        <v>371</v>
       </c>
       <c r="E1015">
-        <v>0.6937477923896846</v>
+        <v>0.617421340031604</v>
       </c>
       <c r="F1015">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1015">
-        <v>0.01692503272658962</v>
+        <v>0.0126806921766237</v>
       </c>
       <c r="H1015">
-        <v>0.01510625220761032</v>
+        <v>0.0117225786599684</v>
       </c>
       <c r="I1015">
-        <v>0.5012194810206996</v>
+        <v>0.1981135166553054</v>
       </c>
       <c r="J1015">
         <v>1.344450038733268</v>
       </c>
       <c r="K1015">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L1015">
-        <v>9.06</v>
+        <v>6.55</v>
       </c>
       <c r="M1015">
-        <v>5.36</v>
+        <v>4.13</v>
       </c>
       <c r="N1015">
-        <v>7.9</v>
+        <v>6.17</v>
       </c>
       <c r="O1015">
         <v>1</v>
@@ -52596,46 +52599,46 @@
     </row>
     <row r="1016" spans="1:16">
       <c r="A1016" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1016" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C1016">
-        <v>0.4134193260876273</v>
+        <v>0.3854203330596162</v>
       </c>
       <c r="D1016" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1016">
-        <v>0.5526428349962798</v>
+        <v>0.617421340031604</v>
       </c>
       <c r="F1016">
         <v>1</v>
       </c>
       <c r="G1016">
-        <v>0.01248658067391237</v>
+        <v>0.01197457966694038</v>
       </c>
       <c r="H1016">
-        <v>0.01200735716500372</v>
+        <v>0.0117225786599684</v>
       </c>
       <c r="I1016">
-        <v>0.1392235089086524</v>
+        <v>0.2320010069719878</v>
       </c>
       <c r="J1016">
         <v>1.344450038733268</v>
       </c>
       <c r="K1016">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="L1016">
-        <v>6.45</v>
+        <v>6.18</v>
       </c>
       <c r="M1016">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1016">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1016">
         <v>1</v>
@@ -52646,207 +52649,207 @@
     </row>
     <row r="1017" spans="1:16">
       <c r="A1017" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1017" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C1017">
-        <v>0.3854203330596162</v>
+        <v>1.166955212765879</v>
       </c>
       <c r="D1017" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E1017">
-        <v>0.5526428349962798</v>
+        <v>0.5846098647026094</v>
       </c>
       <c r="F1017">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1017">
-        <v>0.01197457966694038</v>
+        <v>0.01695304478723412</v>
       </c>
       <c r="H1017">
-        <v>0.01200735716500372</v>
+        <v>0.01337539013529739</v>
       </c>
       <c r="I1017">
-        <v>0.1672225019366635</v>
+        <v>0.5823453480632699</v>
       </c>
       <c r="J1017">
-        <v>1.344450038733268</v>
+        <v>1.349238425168226</v>
       </c>
       <c r="K1017">
-        <v>4.31</v>
+        <v>5.85</v>
       </c>
       <c r="L1017">
-        <v>6.18</v>
+        <v>9.06</v>
       </c>
       <c r="M1017">
-        <v>4.26</v>
+        <v>4.74</v>
       </c>
       <c r="N1017">
-        <v>6.28</v>
+        <v>6.98</v>
       </c>
       <c r="O1017">
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>192</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
       <c r="A1018" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1018" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1018">
-        <v>1.166955212765879</v>
+        <v>0.3974727812328904</v>
       </c>
       <c r="D1018" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E1018">
-        <v>0.5846098647026094</v>
+        <v>0.5976453040552272</v>
       </c>
       <c r="F1018">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1018">
-        <v>0.01695304478723412</v>
+        <v>0.01270252721876711</v>
       </c>
       <c r="H1018">
-        <v>0.01337539013529739</v>
+        <v>0.01174235469594477</v>
       </c>
       <c r="I1018">
-        <v>0.5823453480632699</v>
+        <v>0.2001725228223368</v>
       </c>
       <c r="J1018">
         <v>1.349238425168226</v>
       </c>
       <c r="K1018">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L1018">
-        <v>9.06</v>
+        <v>6.55</v>
       </c>
       <c r="M1018">
-        <v>4.74</v>
+        <v>4.13</v>
       </c>
       <c r="N1018">
-        <v>6.98</v>
+        <v>6.17</v>
       </c>
       <c r="O1018">
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
       <c r="A1019" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1019" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C1019">
-        <v>0.3974727812328904</v>
+        <v>0.3647823875249463</v>
       </c>
       <c r="D1019" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1019">
-        <v>0.5322443087833584</v>
+        <v>0.5976453040552272</v>
       </c>
       <c r="F1019">
         <v>1</v>
       </c>
       <c r="G1019">
-        <v>0.01270252721876711</v>
+        <v>0.01199521761247505</v>
       </c>
       <c r="H1019">
-        <v>0.01202775569121664</v>
+        <v>0.01174235469594477</v>
       </c>
       <c r="I1019">
-        <v>0.134771527550468</v>
+        <v>0.2328629165302809</v>
       </c>
       <c r="J1019">
         <v>1.349238425168226</v>
       </c>
       <c r="K1019">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1019">
-        <v>6.55</v>
+        <v>6.18</v>
       </c>
       <c r="M1019">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1019">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1019">
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
       <c r="A1020" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1020" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C1020">
-        <v>0.3647823875249463</v>
+        <v>0.8542276829218149</v>
       </c>
       <c r="D1020" t="s">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="E1020">
-        <v>0.5322443087833584</v>
+        <v>0.5065638875223204</v>
       </c>
       <c r="F1020">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1020">
-        <v>0.01199521761247505</v>
+        <v>0.01698577231707819</v>
       </c>
       <c r="H1020">
-        <v>0.01202775569121664</v>
+        <v>0.01577343611247768</v>
       </c>
       <c r="I1020">
-        <v>0.1674619212584121</v>
+        <v>0.3476637953994945</v>
       </c>
       <c r="J1020">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1020">
-        <v>4.31</v>
+        <v>5.97</v>
       </c>
       <c r="L1020">
-        <v>6.18</v>
+        <v>8.92</v>
       </c>
       <c r="M1020">
-        <v>4.26</v>
+        <v>5.65</v>
       </c>
       <c r="N1020">
-        <v>6.28</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O1020">
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
       <c r="A1021" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1021" t="s">
         <v>197</v>
@@ -52891,12 +52894,12 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
       <c r="A1022" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1022" t="s">
         <v>200</v>
@@ -52905,10 +52908,10 @@
         <v>0.3892090844427933</v>
       </c>
       <c r="D1022" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1022">
-        <v>0.524524276255768</v>
+        <v>0.5901608593747225</v>
       </c>
       <c r="F1022">
         <v>1</v>
@@ -52917,10 +52920,10 @@
         <v>0.01271079091555721</v>
       </c>
       <c r="H1022">
-        <v>0.01203547572374423</v>
+        <v>0.01174983914062528</v>
       </c>
       <c r="I1022">
-        <v>0.1353151918129747</v>
+        <v>0.2009517749319292</v>
       </c>
       <c r="J1022">
         <v>1.35105063937658</v>
@@ -52932,21 +52935,21 @@
         <v>6.55</v>
       </c>
       <c r="M1022">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1022">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1022">
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
       <c r="A1023" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1023" t="s">
         <v>201</v>
@@ -52955,10 +52958,10 @@
         <v>0.3569717442869385</v>
       </c>
       <c r="D1023" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1023">
-        <v>0.524524276255768</v>
+        <v>0.5901608593747225</v>
       </c>
       <c r="F1023">
         <v>1</v>
@@ -52967,10 +52970,10 @@
         <v>0.01200302825571306</v>
       </c>
       <c r="H1023">
-        <v>0.01203547572374423</v>
+        <v>0.01174983914062528</v>
       </c>
       <c r="I1023">
-        <v>0.1675525319688296</v>
+        <v>0.2331891150877841</v>
       </c>
       <c r="J1023">
         <v>1.35105063937658</v>
@@ -52982,16 +52985,16 @@
         <v>6.18</v>
       </c>
       <c r="M1023">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1023">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1023">
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -52999,7 +53002,7 @@
         <v>0</v>
       </c>
       <c r="B1024" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C1024">
         <v>0.8495456676775177</v>
@@ -53041,7 +53044,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53055,10 +53058,10 @@
         <v>0.3856328717938826</v>
       </c>
       <c r="D1025" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1025">
-        <v>0.5211833407548117</v>
+        <v>0.5869218773045475</v>
       </c>
       <c r="F1025">
         <v>1</v>
@@ -53067,10 +53070,10 @@
         <v>0.01271436712820612</v>
       </c>
       <c r="H1025">
-        <v>0.01203881665924519</v>
+        <v>0.01175307812269545</v>
       </c>
       <c r="I1025">
-        <v>0.135550468960929</v>
+        <v>0.2012890055106649</v>
       </c>
       <c r="J1025">
         <v>1.351834896536429</v>
@@ -53082,16 +53085,16 @@
         <v>6.55</v>
       </c>
       <c r="M1025">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1025">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1025">
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53105,10 +53108,10 @@
         <v>0.3535915959279903</v>
       </c>
       <c r="D1026" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1026">
-        <v>0.5211833407548117</v>
+        <v>0.5869218773045475</v>
       </c>
       <c r="F1026">
         <v>1</v>
@@ -53117,10 +53120,10 @@
         <v>0.01200640840407201</v>
       </c>
       <c r="H1026">
-        <v>0.01203881665924519</v>
+        <v>0.01175307812269545</v>
       </c>
       <c r="I1026">
-        <v>0.1675917448268214</v>
+        <v>0.2333302813765572</v>
       </c>
       <c r="J1026">
         <v>1.351834896536429</v>
@@ -53132,16 +53135,16 @@
         <v>6.18</v>
       </c>
       <c r="M1026">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1026">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1026">
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53149,7 +53152,7 @@
         <v>0</v>
       </c>
       <c r="B1027" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C1027">
         <v>0.8476088036369962</v>
@@ -53191,7 +53194,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53199,49 +53202,49 @@
         <v>1</v>
       </c>
       <c r="B1028" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C1028">
-        <v>0.3788046111105716</v>
+        <v>0.3841534580543895</v>
       </c>
       <c r="D1028" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1028">
-        <v>0.5198012568666011</v>
+        <v>0.5855819696852249</v>
       </c>
       <c r="F1028">
         <v>1</v>
       </c>
       <c r="G1028">
-        <v>0.01252119538888943</v>
+        <v>0.01271584654194561</v>
       </c>
       <c r="H1028">
-        <v>0.0120401987431334</v>
+        <v>0.01175441803031477</v>
       </c>
       <c r="I1028">
-        <v>0.1409966457560294</v>
+        <v>0.2014285116308354</v>
       </c>
       <c r="J1028">
         <v>1.352159329374037</v>
       </c>
       <c r="K1028">
-        <v>4.49</v>
+        <v>4.56</v>
       </c>
       <c r="L1028">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="M1028">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1028">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1028">
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53255,10 +53258,10 @@
         <v>0.3521932903978984</v>
       </c>
       <c r="D1029" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1029">
-        <v>0.5198012568666011</v>
+        <v>0.5855819696852249</v>
       </c>
       <c r="F1029">
         <v>1</v>
@@ -53267,10 +53270,10 @@
         <v>0.0120078067096021</v>
       </c>
       <c r="H1029">
-        <v>0.0120401987431334</v>
+        <v>0.01175441803031477</v>
       </c>
       <c r="I1029">
-        <v>0.1676079664687027</v>
+        <v>0.2333886792873265</v>
       </c>
       <c r="J1029">
         <v>1.352159329374037</v>
@@ -53282,16 +53285,16 @@
         <v>6.18</v>
       </c>
       <c r="M1029">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1029">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1029">
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53299,7 +53302,7 @@
         <v>0</v>
       </c>
       <c r="B1030" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C1030">
         <v>0.844077502681861</v>
@@ -53341,7 +53344,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53349,7 +53352,7 @@
         <v>1</v>
       </c>
       <c r="B1031" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C1031">
         <v>0.7957603626226968</v>
@@ -53391,7 +53394,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53399,49 +53402,49 @@
         <v>2</v>
       </c>
       <c r="B1032" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C1032">
-        <v>0.3761487415479987</v>
+        <v>0.7845305970027789</v>
       </c>
       <c r="D1032" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E1032">
-        <v>0.5172814340744942</v>
+        <v>0.5679610322800706</v>
       </c>
       <c r="F1032">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1032">
-        <v>0.012523851258452</v>
+        <v>0.01501546940299722</v>
       </c>
       <c r="H1032">
-        <v>0.01204271856592551</v>
+        <v>0.01339203896771993</v>
       </c>
       <c r="I1032">
-        <v>0.1411326925264955</v>
+        <v>0.2165695647227084</v>
       </c>
       <c r="J1032">
         <v>1.352750837071715</v>
       </c>
       <c r="K1032">
-        <v>4.49</v>
+        <v>5.26</v>
       </c>
       <c r="L1032">
-        <v>6.45</v>
+        <v>7.9</v>
       </c>
       <c r="M1032">
-        <v>4.26</v>
+        <v>4.74</v>
       </c>
       <c r="N1032">
-        <v>6.28</v>
+        <v>6.98</v>
       </c>
       <c r="O1032">
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53449,143 +53452,143 @@
         <v>3</v>
       </c>
       <c r="B1033" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C1033">
-        <v>0.3496438922209082</v>
+        <v>0.3761487415479987</v>
       </c>
       <c r="D1033" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1033">
-        <v>0.5172814340744942</v>
+        <v>0.5831390428938166</v>
       </c>
       <c r="F1033">
         <v>1</v>
       </c>
       <c r="G1033">
-        <v>0.01201035610777909</v>
+        <v>0.012523851258452</v>
       </c>
       <c r="H1033">
-        <v>0.01204271856592551</v>
+        <v>0.01175686095710619</v>
       </c>
       <c r="I1033">
-        <v>0.167637541853586</v>
+        <v>0.2069903013458179</v>
       </c>
       <c r="J1033">
         <v>1.352750837071715</v>
       </c>
       <c r="K1033">
-        <v>4.31</v>
+        <v>4.49</v>
       </c>
       <c r="L1033">
-        <v>6.18</v>
+        <v>6.45</v>
       </c>
       <c r="M1033">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1033">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1033">
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
       <c r="A1034" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1034" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C1034">
-        <v>0.8389074160156742</v>
+        <v>0.3496438922209082</v>
       </c>
       <c r="D1034" t="s">
-        <v>196</v>
+        <v>371</v>
       </c>
       <c r="E1034">
-        <v>0.4920648074520191</v>
+        <v>0.5831390428938166</v>
       </c>
       <c r="F1034">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1034">
-        <v>0.01700109258398433</v>
+        <v>0.01201035610777909</v>
       </c>
       <c r="H1034">
-        <v>0.01578793519254798</v>
+        <v>0.01175686095710619</v>
       </c>
       <c r="I1034">
-        <v>0.3468426085636551</v>
+        <v>0.2334951506729084</v>
       </c>
       <c r="J1034">
-        <v>1.353616848238581</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1034">
-        <v>5.97</v>
+        <v>4.31</v>
       </c>
       <c r="L1034">
-        <v>8.92</v>
+        <v>6.18</v>
       </c>
       <c r="M1034">
-        <v>5.65</v>
+        <v>4.13</v>
       </c>
       <c r="N1034">
-        <v>8.140000000000001</v>
+        <v>6.17</v>
       </c>
       <c r="O1034">
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>362</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
       <c r="A1035" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1035" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C1035">
-        <v>0.7909626607582627</v>
+        <v>0.8389074160156742</v>
       </c>
       <c r="D1035" t="s">
-        <v>363</v>
+        <v>196</v>
       </c>
       <c r="E1035">
-        <v>0.5638561393491281</v>
+        <v>0.4920648074520191</v>
       </c>
       <c r="F1035">
         <v>-1</v>
       </c>
       <c r="G1035">
-        <v>0.01578903733924173</v>
+        <v>0.01700109258398433</v>
       </c>
       <c r="H1035">
-        <v>0.01339614386065087</v>
+        <v>0.01578793519254798</v>
       </c>
       <c r="I1035">
-        <v>0.2271065214091346</v>
+        <v>0.3468426085636551</v>
       </c>
       <c r="J1035">
         <v>1.353616848238581</v>
       </c>
       <c r="K1035">
-        <v>5.54</v>
+        <v>5.97</v>
       </c>
       <c r="L1035">
-        <v>8.289999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="M1035">
-        <v>4.74</v>
+        <v>5.65</v>
       </c>
       <c r="N1035">
-        <v>6.98</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O1035">
         <v>1</v>
@@ -53596,13 +53599,13 @@
     </row>
     <row r="1036" spans="1:16">
       <c r="A1036" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1036" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C1036">
-        <v>0.7799753782650667</v>
+        <v>0.7909626607582627</v>
       </c>
       <c r="D1036" t="s">
         <v>363</v>
@@ -53614,22 +53617,22 @@
         <v>-1</v>
       </c>
       <c r="G1036">
-        <v>0.01502002462173493</v>
+        <v>0.01578903733924173</v>
       </c>
       <c r="H1036">
         <v>0.01339614386065087</v>
       </c>
       <c r="I1036">
-        <v>0.2161192389159385</v>
+        <v>0.2271065214091346</v>
       </c>
       <c r="J1036">
         <v>1.353616848238581</v>
       </c>
       <c r="K1036">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1036">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1036">
         <v>4.74</v>
@@ -53646,46 +53649,46 @@
     </row>
     <row r="1037" spans="1:16">
       <c r="A1037" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1037" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C1037">
-        <v>0.2664050253383161</v>
+        <v>0.7799753782650667</v>
       </c>
       <c r="D1037" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E1037">
-        <v>0.513592226503647</v>
+        <v>0.5638561393491281</v>
       </c>
       <c r="F1037">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1037">
-        <v>0.01231359497466168</v>
+        <v>0.01502002462173493</v>
       </c>
       <c r="H1037">
-        <v>0.01204640777349635</v>
+        <v>0.01339614386065087</v>
       </c>
       <c r="I1037">
-        <v>0.2471872011653309</v>
+        <v>0.2161192389159385</v>
       </c>
       <c r="J1037">
         <v>1.353616848238581</v>
       </c>
       <c r="K1037">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1037">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1037">
-        <v>4.26</v>
+        <v>4.74</v>
       </c>
       <c r="N1037">
-        <v>6.28</v>
+        <v>6.98</v>
       </c>
       <c r="O1037">
         <v>1</v>
@@ -53696,46 +53699,46 @@
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1038" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C1038">
-        <v>0.3459113840917176</v>
+        <v>0.372260351408773</v>
       </c>
       <c r="D1038" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1038">
-        <v>0.513592226503647</v>
+        <v>0.579562416774662</v>
       </c>
       <c r="F1038">
         <v>1</v>
       </c>
       <c r="G1038">
-        <v>0.01201408861590828</v>
+        <v>0.01252773964859123</v>
       </c>
       <c r="H1038">
-        <v>0.01204640777349635</v>
+        <v>0.01176043758322534</v>
       </c>
       <c r="I1038">
-        <v>0.1676808424119294</v>
+        <v>0.207302065365889</v>
       </c>
       <c r="J1038">
         <v>1.353616848238581</v>
       </c>
       <c r="K1038">
-        <v>4.31</v>
+        <v>4.49</v>
       </c>
       <c r="L1038">
-        <v>6.18</v>
+        <v>6.45</v>
       </c>
       <c r="M1038">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="N1038">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
       <c r="O1038">
         <v>1</v>
@@ -53746,63 +53749,63 @@
     </row>
     <row r="1039" spans="1:16">
       <c r="A1039" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1039" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C1039">
-        <v>0.8032731591004225</v>
+        <v>0.3459113840917176</v>
       </c>
       <c r="D1039" t="s">
-        <v>198</v>
+        <v>371</v>
       </c>
       <c r="E1039">
-        <v>0.4949307904987359</v>
+        <v>0.579562416774662</v>
       </c>
       <c r="F1039">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1039">
-        <v>0.01577672684089958</v>
+        <v>0.01201408861590828</v>
       </c>
       <c r="H1039">
-        <v>0.01322506920950126</v>
+        <v>0.01176043758322534</v>
       </c>
       <c r="I1039">
-        <v>0.3083423686016866</v>
+        <v>0.2336510326829444</v>
       </c>
       <c r="J1039">
-        <v>1.351394736624472</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1039">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1039">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1039">
-        <v>4.71</v>
+        <v>4.13</v>
       </c>
       <c r="N1039">
-        <v>6.86</v>
+        <v>6.17</v>
       </c>
       <c r="O1039">
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>203</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1040" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C1040">
-        <v>0.7916636853552763</v>
+        <v>0.8032731591004225</v>
       </c>
       <c r="D1040" t="s">
         <v>198</v>
@@ -53814,22 +53817,22 @@
         <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.01500833631464472</v>
+        <v>0.01577672684089958</v>
       </c>
       <c r="H1040">
         <v>0.01322506920950126</v>
       </c>
       <c r="I1040">
-        <v>0.2967328948565404</v>
+        <v>0.3083423686016866</v>
       </c>
       <c r="J1040">
         <v>1.351394736624472</v>
       </c>
       <c r="K1040">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1040">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1040">
         <v>4.71</v>
@@ -53841,68 +53844,68 @@
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1041" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C1041">
-        <v>0.276293422021098</v>
+        <v>0.7916636853552763</v>
       </c>
       <c r="D1041" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1041">
-        <v>0.5727955272059084</v>
+        <v>0.4949307904987359</v>
       </c>
       <c r="F1041">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1041">
-        <v>0.0123037065779789</v>
+        <v>0.01500833631464472</v>
       </c>
       <c r="H1041">
-        <v>0.01162720447279409</v>
+        <v>0.01322506920950126</v>
       </c>
       <c r="I1041">
-        <v>0.2965021051848105</v>
+        <v>0.2967328948565404</v>
       </c>
       <c r="J1041">
         <v>1.351394736624472</v>
       </c>
       <c r="K1041">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1041">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1041">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1041">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1041">
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1042" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1042">
-        <v>0.3554886851485248</v>
+        <v>0.276293422021098</v>
       </c>
       <c r="D1042" t="s">
         <v>369</v>
@@ -53914,22 +53917,22 @@
         <v>1</v>
       </c>
       <c r="G1042">
-        <v>0.01200451131485147</v>
+        <v>0.0123037065779789</v>
       </c>
       <c r="H1042">
         <v>0.01162720447279409</v>
       </c>
       <c r="I1042">
-        <v>0.2173068420573836</v>
+        <v>0.2965021051848105</v>
       </c>
       <c r="J1042">
         <v>1.351394736624472</v>
       </c>
       <c r="K1042">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1042">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1042">
         <v>4.09</v>
@@ -53941,68 +53944,68 @@
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1043" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C1043">
-        <v>0.8031318580204516</v>
+        <v>0.3554886851485248</v>
       </c>
       <c r="D1043" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1043">
-        <v>0.4948106590751502</v>
+        <v>0.5727955272059084</v>
       </c>
       <c r="F1043">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1043">
-        <v>0.01577686814197955</v>
+        <v>0.01200451131485147</v>
       </c>
       <c r="H1043">
-        <v>0.01322518934092485</v>
+        <v>0.01162720447279409</v>
       </c>
       <c r="I1043">
-        <v>0.3083211989453014</v>
+        <v>0.2173068420573836</v>
       </c>
       <c r="J1043">
-        <v>1.351420242234575</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1043">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1043">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1043">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1043">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1043">
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1044" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C1044">
-        <v>0.7915295258461343</v>
+        <v>0.8031318580204516</v>
       </c>
       <c r="D1044" t="s">
         <v>198</v>
@@ -54014,22 +54017,22 @@
         <v>-1</v>
       </c>
       <c r="G1044">
-        <v>0.01500847047415387</v>
+        <v>0.01577686814197955</v>
       </c>
       <c r="H1044">
         <v>0.01322518934092485</v>
       </c>
       <c r="I1044">
-        <v>0.2967188667709841</v>
+        <v>0.3083211989453014</v>
       </c>
       <c r="J1044">
         <v>1.351420242234575</v>
       </c>
       <c r="K1044">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1044">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1044">
         <v>4.71</v>
@@ -54046,46 +54049,46 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1045" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C1045">
-        <v>0.2761799220561398</v>
+        <v>0.7915295258461343</v>
       </c>
       <c r="D1045" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1045">
-        <v>0.5726912092605865</v>
+        <v>0.4948106590751502</v>
       </c>
       <c r="F1045">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.01230382007794386</v>
+        <v>0.01500847047415387</v>
       </c>
       <c r="H1045">
-        <v>0.01162730879073941</v>
+        <v>0.01322518934092485</v>
       </c>
       <c r="I1045">
-        <v>0.2965112872044466</v>
+        <v>0.2967188667709841</v>
       </c>
       <c r="J1045">
         <v>1.351420242234575</v>
       </c>
       <c r="K1045">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1045">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1045">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1045">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1045">
         <v>1</v>
@@ -54096,13 +54099,13 @@
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1046" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1046">
-        <v>0.3553787559689807</v>
+        <v>0.2761799220561398</v>
       </c>
       <c r="D1046" t="s">
         <v>369</v>
@@ -54114,22 +54117,22 @@
         <v>1</v>
       </c>
       <c r="G1046">
-        <v>0.01200462124403102</v>
+        <v>0.01230382007794386</v>
       </c>
       <c r="H1046">
         <v>0.01162730879073941</v>
       </c>
       <c r="I1046">
-        <v>0.2173124532916058</v>
+        <v>0.2965112872044466</v>
       </c>
       <c r="J1046">
         <v>1.351420242234575</v>
       </c>
       <c r="K1046">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1046">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1046">
         <v>4.09</v>
@@ -54146,63 +54149,63 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1047" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C1047">
-        <v>0.8327877653809024</v>
+        <v>0.3553787559689807</v>
       </c>
       <c r="D1047" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1047">
-        <v>0.5200235333834033</v>
+        <v>0.5726912092605865</v>
       </c>
       <c r="F1047">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.0157472122346191</v>
+        <v>0.01200462124403102</v>
       </c>
       <c r="H1047">
-        <v>0.0131999764666166</v>
+        <v>0.01162730879073941</v>
       </c>
       <c r="I1047">
-        <v>0.312764231997499</v>
+        <v>0.2173124532916058</v>
       </c>
       <c r="J1047">
-        <v>1.346067190364458</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1047">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1047">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1047">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1047">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1048" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C1048">
-        <v>0.8196865786829521</v>
+        <v>0.8327877653809024</v>
       </c>
       <c r="D1048" t="s">
         <v>198</v>
@@ -54214,22 +54217,22 @@
         <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.01498031342131705</v>
+        <v>0.0157472122346191</v>
       </c>
       <c r="H1048">
         <v>0.0131999764666166</v>
       </c>
       <c r="I1048">
-        <v>0.2996630452995488</v>
+        <v>0.312764231997499</v>
       </c>
       <c r="J1048">
         <v>1.346067190364458</v>
       </c>
       <c r="K1048">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1048">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1048">
         <v>4.71</v>
@@ -54246,46 +54249,46 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1049" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C1049">
-        <v>0.3000010028781626</v>
+        <v>0.8196865786829521</v>
       </c>
       <c r="D1049" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1049">
-        <v>0.5945851914093669</v>
+        <v>0.5200235333834033</v>
       </c>
       <c r="F1049">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.01227999899712184</v>
+        <v>0.01498031342131705</v>
       </c>
       <c r="H1049">
-        <v>0.01160541480859063</v>
+        <v>0.0131999764666166</v>
       </c>
       <c r="I1049">
-        <v>0.2945841885312044</v>
+        <v>0.2996630452995488</v>
       </c>
       <c r="J1049">
         <v>1.346067190364458</v>
       </c>
       <c r="K1049">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1049">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1049">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1049">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1049">
         <v>1</v>
@@ -54296,13 +54299,13 @@
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1050" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1050">
-        <v>0.3784504095291865</v>
+        <v>0.3000010028781626</v>
       </c>
       <c r="D1050" t="s">
         <v>369</v>
@@ -54314,22 +54317,22 @@
         <v>1</v>
       </c>
       <c r="G1050">
-        <v>0.01198154959047081</v>
+        <v>0.01227999899712184</v>
       </c>
       <c r="H1050">
         <v>0.01160541480859063</v>
       </c>
       <c r="I1050">
-        <v>0.2161347818801804</v>
+        <v>0.2945841885312044</v>
       </c>
       <c r="J1050">
         <v>1.346067190364458</v>
       </c>
       <c r="K1050">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1050">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1050">
         <v>4.09</v>
@@ -54346,96 +54349,96 @@
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1051" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C1051">
-        <v>0.8114319364950138</v>
+        <v>0.3784504095291865</v>
       </c>
       <c r="D1051" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1051">
-        <v>0.5126320191808968</v>
+        <v>0.5945851914093669</v>
       </c>
       <c r="F1051">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1051">
-        <v>0.01498856806350499</v>
+        <v>0.01198154959047081</v>
       </c>
       <c r="H1051">
-        <v>0.0132073679808191</v>
+        <v>0.01160541480859063</v>
       </c>
       <c r="I1051">
-        <v>0.2987999173141169</v>
+        <v>0.2161347818801804</v>
       </c>
       <c r="J1051">
-        <v>1.347636513974332</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1051">
-        <v>5.26</v>
+        <v>4.31</v>
       </c>
       <c r="L1051">
-        <v>7.9</v>
+        <v>6.18</v>
       </c>
       <c r="M1051">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1051">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1051">
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>365</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1052" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C1052">
-        <v>0.2930175128142221</v>
+        <v>0.8114319364950138</v>
       </c>
       <c r="D1052" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1052">
-        <v>0.5881666578449822</v>
+        <v>0.5126320191808968</v>
       </c>
       <c r="F1052">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.01228698248718578</v>
+        <v>0.01498856806350499</v>
       </c>
       <c r="H1052">
-        <v>0.01161183334215502</v>
+        <v>0.0132073679808191</v>
       </c>
       <c r="I1052">
-        <v>0.2951491450307602</v>
+        <v>0.2987999173141169</v>
       </c>
       <c r="J1052">
         <v>1.347636513974332</v>
       </c>
       <c r="K1052">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1052">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1052">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1052">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1052">
         <v>1</v>
@@ -54446,13 +54449,13 @@
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1053" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1053">
-        <v>0.3716866247706294</v>
+        <v>0.2930175128142221</v>
       </c>
       <c r="D1053" t="s">
         <v>369</v>
@@ -54464,22 +54467,22 @@
         <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.01198831337522937</v>
+        <v>0.01228698248718578</v>
       </c>
       <c r="H1053">
         <v>0.01161183334215502</v>
       </c>
       <c r="I1053">
-        <v>0.2164800330743528</v>
+        <v>0.2951491450307602</v>
       </c>
       <c r="J1053">
         <v>1.347636513974332</v>
       </c>
       <c r="K1053">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1053">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1053">
         <v>4.09</v>
@@ -54496,63 +54499,63 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1054" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1054">
-        <v>0.6963736868234349</v>
+        <v>0.3716866247706294</v>
       </c>
       <c r="D1054" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1054">
-        <v>0.5070592712848851</v>
+        <v>0.5881666578449822</v>
       </c>
       <c r="F1054">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1054">
-        <v>0.01526362631317657</v>
+        <v>0.01198831337522937</v>
       </c>
       <c r="H1054">
-        <v>0.01321294072871512</v>
+        <v>0.01161183334215502</v>
       </c>
       <c r="I1054">
-        <v>0.1893144155385498</v>
+        <v>0.2164800330743528</v>
       </c>
       <c r="J1054">
-        <v>1.34881968762529</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1054">
-        <v>5.4</v>
+        <v>4.31</v>
       </c>
       <c r="L1054">
-        <v>7.98</v>
+        <v>6.18</v>
       </c>
       <c r="M1054">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1054">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>204</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1055" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C1055">
-        <v>0.6986891056461033</v>
+        <v>0.6963736868234349</v>
       </c>
       <c r="D1055" t="s">
         <v>198</v>
@@ -54564,22 +54567,22 @@
         <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.0137013108943539</v>
+        <v>0.01526362631317657</v>
       </c>
       <c r="H1055">
         <v>0.01321294072871512</v>
       </c>
       <c r="I1055">
-        <v>0.1916298343612182</v>
+        <v>0.1893144155385498</v>
       </c>
       <c r="J1055">
         <v>1.34881968762529</v>
       </c>
       <c r="K1055">
-        <v>4.82</v>
+        <v>5.4</v>
       </c>
       <c r="L1055">
-        <v>7.2</v>
+        <v>7.98</v>
       </c>
       <c r="M1055">
         <v>4.71</v>
@@ -54591,68 +54594,68 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1056" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C1056">
-        <v>0.2877523900674603</v>
+        <v>0.6986891056461033</v>
       </c>
       <c r="D1056" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1056">
-        <v>0.5833274776125643</v>
+        <v>0.5070592712848851</v>
       </c>
       <c r="F1056">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.01229224760993254</v>
+        <v>0.0137013108943539</v>
       </c>
       <c r="H1056">
-        <v>0.01161667252238744</v>
+        <v>0.01321294072871512</v>
       </c>
       <c r="I1056">
-        <v>0.295575087545104</v>
+        <v>0.1916298343612182</v>
       </c>
       <c r="J1056">
         <v>1.34881968762529</v>
       </c>
       <c r="K1056">
-        <v>4.45</v>
+        <v>4.82</v>
       </c>
       <c r="L1056">
-        <v>6.29</v>
+        <v>7.2</v>
       </c>
       <c r="M1056">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1056">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1057" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1057">
-        <v>0.366587146335001</v>
+        <v>0.2877523900674603</v>
       </c>
       <c r="D1057" t="s">
         <v>369</v>
@@ -54664,22 +54667,22 @@
         <v>1</v>
       </c>
       <c r="G1057">
-        <v>0.011993412853665</v>
+        <v>0.01229224760993254</v>
       </c>
       <c r="H1057">
         <v>0.01161667252238744</v>
       </c>
       <c r="I1057">
-        <v>0.2167403312775633</v>
+        <v>0.295575087545104</v>
       </c>
       <c r="J1057">
         <v>1.34881968762529</v>
       </c>
       <c r="K1057">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1057">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1057">
         <v>4.09</v>
@@ -54691,68 +54694,68 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1058" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C1058">
-        <v>0.685527947714454</v>
+        <v>0.366587146335001</v>
       </c>
       <c r="D1058" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1058">
-        <v>0.4975993766176074</v>
+        <v>0.5833274776125643</v>
       </c>
       <c r="F1058">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.01527447205228555</v>
+        <v>0.011993412853665</v>
       </c>
       <c r="H1058">
-        <v>0.01322240062338239</v>
+        <v>0.01161667252238744</v>
       </c>
       <c r="I1058">
-        <v>0.1879285710968466</v>
+        <v>0.2167403312775633</v>
       </c>
       <c r="J1058">
-        <v>1.350828157830657</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1058">
-        <v>5.4</v>
+        <v>4.31</v>
       </c>
       <c r="L1058">
-        <v>7.98</v>
+        <v>6.18</v>
       </c>
       <c r="M1058">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1058">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1059" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C1059">
-        <v>0.6760248424128479</v>
+        <v>0.685527947714454</v>
       </c>
       <c r="D1059" t="s">
         <v>198</v>
@@ -54764,22 +54767,22 @@
         <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.01364397515758715</v>
+        <v>0.01527447205228555</v>
       </c>
       <c r="H1059">
         <v>0.01322240062338239</v>
       </c>
       <c r="I1059">
-        <v>0.1784254657952404</v>
+        <v>0.1879285710968466</v>
       </c>
       <c r="J1059">
         <v>1.350828157830657</v>
       </c>
       <c r="K1059">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L1059">
-        <v>7.16</v>
+        <v>7.98</v>
       </c>
       <c r="M1059">
         <v>4.71</v>
@@ -54796,46 +54799,46 @@
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1060" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1060">
-        <v>0.2788146976535772</v>
+        <v>0.6760248424128479</v>
       </c>
       <c r="D1060" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1060">
-        <v>0.5751128344726144</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1060">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.01230118530234642</v>
+        <v>0.01364397515758715</v>
       </c>
       <c r="H1060">
-        <v>0.01162488716552739</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1060">
-        <v>0.2962981368190372</v>
+        <v>0.1784254657952404</v>
       </c>
       <c r="J1060">
         <v>1.350828157830657</v>
       </c>
       <c r="K1060">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1060">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1060">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1060">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1060">
         <v>1</v>
@@ -54846,13 +54849,13 @@
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1061" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1061">
-        <v>0.3579306397498696</v>
+        <v>0.2788146976535772</v>
       </c>
       <c r="D1061" t="s">
         <v>369</v>
@@ -54864,22 +54867,22 @@
         <v>1</v>
       </c>
       <c r="G1061">
-        <v>0.01200206936025013</v>
+        <v>0.01230118530234642</v>
       </c>
       <c r="H1061">
         <v>0.01162488716552739</v>
       </c>
       <c r="I1061">
-        <v>0.2171821947227448</v>
+        <v>0.2962981368190372</v>
       </c>
       <c r="J1061">
         <v>1.350828157830657</v>
       </c>
       <c r="K1061">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1061">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1061">
         <v>4.09</v>
@@ -54896,96 +54899,96 @@
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1062" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1062">
-        <v>0.6767185447573851</v>
+        <v>0.3579306397498696</v>
       </c>
       <c r="D1062" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1062">
-        <v>0.4982800720431841</v>
+        <v>0.5751128344726144</v>
       </c>
       <c r="F1062">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.01364328145524261</v>
+        <v>0.01200206936025013</v>
       </c>
       <c r="H1062">
-        <v>0.01322171992795682</v>
+        <v>0.01162488716552739</v>
       </c>
       <c r="I1062">
-        <v>0.178438472714201</v>
+        <v>0.2171821947227448</v>
       </c>
       <c r="J1062">
-        <v>1.350683636508878</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1062">
-        <v>4.8</v>
+        <v>4.31</v>
       </c>
       <c r="L1062">
-        <v>7.16</v>
+        <v>6.18</v>
       </c>
       <c r="M1062">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1062">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1062">
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1063" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1063">
-        <v>0.2794578175354925</v>
+        <v>0.6767185447573851</v>
       </c>
       <c r="D1063" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1063">
-        <v>0.5757039266786883</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1063">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1063">
-        <v>0.01230054218246451</v>
+        <v>0.01364328145524261</v>
       </c>
       <c r="H1063">
-        <v>0.01162429607332131</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1063">
-        <v>0.2962461091431958</v>
+        <v>0.178438472714201</v>
       </c>
       <c r="J1063">
         <v>1.350683636508878</v>
       </c>
       <c r="K1063">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1063">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1063">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1063">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1063">
         <v>1</v>
@@ -54996,13 +54999,13 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1064" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1064">
-        <v>0.2015398539165574</v>
+        <v>0.2794578175354925</v>
       </c>
       <c r="D1064" t="s">
         <v>369</v>
@@ -55014,22 +55017,22 @@
         <v>1</v>
       </c>
       <c r="G1064">
-        <v>0.01189846014608344</v>
+        <v>0.01230054218246451</v>
       </c>
       <c r="H1064">
         <v>0.01162429607332131</v>
       </c>
       <c r="I1064">
-        <v>0.3741640727621309</v>
+        <v>0.2962461091431958</v>
       </c>
       <c r="J1064">
         <v>1.350683636508878</v>
       </c>
       <c r="K1064">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="L1064">
-        <v>6.05</v>
+        <v>6.29</v>
       </c>
       <c r="M1064">
         <v>4.09</v>
@@ -55046,163 +55049,163 @@
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1065" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1065">
-        <v>0.6674364420145809</v>
+        <v>0.3585535266467357</v>
       </c>
       <c r="D1065" t="s">
-        <v>199</v>
+        <v>369</v>
       </c>
       <c r="E1065">
-        <v>0.4167478384678054</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1065">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1065">
-        <v>0.01365256355798542</v>
+        <v>0.01200144647335326</v>
       </c>
       <c r="H1065">
-        <v>0.01256325216153219</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1065">
-        <v>0.2506886035467755</v>
+        <v>0.2171504000319526</v>
       </c>
       <c r="J1065">
-        <v>1.352617407913629</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1065">
-        <v>4.8</v>
+        <v>4.31</v>
       </c>
       <c r="L1065">
-        <v>7.16</v>
+        <v>6.18</v>
       </c>
       <c r="M1065">
-        <v>4.49</v>
+        <v>4.09</v>
       </c>
       <c r="N1065">
-        <v>6.49</v>
+        <v>6.1</v>
       </c>
       <c r="O1065">
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1066" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C1066">
-        <v>0.6421196605685342</v>
+        <v>0.6674364420145809</v>
       </c>
       <c r="D1066" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E1066">
-        <v>0.4167478384678054</v>
+        <v>0.4891720087268077</v>
       </c>
       <c r="F1066">
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.01343788033943147</v>
+        <v>0.01365256355798542</v>
       </c>
       <c r="H1066">
-        <v>0.01256325216153219</v>
+        <v>0.01323082799127319</v>
       </c>
       <c r="I1066">
-        <v>0.2253718221007288</v>
+        <v>0.1782644332877732</v>
       </c>
       <c r="J1066">
         <v>1.352617407913629</v>
       </c>
       <c r="K1066">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="L1066">
-        <v>7.04</v>
+        <v>7.16</v>
       </c>
       <c r="M1066">
-        <v>4.49</v>
+        <v>4.71</v>
       </c>
       <c r="N1066">
-        <v>6.49</v>
+        <v>6.86</v>
       </c>
       <c r="O1066">
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1067" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C1067">
-        <v>0.2708525347843507</v>
+        <v>0.6421196605685342</v>
       </c>
       <c r="D1067" t="s">
-        <v>368</v>
+        <v>198</v>
       </c>
       <c r="E1067">
-        <v>0.4960592349210309</v>
+        <v>0.4891720087268077</v>
       </c>
       <c r="F1067">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.01230914746521565</v>
+        <v>0.01343788033943147</v>
       </c>
       <c r="H1067">
-        <v>0.01180394076507897</v>
+        <v>0.01323082799127319</v>
       </c>
       <c r="I1067">
-        <v>0.2252067001366802</v>
+        <v>0.1529476518417265</v>
       </c>
       <c r="J1067">
         <v>1.352617407913629</v>
       </c>
       <c r="K1067">
-        <v>4.45</v>
+        <v>4.73</v>
       </c>
       <c r="L1067">
-        <v>6.29</v>
+        <v>7.04</v>
       </c>
       <c r="M1067">
-        <v>4.18</v>
+        <v>4.71</v>
       </c>
       <c r="N1067">
-        <v>6.15</v>
+        <v>6.86</v>
       </c>
       <c r="O1067">
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1068" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1068">
-        <v>0.193166623733986</v>
+        <v>0.2708525347843507</v>
       </c>
       <c r="D1068" t="s">
         <v>368</v>
@@ -55214,22 +55217,22 @@
         <v>1</v>
       </c>
       <c r="G1068">
-        <v>0.01190683337626602</v>
+        <v>0.01230914746521565</v>
       </c>
       <c r="H1068">
         <v>0.01180394076507897</v>
       </c>
       <c r="I1068">
-        <v>0.3028926111870449</v>
+        <v>0.2252067001366802</v>
       </c>
       <c r="J1068">
         <v>1.352617407913629</v>
       </c>
       <c r="K1068">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="L1068">
-        <v>6.05</v>
+        <v>6.29</v>
       </c>
       <c r="M1068">
         <v>4.18</v>
@@ -55241,101 +55244,101 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1069" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C1069">
-        <v>0.653707777522631</v>
+        <v>0.193166623733986</v>
       </c>
       <c r="D1069" t="s">
-        <v>199</v>
+        <v>368</v>
       </c>
       <c r="E1069">
-        <v>0.4039058168909611</v>
+        <v>0.4960592349210309</v>
       </c>
       <c r="F1069">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1069">
-        <v>0.01366629222247737</v>
+        <v>0.01190683337626602</v>
       </c>
       <c r="H1069">
-        <v>0.01257609418310904</v>
+        <v>0.01180394076507897</v>
       </c>
       <c r="I1069">
-        <v>0.2498019606316699</v>
+        <v>0.3028926111870449</v>
       </c>
       <c r="J1069">
-        <v>1.355477546349452</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1069">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="L1069">
-        <v>7.16</v>
+        <v>6.05</v>
       </c>
       <c r="M1069">
-        <v>4.49</v>
+        <v>4.18</v>
       </c>
       <c r="N1069">
-        <v>6.49</v>
+        <v>6.15</v>
       </c>
       <c r="O1069">
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1070" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1070">
-        <v>0.2581249187449384</v>
+        <v>0.653707777522631</v>
       </c>
       <c r="D1070" t="s">
-        <v>368</v>
+        <v>199</v>
       </c>
       <c r="E1070">
-        <v>0.4841038562592912</v>
+        <v>0.4039058168909611</v>
       </c>
       <c r="F1070">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.01232187508125506</v>
+        <v>0.01366629222247737</v>
       </c>
       <c r="H1070">
-        <v>0.01181589614374071</v>
+        <v>0.01257609418310904</v>
       </c>
       <c r="I1070">
-        <v>0.2259789375143528</v>
+        <v>0.2498019606316699</v>
       </c>
       <c r="J1070">
         <v>1.355477546349452</v>
       </c>
       <c r="K1070">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1070">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1070">
-        <v>4.18</v>
+        <v>4.49</v>
       </c>
       <c r="N1070">
-        <v>6.15</v>
+        <v>6.49</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55346,13 +55349,13 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1071" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1071">
-        <v>0.1807822243068724</v>
+        <v>0.2581249187449384</v>
       </c>
       <c r="D1071" t="s">
         <v>368</v>
@@ -55364,22 +55367,22 @@
         <v>1</v>
       </c>
       <c r="G1071">
-        <v>0.01191921777569313</v>
+        <v>0.01232187508125506</v>
       </c>
       <c r="H1071">
         <v>0.01181589614374071</v>
       </c>
       <c r="I1071">
-        <v>0.3033216319524188</v>
+        <v>0.2259789375143528</v>
       </c>
       <c r="J1071">
         <v>1.355477546349452</v>
       </c>
       <c r="K1071">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="L1071">
-        <v>6.05</v>
+        <v>6.29</v>
       </c>
       <c r="M1071">
         <v>4.18</v>
@@ -55396,96 +55399,96 @@
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1072" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C1072">
-        <v>0.6493738814716474</v>
+        <v>0.1807822243068724</v>
       </c>
       <c r="D1072" t="s">
-        <v>199</v>
+        <v>368</v>
       </c>
       <c r="E1072">
-        <v>0.3998518182932695</v>
+        <v>0.4841038562592912</v>
       </c>
       <c r="F1072">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1072">
-        <v>0.01367062611852835</v>
+        <v>0.01191921777569313</v>
       </c>
       <c r="H1072">
-        <v>0.01258014818170673</v>
+        <v>0.01181589614374071</v>
       </c>
       <c r="I1072">
-        <v>0.2495220631783779</v>
+        <v>0.3033216319524188</v>
       </c>
       <c r="J1072">
-        <v>1.356380441360074</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1072">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="L1072">
-        <v>7.16</v>
+        <v>6.05</v>
       </c>
       <c r="M1072">
-        <v>4.49</v>
+        <v>4.18</v>
       </c>
       <c r="N1072">
-        <v>6.49</v>
+        <v>6.15</v>
       </c>
       <c r="O1072">
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1073" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1073">
-        <v>0.2541070359476727</v>
+        <v>0.6493738814716474</v>
       </c>
       <c r="D1073" t="s">
-        <v>368</v>
+        <v>199</v>
       </c>
       <c r="E1073">
-        <v>0.4803297551148935</v>
+        <v>0.3998518182932695</v>
       </c>
       <c r="F1073">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1073">
-        <v>0.01232589296405233</v>
+        <v>0.01367062611852835</v>
       </c>
       <c r="H1073">
-        <v>0.01181967024488511</v>
+        <v>0.01258014818170673</v>
       </c>
       <c r="I1073">
-        <v>0.2262227191672208</v>
+        <v>0.2495220631783779</v>
       </c>
       <c r="J1073">
         <v>1.356380441360074</v>
       </c>
       <c r="K1073">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1073">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1073">
-        <v>4.18</v>
+        <v>4.49</v>
       </c>
       <c r="N1073">
-        <v>6.15</v>
+        <v>6.49</v>
       </c>
       <c r="O1073">
         <v>1</v>
@@ -55496,13 +55499,13 @@
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1074" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1074">
-        <v>0.1768726889108816</v>
+        <v>0.2541070359476727</v>
       </c>
       <c r="D1074" t="s">
         <v>368</v>
@@ -55514,22 +55517,22 @@
         <v>1</v>
       </c>
       <c r="G1074">
-        <v>0.01192312731108912</v>
+        <v>0.01232589296405233</v>
       </c>
       <c r="H1074">
         <v>0.01181967024488511</v>
       </c>
       <c r="I1074">
-        <v>0.3034570662040119</v>
+        <v>0.2262227191672208</v>
       </c>
       <c r="J1074">
         <v>1.356380441360074</v>
       </c>
       <c r="K1074">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="L1074">
-        <v>6.05</v>
+        <v>6.29</v>
       </c>
       <c r="M1074">
         <v>4.18</v>
@@ -55541,6 +55544,56 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:16">
+      <c r="A1075" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1075">
+        <v>0.1768726889108816</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>368</v>
+      </c>
+      <c r="E1075">
+        <v>0.4803297551148935</v>
+      </c>
+      <c r="F1075">
+        <v>1</v>
+      </c>
+      <c r="G1075">
+        <v>0.01192312731108912</v>
+      </c>
+      <c r="H1075">
+        <v>0.01181967024488511</v>
+      </c>
+      <c r="I1075">
+        <v>0.3034570662040119</v>
+      </c>
+      <c r="J1075">
+        <v>1.356380441360074</v>
+      </c>
+      <c r="K1075">
+        <v>4.33</v>
+      </c>
+      <c r="L1075">
+        <v>6.05</v>
+      </c>
+      <c r="M1075">
+        <v>4.18</v>
+      </c>
+      <c r="N1075">
+        <v>6.15</v>
+      </c>
+      <c r="O1075">
+        <v>1</v>
+      </c>
+      <c r="P1075" t="s">
         <v>208</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="494">
   <si>
     <t>trade_time</t>
   </si>
@@ -1132,6 +1132,12 @@
     <t>2021-11-25</t>
   </si>
   <si>
+    <t>2021-11-26</t>
+  </si>
+  <si>
+    <t>2021-11-29</t>
+  </si>
+  <si>
     <t>2016-10-17</t>
   </si>
   <si>
@@ -1847,7 +1853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1075"/>
+  <dimension ref="A1:P1073"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1944,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1994,7 +2000,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2044,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2094,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2144,7 +2150,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2194,7 +2200,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2244,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2544,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2594,7 +2600,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2644,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2694,7 +2700,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2744,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2794,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2844,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2894,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2944,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3194,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3244,7 +3250,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3294,7 +3300,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3344,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3394,7 +3400,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3444,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3494,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3544,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3594,7 +3600,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3644,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3694,7 +3700,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3744,7 +3750,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4044,7 +4050,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4094,7 +4100,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4144,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4194,7 +4200,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4244,7 +4250,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4294,7 +4300,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4344,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4394,7 +4400,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4444,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4494,7 +4500,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4544,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4594,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4644,7 +4650,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4694,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4744,7 +4750,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4794,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4844,7 +4850,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4894,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4944,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4994,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5044,7 +5050,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5494,7 +5500,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5544,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5594,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5644,7 +5650,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5694,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5744,7 +5750,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6144,7 +6150,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6194,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6244,7 +6250,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6294,7 +6300,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6344,7 +6350,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6394,7 +6400,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6644,7 +6650,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6694,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6744,7 +6750,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6794,7 +6800,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6844,7 +6850,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6894,7 +6900,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6944,7 +6950,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6994,7 +7000,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7044,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7094,7 +7100,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7144,7 +7150,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7194,7 +7200,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7244,7 +7250,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7294,7 +7300,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7344,7 +7350,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7394,7 +7400,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7444,7 +7450,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7494,7 +7500,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7544,7 +7550,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7594,7 +7600,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7644,7 +7650,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7694,7 +7700,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7744,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7794,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7844,7 +7850,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7894,7 +7900,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7944,7 +7950,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7994,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8044,7 +8050,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8094,7 +8100,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8144,7 +8150,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8194,7 +8200,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8244,7 +8250,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8294,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8344,7 +8350,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8394,7 +8400,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8444,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8494,7 +8500,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8544,7 +8550,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8594,7 +8600,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8644,7 +8650,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8694,7 +8700,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8744,7 +8750,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8794,7 +8800,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8844,7 +8850,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8894,7 +8900,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8944,7 +8950,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8994,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9044,7 +9050,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9094,7 +9100,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9144,7 +9150,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9194,7 +9200,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9244,7 +9250,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9294,7 +9300,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9544,7 +9550,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9594,7 +9600,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9644,7 +9650,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9694,7 +9700,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9744,7 +9750,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9794,7 +9800,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9844,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9894,7 +9900,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10244,7 +10250,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10294,7 +10300,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10344,7 +10350,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10594,7 +10600,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10644,7 +10650,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10694,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10744,7 +10750,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10794,7 +10800,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10844,7 +10850,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10894,7 +10900,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10944,7 +10950,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10994,7 +11000,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11044,7 +11050,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11094,7 +11100,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11144,7 +11150,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11194,7 +11200,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11594,7 +11600,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11844,7 +11850,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11894,7 +11900,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11944,7 +11950,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11994,7 +12000,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12044,7 +12050,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12094,7 +12100,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12144,7 +12150,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12194,7 +12200,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12244,7 +12250,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12294,7 +12300,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12344,7 +12350,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12394,7 +12400,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12444,7 +12450,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12494,7 +12500,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12544,7 +12550,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12594,7 +12600,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12644,7 +12650,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16494,7 +16500,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16544,7 +16550,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16594,7 +16600,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16644,7 +16650,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16694,7 +16700,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16744,7 +16750,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16944,7 +16950,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16994,7 +17000,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17044,7 +17050,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17094,7 +17100,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17144,7 +17150,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17194,7 +17200,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17444,7 +17450,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17494,7 +17500,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17544,7 +17550,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17594,7 +17600,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17644,7 +17650,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17694,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17744,7 +17750,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17794,7 +17800,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17844,7 +17850,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18994,7 +19000,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19044,7 +19050,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19094,7 +19100,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19144,7 +19150,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19194,7 +19200,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19244,7 +19250,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19294,7 +19300,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19344,7 +19350,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19394,7 +19400,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19444,7 +19450,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -20044,7 +20050,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20094,7 +20100,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20144,7 +20150,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20194,7 +20200,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20244,7 +20250,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20294,7 +20300,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -22044,7 +22050,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22094,7 +22100,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22144,7 +22150,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22194,7 +22200,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22244,7 +22250,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22294,7 +22300,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22344,7 +22350,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22394,7 +22400,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22444,7 +22450,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22494,7 +22500,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22544,7 +22550,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22594,7 +22600,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22644,7 +22650,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22694,7 +22700,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22744,7 +22750,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22794,7 +22800,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22844,7 +22850,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22894,7 +22900,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22944,7 +22950,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23294,7 +23300,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23344,7 +23350,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23394,7 +23400,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23444,7 +23450,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23494,7 +23500,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23544,7 +23550,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23594,7 +23600,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23644,7 +23650,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23694,7 +23700,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23744,7 +23750,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23794,7 +23800,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23844,7 +23850,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23894,7 +23900,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23944,7 +23950,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23994,7 +24000,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24044,7 +24050,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24094,7 +24100,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24144,7 +24150,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24194,7 +24200,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24244,7 +24250,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24294,7 +24300,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24344,7 +24350,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24744,7 +24750,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24794,7 +24800,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24844,7 +24850,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24894,7 +24900,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24944,7 +24950,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24994,7 +25000,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25044,7 +25050,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25644,7 +25650,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25694,7 +25700,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25744,7 +25750,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25794,7 +25800,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25844,7 +25850,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25894,7 +25900,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25944,7 +25950,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25994,7 +26000,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26044,7 +26050,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26094,7 +26100,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26144,7 +26150,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26194,7 +26200,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26244,7 +26250,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26294,7 +26300,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26344,7 +26350,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26394,7 +26400,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26444,7 +26450,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26494,7 +26500,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26544,7 +26550,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26594,7 +26600,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26794,7 +26800,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26844,7 +26850,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26894,7 +26900,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26944,7 +26950,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26994,7 +27000,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27044,7 +27050,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27094,7 +27100,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -28044,7 +28050,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28094,7 +28100,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28144,7 +28150,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29444,7 +29450,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29494,7 +29500,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29544,7 +29550,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29594,7 +29600,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29644,7 +29650,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29694,7 +29700,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29744,7 +29750,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29794,7 +29800,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29844,7 +29850,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29894,7 +29900,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30194,7 +30200,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30244,7 +30250,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30294,7 +30300,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30344,7 +30350,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30394,7 +30400,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30444,7 +30450,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30494,7 +30500,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30544,7 +30550,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30594,7 +30600,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30644,7 +30650,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30694,7 +30700,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30894,7 +30900,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30944,7 +30950,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30994,7 +31000,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31044,7 +31050,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31094,7 +31100,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31144,7 +31150,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31194,7 +31200,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31244,7 +31250,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31294,7 +31300,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31594,7 +31600,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31644,7 +31650,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31694,7 +31700,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31744,7 +31750,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31794,7 +31800,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31844,7 +31850,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31894,7 +31900,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31944,7 +31950,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31994,7 +32000,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32044,7 +32050,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32094,7 +32100,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32144,7 +32150,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32744,7 +32750,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32794,7 +32800,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32844,7 +32850,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32894,7 +32900,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32944,7 +32950,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32994,7 +33000,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33044,7 +33050,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33094,7 +33100,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33144,7 +33150,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33194,7 +33200,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33394,7 +33400,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33444,7 +33450,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33494,7 +33500,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33544,7 +33550,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33594,7 +33600,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34494,7 +34500,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34544,7 +34550,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34594,7 +34600,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34644,7 +34650,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34694,7 +34700,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34744,7 +34750,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34794,7 +34800,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34844,7 +34850,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34894,7 +34900,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35544,7 +35550,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35594,7 +35600,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35644,7 +35650,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35694,7 +35700,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35744,7 +35750,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35794,7 +35800,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35844,7 +35850,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35894,7 +35900,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35944,7 +35950,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36344,7 +36350,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36394,7 +36400,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36444,7 +36450,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36494,7 +36500,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36544,7 +36550,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36594,7 +36600,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36644,7 +36650,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36694,7 +36700,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36744,7 +36750,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36794,7 +36800,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36844,7 +36850,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36894,7 +36900,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36944,7 +36950,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37244,7 +37250,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37294,7 +37300,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37344,7 +37350,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37394,7 +37400,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37694,7 +37700,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37744,7 +37750,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37794,7 +37800,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37844,7 +37850,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37894,7 +37900,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37944,7 +37950,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37994,7 +38000,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38044,7 +38050,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38094,7 +38100,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38144,7 +38150,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38394,7 +38400,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38444,7 +38450,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38494,7 +38500,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38544,7 +38550,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38594,7 +38600,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39194,7 +39200,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39244,7 +39250,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39294,7 +39300,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39344,7 +39350,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39394,7 +39400,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39444,7 +39450,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39494,7 +39500,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39544,7 +39550,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39594,7 +39600,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39644,7 +39650,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40444,7 +40450,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40494,7 +40500,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40544,7 +40550,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40594,7 +40600,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40644,7 +40650,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40694,7 +40700,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40744,7 +40750,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42444,7 +42450,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42494,7 +42500,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42544,7 +42550,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42594,7 +42600,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42644,7 +42650,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43194,7 +43200,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43244,7 +43250,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43294,7 +43300,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43344,7 +43350,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43394,7 +43400,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43444,7 +43450,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43594,7 +43600,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43644,7 +43650,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43694,7 +43700,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43744,7 +43750,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43794,7 +43800,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43844,7 +43850,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43894,7 +43900,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43944,7 +43950,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43994,7 +44000,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44044,7 +44050,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44094,7 +44100,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44144,7 +44150,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44194,7 +44200,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44244,7 +44250,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44294,7 +44300,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44344,7 +44350,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44394,7 +44400,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44444,7 +44450,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44494,7 +44500,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44544,7 +44550,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44844,7 +44850,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44894,7 +44900,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44944,7 +44950,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44994,7 +45000,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45044,7 +45050,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45094,7 +45100,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45144,7 +45150,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45194,7 +45200,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45244,7 +45250,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45294,7 +45300,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45344,7 +45350,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45394,7 +45400,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45444,7 +45450,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45494,7 +45500,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45544,7 +45550,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45594,7 +45600,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45644,7 +45650,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45694,7 +45700,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45994,7 +46000,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46044,7 +46050,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46094,7 +46100,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46144,7 +46150,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46194,7 +46200,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46444,7 +46450,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46494,7 +46500,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46544,7 +46550,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46594,7 +46600,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46844,7 +46850,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46894,7 +46900,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46944,7 +46950,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -46994,7 +47000,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47044,7 +47050,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47094,7 +47100,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47144,7 +47150,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47194,7 +47200,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47244,7 +47250,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47294,7 +47300,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47344,7 +47350,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47694,7 +47700,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47744,7 +47750,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47794,7 +47800,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47844,7 +47850,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47894,7 +47900,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47944,7 +47950,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -47994,7 +48000,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48044,7 +48050,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48094,7 +48100,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48144,7 +48150,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48194,7 +48200,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48244,7 +48250,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48294,7 +48300,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48344,7 +48350,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48394,7 +48400,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48944,7 +48950,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -48994,7 +49000,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49044,7 +49050,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49094,7 +49100,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49294,7 +49300,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49344,7 +49350,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49394,7 +49400,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49444,7 +49450,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49494,7 +49500,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49544,7 +49550,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49594,7 +49600,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49644,7 +49650,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49694,7 +49700,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50694,7 +50700,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50744,7 +50750,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50794,7 +50800,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50844,7 +50850,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50894,7 +50900,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50944,7 +50950,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -50994,7 +51000,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51044,7 +51050,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51094,7 +51100,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51144,7 +51150,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51194,7 +51200,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51244,7 +51250,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51294,7 +51300,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51344,7 +51350,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51394,7 +51400,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51444,7 +51450,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51494,7 +51500,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51544,7 +51550,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51594,7 +51600,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51644,7 +51650,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51694,7 +51700,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51744,7 +51750,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51794,7 +51800,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51844,7 +51850,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51894,7 +51900,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -51944,7 +51950,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -51994,7 +52000,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52044,7 +52050,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52094,7 +52100,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52144,7 +52150,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52194,7 +52200,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52244,7 +52250,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52294,7 +52300,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52444,7 +52450,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52494,7 +52500,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52558,10 +52564,10 @@
         <v>0.4193078233762986</v>
       </c>
       <c r="D1015" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E1015">
-        <v>0.617421340031604</v>
+        <v>0.6015328427429329</v>
       </c>
       <c r="F1015">
         <v>1</v>
@@ -52570,10 +52576,10 @@
         <v>0.0126806921766237</v>
       </c>
       <c r="H1015">
-        <v>0.0117225786599684</v>
+        <v>0.01151846715725707</v>
       </c>
       <c r="I1015">
-        <v>0.1981135166553054</v>
+        <v>0.1822250193666344</v>
       </c>
       <c r="J1015">
         <v>1.344450038733268</v>
@@ -52585,10 +52591,10 @@
         <v>6.55</v>
       </c>
       <c r="M1015">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="N1015">
-        <v>6.17</v>
+        <v>6.06</v>
       </c>
       <c r="O1015">
         <v>1</v>
@@ -52608,10 +52614,10 @@
         <v>0.3854203330596162</v>
       </c>
       <c r="D1016" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E1016">
-        <v>0.617421340031604</v>
+        <v>0.6015328427429329</v>
       </c>
       <c r="F1016">
         <v>1</v>
@@ -52620,10 +52626,10 @@
         <v>0.01197457966694038</v>
       </c>
       <c r="H1016">
-        <v>0.0117225786599684</v>
+        <v>0.01151846715725707</v>
       </c>
       <c r="I1016">
-        <v>0.2320010069719878</v>
+        <v>0.2161125096833167</v>
       </c>
       <c r="J1016">
         <v>1.344450038733268</v>
@@ -52635,10 +52641,10 @@
         <v>6.18</v>
       </c>
       <c r="M1016">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="N1016">
-        <v>6.17</v>
+        <v>6.06</v>
       </c>
       <c r="O1016">
         <v>1</v>
@@ -52694,7 +52700,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52708,10 +52714,10 @@
         <v>0.3974727812328904</v>
       </c>
       <c r="D1018" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E1018">
-        <v>0.5976453040552272</v>
+        <v>0.5485996095653203</v>
       </c>
       <c r="F1018">
         <v>1</v>
@@ -52720,10 +52726,10 @@
         <v>0.01270252721876711</v>
       </c>
       <c r="H1018">
-        <v>0.01174235469594477</v>
+        <v>0.01153140039043468</v>
       </c>
       <c r="I1018">
-        <v>0.2001725228223368</v>
+        <v>0.1511268283324299</v>
       </c>
       <c r="J1018">
         <v>1.349238425168226</v>
@@ -52735,198 +52741,198 @@
         <v>6.55</v>
       </c>
       <c r="M1018">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="N1018">
-        <v>6.17</v>
+        <v>6.04</v>
       </c>
       <c r="O1018">
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
       <c r="A1019" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1019" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C1019">
-        <v>0.3647823875249463</v>
+        <v>0.8542276829218149</v>
       </c>
       <c r="D1019" t="s">
-        <v>371</v>
+        <v>196</v>
       </c>
       <c r="E1019">
-        <v>0.5976453040552272</v>
+        <v>0.5065638875223204</v>
       </c>
       <c r="F1019">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1019">
-        <v>0.01199521761247505</v>
+        <v>0.01698577231707819</v>
       </c>
       <c r="H1019">
-        <v>0.01174235469594477</v>
+        <v>0.01577343611247768</v>
       </c>
       <c r="I1019">
-        <v>0.2328629165302809</v>
+        <v>0.3476637953994945</v>
       </c>
       <c r="J1019">
-        <v>1.349238425168226</v>
+        <v>1.35105063937658</v>
       </c>
       <c r="K1019">
-        <v>4.31</v>
+        <v>5.97</v>
       </c>
       <c r="L1019">
-        <v>6.18</v>
+        <v>8.92</v>
       </c>
       <c r="M1019">
-        <v>4.13</v>
+        <v>5.65</v>
       </c>
       <c r="N1019">
-        <v>6.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O1019">
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
       <c r="A1020" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1020" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C1020">
-        <v>0.8542276829218149</v>
+        <v>0.3892090844427933</v>
       </c>
       <c r="D1020" t="s">
-        <v>196</v>
+        <v>373</v>
       </c>
       <c r="E1020">
-        <v>0.5065638875223204</v>
+        <v>0.5412238977373169</v>
       </c>
       <c r="F1020">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1020">
-        <v>0.01698577231707819</v>
+        <v>0.01271079091555721</v>
       </c>
       <c r="H1020">
-        <v>0.01577343611247768</v>
+        <v>0.01153877610226269</v>
       </c>
       <c r="I1020">
-        <v>0.3476637953994945</v>
+        <v>0.1520148132945236</v>
       </c>
       <c r="J1020">
         <v>1.35105063937658</v>
       </c>
       <c r="K1020">
-        <v>5.97</v>
+        <v>4.56</v>
       </c>
       <c r="L1020">
-        <v>8.92</v>
+        <v>6.55</v>
       </c>
       <c r="M1020">
-        <v>5.65</v>
+        <v>4.07</v>
       </c>
       <c r="N1020">
-        <v>8.140000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="O1020">
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
       <c r="A1021" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1021" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C1021">
-        <v>1.156353759647005</v>
+        <v>0.8495456676775177</v>
       </c>
       <c r="D1021" t="s">
-        <v>363</v>
+        <v>196</v>
       </c>
       <c r="E1021">
-        <v>0.5760199693550092</v>
+        <v>0.5021328345691742</v>
       </c>
       <c r="F1021">
         <v>-1</v>
       </c>
       <c r="G1021">
-        <v>0.016963646240353</v>
+        <v>0.01699045433232248</v>
       </c>
       <c r="H1021">
-        <v>0.01338398003064499</v>
+        <v>0.01577786716543083</v>
       </c>
       <c r="I1021">
-        <v>0.5803337902919958</v>
+        <v>0.3474128331083435</v>
       </c>
       <c r="J1021">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1021">
-        <v>5.85</v>
+        <v>5.97</v>
       </c>
       <c r="L1021">
-        <v>9.06</v>
+        <v>8.92</v>
       </c>
       <c r="M1021">
-        <v>4.74</v>
+        <v>5.65</v>
       </c>
       <c r="N1021">
-        <v>6.98</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O1021">
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
       <c r="A1022" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1022" t="s">
         <v>200</v>
       </c>
       <c r="C1022">
-        <v>0.3892090844427933</v>
+        <v>0.3856328717938826</v>
       </c>
       <c r="D1022" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E1022">
-        <v>0.5901608593747225</v>
+        <v>0.5380319710967321</v>
       </c>
       <c r="F1022">
         <v>1</v>
       </c>
       <c r="G1022">
-        <v>0.01271079091555721</v>
+        <v>0.01271436712820612</v>
       </c>
       <c r="H1022">
-        <v>0.01174983914062528</v>
+        <v>0.01154196802890327</v>
       </c>
       <c r="I1022">
-        <v>0.2009517749319292</v>
+        <v>0.1523990993028495</v>
       </c>
       <c r="J1022">
-        <v>1.35105063937658</v>
+        <v>1.351834896536429</v>
       </c>
       <c r="K1022">
         <v>4.56</v>
@@ -52935,148 +52941,148 @@
         <v>6.55</v>
       </c>
       <c r="M1022">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="N1022">
-        <v>6.17</v>
+        <v>6.04</v>
       </c>
       <c r="O1022">
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
       <c r="A1023" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1023" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C1023">
-        <v>0.3569717442869385</v>
+        <v>0.8476088036369962</v>
       </c>
       <c r="D1023" t="s">
-        <v>371</v>
+        <v>196</v>
       </c>
       <c r="E1023">
-        <v>0.5901608593747225</v>
+        <v>0.5002997890366885</v>
       </c>
       <c r="F1023">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1023">
-        <v>0.01200302825571306</v>
+        <v>0.016992391196363</v>
       </c>
       <c r="H1023">
-        <v>0.01174983914062528</v>
+        <v>0.01577970021096331</v>
       </c>
       <c r="I1023">
-        <v>0.2331891150877841</v>
+        <v>0.3473090146003077</v>
       </c>
       <c r="J1023">
-        <v>1.35105063937658</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1023">
-        <v>4.31</v>
+        <v>5.97</v>
       </c>
       <c r="L1023">
-        <v>6.18</v>
+        <v>8.92</v>
       </c>
       <c r="M1023">
-        <v>4.13</v>
+        <v>5.65</v>
       </c>
       <c r="N1023">
-        <v>6.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O1023">
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
       <c r="A1024" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1024" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C1024">
-        <v>0.8495456676775177</v>
+        <v>0.7990373152678316</v>
       </c>
       <c r="D1024" t="s">
-        <v>196</v>
+        <v>363</v>
       </c>
       <c r="E1024">
-        <v>0.5021328345691742</v>
+        <v>0.5707647787670629</v>
       </c>
       <c r="F1024">
         <v>-1</v>
       </c>
       <c r="G1024">
-        <v>0.01699045433232248</v>
+        <v>0.01578096268473217</v>
       </c>
       <c r="H1024">
-        <v>0.01577786716543083</v>
+        <v>0.01338923522123294</v>
       </c>
       <c r="I1024">
-        <v>0.3474128331083435</v>
+        <v>0.2282725365007687</v>
       </c>
       <c r="J1024">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1024">
-        <v>5.97</v>
+        <v>5.54</v>
       </c>
       <c r="L1024">
-        <v>8.92</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1024">
-        <v>5.65</v>
+        <v>4.74</v>
       </c>
       <c r="N1024">
-        <v>8.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="O1024">
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
       <c r="A1025" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1025" t="s">
         <v>200</v>
       </c>
       <c r="C1025">
-        <v>0.3856328717938826</v>
+        <v>0.3841534580543895</v>
       </c>
       <c r="D1025" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E1025">
-        <v>0.5869218773045475</v>
+        <v>0.5367115294476674</v>
       </c>
       <c r="F1025">
         <v>1</v>
       </c>
       <c r="G1025">
-        <v>0.01271436712820612</v>
+        <v>0.01271584654194561</v>
       </c>
       <c r="H1025">
-        <v>0.01175307812269545</v>
+        <v>0.01154328847055233</v>
       </c>
       <c r="I1025">
-        <v>0.2012890055106649</v>
+        <v>0.1525580713932779</v>
       </c>
       <c r="J1025">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1025">
         <v>4.56</v>
@@ -53085,48 +53091,48 @@
         <v>6.55</v>
       </c>
       <c r="M1025">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="N1025">
-        <v>6.17</v>
+        <v>6.04</v>
       </c>
       <c r="O1025">
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
       <c r="A1026" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1026" t="s">
         <v>201</v>
       </c>
       <c r="C1026">
-        <v>0.3535915959279903</v>
+        <v>0.3521932903978984</v>
       </c>
       <c r="D1026" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E1026">
-        <v>0.5869218773045475</v>
+        <v>0.5367115294476674</v>
       </c>
       <c r="F1026">
         <v>1</v>
       </c>
       <c r="G1026">
-        <v>0.01200640840407201</v>
+        <v>0.0120078067096021</v>
       </c>
       <c r="H1026">
-        <v>0.01175307812269545</v>
+        <v>0.01154328847055233</v>
       </c>
       <c r="I1026">
-        <v>0.2333302813765572</v>
+        <v>0.1845182390497691</v>
       </c>
       <c r="J1026">
-        <v>1.351834896536429</v>
+        <v>1.352159329374037</v>
       </c>
       <c r="K1026">
         <v>4.31</v>
@@ -53135,16 +53141,16 @@
         <v>6.18</v>
       </c>
       <c r="M1026">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="N1026">
-        <v>6.17</v>
+        <v>6.04</v>
       </c>
       <c r="O1026">
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53155,28 +53161,28 @@
         <v>202</v>
       </c>
       <c r="C1027">
-        <v>0.8476088036369962</v>
+        <v>0.844077502681861</v>
       </c>
       <c r="D1027" t="s">
         <v>196</v>
       </c>
       <c r="E1027">
-        <v>0.5002997890366885</v>
+        <v>0.4969577705448094</v>
       </c>
       <c r="F1027">
         <v>-1</v>
       </c>
       <c r="G1027">
-        <v>0.016992391196363</v>
+        <v>0.01699592249731814</v>
       </c>
       <c r="H1027">
-        <v>0.01577970021096331</v>
+        <v>0.01578304222945519</v>
       </c>
       <c r="I1027">
-        <v>0.3473090146003077</v>
+        <v>0.3471197321370516</v>
       </c>
       <c r="J1027">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1027">
         <v>5.97</v>
@@ -53194,7 +53200,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53202,49 +53208,49 @@
         <v>1</v>
       </c>
       <c r="B1028" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C1028">
-        <v>0.3841534580543895</v>
+        <v>0.7957603626226968</v>
       </c>
       <c r="D1028" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E1028">
-        <v>0.5855819696852249</v>
+        <v>0.5679610322800706</v>
       </c>
       <c r="F1028">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1028">
-        <v>0.01271584654194561</v>
+        <v>0.0157842396373773</v>
       </c>
       <c r="H1028">
-        <v>0.01175441803031477</v>
+        <v>0.01339203896771993</v>
       </c>
       <c r="I1028">
-        <v>0.2014285116308354</v>
+        <v>0.2277993303426262</v>
       </c>
       <c r="J1028">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1028">
-        <v>4.56</v>
+        <v>5.54</v>
       </c>
       <c r="L1028">
-        <v>6.55</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1028">
-        <v>4.13</v>
+        <v>4.74</v>
       </c>
       <c r="N1028">
-        <v>6.17</v>
+        <v>6.98</v>
       </c>
       <c r="O1028">
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53252,343 +53258,343 @@
         <v>2</v>
       </c>
       <c r="B1029" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C1029">
-        <v>0.3521932903978984</v>
+        <v>0.7845305970027789</v>
       </c>
       <c r="D1029" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E1029">
-        <v>0.5855819696852249</v>
+        <v>0.5679610322800706</v>
       </c>
       <c r="F1029">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1029">
-        <v>0.0120078067096021</v>
+        <v>0.01501546940299722</v>
       </c>
       <c r="H1029">
-        <v>0.01175441803031477</v>
+        <v>0.01339203896771993</v>
       </c>
       <c r="I1029">
-        <v>0.2333886792873265</v>
+        <v>0.2165695647227084</v>
       </c>
       <c r="J1029">
-        <v>1.352159329374037</v>
+        <v>1.352750837071715</v>
       </c>
       <c r="K1029">
-        <v>4.31</v>
+        <v>5.26</v>
       </c>
       <c r="L1029">
-        <v>6.18</v>
+        <v>7.9</v>
       </c>
       <c r="M1029">
-        <v>4.13</v>
+        <v>4.74</v>
       </c>
       <c r="N1029">
-        <v>6.17</v>
+        <v>6.98</v>
       </c>
       <c r="O1029">
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
       <c r="A1030" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1030" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C1030">
-        <v>0.844077502681861</v>
+        <v>0.381456182952979</v>
       </c>
       <c r="D1030" t="s">
-        <v>196</v>
+        <v>371</v>
       </c>
       <c r="E1030">
-        <v>0.4969577705448094</v>
+        <v>0.5831390428938166</v>
       </c>
       <c r="F1030">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1030">
-        <v>0.01699592249731814</v>
+        <v>0.01271854381704702</v>
       </c>
       <c r="H1030">
-        <v>0.01578304222945519</v>
+        <v>0.01175686095710619</v>
       </c>
       <c r="I1030">
-        <v>0.3471197321370516</v>
+        <v>0.2016828599408376</v>
       </c>
       <c r="J1030">
         <v>1.352750837071715</v>
       </c>
       <c r="K1030">
-        <v>5.97</v>
+        <v>4.56</v>
       </c>
       <c r="L1030">
-        <v>8.92</v>
+        <v>6.55</v>
       </c>
       <c r="M1030">
-        <v>5.65</v>
+        <v>4.13</v>
       </c>
       <c r="N1030">
-        <v>8.140000000000001</v>
+        <v>6.17</v>
       </c>
       <c r="O1030">
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
       <c r="A1031" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1031" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C1031">
-        <v>0.7957603626226968</v>
+        <v>0.3496438922209082</v>
       </c>
       <c r="D1031" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E1031">
-        <v>0.5679610322800706</v>
+        <v>0.5831390428938166</v>
       </c>
       <c r="F1031">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1031">
-        <v>0.0157842396373773</v>
+        <v>0.01201035610777909</v>
       </c>
       <c r="H1031">
-        <v>0.01339203896771993</v>
+        <v>0.01175686095710619</v>
       </c>
       <c r="I1031">
-        <v>0.2277993303426262</v>
+        <v>0.2334951506729084</v>
       </c>
       <c r="J1031">
         <v>1.352750837071715</v>
       </c>
       <c r="K1031">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1031">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1031">
-        <v>4.74</v>
+        <v>4.13</v>
       </c>
       <c r="N1031">
-        <v>6.98</v>
+        <v>6.17</v>
       </c>
       <c r="O1031">
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
       <c r="A1032" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1032" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C1032">
-        <v>0.7845305970027789</v>
+        <v>0.8389074160156742</v>
       </c>
       <c r="D1032" t="s">
-        <v>363</v>
+        <v>196</v>
       </c>
       <c r="E1032">
-        <v>0.5679610322800706</v>
+        <v>0.4920648074520191</v>
       </c>
       <c r="F1032">
         <v>-1</v>
       </c>
       <c r="G1032">
-        <v>0.01501546940299722</v>
+        <v>0.01700109258398433</v>
       </c>
       <c r="H1032">
-        <v>0.01339203896771993</v>
+        <v>0.01578793519254798</v>
       </c>
       <c r="I1032">
-        <v>0.2165695647227084</v>
+        <v>0.3468426085636551</v>
       </c>
       <c r="J1032">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1032">
-        <v>5.26</v>
+        <v>5.97</v>
       </c>
       <c r="L1032">
-        <v>7.9</v>
+        <v>8.92</v>
       </c>
       <c r="M1032">
-        <v>4.74</v>
+        <v>5.65</v>
       </c>
       <c r="N1032">
-        <v>6.98</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O1032">
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>491</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
       <c r="A1033" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1033" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C1033">
-        <v>0.3761487415479987</v>
+        <v>0.7909626607582627</v>
       </c>
       <c r="D1033" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E1033">
-        <v>0.5831390428938166</v>
+        <v>0.5638561393491281</v>
       </c>
       <c r="F1033">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1033">
-        <v>0.012523851258452</v>
+        <v>0.01578903733924173</v>
       </c>
       <c r="H1033">
-        <v>0.01175686095710619</v>
+        <v>0.01339614386065087</v>
       </c>
       <c r="I1033">
-        <v>0.2069903013458179</v>
+        <v>0.2271065214091346</v>
       </c>
       <c r="J1033">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1033">
-        <v>4.49</v>
+        <v>5.54</v>
       </c>
       <c r="L1033">
-        <v>6.45</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1033">
-        <v>4.13</v>
+        <v>4.74</v>
       </c>
       <c r="N1033">
-        <v>6.17</v>
+        <v>6.98</v>
       </c>
       <c r="O1033">
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>491</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
       <c r="A1034" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1034" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C1034">
-        <v>0.3496438922209082</v>
+        <v>0.7799753782650667</v>
       </c>
       <c r="D1034" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E1034">
-        <v>0.5831390428938166</v>
+        <v>0.5638561393491281</v>
       </c>
       <c r="F1034">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1034">
-        <v>0.01201035610777909</v>
+        <v>0.01502002462173493</v>
       </c>
       <c r="H1034">
-        <v>0.01175686095710619</v>
+        <v>0.01339614386065087</v>
       </c>
       <c r="I1034">
-        <v>0.2334951506729084</v>
+        <v>0.2161192389159385</v>
       </c>
       <c r="J1034">
-        <v>1.352750837071715</v>
+        <v>1.353616848238581</v>
       </c>
       <c r="K1034">
-        <v>4.31</v>
+        <v>5.26</v>
       </c>
       <c r="L1034">
-        <v>6.18</v>
+        <v>7.9</v>
       </c>
       <c r="M1034">
-        <v>4.13</v>
+        <v>4.74</v>
       </c>
       <c r="N1034">
-        <v>6.17</v>
+        <v>6.98</v>
       </c>
       <c r="O1034">
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>491</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
       <c r="A1035" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1035" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C1035">
-        <v>0.8389074160156742</v>
+        <v>0.3775071720320726</v>
       </c>
       <c r="D1035" t="s">
-        <v>196</v>
+        <v>371</v>
       </c>
       <c r="E1035">
-        <v>0.4920648074520191</v>
+        <v>0.579562416774662</v>
       </c>
       <c r="F1035">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1035">
-        <v>0.01700109258398433</v>
+        <v>0.01272249282796793</v>
       </c>
       <c r="H1035">
-        <v>0.01578793519254798</v>
+        <v>0.01176043758322534</v>
       </c>
       <c r="I1035">
-        <v>0.3468426085636551</v>
+        <v>0.2020552447425894</v>
       </c>
       <c r="J1035">
         <v>1.353616848238581</v>
       </c>
       <c r="K1035">
-        <v>5.97</v>
+        <v>4.56</v>
       </c>
       <c r="L1035">
-        <v>8.92</v>
+        <v>6.55</v>
       </c>
       <c r="M1035">
-        <v>5.65</v>
+        <v>4.13</v>
       </c>
       <c r="N1035">
-        <v>8.140000000000001</v>
+        <v>6.17</v>
       </c>
       <c r="O1035">
         <v>1</v>
@@ -53599,46 +53605,46 @@
     </row>
     <row r="1036" spans="1:16">
       <c r="A1036" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1036" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C1036">
-        <v>0.7909626607582627</v>
+        <v>0.3459113840917176</v>
       </c>
       <c r="D1036" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E1036">
-        <v>0.5638561393491281</v>
+        <v>0.579562416774662</v>
       </c>
       <c r="F1036">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1036">
-        <v>0.01578903733924173</v>
+        <v>0.01201408861590828</v>
       </c>
       <c r="H1036">
-        <v>0.01339614386065087</v>
+        <v>0.01176043758322534</v>
       </c>
       <c r="I1036">
-        <v>0.2271065214091346</v>
+        <v>0.2336510326829444</v>
       </c>
       <c r="J1036">
         <v>1.353616848238581</v>
       </c>
       <c r="K1036">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1036">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1036">
-        <v>4.74</v>
+        <v>4.13</v>
       </c>
       <c r="N1036">
-        <v>6.98</v>
+        <v>6.17</v>
       </c>
       <c r="O1036">
         <v>1</v>
@@ -53649,196 +53655,196 @@
     </row>
     <row r="1037" spans="1:16">
       <c r="A1037" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1037" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C1037">
-        <v>0.7799753782650667</v>
+        <v>0.8032731591004225</v>
       </c>
       <c r="D1037" t="s">
-        <v>363</v>
+        <v>198</v>
       </c>
       <c r="E1037">
-        <v>0.5638561393491281</v>
+        <v>0.4949307904987359</v>
       </c>
       <c r="F1037">
         <v>-1</v>
       </c>
       <c r="G1037">
-        <v>0.01502002462173493</v>
+        <v>0.01577672684089958</v>
       </c>
       <c r="H1037">
-        <v>0.01339614386065087</v>
+        <v>0.01322506920950126</v>
       </c>
       <c r="I1037">
-        <v>0.2161192389159385</v>
+        <v>0.3083423686016866</v>
       </c>
       <c r="J1037">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1037">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1037">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1037">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="N1037">
-        <v>6.98</v>
+        <v>6.86</v>
       </c>
       <c r="O1037">
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1038" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C1038">
-        <v>0.372260351408773</v>
+        <v>0.7916636853552763</v>
       </c>
       <c r="D1038" t="s">
-        <v>371</v>
+        <v>198</v>
       </c>
       <c r="E1038">
-        <v>0.579562416774662</v>
+        <v>0.4949307904987359</v>
       </c>
       <c r="F1038">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1038">
-        <v>0.01252773964859123</v>
+        <v>0.01500833631464472</v>
       </c>
       <c r="H1038">
-        <v>0.01176043758322534</v>
+        <v>0.01322506920950126</v>
       </c>
       <c r="I1038">
-        <v>0.207302065365889</v>
+        <v>0.2967328948565404</v>
       </c>
       <c r="J1038">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1038">
-        <v>4.49</v>
+        <v>5.26</v>
       </c>
       <c r="L1038">
-        <v>6.45</v>
+        <v>7.9</v>
       </c>
       <c r="M1038">
-        <v>4.13</v>
+        <v>4.71</v>
       </c>
       <c r="N1038">
-        <v>6.17</v>
+        <v>6.86</v>
       </c>
       <c r="O1038">
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
       <c r="A1039" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1039" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C1039">
-        <v>0.3459113840917176</v>
+        <v>0.3822376325561194</v>
       </c>
       <c r="D1039" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E1039">
-        <v>0.579562416774662</v>
+        <v>0.5727955272059084</v>
       </c>
       <c r="F1039">
         <v>1</v>
       </c>
       <c r="G1039">
-        <v>0.01201408861590828</v>
+        <v>0.01251776236744388</v>
       </c>
       <c r="H1039">
-        <v>0.01176043758322534</v>
+        <v>0.01162720447279409</v>
       </c>
       <c r="I1039">
-        <v>0.2336510326829444</v>
+        <v>0.190557894649789</v>
       </c>
       <c r="J1039">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1039">
-        <v>4.31</v>
+        <v>4.49</v>
       </c>
       <c r="L1039">
-        <v>6.18</v>
+        <v>6.45</v>
       </c>
       <c r="M1039">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="N1039">
-        <v>6.17</v>
+        <v>6.1</v>
       </c>
       <c r="O1039">
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1040" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C1040">
-        <v>0.8032731591004225</v>
+        <v>0.3554886851485248</v>
       </c>
       <c r="D1040" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1040">
-        <v>0.4949307904987359</v>
+        <v>0.5727955272059084</v>
       </c>
       <c r="F1040">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1040">
-        <v>0.01577672684089958</v>
+        <v>0.01200451131485147</v>
       </c>
       <c r="H1040">
-        <v>0.01322506920950126</v>
+        <v>0.01162720447279409</v>
       </c>
       <c r="I1040">
-        <v>0.3083423686016866</v>
+        <v>0.2173068420573836</v>
       </c>
       <c r="J1040">
         <v>1.351394736624472</v>
       </c>
       <c r="K1040">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1040">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1040">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1040">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1040">
         <v>1</v>
@@ -53849,40 +53855,40 @@
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1041" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C1041">
-        <v>0.7916636853552763</v>
+        <v>0.8031318580204516</v>
       </c>
       <c r="D1041" t="s">
         <v>198</v>
       </c>
       <c r="E1041">
-        <v>0.4949307904987359</v>
+        <v>0.4948106590751502</v>
       </c>
       <c r="F1041">
         <v>-1</v>
       </c>
       <c r="G1041">
-        <v>0.01500833631464472</v>
+        <v>0.01577686814197955</v>
       </c>
       <c r="H1041">
-        <v>0.01322506920950126</v>
+        <v>0.01322518934092485</v>
       </c>
       <c r="I1041">
-        <v>0.2967328948565404</v>
+        <v>0.3083211989453014</v>
       </c>
       <c r="J1041">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1041">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1041">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1041">
         <v>4.71</v>
@@ -53894,95 +53900,95 @@
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1042" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C1042">
-        <v>0.276293422021098</v>
+        <v>0.7915295258461343</v>
       </c>
       <c r="D1042" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1042">
-        <v>0.5727955272059084</v>
+        <v>0.4948106590751502</v>
       </c>
       <c r="F1042">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1042">
-        <v>0.0123037065779789</v>
+        <v>0.01500847047415387</v>
       </c>
       <c r="H1042">
-        <v>0.01162720447279409</v>
+        <v>0.01322518934092485</v>
       </c>
       <c r="I1042">
-        <v>0.2965021051848105</v>
+        <v>0.2967188667709841</v>
       </c>
       <c r="J1042">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1042">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1042">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1042">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1042">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1042">
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1043" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1043">
-        <v>0.3554886851485248</v>
+        <v>0.2761799220561398</v>
       </c>
       <c r="D1043" t="s">
         <v>369</v>
       </c>
       <c r="E1043">
-        <v>0.5727955272059084</v>
+        <v>0.5726912092605865</v>
       </c>
       <c r="F1043">
         <v>1</v>
       </c>
       <c r="G1043">
-        <v>0.01200451131485147</v>
+        <v>0.01230382007794386</v>
       </c>
       <c r="H1043">
-        <v>0.01162720447279409</v>
+        <v>0.01162730879073941</v>
       </c>
       <c r="I1043">
-        <v>0.2173068420573836</v>
+        <v>0.2965112872044466</v>
       </c>
       <c r="J1043">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1043">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1043">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1043">
         <v>4.09</v>
@@ -53994,51 +54000,51 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1044" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C1044">
-        <v>0.8031318580204516</v>
+        <v>0.3553787559689807</v>
       </c>
       <c r="D1044" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1044">
-        <v>0.4948106590751502</v>
+        <v>0.5726912092605865</v>
       </c>
       <c r="F1044">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1044">
-        <v>0.01577686814197955</v>
+        <v>0.01200462124403102</v>
       </c>
       <c r="H1044">
-        <v>0.01322518934092485</v>
+        <v>0.01162730879073941</v>
       </c>
       <c r="I1044">
-        <v>0.3083211989453014</v>
+        <v>0.2173124532916058</v>
       </c>
       <c r="J1044">
         <v>1.351420242234575</v>
       </c>
       <c r="K1044">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1044">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1044">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1044">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1044">
         <v>1</v>
@@ -54049,40 +54055,40 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1045" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C1045">
-        <v>0.7915295258461343</v>
+        <v>0.8327877653809024</v>
       </c>
       <c r="D1045" t="s">
         <v>198</v>
       </c>
       <c r="E1045">
-        <v>0.4948106590751502</v>
+        <v>0.5200235333834033</v>
       </c>
       <c r="F1045">
         <v>-1</v>
       </c>
       <c r="G1045">
-        <v>0.01500847047415387</v>
+        <v>0.0157472122346191</v>
       </c>
       <c r="H1045">
-        <v>0.01322518934092485</v>
+        <v>0.0131999764666166</v>
       </c>
       <c r="I1045">
-        <v>0.2967188667709841</v>
+        <v>0.312764231997499</v>
       </c>
       <c r="J1045">
-        <v>1.351420242234575</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1045">
-        <v>5.26</v>
+        <v>5.54</v>
       </c>
       <c r="L1045">
-        <v>7.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1045">
         <v>4.71</v>
@@ -54094,95 +54100,95 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1046" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C1046">
-        <v>0.2761799220561398</v>
+        <v>0.8196865786829521</v>
       </c>
       <c r="D1046" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1046">
-        <v>0.5726912092605865</v>
+        <v>0.5200235333834033</v>
       </c>
       <c r="F1046">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.01230382007794386</v>
+        <v>0.01498031342131705</v>
       </c>
       <c r="H1046">
-        <v>0.01162730879073941</v>
+        <v>0.0131999764666166</v>
       </c>
       <c r="I1046">
-        <v>0.2965112872044466</v>
+        <v>0.2996630452995488</v>
       </c>
       <c r="J1046">
-        <v>1.351420242234575</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1046">
-        <v>4.45</v>
+        <v>5.26</v>
       </c>
       <c r="L1046">
-        <v>6.29</v>
+        <v>7.9</v>
       </c>
       <c r="M1046">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1046">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1046">
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1047" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1047">
-        <v>0.3553787559689807</v>
+        <v>0.3000010028781626</v>
       </c>
       <c r="D1047" t="s">
         <v>369</v>
       </c>
       <c r="E1047">
-        <v>0.5726912092605865</v>
+        <v>0.5945851914093669</v>
       </c>
       <c r="F1047">
         <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.01200462124403102</v>
+        <v>0.01227999899712184</v>
       </c>
       <c r="H1047">
-        <v>0.01162730879073941</v>
+        <v>0.01160541480859063</v>
       </c>
       <c r="I1047">
-        <v>0.2173124532916058</v>
+        <v>0.2945841885312044</v>
       </c>
       <c r="J1047">
-        <v>1.351420242234575</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1047">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1047">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1047">
         <v>4.09</v>
@@ -54194,51 +54200,51 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1048" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C1048">
-        <v>0.8327877653809024</v>
+        <v>0.3784504095291865</v>
       </c>
       <c r="D1048" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1048">
-        <v>0.5200235333834033</v>
+        <v>0.5945851914093669</v>
       </c>
       <c r="F1048">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1048">
-        <v>0.0157472122346191</v>
+        <v>0.01198154959047081</v>
       </c>
       <c r="H1048">
-        <v>0.0131999764666166</v>
+        <v>0.01160541480859063</v>
       </c>
       <c r="I1048">
-        <v>0.312764231997499</v>
+        <v>0.2161347818801804</v>
       </c>
       <c r="J1048">
         <v>1.346067190364458</v>
       </c>
       <c r="K1048">
-        <v>5.54</v>
+        <v>4.31</v>
       </c>
       <c r="L1048">
-        <v>8.289999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="M1048">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1048">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1048">
         <v>1</v>
@@ -54249,40 +54255,40 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1049" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C1049">
-        <v>0.8196865786829521</v>
+        <v>0.7027628245386071</v>
       </c>
       <c r="D1049" t="s">
         <v>198</v>
       </c>
       <c r="E1049">
-        <v>0.5200235333834033</v>
+        <v>0.5126320191808968</v>
       </c>
       <c r="F1049">
         <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.01498031342131705</v>
+        <v>0.0152572371754614</v>
       </c>
       <c r="H1049">
-        <v>0.0131999764666166</v>
+        <v>0.0132073679808191</v>
       </c>
       <c r="I1049">
-        <v>0.2996630452995488</v>
+        <v>0.1901308053577102</v>
       </c>
       <c r="J1049">
-        <v>1.346067190364458</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1049">
-        <v>5.26</v>
+        <v>5.4</v>
       </c>
       <c r="L1049">
-        <v>7.9</v>
+        <v>7.98</v>
       </c>
       <c r="M1049">
         <v>4.71</v>
@@ -54294,95 +54300,95 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1050" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C1050">
-        <v>0.3000010028781626</v>
+        <v>0.7043920026437194</v>
       </c>
       <c r="D1050" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1050">
-        <v>0.5945851914093669</v>
+        <v>0.5126320191808968</v>
       </c>
       <c r="F1050">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.01227999899712184</v>
+        <v>0.01369560799735628</v>
       </c>
       <c r="H1050">
-        <v>0.01160541480859063</v>
+        <v>0.0132073679808191</v>
       </c>
       <c r="I1050">
-        <v>0.2945841885312044</v>
+        <v>0.1917599834628225</v>
       </c>
       <c r="J1050">
-        <v>1.346067190364458</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1050">
-        <v>4.45</v>
+        <v>4.82</v>
       </c>
       <c r="L1050">
-        <v>6.29</v>
+        <v>7.2</v>
       </c>
       <c r="M1050">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1050">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1050">
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1051" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1051">
-        <v>0.3784504095291865</v>
+        <v>0.2930175128142221</v>
       </c>
       <c r="D1051" t="s">
         <v>369</v>
       </c>
       <c r="E1051">
-        <v>0.5945851914093669</v>
+        <v>0.5881666578449822</v>
       </c>
       <c r="F1051">
         <v>1</v>
       </c>
       <c r="G1051">
-        <v>0.01198154959047081</v>
+        <v>0.01228698248718578</v>
       </c>
       <c r="H1051">
-        <v>0.01160541480859063</v>
+        <v>0.01161183334215502</v>
       </c>
       <c r="I1051">
-        <v>0.2161347818801804</v>
+        <v>0.2951491450307602</v>
       </c>
       <c r="J1051">
-        <v>1.346067190364458</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1051">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1051">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1051">
         <v>4.09</v>
@@ -54394,51 +54400,51 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1052" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C1052">
-        <v>0.8114319364950138</v>
+        <v>0.3716866247706294</v>
       </c>
       <c r="D1052" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1052">
-        <v>0.5126320191808968</v>
+        <v>0.5881666578449822</v>
       </c>
       <c r="F1052">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1052">
-        <v>0.01498856806350499</v>
+        <v>0.01198831337522937</v>
       </c>
       <c r="H1052">
-        <v>0.0132073679808191</v>
+        <v>0.01161183334215502</v>
       </c>
       <c r="I1052">
-        <v>0.2987999173141169</v>
+        <v>0.2164800330743528</v>
       </c>
       <c r="J1052">
         <v>1.347636513974332</v>
       </c>
       <c r="K1052">
-        <v>5.26</v>
+        <v>4.31</v>
       </c>
       <c r="L1052">
-        <v>7.9</v>
+        <v>6.18</v>
       </c>
       <c r="M1052">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1052">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1052">
         <v>1</v>
@@ -54449,146 +54455,146 @@
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1053" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C1053">
-        <v>0.2930175128142221</v>
+        <v>0.6963736868234349</v>
       </c>
       <c r="D1053" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1053">
-        <v>0.5881666578449822</v>
+        <v>0.5070592712848851</v>
       </c>
       <c r="F1053">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1053">
-        <v>0.01228698248718578</v>
+        <v>0.01526362631317657</v>
       </c>
       <c r="H1053">
-        <v>0.01161183334215502</v>
+        <v>0.01321294072871512</v>
       </c>
       <c r="I1053">
-        <v>0.2951491450307602</v>
+        <v>0.1893144155385498</v>
       </c>
       <c r="J1053">
-        <v>1.347636513974332</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1053">
-        <v>4.45</v>
+        <v>5.4</v>
       </c>
       <c r="L1053">
-        <v>6.29</v>
+        <v>7.98</v>
       </c>
       <c r="M1053">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1053">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>365</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1054" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C1054">
-        <v>0.3716866247706294</v>
+        <v>0.6986891056461033</v>
       </c>
       <c r="D1054" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1054">
-        <v>0.5881666578449822</v>
+        <v>0.5070592712848851</v>
       </c>
       <c r="F1054">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.01198831337522937</v>
+        <v>0.0137013108943539</v>
       </c>
       <c r="H1054">
-        <v>0.01161183334215502</v>
+        <v>0.01321294072871512</v>
       </c>
       <c r="I1054">
-        <v>0.2164800330743528</v>
+        <v>0.1916298343612182</v>
       </c>
       <c r="J1054">
-        <v>1.347636513974332</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1054">
-        <v>4.31</v>
+        <v>4.82</v>
       </c>
       <c r="L1054">
-        <v>6.18</v>
+        <v>7.2</v>
       </c>
       <c r="M1054">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1054">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>365</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1055" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C1055">
-        <v>0.6963736868234349</v>
+        <v>0.2877523900674603</v>
       </c>
       <c r="D1055" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1055">
-        <v>0.5070592712848851</v>
+        <v>0.5833274776125643</v>
       </c>
       <c r="F1055">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1055">
-        <v>0.01526362631317657</v>
+        <v>0.01229224760993254</v>
       </c>
       <c r="H1055">
-        <v>0.01321294072871512</v>
+        <v>0.01161667252238744</v>
       </c>
       <c r="I1055">
-        <v>0.1893144155385498</v>
+        <v>0.295575087545104</v>
       </c>
       <c r="J1055">
         <v>1.34881968762529</v>
       </c>
       <c r="K1055">
-        <v>5.4</v>
+        <v>4.45</v>
       </c>
       <c r="L1055">
-        <v>7.98</v>
+        <v>6.29</v>
       </c>
       <c r="M1055">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1055">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54599,46 +54605,46 @@
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1056" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C1056">
-        <v>0.6986891056461033</v>
+        <v>0.366587146335001</v>
       </c>
       <c r="D1056" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1056">
-        <v>0.5070592712848851</v>
+        <v>0.5833274776125643</v>
       </c>
       <c r="F1056">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1056">
-        <v>0.0137013108943539</v>
+        <v>0.011993412853665</v>
       </c>
       <c r="H1056">
-        <v>0.01321294072871512</v>
+        <v>0.01161667252238744</v>
       </c>
       <c r="I1056">
-        <v>0.1916298343612182</v>
+        <v>0.2167403312775633</v>
       </c>
       <c r="J1056">
         <v>1.34881968762529</v>
       </c>
       <c r="K1056">
-        <v>4.82</v>
+        <v>4.31</v>
       </c>
       <c r="L1056">
-        <v>7.2</v>
+        <v>6.18</v>
       </c>
       <c r="M1056">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1056">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1056">
         <v>1</v>
@@ -54649,146 +54655,146 @@
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1057" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C1057">
-        <v>0.2877523900674603</v>
+        <v>0.685527947714454</v>
       </c>
       <c r="D1057" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1057">
-        <v>0.5833274776125643</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1057">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.01229224760993254</v>
+        <v>0.01527447205228555</v>
       </c>
       <c r="H1057">
-        <v>0.01161667252238744</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1057">
-        <v>0.295575087545104</v>
+        <v>0.1879285710968466</v>
       </c>
       <c r="J1057">
-        <v>1.34881968762529</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1057">
-        <v>4.45</v>
+        <v>5.4</v>
       </c>
       <c r="L1057">
-        <v>6.29</v>
+        <v>7.98</v>
       </c>
       <c r="M1057">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1057">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1058" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1058">
-        <v>0.366587146335001</v>
+        <v>0.6760248424128479</v>
       </c>
       <c r="D1058" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1058">
-        <v>0.5833274776125643</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1058">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.011993412853665</v>
+        <v>0.01364397515758715</v>
       </c>
       <c r="H1058">
-        <v>0.01161667252238744</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1058">
-        <v>0.2167403312775633</v>
+        <v>0.1784254657952404</v>
       </c>
       <c r="J1058">
-        <v>1.34881968762529</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1058">
-        <v>4.31</v>
+        <v>4.8</v>
       </c>
       <c r="L1058">
-        <v>6.18</v>
+        <v>7.16</v>
       </c>
       <c r="M1058">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1058">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1059" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C1059">
-        <v>0.685527947714454</v>
+        <v>0.2788146976535772</v>
       </c>
       <c r="D1059" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1059">
-        <v>0.4975993766176074</v>
+        <v>0.5751128344726144</v>
       </c>
       <c r="F1059">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1059">
-        <v>0.01527447205228555</v>
+        <v>0.01230118530234642</v>
       </c>
       <c r="H1059">
-        <v>0.01322240062338239</v>
+        <v>0.01162488716552739</v>
       </c>
       <c r="I1059">
-        <v>0.1879285710968466</v>
+        <v>0.2962981368190372</v>
       </c>
       <c r="J1059">
         <v>1.350828157830657</v>
       </c>
       <c r="K1059">
-        <v>5.4</v>
+        <v>4.45</v>
       </c>
       <c r="L1059">
-        <v>7.98</v>
+        <v>6.29</v>
       </c>
       <c r="M1059">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1059">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1059">
         <v>1</v>
@@ -54799,46 +54805,46 @@
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1060" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1060">
-        <v>0.6760248424128479</v>
+        <v>0.3579306397498696</v>
       </c>
       <c r="D1060" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1060">
-        <v>0.4975993766176074</v>
+        <v>0.5751128344726144</v>
       </c>
       <c r="F1060">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1060">
-        <v>0.01364397515758715</v>
+        <v>0.01200206936025013</v>
       </c>
       <c r="H1060">
-        <v>0.01322240062338239</v>
+        <v>0.01162488716552739</v>
       </c>
       <c r="I1060">
-        <v>0.1784254657952404</v>
+        <v>0.2171821947227448</v>
       </c>
       <c r="J1060">
         <v>1.350828157830657</v>
       </c>
       <c r="K1060">
-        <v>4.8</v>
+        <v>4.31</v>
       </c>
       <c r="L1060">
-        <v>7.16</v>
+        <v>6.18</v>
       </c>
       <c r="M1060">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1060">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1060">
         <v>1</v>
@@ -54849,90 +54855,90 @@
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1061" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1061">
-        <v>0.2788146976535772</v>
+        <v>0.6767185447573851</v>
       </c>
       <c r="D1061" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1061">
-        <v>0.5751128344726144</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1061">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.01230118530234642</v>
+        <v>0.01364328145524261</v>
       </c>
       <c r="H1061">
-        <v>0.01162488716552739</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1061">
-        <v>0.2962981368190372</v>
+        <v>0.178438472714201</v>
       </c>
       <c r="J1061">
-        <v>1.350828157830657</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1061">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1061">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1061">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1061">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1061">
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1062" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1062">
-        <v>0.3579306397498696</v>
+        <v>0.2794578175354925</v>
       </c>
       <c r="D1062" t="s">
         <v>369</v>
       </c>
       <c r="E1062">
-        <v>0.5751128344726144</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1062">
         <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.01200206936025013</v>
+        <v>0.01230054218246451</v>
       </c>
       <c r="H1062">
-        <v>0.01162488716552739</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1062">
-        <v>0.2171821947227448</v>
+        <v>0.2962461091431958</v>
       </c>
       <c r="J1062">
-        <v>1.350828157830657</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1062">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1062">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1062">
         <v>4.09</v>
@@ -54944,51 +54950,51 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1063" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1063">
-        <v>0.6767185447573851</v>
+        <v>0.3585535266467357</v>
       </c>
       <c r="D1063" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1063">
-        <v>0.4982800720431841</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1063">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1063">
-        <v>0.01364328145524261</v>
+        <v>0.01200144647335326</v>
       </c>
       <c r="H1063">
-        <v>0.01322171992795682</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1063">
-        <v>0.178438472714201</v>
+        <v>0.2171504000319526</v>
       </c>
       <c r="J1063">
         <v>1.350683636508878</v>
       </c>
       <c r="K1063">
-        <v>4.8</v>
+        <v>4.31</v>
       </c>
       <c r="L1063">
-        <v>7.16</v>
+        <v>6.18</v>
       </c>
       <c r="M1063">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1063">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1063">
         <v>1</v>
@@ -54999,146 +55005,146 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1064" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1064">
-        <v>0.2794578175354925</v>
+        <v>0.6674364420145809</v>
       </c>
       <c r="D1064" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1064">
-        <v>0.5757039266786883</v>
+        <v>0.4891720087268077</v>
       </c>
       <c r="F1064">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.01230054218246451</v>
+        <v>0.01365256355798542</v>
       </c>
       <c r="H1064">
-        <v>0.01162429607332131</v>
+        <v>0.01323082799127319</v>
       </c>
       <c r="I1064">
-        <v>0.2962461091431958</v>
+        <v>0.1782644332877732</v>
       </c>
       <c r="J1064">
-        <v>1.350683636508878</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1064">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1064">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1064">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1064">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1065" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1065">
-        <v>0.3585535266467357</v>
+        <v>0.6421196605685342</v>
       </c>
       <c r="D1065" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1065">
-        <v>0.5757039266786883</v>
+        <v>0.4891720087268077</v>
       </c>
       <c r="F1065">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.01200144647335326</v>
+        <v>0.01343788033943147</v>
       </c>
       <c r="H1065">
-        <v>0.01162429607332131</v>
+        <v>0.01323082799127319</v>
       </c>
       <c r="I1065">
-        <v>0.2171504000319526</v>
+        <v>0.1529476518417265</v>
       </c>
       <c r="J1065">
-        <v>1.350683636508878</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1065">
-        <v>4.31</v>
+        <v>4.73</v>
       </c>
       <c r="L1065">
-        <v>6.18</v>
+        <v>7.04</v>
       </c>
       <c r="M1065">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1065">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1065">
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1066" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C1066">
-        <v>0.6674364420145809</v>
+        <v>0.2708525347843507</v>
       </c>
       <c r="D1066" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1066">
-        <v>0.4891720087268077</v>
+        <v>0.5677948016332568</v>
       </c>
       <c r="F1066">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1066">
-        <v>0.01365256355798542</v>
+        <v>0.01230914746521565</v>
       </c>
       <c r="H1066">
-        <v>0.01323082799127319</v>
+        <v>0.01163220519836674</v>
       </c>
       <c r="I1066">
-        <v>0.1782644332877732</v>
+        <v>0.2969422668489061</v>
       </c>
       <c r="J1066">
         <v>1.352617407913629</v>
       </c>
       <c r="K1066">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1066">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1066">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1066">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1066">
         <v>1</v>
@@ -55149,46 +55155,46 @@
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1067" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C1067">
-        <v>0.6421196605685342</v>
+        <v>0.350218971892259</v>
       </c>
       <c r="D1067" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1067">
-        <v>0.4891720087268077</v>
+        <v>0.5677948016332568</v>
       </c>
       <c r="F1067">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1067">
-        <v>0.01343788033943147</v>
+        <v>0.01200978102810774</v>
       </c>
       <c r="H1067">
-        <v>0.01323082799127319</v>
+        <v>0.01163220519836674</v>
       </c>
       <c r="I1067">
-        <v>0.1529476518417265</v>
+        <v>0.2175758297409978</v>
       </c>
       <c r="J1067">
         <v>1.352617407913629</v>
       </c>
       <c r="K1067">
-        <v>4.73</v>
+        <v>4.31</v>
       </c>
       <c r="L1067">
-        <v>7.04</v>
+        <v>6.18</v>
       </c>
       <c r="M1067">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1067">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1067">
         <v>1</v>
@@ -55199,90 +55205,90 @@
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1068" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1068">
-        <v>0.2708525347843507</v>
+        <v>0.653707777522631</v>
       </c>
       <c r="D1068" t="s">
-        <v>368</v>
+        <v>199</v>
       </c>
       <c r="E1068">
-        <v>0.4960592349210309</v>
+        <v>0.4039058168909611</v>
       </c>
       <c r="F1068">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.01230914746521565</v>
+        <v>0.01366629222247737</v>
       </c>
       <c r="H1068">
-        <v>0.01180394076507897</v>
+        <v>0.01257609418310904</v>
       </c>
       <c r="I1068">
-        <v>0.2252067001366802</v>
+        <v>0.2498019606316699</v>
       </c>
       <c r="J1068">
-        <v>1.352617407913629</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1068">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1068">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1068">
-        <v>4.18</v>
+        <v>4.49</v>
       </c>
       <c r="N1068">
-        <v>6.15</v>
+        <v>6.49</v>
       </c>
       <c r="O1068">
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1069" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C1069">
-        <v>0.193166623733986</v>
+        <v>0.2581249187449384</v>
       </c>
       <c r="D1069" t="s">
         <v>368</v>
       </c>
       <c r="E1069">
-        <v>0.4960592349210309</v>
+        <v>0.4841038562592912</v>
       </c>
       <c r="F1069">
         <v>1</v>
       </c>
       <c r="G1069">
-        <v>0.01190683337626602</v>
+        <v>0.01232187508125506</v>
       </c>
       <c r="H1069">
-        <v>0.01180394076507897</v>
+        <v>0.01181589614374071</v>
       </c>
       <c r="I1069">
-        <v>0.3028926111870449</v>
+        <v>0.2259789375143528</v>
       </c>
       <c r="J1069">
-        <v>1.352617407913629</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1069">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="L1069">
-        <v>6.05</v>
+        <v>6.29</v>
       </c>
       <c r="M1069">
         <v>4.18</v>
@@ -55294,51 +55300,51 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1070" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1070">
-        <v>0.653707777522631</v>
+        <v>0.3378917752338619</v>
       </c>
       <c r="D1070" t="s">
-        <v>199</v>
+        <v>368</v>
       </c>
       <c r="E1070">
-        <v>0.4039058168909611</v>
+        <v>0.4841038562592912</v>
       </c>
       <c r="F1070">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1070">
-        <v>0.01366629222247737</v>
+        <v>0.01202210822476614</v>
       </c>
       <c r="H1070">
-        <v>0.01257609418310904</v>
+        <v>0.01181589614374071</v>
       </c>
       <c r="I1070">
-        <v>0.2498019606316699</v>
+        <v>0.1462120810254293</v>
       </c>
       <c r="J1070">
         <v>1.355477546349452</v>
       </c>
       <c r="K1070">
-        <v>4.8</v>
+        <v>4.31</v>
       </c>
       <c r="L1070">
-        <v>7.16</v>
+        <v>6.18</v>
       </c>
       <c r="M1070">
-        <v>4.49</v>
+        <v>4.18</v>
       </c>
       <c r="N1070">
-        <v>6.49</v>
+        <v>6.15</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55349,90 +55355,90 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1071" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1071">
-        <v>0.2581249187449384</v>
+        <v>0.6493738814716474</v>
       </c>
       <c r="D1071" t="s">
-        <v>368</v>
+        <v>199</v>
       </c>
       <c r="E1071">
-        <v>0.4841038562592912</v>
+        <v>0.3998518182932695</v>
       </c>
       <c r="F1071">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.01232187508125506</v>
+        <v>0.01367062611852835</v>
       </c>
       <c r="H1071">
-        <v>0.01181589614374071</v>
+        <v>0.01258014818170673</v>
       </c>
       <c r="I1071">
-        <v>0.2259789375143528</v>
+        <v>0.2495220631783779</v>
       </c>
       <c r="J1071">
-        <v>1.355477546349452</v>
+        <v>1.356380441360074</v>
       </c>
       <c r="K1071">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1071">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1071">
-        <v>4.18</v>
+        <v>4.49</v>
       </c>
       <c r="N1071">
-        <v>6.15</v>
+        <v>6.49</v>
       </c>
       <c r="O1071">
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1072" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C1072">
-        <v>0.1807822243068724</v>
+        <v>0.2541070359476727</v>
       </c>
       <c r="D1072" t="s">
         <v>368</v>
       </c>
       <c r="E1072">
-        <v>0.4841038562592912</v>
+        <v>0.4803297551148935</v>
       </c>
       <c r="F1072">
         <v>1</v>
       </c>
       <c r="G1072">
-        <v>0.01191921777569313</v>
+        <v>0.01232589296405233</v>
       </c>
       <c r="H1072">
-        <v>0.01181589614374071</v>
+        <v>0.01181967024488511</v>
       </c>
       <c r="I1072">
-        <v>0.3033216319524188</v>
+        <v>0.2262227191672208</v>
       </c>
       <c r="J1072">
-        <v>1.355477546349452</v>
+        <v>1.356380441360074</v>
       </c>
       <c r="K1072">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="L1072">
-        <v>6.05</v>
+        <v>6.29</v>
       </c>
       <c r="M1072">
         <v>4.18</v>
@@ -55444,156 +55450,56 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1073" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C1073">
-        <v>0.6493738814716474</v>
+        <v>0.1768726889108816</v>
       </c>
       <c r="D1073" t="s">
-        <v>199</v>
+        <v>368</v>
       </c>
       <c r="E1073">
-        <v>0.3998518182932695</v>
+        <v>0.4803297551148935</v>
       </c>
       <c r="F1073">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1073">
-        <v>0.01367062611852835</v>
+        <v>0.01192312731108912</v>
       </c>
       <c r="H1073">
-        <v>0.01258014818170673</v>
+        <v>0.01181967024488511</v>
       </c>
       <c r="I1073">
-        <v>0.2495220631783779</v>
+        <v>0.3034570662040119</v>
       </c>
       <c r="J1073">
         <v>1.356380441360074</v>
       </c>
       <c r="K1073">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="L1073">
-        <v>7.16</v>
+        <v>6.05</v>
       </c>
       <c r="M1073">
-        <v>4.49</v>
+        <v>4.18</v>
       </c>
       <c r="N1073">
-        <v>6.49</v>
+        <v>6.15</v>
       </c>
       <c r="O1073">
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="1074" spans="1:16">
-      <c r="A1074" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>206</v>
-      </c>
-      <c r="C1074">
-        <v>0.2541070359476727</v>
-      </c>
-      <c r="D1074" t="s">
-        <v>368</v>
-      </c>
-      <c r="E1074">
-        <v>0.4803297551148935</v>
-      </c>
-      <c r="F1074">
-        <v>1</v>
-      </c>
-      <c r="G1074">
-        <v>0.01232589296405233</v>
-      </c>
-      <c r="H1074">
-        <v>0.01181967024488511</v>
-      </c>
-      <c r="I1074">
-        <v>0.2262227191672208</v>
-      </c>
-      <c r="J1074">
-        <v>1.356380441360074</v>
-      </c>
-      <c r="K1074">
-        <v>4.45</v>
-      </c>
-      <c r="L1074">
-        <v>6.29</v>
-      </c>
-      <c r="M1074">
-        <v>4.18</v>
-      </c>
-      <c r="N1074">
-        <v>6.15</v>
-      </c>
-      <c r="O1074">
-        <v>1</v>
-      </c>
-      <c r="P1074" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="1075" spans="1:16">
-      <c r="A1075" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>211</v>
-      </c>
-      <c r="C1075">
-        <v>0.1768726889108816</v>
-      </c>
-      <c r="D1075" t="s">
-        <v>368</v>
-      </c>
-      <c r="E1075">
-        <v>0.4803297551148935</v>
-      </c>
-      <c r="F1075">
-        <v>1</v>
-      </c>
-      <c r="G1075">
-        <v>0.01192312731108912</v>
-      </c>
-      <c r="H1075">
-        <v>0.01181967024488511</v>
-      </c>
-      <c r="I1075">
-        <v>0.3034570662040119</v>
-      </c>
-      <c r="J1075">
-        <v>1.356380441360074</v>
-      </c>
-      <c r="K1075">
-        <v>4.33</v>
-      </c>
-      <c r="L1075">
-        <v>6.05</v>
-      </c>
-      <c r="M1075">
-        <v>4.18</v>
-      </c>
-      <c r="N1075">
-        <v>6.15</v>
-      </c>
-      <c r="O1075">
-        <v>1</v>
-      </c>
-      <c r="P1075" t="s">
         <v>208</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3243" uniqueCount="495">
   <si>
     <t>trade_time</t>
   </si>
@@ -631,19 +631,19 @@
     <t>2021-10-26</t>
   </si>
   <si>
-    <t>2021-11-09</t>
+    <t>2021-11-10</t>
   </si>
   <si>
-    <t>2021-11-10</t>
+    <t>2021-10-25</t>
   </si>
   <si>
     <t>2021-10-28</t>
   </si>
   <si>
-    <t>2021-11-30</t>
+    <t>2021-11-09</t>
   </si>
   <si>
-    <t>2021-10-25</t>
+    <t>2021-11-30</t>
   </si>
   <si>
     <t>2021-11-01</t>
@@ -1138,7 +1138,7 @@
     <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-12-01</t>
+    <t>2021-12-02</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1856,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1079"/>
+  <dimension ref="A1:P1077"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51667,7 +51667,7 @@
         <v>0.5439992376982135</v>
       </c>
       <c r="D997" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E997">
         <v>0.4290141353004202</v>
@@ -52867,7 +52867,7 @@
         <v>0.3892090844427933</v>
       </c>
       <c r="D1021" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E1021">
         <v>0.7538814936438047</v>
@@ -52967,7 +52967,7 @@
         <v>0.3856328717938826</v>
       </c>
       <c r="D1023" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E1023">
         <v>0.750807205577197</v>
@@ -53117,7 +53117,7 @@
         <v>0.3841534580543895</v>
       </c>
       <c r="D1026" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E1026">
         <v>0.7495354288537728</v>
@@ -53317,10 +53317,10 @@
         <v>0.381456182952979</v>
       </c>
       <c r="D1030" t="s">
-        <v>208</v>
+        <v>371</v>
       </c>
       <c r="E1030">
-        <v>0.7472167186788763</v>
+        <v>0.5831390428938166</v>
       </c>
       <c r="F1030">
         <v>1</v>
@@ -53329,10 +53329,10 @@
         <v>0.01271854381704702</v>
       </c>
       <c r="H1030">
-        <v>0.01135278328132112</v>
+        <v>0.01175686095710619</v>
       </c>
       <c r="I1030">
-        <v>0.3657605357258973</v>
+        <v>0.2016828599408376</v>
       </c>
       <c r="J1030">
         <v>1.352750837071715</v>
@@ -53344,10 +53344,10 @@
         <v>6.55</v>
       </c>
       <c r="M1030">
-        <v>3.92</v>
+        <v>4.13</v>
       </c>
       <c r="N1030">
-        <v>6.05</v>
+        <v>6.17</v>
       </c>
       <c r="O1030">
         <v>1</v>
@@ -53558,63 +53558,63 @@
     </row>
     <row r="1035" spans="1:16">
       <c r="A1035" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1035" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1035">
-        <v>0.3459113840917176</v>
+        <v>0.8032731591004225</v>
       </c>
       <c r="D1035" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E1035">
-        <v>0.579562416774662</v>
+        <v>0.5743889484000011</v>
       </c>
       <c r="F1035">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1035">
-        <v>0.01201408861590828</v>
+        <v>0.01577672684089958</v>
       </c>
       <c r="H1035">
-        <v>0.01176043758322534</v>
+        <v>0.0133856110516</v>
       </c>
       <c r="I1035">
-        <v>0.2336510326829444</v>
+        <v>0.2288842107004214</v>
       </c>
       <c r="J1035">
-        <v>1.353616848238581</v>
+        <v>1.351394736624472</v>
       </c>
       <c r="K1035">
-        <v>4.31</v>
+        <v>5.54</v>
       </c>
       <c r="L1035">
-        <v>6.18</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1035">
-        <v>4.13</v>
+        <v>4.74</v>
       </c>
       <c r="N1035">
-        <v>6.17</v>
+        <v>6.98</v>
       </c>
       <c r="O1035">
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>362</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
       <c r="A1036" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1036" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C1036">
-        <v>0.8032731591004225</v>
+        <v>0.7916636853552763</v>
       </c>
       <c r="D1036" t="s">
         <v>363</v>
@@ -53626,22 +53626,22 @@
         <v>-1</v>
       </c>
       <c r="G1036">
-        <v>0.01577672684089958</v>
+        <v>0.01500833631464472</v>
       </c>
       <c r="H1036">
         <v>0.0133856110516</v>
       </c>
       <c r="I1036">
-        <v>0.2288842107004214</v>
+        <v>0.2172747369552752</v>
       </c>
       <c r="J1036">
         <v>1.351394736624472</v>
       </c>
       <c r="K1036">
-        <v>5.54</v>
+        <v>5.26</v>
       </c>
       <c r="L1036">
-        <v>8.289999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="M1036">
         <v>4.74</v>
@@ -53658,46 +53658,46 @@
     </row>
     <row r="1037" spans="1:16">
       <c r="A1037" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1037" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1037">
-        <v>0.7916636853552763</v>
+        <v>0.3876400009924064</v>
       </c>
       <c r="D1037" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E1037">
-        <v>0.5743889484000011</v>
+        <v>0.5887397377409291</v>
       </c>
       <c r="F1037">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1037">
-        <v>0.01500833631464472</v>
+        <v>0.01271235999900759</v>
       </c>
       <c r="H1037">
-        <v>0.0133856110516</v>
+        <v>0.01175126026225907</v>
       </c>
       <c r="I1037">
-        <v>0.2172747369552752</v>
+        <v>0.2010997367485228</v>
       </c>
       <c r="J1037">
         <v>1.351394736624472</v>
       </c>
       <c r="K1037">
-        <v>5.26</v>
+        <v>4.56</v>
       </c>
       <c r="L1037">
-        <v>7.9</v>
+        <v>6.55</v>
       </c>
       <c r="M1037">
-        <v>4.74</v>
+        <v>4.13</v>
       </c>
       <c r="N1037">
-        <v>6.98</v>
+        <v>6.17</v>
       </c>
       <c r="O1037">
         <v>1</v>
@@ -53708,13 +53708,13 @@
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1038" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C1038">
-        <v>0.3876400009924064</v>
+        <v>0.3554886851485248</v>
       </c>
       <c r="D1038" t="s">
         <v>371</v>
@@ -53726,22 +53726,22 @@
         <v>1</v>
       </c>
       <c r="G1038">
-        <v>0.01271235999900759</v>
+        <v>0.01200451131485147</v>
       </c>
       <c r="H1038">
         <v>0.01175126026225907</v>
       </c>
       <c r="I1038">
-        <v>0.2010997367485228</v>
+        <v>0.2332510525924043</v>
       </c>
       <c r="J1038">
         <v>1.351394736624472</v>
       </c>
       <c r="K1038">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1038">
-        <v>6.55</v>
+        <v>6.18</v>
       </c>
       <c r="M1038">
         <v>4.13</v>
@@ -53758,63 +53758,63 @@
     </row>
     <row r="1039" spans="1:16">
       <c r="A1039" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1039" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1039">
-        <v>0.3554886851485248</v>
+        <v>0.8031318580204516</v>
       </c>
       <c r="D1039" t="s">
-        <v>371</v>
+        <v>198</v>
       </c>
       <c r="E1039">
-        <v>0.5887397377409291</v>
+        <v>0.4948106590751502</v>
       </c>
       <c r="F1039">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1039">
-        <v>0.01200451131485147</v>
+        <v>0.01577686814197955</v>
       </c>
       <c r="H1039">
-        <v>0.01175126026225907</v>
+        <v>0.01322518934092485</v>
       </c>
       <c r="I1039">
-        <v>0.2332510525924043</v>
+        <v>0.3083211989453014</v>
       </c>
       <c r="J1039">
-        <v>1.351394736624472</v>
+        <v>1.351420242234575</v>
       </c>
       <c r="K1039">
-        <v>4.31</v>
+        <v>5.54</v>
       </c>
       <c r="L1039">
-        <v>6.18</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1039">
-        <v>4.13</v>
+        <v>4.71</v>
       </c>
       <c r="N1039">
-        <v>6.17</v>
+        <v>6.86</v>
       </c>
       <c r="O1039">
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1040" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C1040">
-        <v>0.8031318580204516</v>
+        <v>0.7915295258461343</v>
       </c>
       <c r="D1040" t="s">
         <v>198</v>
@@ -53826,22 +53826,22 @@
         <v>-1</v>
       </c>
       <c r="G1040">
-        <v>0.01577686814197955</v>
+        <v>0.01500847047415387</v>
       </c>
       <c r="H1040">
         <v>0.01322518934092485</v>
       </c>
       <c r="I1040">
-        <v>0.3083211989453014</v>
+        <v>0.2967188667709841</v>
       </c>
       <c r="J1040">
         <v>1.351420242234575</v>
       </c>
       <c r="K1040">
-        <v>5.54</v>
+        <v>5.26</v>
       </c>
       <c r="L1040">
-        <v>8.289999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="M1040">
         <v>4.71</v>
@@ -53858,46 +53858,46 @@
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1041" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1041">
-        <v>0.7915295258461343</v>
+        <v>0.3875236954103372</v>
       </c>
       <c r="D1041" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1041">
-        <v>0.4948106590751502</v>
+        <v>0.5726912092605865</v>
       </c>
       <c r="F1041">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1041">
-        <v>0.01500847047415387</v>
+        <v>0.01271247630458966</v>
       </c>
       <c r="H1041">
-        <v>0.01322518934092485</v>
+        <v>0.01162730879073941</v>
       </c>
       <c r="I1041">
-        <v>0.2967188667709841</v>
+        <v>0.1851675138502493</v>
       </c>
       <c r="J1041">
         <v>1.351420242234575</v>
       </c>
       <c r="K1041">
-        <v>5.26</v>
+        <v>4.56</v>
       </c>
       <c r="L1041">
-        <v>7.9</v>
+        <v>6.55</v>
       </c>
       <c r="M1041">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1041">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1041">
         <v>1</v>
@@ -53908,13 +53908,13 @@
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1042" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C1042">
-        <v>0.3821231123667568</v>
+        <v>0.3553787559689807</v>
       </c>
       <c r="D1042" t="s">
         <v>369</v>
@@ -53926,22 +53926,22 @@
         <v>1</v>
       </c>
       <c r="G1042">
-        <v>0.01251787688763324</v>
+        <v>0.01200462124403102</v>
       </c>
       <c r="H1042">
         <v>0.01162730879073941</v>
       </c>
       <c r="I1042">
-        <v>0.1905680968938297</v>
+        <v>0.2173124532916058</v>
       </c>
       <c r="J1042">
         <v>1.351420242234575</v>
       </c>
       <c r="K1042">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="L1042">
-        <v>6.45</v>
+        <v>6.18</v>
       </c>
       <c r="M1042">
         <v>4.09</v>
@@ -53958,63 +53958,63 @@
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1043" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1043">
-        <v>0.3553787559689807</v>
+        <v>0.8327877653809024</v>
       </c>
       <c r="D1043" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1043">
-        <v>0.5726912092605865</v>
+        <v>0.5200235333834033</v>
       </c>
       <c r="F1043">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1043">
-        <v>0.01200462124403102</v>
+        <v>0.0157472122346191</v>
       </c>
       <c r="H1043">
-        <v>0.01162730879073941</v>
+        <v>0.0131999764666166</v>
       </c>
       <c r="I1043">
-        <v>0.2173124532916058</v>
+        <v>0.312764231997499</v>
       </c>
       <c r="J1043">
-        <v>1.351420242234575</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1043">
-        <v>4.31</v>
+        <v>5.54</v>
       </c>
       <c r="L1043">
-        <v>6.18</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M1043">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1043">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1043">
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1044" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C1044">
-        <v>0.8327877653809024</v>
+        <v>0.8196865786829521</v>
       </c>
       <c r="D1044" t="s">
         <v>198</v>
@@ -54026,22 +54026,22 @@
         <v>-1</v>
       </c>
       <c r="G1044">
-        <v>0.0157472122346191</v>
+        <v>0.01498031342131705</v>
       </c>
       <c r="H1044">
         <v>0.0131999764666166</v>
       </c>
       <c r="I1044">
-        <v>0.312764231997499</v>
+        <v>0.2996630452995488</v>
       </c>
       <c r="J1044">
         <v>1.346067190364458</v>
       </c>
       <c r="K1044">
-        <v>5.54</v>
+        <v>5.26</v>
       </c>
       <c r="L1044">
-        <v>8.289999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="M1044">
         <v>4.71</v>
@@ -54058,46 +54058,46 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1045" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C1045">
-        <v>0.8196865786829521</v>
+        <v>0.3000010028781626</v>
       </c>
       <c r="D1045" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1045">
-        <v>0.5200235333834033</v>
+        <v>0.5945851914093669</v>
       </c>
       <c r="F1045">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1045">
-        <v>0.01498031342131705</v>
+        <v>0.01227999899712184</v>
       </c>
       <c r="H1045">
-        <v>0.0131999764666166</v>
+        <v>0.01160541480859063</v>
       </c>
       <c r="I1045">
-        <v>0.2996630452995488</v>
+        <v>0.2945841885312044</v>
       </c>
       <c r="J1045">
         <v>1.346067190364458</v>
       </c>
       <c r="K1045">
-        <v>5.26</v>
+        <v>4.45</v>
       </c>
       <c r="L1045">
-        <v>7.9</v>
+        <v>6.29</v>
       </c>
       <c r="M1045">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1045">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1045">
         <v>1</v>
@@ -54108,13 +54108,13 @@
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1046" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1046">
-        <v>0.3000010028781626</v>
+        <v>0.3784504095291865</v>
       </c>
       <c r="D1046" t="s">
         <v>369</v>
@@ -54126,22 +54126,22 @@
         <v>1</v>
       </c>
       <c r="G1046">
-        <v>0.01227999899712184</v>
+        <v>0.01198154959047081</v>
       </c>
       <c r="H1046">
         <v>0.01160541480859063</v>
       </c>
       <c r="I1046">
-        <v>0.2945841885312044</v>
+        <v>0.2161347818801804</v>
       </c>
       <c r="J1046">
         <v>1.346067190364458</v>
       </c>
       <c r="K1046">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1046">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1046">
         <v>4.09</v>
@@ -54158,96 +54158,96 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1047" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C1047">
-        <v>0.3784504095291865</v>
+        <v>0.8114319364950138</v>
       </c>
       <c r="D1047" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1047">
-        <v>0.5945851914093669</v>
+        <v>0.5126320191808968</v>
       </c>
       <c r="F1047">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1047">
-        <v>0.01198154959047081</v>
+        <v>0.01498856806350499</v>
       </c>
       <c r="H1047">
-        <v>0.01160541480859063</v>
+        <v>0.0132073679808191</v>
       </c>
       <c r="I1047">
-        <v>0.2161347818801804</v>
+        <v>0.2987999173141169</v>
       </c>
       <c r="J1047">
-        <v>1.346067190364458</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1047">
-        <v>4.31</v>
+        <v>5.26</v>
       </c>
       <c r="L1047">
-        <v>6.18</v>
+        <v>7.9</v>
       </c>
       <c r="M1047">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1047">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1048" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1048">
-        <v>0.8114319364950138</v>
+        <v>0.4047774962770463</v>
       </c>
       <c r="D1048" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1048">
-        <v>0.5126320191808968</v>
+        <v>0.5881666578449822</v>
       </c>
       <c r="F1048">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1048">
-        <v>0.01498856806350499</v>
+        <v>0.01269522250372295</v>
       </c>
       <c r="H1048">
-        <v>0.0132073679808191</v>
+        <v>0.01161183334215502</v>
       </c>
       <c r="I1048">
-        <v>0.2987999173141169</v>
+        <v>0.1833891615679359</v>
       </c>
       <c r="J1048">
         <v>1.347636513974332</v>
       </c>
       <c r="K1048">
-        <v>5.26</v>
+        <v>4.56</v>
       </c>
       <c r="L1048">
-        <v>7.9</v>
+        <v>6.55</v>
       </c>
       <c r="M1048">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1048">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1048">
         <v>1</v>
@@ -54258,13 +54258,13 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1049" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C1049">
-        <v>0.4047774962770463</v>
+        <v>0.3716866247706294</v>
       </c>
       <c r="D1049" t="s">
         <v>369</v>
@@ -54276,22 +54276,22 @@
         <v>1</v>
       </c>
       <c r="G1049">
-        <v>0.01269522250372295</v>
+        <v>0.01198831337522937</v>
       </c>
       <c r="H1049">
         <v>0.01161183334215502</v>
       </c>
       <c r="I1049">
-        <v>0.1833891615679359</v>
+        <v>0.2164800330743528</v>
       </c>
       <c r="J1049">
         <v>1.347636513974332</v>
       </c>
       <c r="K1049">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1049">
-        <v>6.55</v>
+        <v>6.18</v>
       </c>
       <c r="M1049">
         <v>4.09</v>
@@ -54308,63 +54308,63 @@
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1050" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1050">
-        <v>0.3716866247706294</v>
+        <v>0.6963736868234349</v>
       </c>
       <c r="D1050" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1050">
-        <v>0.5881666578449822</v>
+        <v>0.5070592712848851</v>
       </c>
       <c r="F1050">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.01198831337522937</v>
+        <v>0.01526362631317657</v>
       </c>
       <c r="H1050">
-        <v>0.01161183334215502</v>
+        <v>0.01321294072871512</v>
       </c>
       <c r="I1050">
-        <v>0.2164800330743528</v>
+        <v>0.1893144155385498</v>
       </c>
       <c r="J1050">
-        <v>1.347636513974332</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1050">
-        <v>4.31</v>
+        <v>5.4</v>
       </c>
       <c r="L1050">
-        <v>6.18</v>
+        <v>7.98</v>
       </c>
       <c r="M1050">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1050">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1050">
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>365</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1051" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C1051">
-        <v>0.8052084430909758</v>
+        <v>0.6986891056461033</v>
       </c>
       <c r="D1051" t="s">
         <v>198</v>
@@ -54376,22 +54376,22 @@
         <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.01499479155690902</v>
+        <v>0.0137013108943539</v>
       </c>
       <c r="H1051">
         <v>0.01321294072871512</v>
       </c>
       <c r="I1051">
-        <v>0.2981491718060907</v>
+        <v>0.1916298343612182</v>
       </c>
       <c r="J1051">
         <v>1.34881968762529</v>
       </c>
       <c r="K1051">
-        <v>5.26</v>
+        <v>4.82</v>
       </c>
       <c r="L1051">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="M1051">
         <v>4.71</v>
@@ -54408,46 +54408,46 @@
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1052" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C1052">
-        <v>0.6986891056461033</v>
+        <v>0.3937996025624484</v>
       </c>
       <c r="D1052" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1052">
-        <v>0.5070592712848851</v>
+        <v>0.5833274776125643</v>
       </c>
       <c r="F1052">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1052">
-        <v>0.0137013108943539</v>
+        <v>0.01250620039743755</v>
       </c>
       <c r="H1052">
-        <v>0.01321294072871512</v>
+        <v>0.01161667252238744</v>
       </c>
       <c r="I1052">
-        <v>0.1916298343612182</v>
+        <v>0.1895278750501159</v>
       </c>
       <c r="J1052">
         <v>1.34881968762529</v>
       </c>
       <c r="K1052">
-        <v>4.82</v>
+        <v>4.49</v>
       </c>
       <c r="L1052">
-        <v>7.2</v>
+        <v>6.45</v>
       </c>
       <c r="M1052">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1052">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1052">
         <v>1</v>
@@ -54458,13 +54458,13 @@
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1053" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C1053">
-        <v>0.3937996025624484</v>
+        <v>0.366587146335001</v>
       </c>
       <c r="D1053" t="s">
         <v>369</v>
@@ -54476,22 +54476,22 @@
         <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.01250620039743755</v>
+        <v>0.011993412853665</v>
       </c>
       <c r="H1053">
         <v>0.01161667252238744</v>
       </c>
       <c r="I1053">
-        <v>0.1895278750501159</v>
+        <v>0.2167403312775633</v>
       </c>
       <c r="J1053">
         <v>1.34881968762529</v>
       </c>
       <c r="K1053">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="L1053">
-        <v>6.45</v>
+        <v>6.18</v>
       </c>
       <c r="M1053">
         <v>4.09</v>
@@ -54508,46 +54508,46 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1054" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1054">
-        <v>0.366587146335001</v>
+        <v>0.7626268245088639</v>
       </c>
       <c r="D1054" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1054">
-        <v>0.5833274776125643</v>
+        <v>0.5584455088500349</v>
       </c>
       <c r="F1054">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.011993412853665</v>
+        <v>0.01133737317549114</v>
       </c>
       <c r="H1054">
-        <v>0.01161667252238744</v>
+        <v>0.01186155449114997</v>
       </c>
       <c r="I1054">
-        <v>0.2167403312775633</v>
+        <v>0.204181315658829</v>
       </c>
       <c r="J1054">
         <v>1.34881968762529</v>
       </c>
       <c r="K1054">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1054">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1054">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="N1054">
-        <v>6.1</v>
+        <v>6.21</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54558,63 +54558,63 @@
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1055" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C1055">
-        <v>0.7626268245088639</v>
+        <v>0.685527947714454</v>
       </c>
       <c r="D1055" t="s">
-        <v>374</v>
+        <v>198</v>
       </c>
       <c r="E1055">
-        <v>0.5723982963550469</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1055">
         <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.01133737317549114</v>
+        <v>0.01527447205228555</v>
       </c>
       <c r="H1055">
-        <v>0.01176760170364495</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1055">
-        <v>0.190228528153817</v>
+        <v>0.1879285710968466</v>
       </c>
       <c r="J1055">
-        <v>1.34881968762529</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1055">
-        <v>3.92</v>
+        <v>5.4</v>
       </c>
       <c r="L1055">
-        <v>6.05</v>
+        <v>7.98</v>
       </c>
       <c r="M1055">
-        <v>4.15</v>
+        <v>4.71</v>
       </c>
       <c r="N1055">
-        <v>6.17</v>
+        <v>6.86</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1056" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C1056">
-        <v>0.685527947714454</v>
+        <v>0.6890082792562344</v>
       </c>
       <c r="D1056" t="s">
         <v>198</v>
@@ -54626,22 +54626,22 @@
         <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.01527447205228555</v>
+        <v>0.01371099172074377</v>
       </c>
       <c r="H1056">
         <v>0.01322240062338239</v>
       </c>
       <c r="I1056">
-        <v>0.1879285710968466</v>
+        <v>0.191408902638627</v>
       </c>
       <c r="J1056">
         <v>1.350828157830657</v>
       </c>
       <c r="K1056">
-        <v>5.4</v>
+        <v>4.82</v>
       </c>
       <c r="L1056">
-        <v>7.98</v>
+        <v>7.2</v>
       </c>
       <c r="M1056">
         <v>4.71</v>
@@ -54658,13 +54658,13 @@
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1057" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C1057">
-        <v>0.6890082792562344</v>
+        <v>0.6760248424128479</v>
       </c>
       <c r="D1057" t="s">
         <v>198</v>
@@ -54676,22 +54676,22 @@
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.01371099172074377</v>
+        <v>0.01364397515758715</v>
       </c>
       <c r="H1057">
         <v>0.01322240062338239</v>
       </c>
       <c r="I1057">
-        <v>0.191408902638627</v>
+        <v>0.1784254657952404</v>
       </c>
       <c r="J1057">
         <v>1.350828157830657</v>
       </c>
       <c r="K1057">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="L1057">
-        <v>7.2</v>
+        <v>7.16</v>
       </c>
       <c r="M1057">
         <v>4.71</v>
@@ -54708,46 +54708,46 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1058" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C1058">
-        <v>0.6760248424128479</v>
+        <v>0.3847815713403513</v>
       </c>
       <c r="D1058" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1058">
-        <v>0.4975993766176074</v>
+        <v>0.5751128344726144</v>
       </c>
       <c r="F1058">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.01364397515758715</v>
+        <v>0.01251521842865965</v>
       </c>
       <c r="H1058">
-        <v>0.01322240062338239</v>
+        <v>0.01162488716552739</v>
       </c>
       <c r="I1058">
-        <v>0.1784254657952404</v>
+        <v>0.1903312631322631</v>
       </c>
       <c r="J1058">
         <v>1.350828157830657</v>
       </c>
       <c r="K1058">
-        <v>4.8</v>
+        <v>4.49</v>
       </c>
       <c r="L1058">
-        <v>7.16</v>
+        <v>6.45</v>
       </c>
       <c r="M1058">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1058">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1058">
         <v>1</v>
@@ -54758,13 +54758,13 @@
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1059" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1059">
-        <v>0.2788146976535772</v>
+        <v>0.3579306397498696</v>
       </c>
       <c r="D1059" t="s">
         <v>369</v>
@@ -54776,22 +54776,22 @@
         <v>1</v>
       </c>
       <c r="G1059">
-        <v>0.01230118530234642</v>
+        <v>0.01200206936025013</v>
       </c>
       <c r="H1059">
         <v>0.01162488716552739</v>
       </c>
       <c r="I1059">
-        <v>0.2962981368190372</v>
+        <v>0.2171821947227448</v>
       </c>
       <c r="J1059">
         <v>1.350828157830657</v>
       </c>
       <c r="K1059">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1059">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1059">
         <v>4.09</v>
@@ -54808,46 +54808,46 @@
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1060" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1060">
-        <v>0.3579306397498696</v>
+        <v>0.7547536213038253</v>
       </c>
       <c r="D1060" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1060">
-        <v>0.5751128344726144</v>
+        <v>0.5500300186895482</v>
       </c>
       <c r="F1060">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.01200206936025013</v>
+        <v>0.01134524637869617</v>
       </c>
       <c r="H1060">
-        <v>0.01162488716552739</v>
+        <v>0.01186996998131045</v>
       </c>
       <c r="I1060">
-        <v>0.2171821947227448</v>
+        <v>0.2047236026142771</v>
       </c>
       <c r="J1060">
         <v>1.350828157830657</v>
       </c>
       <c r="K1060">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1060">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1060">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="N1060">
-        <v>6.1</v>
+        <v>6.21</v>
       </c>
       <c r="O1060">
         <v>1</v>
@@ -54858,346 +54858,346 @@
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1061" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C1061">
-        <v>0.7547536213038253</v>
+        <v>0.6767185447573851</v>
       </c>
       <c r="D1061" t="s">
-        <v>374</v>
+        <v>198</v>
       </c>
       <c r="E1061">
-        <v>0.5640631450027742</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1061">
         <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.01134524637869617</v>
+        <v>0.01364328145524261</v>
       </c>
       <c r="H1061">
-        <v>0.01177593685499723</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1061">
-        <v>0.1906904763010511</v>
+        <v>0.178438472714201</v>
       </c>
       <c r="J1061">
-        <v>1.350828157830657</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1061">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1061">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1061">
-        <v>4.15</v>
+        <v>4.71</v>
       </c>
       <c r="N1061">
-        <v>6.17</v>
+        <v>6.86</v>
       </c>
       <c r="O1061">
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1062" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C1062">
-        <v>0.6897048720272076</v>
+        <v>0.2794578175354925</v>
       </c>
       <c r="D1062" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1062">
-        <v>0.4982800720431841</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1062">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.01371029512797279</v>
+        <v>0.01230054218246451</v>
       </c>
       <c r="H1062">
-        <v>0.01322171992795682</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1062">
-        <v>0.1914247999840235</v>
+        <v>0.2962461091431958</v>
       </c>
       <c r="J1062">
         <v>1.350683636508878</v>
       </c>
       <c r="K1062">
-        <v>4.82</v>
+        <v>4.45</v>
       </c>
       <c r="L1062">
-        <v>7.2</v>
+        <v>6.29</v>
       </c>
       <c r="M1062">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1062">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1062">
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1063" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C1063">
-        <v>0.6767185447573851</v>
+        <v>0.3585535266467357</v>
       </c>
       <c r="D1063" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1063">
-        <v>0.4982800720431841</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1063">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1063">
-        <v>0.01364328145524261</v>
+        <v>0.01200144647335326</v>
       </c>
       <c r="H1063">
-        <v>0.01322171992795682</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1063">
-        <v>0.178438472714201</v>
+        <v>0.2171504000319526</v>
       </c>
       <c r="J1063">
         <v>1.350683636508878</v>
       </c>
       <c r="K1063">
-        <v>4.8</v>
+        <v>4.31</v>
       </c>
       <c r="L1063">
-        <v>7.16</v>
+        <v>6.18</v>
       </c>
       <c r="M1063">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1063">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1063">
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1064" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1064">
-        <v>0.2794578175354925</v>
+        <v>0.7553201448851974</v>
       </c>
       <c r="D1064" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1064">
-        <v>0.5757039266786883</v>
+        <v>0.5506355630278001</v>
       </c>
       <c r="F1064">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.01230054218246451</v>
+        <v>0.0113446798551148</v>
       </c>
       <c r="H1064">
-        <v>0.01162429607332131</v>
+        <v>0.0118693644369722</v>
       </c>
       <c r="I1064">
-        <v>0.2962461091431958</v>
+        <v>0.2046845818573972</v>
       </c>
       <c r="J1064">
         <v>1.350683636508878</v>
       </c>
       <c r="K1064">
-        <v>4.45</v>
+        <v>3.92</v>
       </c>
       <c r="L1064">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="M1064">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="N1064">
-        <v>6.1</v>
+        <v>6.21</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1065" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1065">
-        <v>0.3585535266467357</v>
+        <v>0.6674364420145809</v>
       </c>
       <c r="D1065" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1065">
-        <v>0.5757039266786883</v>
+        <v>0.4891720087268077</v>
       </c>
       <c r="F1065">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.01200144647335326</v>
+        <v>0.01365256355798542</v>
       </c>
       <c r="H1065">
-        <v>0.01162429607332131</v>
+        <v>0.01323082799127319</v>
       </c>
       <c r="I1065">
-        <v>0.2171504000319526</v>
+        <v>0.1782644332877732</v>
       </c>
       <c r="J1065">
-        <v>1.350683636508878</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1065">
-        <v>4.31</v>
+        <v>4.8</v>
       </c>
       <c r="L1065">
-        <v>6.18</v>
+        <v>7.16</v>
       </c>
       <c r="M1065">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1065">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1065">
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1066" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C1066">
-        <v>0.7553201448851974</v>
+        <v>0.2708525347843507</v>
       </c>
       <c r="D1066" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E1066">
-        <v>0.5646629084881551</v>
+        <v>0.5677948016332568</v>
       </c>
       <c r="F1066">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1066">
-        <v>0.0113446798551148</v>
+        <v>0.01230914746521565</v>
       </c>
       <c r="H1066">
-        <v>0.01177533709151184</v>
+        <v>0.01163220519836674</v>
       </c>
       <c r="I1066">
-        <v>0.1906572363970422</v>
+        <v>0.2969422668489061</v>
       </c>
       <c r="J1066">
-        <v>1.350683636508878</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1066">
-        <v>3.92</v>
+        <v>4.45</v>
       </c>
       <c r="L1066">
-        <v>6.05</v>
+        <v>6.29</v>
       </c>
       <c r="M1066">
-        <v>4.15</v>
+        <v>4.09</v>
       </c>
       <c r="N1066">
-        <v>6.17</v>
+        <v>6.1</v>
       </c>
       <c r="O1066">
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1067" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C1067">
-        <v>0.6674364420145809</v>
+        <v>0.350218971892259</v>
       </c>
       <c r="D1067" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1067">
-        <v>0.4891720087268077</v>
+        <v>0.5677948016332568</v>
       </c>
       <c r="F1067">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1067">
-        <v>0.01365256355798542</v>
+        <v>0.01200978102810774</v>
       </c>
       <c r="H1067">
-        <v>0.01323082799127319</v>
+        <v>0.01163220519836674</v>
       </c>
       <c r="I1067">
-        <v>0.1782644332877732</v>
+        <v>0.2175758297409978</v>
       </c>
       <c r="J1067">
         <v>1.352617407913629</v>
       </c>
       <c r="K1067">
-        <v>4.8</v>
+        <v>4.31</v>
       </c>
       <c r="L1067">
-        <v>7.16</v>
+        <v>6.18</v>
       </c>
       <c r="M1067">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1067">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1067">
         <v>1</v>
@@ -55208,46 +55208,46 @@
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1068" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1068">
-        <v>0.2708525347843507</v>
+        <v>0.7477397609785736</v>
       </c>
       <c r="D1068" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1068">
-        <v>0.5677948016332568</v>
+        <v>0.5425330608418939</v>
       </c>
       <c r="F1068">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.01230914746521565</v>
+        <v>0.01135226023902143</v>
       </c>
       <c r="H1068">
-        <v>0.01163220519836674</v>
+        <v>0.01187746693915811</v>
       </c>
       <c r="I1068">
-        <v>0.2969422668489061</v>
+        <v>0.2052067001366797</v>
       </c>
       <c r="J1068">
         <v>1.352617407913629</v>
       </c>
       <c r="K1068">
-        <v>4.45</v>
+        <v>3.92</v>
       </c>
       <c r="L1068">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="M1068">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="N1068">
-        <v>6.1</v>
+        <v>6.21</v>
       </c>
       <c r="O1068">
         <v>1</v>
@@ -55258,146 +55258,146 @@
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1069" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1069">
-        <v>0.350218971892259</v>
+        <v>0.653707777522631</v>
       </c>
       <c r="D1069" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1069">
-        <v>0.5677948016332568</v>
+        <v>0.4757007566940814</v>
       </c>
       <c r="F1069">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1069">
-        <v>0.01200978102810774</v>
+        <v>0.01366629222247737</v>
       </c>
       <c r="H1069">
-        <v>0.01163220519836674</v>
+        <v>0.01324429924330592</v>
       </c>
       <c r="I1069">
-        <v>0.2175758297409978</v>
+        <v>0.1780070208285496</v>
       </c>
       <c r="J1069">
-        <v>1.352617407913629</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1069">
-        <v>4.31</v>
+        <v>4.8</v>
       </c>
       <c r="L1069">
-        <v>6.18</v>
+        <v>7.16</v>
       </c>
       <c r="M1069">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1069">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1069">
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1070" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C1070">
-        <v>0.7477397609785736</v>
+        <v>0.6285912057670915</v>
       </c>
       <c r="D1070" t="s">
-        <v>374</v>
+        <v>198</v>
       </c>
       <c r="E1070">
-        <v>0.5566377571584384</v>
+        <v>0.4757007566940814</v>
       </c>
       <c r="F1070">
         <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.01135226023902143</v>
+        <v>0.01345140879423291</v>
       </c>
       <c r="H1070">
-        <v>0.01178336224284156</v>
+        <v>0.01324429924330592</v>
       </c>
       <c r="I1070">
-        <v>0.1911020038201352</v>
+        <v>0.1528904490730101</v>
       </c>
       <c r="J1070">
-        <v>1.352617407913629</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1070">
-        <v>3.92</v>
+        <v>4.73</v>
       </c>
       <c r="L1070">
-        <v>6.05</v>
+        <v>7.04</v>
       </c>
       <c r="M1070">
-        <v>4.15</v>
+        <v>4.71</v>
       </c>
       <c r="N1070">
-        <v>6.17</v>
+        <v>6.86</v>
       </c>
       <c r="O1070">
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1071" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C1071">
-        <v>0.653707777522631</v>
+        <v>0.2581249187449384</v>
       </c>
       <c r="D1071" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1071">
-        <v>0.4757007566940814</v>
+        <v>0.5560968354307416</v>
       </c>
       <c r="F1071">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1071">
-        <v>0.01366629222247737</v>
+        <v>0.01232187508125506</v>
       </c>
       <c r="H1071">
-        <v>0.01324429924330592</v>
+        <v>0.01164390316456926</v>
       </c>
       <c r="I1071">
-        <v>0.1780070208285496</v>
+        <v>0.2979719166858033</v>
       </c>
       <c r="J1071">
         <v>1.355477546349452</v>
       </c>
       <c r="K1071">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1071">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1071">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1071">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1071">
         <v>1</v>
@@ -55408,46 +55408,46 @@
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1072" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C1072">
-        <v>0.6285912057670915</v>
+        <v>0.3378917752338619</v>
       </c>
       <c r="D1072" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1072">
-        <v>0.4757007566940814</v>
+        <v>0.5560968354307416</v>
       </c>
       <c r="F1072">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1072">
-        <v>0.01345140879423291</v>
+        <v>0.01202210822476614</v>
       </c>
       <c r="H1072">
-        <v>0.01324429924330592</v>
+        <v>0.01164390316456926</v>
       </c>
       <c r="I1072">
-        <v>0.1528904490730101</v>
+        <v>0.2182050601968797</v>
       </c>
       <c r="J1072">
         <v>1.355477546349452</v>
       </c>
       <c r="K1072">
-        <v>4.73</v>
+        <v>4.31</v>
       </c>
       <c r="L1072">
-        <v>7.04</v>
+        <v>6.18</v>
       </c>
       <c r="M1072">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1072">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1072">
         <v>1</v>
@@ -55458,46 +55458,46 @@
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1073" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1073">
-        <v>0.2581249187449384</v>
+        <v>0.7365280183101479</v>
       </c>
       <c r="D1073" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1073">
-        <v>0.5560968354307416</v>
+        <v>0.5305490807957955</v>
       </c>
       <c r="F1073">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1073">
-        <v>0.01232187508125506</v>
+        <v>0.01136347198168985</v>
       </c>
       <c r="H1073">
-        <v>0.01164390316456926</v>
+        <v>0.01188945091920421</v>
       </c>
       <c r="I1073">
-        <v>0.2979719166858033</v>
+        <v>0.2059789375143524</v>
       </c>
       <c r="J1073">
         <v>1.355477546349452</v>
       </c>
       <c r="K1073">
-        <v>4.45</v>
+        <v>3.92</v>
       </c>
       <c r="L1073">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="M1073">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="N1073">
-        <v>6.1</v>
+        <v>6.21</v>
       </c>
       <c r="O1073">
         <v>1</v>
@@ -55508,146 +55508,146 @@
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1074" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1074">
-        <v>0.3378917752338619</v>
+        <v>0.6493738814716474</v>
       </c>
       <c r="D1074" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1074">
-        <v>0.5560968354307416</v>
+        <v>0.4714481211940544</v>
       </c>
       <c r="F1074">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1074">
-        <v>0.01202210822476614</v>
+        <v>0.01367062611852835</v>
       </c>
       <c r="H1074">
-        <v>0.01164390316456926</v>
+        <v>0.01324855187880595</v>
       </c>
       <c r="I1074">
-        <v>0.2182050601968797</v>
+        <v>0.177925760277593</v>
       </c>
       <c r="J1074">
-        <v>1.355477546349452</v>
+        <v>1.356380441360074</v>
       </c>
       <c r="K1074">
-        <v>4.31</v>
+        <v>4.8</v>
       </c>
       <c r="L1074">
-        <v>6.18</v>
+        <v>7.16</v>
       </c>
       <c r="M1074">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1074">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1074">
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1075" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C1075">
-        <v>0.7365280183101479</v>
+        <v>0.2541070359476727</v>
       </c>
       <c r="D1075" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E1075">
-        <v>0.5447681826497739</v>
+        <v>0.4803297551148935</v>
       </c>
       <c r="F1075">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1075">
-        <v>0.01136347198168985</v>
+        <v>0.01232589296405233</v>
       </c>
       <c r="H1075">
-        <v>0.01179523181735023</v>
+        <v>0.01181967024488511</v>
       </c>
       <c r="I1075">
-        <v>0.191759835660374</v>
+        <v>0.2262227191672208</v>
       </c>
       <c r="J1075">
-        <v>1.355477546349452</v>
+        <v>1.356380441360074</v>
       </c>
       <c r="K1075">
-        <v>3.92</v>
+        <v>4.45</v>
       </c>
       <c r="L1075">
-        <v>6.05</v>
+        <v>6.29</v>
       </c>
       <c r="M1075">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="N1075">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
       <c r="O1075">
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
       <c r="A1076" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1076" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C1076">
-        <v>0.6493738814716474</v>
+        <v>0.3340002977380836</v>
       </c>
       <c r="D1076" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="E1076">
-        <v>0.4714481211940544</v>
+        <v>0.4803297551148935</v>
       </c>
       <c r="F1076">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1076">
-        <v>0.01367062611852835</v>
+        <v>0.01202599970226192</v>
       </c>
       <c r="H1076">
-        <v>0.01324855187880595</v>
+        <v>0.01181967024488511</v>
       </c>
       <c r="I1076">
-        <v>0.177925760277593</v>
+        <v>0.1463294573768099</v>
       </c>
       <c r="J1076">
         <v>1.356380441360074</v>
       </c>
       <c r="K1076">
-        <v>4.8</v>
+        <v>4.31</v>
       </c>
       <c r="L1076">
-        <v>7.16</v>
+        <v>6.18</v>
       </c>
       <c r="M1076">
-        <v>4.71</v>
+        <v>4.18</v>
       </c>
       <c r="N1076">
-        <v>6.86</v>
+        <v>6.15</v>
       </c>
       <c r="O1076">
         <v>1</v>
@@ -55658,151 +55658,51 @@
     </row>
     <row r="1077" spans="1:16">
       <c r="A1077" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1077" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1077">
-        <v>0.2541070359476727</v>
+        <v>0.7329886698685115</v>
       </c>
       <c r="D1077" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E1077">
-        <v>0.4803297551148935</v>
+        <v>0.5267659507012912</v>
       </c>
       <c r="F1077">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1077">
-        <v>0.01232589296405233</v>
+        <v>0.01136701133013149</v>
       </c>
       <c r="H1077">
-        <v>0.01181967024488511</v>
+        <v>0.01189323404929871</v>
       </c>
       <c r="I1077">
-        <v>0.2262227191672208</v>
+        <v>0.2062227191672203</v>
       </c>
       <c r="J1077">
         <v>1.356380441360074</v>
       </c>
       <c r="K1077">
-        <v>4.45</v>
+        <v>3.92</v>
       </c>
       <c r="L1077">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="M1077">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="N1077">
-        <v>6.15</v>
+        <v>6.21</v>
       </c>
       <c r="O1077">
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="1078" spans="1:16">
-      <c r="A1078" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>201</v>
-      </c>
-      <c r="C1078">
-        <v>0.3340002977380836</v>
-      </c>
-      <c r="D1078" t="s">
-        <v>368</v>
-      </c>
-      <c r="E1078">
-        <v>0.4803297551148935</v>
-      </c>
-      <c r="F1078">
-        <v>1</v>
-      </c>
-      <c r="G1078">
-        <v>0.01202599970226192</v>
-      </c>
-      <c r="H1078">
-        <v>0.01181967024488511</v>
-      </c>
-      <c r="I1078">
-        <v>0.1463294573768099</v>
-      </c>
-      <c r="J1078">
-        <v>1.356380441360074</v>
-      </c>
-      <c r="K1078">
-        <v>4.31</v>
-      </c>
-      <c r="L1078">
-        <v>6.18</v>
-      </c>
-      <c r="M1078">
-        <v>4.18</v>
-      </c>
-      <c r="N1078">
-        <v>6.15</v>
-      </c>
-      <c r="O1078">
-        <v>1</v>
-      </c>
-      <c r="P1078" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="1079" spans="1:16">
-      <c r="A1079" s="1">
-        <v>3</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>208</v>
-      </c>
-      <c r="C1079">
-        <v>0.7329886698685115</v>
-      </c>
-      <c r="D1079" t="s">
-        <v>374</v>
-      </c>
-      <c r="E1079">
-        <v>0.5410211683556945</v>
-      </c>
-      <c r="F1079">
-        <v>-1</v>
-      </c>
-      <c r="G1079">
-        <v>0.01136701133013149</v>
-      </c>
-      <c r="H1079">
-        <v>0.01179897883164431</v>
-      </c>
-      <c r="I1079">
-        <v>0.1919675015128171</v>
-      </c>
-      <c r="J1079">
-        <v>1.356380441360074</v>
-      </c>
-      <c r="K1079">
-        <v>3.92</v>
-      </c>
-      <c r="L1079">
-        <v>6.05</v>
-      </c>
-      <c r="M1079">
-        <v>4.15</v>
-      </c>
-      <c r="N1079">
-        <v>6.17</v>
-      </c>
-      <c r="O1079">
-        <v>1</v>
-      </c>
-      <c r="P1079" t="s">
         <v>207</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="494">
   <si>
     <t>trade_time</t>
   </si>
@@ -1853,7 +1853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1076"/>
+  <dimension ref="A1:P1075"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -54305,63 +54305,63 @@
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1050" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1050">
-        <v>0.3716866247706294</v>
+        <v>0.6963736868234349</v>
       </c>
       <c r="D1050" t="s">
-        <v>368</v>
+        <v>198</v>
       </c>
       <c r="E1050">
-        <v>0.5881666578449822</v>
+        <v>0.5070592712848851</v>
       </c>
       <c r="F1050">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.01198831337522937</v>
+        <v>0.01526362631317657</v>
       </c>
       <c r="H1050">
-        <v>0.01161183334215502</v>
+        <v>0.01321294072871512</v>
       </c>
       <c r="I1050">
-        <v>0.2164800330743528</v>
+        <v>0.1893144155385498</v>
       </c>
       <c r="J1050">
-        <v>1.347636513974332</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1050">
-        <v>4.31</v>
+        <v>5.4</v>
       </c>
       <c r="L1050">
-        <v>6.18</v>
+        <v>7.98</v>
       </c>
       <c r="M1050">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1050">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1050">
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>364</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1051" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C1051">
-        <v>0.6963736868234349</v>
+        <v>0.6986891056461033</v>
       </c>
       <c r="D1051" t="s">
         <v>198</v>
@@ -54373,22 +54373,22 @@
         <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.01526362631317657</v>
+        <v>0.0137013108943539</v>
       </c>
       <c r="H1051">
         <v>0.01321294072871512</v>
       </c>
       <c r="I1051">
-        <v>0.1893144155385498</v>
+        <v>0.1916298343612182</v>
       </c>
       <c r="J1051">
         <v>1.34881968762529</v>
       </c>
       <c r="K1051">
-        <v>5.4</v>
+        <v>4.82</v>
       </c>
       <c r="L1051">
-        <v>7.98</v>
+        <v>7.2</v>
       </c>
       <c r="M1051">
         <v>4.71</v>
@@ -54405,46 +54405,46 @@
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1052" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C1052">
-        <v>0.6986891056461033</v>
+        <v>0.3993822244286784</v>
       </c>
       <c r="D1052" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="E1052">
-        <v>0.5070592712848851</v>
+        <v>0.5833274776125643</v>
       </c>
       <c r="F1052">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1052">
-        <v>0.0137013108943539</v>
+        <v>0.01270061777557132</v>
       </c>
       <c r="H1052">
-        <v>0.01321294072871512</v>
+        <v>0.01161667252238744</v>
       </c>
       <c r="I1052">
-        <v>0.1916298343612182</v>
+        <v>0.1839452531838859</v>
       </c>
       <c r="J1052">
         <v>1.34881968762529</v>
       </c>
       <c r="K1052">
-        <v>4.82</v>
+        <v>4.56</v>
       </c>
       <c r="L1052">
-        <v>7.2</v>
+        <v>6.55</v>
       </c>
       <c r="M1052">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1052">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1052">
         <v>1</v>
@@ -54455,13 +54455,13 @@
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1053" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C1053">
-        <v>0.3993822244286784</v>
+        <v>0.366587146335001</v>
       </c>
       <c r="D1053" t="s">
         <v>368</v>
@@ -54473,22 +54473,22 @@
         <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.01270061777557132</v>
+        <v>0.011993412853665</v>
       </c>
       <c r="H1053">
         <v>0.01161667252238744</v>
       </c>
       <c r="I1053">
-        <v>0.1839452531838859</v>
+        <v>0.2167403312775633</v>
       </c>
       <c r="J1053">
         <v>1.34881968762529</v>
       </c>
       <c r="K1053">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1053">
-        <v>6.55</v>
+        <v>6.18</v>
       </c>
       <c r="M1053">
         <v>4.09</v>
@@ -54505,46 +54505,46 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1054" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C1054">
-        <v>0.366587146335001</v>
+        <v>0.7626268245088639</v>
       </c>
       <c r="D1054" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E1054">
-        <v>0.5833274776125643</v>
+        <v>0.500775996314955</v>
       </c>
       <c r="F1054">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.011993412853665</v>
+        <v>0.01133737317549114</v>
       </c>
       <c r="H1054">
-        <v>0.01161667252238744</v>
+        <v>0.01255922400368505</v>
       </c>
       <c r="I1054">
-        <v>0.2167403312775633</v>
+        <v>0.2618508281939089</v>
       </c>
       <c r="J1054">
         <v>1.34881968762529</v>
       </c>
       <c r="K1054">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1054">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1054">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1054">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54555,63 +54555,63 @@
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1055" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C1055">
-        <v>0.7626268245088639</v>
+        <v>0.685527947714454</v>
       </c>
       <c r="D1055" t="s">
-        <v>373</v>
+        <v>198</v>
       </c>
       <c r="E1055">
-        <v>0.500775996314955</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1055">
         <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.01133737317549114</v>
+        <v>0.01527447205228555</v>
       </c>
       <c r="H1055">
-        <v>0.01255922400368505</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1055">
-        <v>0.2618508281939089</v>
+        <v>0.1879285710968466</v>
       </c>
       <c r="J1055">
-        <v>1.34881968762529</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1055">
-        <v>3.92</v>
+        <v>5.4</v>
       </c>
       <c r="L1055">
-        <v>6.05</v>
+        <v>7.98</v>
       </c>
       <c r="M1055">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1055">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1056" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1056">
-        <v>0.685527947714454</v>
+        <v>0.6760248424128479</v>
       </c>
       <c r="D1056" t="s">
         <v>198</v>
@@ -54623,22 +54623,22 @@
         <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.01527447205228555</v>
+        <v>0.01364397515758715</v>
       </c>
       <c r="H1056">
         <v>0.01322240062338239</v>
       </c>
       <c r="I1056">
-        <v>0.1879285710968466</v>
+        <v>0.1784254657952404</v>
       </c>
       <c r="J1056">
         <v>1.350828157830657</v>
       </c>
       <c r="K1056">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L1056">
-        <v>7.98</v>
+        <v>7.16</v>
       </c>
       <c r="M1056">
         <v>4.71</v>
@@ -54655,46 +54655,46 @@
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1057" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C1057">
-        <v>0.6760248424128479</v>
+        <v>0.3902236002922059</v>
       </c>
       <c r="D1057" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="E1057">
-        <v>0.4975993766176074</v>
+        <v>0.5751128344726144</v>
       </c>
       <c r="F1057">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1057">
-        <v>0.01364397515758715</v>
+        <v>0.01270977639970779</v>
       </c>
       <c r="H1057">
-        <v>0.01322240062338239</v>
+        <v>0.01162488716552739</v>
       </c>
       <c r="I1057">
-        <v>0.1784254657952404</v>
+        <v>0.1848892341804085</v>
       </c>
       <c r="J1057">
         <v>1.350828157830657</v>
       </c>
       <c r="K1057">
-        <v>4.8</v>
+        <v>4.56</v>
       </c>
       <c r="L1057">
-        <v>7.16</v>
+        <v>6.55</v>
       </c>
       <c r="M1057">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1057">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -54705,13 +54705,13 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1058" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C1058">
-        <v>0.3847815713403513</v>
+        <v>0.3579306397498696</v>
       </c>
       <c r="D1058" t="s">
         <v>368</v>
@@ -54723,22 +54723,22 @@
         <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.01251521842865965</v>
+        <v>0.01200206936025013</v>
       </c>
       <c r="H1058">
         <v>0.01162488716552739</v>
       </c>
       <c r="I1058">
-        <v>0.1903312631322631</v>
+        <v>0.2171821947227448</v>
       </c>
       <c r="J1058">
         <v>1.350828157830657</v>
       </c>
       <c r="K1058">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="L1058">
-        <v>6.45</v>
+        <v>6.18</v>
       </c>
       <c r="M1058">
         <v>4.09</v>
@@ -54755,46 +54755,46 @@
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1059" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C1059">
-        <v>0.3579306397498696</v>
+        <v>0.7547536213038253</v>
       </c>
       <c r="D1059" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E1059">
-        <v>0.5751128344726144</v>
+        <v>0.4917981344969649</v>
       </c>
       <c r="F1059">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.01200206936025013</v>
+        <v>0.01134524637869617</v>
       </c>
       <c r="H1059">
-        <v>0.01162488716552739</v>
+        <v>0.01256820186550303</v>
       </c>
       <c r="I1059">
-        <v>0.2171821947227448</v>
+        <v>0.2629554868068604</v>
       </c>
       <c r="J1059">
         <v>1.350828157830657</v>
       </c>
       <c r="K1059">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1059">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1059">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1059">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1059">
         <v>1</v>
@@ -54805,96 +54805,96 @@
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1060" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C1060">
-        <v>0.7547536213038253</v>
+        <v>0.6767185447573851</v>
       </c>
       <c r="D1060" t="s">
-        <v>373</v>
+        <v>198</v>
       </c>
       <c r="E1060">
-        <v>0.4917981344969649</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1060">
         <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.01134524637869617</v>
+        <v>0.01364328145524261</v>
       </c>
       <c r="H1060">
-        <v>0.01256820186550303</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1060">
-        <v>0.2629554868068604</v>
+        <v>0.178438472714201</v>
       </c>
       <c r="J1060">
-        <v>1.350828157830657</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1060">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1060">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1060">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1060">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1060">
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1061" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1061">
-        <v>0.6767185447573851</v>
+        <v>0.3854304720751367</v>
       </c>
       <c r="D1061" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="E1061">
-        <v>0.4982800720431841</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1061">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1061">
-        <v>0.01364328145524261</v>
+        <v>0.01251456952792486</v>
       </c>
       <c r="H1061">
-        <v>0.01322171992795682</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1061">
-        <v>0.178438472714201</v>
+        <v>0.1902734546035516</v>
       </c>
       <c r="J1061">
         <v>1.350683636508878</v>
       </c>
       <c r="K1061">
-        <v>4.8</v>
+        <v>4.49</v>
       </c>
       <c r="L1061">
-        <v>7.16</v>
+        <v>6.45</v>
       </c>
       <c r="M1061">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1061">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1061">
         <v>1</v>
@@ -54905,13 +54905,13 @@
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1062" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C1062">
-        <v>0.3854304720751367</v>
+        <v>0.3585535266467357</v>
       </c>
       <c r="D1062" t="s">
         <v>368</v>
@@ -54923,22 +54923,22 @@
         <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.01251456952792486</v>
+        <v>0.01200144647335326</v>
       </c>
       <c r="H1062">
         <v>0.01162429607332131</v>
       </c>
       <c r="I1062">
-        <v>0.1902734546035516</v>
+        <v>0.2171504000319526</v>
       </c>
       <c r="J1062">
         <v>1.350683636508878</v>
       </c>
       <c r="K1062">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="L1062">
-        <v>6.45</v>
+        <v>6.18</v>
       </c>
       <c r="M1062">
         <v>4.09</v>
@@ -54955,46 +54955,46 @@
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1063" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C1063">
-        <v>0.3585535266467357</v>
+        <v>0.7553201448851974</v>
       </c>
       <c r="D1063" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E1063">
-        <v>0.5757039266786883</v>
+        <v>0.4924441448053152</v>
       </c>
       <c r="F1063">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1063">
-        <v>0.01200144647335326</v>
+        <v>0.0113446798551148</v>
       </c>
       <c r="H1063">
-        <v>0.01162429607332131</v>
+        <v>0.01256755585519469</v>
       </c>
       <c r="I1063">
-        <v>0.2171504000319526</v>
+        <v>0.2628760000798822</v>
       </c>
       <c r="J1063">
         <v>1.350683636508878</v>
       </c>
       <c r="K1063">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1063">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1063">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1063">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1063">
         <v>1</v>
@@ -55005,96 +55005,96 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1064" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C1064">
-        <v>0.7553201448851974</v>
+        <v>0.6674364420145809</v>
       </c>
       <c r="D1064" t="s">
-        <v>373</v>
+        <v>198</v>
       </c>
       <c r="E1064">
-        <v>0.4924441448053152</v>
+        <v>0.4891720087268077</v>
       </c>
       <c r="F1064">
         <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.0113446798551148</v>
+        <v>0.01365256355798542</v>
       </c>
       <c r="H1064">
-        <v>0.01256755585519469</v>
+        <v>0.01323082799127319</v>
       </c>
       <c r="I1064">
-        <v>0.2628760000798822</v>
+        <v>0.1782644332877732</v>
       </c>
       <c r="J1064">
-        <v>1.350683636508878</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1064">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1064">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1064">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1064">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1065" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C1065">
-        <v>0.6674364420145809</v>
+        <v>0.2708525347843507</v>
       </c>
       <c r="D1065" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="E1065">
-        <v>0.4891720087268077</v>
+        <v>0.5677948016332568</v>
       </c>
       <c r="F1065">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1065">
-        <v>0.01365256355798542</v>
+        <v>0.01230914746521565</v>
       </c>
       <c r="H1065">
-        <v>0.01323082799127319</v>
+        <v>0.01163220519836674</v>
       </c>
       <c r="I1065">
-        <v>0.1782644332877732</v>
+        <v>0.2969422668489061</v>
       </c>
       <c r="J1065">
         <v>1.352617407913629</v>
       </c>
       <c r="K1065">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1065">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1065">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1065">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1065">
         <v>1</v>
@@ -55105,13 +55105,13 @@
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1066" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C1066">
-        <v>0.2708525347843507</v>
+        <v>0.350218971892259</v>
       </c>
       <c r="D1066" t="s">
         <v>368</v>
@@ -55123,22 +55123,22 @@
         <v>1</v>
       </c>
       <c r="G1066">
-        <v>0.01230914746521565</v>
+        <v>0.01200978102810774</v>
       </c>
       <c r="H1066">
         <v>0.01163220519836674</v>
       </c>
       <c r="I1066">
-        <v>0.2969422668489061</v>
+        <v>0.2175758297409978</v>
       </c>
       <c r="J1066">
         <v>1.352617407913629</v>
       </c>
       <c r="K1066">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1066">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1066">
         <v>4.09</v>
@@ -55155,46 +55155,46 @@
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1067" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C1067">
-        <v>0.350218971892259</v>
+        <v>0.7477397609785736</v>
       </c>
       <c r="D1067" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E1067">
-        <v>0.5677948016332568</v>
+        <v>0.4838001866260786</v>
       </c>
       <c r="F1067">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.01200978102810774</v>
+        <v>0.01135226023902143</v>
       </c>
       <c r="H1067">
-        <v>0.01163220519836674</v>
+        <v>0.01257619981337392</v>
       </c>
       <c r="I1067">
-        <v>0.2175758297409978</v>
+        <v>0.263939574352495</v>
       </c>
       <c r="J1067">
         <v>1.352617407913629</v>
       </c>
       <c r="K1067">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1067">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1067">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1067">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1067">
         <v>1</v>
@@ -55205,96 +55205,96 @@
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1068" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C1068">
-        <v>0.7477397609785736</v>
+        <v>0.653707777522631</v>
       </c>
       <c r="D1068" t="s">
-        <v>373</v>
+        <v>198</v>
       </c>
       <c r="E1068">
-        <v>0.4838001866260786</v>
+        <v>0.4757007566940814</v>
       </c>
       <c r="F1068">
         <v>-1</v>
       </c>
       <c r="G1068">
-        <v>0.01135226023902143</v>
+        <v>0.01366629222247737</v>
       </c>
       <c r="H1068">
-        <v>0.01257619981337392</v>
+        <v>0.01324429924330592</v>
       </c>
       <c r="I1068">
-        <v>0.263939574352495</v>
+        <v>0.1780070208285496</v>
       </c>
       <c r="J1068">
-        <v>1.352617407913629</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1068">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1068">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1068">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1068">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1068">
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1069" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C1069">
-        <v>0.653707777522631</v>
+        <v>0.2581249187449384</v>
       </c>
       <c r="D1069" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="E1069">
-        <v>0.4757007566940814</v>
+        <v>0.5560968354307416</v>
       </c>
       <c r="F1069">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1069">
-        <v>0.01366629222247737</v>
+        <v>0.01232187508125506</v>
       </c>
       <c r="H1069">
-        <v>0.01324429924330592</v>
+        <v>0.01164390316456926</v>
       </c>
       <c r="I1069">
-        <v>0.1780070208285496</v>
+        <v>0.2979719166858033</v>
       </c>
       <c r="J1069">
         <v>1.355477546349452</v>
       </c>
       <c r="K1069">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1069">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1069">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1069">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1069">
         <v>1</v>
@@ -55305,13 +55305,13 @@
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1070" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C1070">
-        <v>0.2581249187449384</v>
+        <v>0.3378917752338619</v>
       </c>
       <c r="D1070" t="s">
         <v>368</v>
@@ -55323,22 +55323,22 @@
         <v>1</v>
       </c>
       <c r="G1070">
-        <v>0.01232187508125506</v>
+        <v>0.01202210822476614</v>
       </c>
       <c r="H1070">
         <v>0.01164390316456926</v>
       </c>
       <c r="I1070">
-        <v>0.2979719166858033</v>
+        <v>0.2182050601968797</v>
       </c>
       <c r="J1070">
         <v>1.355477546349452</v>
       </c>
       <c r="K1070">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1070">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1070">
         <v>4.09</v>
@@ -55355,46 +55355,46 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1071" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C1071">
-        <v>0.3378917752338619</v>
+        <v>0.7365280183101479</v>
       </c>
       <c r="D1071" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E1071">
-        <v>0.5560968354307416</v>
+        <v>0.4710153678179507</v>
       </c>
       <c r="F1071">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.01202210822476614</v>
+        <v>0.01136347198168985</v>
       </c>
       <c r="H1071">
-        <v>0.01164390316456926</v>
+        <v>0.01258898463218205</v>
       </c>
       <c r="I1071">
-        <v>0.2182050601968797</v>
+        <v>0.2655126504921972</v>
       </c>
       <c r="J1071">
         <v>1.355477546349452</v>
       </c>
       <c r="K1071">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1071">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1071">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1071">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1071">
         <v>1</v>
@@ -55405,96 +55405,96 @@
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1072" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C1072">
-        <v>0.7365280183101479</v>
+        <v>0.6493738814716474</v>
       </c>
       <c r="D1072" t="s">
-        <v>373</v>
+        <v>198</v>
       </c>
       <c r="E1072">
-        <v>0.4710153678179507</v>
+        <v>0.4714481211940544</v>
       </c>
       <c r="F1072">
         <v>-1</v>
       </c>
       <c r="G1072">
-        <v>0.01136347198168985</v>
+        <v>0.01367062611852835</v>
       </c>
       <c r="H1072">
-        <v>0.01258898463218205</v>
+        <v>0.01324855187880595</v>
       </c>
       <c r="I1072">
-        <v>0.2655126504921972</v>
+        <v>0.177925760277593</v>
       </c>
       <c r="J1072">
-        <v>1.355477546349452</v>
+        <v>1.356380441360074</v>
       </c>
       <c r="K1072">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1072">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1072">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1072">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1072">
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1073" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C1073">
-        <v>0.6493738814716474</v>
+        <v>0.2541070359476727</v>
       </c>
       <c r="D1073" t="s">
-        <v>198</v>
+        <v>367</v>
       </c>
       <c r="E1073">
-        <v>0.4714481211940544</v>
+        <v>0.4803297551148935</v>
       </c>
       <c r="F1073">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1073">
-        <v>0.01367062611852835</v>
+        <v>0.01232589296405233</v>
       </c>
       <c r="H1073">
-        <v>0.01324855187880595</v>
+        <v>0.01181967024488511</v>
       </c>
       <c r="I1073">
-        <v>0.177925760277593</v>
+        <v>0.2262227191672208</v>
       </c>
       <c r="J1073">
         <v>1.356380441360074</v>
       </c>
       <c r="K1073">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1073">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1073">
-        <v>4.71</v>
+        <v>4.18</v>
       </c>
       <c r="N1073">
-        <v>6.86</v>
+        <v>6.15</v>
       </c>
       <c r="O1073">
         <v>1</v>
@@ -55505,13 +55505,13 @@
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1074" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C1074">
-        <v>0.2541070359476727</v>
+        <v>0.3340002977380836</v>
       </c>
       <c r="D1074" t="s">
         <v>367</v>
@@ -55523,22 +55523,22 @@
         <v>1</v>
       </c>
       <c r="G1074">
-        <v>0.01232589296405233</v>
+        <v>0.01202599970226192</v>
       </c>
       <c r="H1074">
         <v>0.01181967024488511</v>
       </c>
       <c r="I1074">
-        <v>0.2262227191672208</v>
+        <v>0.1463294573768099</v>
       </c>
       <c r="J1074">
         <v>1.356380441360074</v>
       </c>
       <c r="K1074">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1074">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1074">
         <v>4.18</v>
@@ -55555,101 +55555,51 @@
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1075" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C1075">
-        <v>0.3340002977380836</v>
+        <v>0.7329886698685115</v>
       </c>
       <c r="D1075" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E1075">
-        <v>0.4803297551148935</v>
+        <v>0.4669794271204717</v>
       </c>
       <c r="F1075">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1075">
-        <v>0.01202599970226192</v>
+        <v>0.01136701133013149</v>
       </c>
       <c r="H1075">
-        <v>0.01181967024488511</v>
+        <v>0.01259302057287953</v>
       </c>
       <c r="I1075">
-        <v>0.1463294573768099</v>
+        <v>0.2660092427480398</v>
       </c>
       <c r="J1075">
         <v>1.356380441360074</v>
       </c>
       <c r="K1075">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1075">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1075">
-        <v>4.18</v>
+        <v>4.47</v>
       </c>
       <c r="N1075">
-        <v>6.15</v>
+        <v>6.53</v>
       </c>
       <c r="O1075">
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="1076" spans="1:16">
-      <c r="A1076" s="1">
-        <v>3</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>208</v>
-      </c>
-      <c r="C1076">
-        <v>0.7329886698685115</v>
-      </c>
-      <c r="D1076" t="s">
-        <v>373</v>
-      </c>
-      <c r="E1076">
-        <v>0.4669794271204717</v>
-      </c>
-      <c r="F1076">
-        <v>-1</v>
-      </c>
-      <c r="G1076">
-        <v>0.01136701133013149</v>
-      </c>
-      <c r="H1076">
-        <v>0.01259302057287953</v>
-      </c>
-      <c r="I1076">
-        <v>0.2660092427480398</v>
-      </c>
-      <c r="J1076">
-        <v>1.356380441360074</v>
-      </c>
-      <c r="K1076">
-        <v>3.92</v>
-      </c>
-      <c r="L1076">
-        <v>6.05</v>
-      </c>
-      <c r="M1076">
-        <v>4.47</v>
-      </c>
-      <c r="N1076">
-        <v>6.53</v>
-      </c>
-      <c r="O1076">
-        <v>1</v>
-      </c>
-      <c r="P1076" t="s">
         <v>207</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="495">
   <si>
     <t>trade_time</t>
   </si>
@@ -1856,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1079"/>
+  <dimension ref="A1:P1078"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -54261,10 +54261,10 @@
         <v>2</v>
       </c>
       <c r="B1049" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C1049">
-        <v>0.4047774962770463</v>
+        <v>0.3991120522552487</v>
       </c>
       <c r="D1049" t="s">
         <v>369</v>
@@ -54276,22 +54276,22 @@
         <v>1</v>
       </c>
       <c r="G1049">
-        <v>0.01269522250372295</v>
+        <v>0.01250088794774475</v>
       </c>
       <c r="H1049">
         <v>0.01161183334215502</v>
       </c>
       <c r="I1049">
-        <v>0.1833891615679359</v>
+        <v>0.1890546055897335</v>
       </c>
       <c r="J1049">
         <v>1.347636513974332</v>
       </c>
       <c r="K1049">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="L1049">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="M1049">
         <v>4.09</v>
@@ -54561,10 +54561,10 @@
         <v>3</v>
       </c>
       <c r="B1055" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C1055">
-        <v>0.3937996025624484</v>
+        <v>0.2877523900674603</v>
       </c>
       <c r="D1055" t="s">
         <v>369</v>
@@ -54576,22 +54576,22 @@
         <v>1</v>
       </c>
       <c r="G1055">
-        <v>0.01250620039743755</v>
+        <v>0.01229224760993254</v>
       </c>
       <c r="H1055">
         <v>0.01161667252238744</v>
       </c>
       <c r="I1055">
-        <v>0.1895278750501159</v>
+        <v>0.295575087545104</v>
       </c>
       <c r="J1055">
         <v>1.34881968762529</v>
       </c>
       <c r="K1055">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="L1055">
-        <v>6.45</v>
+        <v>6.29</v>
       </c>
       <c r="M1055">
         <v>4.09</v>
@@ -54711,10 +54711,10 @@
         <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C1058">
-        <v>0.685527947714454</v>
+        <v>0.6760248424128479</v>
       </c>
       <c r="D1058" t="s">
         <v>198</v>
@@ -54726,22 +54726,22 @@
         <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.01527447205228555</v>
+        <v>0.01364397515758715</v>
       </c>
       <c r="H1058">
         <v>0.01322240062338239</v>
       </c>
       <c r="I1058">
-        <v>0.1879285710968466</v>
+        <v>0.1784254657952404</v>
       </c>
       <c r="J1058">
         <v>1.350828157830657</v>
       </c>
       <c r="K1058">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L1058">
-        <v>7.98</v>
+        <v>7.16</v>
       </c>
       <c r="M1058">
         <v>4.71</v>
@@ -54761,43 +54761,43 @@
         <v>1</v>
       </c>
       <c r="B1059" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1059">
-        <v>0.6760248424128479</v>
+        <v>0.2788146976535772</v>
       </c>
       <c r="D1059" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1059">
-        <v>0.4975993766176074</v>
+        <v>0.5751128344726144</v>
       </c>
       <c r="F1059">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1059">
-        <v>0.01364397515758715</v>
+        <v>0.01230118530234642</v>
       </c>
       <c r="H1059">
-        <v>0.01322240062338239</v>
+        <v>0.01162488716552739</v>
       </c>
       <c r="I1059">
-        <v>0.1784254657952404</v>
+        <v>0.2962981368190372</v>
       </c>
       <c r="J1059">
         <v>1.350828157830657</v>
       </c>
       <c r="K1059">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1059">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1059">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1059">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1059">
         <v>1</v>
@@ -54811,10 +54811,10 @@
         <v>2</v>
       </c>
       <c r="B1060" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C1060">
-        <v>0.3847815713403513</v>
+        <v>0.3579306397498696</v>
       </c>
       <c r="D1060" t="s">
         <v>369</v>
@@ -54826,22 +54826,22 @@
         <v>1</v>
       </c>
       <c r="G1060">
-        <v>0.01251521842865965</v>
+        <v>0.01200206936025013</v>
       </c>
       <c r="H1060">
         <v>0.01162488716552739</v>
       </c>
       <c r="I1060">
-        <v>0.1903312631322631</v>
+        <v>0.2171821947227448</v>
       </c>
       <c r="J1060">
         <v>1.350828157830657</v>
       </c>
       <c r="K1060">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="L1060">
-        <v>6.45</v>
+        <v>6.18</v>
       </c>
       <c r="M1060">
         <v>4.09</v>
@@ -54861,43 +54861,43 @@
         <v>3</v>
       </c>
       <c r="B1061" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1061">
-        <v>0.3579306397498696</v>
+        <v>0.7547536213038253</v>
       </c>
       <c r="D1061" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1061">
-        <v>0.5751128344726144</v>
+        <v>0.4917981344969649</v>
       </c>
       <c r="F1061">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.01200206936025013</v>
+        <v>0.01134524637869617</v>
       </c>
       <c r="H1061">
-        <v>0.01162488716552739</v>
+        <v>0.01256820186550303</v>
       </c>
       <c r="I1061">
-        <v>0.2171821947227448</v>
+        <v>0.2629554868068604</v>
       </c>
       <c r="J1061">
         <v>1.350828157830657</v>
       </c>
       <c r="K1061">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1061">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1061">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1061">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1061">
         <v>1</v>
@@ -54908,96 +54908,96 @@
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1062" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1062">
-        <v>0.7547536213038253</v>
+        <v>0.6767185447573851</v>
       </c>
       <c r="D1062" t="s">
-        <v>374</v>
+        <v>198</v>
       </c>
       <c r="E1062">
-        <v>0.4917981344969649</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1062">
         <v>-1</v>
       </c>
       <c r="G1062">
-        <v>0.01134524637869617</v>
+        <v>0.01364328145524261</v>
       </c>
       <c r="H1062">
-        <v>0.01256820186550303</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1062">
-        <v>0.2629554868068604</v>
+        <v>0.178438472714201</v>
       </c>
       <c r="J1062">
-        <v>1.350828157830657</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1062">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1062">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1062">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1062">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1062">
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1063" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1063">
-        <v>0.6767185447573851</v>
+        <v>0.2794578175354925</v>
       </c>
       <c r="D1063" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1063">
-        <v>0.4982800720431841</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1063">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1063">
-        <v>0.01364328145524261</v>
+        <v>0.01230054218246451</v>
       </c>
       <c r="H1063">
-        <v>0.01322171992795682</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1063">
-        <v>0.178438472714201</v>
+        <v>0.2962461091431958</v>
       </c>
       <c r="J1063">
         <v>1.350683636508878</v>
       </c>
       <c r="K1063">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1063">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1063">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1063">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1063">
         <v>1</v>
@@ -55008,13 +55008,13 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1064" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1064">
-        <v>0.2794578175354925</v>
+        <v>0.3585535266467357</v>
       </c>
       <c r="D1064" t="s">
         <v>369</v>
@@ -55026,22 +55026,22 @@
         <v>1</v>
       </c>
       <c r="G1064">
-        <v>0.01230054218246451</v>
+        <v>0.01200144647335326</v>
       </c>
       <c r="H1064">
         <v>0.01162429607332131</v>
       </c>
       <c r="I1064">
-        <v>0.2962461091431958</v>
+        <v>0.2171504000319526</v>
       </c>
       <c r="J1064">
         <v>1.350683636508878</v>
       </c>
       <c r="K1064">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1064">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1064">
         <v>4.09</v>
@@ -55058,46 +55058,46 @@
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1065" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1065">
-        <v>0.3585535266467357</v>
+        <v>0.7553201448851974</v>
       </c>
       <c r="D1065" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1065">
-        <v>0.5757039266786883</v>
+        <v>0.4924441448053152</v>
       </c>
       <c r="F1065">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.01200144647335326</v>
+        <v>0.0113446798551148</v>
       </c>
       <c r="H1065">
-        <v>0.01162429607332131</v>
+        <v>0.01256755585519469</v>
       </c>
       <c r="I1065">
-        <v>0.2171504000319526</v>
+        <v>0.2628760000798822</v>
       </c>
       <c r="J1065">
         <v>1.350683636508878</v>
       </c>
       <c r="K1065">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1065">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1065">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1065">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1065">
         <v>1</v>
@@ -55108,63 +55108,63 @@
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1066" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1066">
-        <v>0.7553201448851974</v>
+        <v>0.6674364420145809</v>
       </c>
       <c r="D1066" t="s">
-        <v>374</v>
+        <v>198</v>
       </c>
       <c r="E1066">
-        <v>0.4924441448053152</v>
+        <v>0.4891720087268077</v>
       </c>
       <c r="F1066">
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.0113446798551148</v>
+        <v>0.01365256355798542</v>
       </c>
       <c r="H1066">
-        <v>0.01256755585519469</v>
+        <v>0.01323082799127319</v>
       </c>
       <c r="I1066">
-        <v>0.2628760000798822</v>
+        <v>0.1782644332877732</v>
       </c>
       <c r="J1066">
-        <v>1.350683636508878</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1066">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1066">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1066">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1066">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1066">
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1067" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1067">
-        <v>0.6674364420145809</v>
+        <v>0.6421196605685342</v>
       </c>
       <c r="D1067" t="s">
         <v>198</v>
@@ -55176,22 +55176,22 @@
         <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.01365256355798542</v>
+        <v>0.01343788033943147</v>
       </c>
       <c r="H1067">
         <v>0.01323082799127319</v>
       </c>
       <c r="I1067">
-        <v>0.1782644332877732</v>
+        <v>0.1529476518417265</v>
       </c>
       <c r="J1067">
         <v>1.352617407913629</v>
       </c>
       <c r="K1067">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="L1067">
-        <v>7.16</v>
+        <v>7.04</v>
       </c>
       <c r="M1067">
         <v>4.71</v>
@@ -55208,46 +55208,46 @@
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1068" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C1068">
-        <v>0.6421196605685342</v>
+        <v>0.2708525347843507</v>
       </c>
       <c r="D1068" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1068">
-        <v>0.4891720087268077</v>
+        <v>0.5677948016332568</v>
       </c>
       <c r="F1068">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1068">
-        <v>0.01343788033943147</v>
+        <v>0.01230914746521565</v>
       </c>
       <c r="H1068">
-        <v>0.01323082799127319</v>
+        <v>0.01163220519836674</v>
       </c>
       <c r="I1068">
-        <v>0.1529476518417265</v>
+        <v>0.2969422668489061</v>
       </c>
       <c r="J1068">
         <v>1.352617407913629</v>
       </c>
       <c r="K1068">
-        <v>4.73</v>
+        <v>4.45</v>
       </c>
       <c r="L1068">
-        <v>7.04</v>
+        <v>6.29</v>
       </c>
       <c r="M1068">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1068">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1068">
         <v>1</v>
@@ -55258,13 +55258,13 @@
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1069" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1069">
-        <v>0.2708525347843507</v>
+        <v>0.350218971892259</v>
       </c>
       <c r="D1069" t="s">
         <v>369</v>
@@ -55276,22 +55276,22 @@
         <v>1</v>
       </c>
       <c r="G1069">
-        <v>0.01230914746521565</v>
+        <v>0.01200978102810774</v>
       </c>
       <c r="H1069">
         <v>0.01163220519836674</v>
       </c>
       <c r="I1069">
-        <v>0.2969422668489061</v>
+        <v>0.2175758297409978</v>
       </c>
       <c r="J1069">
         <v>1.352617407913629</v>
       </c>
       <c r="K1069">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1069">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1069">
         <v>4.09</v>
@@ -55308,46 +55308,46 @@
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1070" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1070">
-        <v>0.350218971892259</v>
+        <v>0.7477397609785736</v>
       </c>
       <c r="D1070" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1070">
-        <v>0.5677948016332568</v>
+        <v>0.4838001866260786</v>
       </c>
       <c r="F1070">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.01200978102810774</v>
+        <v>0.01135226023902143</v>
       </c>
       <c r="H1070">
-        <v>0.01163220519836674</v>
+        <v>0.01257619981337392</v>
       </c>
       <c r="I1070">
-        <v>0.2175758297409978</v>
+        <v>0.263939574352495</v>
       </c>
       <c r="J1070">
         <v>1.352617407913629</v>
       </c>
       <c r="K1070">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1070">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1070">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1070">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55358,96 +55358,96 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1071" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1071">
-        <v>0.7477397609785736</v>
+        <v>0.653707777522631</v>
       </c>
       <c r="D1071" t="s">
-        <v>374</v>
+        <v>198</v>
       </c>
       <c r="E1071">
-        <v>0.4838001866260786</v>
+        <v>0.4757007566940814</v>
       </c>
       <c r="F1071">
         <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.01135226023902143</v>
+        <v>0.01366629222247737</v>
       </c>
       <c r="H1071">
-        <v>0.01257619981337392</v>
+        <v>0.01324429924330592</v>
       </c>
       <c r="I1071">
-        <v>0.263939574352495</v>
+        <v>0.1780070208285496</v>
       </c>
       <c r="J1071">
-        <v>1.352617407913629</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1071">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1071">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1071">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1071">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1071">
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1072" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1072">
-        <v>0.653707777522631</v>
+        <v>0.2581249187449384</v>
       </c>
       <c r="D1072" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="E1072">
-        <v>0.4757007566940814</v>
+        <v>0.4841038562592912</v>
       </c>
       <c r="F1072">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1072">
-        <v>0.01366629222247737</v>
+        <v>0.01232187508125506</v>
       </c>
       <c r="H1072">
-        <v>0.01324429924330592</v>
+        <v>0.01181589614374071</v>
       </c>
       <c r="I1072">
-        <v>0.1780070208285496</v>
+        <v>0.2259789375143528</v>
       </c>
       <c r="J1072">
         <v>1.355477546349452</v>
       </c>
       <c r="K1072">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1072">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1072">
-        <v>4.71</v>
+        <v>4.18</v>
       </c>
       <c r="N1072">
-        <v>6.86</v>
+        <v>6.15</v>
       </c>
       <c r="O1072">
         <v>1</v>
@@ -55458,46 +55458,46 @@
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1073" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1073">
-        <v>0.2581249187449384</v>
+        <v>0.3378917752338619</v>
       </c>
       <c r="D1073" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E1073">
-        <v>0.5560968354307416</v>
+        <v>0.4841038562592912</v>
       </c>
       <c r="F1073">
         <v>1</v>
       </c>
       <c r="G1073">
-        <v>0.01232187508125506</v>
+        <v>0.01202210822476614</v>
       </c>
       <c r="H1073">
-        <v>0.01164390316456926</v>
+        <v>0.01181589614374071</v>
       </c>
       <c r="I1073">
-        <v>0.2979719166858033</v>
+        <v>0.1462120810254293</v>
       </c>
       <c r="J1073">
         <v>1.355477546349452</v>
       </c>
       <c r="K1073">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1073">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1073">
-        <v>4.09</v>
+        <v>4.18</v>
       </c>
       <c r="N1073">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="O1073">
         <v>1</v>
@@ -55508,46 +55508,46 @@
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1074" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1074">
-        <v>0.3378917752338619</v>
+        <v>0.7365280183101479</v>
       </c>
       <c r="D1074" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1074">
-        <v>0.5560968354307416</v>
+        <v>0.4710153678179507</v>
       </c>
       <c r="F1074">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1074">
-        <v>0.01202210822476614</v>
+        <v>0.01136347198168985</v>
       </c>
       <c r="H1074">
-        <v>0.01164390316456926</v>
+        <v>0.01258898463218205</v>
       </c>
       <c r="I1074">
-        <v>0.2182050601968797</v>
+        <v>0.2655126504921972</v>
       </c>
       <c r="J1074">
         <v>1.355477546349452</v>
       </c>
       <c r="K1074">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1074">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1074">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1074">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1074">
         <v>1</v>
@@ -55558,96 +55558,96 @@
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1075" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1075">
-        <v>0.7365280183101479</v>
+        <v>0.6493738814716474</v>
       </c>
       <c r="D1075" t="s">
-        <v>374</v>
+        <v>199</v>
       </c>
       <c r="E1075">
-        <v>0.4710153678179507</v>
+        <v>0.3998518182932695</v>
       </c>
       <c r="F1075">
         <v>-1</v>
       </c>
       <c r="G1075">
-        <v>0.01136347198168985</v>
+        <v>0.01367062611852835</v>
       </c>
       <c r="H1075">
-        <v>0.01258898463218205</v>
+        <v>0.01258014818170673</v>
       </c>
       <c r="I1075">
-        <v>0.2655126504921972</v>
+        <v>0.2495220631783779</v>
       </c>
       <c r="J1075">
-        <v>1.355477546349452</v>
+        <v>1.356380441360074</v>
       </c>
       <c r="K1075">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="L1075">
-        <v>6.05</v>
+        <v>7.16</v>
       </c>
       <c r="M1075">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="N1075">
-        <v>6.53</v>
+        <v>6.49</v>
       </c>
       <c r="O1075">
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
       <c r="A1076" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1076" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1076">
-        <v>0.6493738814716474</v>
+        <v>0.2541070359476727</v>
       </c>
       <c r="D1076" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="E1076">
-        <v>0.4714481211940544</v>
+        <v>0.4803297551148935</v>
       </c>
       <c r="F1076">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1076">
-        <v>0.01367062611852835</v>
+        <v>0.01232589296405233</v>
       </c>
       <c r="H1076">
-        <v>0.01324855187880595</v>
+        <v>0.01181967024488511</v>
       </c>
       <c r="I1076">
-        <v>0.177925760277593</v>
+        <v>0.2262227191672208</v>
       </c>
       <c r="J1076">
         <v>1.356380441360074</v>
       </c>
       <c r="K1076">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1076">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1076">
-        <v>4.71</v>
+        <v>4.18</v>
       </c>
       <c r="N1076">
-        <v>6.86</v>
+        <v>6.15</v>
       </c>
       <c r="O1076">
         <v>1</v>
@@ -55658,13 +55658,13 @@
     </row>
     <row r="1077" spans="1:16">
       <c r="A1077" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1077" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1077">
-        <v>0.2541070359476727</v>
+        <v>0.3340002977380836</v>
       </c>
       <c r="D1077" t="s">
         <v>368</v>
@@ -55676,22 +55676,22 @@
         <v>1</v>
       </c>
       <c r="G1077">
-        <v>0.01232589296405233</v>
+        <v>0.01202599970226192</v>
       </c>
       <c r="H1077">
         <v>0.01181967024488511</v>
       </c>
       <c r="I1077">
-        <v>0.2262227191672208</v>
+        <v>0.1463294573768099</v>
       </c>
       <c r="J1077">
         <v>1.356380441360074</v>
       </c>
       <c r="K1077">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1077">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1077">
         <v>4.18</v>
@@ -55708,101 +55708,51 @@
     </row>
     <row r="1078" spans="1:16">
       <c r="A1078" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1078" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1078">
-        <v>0.3340002977380836</v>
+        <v>0.7329886698685115</v>
       </c>
       <c r="D1078" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E1078">
-        <v>0.4803297551148935</v>
+        <v>0.4669794271204717</v>
       </c>
       <c r="F1078">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1078">
-        <v>0.01202599970226192</v>
+        <v>0.01136701133013149</v>
       </c>
       <c r="H1078">
-        <v>0.01181967024488511</v>
+        <v>0.01259302057287953</v>
       </c>
       <c r="I1078">
-        <v>0.1463294573768099</v>
+        <v>0.2660092427480398</v>
       </c>
       <c r="J1078">
         <v>1.356380441360074</v>
       </c>
       <c r="K1078">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1078">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1078">
-        <v>4.18</v>
+        <v>4.47</v>
       </c>
       <c r="N1078">
-        <v>6.15</v>
+        <v>6.53</v>
       </c>
       <c r="O1078">
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="1079" spans="1:16">
-      <c r="A1079" s="1">
-        <v>3</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>209</v>
-      </c>
-      <c r="C1079">
-        <v>0.7329886698685115</v>
-      </c>
-      <c r="D1079" t="s">
-        <v>374</v>
-      </c>
-      <c r="E1079">
-        <v>0.4669794271204717</v>
-      </c>
-      <c r="F1079">
-        <v>-1</v>
-      </c>
-      <c r="G1079">
-        <v>0.01136701133013149</v>
-      </c>
-      <c r="H1079">
-        <v>0.01259302057287953</v>
-      </c>
-      <c r="I1079">
-        <v>0.2660092427480398</v>
-      </c>
-      <c r="J1079">
-        <v>1.356380441360074</v>
-      </c>
-      <c r="K1079">
-        <v>3.92</v>
-      </c>
-      <c r="L1079">
-        <v>6.05</v>
-      </c>
-      <c r="M1079">
-        <v>4.47</v>
-      </c>
-      <c r="N1079">
-        <v>6.53</v>
-      </c>
-      <c r="O1079">
-        <v>1</v>
-      </c>
-      <c r="P1079" t="s">
         <v>208</v>
       </c>
     </row>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="498">
   <si>
     <t>trade_time</t>
   </si>
@@ -637,16 +637,16 @@
     <t>2021-11-10</t>
   </si>
   <si>
+    <t>2021-12-09</t>
+  </si>
+  <si>
     <t>2021-10-25</t>
   </si>
   <si>
-    <t>2021-10-28</t>
+    <t>2021-11-01</t>
   </si>
   <si>
     <t>2021-11-30</t>
-  </si>
-  <si>
-    <t>2021-11-01</t>
   </si>
   <si>
     <t>2021-11-03</t>
@@ -1138,7 +1138,13 @@
     <t>2021-11-29</t>
   </si>
   <si>
+    <t>2021-12-13</t>
+  </si>
+  <si>
     <t>2021-12-03</t>
+  </si>
+  <si>
+    <t>2021-12-08</t>
   </si>
   <si>
     <t>2016-10-17</t>
@@ -1500,6 +1506,9 @@
   <si>
     <t>2021-09-30</t>
   </si>
+  <si>
+    <t>2021-10-28</t>
+  </si>
 </sst>
 </file>
 
@@ -1856,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1078"/>
+  <dimension ref="A1:P1086"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1953,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2003,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2053,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2103,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2153,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2203,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2253,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2553,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2603,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2653,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2703,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2753,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2803,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2853,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2903,7 +2912,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2953,7 +2962,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3203,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3253,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3303,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3353,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3403,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3453,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3503,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3553,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3603,7 +3612,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3653,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3703,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3753,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4053,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4103,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4153,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4203,7 +4212,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4253,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4303,7 +4312,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4353,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4403,7 +4412,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4453,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4503,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4553,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4603,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4653,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4703,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4753,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4803,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4853,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4903,7 +4912,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4953,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5003,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5053,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5503,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5553,7 +5562,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5603,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5653,7 +5662,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5703,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5753,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6153,7 +6162,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6203,7 +6212,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6253,7 +6262,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6303,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6353,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6403,7 +6412,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6653,7 +6662,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6703,7 +6712,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6753,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6803,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6853,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6903,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6953,7 +6962,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7003,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7053,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7103,7 +7112,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7153,7 +7162,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7203,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7253,7 +7262,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7303,7 +7312,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7353,7 +7362,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7403,7 +7412,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7453,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7503,7 +7512,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7553,7 +7562,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7603,7 +7612,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7653,7 +7662,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7703,7 +7712,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7753,7 +7762,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7803,7 +7812,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7853,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7903,7 +7912,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7953,7 +7962,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8003,7 +8012,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8053,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8103,7 +8112,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8153,7 +8162,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8203,7 +8212,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8253,7 +8262,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8303,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8353,7 +8362,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8403,7 +8412,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8453,7 +8462,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8503,7 +8512,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8553,7 +8562,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8603,7 +8612,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8653,7 +8662,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8703,7 +8712,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8753,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8803,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8853,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8903,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8953,7 +8962,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9003,7 +9012,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9053,7 +9062,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9103,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9153,7 +9162,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9203,7 +9212,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9253,7 +9262,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9303,7 +9312,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9553,7 +9562,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9603,7 +9612,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9653,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9703,7 +9712,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9753,7 +9762,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9803,7 +9812,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9853,7 +9862,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9903,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10253,7 +10262,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10303,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10353,7 +10362,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10603,7 +10612,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10653,7 +10662,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10703,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10753,7 +10762,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10803,7 +10812,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10853,7 +10862,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10903,7 +10912,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10953,7 +10962,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11003,7 +11012,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11053,7 +11062,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11103,7 +11112,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11153,7 +11162,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11203,7 +11212,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11603,7 +11612,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11853,7 +11862,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11903,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11953,7 +11962,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12003,7 +12012,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12053,7 +12062,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12103,7 +12112,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12153,7 +12162,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12203,7 +12212,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12253,7 +12262,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12303,7 +12312,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12353,7 +12362,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12403,7 +12412,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12453,7 +12462,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12503,7 +12512,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12553,7 +12562,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12603,7 +12612,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12653,7 +12662,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16503,7 +16512,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16553,7 +16562,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16603,7 +16612,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16653,7 +16662,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16703,7 +16712,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16753,7 +16762,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16953,7 +16962,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17003,7 +17012,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17053,7 +17062,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17103,7 +17112,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17153,7 +17162,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17203,7 +17212,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17453,7 +17462,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17503,7 +17512,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17553,7 +17562,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17603,7 +17612,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17653,7 +17662,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17703,7 +17712,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17753,7 +17762,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17803,7 +17812,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17853,7 +17862,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -19003,7 +19012,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19053,7 +19062,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19103,7 +19112,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19153,7 +19162,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19203,7 +19212,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19253,7 +19262,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19303,7 +19312,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19353,7 +19362,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19403,7 +19412,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19453,7 +19462,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -20053,7 +20062,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20103,7 +20112,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20153,7 +20162,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20203,7 +20212,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20253,7 +20262,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20303,7 +20312,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -22053,7 +22062,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22103,7 +22112,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22153,7 +22162,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22203,7 +22212,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22253,7 +22262,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22303,7 +22312,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22353,7 +22362,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22403,7 +22412,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22453,7 +22462,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22503,7 +22512,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22553,7 +22562,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22603,7 +22612,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22653,7 +22662,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22703,7 +22712,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22753,7 +22762,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22803,7 +22812,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22853,7 +22862,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22903,7 +22912,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22953,7 +22962,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23303,7 +23312,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23353,7 +23362,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23403,7 +23412,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23453,7 +23462,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23503,7 +23512,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23553,7 +23562,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23603,7 +23612,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23653,7 +23662,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23703,7 +23712,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23753,7 +23762,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23803,7 +23812,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23853,7 +23862,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23903,7 +23912,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23953,7 +23962,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24003,7 +24012,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24053,7 +24062,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24103,7 +24112,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24153,7 +24162,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24203,7 +24212,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24253,7 +24262,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24303,7 +24312,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24353,7 +24362,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24753,7 +24762,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24803,7 +24812,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24853,7 +24862,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24903,7 +24912,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24953,7 +24962,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25003,7 +25012,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25053,7 +25062,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25653,7 +25662,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25703,7 +25712,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25753,7 +25762,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25803,7 +25812,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25853,7 +25862,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25903,7 +25912,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25953,7 +25962,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26003,7 +26012,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26053,7 +26062,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26103,7 +26112,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26153,7 +26162,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26203,7 +26212,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26253,7 +26262,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26303,7 +26312,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26353,7 +26362,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26403,7 +26412,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26453,7 +26462,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26503,7 +26512,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26553,7 +26562,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26603,7 +26612,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26803,7 +26812,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26853,7 +26862,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26903,7 +26912,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26953,7 +26962,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27003,7 +27012,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27053,7 +27062,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27103,7 +27112,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -28053,7 +28062,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28103,7 +28112,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28153,7 +28162,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29453,7 +29462,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29503,7 +29512,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29553,7 +29562,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29603,7 +29612,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29653,7 +29662,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29703,7 +29712,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29753,7 +29762,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29803,7 +29812,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29853,7 +29862,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29903,7 +29912,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30203,7 +30212,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30253,7 +30262,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30303,7 +30312,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30353,7 +30362,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30403,7 +30412,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30453,7 +30462,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30503,7 +30512,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30553,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30603,7 +30612,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30653,7 +30662,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30703,7 +30712,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30903,7 +30912,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30953,7 +30962,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31003,7 +31012,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31053,7 +31062,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31103,7 +31112,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31153,7 +31162,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31203,7 +31212,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31253,7 +31262,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31303,7 +31312,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31603,7 +31612,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31653,7 +31662,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31703,7 +31712,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31753,7 +31762,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31803,7 +31812,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31853,7 +31862,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31903,7 +31912,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31953,7 +31962,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32003,7 +32012,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32053,7 +32062,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32103,7 +32112,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32153,7 +32162,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32753,7 +32762,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32803,7 +32812,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32853,7 +32862,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32903,7 +32912,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32953,7 +32962,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33003,7 +33012,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33053,7 +33062,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33103,7 +33112,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33153,7 +33162,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33203,7 +33212,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33403,7 +33412,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33453,7 +33462,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33503,7 +33512,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33553,7 +33562,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33603,7 +33612,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34503,7 +34512,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34553,7 +34562,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34603,7 +34612,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34653,7 +34662,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34703,7 +34712,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34753,7 +34762,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34803,7 +34812,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34853,7 +34862,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34903,7 +34912,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35553,7 +35562,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35603,7 +35612,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35653,7 +35662,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35703,7 +35712,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35753,7 +35762,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35803,7 +35812,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35853,7 +35862,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35903,7 +35912,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35953,7 +35962,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36353,7 +36362,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36403,7 +36412,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36453,7 +36462,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36503,7 +36512,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36553,7 +36562,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36603,7 +36612,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36653,7 +36662,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36703,7 +36712,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36753,7 +36762,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36803,7 +36812,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36853,7 +36862,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36903,7 +36912,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36953,7 +36962,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37253,7 +37262,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37303,7 +37312,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37353,7 +37362,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37403,7 +37412,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37703,7 +37712,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37753,7 +37762,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37803,7 +37812,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37853,7 +37862,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37903,7 +37912,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37953,7 +37962,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38003,7 +38012,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38053,7 +38062,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38103,7 +38112,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38153,7 +38162,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38403,7 +38412,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38453,7 +38462,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38503,7 +38512,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38553,7 +38562,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38603,7 +38612,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39203,7 +39212,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39253,7 +39262,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39303,7 +39312,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39353,7 +39362,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39403,7 +39412,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39453,7 +39462,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39503,7 +39512,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39553,7 +39562,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39603,7 +39612,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39653,7 +39662,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40453,7 +40462,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40503,7 +40512,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40553,7 +40562,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40603,7 +40612,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40653,7 +40662,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40703,7 +40712,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40753,7 +40762,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42453,7 +42462,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42503,7 +42512,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42553,7 +42562,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42603,7 +42612,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42653,7 +42662,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43203,7 +43212,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43253,7 +43262,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43303,7 +43312,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43353,7 +43362,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43403,7 +43412,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43453,7 +43462,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43603,7 +43612,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43653,7 +43662,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43703,7 +43712,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43753,7 +43762,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43803,7 +43812,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43853,7 +43862,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43903,7 +43912,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43953,7 +43962,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44003,7 +44012,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44053,7 +44062,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44103,7 +44112,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44153,7 +44162,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44203,7 +44212,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44253,7 +44262,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44303,7 +44312,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44353,7 +44362,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44403,7 +44412,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44453,7 +44462,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44503,7 +44512,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44553,7 +44562,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44853,7 +44862,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44903,7 +44912,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44953,7 +44962,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45003,7 +45012,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45053,7 +45062,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45103,7 +45112,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45153,7 +45162,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45203,7 +45212,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45253,7 +45262,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45303,7 +45312,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45353,7 +45362,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45403,7 +45412,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45453,7 +45462,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45503,7 +45512,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45553,7 +45562,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45603,7 +45612,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45653,7 +45662,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45703,7 +45712,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46003,7 +46012,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46053,7 +46062,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46103,7 +46112,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46153,7 +46162,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46203,7 +46212,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46453,7 +46462,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46503,7 +46512,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46553,7 +46562,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46603,7 +46612,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46853,7 +46862,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46903,7 +46912,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46953,7 +46962,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47003,7 +47012,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47053,7 +47062,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47103,7 +47112,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47153,7 +47162,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47203,7 +47212,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47253,7 +47262,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47303,7 +47312,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47353,7 +47362,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47703,7 +47712,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47753,7 +47762,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47803,7 +47812,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47853,7 +47862,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47903,7 +47912,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47953,7 +47962,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48003,7 +48012,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48053,7 +48062,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48103,7 +48112,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48153,7 +48162,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48203,7 +48212,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48253,7 +48262,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48303,7 +48312,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48353,7 +48362,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48403,7 +48412,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48953,7 +48962,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49003,7 +49012,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49053,7 +49062,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49103,7 +49112,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49303,7 +49312,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49353,7 +49362,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49403,7 +49412,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49453,7 +49462,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49503,7 +49512,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49553,7 +49562,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49603,7 +49612,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49653,7 +49662,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49703,7 +49712,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50703,7 +50712,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50753,7 +50762,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50803,7 +50812,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50853,7 +50862,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50903,7 +50912,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50953,7 +50962,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51003,7 +51012,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51053,7 +51062,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51103,7 +51112,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51153,7 +51162,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51203,7 +51212,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51253,7 +51262,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51303,7 +51312,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51353,7 +51362,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51403,7 +51412,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51453,7 +51462,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51503,7 +51512,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51553,7 +51562,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51603,7 +51612,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51653,7 +51662,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51703,7 +51712,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51753,7 +51762,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51803,7 +51812,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51853,7 +51862,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51903,7 +51912,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -51953,7 +51962,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -52003,7 +52012,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52053,7 +52062,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52103,7 +52112,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52153,7 +52162,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52203,7 +52212,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52253,7 +52262,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52303,7 +52312,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52453,7 +52462,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52503,7 +52512,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52703,7 +52712,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52753,7 +52762,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52803,7 +52812,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52853,7 +52862,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52867,7 +52876,7 @@
         <v>0.3892090844427933</v>
       </c>
       <c r="D1021" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E1021">
         <v>0.7538814936438047</v>
@@ -52903,7 +52912,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52953,7 +52962,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -52967,7 +52976,7 @@
         <v>0.3856328717938826</v>
       </c>
       <c r="D1023" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E1023">
         <v>0.750807205577197</v>
@@ -53003,7 +53012,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53053,7 +53062,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53103,7 +53112,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53117,7 +53126,7 @@
         <v>0.3841534580543895</v>
       </c>
       <c r="D1026" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E1026">
         <v>0.7495354288537728</v>
@@ -53153,7 +53162,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53203,7 +53212,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53253,7 +53262,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53303,7 +53312,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53353,7 +53362,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -54158,63 +54167,63 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1047" t="s">
         <v>207</v>
       </c>
       <c r="C1047">
-        <v>0.7027628245386071</v>
+        <v>0.35770890861256</v>
       </c>
       <c r="D1047" t="s">
-        <v>198</v>
+        <v>374</v>
       </c>
       <c r="E1047">
-        <v>0.5126320191808968</v>
+        <v>0.3957762995526517</v>
       </c>
       <c r="F1047">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1047">
-        <v>0.0152572371754614</v>
+        <v>0.01282229109138744</v>
       </c>
       <c r="H1047">
-        <v>0.0132073679808191</v>
+        <v>0.01256422370044735</v>
       </c>
       <c r="I1047">
-        <v>0.1901308053577102</v>
+        <v>0.03806739094009171</v>
       </c>
       <c r="J1047">
-        <v>1.347636513974332</v>
+        <v>1.346067190364458</v>
       </c>
       <c r="K1047">
-        <v>5.4</v>
+        <v>4.63</v>
       </c>
       <c r="L1047">
-        <v>7.98</v>
+        <v>6.59</v>
       </c>
       <c r="M1047">
-        <v>4.71</v>
+        <v>4.52</v>
       </c>
       <c r="N1047">
-        <v>6.86</v>
+        <v>6.48</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>365</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1048" t="s">
         <v>208</v>
       </c>
       <c r="C1048">
-        <v>0.7043920026437194</v>
+        <v>0.7027628245386071</v>
       </c>
       <c r="D1048" t="s">
         <v>198</v>
@@ -54226,22 +54235,22 @@
         <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.01369560799735628</v>
+        <v>0.0152572371754614</v>
       </c>
       <c r="H1048">
         <v>0.0132073679808191</v>
       </c>
       <c r="I1048">
-        <v>0.1917599834628225</v>
+        <v>0.1901308053577102</v>
       </c>
       <c r="J1048">
         <v>1.347636513974332</v>
       </c>
       <c r="K1048">
-        <v>4.82</v>
+        <v>5.4</v>
       </c>
       <c r="L1048">
-        <v>7.2</v>
+        <v>7.98</v>
       </c>
       <c r="M1048">
         <v>4.71</v>
@@ -54258,46 +54267,46 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1049" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C1049">
-        <v>0.3991120522552487</v>
+        <v>0.6913447329232065</v>
       </c>
       <c r="D1049" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1049">
-        <v>0.5881666578449822</v>
+        <v>0.5126320191808968</v>
       </c>
       <c r="F1049">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.01250088794774475</v>
+        <v>0.01362865526707679</v>
       </c>
       <c r="H1049">
-        <v>0.01161183334215502</v>
+        <v>0.0132073679808191</v>
       </c>
       <c r="I1049">
-        <v>0.1890546055897335</v>
+        <v>0.1787127137423097</v>
       </c>
       <c r="J1049">
         <v>1.347636513974332</v>
       </c>
       <c r="K1049">
-        <v>4.49</v>
+        <v>4.8</v>
       </c>
       <c r="L1049">
-        <v>6.45</v>
+        <v>7.16</v>
       </c>
       <c r="M1049">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1049">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1049">
         <v>1</v>
@@ -54308,13 +54317,13 @@
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1050" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1050">
-        <v>0.3716866247706294</v>
+        <v>0.2930175128142221</v>
       </c>
       <c r="D1050" t="s">
         <v>369</v>
@@ -54326,22 +54335,22 @@
         <v>1</v>
       </c>
       <c r="G1050">
-        <v>0.01198831337522937</v>
+        <v>0.01228698248718578</v>
       </c>
       <c r="H1050">
         <v>0.01161183334215502</v>
       </c>
       <c r="I1050">
-        <v>0.2164800330743528</v>
+        <v>0.2951491450307602</v>
       </c>
       <c r="J1050">
         <v>1.347636513974332</v>
       </c>
       <c r="K1050">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1050">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1050">
         <v>4.09</v>
@@ -54358,46 +54367,46 @@
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1051" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1051">
-        <v>0.7672648652206187</v>
+        <v>0.3716866247706294</v>
       </c>
       <c r="D1051" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E1051">
-        <v>0.506064782534736</v>
+        <v>0.5881666578449822</v>
       </c>
       <c r="F1051">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1051">
-        <v>0.01133273513477938</v>
+        <v>0.01198831337522937</v>
       </c>
       <c r="H1051">
-        <v>0.01255393521746526</v>
+        <v>0.01161183334215502</v>
       </c>
       <c r="I1051">
-        <v>0.2612000826858827</v>
+        <v>0.2164800330743528</v>
       </c>
       <c r="J1051">
         <v>1.347636513974332</v>
       </c>
       <c r="K1051">
-        <v>3.92</v>
+        <v>4.31</v>
       </c>
       <c r="L1051">
-        <v>6.05</v>
+        <v>6.18</v>
       </c>
       <c r="M1051">
-        <v>4.47</v>
+        <v>4.09</v>
       </c>
       <c r="N1051">
-        <v>6.53</v>
+        <v>6.1</v>
       </c>
       <c r="O1051">
         <v>1</v>
@@ -54408,113 +54417,113 @@
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1052" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C1052">
-        <v>0.6963736868234349</v>
+        <v>0.7672648652206187</v>
       </c>
       <c r="D1052" t="s">
-        <v>198</v>
+        <v>375</v>
       </c>
       <c r="E1052">
-        <v>0.5070592712848851</v>
+        <v>0.506064782534736</v>
       </c>
       <c r="F1052">
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.01526362631317657</v>
+        <v>0.01133273513477938</v>
       </c>
       <c r="H1052">
-        <v>0.01321294072871512</v>
+        <v>0.01255393521746526</v>
       </c>
       <c r="I1052">
-        <v>0.1893144155385498</v>
+        <v>0.2612000826858827</v>
       </c>
       <c r="J1052">
-        <v>1.34881968762529</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1052">
-        <v>5.4</v>
+        <v>3.92</v>
       </c>
       <c r="L1052">
-        <v>7.98</v>
+        <v>6.05</v>
       </c>
       <c r="M1052">
-        <v>4.71</v>
+        <v>4.47</v>
       </c>
       <c r="N1052">
-        <v>6.86</v>
+        <v>6.53</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>203</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1053" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C1053">
-        <v>0.6986891056461033</v>
+        <v>0.3504429402988425</v>
       </c>
       <c r="D1053" t="s">
-        <v>198</v>
+        <v>374</v>
       </c>
       <c r="E1053">
-        <v>0.5070592712848851</v>
+        <v>0.3886829568360204</v>
       </c>
       <c r="F1053">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.0137013108943539</v>
+        <v>0.01282955705970116</v>
       </c>
       <c r="H1053">
-        <v>0.01321294072871512</v>
+        <v>0.01257131704316398</v>
       </c>
       <c r="I1053">
-        <v>0.1916298343612182</v>
+        <v>0.0382400165371779</v>
       </c>
       <c r="J1053">
-        <v>1.34881968762529</v>
+        <v>1.347636513974332</v>
       </c>
       <c r="K1053">
-        <v>4.82</v>
+        <v>4.63</v>
       </c>
       <c r="L1053">
-        <v>7.2</v>
+        <v>6.59</v>
       </c>
       <c r="M1053">
-        <v>4.71</v>
+        <v>4.52</v>
       </c>
       <c r="N1053">
-        <v>6.86</v>
+        <v>6.48</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>203</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1054" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C1054">
-        <v>0.6856654993986089</v>
+        <v>0.6963736868234349</v>
       </c>
       <c r="D1054" t="s">
         <v>198</v>
@@ -54526,22 +54535,22 @@
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.01363433450060139</v>
+        <v>0.01526362631317657</v>
       </c>
       <c r="H1054">
         <v>0.01321294072871512</v>
       </c>
       <c r="I1054">
-        <v>0.1786062281137237</v>
+        <v>0.1893144155385498</v>
       </c>
       <c r="J1054">
         <v>1.34881968762529</v>
       </c>
       <c r="K1054">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L1054">
-        <v>7.16</v>
+        <v>7.98</v>
       </c>
       <c r="M1054">
         <v>4.71</v>
@@ -54558,46 +54567,46 @@
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1055" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1055">
-        <v>0.2877523900674603</v>
+        <v>0.6856654993986089</v>
       </c>
       <c r="D1055" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1055">
-        <v>0.5833274776125643</v>
+        <v>0.5070592712848851</v>
       </c>
       <c r="F1055">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.01229224760993254</v>
+        <v>0.01363433450060139</v>
       </c>
       <c r="H1055">
-        <v>0.01161667252238744</v>
+        <v>0.01321294072871512</v>
       </c>
       <c r="I1055">
-        <v>0.295575087545104</v>
+        <v>0.1786062281137237</v>
       </c>
       <c r="J1055">
         <v>1.34881968762529</v>
       </c>
       <c r="K1055">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1055">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1055">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1055">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54608,13 +54617,13 @@
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1056" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1056">
-        <v>0.366587146335001</v>
+        <v>0.2877523900674603</v>
       </c>
       <c r="D1056" t="s">
         <v>369</v>
@@ -54626,22 +54635,22 @@
         <v>1</v>
       </c>
       <c r="G1056">
-        <v>0.011993412853665</v>
+        <v>0.01229224760993254</v>
       </c>
       <c r="H1056">
         <v>0.01161667252238744</v>
       </c>
       <c r="I1056">
-        <v>0.2167403312775633</v>
+        <v>0.295575087545104</v>
       </c>
       <c r="J1056">
         <v>1.34881968762529</v>
       </c>
       <c r="K1056">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1056">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1056">
         <v>4.09</v>
@@ -54658,46 +54667,46 @@
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1057" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1057">
-        <v>0.7626268245088639</v>
+        <v>0.366587146335001</v>
       </c>
       <c r="D1057" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E1057">
-        <v>0.500775996314955</v>
+        <v>0.5833274776125643</v>
       </c>
       <c r="F1057">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1057">
-        <v>0.01133737317549114</v>
+        <v>0.011993412853665</v>
       </c>
       <c r="H1057">
-        <v>0.01255922400368505</v>
+        <v>0.01161667252238744</v>
       </c>
       <c r="I1057">
-        <v>0.2618508281939089</v>
+        <v>0.2167403312775633</v>
       </c>
       <c r="J1057">
         <v>1.34881968762529</v>
       </c>
       <c r="K1057">
-        <v>3.92</v>
+        <v>4.31</v>
       </c>
       <c r="L1057">
-        <v>6.05</v>
+        <v>6.18</v>
       </c>
       <c r="M1057">
-        <v>4.47</v>
+        <v>4.09</v>
       </c>
       <c r="N1057">
-        <v>6.53</v>
+        <v>6.1</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -54708,146 +54717,146 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1058" t="s">
         <v>210</v>
       </c>
       <c r="C1058">
-        <v>0.6760248424128479</v>
+        <v>0.7626268245088639</v>
       </c>
       <c r="D1058" t="s">
-        <v>198</v>
+        <v>375</v>
       </c>
       <c r="E1058">
-        <v>0.4975993766176074</v>
+        <v>0.500775996314955</v>
       </c>
       <c r="F1058">
         <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.01364397515758715</v>
+        <v>0.01133737317549114</v>
       </c>
       <c r="H1058">
-        <v>0.01322240062338239</v>
+        <v>0.01255922400368505</v>
       </c>
       <c r="I1058">
-        <v>0.1784254657952404</v>
+        <v>0.2618508281939089</v>
       </c>
       <c r="J1058">
-        <v>1.350828157830657</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1058">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="L1058">
-        <v>7.16</v>
+        <v>6.05</v>
       </c>
       <c r="M1058">
-        <v>4.71</v>
+        <v>4.47</v>
       </c>
       <c r="N1058">
-        <v>6.86</v>
+        <v>6.53</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1059" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C1059">
-        <v>0.2788146976535772</v>
+        <v>0.344964846294908</v>
       </c>
       <c r="D1059" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E1059">
-        <v>0.5751128344726144</v>
+        <v>0.3833350119336911</v>
       </c>
       <c r="F1059">
         <v>1</v>
       </c>
       <c r="G1059">
-        <v>0.01230118530234642</v>
+        <v>0.01283503515370509</v>
       </c>
       <c r="H1059">
-        <v>0.01162488716552739</v>
+        <v>0.01257666498806631</v>
       </c>
       <c r="I1059">
-        <v>0.2962981368190372</v>
+        <v>0.03837016563878315</v>
       </c>
       <c r="J1059">
-        <v>1.350828157830657</v>
+        <v>1.34881968762529</v>
       </c>
       <c r="K1059">
-        <v>4.45</v>
+        <v>4.63</v>
       </c>
       <c r="L1059">
-        <v>6.29</v>
+        <v>6.59</v>
       </c>
       <c r="M1059">
-        <v>4.09</v>
+        <v>4.52</v>
       </c>
       <c r="N1059">
-        <v>6.1</v>
+        <v>6.48</v>
       </c>
       <c r="O1059">
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1060" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1060">
-        <v>0.3579306397498696</v>
+        <v>0.6760248424128479</v>
       </c>
       <c r="D1060" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="E1060">
-        <v>0.5751128344726144</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1060">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.01200206936025013</v>
+        <v>0.01364397515758715</v>
       </c>
       <c r="H1060">
-        <v>0.01162488716552739</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1060">
-        <v>0.2171821947227448</v>
+        <v>0.1784254657952404</v>
       </c>
       <c r="J1060">
         <v>1.350828157830657</v>
       </c>
       <c r="K1060">
-        <v>4.31</v>
+        <v>4.8</v>
       </c>
       <c r="L1060">
-        <v>6.18</v>
+        <v>7.16</v>
       </c>
       <c r="M1060">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="N1060">
-        <v>6.1</v>
+        <v>6.86</v>
       </c>
       <c r="O1060">
         <v>1</v>
@@ -54858,46 +54867,46 @@
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1061" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C1061">
-        <v>0.7547536213038253</v>
+        <v>0.6505828134609937</v>
       </c>
       <c r="D1061" t="s">
-        <v>374</v>
+        <v>198</v>
       </c>
       <c r="E1061">
-        <v>0.4917981344969649</v>
+        <v>0.4975993766176074</v>
       </c>
       <c r="F1061">
         <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.01134524637869617</v>
+        <v>0.01342941718653901</v>
       </c>
       <c r="H1061">
-        <v>0.01256820186550303</v>
+        <v>0.01322240062338239</v>
       </c>
       <c r="I1061">
-        <v>0.2629554868068604</v>
+        <v>0.1529834368433862</v>
       </c>
       <c r="J1061">
         <v>1.350828157830657</v>
       </c>
       <c r="K1061">
-        <v>3.92</v>
+        <v>4.73</v>
       </c>
       <c r="L1061">
-        <v>6.05</v>
+        <v>7.04</v>
       </c>
       <c r="M1061">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="N1061">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="O1061">
         <v>1</v>
@@ -54908,90 +54917,90 @@
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1062" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1062">
-        <v>0.6767185447573851</v>
+        <v>0.2788146976535772</v>
       </c>
       <c r="D1062" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="E1062">
-        <v>0.4982800720431841</v>
+        <v>0.5751128344726144</v>
       </c>
       <c r="F1062">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.01364328145524261</v>
+        <v>0.01230118530234642</v>
       </c>
       <c r="H1062">
-        <v>0.01322171992795682</v>
+        <v>0.01162488716552739</v>
       </c>
       <c r="I1062">
-        <v>0.178438472714201</v>
+        <v>0.2962981368190372</v>
       </c>
       <c r="J1062">
-        <v>1.350683636508878</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1062">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="L1062">
-        <v>7.16</v>
+        <v>6.29</v>
       </c>
       <c r="M1062">
-        <v>4.71</v>
+        <v>4.09</v>
       </c>
       <c r="N1062">
-        <v>6.86</v>
+        <v>6.1</v>
       </c>
       <c r="O1062">
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1063" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C1063">
-        <v>0.2794578175354925</v>
+        <v>0.3579306397498696</v>
       </c>
       <c r="D1063" t="s">
         <v>369</v>
       </c>
       <c r="E1063">
-        <v>0.5757039266786883</v>
+        <v>0.5751128344726144</v>
       </c>
       <c r="F1063">
         <v>1</v>
       </c>
       <c r="G1063">
-        <v>0.01230054218246451</v>
+        <v>0.01200206936025013</v>
       </c>
       <c r="H1063">
-        <v>0.01162429607332131</v>
+        <v>0.01162488716552739</v>
       </c>
       <c r="I1063">
-        <v>0.2962461091431958</v>
+        <v>0.2171821947227448</v>
       </c>
       <c r="J1063">
-        <v>1.350683636508878</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1063">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="L1063">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="M1063">
         <v>4.09</v>
@@ -55003,107 +55012,107 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1064" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1064">
-        <v>0.3585535266467357</v>
+        <v>0.7547536213038253</v>
       </c>
       <c r="D1064" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E1064">
-        <v>0.5757039266786883</v>
+        <v>0.4917981344969649</v>
       </c>
       <c r="F1064">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1064">
-        <v>0.01200144647335326</v>
+        <v>0.01134524637869617</v>
       </c>
       <c r="H1064">
-        <v>0.01162429607332131</v>
+        <v>0.01256820186550303</v>
       </c>
       <c r="I1064">
-        <v>0.2171504000319526</v>
+        <v>0.2629554868068604</v>
       </c>
       <c r="J1064">
-        <v>1.350683636508878</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1064">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="L1064">
-        <v>6.18</v>
+        <v>6.05</v>
       </c>
       <c r="M1064">
-        <v>4.09</v>
+        <v>4.47</v>
       </c>
       <c r="N1064">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1065" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C1065">
-        <v>0.7553201448851974</v>
+        <v>0.3356656292440592</v>
       </c>
       <c r="D1065" t="s">
         <v>374</v>
       </c>
       <c r="E1065">
-        <v>0.4924441448053152</v>
+        <v>0.3742567266054326</v>
       </c>
       <c r="F1065">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1065">
-        <v>0.0113446798551148</v>
+        <v>0.01284433437075594</v>
       </c>
       <c r="H1065">
-        <v>0.01256755585519469</v>
+        <v>0.01258574327339457</v>
       </c>
       <c r="I1065">
-        <v>0.2628760000798822</v>
+        <v>0.03859109736137345</v>
       </c>
       <c r="J1065">
-        <v>1.350683636508878</v>
+        <v>1.350828157830657</v>
       </c>
       <c r="K1065">
-        <v>3.92</v>
+        <v>4.63</v>
       </c>
       <c r="L1065">
-        <v>6.05</v>
+        <v>6.59</v>
       </c>
       <c r="M1065">
-        <v>4.47</v>
+        <v>4.52</v>
       </c>
       <c r="N1065">
-        <v>6.53</v>
+        <v>6.48</v>
       </c>
       <c r="O1065">
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55111,31 +55120,31 @@
         <v>0</v>
       </c>
       <c r="B1066" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C1066">
-        <v>0.6674364420145809</v>
+        <v>0.6767185447573851</v>
       </c>
       <c r="D1066" t="s">
         <v>198</v>
       </c>
       <c r="E1066">
-        <v>0.4891720087268077</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1066">
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.01365256355798542</v>
+        <v>0.01364328145524261</v>
       </c>
       <c r="H1066">
-        <v>0.01323082799127319</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1066">
-        <v>0.1782644332877732</v>
+        <v>0.178438472714201</v>
       </c>
       <c r="J1066">
-        <v>1.352617407913629</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1066">
         <v>4.8</v>
@@ -55153,7 +55162,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55164,28 +55173,28 @@
         <v>211</v>
       </c>
       <c r="C1067">
-        <v>0.6421196605685342</v>
+        <v>0.6512663993130063</v>
       </c>
       <c r="D1067" t="s">
         <v>198</v>
       </c>
       <c r="E1067">
-        <v>0.4891720087268077</v>
+        <v>0.4982800720431841</v>
       </c>
       <c r="F1067">
         <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.01343788033943147</v>
+        <v>0.01342873360068699</v>
       </c>
       <c r="H1067">
-        <v>0.01323082799127319</v>
+        <v>0.01322171992795682</v>
       </c>
       <c r="I1067">
-        <v>0.1529476518417265</v>
+        <v>0.1529863272698222</v>
       </c>
       <c r="J1067">
-        <v>1.352617407913629</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1067">
         <v>4.73</v>
@@ -55203,7 +55212,7 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55214,28 +55223,28 @@
         <v>206</v>
       </c>
       <c r="C1068">
-        <v>0.2708525347843507</v>
+        <v>0.2794578175354925</v>
       </c>
       <c r="D1068" t="s">
         <v>369</v>
       </c>
       <c r="E1068">
-        <v>0.5677948016332568</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1068">
         <v>1</v>
       </c>
       <c r="G1068">
-        <v>0.01230914746521565</v>
+        <v>0.01230054218246451</v>
       </c>
       <c r="H1068">
-        <v>0.01163220519836674</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1068">
-        <v>0.2969422668489061</v>
+        <v>0.2962461091431958</v>
       </c>
       <c r="J1068">
-        <v>1.352617407913629</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1068">
         <v>4.45</v>
@@ -55253,7 +55262,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55264,28 +55273,28 @@
         <v>201</v>
       </c>
       <c r="C1069">
-        <v>0.350218971892259</v>
+        <v>0.3585535266467357</v>
       </c>
       <c r="D1069" t="s">
         <v>369</v>
       </c>
       <c r="E1069">
-        <v>0.5677948016332568</v>
+        <v>0.5757039266786883</v>
       </c>
       <c r="F1069">
         <v>1</v>
       </c>
       <c r="G1069">
-        <v>0.01200978102810774</v>
+        <v>0.01200144647335326</v>
       </c>
       <c r="H1069">
-        <v>0.01163220519836674</v>
+        <v>0.01162429607332131</v>
       </c>
       <c r="I1069">
-        <v>0.2175758297409978</v>
+        <v>0.2171504000319526</v>
       </c>
       <c r="J1069">
-        <v>1.352617407913629</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1069">
         <v>4.31</v>
@@ -55303,7 +55312,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55311,31 +55320,31 @@
         <v>4</v>
       </c>
       <c r="B1070" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C1070">
-        <v>0.7477397609785736</v>
+        <v>0.7553201448851974</v>
       </c>
       <c r="D1070" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E1070">
-        <v>0.4838001866260786</v>
+        <v>0.4924441448053152</v>
       </c>
       <c r="F1070">
         <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.01135226023902143</v>
+        <v>0.0113446798551148</v>
       </c>
       <c r="H1070">
-        <v>0.01257619981337392</v>
+        <v>0.01256755585519469</v>
       </c>
       <c r="I1070">
-        <v>0.263939574352495</v>
+        <v>0.2628760000798822</v>
       </c>
       <c r="J1070">
-        <v>1.352617407913629</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1070">
         <v>3.92</v>
@@ -55353,145 +55362,145 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1071" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C1071">
-        <v>0.653707777522631</v>
+        <v>0.3363347629638946</v>
       </c>
       <c r="D1071" t="s">
-        <v>198</v>
+        <v>374</v>
       </c>
       <c r="E1071">
-        <v>0.4757007566940814</v>
+        <v>0.3749099629798716</v>
       </c>
       <c r="F1071">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1071">
-        <v>0.01366629222247737</v>
+        <v>0.01284366523703611</v>
       </c>
       <c r="H1071">
-        <v>0.01324429924330592</v>
+        <v>0.01258509003702013</v>
       </c>
       <c r="I1071">
-        <v>0.1780070208285496</v>
+        <v>0.03857520001597692</v>
       </c>
       <c r="J1071">
-        <v>1.355477546349452</v>
+        <v>1.350683636508878</v>
       </c>
       <c r="K1071">
-        <v>4.8</v>
+        <v>4.63</v>
       </c>
       <c r="L1071">
-        <v>7.16</v>
+        <v>6.59</v>
       </c>
       <c r="M1071">
-        <v>4.71</v>
+        <v>4.52</v>
       </c>
       <c r="N1071">
-        <v>6.86</v>
+        <v>6.48</v>
       </c>
       <c r="O1071">
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1072" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C1072">
-        <v>0.2581249187449384</v>
+        <v>0.6674364420145809</v>
       </c>
       <c r="D1072" t="s">
-        <v>368</v>
+        <v>198</v>
       </c>
       <c r="E1072">
-        <v>0.4841038562592912</v>
+        <v>0.4891720087268077</v>
       </c>
       <c r="F1072">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1072">
-        <v>0.01232187508125506</v>
+        <v>0.01365256355798542</v>
       </c>
       <c r="H1072">
-        <v>0.01181589614374071</v>
+        <v>0.01323082799127319</v>
       </c>
       <c r="I1072">
-        <v>0.2259789375143528</v>
+        <v>0.1782644332877732</v>
       </c>
       <c r="J1072">
-        <v>1.355477546349452</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1072">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="L1072">
-        <v>6.29</v>
+        <v>7.16</v>
       </c>
       <c r="M1072">
-        <v>4.18</v>
+        <v>4.71</v>
       </c>
       <c r="N1072">
-        <v>6.15</v>
+        <v>6.86</v>
       </c>
       <c r="O1072">
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1073" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1073">
-        <v>0.3378917752338619</v>
+        <v>0.2708525347843507</v>
       </c>
       <c r="D1073" t="s">
         <v>368</v>
       </c>
       <c r="E1073">
-        <v>0.4841038562592912</v>
+        <v>0.4960592349210309</v>
       </c>
       <c r="F1073">
         <v>1</v>
       </c>
       <c r="G1073">
-        <v>0.01202210822476614</v>
+        <v>0.01230914746521565</v>
       </c>
       <c r="H1073">
-        <v>0.01181589614374071</v>
+        <v>0.01180394076507897</v>
       </c>
       <c r="I1073">
-        <v>0.1462120810254293</v>
+        <v>0.2252067001366802</v>
       </c>
       <c r="J1073">
-        <v>1.355477546349452</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1073">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="L1073">
-        <v>6.18</v>
+        <v>6.29</v>
       </c>
       <c r="M1073">
         <v>4.18</v>
@@ -55503,257 +55512,657 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1074" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C1074">
-        <v>0.7365280183101479</v>
+        <v>0.350218971892259</v>
       </c>
       <c r="D1074" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E1074">
-        <v>0.4710153678179507</v>
+        <v>0.4960592349210309</v>
       </c>
       <c r="F1074">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1074">
-        <v>0.01136347198168985</v>
+        <v>0.01200978102810774</v>
       </c>
       <c r="H1074">
-        <v>0.01258898463218205</v>
+        <v>0.01180394076507897</v>
       </c>
       <c r="I1074">
-        <v>0.2655126504921972</v>
+        <v>0.1458402630287718</v>
       </c>
       <c r="J1074">
-        <v>1.355477546349452</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1074">
-        <v>3.92</v>
+        <v>4.31</v>
       </c>
       <c r="L1074">
-        <v>6.05</v>
+        <v>6.18</v>
       </c>
       <c r="M1074">
-        <v>4.47</v>
+        <v>4.18</v>
       </c>
       <c r="N1074">
-        <v>6.53</v>
+        <v>6.15</v>
       </c>
       <c r="O1074">
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1075" t="s">
         <v>210</v>
       </c>
       <c r="C1075">
-        <v>0.6493738814716474</v>
+        <v>0.7477397609785736</v>
       </c>
       <c r="D1075" t="s">
-        <v>199</v>
+        <v>375</v>
       </c>
       <c r="E1075">
-        <v>0.3998518182932695</v>
+        <v>0.4838001866260786</v>
       </c>
       <c r="F1075">
         <v>-1</v>
       </c>
       <c r="G1075">
-        <v>0.01367062611852835</v>
+        <v>0.01135226023902143</v>
       </c>
       <c r="H1075">
-        <v>0.01258014818170673</v>
+        <v>0.01257619981337392</v>
       </c>
       <c r="I1075">
-        <v>0.2495220631783779</v>
+        <v>0.263939574352495</v>
       </c>
       <c r="J1075">
-        <v>1.356380441360074</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1075">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="L1075">
-        <v>7.16</v>
+        <v>6.05</v>
       </c>
       <c r="M1075">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="N1075">
-        <v>6.49</v>
+        <v>6.53</v>
       </c>
       <c r="O1075">
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
       <c r="A1076" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1076" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C1076">
-        <v>0.2541070359476727</v>
+        <v>0.3273814013598972</v>
       </c>
       <c r="D1076" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E1076">
-        <v>0.4803297551148935</v>
+        <v>0.3661693162303976</v>
       </c>
       <c r="F1076">
         <v>1</v>
       </c>
       <c r="G1076">
-        <v>0.01232589296405233</v>
+        <v>0.0128526185986401</v>
       </c>
       <c r="H1076">
-        <v>0.01181967024488511</v>
+        <v>0.0125938306837696</v>
       </c>
       <c r="I1076">
-        <v>0.2262227191672208</v>
+        <v>0.03878791487050037</v>
       </c>
       <c r="J1076">
-        <v>1.356380441360074</v>
+        <v>1.352617407913629</v>
       </c>
       <c r="K1076">
-        <v>4.45</v>
+        <v>4.63</v>
       </c>
       <c r="L1076">
-        <v>6.29</v>
+        <v>6.59</v>
       </c>
       <c r="M1076">
-        <v>4.18</v>
+        <v>4.52</v>
       </c>
       <c r="N1076">
-        <v>6.15</v>
+        <v>6.48</v>
       </c>
       <c r="O1076">
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
       <c r="A1077" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1077" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C1077">
-        <v>0.3340002977380836</v>
+        <v>0.653707777522631</v>
       </c>
       <c r="D1077" t="s">
-        <v>368</v>
+        <v>199</v>
       </c>
       <c r="E1077">
-        <v>0.4803297551148935</v>
+        <v>0.4039058168909611</v>
       </c>
       <c r="F1077">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1077">
-        <v>0.01202599970226192</v>
+        <v>0.01366629222247737</v>
       </c>
       <c r="H1077">
-        <v>0.01181967024488511</v>
+        <v>0.01257609418310904</v>
       </c>
       <c r="I1077">
-        <v>0.1463294573768099</v>
+        <v>0.2498019606316699</v>
       </c>
       <c r="J1077">
-        <v>1.356380441360074</v>
+        <v>1.355477546349452</v>
       </c>
       <c r="K1077">
-        <v>4.31</v>
+        <v>4.8</v>
       </c>
       <c r="L1077">
-        <v>6.18</v>
+        <v>7.16</v>
       </c>
       <c r="M1077">
-        <v>4.18</v>
+        <v>4.49</v>
       </c>
       <c r="N1077">
-        <v>6.15</v>
+        <v>6.49</v>
       </c>
       <c r="O1077">
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
       <c r="A1078" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1078">
+        <v>0.2581249187449384</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>368</v>
+      </c>
+      <c r="E1078">
+        <v>0.4841038562592912</v>
+      </c>
+      <c r="F1078">
+        <v>1</v>
+      </c>
+      <c r="G1078">
+        <v>0.01232187508125506</v>
+      </c>
+      <c r="H1078">
+        <v>0.01181589614374071</v>
+      </c>
+      <c r="I1078">
+        <v>0.2259789375143528</v>
+      </c>
+      <c r="J1078">
+        <v>1.355477546349452</v>
+      </c>
+      <c r="K1078">
+        <v>4.45</v>
+      </c>
+      <c r="L1078">
+        <v>6.29</v>
+      </c>
+      <c r="M1078">
+        <v>4.18</v>
+      </c>
+      <c r="N1078">
+        <v>6.15</v>
+      </c>
+      <c r="O1078">
+        <v>1</v>
+      </c>
+      <c r="P1078" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:16">
+      <c r="A1079" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1079">
+        <v>0.3378917752338619</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>368</v>
+      </c>
+      <c r="E1079">
+        <v>0.4841038562592912</v>
+      </c>
+      <c r="F1079">
+        <v>1</v>
+      </c>
+      <c r="G1079">
+        <v>0.01202210822476614</v>
+      </c>
+      <c r="H1079">
+        <v>0.01181589614374071</v>
+      </c>
+      <c r="I1079">
+        <v>0.1462120810254293</v>
+      </c>
+      <c r="J1079">
+        <v>1.355477546349452</v>
+      </c>
+      <c r="K1079">
+        <v>4.31</v>
+      </c>
+      <c r="L1079">
+        <v>6.18</v>
+      </c>
+      <c r="M1079">
+        <v>4.18</v>
+      </c>
+      <c r="N1079">
+        <v>6.15</v>
+      </c>
+      <c r="O1079">
+        <v>1</v>
+      </c>
+      <c r="P1079" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:16">
+      <c r="A1080" s="1">
         <v>3</v>
       </c>
-      <c r="B1078" t="s">
+      <c r="B1080" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1080">
+        <v>0.7365280183101479</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1080">
+        <v>0.4710153678179507</v>
+      </c>
+      <c r="F1080">
+        <v>-1</v>
+      </c>
+      <c r="G1080">
+        <v>0.01136347198168985</v>
+      </c>
+      <c r="H1080">
+        <v>0.01258898463218205</v>
+      </c>
+      <c r="I1080">
+        <v>0.2655126504921972</v>
+      </c>
+      <c r="J1080">
+        <v>1.355477546349452</v>
+      </c>
+      <c r="K1080">
+        <v>3.92</v>
+      </c>
+      <c r="L1080">
+        <v>6.05</v>
+      </c>
+      <c r="M1080">
+        <v>4.47</v>
+      </c>
+      <c r="N1080">
+        <v>6.53</v>
+      </c>
+      <c r="O1080">
+        <v>1</v>
+      </c>
+      <c r="P1080" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:16">
+      <c r="A1081" s="1">
+        <v>4</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1081">
+        <v>0.3141389604020377</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>374</v>
+      </c>
+      <c r="E1081">
+        <v>0.3532414905004782</v>
+      </c>
+      <c r="F1081">
+        <v>1</v>
+      </c>
+      <c r="G1081">
+        <v>0.01286586103959796</v>
+      </c>
+      <c r="H1081">
+        <v>0.01260675850949952</v>
+      </c>
+      <c r="I1081">
+        <v>0.03910253009844045</v>
+      </c>
+      <c r="J1081">
+        <v>1.355477546349452</v>
+      </c>
+      <c r="K1081">
+        <v>4.63</v>
+      </c>
+      <c r="L1081">
+        <v>6.59</v>
+      </c>
+      <c r="M1081">
+        <v>4.52</v>
+      </c>
+      <c r="N1081">
+        <v>6.48</v>
+      </c>
+      <c r="O1081">
+        <v>1</v>
+      </c>
+      <c r="P1081" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:16">
+      <c r="A1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1082" t="s">
         <v>209</v>
       </c>
-      <c r="C1078">
+      <c r="C1082">
+        <v>0.6493738814716474</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1082">
+        <v>0.3998518182932695</v>
+      </c>
+      <c r="F1082">
+        <v>-1</v>
+      </c>
+      <c r="G1082">
+        <v>0.01367062611852835</v>
+      </c>
+      <c r="H1082">
+        <v>0.01258014818170673</v>
+      </c>
+      <c r="I1082">
+        <v>0.2495220631783779</v>
+      </c>
+      <c r="J1082">
+        <v>1.356380441360074</v>
+      </c>
+      <c r="K1082">
+        <v>4.8</v>
+      </c>
+      <c r="L1082">
+        <v>7.16</v>
+      </c>
+      <c r="M1082">
+        <v>4.49</v>
+      </c>
+      <c r="N1082">
+        <v>6.49</v>
+      </c>
+      <c r="O1082">
+        <v>1</v>
+      </c>
+      <c r="P1082" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:16">
+      <c r="A1083" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1083">
+        <v>0.2541070359476727</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>368</v>
+      </c>
+      <c r="E1083">
+        <v>0.4803297551148935</v>
+      </c>
+      <c r="F1083">
+        <v>1</v>
+      </c>
+      <c r="G1083">
+        <v>0.01232589296405233</v>
+      </c>
+      <c r="H1083">
+        <v>0.01181967024488511</v>
+      </c>
+      <c r="I1083">
+        <v>0.2262227191672208</v>
+      </c>
+      <c r="J1083">
+        <v>1.356380441360074</v>
+      </c>
+      <c r="K1083">
+        <v>4.45</v>
+      </c>
+      <c r="L1083">
+        <v>6.29</v>
+      </c>
+      <c r="M1083">
+        <v>4.18</v>
+      </c>
+      <c r="N1083">
+        <v>6.15</v>
+      </c>
+      <c r="O1083">
+        <v>1</v>
+      </c>
+      <c r="P1083" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:16">
+      <c r="A1084" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1084">
+        <v>0.3340002977380836</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>368</v>
+      </c>
+      <c r="E1084">
+        <v>0.4803297551148935</v>
+      </c>
+      <c r="F1084">
+        <v>1</v>
+      </c>
+      <c r="G1084">
+        <v>0.01202599970226192</v>
+      </c>
+      <c r="H1084">
+        <v>0.01181967024488511</v>
+      </c>
+      <c r="I1084">
+        <v>0.1463294573768099</v>
+      </c>
+      <c r="J1084">
+        <v>1.356380441360074</v>
+      </c>
+      <c r="K1084">
+        <v>4.31</v>
+      </c>
+      <c r="L1084">
+        <v>6.18</v>
+      </c>
+      <c r="M1084">
+        <v>4.18</v>
+      </c>
+      <c r="N1084">
+        <v>6.15</v>
+      </c>
+      <c r="O1084">
+        <v>1</v>
+      </c>
+      <c r="P1084" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:16">
+      <c r="A1085" s="1">
+        <v>3</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1085">
         <v>0.7329886698685115</v>
       </c>
-      <c r="D1078" t="s">
+      <c r="D1085" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1085">
+        <v>0.3642137741572622</v>
+      </c>
+      <c r="F1085">
+        <v>-1</v>
+      </c>
+      <c r="G1085">
+        <v>0.01136701133013149</v>
+      </c>
+      <c r="H1085">
+        <v>0.01281578622584274</v>
+      </c>
+      <c r="I1085">
+        <v>0.3687748957112493</v>
+      </c>
+      <c r="J1085">
+        <v>1.356380441360074</v>
+      </c>
+      <c r="K1085">
+        <v>3.92</v>
+      </c>
+      <c r="L1085">
+        <v>6.05</v>
+      </c>
+      <c r="M1085">
+        <v>4.59</v>
+      </c>
+      <c r="N1085">
+        <v>6.59</v>
+      </c>
+      <c r="O1085">
+        <v>1</v>
+      </c>
+      <c r="P1085" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:16">
+      <c r="A1086" s="1">
+        <v>4</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1086">
+        <v>0.3099585565028598</v>
+      </c>
+      <c r="D1086" t="s">
         <v>374</v>
       </c>
-      <c r="E1078">
-        <v>0.4669794271204717</v>
-      </c>
-      <c r="F1078">
-        <v>-1</v>
-      </c>
-      <c r="G1078">
-        <v>0.01136701133013149</v>
-      </c>
-      <c r="H1078">
-        <v>0.01259302057287953</v>
-      </c>
-      <c r="I1078">
-        <v>0.2660092427480398</v>
-      </c>
-      <c r="J1078">
+      <c r="E1086">
+        <v>0.3491604050524684</v>
+      </c>
+      <c r="F1086">
+        <v>1</v>
+      </c>
+      <c r="G1086">
+        <v>0.01287004144349714</v>
+      </c>
+      <c r="H1086">
+        <v>0.01261083959494753</v>
+      </c>
+      <c r="I1086">
+        <v>0.03920184854960862</v>
+      </c>
+      <c r="J1086">
         <v>1.356380441360074</v>
       </c>
-      <c r="K1078">
-        <v>3.92</v>
-      </c>
-      <c r="L1078">
-        <v>6.05</v>
-      </c>
-      <c r="M1078">
-        <v>4.47</v>
-      </c>
-      <c r="N1078">
-        <v>6.53</v>
-      </c>
-      <c r="O1078">
-        <v>1</v>
-      </c>
-      <c r="P1078" t="s">
-        <v>208</v>
+      <c r="K1086">
+        <v>4.63</v>
+      </c>
+      <c r="L1086">
+        <v>6.59</v>
+      </c>
+      <c r="M1086">
+        <v>4.52</v>
+      </c>
+      <c r="N1086">
+        <v>6.48</v>
+      </c>
+      <c r="O1086">
+        <v>1</v>
+      </c>
+      <c r="P1086" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01898-601898.xlsx
+++ b/s60_signal/position-01898-601898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="503">
   <si>
     <t>trade_time</t>
   </si>
@@ -1159,6 +1159,9 @@
     <t>2021-12-16</t>
   </si>
   <si>
+    <t>2021-12-17</t>
+  </si>
+  <si>
     <t>2016-10-17</t>
   </si>
   <si>
@@ -1974,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2024,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2074,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2124,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2174,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2224,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2274,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2574,7 +2577,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2624,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2674,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2724,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2774,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2824,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2874,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2924,7 +2927,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2974,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3224,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3274,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3324,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3374,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3424,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3474,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3524,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3574,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3624,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3674,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3724,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3774,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4074,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4124,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4174,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4224,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4274,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4324,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4374,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4424,7 +4427,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4474,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4524,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4574,7 +4577,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4624,7 +4627,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4674,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4724,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4774,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4824,7 +4827,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4874,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4924,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4974,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5024,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5074,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5524,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5574,7 +5577,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5624,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5674,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5724,7 +5727,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5774,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6174,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6224,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6274,7 +6277,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6324,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6374,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6424,7 +6427,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6674,7 +6677,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6724,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6774,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6824,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6874,7 +6877,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6924,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6974,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7024,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7074,7 +7077,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7124,7 +7127,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7174,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7224,7 +7227,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7274,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7324,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7374,7 +7377,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7424,7 +7427,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7474,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7524,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7574,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7624,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7674,7 +7677,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7724,7 +7727,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7774,7 +7777,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7824,7 +7827,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7874,7 +7877,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7924,7 +7927,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7974,7 +7977,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8024,7 +8027,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8074,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8124,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8174,7 +8177,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8224,7 +8227,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8274,7 +8277,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8324,7 +8327,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8374,7 +8377,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8424,7 +8427,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8474,7 +8477,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8524,7 +8527,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8574,7 +8577,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8624,7 +8627,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8674,7 +8677,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8724,7 +8727,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8774,7 +8777,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8824,7 +8827,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8874,7 +8877,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8924,7 +8927,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8974,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9024,7 +9027,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9074,7 +9077,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9124,7 +9127,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9174,7 +9177,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9224,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9274,7 +9277,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9324,7 +9327,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9574,7 +9577,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9624,7 +9627,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9674,7 +9677,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9724,7 +9727,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9774,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9824,7 +9827,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9874,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9924,7 +9927,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10274,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10324,7 +10327,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10374,7 +10377,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10624,7 +10627,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10674,7 +10677,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10724,7 +10727,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10774,7 +10777,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10824,7 +10827,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10874,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10924,7 +10927,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10974,7 +10977,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11024,7 +11027,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11074,7 +11077,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11124,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11174,7 +11177,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11224,7 +11227,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11624,7 +11627,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11874,7 +11877,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11924,7 +11927,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11974,7 +11977,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12024,7 +12027,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12074,7 +12077,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12124,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12174,7 +12177,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12224,7 +12227,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12274,7 +12277,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12324,7 +12327,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12374,7 +12377,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12424,7 +12427,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12474,7 +12477,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12524,7 +12527,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12574,7 +12577,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12624,7 +12627,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12674,7 +12677,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16524,7 +16527,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16574,7 +16577,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16624,7 +16627,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16674,7 +16677,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16724,7 +16727,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16774,7 +16777,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16974,7 +16977,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17024,7 +17027,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17074,7 +17077,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17124,7 +17127,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17174,7 +17177,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17224,7 +17227,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17474,7 +17477,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17524,7 +17527,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17574,7 +17577,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17624,7 +17627,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17674,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17724,7 +17727,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17774,7 +17777,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17824,7 +17827,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17874,7 +17877,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -19024,7 +19027,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19074,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19124,7 +19127,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19174,7 +19177,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19224,7 +19227,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19274,7 +19277,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19324,7 +19327,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19374,7 +19377,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19424,7 +19427,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19474,7 +19477,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -20074,7 +20077,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20124,7 +20127,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20174,7 +20177,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20224,7 +20227,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20274,7 +20277,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20324,7 +20327,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -22074,7 +22077,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22124,7 +22127,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22174,7 +22177,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22224,7 +22227,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22274,7 +22277,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22324,7 +22327,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22374,7 +22377,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22424,7 +22427,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22474,7 +22477,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22524,7 +22527,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22574,7 +22577,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22624,7 +22627,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22674,7 +22677,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22724,7 +22727,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22774,7 +22777,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22824,7 +22827,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22874,7 +22877,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22924,7 +22927,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22974,7 +22977,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23324,7 +23327,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23374,7 +23377,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23424,7 +23427,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23474,7 +23477,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23524,7 +23527,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23574,7 +23577,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23624,7 +23627,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23674,7 +23677,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23724,7 +23727,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23774,7 +23777,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23824,7 +23827,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23874,7 +23877,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23924,7 +23927,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23974,7 +23977,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24024,7 +24027,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24074,7 +24077,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24124,7 +24127,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24174,7 +24177,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24224,7 +24227,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24274,7 +24277,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24324,7 +24327,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24374,7 +24377,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24774,7 +24777,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24824,7 +24827,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24874,7 +24877,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24924,7 +24927,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24974,7 +24977,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25024,7 +25027,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25074,7 +25077,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25674,7 +25677,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25724,7 +25727,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25774,7 +25777,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25824,7 +25827,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25874,7 +25877,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25924,7 +25927,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25974,7 +25977,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26024,7 +26027,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26074,7 +26077,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26124,7 +26127,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26174,7 +26177,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26224,7 +26227,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26274,7 +26277,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26324,7 +26327,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26374,7 +26377,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26424,7 +26427,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26474,7 +26477,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26524,7 +26527,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26574,7 +26577,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26624,7 +26627,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26824,7 +26827,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26874,7 +26877,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26924,7 +26927,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26974,7 +26977,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27024,7 +27027,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27074,7 +27077,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27124,7 +27127,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -28074,7 +28077,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28124,7 +28127,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28174,7 +28177,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29474,7 +29477,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29524,7 +29527,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29574,7 +29577,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29624,7 +29627,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29674,7 +29677,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29724,7 +29727,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29774,7 +29777,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29824,7 +29827,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29874,7 +29877,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29924,7 +29927,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30224,7 +30227,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30274,7 +30277,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30324,7 +30327,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30374,7 +30377,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30424,7 +30427,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30474,7 +30477,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30524,7 +30527,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30574,7 +30577,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30624,7 +30627,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30674,7 +30677,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30724,7 +30727,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30924,7 +30927,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30974,7 +30977,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31024,7 +31027,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31074,7 +31077,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31124,7 +31127,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31174,7 +31177,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31224,7 +31227,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31274,7 +31277,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31324,7 +31327,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31624,7 +31627,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31674,7 +31677,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31724,7 +31727,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31774,7 +31777,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31824,7 +31827,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31874,7 +31877,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31924,7 +31927,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31974,7 +31977,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32024,7 +32027,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32074,7 +32077,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32124,7 +32127,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32174,7 +32177,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32774,7 +32777,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32824,7 +32827,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32874,7 +32877,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32924,7 +32927,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32974,7 +32977,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33024,7 +33027,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33074,7 +33077,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33124,7 +33127,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33174,7 +33177,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33224,7 +33227,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33424,7 +33427,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33474,7 +33477,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33524,7 +33527,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33574,7 +33577,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33624,7 +33627,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34524,7 +34527,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34574,7 +34577,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34624,7 +34627,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34674,7 +34677,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34724,7 +34727,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34774,7 +34777,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34824,7 +34827,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34874,7 +34877,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34924,7 +34927,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35574,7 +35577,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35624,7 +35627,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35674,7 +35677,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35724,7 +35727,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35774,7 +35777,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35824,7 +35827,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35874,7 +35877,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35924,7 +35927,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35974,7 +35977,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36374,7 +36377,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36424,7 +36427,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36474,7 +36477,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36524,7 +36527,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36574,7 +36577,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36624,7 +36627,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36674,7 +36677,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36724,7 +36727,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36774,7 +36777,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36824,7 +36827,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36874,7 +36877,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36924,7 +36927,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36974,7 +36977,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37274,7 +37277,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37324,7 +37327,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37374,7 +37377,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37424,7 +37427,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37724,7 +37727,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37774,7 +37777,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37824,7 +37827,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37874,7 +37877,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37924,7 +37927,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37974,7 +37977,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38024,7 +38027,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38074,7 +38077,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38124,7 +38127,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38174,7 +38177,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38424,7 +38427,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38474,7 +38477,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38524,7 +38527,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38574,7 +38577,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38624,7 +38627,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -39224,7 +39227,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39274,7 +39277,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39324,7 +39327,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39374,7 +39377,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39424,7 +39427,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39474,7 +39477,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39524,7 +39527,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39574,7 +39577,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39624,7 +39627,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39674,7 +39677,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40474,7 +40477,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40524,7 +40527,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40574,7 +40577,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40624,7 +40627,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40674,7 +40677,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40724,7 +40727,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40774,7 +40777,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -42474,7 +42477,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42524,7 +42527,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42574,7 +42577,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42624,7 +42627,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42674,7 +42677,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43224,7 +43227,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43274,7 +43277,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43324,7 +43327,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43374,7 +43377,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43424,7 +43427,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43474,7 +43477,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43624,7 +43627,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43674,7 +43677,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43724,7 +43727,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43774,7 +43777,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43824,7 +43827,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43874,7 +43877,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43924,7 +43927,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43974,7 +43977,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44024,7 +44027,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44074,7 +44077,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44124,7 +44127,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44174,7 +44177,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44224,7 +44227,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44274,7 +44277,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44324,7 +44327,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44374,7 +44377,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44424,7 +44427,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44474,7 +44477,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44524,7 +44527,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44574,7 +44577,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44874,7 +44877,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44924,7 +44927,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44974,7 +44977,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45024,7 +45027,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45074,7 +45077,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45124,7 +45127,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45174,7 +45177,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45224,7 +45227,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45274,7 +45277,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45324,7 +45327,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45374,7 +45377,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45424,7 +45427,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45474,7 +45477,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45524,7 +45527,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45574,7 +45577,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45624,7 +45627,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45674,7 +45677,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45724,7 +45727,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46024,7 +46027,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46074,7 +46077,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46124,7 +46127,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46174,7 +46177,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46224,7 +46227,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46474,7 +46477,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46524,7 +46527,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46574,7 +46577,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46624,7 +46627,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46874,7 +46877,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -46924,7 +46927,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -46974,7 +46977,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47024,7 +47027,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47074,7 +47077,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47124,7 +47127,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47174,7 +47177,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47224,7 +47227,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47274,7 +47277,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47324,7 +47327,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47374,7 +47377,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47724,7 +47727,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47774,7 +47777,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -47824,7 +47827,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -47874,7 +47877,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -47924,7 +47927,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -47974,7 +47977,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48024,7 +48027,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48074,7 +48077,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48124,7 +48127,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48174,7 +48177,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48224,7 +48227,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48274,7 +48277,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48324,7 +48327,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48374,7 +48377,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48424,7 +48427,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48974,7 +48977,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49024,7 +49027,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49074,7 +49077,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49124,7 +49127,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49324,7 +49327,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49374,7 +49377,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49424,7 +49427,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49474,7 +49477,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49524,7 +49527,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49574,7 +49577,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49624,7 +49627,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49674,7 +49677,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49724,7 +49727,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50724,7 +50727,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50774,7 +50777,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -50824,7 +50827,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -50874,7 +50877,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -50924,7 +50927,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -50974,7 +50977,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51024,7 +51027,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51074,7 +51077,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51124,7 +51127,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51174,7 +51177,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51224,7 +51227,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51274,7 +51277,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51324,7 +51327,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51374,7 +51377,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51424,7 +51427,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51474,7 +51477,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51524,7 +51527,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51574,7 +51577,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51624,7 +51627,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51674,7 +51677,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51724,7 +51727,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51774,7 +51777,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51824,7 +51827,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -51874,7 +51877,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -51924,7 +51927,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -51974,7 +51977,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -52024,7 +52027,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52074,7 +52077,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52124,7 +52127,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52174,7 +52177,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52224,7 +52227,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52274,7 +52277,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52324,7 +52327,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52474,7 +52477,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52524,7 +52527,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52724,7 +52727,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -52774,7 +52777,7 @@
         <v>1</v>
       </c>
       <c r="P1018" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1019" spans="1:16">
@@ -52824,7 +52827,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -52874,7 +52877,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -52924,7 +52927,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -52974,7 +52977,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -53024,7 +53027,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53074,7 +53077,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53124,7 +53127,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53174,7 +53177,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53224,7 +53227,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53274,7 +53277,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53324,7 +53327,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53374,7 +53377,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -55338,10 +55341,10 @@
         <v>0.2089373084402251</v>
       </c>
       <c r="D1070" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E1070">
-        <v>0.109568144725432</v>
+        <v>0.593211708392297</v>
       </c>
       <c r="F1070">
         <v>1</v>
@@ -55350,10 +55353,10 @@
         <v>0.01231106269155977</v>
       </c>
       <c r="H1070">
-        <v>0.01367043185527457</v>
+        <v>0.0135867882916077</v>
       </c>
       <c r="I1070">
-        <v>-0.0993691637147931</v>
+        <v>0.3842743999520719</v>
       </c>
       <c r="J1070">
         <v>1.350683636508878</v>
@@ -55365,10 +55368,10 @@
         <v>6.26</v>
       </c>
       <c r="M1070">
-        <v>5.02</v>
+        <v>4.81</v>
       </c>
       <c r="N1070">
-        <v>6.89</v>
+        <v>7.09</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55588,10 +55591,10 @@
         <v>0.2002740125469407</v>
       </c>
       <c r="D1075" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E1075">
-        <v>0.09986061227358256</v>
+        <v>0.5839102679354449</v>
       </c>
       <c r="F1075">
         <v>1</v>
@@ -55600,10 +55603,10 @@
         <v>0.01231972598745306</v>
       </c>
       <c r="H1075">
-        <v>0.01368013938772642</v>
+        <v>0.01359608973206456</v>
       </c>
       <c r="I1075">
-        <v>-0.1004134002733581</v>
+        <v>0.3836362553885042</v>
       </c>
       <c r="J1075">
         <v>1.352617407913629</v>
@@ -55615,10 +55618,10 @@
         <v>6.26</v>
       </c>
       <c r="M1075">
-        <v>5.02</v>
+        <v>4.81</v>
       </c>
       <c r="N1075">
-        <v>6.89</v>
+        <v>7.09</v>
       </c>
       <c r="O1075">
         <v>1</v>
@@ -55838,10 +55841,10 @@
         <v>0.1874605923544541</v>
       </c>
       <c r="D1080" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E1080">
-        <v>0.08550271732575165</v>
+        <v>0.5701530020591363</v>
       </c>
       <c r="F1080">
         <v>1</v>
@@ -55850,10 +55853,10 @@
         <v>0.01233253940764554</v>
       </c>
       <c r="H1080">
-        <v>0.01369449728267425</v>
+        <v>0.01360984699794086</v>
       </c>
       <c r="I1080">
-        <v>-0.1019578750287025</v>
+        <v>0.3826924097046822</v>
       </c>
       <c r="J1080">
         <v>1.355477546349452</v>
@@ -55865,10 +55868,10 @@
         <v>6.26</v>
       </c>
       <c r="M1080">
-        <v>5.02</v>
+        <v>4.81</v>
       </c>
       <c r="N1080">
-        <v>6.89</v>
+        <v>7.09</v>
       </c>
       <c r="O1080">
         <v>1</v>
@@ -55924,7 +55927,7 @@
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1082" spans="1:16">
@@ -55974,7 +55977,7 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -56024,7 +56027,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56074,7 +56077,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56088,10 +56091,10 @@
         <v>0.1834156227068702</v>
       </c>
       <c r="D1085" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E1085">
-        <v>0.08097018437243086</v>
+        <v>0.565810077058047</v>
       </c>
       <c r="F1085">
         <v>1</v>
@@ -56100,10 +56103,10 @@
         <v>0.01233658437729313</v>
       </c>
       <c r="H1085">
-        <v>0.01369902981562757</v>
+        <v>0.01361418992294195</v>
       </c>
       <c r="I1085">
-        <v>-0.1024454383344393</v>
+        <v>0.3823944543511768</v>
       </c>
       <c r="J1085">
         <v>1.356380441360074</v>
@@ -56115,16 +56118,16 @@
         <v>6.26</v>
       </c>
       <c r="M1085">
-        <v>5.02</v>
+        <v>4.81</v>
       </c>
       <c r="N1085">
-        <v>6.89</v>
+        <v>7.09</v>
       </c>
       <c r="O1085">
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
